--- a/data/RAT.MI.xlsx
+++ b/data/RAT.MI.xlsx
@@ -62886,6 +62886,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2719">
+      <c r="A2719" s="1" t="n">
+        <v>46279.2916666667</v>
+      </c>
+      <c r="B2719" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2719" t="n">
+        <v>1.05999994277954</v>
+      </c>
+      <c r="D2719" t="n">
+        <v>1.05999994277954</v>
+      </c>
+      <c r="E2719" t="n">
+        <v>1.05999994277954</v>
+      </c>
+      <c r="F2719" t="n">
+        <v>1.05999994277954</v>
+      </c>
+      <c r="G2719" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/RAT.MI.xlsx
+++ b/data/RAT.MI.xlsx
@@ -62909,6 +62909,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2720">
+      <c r="A2720" s="1" t="n">
+        <v>46280.2916666667</v>
+      </c>
+      <c r="B2720" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2720" t="n">
+        <v>1.05999994277954</v>
+      </c>
+      <c r="D2720" t="n">
+        <v>1.05999994277954</v>
+      </c>
+      <c r="E2720" t="n">
+        <v>1.05999994277954</v>
+      </c>
+      <c r="F2720" t="n">
+        <v>1.05999994277954</v>
+      </c>
+      <c r="G2720" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/RAT.MI.xlsx
+++ b/data/RAT.MI.xlsx
@@ -62932,6 +62932,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2721">
+      <c r="A2721" s="1" t="n">
+        <v>46281.2916666667</v>
+      </c>
+      <c r="B2721" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2721" t="n">
+        <v>1.05999994277954</v>
+      </c>
+      <c r="D2721" t="n">
+        <v>1.05999994277954</v>
+      </c>
+      <c r="E2721" t="n">
+        <v>1.05999994277954</v>
+      </c>
+      <c r="F2721" t="n">
+        <v>1.05999994277954</v>
+      </c>
+      <c r="G2721" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/RAT.MI.xlsx
+++ b/data/RAT.MI.xlsx
@@ -62796,19 +62796,19 @@
     </row>
     <row r="2715">
       <c r="A2715" s="1" t="n">
-        <v>46273.2916666667</v>
+        <v>46272.2916666667</v>
       </c>
       <c r="B2715" t="n">
-        <v>0</v>
+        <v>203447</v>
       </c>
       <c r="C2715" t="n">
         <v>1.08000004291534</v>
       </c>
       <c r="D2715" t="n">
-        <v>1.08000004291534</v>
+        <v>1.03999996185303</v>
       </c>
       <c r="E2715" t="n">
-        <v>1.08000004291534</v>
+        <v>1.04999995231628</v>
       </c>
       <c r="F2715" t="n">
         <v>1.08000004291534</v>
@@ -62819,22 +62819,22 @@
     </row>
     <row r="2716">
       <c r="A2716" s="1" t="n">
-        <v>46274.2916666667</v>
+        <v>46273.2916666667</v>
       </c>
       <c r="B2716" t="n">
-        <v>250</v>
+        <v>0</v>
       </c>
       <c r="C2716" t="n">
-        <v>1.07000005245209</v>
+        <v>1.08000004291534</v>
       </c>
       <c r="D2716" t="n">
-        <v>1.02999997138977</v>
+        <v>1.08000004291534</v>
       </c>
       <c r="E2716" t="n">
-        <v>1.02999997138977</v>
+        <v>1.08000004291534</v>
       </c>
       <c r="F2716" t="n">
-        <v>1.07000005245209</v>
+        <v>1.08000004291534</v>
       </c>
       <c r="G2716" t="s">
         <v>7</v>
@@ -62842,10 +62842,10 @@
     </row>
     <row r="2717">
       <c r="A2717" s="1" t="n">
-        <v>46275.2916666667</v>
+        <v>46274.2916666667</v>
       </c>
       <c r="B2717" t="n">
-        <v>391</v>
+        <v>250</v>
       </c>
       <c r="C2717" t="n">
         <v>1.07000005245209</v>
@@ -62865,22 +62865,22 @@
     </row>
     <row r="2718">
       <c r="A2718" s="1" t="n">
-        <v>46276.2916666667</v>
+        <v>46275.2916666667</v>
       </c>
       <c r="B2718" t="n">
-        <v>6773</v>
+        <v>391</v>
       </c>
       <c r="C2718" t="n">
         <v>1.07000005245209</v>
       </c>
       <c r="D2718" t="n">
-        <v>1.01999998092651</v>
+        <v>1.02999997138977</v>
       </c>
       <c r="E2718" t="n">
-        <v>1.04999995231628</v>
+        <v>1.02999997138977</v>
       </c>
       <c r="F2718" t="n">
-        <v>1.05999994277954</v>
+        <v>1.07000005245209</v>
       </c>
       <c r="G2718" t="s">
         <v>7</v>
@@ -62888,19 +62888,19 @@
     </row>
     <row r="2719">
       <c r="A2719" s="1" t="n">
-        <v>46279.2916666667</v>
+        <v>46276.2916666667</v>
       </c>
       <c r="B2719" t="n">
-        <v>0</v>
+        <v>6773</v>
       </c>
       <c r="C2719" t="n">
-        <v>1.05999994277954</v>
+        <v>1.07000005245209</v>
       </c>
       <c r="D2719" t="n">
-        <v>1.05999994277954</v>
+        <v>1.01999998092651</v>
       </c>
       <c r="E2719" t="n">
-        <v>1.05999994277954</v>
+        <v>1.04999995231628</v>
       </c>
       <c r="F2719" t="n">
         <v>1.05999994277954</v>
@@ -62911,7 +62911,7 @@
     </row>
     <row r="2720">
       <c r="A2720" s="1" t="n">
-        <v>46280.2916666667</v>
+        <v>46279.2916666667</v>
       </c>
       <c r="B2720" t="n">
         <v>0</v>
@@ -62934,7 +62934,7 @@
     </row>
     <row r="2721">
       <c r="A2721" s="1" t="n">
-        <v>46281.2916666667</v>
+        <v>46280.2916666667</v>
       </c>
       <c r="B2721" t="n">
         <v>0</v>
@@ -62952,6 +62952,29 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G2721" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2722">
+      <c r="A2722" s="1" t="n">
+        <v>46281.2916666667</v>
+      </c>
+      <c r="B2722" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2722" t="n">
+        <v>1.05999994277954</v>
+      </c>
+      <c r="D2722" t="n">
+        <v>1.05999994277954</v>
+      </c>
+      <c r="E2722" t="n">
+        <v>1.05999994277954</v>
+      </c>
+      <c r="F2722" t="n">
+        <v>1.05999994277954</v>
+      </c>
+      <c r="G2722" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/RAT.MI.xlsx
+++ b/data/RAT.MI.xlsx
@@ -62978,6 +62978,52 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2723">
+      <c r="A2723" s="1" t="n">
+        <v>46282.2916666667</v>
+      </c>
+      <c r="B2723" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2723" t="n">
+        <v>1.05999994277954</v>
+      </c>
+      <c r="D2723" t="n">
+        <v>1.05999994277954</v>
+      </c>
+      <c r="E2723" t="n">
+        <v>1.05999994277954</v>
+      </c>
+      <c r="F2723" t="n">
+        <v>1.05999994277954</v>
+      </c>
+      <c r="G2723" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2724">
+      <c r="A2724" s="1" t="n">
+        <v>46283.2916666667</v>
+      </c>
+      <c r="B2724" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2724" t="n">
+        <v>1.05999994277954</v>
+      </c>
+      <c r="D2724" t="n">
+        <v>1.05999994277954</v>
+      </c>
+      <c r="E2724" t="n">
+        <v>1.05999994277954</v>
+      </c>
+      <c r="F2724" t="n">
+        <v>1.05999994277954</v>
+      </c>
+      <c r="G2724" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/RAT.MI.xlsx
+++ b/data/RAT.MI.xlsx
@@ -63024,6 +63024,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2725">
+      <c r="A2725" s="1" t="n">
+        <v>46286.2916666667</v>
+      </c>
+      <c r="B2725" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2725" t="n">
+        <v>1.05999994277954</v>
+      </c>
+      <c r="D2725" t="n">
+        <v>1.05999994277954</v>
+      </c>
+      <c r="E2725" t="n">
+        <v>1.05999994277954</v>
+      </c>
+      <c r="F2725" t="n">
+        <v>1.05999994277954</v>
+      </c>
+      <c r="G2725" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/RAT.MI.xlsx
+++ b/data/RAT.MI.xlsx
@@ -421,7 +421,7 @@
         <v>2.3659999370575</v>
       </c>
       <c r="G2" t="n">
-        <v>1.85825955867767</v>
+        <v>1.8582592010498</v>
       </c>
       <c r="H2" t="s">
         <v>8</v>
@@ -447,7 +447,7 @@
         <v>2.43600010871887</v>
       </c>
       <c r="G3" t="n">
-        <v>1.9132376909256</v>
+        <v>1.91323781013489</v>
       </c>
       <c r="H3" t="s">
         <v>8</v>
@@ -473,7 +473,7 @@
         <v>2.44600009918213</v>
       </c>
       <c r="G4" t="n">
-        <v>1.92109167575836</v>
+        <v>1.92109143733978</v>
       </c>
       <c r="H4" t="s">
         <v>8</v>
@@ -499,7 +499,7 @@
         <v>2.44600009918213</v>
       </c>
       <c r="G5" t="n">
-        <v>1.92109167575836</v>
+        <v>1.92109143733978</v>
       </c>
       <c r="H5" t="s">
         <v>8</v>
@@ -525,7 +525,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G6" t="n">
-        <v>1.88496327400208</v>
+        <v>1.8849630355835</v>
       </c>
       <c r="H6" t="s">
         <v>8</v>
@@ -551,7 +551,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G7" t="n">
-        <v>1.88496327400208</v>
+        <v>1.8849630355835</v>
       </c>
       <c r="H7" t="s">
         <v>8</v>
@@ -577,7 +577,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G8" t="n">
-        <v>1.92423319816589</v>
+        <v>1.9242330789566</v>
       </c>
       <c r="H8" t="s">
         <v>8</v>
@@ -603,7 +603,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G9" t="n">
-        <v>1.88496327400208</v>
+        <v>1.8849630355835</v>
       </c>
       <c r="H9" t="s">
         <v>8</v>
@@ -629,7 +629,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G10" t="n">
-        <v>1.88496327400208</v>
+        <v>1.8849630355835</v>
       </c>
       <c r="H10" t="s">
         <v>8</v>
@@ -655,7 +655,7 @@
         <v>2.3659999370575</v>
       </c>
       <c r="G11" t="n">
-        <v>1.85825955867767</v>
+        <v>1.8582592010498</v>
       </c>
       <c r="H11" t="s">
         <v>8</v>
@@ -759,7 +759,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G15" t="n">
-        <v>1.79856884479523</v>
+        <v>1.79856872558594</v>
       </c>
       <c r="H15" t="s">
         <v>8</v>
@@ -785,7 +785,7 @@
         <v>2.25</v>
       </c>
       <c r="G16" t="n">
-        <v>1.76715290546417</v>
+        <v>1.76715302467346</v>
       </c>
       <c r="H16" t="s">
         <v>8</v>
@@ -811,7 +811,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G17" t="n">
-        <v>1.85354697704315</v>
+        <v>1.85354685783386</v>
       </c>
       <c r="H17" t="s">
         <v>8</v>
@@ -837,7 +837,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G18" t="n">
-        <v>1.85354697704315</v>
+        <v>1.85354685783386</v>
       </c>
       <c r="H18" t="s">
         <v>8</v>
@@ -863,7 +863,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G19" t="n">
-        <v>1.86925506591797</v>
+        <v>1.86925542354584</v>
       </c>
       <c r="H19" t="s">
         <v>8</v>
@@ -889,7 +889,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G20" t="n">
-        <v>1.87710916996002</v>
+        <v>1.87710905075073</v>
       </c>
       <c r="H20" t="s">
         <v>8</v>
@@ -915,7 +915,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G21" t="n">
-        <v>1.89281690120697</v>
+        <v>1.89281725883484</v>
       </c>
       <c r="H21" t="s">
         <v>8</v>
@@ -967,7 +967,7 @@
         <v>2.31200003623962</v>
       </c>
       <c r="G23" t="n">
-        <v>1.81584787368774</v>
+        <v>1.81584811210632</v>
       </c>
       <c r="H23" t="s">
         <v>8</v>
@@ -1045,7 +1045,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G26" t="n">
-        <v>1.88496327400208</v>
+        <v>1.8849630355835</v>
       </c>
       <c r="H26" t="s">
         <v>8</v>
@@ -1123,7 +1123,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G29" t="n">
-        <v>1.88496327400208</v>
+        <v>1.8849630355835</v>
       </c>
       <c r="H29" t="s">
         <v>8</v>
@@ -1175,7 +1175,7 @@
         <v>2.32599997520447</v>
       </c>
       <c r="G31" t="n">
-        <v>1.82684350013733</v>
+        <v>1.82684326171875</v>
       </c>
       <c r="H31" t="s">
         <v>8</v>
@@ -1201,7 +1201,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G32" t="n">
-        <v>1.8456928730011</v>
+        <v>1.84569299221039</v>
       </c>
       <c r="H32" t="s">
         <v>8</v>
@@ -1227,7 +1227,7 @@
         <v>2.31599998474121</v>
       </c>
       <c r="G33" t="n">
-        <v>1.81898927688599</v>
+        <v>1.81898939609528</v>
       </c>
       <c r="H33" t="s">
         <v>8</v>
@@ -1253,7 +1253,7 @@
         <v>2.33800005912781</v>
       </c>
       <c r="G34" t="n">
-        <v>1.83626818656921</v>
+        <v>1.8362683057785</v>
       </c>
       <c r="H34" t="s">
         <v>8</v>
@@ -1357,7 +1357,7 @@
         <v>2.29800009727478</v>
       </c>
       <c r="G38" t="n">
-        <v>1.80485224723816</v>
+        <v>1.80485200881958</v>
       </c>
       <c r="H38" t="s">
         <v>8</v>
@@ -1409,7 +1409,7 @@
         <v>2.31399989128113</v>
       </c>
       <c r="G40" t="n">
-        <v>1.81741869449615</v>
+        <v>1.81741845607758</v>
       </c>
       <c r="H40" t="s">
         <v>8</v>
@@ -1435,7 +1435,7 @@
         <v>2.31399989128113</v>
       </c>
       <c r="G41" t="n">
-        <v>1.81741869449615</v>
+        <v>1.81741845607758</v>
       </c>
       <c r="H41" t="s">
         <v>8</v>
@@ -1461,7 +1461,7 @@
         <v>2.31399989128113</v>
       </c>
       <c r="G42" t="n">
-        <v>1.81741869449615</v>
+        <v>1.81741845607758</v>
       </c>
       <c r="H42" t="s">
         <v>8</v>
@@ -1487,7 +1487,7 @@
         <v>2.33800005912781</v>
       </c>
       <c r="G43" t="n">
-        <v>1.83626818656921</v>
+        <v>1.8362683057785</v>
       </c>
       <c r="H43" t="s">
         <v>8</v>
@@ -1565,7 +1565,7 @@
         <v>2.35599994659424</v>
       </c>
       <c r="G46" t="n">
-        <v>1.85040545463562</v>
+        <v>1.85040557384491</v>
       </c>
       <c r="H46" t="s">
         <v>8</v>
@@ -1591,7 +1591,7 @@
         <v>2.39400005340576</v>
       </c>
       <c r="G47" t="n">
-        <v>1.88025081157684</v>
+        <v>1.88025057315826</v>
       </c>
       <c r="H47" t="s">
         <v>8</v>
@@ -1617,7 +1617,7 @@
         <v>2.39400005340576</v>
       </c>
       <c r="G48" t="n">
-        <v>1.88025081157684</v>
+        <v>1.88025057315826</v>
       </c>
       <c r="H48" t="s">
         <v>8</v>
@@ -1643,7 +1643,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G49" t="n">
-        <v>1.81427693367004</v>
+        <v>1.81427681446075</v>
       </c>
       <c r="H49" t="s">
         <v>8</v>
@@ -1669,7 +1669,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G50" t="n">
-        <v>1.8456928730011</v>
+        <v>1.84569299221039</v>
       </c>
       <c r="H50" t="s">
         <v>8</v>
@@ -1695,7 +1695,7 @@
         <v>2.33800005912781</v>
       </c>
       <c r="G51" t="n">
-        <v>1.83626818656921</v>
+        <v>1.8362683057785</v>
       </c>
       <c r="H51" t="s">
         <v>8</v>
@@ -1721,7 +1721,7 @@
         <v>2.35800004005432</v>
       </c>
       <c r="G52" t="n">
-        <v>1.85197603702545</v>
+        <v>1.85197627544403</v>
       </c>
       <c r="H52" t="s">
         <v>8</v>
@@ -1747,7 +1747,7 @@
         <v>2.34800004959106</v>
       </c>
       <c r="G53" t="n">
-        <v>1.84412217140198</v>
+        <v>1.84412240982056</v>
       </c>
       <c r="H53" t="s">
         <v>8</v>
@@ -1799,7 +1799,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G55" t="n">
-        <v>1.8456928730011</v>
+        <v>1.84569299221039</v>
       </c>
       <c r="H55" t="s">
         <v>8</v>
@@ -1825,7 +1825,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G56" t="n">
-        <v>1.8456928730011</v>
+        <v>1.84569299221039</v>
       </c>
       <c r="H56" t="s">
         <v>8</v>
@@ -1851,7 +1851,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G57" t="n">
-        <v>1.85354697704315</v>
+        <v>1.85354685783386</v>
       </c>
       <c r="H57" t="s">
         <v>8</v>
@@ -1877,7 +1877,7 @@
         <v>2.32200002670288</v>
       </c>
       <c r="G58" t="n">
-        <v>1.82370185852051</v>
+        <v>1.82370162010193</v>
       </c>
       <c r="H58" t="s">
         <v>8</v>
@@ -1903,7 +1903,7 @@
         <v>2.32200002670288</v>
       </c>
       <c r="G59" t="n">
-        <v>1.82370185852051</v>
+        <v>1.82370162010193</v>
       </c>
       <c r="H59" t="s">
         <v>8</v>
@@ -1929,7 +1929,7 @@
         <v>2.30599999427795</v>
       </c>
       <c r="G60" t="n">
-        <v>1.81113541126251</v>
+        <v>1.81113529205322</v>
       </c>
       <c r="H60" t="s">
         <v>8</v>
@@ -1955,7 +1955,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G61" t="n">
-        <v>1.81427693367004</v>
+        <v>1.81427681446075</v>
       </c>
       <c r="H61" t="s">
         <v>8</v>
@@ -2007,7 +2007,7 @@
         <v>2.35599994659424</v>
       </c>
       <c r="G63" t="n">
-        <v>1.85040545463562</v>
+        <v>1.85040557384491</v>
       </c>
       <c r="H63" t="s">
         <v>8</v>
@@ -2033,7 +2033,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G64" t="n">
-        <v>1.8456928730011</v>
+        <v>1.84569299221039</v>
       </c>
       <c r="H64" t="s">
         <v>8</v>
@@ -2059,7 +2059,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G65" t="n">
-        <v>1.92423319816589</v>
+        <v>1.9242330789566</v>
       </c>
       <c r="H65" t="s">
         <v>8</v>
@@ -2085,7 +2085,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G66" t="n">
-        <v>1.92423319816589</v>
+        <v>1.9242330789566</v>
       </c>
       <c r="H66" t="s">
         <v>8</v>
@@ -2111,7 +2111,7 @@
         <v>2.46600008010864</v>
       </c>
       <c r="G67" t="n">
-        <v>1.93679976463318</v>
+        <v>1.93679964542389</v>
       </c>
       <c r="H67" t="s">
         <v>8</v>
@@ -2137,7 +2137,7 @@
         <v>2.4779999256134</v>
       </c>
       <c r="G68" t="n">
-        <v>1.94622421264648</v>
+        <v>1.94622457027435</v>
       </c>
       <c r="H68" t="s">
         <v>8</v>
@@ -2163,7 +2163,7 @@
         <v>2.48799991607666</v>
       </c>
       <c r="G69" t="n">
-        <v>1.95407831668854</v>
+        <v>1.95407819747925</v>
       </c>
       <c r="H69" t="s">
         <v>8</v>
@@ -2189,7 +2189,7 @@
         <v>2.5</v>
       </c>
       <c r="G70" t="n">
-        <v>1.96350347995758</v>
+        <v>1.96350336074829</v>
       </c>
       <c r="H70" t="s">
         <v>8</v>
@@ -2215,7 +2215,7 @@
         <v>2.50200009346008</v>
       </c>
       <c r="G71" t="n">
-        <v>1.96507406234741</v>
+        <v>1.9650741815567</v>
       </c>
       <c r="H71" t="s">
         <v>8</v>
@@ -2241,7 +2241,7 @@
         <v>2.53800010681152</v>
       </c>
       <c r="G72" t="n">
-        <v>1.99334859848022</v>
+        <v>1.99334836006165</v>
       </c>
       <c r="H72" t="s">
         <v>8</v>
@@ -2293,7 +2293,7 @@
         <v>2.5</v>
       </c>
       <c r="G74" t="n">
-        <v>1.96350347995758</v>
+        <v>1.96350336074829</v>
       </c>
       <c r="H74" t="s">
         <v>8</v>
@@ -2345,7 +2345,7 @@
         <v>2.50200009346008</v>
       </c>
       <c r="G76" t="n">
-        <v>1.96507406234741</v>
+        <v>1.9650741815567</v>
       </c>
       <c r="H76" t="s">
         <v>8</v>
@@ -2397,7 +2397,7 @@
         <v>2.57800006866455</v>
       </c>
       <c r="G78" t="n">
-        <v>2.02476453781128</v>
+        <v>2.0247642993927</v>
       </c>
       <c r="H78" t="s">
         <v>8</v>
@@ -2423,7 +2423,7 @@
         <v>2.45799994468689</v>
       </c>
       <c r="G79" t="n">
-        <v>1.93051624298096</v>
+        <v>1.93051612377167</v>
       </c>
       <c r="H79" t="s">
         <v>8</v>
@@ -2449,7 +2449,7 @@
         <v>2.45799994468689</v>
       </c>
       <c r="G80" t="n">
-        <v>1.93051624298096</v>
+        <v>1.93051612377167</v>
       </c>
       <c r="H80" t="s">
         <v>8</v>
@@ -2475,7 +2475,7 @@
         <v>2.5</v>
       </c>
       <c r="G81" t="n">
-        <v>1.96350347995758</v>
+        <v>1.96350336074829</v>
       </c>
       <c r="H81" t="s">
         <v>8</v>
@@ -2553,7 +2553,7 @@
         <v>2.48799991607666</v>
       </c>
       <c r="G84" t="n">
-        <v>1.95407831668854</v>
+        <v>1.95407819747925</v>
       </c>
       <c r="H84" t="s">
         <v>8</v>
@@ -2657,7 +2657,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G88" t="n">
-        <v>1.91637921333313</v>
+        <v>1.91637933254242</v>
       </c>
       <c r="H88" t="s">
         <v>8</v>
@@ -2683,7 +2683,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G89" t="n">
-        <v>1.88496327400208</v>
+        <v>1.8849630355835</v>
       </c>
       <c r="H89" t="s">
         <v>8</v>
@@ -2709,7 +2709,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G90" t="n">
-        <v>1.91637921333313</v>
+        <v>1.91637933254242</v>
       </c>
       <c r="H90" t="s">
         <v>8</v>
@@ -2735,7 +2735,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G91" t="n">
-        <v>1.91637921333313</v>
+        <v>1.91637933254242</v>
       </c>
       <c r="H91" t="s">
         <v>8</v>
@@ -2761,7 +2761,7 @@
         <v>2.39400005340576</v>
       </c>
       <c r="G92" t="n">
-        <v>1.88025081157684</v>
+        <v>1.88025057315826</v>
       </c>
       <c r="H92" t="s">
         <v>8</v>
@@ -2787,7 +2787,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G93" t="n">
-        <v>1.87710916996002</v>
+        <v>1.87710905075073</v>
       </c>
       <c r="H93" t="s">
         <v>8</v>
@@ -2813,7 +2813,7 @@
         <v>2.38599991798401</v>
       </c>
       <c r="G94" t="n">
-        <v>1.87396728992462</v>
+        <v>1.87396740913391</v>
       </c>
       <c r="H94" t="s">
         <v>8</v>
@@ -2839,7 +2839,7 @@
         <v>2.38599991798401</v>
       </c>
       <c r="G95" t="n">
-        <v>1.87396728992462</v>
+        <v>1.87396740913391</v>
       </c>
       <c r="H95" t="s">
         <v>8</v>
@@ -2865,7 +2865,7 @@
         <v>2.29800009727478</v>
       </c>
       <c r="G96" t="n">
-        <v>1.80485224723816</v>
+        <v>1.80485200881958</v>
       </c>
       <c r="H96" t="s">
         <v>8</v>
@@ -2891,7 +2891,7 @@
         <v>2.29800009727478</v>
       </c>
       <c r="G97" t="n">
-        <v>1.80485224723816</v>
+        <v>1.80485200881958</v>
       </c>
       <c r="H97" t="s">
         <v>8</v>
@@ -2917,7 +2917,7 @@
         <v>2.34800004959106</v>
       </c>
       <c r="G98" t="n">
-        <v>1.84412217140198</v>
+        <v>1.84412240982056</v>
       </c>
       <c r="H98" t="s">
         <v>8</v>
@@ -2943,7 +2943,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G99" t="n">
-        <v>1.89281690120697</v>
+        <v>1.89281725883484</v>
       </c>
       <c r="H99" t="s">
         <v>8</v>
@@ -2969,7 +2969,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G100" t="n">
-        <v>1.93378698825836</v>
+        <v>1.93378710746765</v>
       </c>
       <c r="H100" t="s">
         <v>8</v>
@@ -2995,7 +2995,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G101" t="n">
-        <v>1.95017516613007</v>
+        <v>1.95017564296722</v>
       </c>
       <c r="H101" t="s">
         <v>8</v>
@@ -3047,7 +3047,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G103" t="n">
-        <v>1.93378698825836</v>
+        <v>1.93378710746765</v>
       </c>
       <c r="H103" t="s">
         <v>8</v>
@@ -3099,7 +3099,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G105" t="n">
-        <v>1.96656334400177</v>
+        <v>1.96656322479248</v>
       </c>
       <c r="H105" t="s">
         <v>8</v>
@@ -3125,7 +3125,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G106" t="n">
-        <v>1.96656334400177</v>
+        <v>1.96656322479248</v>
       </c>
       <c r="H106" t="s">
         <v>8</v>
@@ -3151,7 +3151,7 @@
         <v>2.38599991798401</v>
       </c>
       <c r="G107" t="n">
-        <v>1.95509135723114</v>
+        <v>1.95509171485901</v>
       </c>
       <c r="H107" t="s">
         <v>8</v>
@@ -3229,7 +3229,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G110" t="n">
-        <v>1.95017516613007</v>
+        <v>1.95017564296722</v>
       </c>
       <c r="H110" t="s">
         <v>8</v>
@@ -3255,7 +3255,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G111" t="n">
-        <v>1.95017516613007</v>
+        <v>1.95017564296722</v>
       </c>
       <c r="H111" t="s">
         <v>8</v>
@@ -3281,7 +3281,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G112" t="n">
-        <v>1.91739904880524</v>
+        <v>1.91739916801453</v>
       </c>
       <c r="H112" t="s">
         <v>8</v>
@@ -3307,7 +3307,7 @@
         <v>2.36199998855591</v>
       </c>
       <c r="G113" t="n">
-        <v>1.93542587757111</v>
+        <v>1.9354259967804</v>
       </c>
       <c r="H113" t="s">
         <v>8</v>
@@ -3333,7 +3333,7 @@
         <v>2.36199998855591</v>
       </c>
       <c r="G114" t="n">
-        <v>1.93542587757111</v>
+        <v>1.9354259967804</v>
       </c>
       <c r="H114" t="s">
         <v>8</v>
@@ -3359,7 +3359,7 @@
         <v>2.36199998855591</v>
       </c>
       <c r="G115" t="n">
-        <v>1.93542587757111</v>
+        <v>1.9354259967804</v>
       </c>
       <c r="H115" t="s">
         <v>8</v>
@@ -3385,7 +3385,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G116" t="n">
-        <v>1.94198131561279</v>
+        <v>1.94198095798492</v>
       </c>
       <c r="H116" t="s">
         <v>8</v>
@@ -3411,7 +3411,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G117" t="n">
-        <v>1.94198131561279</v>
+        <v>1.94198095798492</v>
       </c>
       <c r="H117" t="s">
         <v>8</v>
@@ -3437,7 +3437,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G118" t="n">
-        <v>1.91739904880524</v>
+        <v>1.91739916801453</v>
       </c>
       <c r="H118" t="s">
         <v>8</v>
@@ -3463,7 +3463,7 @@
         <v>2.33400011062622</v>
       </c>
       <c r="G119" t="n">
-        <v>1.91248261928558</v>
+        <v>1.91248285770416</v>
       </c>
       <c r="H119" t="s">
         <v>8</v>
@@ -3489,7 +3489,7 @@
         <v>2.33200001716614</v>
       </c>
       <c r="G120" t="n">
-        <v>1.91084384918213</v>
+        <v>1.91084420681</v>
       </c>
       <c r="H120" t="s">
         <v>8</v>
@@ -3515,7 +3515,7 @@
         <v>2.33200001716614</v>
       </c>
       <c r="G121" t="n">
-        <v>1.91084384918213</v>
+        <v>1.91084420681</v>
       </c>
       <c r="H121" t="s">
         <v>8</v>
@@ -3541,7 +3541,7 @@
         <v>2.33400011062622</v>
       </c>
       <c r="G122" t="n">
-        <v>1.91248261928558</v>
+        <v>1.91248285770416</v>
       </c>
       <c r="H122" t="s">
         <v>8</v>
@@ -3567,7 +3567,7 @@
         <v>2.33400011062622</v>
       </c>
       <c r="G123" t="n">
-        <v>1.91248261928558</v>
+        <v>1.91248285770416</v>
       </c>
       <c r="H123" t="s">
         <v>8</v>
@@ -3593,7 +3593,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G124" t="n">
-        <v>1.83545911312103</v>
+        <v>1.83545899391174</v>
       </c>
       <c r="H124" t="s">
         <v>8</v>
@@ -3671,7 +3671,7 @@
         <v>2.23600006103516</v>
       </c>
       <c r="G127" t="n">
-        <v>1.83218133449554</v>
+        <v>1.83218145370483</v>
       </c>
       <c r="H127" t="s">
         <v>8</v>
@@ -3723,7 +3723,7 @@
         <v>2.29800009727478</v>
       </c>
       <c r="G129" t="n">
-        <v>1.88298439979553</v>
+        <v>1.88298416137695</v>
       </c>
       <c r="H129" t="s">
         <v>8</v>
@@ -3749,7 +3749,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G130" t="n">
-        <v>1.86823511123657</v>
+        <v>1.86823523044586</v>
       </c>
       <c r="H130" t="s">
         <v>8</v>
@@ -3775,7 +3775,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G131" t="n">
-        <v>1.94198131561279</v>
+        <v>1.94198095798492</v>
       </c>
       <c r="H131" t="s">
         <v>8</v>
@@ -3801,7 +3801,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G132" t="n">
-        <v>1.94198131561279</v>
+        <v>1.94198095798492</v>
       </c>
       <c r="H132" t="s">
         <v>8</v>
@@ -3827,7 +3827,7 @@
         <v>2.32800006866455</v>
       </c>
       <c r="G133" t="n">
-        <v>1.90756618976593</v>
+        <v>1.90756630897522</v>
       </c>
       <c r="H133" t="s">
         <v>8</v>
@@ -3853,7 +3853,7 @@
         <v>2.32800006866455</v>
       </c>
       <c r="G134" t="n">
-        <v>1.90756618976593</v>
+        <v>1.90756630897522</v>
       </c>
       <c r="H134" t="s">
         <v>8</v>
@@ -3879,7 +3879,7 @@
         <v>2.32800006866455</v>
       </c>
       <c r="G135" t="n">
-        <v>1.90756618976593</v>
+        <v>1.90756630897522</v>
       </c>
       <c r="H135" t="s">
         <v>8</v>
@@ -3931,7 +3931,7 @@
         <v>2.32599997520447</v>
       </c>
       <c r="G137" t="n">
-        <v>1.90592765808105</v>
+        <v>1.90592741966248</v>
       </c>
       <c r="H137" t="s">
         <v>8</v>
@@ -3957,7 +3957,7 @@
         <v>2.32599997520447</v>
       </c>
       <c r="G138" t="n">
-        <v>1.90592765808105</v>
+        <v>1.90592741966248</v>
       </c>
       <c r="H138" t="s">
         <v>8</v>
@@ -3983,7 +3983,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G139" t="n">
-        <v>1.88462328910828</v>
+        <v>1.88462316989899</v>
       </c>
       <c r="H139" t="s">
         <v>8</v>
@@ -4009,7 +4009,7 @@
         <v>2.32599997520447</v>
       </c>
       <c r="G140" t="n">
-        <v>1.90592765808105</v>
+        <v>1.90592741966248</v>
       </c>
       <c r="H140" t="s">
         <v>8</v>
@@ -4035,7 +4035,7 @@
         <v>2.32599997520447</v>
       </c>
       <c r="G141" t="n">
-        <v>1.90592765808105</v>
+        <v>1.90592741966248</v>
       </c>
       <c r="H141" t="s">
         <v>8</v>
@@ -4061,7 +4061,7 @@
         <v>2.32800006866455</v>
       </c>
       <c r="G142" t="n">
-        <v>1.90756618976593</v>
+        <v>1.90756630897522</v>
       </c>
       <c r="H142" t="s">
         <v>8</v>
@@ -4165,7 +4165,7 @@
         <v>2.31599998474121</v>
       </c>
       <c r="G146" t="n">
-        <v>1.89773344993591</v>
+        <v>1.8977335691452</v>
       </c>
       <c r="H146" t="s">
         <v>8</v>
@@ -4191,7 +4191,7 @@
         <v>2.32599997520447</v>
       </c>
       <c r="G147" t="n">
-        <v>1.90592765808105</v>
+        <v>1.90592741966248</v>
       </c>
       <c r="H147" t="s">
         <v>8</v>
@@ -4243,7 +4243,7 @@
         <v>2.2260000705719</v>
       </c>
       <c r="G149" t="n">
-        <v>1.82398760318756</v>
+        <v>1.82398748397827</v>
       </c>
       <c r="H149" t="s">
         <v>8</v>
@@ -4295,7 +4295,7 @@
         <v>2.15599989891052</v>
       </c>
       <c r="G151" t="n">
-        <v>1.76662933826447</v>
+        <v>1.76662921905518</v>
       </c>
       <c r="H151" t="s">
         <v>8</v>
@@ -4321,7 +4321,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G152" t="n">
-        <v>1.78629505634308</v>
+        <v>1.7862948179245</v>
       </c>
       <c r="H152" t="s">
         <v>8</v>
@@ -4347,7 +4347,7 @@
         <v>2.16799998283386</v>
       </c>
       <c r="G153" t="n">
-        <v>1.77646219730377</v>
+        <v>1.77646195888519</v>
       </c>
       <c r="H153" t="s">
         <v>8</v>
@@ -4373,7 +4373,7 @@
         <v>2.13800001144409</v>
       </c>
       <c r="G154" t="n">
-        <v>1.75188016891479</v>
+        <v>1.75188004970551</v>
       </c>
       <c r="H154" t="s">
         <v>8</v>
@@ -4399,7 +4399,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G155" t="n">
-        <v>1.75351881980896</v>
+        <v>1.75351893901825</v>
       </c>
       <c r="H155" t="s">
         <v>8</v>
@@ -4425,7 +4425,7 @@
         <v>2.17199993133545</v>
       </c>
       <c r="G156" t="n">
-        <v>1.77973961830139</v>
+        <v>1.77973973751068</v>
       </c>
       <c r="H156" t="s">
         <v>8</v>
@@ -4451,7 +4451,7 @@
         <v>2.17199993133545</v>
       </c>
       <c r="G157" t="n">
-        <v>1.77973961830139</v>
+        <v>1.77973973751068</v>
       </c>
       <c r="H157" t="s">
         <v>8</v>
@@ -4477,7 +4477,7 @@
         <v>2.13599991798401</v>
       </c>
       <c r="G158" t="n">
-        <v>1.75024127960205</v>
+        <v>1.75024116039276</v>
       </c>
       <c r="H158" t="s">
         <v>8</v>
@@ -4503,7 +4503,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G159" t="n">
-        <v>1.72074282169342</v>
+        <v>1.72074270248413</v>
       </c>
       <c r="H159" t="s">
         <v>8</v>
@@ -4789,7 +4789,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G170" t="n">
-        <v>1.7043548822403</v>
+        <v>1.70435476303101</v>
       </c>
       <c r="H170" t="s">
         <v>8</v>
@@ -4815,7 +4815,7 @@
         <v>2.11800003051758</v>
       </c>
       <c r="G171" t="n">
-        <v>1.73549222946167</v>
+        <v>1.73549211025238</v>
       </c>
       <c r="H171" t="s">
         <v>8</v>
@@ -4919,7 +4919,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G175" t="n">
-        <v>1.63060867786407</v>
+        <v>1.63060879707336</v>
       </c>
       <c r="H175" t="s">
         <v>8</v>
@@ -4945,7 +4945,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G176" t="n">
-        <v>1.67157864570618</v>
+        <v>1.67157876491547</v>
       </c>
       <c r="H176" t="s">
         <v>8</v>
@@ -5101,7 +5101,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G182" t="n">
-        <v>1.67157864570618</v>
+        <v>1.67157876491547</v>
       </c>
       <c r="H182" t="s">
         <v>8</v>
@@ -5127,7 +5127,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G183" t="n">
-        <v>1.67157864570618</v>
+        <v>1.67157876491547</v>
       </c>
       <c r="H183" t="s">
         <v>8</v>
@@ -5153,7 +5153,7 @@
         <v>2.04200005531311</v>
       </c>
       <c r="G184" t="n">
-        <v>1.67321753501892</v>
+        <v>1.67321765422821</v>
       </c>
       <c r="H184" t="s">
         <v>8</v>
@@ -5179,7 +5179,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G185" t="n">
-        <v>1.67157864570618</v>
+        <v>1.67157876491547</v>
       </c>
       <c r="H185" t="s">
         <v>8</v>
@@ -5309,7 +5309,7 @@
         <v>2</v>
       </c>
       <c r="G190" t="n">
-        <v>1.63880264759064</v>
+        <v>1.63880276679993</v>
       </c>
       <c r="H190" t="s">
         <v>8</v>
@@ -5621,7 +5621,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G202" t="n">
-        <v>1.64699685573578</v>
+        <v>1.6469966173172</v>
       </c>
       <c r="H202" t="s">
         <v>8</v>
@@ -5647,7 +5647,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G203" t="n">
-        <v>1.64699685573578</v>
+        <v>1.6469966173172</v>
       </c>
       <c r="H203" t="s">
         <v>8</v>
@@ -5673,7 +5673,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G204" t="n">
-        <v>1.64699685573578</v>
+        <v>1.6469966173172</v>
       </c>
       <c r="H204" t="s">
         <v>8</v>
@@ -5699,7 +5699,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G205" t="n">
-        <v>1.64699685573578</v>
+        <v>1.6469966173172</v>
       </c>
       <c r="H205" t="s">
         <v>8</v>
@@ -5725,7 +5725,7 @@
         <v>1.99899995326996</v>
       </c>
       <c r="G206" t="n">
-        <v>1.63798320293427</v>
+        <v>1.63798308372498</v>
       </c>
       <c r="H206" t="s">
         <v>8</v>
@@ -5751,7 +5751,7 @@
         <v>1.95099997520447</v>
       </c>
       <c r="G207" t="n">
-        <v>1.59865212440491</v>
+        <v>1.59865200519562</v>
       </c>
       <c r="H207" t="s">
         <v>8</v>
@@ -5777,7 +5777,7 @@
         <v>1.9889999628067</v>
       </c>
       <c r="G208" t="n">
-        <v>1.6297892332077</v>
+        <v>1.62978911399841</v>
       </c>
       <c r="H208" t="s">
         <v>8</v>
@@ -5829,7 +5829,7 @@
         <v>1.94700002670288</v>
       </c>
       <c r="G210" t="n">
-        <v>1.59537446498871</v>
+        <v>1.59537434577942</v>
       </c>
       <c r="H210" t="s">
         <v>8</v>
@@ -5933,7 +5933,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G214" t="n">
-        <v>1.54047453403473</v>
+        <v>1.54047465324402</v>
       </c>
       <c r="H214" t="s">
         <v>8</v>
@@ -5959,7 +5959,7 @@
         <v>1.91299998760223</v>
       </c>
       <c r="G215" t="n">
-        <v>1.56751465797424</v>
+        <v>1.56751477718353</v>
       </c>
       <c r="H215" t="s">
         <v>8</v>
@@ -5985,7 +5985,7 @@
         <v>1.91600000858307</v>
       </c>
       <c r="G216" t="n">
-        <v>1.56997311115265</v>
+        <v>1.56997299194336</v>
       </c>
       <c r="H216" t="s">
         <v>8</v>
@@ -6011,7 +6011,7 @@
         <v>1.91199994087219</v>
       </c>
       <c r="G217" t="n">
-        <v>1.56669533252716</v>
+        <v>1.56669521331787</v>
       </c>
       <c r="H217" t="s">
         <v>8</v>
@@ -6219,7 +6219,7 @@
         <v>1.85399997234344</v>
       </c>
       <c r="G225" t="n">
-        <v>1.51917004585266</v>
+        <v>1.51916992664337</v>
       </c>
       <c r="H225" t="s">
         <v>8</v>
@@ -6245,7 +6245,7 @@
         <v>1.90600001811981</v>
       </c>
       <c r="G226" t="n">
-        <v>1.5617790222168</v>
+        <v>1.56177890300751</v>
       </c>
       <c r="H226" t="s">
         <v>8</v>
@@ -6271,7 +6271,7 @@
         <v>1.8860000371933</v>
       </c>
       <c r="G227" t="n">
-        <v>1.54539096355438</v>
+        <v>1.54539108276367</v>
       </c>
       <c r="H227" t="s">
         <v>8</v>
@@ -6297,7 +6297,7 @@
         <v>1.67999994754791</v>
       </c>
       <c r="G228" t="n">
-        <v>1.37659406661987</v>
+        <v>1.37659418582916</v>
       </c>
       <c r="H228" t="s">
         <v>8</v>
@@ -6349,7 +6349,7 @@
         <v>1.70200002193451</v>
       </c>
       <c r="G230" t="n">
-        <v>1.39462113380432</v>
+        <v>1.39462101459503</v>
       </c>
       <c r="H230" t="s">
         <v>8</v>
@@ -6375,7 +6375,7 @@
         <v>1.77900004386902</v>
       </c>
       <c r="G231" t="n">
-        <v>1.45771491527557</v>
+        <v>1.45771503448486</v>
       </c>
       <c r="H231" t="s">
         <v>8</v>
@@ -6401,7 +6401,7 @@
         <v>1.79499995708466</v>
       </c>
       <c r="G232" t="n">
-        <v>1.47082531452179</v>
+        <v>1.47082543373108</v>
       </c>
       <c r="H232" t="s">
         <v>8</v>
@@ -6427,7 +6427,7 @@
         <v>1.87199997901917</v>
       </c>
       <c r="G233" t="n">
-        <v>1.53391933441162</v>
+        <v>1.53391945362091</v>
       </c>
       <c r="H233" t="s">
         <v>8</v>
@@ -6635,7 +6635,7 @@
         <v>1.84500002861023</v>
       </c>
       <c r="G241" t="n">
-        <v>1.51179540157318</v>
+        <v>1.51179552078247</v>
       </c>
       <c r="H241" t="s">
         <v>8</v>
@@ -6661,7 +6661,7 @@
         <v>1.89800000190735</v>
       </c>
       <c r="G242" t="n">
-        <v>1.55522358417511</v>
+        <v>1.55522382259369</v>
       </c>
       <c r="H242" t="s">
         <v>8</v>
@@ -6687,7 +6687,7 @@
         <v>1.89800000190735</v>
       </c>
       <c r="G243" t="n">
-        <v>1.55522358417511</v>
+        <v>1.55522382259369</v>
       </c>
       <c r="H243" t="s">
         <v>8</v>
@@ -6739,7 +6739,7 @@
         <v>1.90900003910065</v>
       </c>
       <c r="G245" t="n">
-        <v>1.56423723697662</v>
+        <v>1.56423711776733</v>
       </c>
       <c r="H245" t="s">
         <v>8</v>
@@ -6765,7 +6765,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G246" t="n">
-        <v>1.54047453403473</v>
+        <v>1.54047465324402</v>
       </c>
       <c r="H246" t="s">
         <v>8</v>
@@ -6843,7 +6843,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G249" t="n">
-        <v>1.55686247348785</v>
+        <v>1.55686259269714</v>
       </c>
       <c r="H249" t="s">
         <v>8</v>
@@ -6895,7 +6895,7 @@
         <v>1.88100004196167</v>
       </c>
       <c r="G251" t="n">
-        <v>1.5412939786911</v>
+        <v>1.54129385948181</v>
       </c>
       <c r="H251" t="s">
         <v>8</v>
@@ -6947,7 +6947,7 @@
         <v>1.84399998188019</v>
       </c>
       <c r="G253" t="n">
-        <v>1.5109760761261</v>
+        <v>1.51097619533539</v>
       </c>
       <c r="H253" t="s">
         <v>8</v>
@@ -7025,7 +7025,7 @@
         <v>1.89400005340576</v>
       </c>
       <c r="G256" t="n">
-        <v>1.55194616317749</v>
+        <v>1.55194628238678</v>
       </c>
       <c r="H256" t="s">
         <v>8</v>
@@ -7051,7 +7051,7 @@
         <v>1.84099996089935</v>
       </c>
       <c r="G257" t="n">
-        <v>1.50851774215698</v>
+        <v>1.50851786136627</v>
       </c>
       <c r="H257" t="s">
         <v>8</v>
@@ -7077,7 +7077,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G258" t="n">
-        <v>1.53228056430817</v>
+        <v>1.53228044509888</v>
       </c>
       <c r="H258" t="s">
         <v>8</v>
@@ -7103,7 +7103,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G259" t="n">
-        <v>1.53228056430817</v>
+        <v>1.53228044509888</v>
       </c>
       <c r="H259" t="s">
         <v>8</v>
@@ -7155,7 +7155,7 @@
         <v>1.84099996089935</v>
       </c>
       <c r="G261" t="n">
-        <v>1.50851774215698</v>
+        <v>1.50851786136627</v>
       </c>
       <c r="H261" t="s">
         <v>8</v>
@@ -7259,7 +7259,7 @@
         <v>1.83399999141693</v>
       </c>
       <c r="G265" t="n">
-        <v>1.50278210639954</v>
+        <v>1.50278222560883</v>
       </c>
       <c r="H265" t="s">
         <v>8</v>
@@ -7311,7 +7311,7 @@
         <v>1.84300005435944</v>
       </c>
       <c r="G267" t="n">
-        <v>1.51015675067902</v>
+        <v>1.51015663146973</v>
       </c>
       <c r="H267" t="s">
         <v>8</v>
@@ -7337,7 +7337,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G268" t="n">
-        <v>1.54047453403473</v>
+        <v>1.54047465324402</v>
       </c>
       <c r="H268" t="s">
         <v>8</v>
@@ -7363,7 +7363,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G269" t="n">
-        <v>1.57325041294098</v>
+        <v>1.57325053215027</v>
       </c>
       <c r="H269" t="s">
         <v>8</v>
@@ -7389,7 +7389,7 @@
         <v>1.93499994277954</v>
       </c>
       <c r="G270" t="n">
-        <v>1.5855416059494</v>
+        <v>1.58554148674011</v>
       </c>
       <c r="H270" t="s">
         <v>8</v>
@@ -7415,7 +7415,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G271" t="n">
-        <v>1.55686247348785</v>
+        <v>1.55686259269714</v>
       </c>
       <c r="H271" t="s">
         <v>8</v>
@@ -7441,7 +7441,7 @@
         <v>1.94599997997284</v>
       </c>
       <c r="G272" t="n">
-        <v>1.59455490112305</v>
+        <v>1.59455502033234</v>
       </c>
       <c r="H272" t="s">
         <v>8</v>
@@ -7467,7 +7467,7 @@
         <v>1.96099996566772</v>
       </c>
       <c r="G273" t="n">
-        <v>1.60684597492218</v>
+        <v>1.60684585571289</v>
       </c>
       <c r="H273" t="s">
         <v>8</v>
@@ -7545,7 +7545,7 @@
         <v>1.97899997234344</v>
       </c>
       <c r="G276" t="n">
-        <v>1.62159526348114</v>
+        <v>1.62159538269043</v>
       </c>
       <c r="H276" t="s">
         <v>8</v>
@@ -7623,7 +7623,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G279" t="n">
-        <v>1.53228056430817</v>
+        <v>1.53228044509888</v>
       </c>
       <c r="H279" t="s">
         <v>8</v>
@@ -7701,7 +7701,7 @@
         <v>1.88699996471405</v>
       </c>
       <c r="G282" t="n">
-        <v>1.54621016979218</v>
+        <v>1.54621028900146</v>
       </c>
       <c r="H282" t="s">
         <v>8</v>
@@ -7727,7 +7727,7 @@
         <v>1.90100002288818</v>
       </c>
       <c r="G283" t="n">
-        <v>1.55768203735352</v>
+        <v>1.55768191814423</v>
       </c>
       <c r="H283" t="s">
         <v>8</v>
@@ -7753,7 +7753,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G284" t="n">
-        <v>1.55686247348785</v>
+        <v>1.55686259269714</v>
       </c>
       <c r="H284" t="s">
         <v>8</v>
@@ -7779,7 +7779,7 @@
         <v>1.93799996376038</v>
       </c>
       <c r="G285" t="n">
-        <v>1.58799993991852</v>
+        <v>1.58799982070923</v>
       </c>
       <c r="H285" t="s">
         <v>8</v>
@@ -7805,7 +7805,7 @@
         <v>1.87300002574921</v>
       </c>
       <c r="G286" t="n">
-        <v>1.53473877906799</v>
+        <v>1.5347386598587</v>
       </c>
       <c r="H286" t="s">
         <v>8</v>
@@ -7831,7 +7831,7 @@
         <v>1.93099999427795</v>
       </c>
       <c r="G287" t="n">
-        <v>1.5822639465332</v>
+        <v>1.58226382732391</v>
       </c>
       <c r="H287" t="s">
         <v>8</v>
@@ -7857,7 +7857,7 @@
         <v>1.88699996471405</v>
       </c>
       <c r="G288" t="n">
-        <v>1.54621016979218</v>
+        <v>1.54621028900146</v>
       </c>
       <c r="H288" t="s">
         <v>8</v>
@@ -7883,7 +7883,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G289" t="n">
-        <v>1.54047453403473</v>
+        <v>1.54047465324402</v>
       </c>
       <c r="H289" t="s">
         <v>8</v>
@@ -7961,7 +7961,7 @@
         <v>1.87800002098083</v>
       </c>
       <c r="G292" t="n">
-        <v>1.53883576393127</v>
+        <v>1.53883588314056</v>
       </c>
       <c r="H292" t="s">
         <v>8</v>
@@ -8013,7 +8013,7 @@
         <v>1.89400005340576</v>
       </c>
       <c r="G294" t="n">
-        <v>1.55194616317749</v>
+        <v>1.55194628238678</v>
       </c>
       <c r="H294" t="s">
         <v>8</v>
@@ -8091,7 +8091,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G297" t="n">
-        <v>1.55686247348785</v>
+        <v>1.55686259269714</v>
       </c>
       <c r="H297" t="s">
         <v>8</v>
@@ -8195,7 +8195,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G301" t="n">
-        <v>1.53228056430817</v>
+        <v>1.53228044509888</v>
       </c>
       <c r="H301" t="s">
         <v>8</v>
@@ -8221,7 +8221,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G302" t="n">
-        <v>1.54866850376129</v>
+        <v>1.54866862297058</v>
       </c>
       <c r="H302" t="s">
         <v>8</v>
@@ -8299,7 +8299,7 @@
         <v>1.87899994850159</v>
       </c>
       <c r="G305" t="n">
-        <v>1.53965520858765</v>
+        <v>1.53965497016907</v>
       </c>
       <c r="H305" t="s">
         <v>8</v>
@@ -8325,7 +8325,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G306" t="n">
-        <v>1.54866850376129</v>
+        <v>1.54866862297058</v>
       </c>
       <c r="H306" t="s">
         <v>8</v>
@@ -8403,7 +8403,7 @@
         <v>2</v>
       </c>
       <c r="G309" t="n">
-        <v>1.63880264759064</v>
+        <v>1.63880276679993</v>
       </c>
       <c r="H309" t="s">
         <v>8</v>
@@ -8429,7 +8429,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G310" t="n">
-        <v>1.63060867786407</v>
+        <v>1.63060879707336</v>
       </c>
       <c r="H310" t="s">
         <v>8</v>
@@ -8455,7 +8455,7 @@
         <v>2.01600003242493</v>
       </c>
       <c r="G311" t="n">
-        <v>1.65191316604614</v>
+        <v>1.65191304683685</v>
       </c>
       <c r="H311" t="s">
         <v>8</v>
@@ -8481,7 +8481,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G312" t="n">
-        <v>1.64699685573578</v>
+        <v>1.6469966173172</v>
       </c>
       <c r="H312" t="s">
         <v>8</v>
@@ -8533,7 +8533,7 @@
         <v>2.04200005531311</v>
       </c>
       <c r="G314" t="n">
-        <v>1.67321753501892</v>
+        <v>1.67321765422821</v>
       </c>
       <c r="H314" t="s">
         <v>8</v>
@@ -8559,7 +8559,7 @@
         <v>2.01799988746643</v>
       </c>
       <c r="G315" t="n">
-        <v>1.65355181694031</v>
+        <v>1.65355169773102</v>
       </c>
       <c r="H315" t="s">
         <v>8</v>
@@ -8637,7 +8637,7 @@
         <v>2.29800009727478</v>
       </c>
       <c r="G318" t="n">
-        <v>1.88298439979553</v>
+        <v>1.88298416137695</v>
       </c>
       <c r="H318" t="s">
         <v>8</v>
@@ -8663,7 +8663,7 @@
         <v>2.22199988365173</v>
       </c>
       <c r="G319" t="n">
-        <v>1.82070958614349</v>
+        <v>1.82070970535278</v>
       </c>
       <c r="H319" t="s">
         <v>8</v>
@@ -8689,7 +8689,7 @@
         <v>2.23200011253357</v>
       </c>
       <c r="G320" t="n">
-        <v>1.82890391349792</v>
+        <v>1.82890379428864</v>
       </c>
       <c r="H320" t="s">
         <v>8</v>
@@ -8715,7 +8715,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G321" t="n">
-        <v>1.78629505634308</v>
+        <v>1.7862948179245</v>
       </c>
       <c r="H321" t="s">
         <v>8</v>
@@ -8741,7 +8741,7 @@
         <v>2.21799993515015</v>
       </c>
       <c r="G322" t="n">
-        <v>1.81743228435516</v>
+        <v>1.81743204593658</v>
       </c>
       <c r="H322" t="s">
         <v>8</v>
@@ -8767,7 +8767,7 @@
         <v>2.21600008010864</v>
       </c>
       <c r="G323" t="n">
-        <v>1.81579351425171</v>
+        <v>1.81579327583313</v>
       </c>
       <c r="H323" t="s">
         <v>8</v>
@@ -8793,7 +8793,7 @@
         <v>2.17199993133545</v>
       </c>
       <c r="G324" t="n">
-        <v>1.77973961830139</v>
+        <v>1.77973973751068</v>
       </c>
       <c r="H324" t="s">
         <v>8</v>
@@ -8871,7 +8871,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G327" t="n">
-        <v>1.79448890686035</v>
+        <v>1.79448914527893</v>
       </c>
       <c r="H327" t="s">
         <v>8</v>
@@ -8897,7 +8897,7 @@
         <v>2.19799995422363</v>
       </c>
       <c r="G328" t="n">
-        <v>1.80104398727417</v>
+        <v>1.80104410648346</v>
       </c>
       <c r="H328" t="s">
         <v>8</v>
@@ -8923,7 +8923,7 @@
         <v>2.2260000705719</v>
       </c>
       <c r="G329" t="n">
-        <v>1.82398760318756</v>
+        <v>1.82398748397827</v>
       </c>
       <c r="H329" t="s">
         <v>8</v>
@@ -8949,7 +8949,7 @@
         <v>2.21600008010864</v>
       </c>
       <c r="G330" t="n">
-        <v>1.81579351425171</v>
+        <v>1.81579327583313</v>
       </c>
       <c r="H330" t="s">
         <v>8</v>
@@ -8975,7 +8975,7 @@
         <v>2.19799995422363</v>
       </c>
       <c r="G331" t="n">
-        <v>1.80104398727417</v>
+        <v>1.80104410648346</v>
       </c>
       <c r="H331" t="s">
         <v>8</v>
@@ -9001,7 +9001,7 @@
         <v>2.12199997901917</v>
       </c>
       <c r="G332" t="n">
-        <v>1.73876965045929</v>
+        <v>1.73876953125</v>
       </c>
       <c r="H332" t="s">
         <v>8</v>
@@ -9105,7 +9105,7 @@
         <v>2.15199995040894</v>
       </c>
       <c r="G336" t="n">
-        <v>1.76335155963898</v>
+        <v>1.76335179805756</v>
       </c>
       <c r="H336" t="s">
         <v>8</v>
@@ -9183,7 +9183,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G339" t="n">
-        <v>1.83545911312103</v>
+        <v>1.83545899391174</v>
       </c>
       <c r="H339" t="s">
         <v>8</v>
@@ -9209,7 +9209,7 @@
         <v>2.25399994850159</v>
       </c>
       <c r="G340" t="n">
-        <v>1.84693050384521</v>
+        <v>1.84693038463593</v>
       </c>
       <c r="H340" t="s">
         <v>8</v>
@@ -9235,7 +9235,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G341" t="n">
-        <v>1.81087708473206</v>
+        <v>1.81087684631348</v>
       </c>
       <c r="H341" t="s">
         <v>8</v>
@@ -9261,7 +9261,7 @@
         <v>2.20799994468689</v>
       </c>
       <c r="G342" t="n">
-        <v>1.80923819541931</v>
+        <v>1.80923807621002</v>
       </c>
       <c r="H342" t="s">
         <v>8</v>
@@ -9313,7 +9313,7 @@
         <v>2.2720000743866</v>
       </c>
       <c r="G344" t="n">
-        <v>1.86167967319489</v>
+        <v>1.86168003082275</v>
       </c>
       <c r="H344" t="s">
         <v>8</v>
@@ -9339,7 +9339,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G345" t="n">
-        <v>1.83545911312103</v>
+        <v>1.83545899391174</v>
       </c>
       <c r="H345" t="s">
         <v>8</v>
@@ -9365,7 +9365,7 @@
         <v>2.27600002288818</v>
       </c>
       <c r="G346" t="n">
-        <v>1.86495745182037</v>
+        <v>1.86495757102966</v>
       </c>
       <c r="H346" t="s">
         <v>8</v>
@@ -9417,7 +9417,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G348" t="n">
-        <v>1.87642908096313</v>
+        <v>1.87642872333527</v>
       </c>
       <c r="H348" t="s">
         <v>8</v>
@@ -9443,7 +9443,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G349" t="n">
-        <v>1.88462328910828</v>
+        <v>1.88462316989899</v>
       </c>
       <c r="H349" t="s">
         <v>8</v>
@@ -9495,7 +9495,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G351" t="n">
-        <v>1.91739904880524</v>
+        <v>1.91739916801453</v>
       </c>
       <c r="H351" t="s">
         <v>8</v>
@@ -9547,7 +9547,7 @@
         <v>2.27600002288818</v>
       </c>
       <c r="G353" t="n">
-        <v>1.86495745182037</v>
+        <v>1.86495757102966</v>
       </c>
       <c r="H353" t="s">
         <v>8</v>
@@ -9573,7 +9573,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G354" t="n">
-        <v>1.86823511123657</v>
+        <v>1.86823523044586</v>
       </c>
       <c r="H354" t="s">
         <v>8</v>
@@ -9599,7 +9599,7 @@
         <v>2.24600005149841</v>
       </c>
       <c r="G355" t="n">
-        <v>1.92479622364044</v>
+        <v>1.92479634284973</v>
       </c>
       <c r="H355" t="s">
         <v>8</v>
@@ -9625,7 +9625,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G356" t="n">
-        <v>1.93679404258728</v>
+        <v>1.93679392337799</v>
       </c>
       <c r="H356" t="s">
         <v>8</v>
@@ -9677,7 +9677,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G358" t="n">
-        <v>1.9710738658905</v>
+        <v>1.97107374668121</v>
       </c>
       <c r="H358" t="s">
         <v>8</v>
@@ -9703,7 +9703,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G359" t="n">
-        <v>1.9710738658905</v>
+        <v>1.97107374668121</v>
       </c>
       <c r="H359" t="s">
         <v>8</v>
@@ -9807,7 +9807,7 @@
         <v>2.28600001335144</v>
       </c>
       <c r="G363" t="n">
-        <v>1.95907604694366</v>
+        <v>1.95907580852509</v>
       </c>
       <c r="H363" t="s">
         <v>8</v>
@@ -9833,7 +9833,7 @@
         <v>2.28600001335144</v>
       </c>
       <c r="G364" t="n">
-        <v>1.95907604694366</v>
+        <v>1.95907580852509</v>
       </c>
       <c r="H364" t="s">
         <v>8</v>
@@ -9911,7 +9911,7 @@
         <v>2.24799990653992</v>
       </c>
       <c r="G367" t="n">
-        <v>1.9265102148056</v>
+        <v>1.92651009559631</v>
       </c>
       <c r="H367" t="s">
         <v>8</v>
@@ -9937,7 +9937,7 @@
         <v>2.24799990653992</v>
       </c>
       <c r="G368" t="n">
-        <v>1.9265102148056</v>
+        <v>1.92651009559631</v>
       </c>
       <c r="H368" t="s">
         <v>8</v>
@@ -9963,7 +9963,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G369" t="n">
-        <v>1.95393395423889</v>
+        <v>1.95393407344818</v>
       </c>
       <c r="H369" t="s">
         <v>8</v>
@@ -9989,7 +9989,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G370" t="n">
-        <v>1.95393395423889</v>
+        <v>1.95393407344818</v>
       </c>
       <c r="H370" t="s">
         <v>8</v>
@@ -10041,7 +10041,7 @@
         <v>2.22399997711182</v>
       </c>
       <c r="G372" t="n">
-        <v>1.90594255924225</v>
+        <v>1.90594244003296</v>
       </c>
       <c r="H372" t="s">
         <v>8</v>
@@ -10067,7 +10067,7 @@
         <v>2.22399997711182</v>
       </c>
       <c r="G373" t="n">
-        <v>1.90594255924225</v>
+        <v>1.90594244003296</v>
       </c>
       <c r="H373" t="s">
         <v>8</v>
@@ -10093,7 +10093,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G374" t="n">
-        <v>1.8939448595047</v>
+        <v>1.89394462108612</v>
       </c>
       <c r="H374" t="s">
         <v>8</v>
@@ -10171,7 +10171,7 @@
         <v>2.21799993515015</v>
       </c>
       <c r="G377" t="n">
-        <v>1.90080070495605</v>
+        <v>1.90080058574677</v>
       </c>
       <c r="H377" t="s">
         <v>8</v>
@@ -10197,7 +10197,7 @@
         <v>2.23399996757507</v>
       </c>
       <c r="G378" t="n">
-        <v>1.91451239585876</v>
+        <v>1.91451251506805</v>
       </c>
       <c r="H378" t="s">
         <v>8</v>
@@ -10223,7 +10223,7 @@
         <v>2.20199990272522</v>
       </c>
       <c r="G379" t="n">
-        <v>1.88708865642548</v>
+        <v>1.88708877563477</v>
       </c>
       <c r="H379" t="s">
         <v>8</v>
@@ -10249,7 +10249,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G380" t="n">
-        <v>1.87680494785309</v>
+        <v>1.87680518627167</v>
       </c>
       <c r="H380" t="s">
         <v>8</v>
@@ -10275,7 +10275,7 @@
         <v>2.23799991607666</v>
       </c>
       <c r="G381" t="n">
-        <v>1.91794049739838</v>
+        <v>1.9179402589798</v>
       </c>
       <c r="H381" t="s">
         <v>8</v>
@@ -10327,7 +10327,7 @@
         <v>2.18199992179871</v>
       </c>
       <c r="G383" t="n">
-        <v>1.86994910240173</v>
+        <v>1.86994898319244</v>
       </c>
       <c r="H383" t="s">
         <v>8</v>
@@ -10379,7 +10379,7 @@
         <v>2.2279999256134</v>
       </c>
       <c r="G385" t="n">
-        <v>1.90937054157257</v>
+        <v>1.90937066078186</v>
       </c>
       <c r="H385" t="s">
         <v>8</v>
@@ -10405,7 +10405,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G386" t="n">
-        <v>1.90251457691193</v>
+        <v>1.90251469612122</v>
       </c>
       <c r="H386" t="s">
         <v>8</v>
@@ -10431,7 +10431,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G387" t="n">
-        <v>1.8939448595047</v>
+        <v>1.89394462108612</v>
       </c>
       <c r="H387" t="s">
         <v>8</v>
@@ -10457,7 +10457,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G388" t="n">
-        <v>1.8939448595047</v>
+        <v>1.89394462108612</v>
       </c>
       <c r="H388" t="s">
         <v>8</v>
@@ -10483,7 +10483,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G389" t="n">
-        <v>1.8939448595047</v>
+        <v>1.89394462108612</v>
       </c>
       <c r="H389" t="s">
         <v>8</v>
@@ -10509,7 +10509,7 @@
         <v>2.23399996757507</v>
       </c>
       <c r="G390" t="n">
-        <v>1.91451239585876</v>
+        <v>1.91451251506805</v>
       </c>
       <c r="H390" t="s">
         <v>8</v>
@@ -10535,7 +10535,7 @@
         <v>2.23799991607666</v>
       </c>
       <c r="G391" t="n">
-        <v>1.91794049739838</v>
+        <v>1.9179402589798</v>
       </c>
       <c r="H391" t="s">
         <v>8</v>
@@ -10613,7 +10613,7 @@
         <v>2.29200005531311</v>
       </c>
       <c r="G394" t="n">
-        <v>1.96421802043915</v>
+        <v>1.96421790122986</v>
       </c>
       <c r="H394" t="s">
         <v>8</v>
@@ -10639,7 +10639,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G395" t="n">
-        <v>1.96250379085541</v>
+        <v>1.96250355243683</v>
       </c>
       <c r="H395" t="s">
         <v>8</v>
@@ -10665,7 +10665,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G396" t="n">
-        <v>1.9710738658905</v>
+        <v>1.97107374668121</v>
       </c>
       <c r="H396" t="s">
         <v>8</v>
@@ -10691,7 +10691,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G397" t="n">
-        <v>1.98821341991425</v>
+        <v>1.98821353912354</v>
       </c>
       <c r="H397" t="s">
         <v>8</v>
@@ -10717,7 +10717,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G398" t="n">
-        <v>1.98821341991425</v>
+        <v>1.98821353912354</v>
       </c>
       <c r="H398" t="s">
         <v>8</v>
@@ -10821,7 +10821,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G402" t="n">
-        <v>2.12533140182495</v>
+        <v>2.12533164024353</v>
       </c>
       <c r="H402" t="s">
         <v>8</v>
@@ -10847,7 +10847,7 @@
         <v>2.43400001525879</v>
       </c>
       <c r="G403" t="n">
-        <v>2.0859100818634</v>
+        <v>2.08591032028198</v>
       </c>
       <c r="H403" t="s">
         <v>8</v>
@@ -10925,7 +10925,7 @@
         <v>2.42799997329712</v>
       </c>
       <c r="G406" t="n">
-        <v>2.08076810836792</v>
+        <v>2.0807683467865</v>
       </c>
       <c r="H406" t="s">
         <v>8</v>
@@ -10951,7 +10951,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G407" t="n">
-        <v>2.06534218788147</v>
+        <v>2.06534266471863</v>
       </c>
       <c r="H407" t="s">
         <v>8</v>
@@ -10977,7 +10977,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G408" t="n">
-        <v>2.06534218788147</v>
+        <v>2.06534266471863</v>
       </c>
       <c r="H408" t="s">
         <v>8</v>
@@ -11029,7 +11029,7 @@
         <v>2.41799998283386</v>
       </c>
       <c r="G410" t="n">
-        <v>2.07219839096069</v>
+        <v>2.07219815254211</v>
       </c>
       <c r="H410" t="s">
         <v>8</v>
@@ -11055,7 +11055,7 @@
         <v>2.41799998283386</v>
       </c>
       <c r="G411" t="n">
-        <v>2.07219839096069</v>
+        <v>2.07219815254211</v>
       </c>
       <c r="H411" t="s">
         <v>8</v>
@@ -11081,7 +11081,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G412" t="n">
-        <v>2.12533140182495</v>
+        <v>2.12533164024353</v>
       </c>
       <c r="H412" t="s">
         <v>8</v>
@@ -11107,7 +11107,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G413" t="n">
-        <v>2.13390135765076</v>
+        <v>2.13390159606934</v>
       </c>
       <c r="H413" t="s">
         <v>8</v>
@@ -11159,7 +11159,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G415" t="n">
-        <v>2.09962201118469</v>
+        <v>2.09962177276611</v>
       </c>
       <c r="H415" t="s">
         <v>8</v>
@@ -11185,7 +11185,7 @@
         <v>2.4539999961853</v>
       </c>
       <c r="G416" t="n">
-        <v>2.10304975509644</v>
+        <v>2.10304999351501</v>
       </c>
       <c r="H416" t="s">
         <v>8</v>
@@ -11211,7 +11211,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G417" t="n">
-        <v>2.03963279724121</v>
+        <v>2.03963303565979</v>
       </c>
       <c r="H417" t="s">
         <v>8</v>
@@ -11237,7 +11237,7 @@
         <v>2.41400003433228</v>
       </c>
       <c r="G418" t="n">
-        <v>2.06877064704895</v>
+        <v>2.06877040863037</v>
       </c>
       <c r="H418" t="s">
         <v>8</v>
@@ -11341,7 +11341,7 @@
         <v>2.44799995422363</v>
       </c>
       <c r="G422" t="n">
-        <v>2.09790802001953</v>
+        <v>2.09790825843811</v>
       </c>
       <c r="H422" t="s">
         <v>8</v>
@@ -11367,7 +11367,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G423" t="n">
-        <v>2.1167619228363</v>
+        <v>2.11676168441772</v>
       </c>
       <c r="H423" t="s">
         <v>8</v>
@@ -11419,7 +11419,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G425" t="n">
-        <v>2.09962201118469</v>
+        <v>2.09962177276611</v>
       </c>
       <c r="H425" t="s">
         <v>8</v>
@@ -11445,7 +11445,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G426" t="n">
-        <v>2.08248233795166</v>
+        <v>2.08248209953308</v>
       </c>
       <c r="H426" t="s">
         <v>8</v>
@@ -11497,7 +11497,7 @@
         <v>2.41199994087219</v>
       </c>
       <c r="G428" t="n">
-        <v>2.06705641746521</v>
+        <v>2.06705617904663</v>
       </c>
       <c r="H428" t="s">
         <v>8</v>
@@ -11523,7 +11523,7 @@
         <v>2.4760000705719</v>
       </c>
       <c r="G429" t="n">
-        <v>2.12190365791321</v>
+        <v>2.12190389633179</v>
       </c>
       <c r="H429" t="s">
         <v>8</v>
@@ -11627,7 +11627,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G433" t="n">
-        <v>2.09962201118469</v>
+        <v>2.09962177276611</v>
       </c>
       <c r="H433" t="s">
         <v>8</v>
@@ -11653,7 +11653,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G434" t="n">
-        <v>2.13390135765076</v>
+        <v>2.13390159606934</v>
       </c>
       <c r="H434" t="s">
         <v>8</v>
@@ -11679,7 +11679,7 @@
         <v>2.43799996376038</v>
       </c>
       <c r="G435" t="n">
-        <v>2.0893383026123</v>
+        <v>2.08933806419373</v>
       </c>
       <c r="H435" t="s">
         <v>8</v>
@@ -11705,7 +11705,7 @@
         <v>2.39400005340576</v>
       </c>
       <c r="G436" t="n">
-        <v>2.05163073539734</v>
+        <v>2.05163049697876</v>
       </c>
       <c r="H436" t="s">
         <v>8</v>
@@ -11731,7 +11731,7 @@
         <v>2.44799995422363</v>
       </c>
       <c r="G437" t="n">
-        <v>2.09790802001953</v>
+        <v>2.09790825843811</v>
       </c>
       <c r="H437" t="s">
         <v>8</v>
@@ -11757,7 +11757,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G438" t="n">
-        <v>2.08248233795166</v>
+        <v>2.08248209953308</v>
       </c>
       <c r="H438" t="s">
         <v>8</v>
@@ -11783,7 +11783,7 @@
         <v>2.44799995422363</v>
       </c>
       <c r="G439" t="n">
-        <v>2.09790802001953</v>
+        <v>2.09790825843811</v>
       </c>
       <c r="H439" t="s">
         <v>8</v>
@@ -11809,7 +11809,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G440" t="n">
-        <v>2.17675113677979</v>
+        <v>2.17675089836121</v>
       </c>
       <c r="H440" t="s">
         <v>8</v>
@@ -11861,7 +11861,7 @@
         <v>2.48799991607666</v>
       </c>
       <c r="G442" t="n">
-        <v>2.13218760490417</v>
+        <v>2.1321873664856</v>
       </c>
       <c r="H442" t="s">
         <v>8</v>
@@ -11913,7 +11913,7 @@
         <v>2.48799991607666</v>
       </c>
       <c r="G444" t="n">
-        <v>2.13218760490417</v>
+        <v>2.1321873664856</v>
       </c>
       <c r="H444" t="s">
         <v>8</v>
@@ -11965,7 +11965,7 @@
         <v>2.47199988365173</v>
       </c>
       <c r="G446" t="n">
-        <v>2.11847543716431</v>
+        <v>2.11847591400146</v>
       </c>
       <c r="H446" t="s">
         <v>8</v>
@@ -11991,7 +11991,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G447" t="n">
-        <v>2.1167619228363</v>
+        <v>2.11676168441772</v>
       </c>
       <c r="H447" t="s">
         <v>8</v>
@@ -12043,7 +12043,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G449" t="n">
-        <v>2.09962201118469</v>
+        <v>2.09962177276611</v>
       </c>
       <c r="H449" t="s">
         <v>8</v>
@@ -12069,7 +12069,7 @@
         <v>2.4779999256134</v>
       </c>
       <c r="G450" t="n">
-        <v>2.12361741065979</v>
+        <v>2.12361764907837</v>
       </c>
       <c r="H450" t="s">
         <v>8</v>
@@ -12173,7 +12173,7 @@
         <v>2.4539999961853</v>
       </c>
       <c r="G454" t="n">
-        <v>2.10304975509644</v>
+        <v>2.10304999351501</v>
       </c>
       <c r="H454" t="s">
         <v>8</v>
@@ -12225,7 +12225,7 @@
         <v>2.4779999256134</v>
       </c>
       <c r="G456" t="n">
-        <v>2.12361741065979</v>
+        <v>2.12361764907837</v>
       </c>
       <c r="H456" t="s">
         <v>8</v>
@@ -12277,7 +12277,7 @@
         <v>2.48799991607666</v>
       </c>
       <c r="G458" t="n">
-        <v>2.13218760490417</v>
+        <v>2.1321873664856</v>
       </c>
       <c r="H458" t="s">
         <v>8</v>
@@ -12381,7 +12381,7 @@
         <v>2.49799990653992</v>
       </c>
       <c r="G462" t="n">
-        <v>2.1407573223114</v>
+        <v>2.14075708389282</v>
       </c>
       <c r="H462" t="s">
         <v>8</v>
@@ -12433,7 +12433,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G464" t="n">
-        <v>2.13390135765076</v>
+        <v>2.13390159606934</v>
       </c>
       <c r="H464" t="s">
         <v>8</v>
@@ -12459,7 +12459,7 @@
         <v>2.50799989700317</v>
       </c>
       <c r="G465" t="n">
-        <v>2.14932751655579</v>
+        <v>2.14932727813721</v>
       </c>
       <c r="H465" t="s">
         <v>8</v>
@@ -12589,7 +12589,7 @@
         <v>2.4760000705719</v>
       </c>
       <c r="G470" t="n">
-        <v>2.12190365791321</v>
+        <v>2.12190389633179</v>
       </c>
       <c r="H470" t="s">
         <v>8</v>
@@ -12615,7 +12615,7 @@
         <v>2.49799990653992</v>
       </c>
       <c r="G471" t="n">
-        <v>2.1407573223114</v>
+        <v>2.14075708389282</v>
       </c>
       <c r="H471" t="s">
         <v>8</v>
@@ -12641,7 +12641,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G472" t="n">
-        <v>2.12533140182495</v>
+        <v>2.12533164024353</v>
       </c>
       <c r="H472" t="s">
         <v>8</v>
@@ -12693,7 +12693,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G474" t="n">
-        <v>2.15104150772095</v>
+        <v>2.15104126930237</v>
       </c>
       <c r="H474" t="s">
         <v>8</v>
@@ -12745,7 +12745,7 @@
         <v>2.47399997711182</v>
       </c>
       <c r="G476" t="n">
-        <v>2.12018966674805</v>
+        <v>2.12018942832947</v>
       </c>
       <c r="H476" t="s">
         <v>8</v>
@@ -12771,7 +12771,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G477" t="n">
-        <v>2.09962201118469</v>
+        <v>2.09962177276611</v>
       </c>
       <c r="H477" t="s">
         <v>8</v>
@@ -12875,7 +12875,7 @@
         <v>2.37199997901917</v>
       </c>
       <c r="G481" t="n">
-        <v>2.03277683258057</v>
+        <v>2.03277707099915</v>
       </c>
       <c r="H481" t="s">
         <v>8</v>
@@ -12979,7 +12979,7 @@
         <v>2.41599988937378</v>
       </c>
       <c r="G485" t="n">
-        <v>2.07048416137695</v>
+        <v>2.07048439979553</v>
       </c>
       <c r="H485" t="s">
         <v>8</v>
@@ -13005,7 +13005,7 @@
         <v>2.37199997901917</v>
       </c>
       <c r="G486" t="n">
-        <v>2.03277683258057</v>
+        <v>2.03277707099915</v>
       </c>
       <c r="H486" t="s">
         <v>8</v>
@@ -13031,7 +13031,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G487" t="n">
-        <v>2.06534218788147</v>
+        <v>2.06534266471863</v>
       </c>
       <c r="H487" t="s">
         <v>8</v>
@@ -13083,7 +13083,7 @@
         <v>2.49799990653992</v>
       </c>
       <c r="G489" t="n">
-        <v>2.1407573223114</v>
+        <v>2.14075708389282</v>
       </c>
       <c r="H489" t="s">
         <v>8</v>
@@ -13135,7 +13135,7 @@
         <v>2.44799995422363</v>
       </c>
       <c r="G491" t="n">
-        <v>2.09790802001953</v>
+        <v>2.09790825843811</v>
       </c>
       <c r="H491" t="s">
         <v>8</v>
@@ -13161,7 +13161,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G492" t="n">
-        <v>2.12533140182495</v>
+        <v>2.12533164024353</v>
       </c>
       <c r="H492" t="s">
         <v>8</v>
@@ -13239,7 +13239,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G495" t="n">
-        <v>2.12533140182495</v>
+        <v>2.12533164024353</v>
       </c>
       <c r="H495" t="s">
         <v>8</v>
@@ -13265,7 +13265,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G496" t="n">
-        <v>2.1167619228363</v>
+        <v>2.11676168441772</v>
       </c>
       <c r="H496" t="s">
         <v>8</v>
@@ -13291,7 +13291,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G497" t="n">
-        <v>2.1167619228363</v>
+        <v>2.11676168441772</v>
       </c>
       <c r="H497" t="s">
         <v>8</v>
@@ -13317,7 +13317,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G498" t="n">
-        <v>2.1167619228363</v>
+        <v>2.11676168441772</v>
       </c>
       <c r="H498" t="s">
         <v>8</v>
@@ -13343,7 +13343,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G499" t="n">
-        <v>2.1167619228363</v>
+        <v>2.11676168441772</v>
       </c>
       <c r="H499" t="s">
         <v>8</v>
@@ -13369,7 +13369,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G500" t="n">
-        <v>2.08248233795166</v>
+        <v>2.08248209953308</v>
       </c>
       <c r="H500" t="s">
         <v>8</v>
@@ -13421,7 +13421,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G502" t="n">
-        <v>2.03963279724121</v>
+        <v>2.03963303565979</v>
       </c>
       <c r="H502" t="s">
         <v>8</v>
@@ -13447,7 +13447,7 @@
         <v>2.35800004005432</v>
       </c>
       <c r="G503" t="n">
-        <v>2.02077889442444</v>
+        <v>2.02077913284302</v>
       </c>
       <c r="H503" t="s">
         <v>8</v>
@@ -13499,7 +13499,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G505" t="n">
-        <v>2.08248233795166</v>
+        <v>2.08248209953308</v>
       </c>
       <c r="H505" t="s">
         <v>8</v>
@@ -13551,7 +13551,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G507" t="n">
-        <v>2.09962201118469</v>
+        <v>2.09962177276611</v>
       </c>
       <c r="H507" t="s">
         <v>8</v>
@@ -13577,7 +13577,7 @@
         <v>2.44799995422363</v>
       </c>
       <c r="G508" t="n">
-        <v>2.09790802001953</v>
+        <v>2.09790825843811</v>
       </c>
       <c r="H508" t="s">
         <v>8</v>
@@ -13603,7 +13603,7 @@
         <v>2.44799995422363</v>
       </c>
       <c r="G509" t="n">
-        <v>2.09790802001953</v>
+        <v>2.09790825843811</v>
       </c>
       <c r="H509" t="s">
         <v>8</v>
@@ -13629,7 +13629,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G510" t="n">
-        <v>2.09962201118469</v>
+        <v>2.09962177276611</v>
       </c>
       <c r="H510" t="s">
         <v>8</v>
@@ -13655,7 +13655,7 @@
         <v>2.41599988937378</v>
       </c>
       <c r="G511" t="n">
-        <v>2.07048416137695</v>
+        <v>2.07048439979553</v>
       </c>
       <c r="H511" t="s">
         <v>8</v>
@@ -13681,7 +13681,7 @@
         <v>2.4760000705719</v>
       </c>
       <c r="G512" t="n">
-        <v>2.12190365791321</v>
+        <v>2.12190389633179</v>
       </c>
       <c r="H512" t="s">
         <v>8</v>
@@ -13707,7 +13707,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G513" t="n">
-        <v>2.09962201118469</v>
+        <v>2.09962177276611</v>
       </c>
       <c r="H513" t="s">
         <v>8</v>
@@ -13785,7 +13785,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G516" t="n">
-        <v>2.08248233795166</v>
+        <v>2.08248209953308</v>
       </c>
       <c r="H516" t="s">
         <v>8</v>
@@ -13863,7 +13863,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G519" t="n">
-        <v>2.08248233795166</v>
+        <v>2.08248209953308</v>
       </c>
       <c r="H519" t="s">
         <v>8</v>
@@ -13889,7 +13889,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G520" t="n">
-        <v>2.08248233795166</v>
+        <v>2.08248209953308</v>
       </c>
       <c r="H520" t="s">
         <v>8</v>
@@ -13915,7 +13915,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G521" t="n">
-        <v>2.03963279724121</v>
+        <v>2.03963303565979</v>
       </c>
       <c r="H521" t="s">
         <v>8</v>
@@ -13941,7 +13941,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G522" t="n">
-        <v>2.03963279724121</v>
+        <v>2.03963303565979</v>
       </c>
       <c r="H522" t="s">
         <v>8</v>
@@ -13967,7 +13967,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G523" t="n">
-        <v>2.03963279724121</v>
+        <v>2.03963303565979</v>
       </c>
       <c r="H523" t="s">
         <v>8</v>
@@ -13993,7 +13993,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G524" t="n">
-        <v>2.03963279724121</v>
+        <v>2.03963303565979</v>
       </c>
       <c r="H524" t="s">
         <v>8</v>
@@ -14149,7 +14149,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G530" t="n">
-        <v>2.09962201118469</v>
+        <v>2.09962177276611</v>
       </c>
       <c r="H530" t="s">
         <v>8</v>
@@ -14331,7 +14331,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G537" t="n">
-        <v>2.01392292976379</v>
+        <v>2.01392316818237</v>
       </c>
       <c r="H537" t="s">
         <v>8</v>
@@ -14487,7 +14487,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G543" t="n">
-        <v>2.09962201118469</v>
+        <v>2.09962177276611</v>
       </c>
       <c r="H543" t="s">
         <v>8</v>
@@ -14513,7 +14513,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G544" t="n">
-        <v>2.09962201118469</v>
+        <v>2.09962177276611</v>
       </c>
       <c r="H544" t="s">
         <v>8</v>
@@ -14539,7 +14539,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G545" t="n">
-        <v>2.09962201118469</v>
+        <v>2.09962177276611</v>
       </c>
       <c r="H545" t="s">
         <v>8</v>
@@ -14591,7 +14591,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G547" t="n">
-        <v>2.08248233795166</v>
+        <v>2.08248209953308</v>
       </c>
       <c r="H547" t="s">
         <v>8</v>
@@ -14643,7 +14643,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G549" t="n">
-        <v>2.03963279724121</v>
+        <v>2.03963303565979</v>
       </c>
       <c r="H549" t="s">
         <v>8</v>
@@ -14669,7 +14669,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G550" t="n">
-        <v>2.08248233795166</v>
+        <v>2.08248209953308</v>
       </c>
       <c r="H550" t="s">
         <v>8</v>
@@ -14695,7 +14695,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G551" t="n">
-        <v>2.03963279724121</v>
+        <v>2.03963303565979</v>
       </c>
       <c r="H551" t="s">
         <v>8</v>
@@ -14721,7 +14721,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G552" t="n">
-        <v>2.03963279724121</v>
+        <v>2.03963303565979</v>
       </c>
       <c r="H552" t="s">
         <v>8</v>
@@ -14747,7 +14747,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G553" t="n">
-        <v>2.08248233795166</v>
+        <v>2.08248209953308</v>
       </c>
       <c r="H553" t="s">
         <v>8</v>
@@ -14799,7 +14799,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G555" t="n">
-        <v>2.06534218788147</v>
+        <v>2.06534266471863</v>
       </c>
       <c r="H555" t="s">
         <v>8</v>
@@ -14825,7 +14825,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G556" t="n">
-        <v>2.03963279724121</v>
+        <v>2.03963303565979</v>
       </c>
       <c r="H556" t="s">
         <v>8</v>
@@ -14851,7 +14851,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G557" t="n">
-        <v>2.1167619228363</v>
+        <v>2.11676168441772</v>
       </c>
       <c r="H557" t="s">
         <v>8</v>
@@ -14903,7 +14903,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G559" t="n">
-        <v>2.06534218788147</v>
+        <v>2.06534266471863</v>
       </c>
       <c r="H559" t="s">
         <v>8</v>
@@ -14929,7 +14929,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G560" t="n">
-        <v>2.06534218788147</v>
+        <v>2.06534266471863</v>
       </c>
       <c r="H560" t="s">
         <v>8</v>
@@ -14981,7 +14981,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G562" t="n">
-        <v>2.08248233795166</v>
+        <v>2.08248209953308</v>
       </c>
       <c r="H562" t="s">
         <v>8</v>
@@ -15007,7 +15007,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G563" t="n">
-        <v>2.08248233795166</v>
+        <v>2.08248209953308</v>
       </c>
       <c r="H563" t="s">
         <v>8</v>
@@ -15085,7 +15085,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G566" t="n">
-        <v>2.12533140182495</v>
+        <v>2.12533164024353</v>
       </c>
       <c r="H566" t="s">
         <v>8</v>
@@ -15189,7 +15189,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G570" t="n">
-        <v>2.09962201118469</v>
+        <v>2.09962177276611</v>
       </c>
       <c r="H570" t="s">
         <v>8</v>
@@ -15293,7 +15293,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G574" t="n">
-        <v>2.09962201118469</v>
+        <v>2.09962177276611</v>
       </c>
       <c r="H574" t="s">
         <v>8</v>
@@ -15345,7 +15345,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G576" t="n">
-        <v>2.09962201118469</v>
+        <v>2.09962177276611</v>
       </c>
       <c r="H576" t="s">
         <v>8</v>
@@ -15371,7 +15371,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G577" t="n">
-        <v>2.13390135765076</v>
+        <v>2.13390159606934</v>
       </c>
       <c r="H577" t="s">
         <v>8</v>
@@ -15449,7 +15449,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G580" t="n">
-        <v>2.13390135765076</v>
+        <v>2.13390159606934</v>
       </c>
       <c r="H580" t="s">
         <v>8</v>
@@ -15709,7 +15709,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G590" t="n">
-        <v>2.17675113677979</v>
+        <v>2.17675089836121</v>
       </c>
       <c r="H590" t="s">
         <v>8</v>
@@ -15761,7 +15761,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G592" t="n">
-        <v>2.29672932624817</v>
+        <v>2.29672956466675</v>
       </c>
       <c r="H592" t="s">
         <v>8</v>
@@ -15787,7 +15787,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G593" t="n">
-        <v>2.29672932624817</v>
+        <v>2.29672956466675</v>
       </c>
       <c r="H593" t="s">
         <v>8</v>
@@ -15891,7 +15891,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G597" t="n">
-        <v>2.44241714477539</v>
+        <v>2.44241738319397</v>
       </c>
       <c r="H597" t="s">
         <v>8</v>
@@ -15969,7 +15969,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G600" t="n">
-        <v>2.47669696807861</v>
+        <v>2.47669720649719</v>
       </c>
       <c r="H600" t="s">
         <v>8</v>
@@ -16125,7 +16125,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G606" t="n">
-        <v>2.61381506919861</v>
+        <v>2.61381530761719</v>
       </c>
       <c r="H606" t="s">
         <v>8</v>
@@ -16151,7 +16151,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G607" t="n">
-        <v>2.55382585525513</v>
+        <v>2.55382609367371</v>
       </c>
       <c r="H607" t="s">
         <v>8</v>
@@ -16177,7 +16177,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G608" t="n">
-        <v>2.63447332382202</v>
+        <v>2.63447308540344</v>
       </c>
       <c r="H608" t="s">
         <v>8</v>
@@ -16255,7 +16255,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G611" t="n">
-        <v>2.61655139923096</v>
+        <v>2.61655163764954</v>
       </c>
       <c r="H611" t="s">
         <v>8</v>
@@ -16281,7 +16281,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G612" t="n">
-        <v>2.55382561683655</v>
+        <v>2.55382585525513</v>
       </c>
       <c r="H612" t="s">
         <v>8</v>
@@ -16463,7 +16463,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G619" t="n">
-        <v>2.45525741577148</v>
+        <v>2.45525717735291</v>
       </c>
       <c r="H619" t="s">
         <v>8</v>
@@ -16489,7 +16489,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G620" t="n">
-        <v>2.45525741577148</v>
+        <v>2.45525717735291</v>
       </c>
       <c r="H620" t="s">
         <v>8</v>
@@ -16567,7 +16567,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G623" t="n">
-        <v>2.55382561683655</v>
+        <v>2.55382585525513</v>
       </c>
       <c r="H623" t="s">
         <v>8</v>
@@ -16593,7 +16593,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G624" t="n">
-        <v>2.57174754142761</v>
+        <v>2.57174730300903</v>
       </c>
       <c r="H624" t="s">
         <v>8</v>
@@ -16619,7 +16619,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G625" t="n">
-        <v>2.57174754142761</v>
+        <v>2.57174730300903</v>
       </c>
       <c r="H625" t="s">
         <v>8</v>
@@ -16645,7 +16645,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G626" t="n">
-        <v>2.55382561683655</v>
+        <v>2.55382585525513</v>
       </c>
       <c r="H626" t="s">
         <v>8</v>
@@ -16671,7 +16671,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G627" t="n">
-        <v>2.51798295974731</v>
+        <v>2.51798272132874</v>
       </c>
       <c r="H627" t="s">
         <v>8</v>
@@ -16749,7 +16749,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G630" t="n">
-        <v>2.51798295974731</v>
+        <v>2.51798272132874</v>
       </c>
       <c r="H630" t="s">
         <v>8</v>
@@ -16775,7 +16775,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G631" t="n">
-        <v>2.53590416908264</v>
+        <v>2.53590440750122</v>
       </c>
       <c r="H631" t="s">
         <v>8</v>
@@ -16879,7 +16879,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G635" t="n">
-        <v>2.51798295974731</v>
+        <v>2.51798272132874</v>
       </c>
       <c r="H635" t="s">
         <v>8</v>
@@ -16931,7 +16931,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G637" t="n">
-        <v>2.55382561683655</v>
+        <v>2.55382585525513</v>
       </c>
       <c r="H637" t="s">
         <v>8</v>
@@ -16957,7 +16957,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G638" t="n">
-        <v>2.55382561683655</v>
+        <v>2.55382585525513</v>
       </c>
       <c r="H638" t="s">
         <v>8</v>
@@ -16983,7 +16983,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G639" t="n">
-        <v>2.53590416908264</v>
+        <v>2.53590440750122</v>
       </c>
       <c r="H639" t="s">
         <v>8</v>
@@ -17009,7 +17009,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G640" t="n">
-        <v>2.53590416908264</v>
+        <v>2.53590440750122</v>
       </c>
       <c r="H640" t="s">
         <v>8</v>
@@ -17035,7 +17035,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G641" t="n">
-        <v>2.53590416908264</v>
+        <v>2.53590440750122</v>
       </c>
       <c r="H641" t="s">
         <v>8</v>
@@ -17061,7 +17061,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G642" t="n">
-        <v>2.53590416908264</v>
+        <v>2.53590440750122</v>
       </c>
       <c r="H642" t="s">
         <v>8</v>
@@ -17087,7 +17087,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G643" t="n">
-        <v>2.53590416908264</v>
+        <v>2.53590440750122</v>
       </c>
       <c r="H643" t="s">
         <v>8</v>
@@ -17139,7 +17139,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G645" t="n">
-        <v>2.53590416908264</v>
+        <v>2.53590440750122</v>
       </c>
       <c r="H645" t="s">
         <v>8</v>
@@ -17165,7 +17165,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G646" t="n">
-        <v>2.47317862510681</v>
+        <v>2.47317886352539</v>
       </c>
       <c r="H646" t="s">
         <v>8</v>
@@ -17191,7 +17191,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G647" t="n">
-        <v>2.51798295974731</v>
+        <v>2.51798272132874</v>
       </c>
       <c r="H647" t="s">
         <v>8</v>
@@ -17217,7 +17217,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G648" t="n">
-        <v>2.51798295974731</v>
+        <v>2.51798272132874</v>
       </c>
       <c r="H648" t="s">
         <v>8</v>
@@ -17243,7 +17243,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G649" t="n">
-        <v>2.51798295974731</v>
+        <v>2.51798272132874</v>
       </c>
       <c r="H649" t="s">
         <v>8</v>
@@ -17399,7 +17399,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G655" t="n">
-        <v>2.55382561683655</v>
+        <v>2.55382585525513</v>
       </c>
       <c r="H655" t="s">
         <v>8</v>
@@ -17451,7 +17451,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G657" t="n">
-        <v>2.75992441177368</v>
+        <v>2.7599241733551</v>
       </c>
       <c r="H657" t="s">
         <v>8</v>
@@ -17529,7 +17529,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G660" t="n">
-        <v>2.75992441177368</v>
+        <v>2.7599241733551</v>
       </c>
       <c r="H660" t="s">
         <v>8</v>
@@ -17711,7 +17711,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G667" t="n">
-        <v>2.75096321105957</v>
+        <v>2.75096344947815</v>
       </c>
       <c r="H667" t="s">
         <v>8</v>
@@ -17737,7 +17737,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G668" t="n">
-        <v>2.67031621932983</v>
+        <v>2.67031645774841</v>
       </c>
       <c r="H668" t="s">
         <v>8</v>
@@ -17763,7 +17763,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G669" t="n">
-        <v>2.63447332382202</v>
+        <v>2.63447308540344</v>
       </c>
       <c r="H669" t="s">
         <v>8</v>
@@ -17815,7 +17815,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G671" t="n">
-        <v>2.75096321105957</v>
+        <v>2.75096344947815</v>
       </c>
       <c r="H671" t="s">
         <v>8</v>
@@ -17893,7 +17893,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G674" t="n">
-        <v>2.65239477157593</v>
+        <v>2.65239453315735</v>
       </c>
       <c r="H674" t="s">
         <v>8</v>
@@ -17919,7 +17919,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G675" t="n">
-        <v>2.65239477157593</v>
+        <v>2.65239453315735</v>
       </c>
       <c r="H675" t="s">
         <v>8</v>
@@ -17971,7 +17971,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G677" t="n">
-        <v>2.67031621932983</v>
+        <v>2.67031645774841</v>
       </c>
       <c r="H677" t="s">
         <v>8</v>
@@ -17997,7 +17997,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G678" t="n">
-        <v>2.67031621932983</v>
+        <v>2.67031645774841</v>
       </c>
       <c r="H678" t="s">
         <v>8</v>
@@ -18049,7 +18049,7 @@
         <v>3</v>
       </c>
       <c r="G680" t="n">
-        <v>2.68823766708374</v>
+        <v>2.68823790550232</v>
       </c>
       <c r="H680" t="s">
         <v>8</v>
@@ -18101,7 +18101,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G682" t="n">
-        <v>2.75096321105957</v>
+        <v>2.75096344947815</v>
       </c>
       <c r="H682" t="s">
         <v>8</v>
@@ -18127,7 +18127,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G683" t="n">
-        <v>2.73304176330566</v>
+        <v>2.73304200172424</v>
       </c>
       <c r="H683" t="s">
         <v>8</v>
@@ -18153,7 +18153,7 @@
         <v>3</v>
       </c>
       <c r="G684" t="n">
-        <v>2.68823766708374</v>
+        <v>2.68823790550232</v>
       </c>
       <c r="H684" t="s">
         <v>8</v>
@@ -18179,7 +18179,7 @@
         <v>3</v>
       </c>
       <c r="G685" t="n">
-        <v>2.68823766708374</v>
+        <v>2.68823790550232</v>
       </c>
       <c r="H685" t="s">
         <v>8</v>
@@ -18205,7 +18205,7 @@
         <v>3</v>
       </c>
       <c r="G686" t="n">
-        <v>2.68823766708374</v>
+        <v>2.68823790550232</v>
       </c>
       <c r="H686" t="s">
         <v>8</v>
@@ -18257,7 +18257,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G688" t="n">
-        <v>2.75096321105957</v>
+        <v>2.75096344947815</v>
       </c>
       <c r="H688" t="s">
         <v>8</v>
@@ -18309,7 +18309,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G690" t="n">
-        <v>2.69719886779785</v>
+        <v>2.69719862937927</v>
       </c>
       <c r="H690" t="s">
         <v>8</v>
@@ -18335,7 +18335,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G691" t="n">
-        <v>2.67927694320679</v>
+        <v>2.67927718162537</v>
       </c>
       <c r="H691" t="s">
         <v>8</v>
@@ -18361,7 +18361,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G692" t="n">
-        <v>2.75992441177368</v>
+        <v>2.7599241733551</v>
       </c>
       <c r="H692" t="s">
         <v>8</v>
@@ -18413,7 +18413,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G694" t="n">
-        <v>2.86745357513428</v>
+        <v>2.86745381355286</v>
       </c>
       <c r="H694" t="s">
         <v>8</v>
@@ -18465,7 +18465,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G696" t="n">
-        <v>2.73304176330566</v>
+        <v>2.73304200172424</v>
       </c>
       <c r="H696" t="s">
         <v>8</v>
@@ -18491,7 +18491,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G697" t="n">
-        <v>2.75096321105957</v>
+        <v>2.75096344947815</v>
       </c>
       <c r="H697" t="s">
         <v>8</v>
@@ -18543,7 +18543,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G699" t="n">
-        <v>2.75992441177368</v>
+        <v>2.7599241733551</v>
       </c>
       <c r="H699" t="s">
         <v>8</v>
@@ -18569,7 +18569,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G700" t="n">
-        <v>2.75096321105957</v>
+        <v>2.75096344947815</v>
       </c>
       <c r="H700" t="s">
         <v>8</v>
@@ -18595,7 +18595,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G701" t="n">
-        <v>2.75096321105957</v>
+        <v>2.75096344947815</v>
       </c>
       <c r="H701" t="s">
         <v>8</v>
@@ -18621,7 +18621,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G702" t="n">
-        <v>2.75096321105957</v>
+        <v>2.75096344947815</v>
       </c>
       <c r="H702" t="s">
         <v>8</v>
@@ -18673,7 +18673,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G704" t="n">
-        <v>2.65239477157593</v>
+        <v>2.65239453315735</v>
       </c>
       <c r="H704" t="s">
         <v>8</v>
@@ -18699,7 +18699,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G705" t="n">
-        <v>2.69719886779785</v>
+        <v>2.69719862937927</v>
       </c>
       <c r="H705" t="s">
         <v>8</v>
@@ -18725,7 +18725,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G706" t="n">
-        <v>2.67927694320679</v>
+        <v>2.67927718162537</v>
       </c>
       <c r="H706" t="s">
         <v>8</v>
@@ -18751,7 +18751,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G707" t="n">
-        <v>2.6434338092804</v>
+        <v>2.64343404769897</v>
       </c>
       <c r="H707" t="s">
         <v>8</v>
@@ -18777,7 +18777,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G708" t="n">
-        <v>2.63447332382202</v>
+        <v>2.63447308540344</v>
       </c>
       <c r="H708" t="s">
         <v>8</v>
@@ -18881,7 +18881,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G712" t="n">
-        <v>2.55382561683655</v>
+        <v>2.55382585525513</v>
       </c>
       <c r="H712" t="s">
         <v>8</v>
@@ -18907,7 +18907,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G713" t="n">
-        <v>2.61655139923096</v>
+        <v>2.61655163764954</v>
       </c>
       <c r="H713" t="s">
         <v>8</v>
@@ -19037,7 +19037,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G718" t="n">
-        <v>2.57174754142761</v>
+        <v>2.57174730300903</v>
       </c>
       <c r="H718" t="s">
         <v>8</v>
@@ -19089,7 +19089,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G720" t="n">
-        <v>2.61655139923096</v>
+        <v>2.61655163764954</v>
       </c>
       <c r="H720" t="s">
         <v>8</v>
@@ -19115,7 +19115,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G721" t="n">
-        <v>2.61655139923096</v>
+        <v>2.61655163764954</v>
       </c>
       <c r="H721" t="s">
         <v>8</v>
@@ -19271,7 +19271,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G727" t="n">
-        <v>2.61655139923096</v>
+        <v>2.61655163764954</v>
       </c>
       <c r="H727" t="s">
         <v>8</v>
@@ -19297,7 +19297,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G728" t="n">
-        <v>2.61655139923096</v>
+        <v>2.61655163764954</v>
       </c>
       <c r="H728" t="s">
         <v>8</v>
@@ -19323,7 +19323,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G729" t="n">
-        <v>2.61655139923096</v>
+        <v>2.61655163764954</v>
       </c>
       <c r="H729" t="s">
         <v>8</v>
@@ -19375,7 +19375,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G731" t="n">
-        <v>2.61655139923096</v>
+        <v>2.61655163764954</v>
       </c>
       <c r="H731" t="s">
         <v>8</v>
@@ -19479,7 +19479,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G735" t="n">
-        <v>2.45525741577148</v>
+        <v>2.45525717735291</v>
       </c>
       <c r="H735" t="s">
         <v>8</v>
@@ -19557,7 +19557,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G738" t="n">
-        <v>2.57174754142761</v>
+        <v>2.57174730300903</v>
       </c>
       <c r="H738" t="s">
         <v>8</v>
@@ -19583,7 +19583,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G739" t="n">
-        <v>2.45525741577148</v>
+        <v>2.45525717735291</v>
       </c>
       <c r="H739" t="s">
         <v>8</v>
@@ -19765,7 +19765,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G746" t="n">
-        <v>2.41941404342651</v>
+        <v>2.41941428184509</v>
       </c>
       <c r="H746" t="s">
         <v>8</v>
@@ -19817,7 +19817,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G748" t="n">
-        <v>2.57174754142761</v>
+        <v>2.57174730300903</v>
       </c>
       <c r="H748" t="s">
         <v>8</v>
@@ -19869,7 +19869,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G750" t="n">
-        <v>2.57174754142761</v>
+        <v>2.57174730300903</v>
       </c>
       <c r="H750" t="s">
         <v>8</v>
@@ -19895,7 +19895,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G751" t="n">
-        <v>2.57174754142761</v>
+        <v>2.57174730300903</v>
       </c>
       <c r="H751" t="s">
         <v>8</v>
@@ -19921,7 +19921,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G752" t="n">
-        <v>2.57174754142761</v>
+        <v>2.57174730300903</v>
       </c>
       <c r="H752" t="s">
         <v>8</v>
@@ -19973,7 +19973,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G754" t="n">
-        <v>2.55382561683655</v>
+        <v>2.55382585525513</v>
       </c>
       <c r="H754" t="s">
         <v>8</v>
@@ -19999,7 +19999,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G755" t="n">
-        <v>2.55382561683655</v>
+        <v>2.55382585525513</v>
       </c>
       <c r="H755" t="s">
         <v>8</v>
@@ -20025,7 +20025,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G756" t="n">
-        <v>2.53590416908264</v>
+        <v>2.53590440750122</v>
       </c>
       <c r="H756" t="s">
         <v>8</v>
@@ -20051,7 +20051,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G757" t="n">
-        <v>2.53590416908264</v>
+        <v>2.53590440750122</v>
       </c>
       <c r="H757" t="s">
         <v>8</v>
@@ -20077,7 +20077,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G758" t="n">
-        <v>2.53590416908264</v>
+        <v>2.53590440750122</v>
       </c>
       <c r="H758" t="s">
         <v>8</v>
@@ -20207,7 +20207,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G763" t="n">
-        <v>2.53590416908264</v>
+        <v>2.53590440750122</v>
       </c>
       <c r="H763" t="s">
         <v>8</v>
@@ -20233,7 +20233,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G764" t="n">
-        <v>2.53590416908264</v>
+        <v>2.53590440750122</v>
       </c>
       <c r="H764" t="s">
         <v>8</v>
@@ -20285,7 +20285,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G766" t="n">
-        <v>2.63447332382202</v>
+        <v>2.63447308540344</v>
       </c>
       <c r="H766" t="s">
         <v>8</v>
@@ -20311,7 +20311,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G767" t="n">
-        <v>2.67031621932983</v>
+        <v>2.67031645774841</v>
       </c>
       <c r="H767" t="s">
         <v>8</v>
@@ -20363,7 +20363,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G769" t="n">
-        <v>2.67031621932983</v>
+        <v>2.67031645774841</v>
       </c>
       <c r="H769" t="s">
         <v>8</v>
@@ -20389,7 +20389,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G770" t="n">
-        <v>2.69719886779785</v>
+        <v>2.69719862937927</v>
       </c>
       <c r="H770" t="s">
         <v>8</v>
@@ -20415,7 +20415,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G771" t="n">
-        <v>2.67927694320679</v>
+        <v>2.67927718162537</v>
       </c>
       <c r="H771" t="s">
         <v>8</v>
@@ -20441,7 +20441,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G772" t="n">
-        <v>2.67031621932983</v>
+        <v>2.67031645774841</v>
       </c>
       <c r="H772" t="s">
         <v>8</v>
@@ -20493,7 +20493,7 @@
         <v>3</v>
       </c>
       <c r="G774" t="n">
-        <v>2.68823766708374</v>
+        <v>2.68823790550232</v>
       </c>
       <c r="H774" t="s">
         <v>8</v>
@@ -20519,7 +20519,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G775" t="n">
-        <v>2.69719886779785</v>
+        <v>2.69719862937927</v>
       </c>
       <c r="H775" t="s">
         <v>8</v>
@@ -20545,7 +20545,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G776" t="n">
-        <v>2.67927694320679</v>
+        <v>2.67927718162537</v>
       </c>
       <c r="H776" t="s">
         <v>8</v>
@@ -20571,7 +20571,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G777" t="n">
-        <v>2.75096321105957</v>
+        <v>2.75096344947815</v>
       </c>
       <c r="H777" t="s">
         <v>8</v>
@@ -20597,7 +20597,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G778" t="n">
-        <v>2.81368899345398</v>
+        <v>2.81368923187256</v>
       </c>
       <c r="H778" t="s">
         <v>8</v>
@@ -20649,7 +20649,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G780" t="n">
-        <v>2.93914008140564</v>
+        <v>2.93914031982422</v>
       </c>
       <c r="H780" t="s">
         <v>8</v>
@@ -20675,7 +20675,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G781" t="n">
-        <v>2.87641453742981</v>
+        <v>2.87641477584839</v>
       </c>
       <c r="H781" t="s">
         <v>8</v>
@@ -20727,7 +20727,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G783" t="n">
-        <v>2.82264971733093</v>
+        <v>2.82264995574951</v>
       </c>
       <c r="H783" t="s">
         <v>8</v>
@@ -20805,7 +20805,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G786" t="n">
-        <v>2.82264971733093</v>
+        <v>2.82264995574951</v>
       </c>
       <c r="H786" t="s">
         <v>8</v>
@@ -21013,7 +21013,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G794" t="n">
-        <v>2.87641453742981</v>
+        <v>2.87641477584839</v>
       </c>
       <c r="H794" t="s">
         <v>8</v>
@@ -21039,7 +21039,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G795" t="n">
-        <v>2.87641453742981</v>
+        <v>2.87641477584839</v>
       </c>
       <c r="H795" t="s">
         <v>8</v>
@@ -21091,7 +21091,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G797" t="n">
-        <v>3.12731647491455</v>
+        <v>3.12731671333313</v>
       </c>
       <c r="H797" t="s">
         <v>8</v>
@@ -21169,7 +21169,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G800" t="n">
-        <v>3.19004201889038</v>
+        <v>3.19004225730896</v>
       </c>
       <c r="H800" t="s">
         <v>8</v>
@@ -21195,7 +21195,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G801" t="n">
-        <v>3.25276780128479</v>
+        <v>3.25276803970337</v>
       </c>
       <c r="H801" t="s">
         <v>8</v>
@@ -21247,7 +21247,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G803" t="n">
-        <v>3.25276780128479</v>
+        <v>3.25276803970337</v>
       </c>
       <c r="H803" t="s">
         <v>8</v>
@@ -21273,7 +21273,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G804" t="n">
-        <v>3.19004201889038</v>
+        <v>3.19004225730896</v>
       </c>
       <c r="H804" t="s">
         <v>8</v>
@@ -21299,7 +21299,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G805" t="n">
-        <v>3.28861117362976</v>
+        <v>3.28861093521118</v>
       </c>
       <c r="H805" t="s">
         <v>8</v>
@@ -21325,7 +21325,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G806" t="n">
-        <v>3.29757189750671</v>
+        <v>3.29757165908813</v>
       </c>
       <c r="H806" t="s">
         <v>8</v>
@@ -21481,7 +21481,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G812" t="n">
-        <v>3.34237575531006</v>
+        <v>3.34237551689148</v>
       </c>
       <c r="H812" t="s">
         <v>8</v>
@@ -21507,7 +21507,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G813" t="n">
-        <v>3.42302298545837</v>
+        <v>3.42302274703979</v>
       </c>
       <c r="H813" t="s">
         <v>8</v>
@@ -21559,7 +21559,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G815" t="n">
-        <v>3.40510129928589</v>
+        <v>3.40510106086731</v>
       </c>
       <c r="H815" t="s">
         <v>8</v>
@@ -21611,7 +21611,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G817" t="n">
-        <v>3.36925792694092</v>
+        <v>3.3692581653595</v>
       </c>
       <c r="H817" t="s">
         <v>8</v>
@@ -21663,7 +21663,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G819" t="n">
-        <v>3.40510129928589</v>
+        <v>3.40510106086731</v>
       </c>
       <c r="H819" t="s">
         <v>8</v>
@@ -21715,7 +21715,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G821" t="n">
-        <v>3.45886564254761</v>
+        <v>3.45886588096619</v>
       </c>
       <c r="H821" t="s">
         <v>8</v>
@@ -21741,7 +21741,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G822" t="n">
-        <v>3.48574876785278</v>
+        <v>3.48574829101562</v>
       </c>
       <c r="H822" t="s">
         <v>8</v>
@@ -21845,7 +21845,7 @@
         <v>4</v>
       </c>
       <c r="G826" t="n">
-        <v>3.58431696891785</v>
+        <v>3.58431720733643</v>
       </c>
       <c r="H826" t="s">
         <v>8</v>
@@ -21923,7 +21923,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G829" t="n">
-        <v>3.59327793121338</v>
+        <v>3.59327816963196</v>
       </c>
       <c r="H829" t="s">
         <v>8</v>
@@ -21975,7 +21975,7 @@
         <v>4</v>
       </c>
       <c r="G831" t="n">
-        <v>3.58431696891785</v>
+        <v>3.58431720733643</v>
       </c>
       <c r="H831" t="s">
         <v>8</v>
@@ -22001,7 +22001,7 @@
         <v>4</v>
       </c>
       <c r="G832" t="n">
-        <v>3.58431696891785</v>
+        <v>3.58431720733643</v>
       </c>
       <c r="H832" t="s">
         <v>8</v>
@@ -22027,7 +22027,7 @@
         <v>3.9300000667572</v>
       </c>
       <c r="G833" t="n">
-        <v>3.52159142494202</v>
+        <v>3.5215916633606</v>
       </c>
       <c r="H833" t="s">
         <v>8</v>
@@ -22053,7 +22053,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G834" t="n">
-        <v>3.51263093948364</v>
+        <v>3.51263070106506</v>
       </c>
       <c r="H834" t="s">
         <v>8</v>
@@ -22079,7 +22079,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G835" t="n">
-        <v>3.51263093948364</v>
+        <v>3.51263070106506</v>
       </c>
       <c r="H835" t="s">
         <v>8</v>
@@ -22131,7 +22131,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G837" t="n">
-        <v>3.51263093948364</v>
+        <v>3.51263070106506</v>
       </c>
       <c r="H837" t="s">
         <v>8</v>
@@ -22183,7 +22183,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G839" t="n">
-        <v>3.45886564254761</v>
+        <v>3.45886588096619</v>
       </c>
       <c r="H839" t="s">
         <v>8</v>
@@ -22209,7 +22209,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G840" t="n">
-        <v>3.51263093948364</v>
+        <v>3.51263070106506</v>
       </c>
       <c r="H840" t="s">
         <v>8</v>
@@ -22235,7 +22235,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G841" t="n">
-        <v>3.60223889350891</v>
+        <v>3.60223865509033</v>
       </c>
       <c r="H841" t="s">
         <v>8</v>
@@ -22261,7 +22261,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G842" t="n">
-        <v>3.65600323677063</v>
+        <v>3.65600347518921</v>
       </c>
       <c r="H842" t="s">
         <v>8</v>
@@ -22287,7 +22287,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G843" t="n">
-        <v>3.65600323677063</v>
+        <v>3.65600347518921</v>
       </c>
       <c r="H843" t="s">
         <v>8</v>
@@ -22339,7 +22339,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G845" t="n">
-        <v>3.72768998146057</v>
+        <v>3.72768974304199</v>
       </c>
       <c r="H845" t="s">
         <v>8</v>
@@ -22365,7 +22365,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G846" t="n">
-        <v>3.71872925758362</v>
+        <v>3.71872901916504</v>
       </c>
       <c r="H846" t="s">
         <v>8</v>
@@ -22391,7 +22391,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G847" t="n">
-        <v>3.6918466091156</v>
+        <v>3.69184637069702</v>
       </c>
       <c r="H847" t="s">
         <v>8</v>
@@ -22417,7 +22417,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G848" t="n">
-        <v>3.70976781845093</v>
+        <v>3.70976829528809</v>
       </c>
       <c r="H848" t="s">
         <v>8</v>
@@ -22443,7 +22443,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G849" t="n">
-        <v>3.68288588523865</v>
+        <v>3.68288612365723</v>
       </c>
       <c r="H849" t="s">
         <v>8</v>
@@ -22495,7 +22495,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G851" t="n">
-        <v>3.70976781845093</v>
+        <v>3.70976829528809</v>
       </c>
       <c r="H851" t="s">
         <v>8</v>
@@ -22521,7 +22521,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G852" t="n">
-        <v>3.76353287696838</v>
+        <v>3.7635326385498</v>
       </c>
       <c r="H852" t="s">
         <v>8</v>
@@ -22599,7 +22599,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G855" t="n">
-        <v>3.79041504859924</v>
+        <v>3.7904155254364</v>
       </c>
       <c r="H855" t="s">
         <v>8</v>
@@ -22729,7 +22729,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G860" t="n">
-        <v>4.00759792327881</v>
+        <v>4.00759744644165</v>
       </c>
       <c r="H860" t="s">
         <v>8</v>
@@ -22781,7 +22781,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G862" t="n">
-        <v>3.81988835334778</v>
+        <v>3.81988859176636</v>
       </c>
       <c r="H862" t="s">
         <v>8</v>
@@ -23223,7 +23223,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G879" t="n">
-        <v>3.99821257591248</v>
+        <v>3.9982123374939</v>
       </c>
       <c r="H879" t="s">
         <v>8</v>
@@ -23249,7 +23249,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G880" t="n">
-        <v>3.99821257591248</v>
+        <v>3.9982123374939</v>
       </c>
       <c r="H880" t="s">
         <v>8</v>
@@ -23275,7 +23275,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G881" t="n">
-        <v>3.99821257591248</v>
+        <v>3.9982123374939</v>
       </c>
       <c r="H881" t="s">
         <v>8</v>
@@ -23301,7 +23301,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G882" t="n">
-        <v>3.99821257591248</v>
+        <v>3.9982123374939</v>
       </c>
       <c r="H882" t="s">
         <v>8</v>
@@ -23327,7 +23327,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G883" t="n">
-        <v>3.97944092750549</v>
+        <v>3.97944116592407</v>
       </c>
       <c r="H883" t="s">
         <v>8</v>
@@ -23353,7 +23353,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G884" t="n">
-        <v>3.85743021965027</v>
+        <v>3.85743045806885</v>
       </c>
       <c r="H884" t="s">
         <v>8</v>
@@ -23405,7 +23405,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G886" t="n">
-        <v>3.85743021965027</v>
+        <v>3.85743045806885</v>
       </c>
       <c r="H886" t="s">
         <v>8</v>
@@ -23431,7 +23431,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G887" t="n">
-        <v>3.81050252914429</v>
+        <v>3.81050276756287</v>
       </c>
       <c r="H887" t="s">
         <v>8</v>
@@ -23457,7 +23457,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G888" t="n">
-        <v>3.7448046207428</v>
+        <v>3.74480438232422</v>
       </c>
       <c r="H888" t="s">
         <v>8</v>
@@ -23483,7 +23483,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G889" t="n">
-        <v>3.89497232437134</v>
+        <v>3.89497208595276</v>
       </c>
       <c r="H889" t="s">
         <v>8</v>
@@ -23509,7 +23509,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G890" t="n">
-        <v>3.94189953804016</v>
+        <v>3.941899061203</v>
       </c>
       <c r="H890" t="s">
         <v>8</v>
@@ -23535,7 +23535,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G891" t="n">
-        <v>3.99821257591248</v>
+        <v>3.9982123374939</v>
       </c>
       <c r="H891" t="s">
         <v>8</v>
@@ -23561,7 +23561,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G892" t="n">
-        <v>4.00759792327881</v>
+        <v>4.00759744644165</v>
       </c>
       <c r="H892" t="s">
         <v>8</v>
@@ -23665,7 +23665,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G896" t="n">
-        <v>3.93251395225525</v>
+        <v>3.93251419067383</v>
       </c>
       <c r="H896" t="s">
         <v>8</v>
@@ -23691,7 +23691,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G897" t="n">
-        <v>3.93251395225525</v>
+        <v>3.93251419067383</v>
       </c>
       <c r="H897" t="s">
         <v>8</v>
@@ -23795,7 +23795,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G901" t="n">
-        <v>4.11083793640137</v>
+        <v>4.11083841323853</v>
       </c>
       <c r="H901" t="s">
         <v>8</v>
@@ -23821,7 +23821,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G902" t="n">
-        <v>4.11083793640137</v>
+        <v>4.11083841323853</v>
       </c>
       <c r="H902" t="s">
         <v>8</v>
@@ -24003,7 +24003,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G909" t="n">
-        <v>4.19530725479126</v>
+        <v>4.1953067779541</v>
       </c>
       <c r="H909" t="s">
         <v>8</v>
@@ -24107,7 +24107,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G913" t="n">
-        <v>4.26100587844849</v>
+        <v>4.26100540161133</v>
       </c>
       <c r="H913" t="s">
         <v>8</v>
@@ -24159,7 +24159,7 @@
         <v>4.63000011444092</v>
       </c>
       <c r="G915" t="n">
-        <v>4.34547472000122</v>
+        <v>4.34547519683838</v>
       </c>
       <c r="H915" t="s">
         <v>8</v>
@@ -24263,7 +24263,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G919" t="n">
-        <v>4.26100587844849</v>
+        <v>4.26100540161133</v>
       </c>
       <c r="H919" t="s">
         <v>8</v>
@@ -24419,7 +24419,7 @@
         <v>4.78999996185303</v>
       </c>
       <c r="G925" t="n">
-        <v>4.49564266204834</v>
+        <v>4.49564218521118</v>
       </c>
       <c r="H925" t="s">
         <v>8</v>
@@ -24523,7 +24523,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G929" t="n">
-        <v>4.54257011413574</v>
+        <v>4.54256963729858</v>
       </c>
       <c r="H929" t="s">
         <v>8</v>
@@ -24601,7 +24601,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G932" t="n">
-        <v>4.44871520996094</v>
+        <v>4.44871473312378</v>
       </c>
       <c r="H932" t="s">
         <v>8</v>
@@ -24705,7 +24705,7 @@
         <v>4.78999996185303</v>
       </c>
       <c r="G936" t="n">
-        <v>4.49564266204834</v>
+        <v>4.49564218521118</v>
       </c>
       <c r="H936" t="s">
         <v>8</v>
@@ -24757,7 +24757,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G938" t="n">
-        <v>4.44871520996094</v>
+        <v>4.44871473312378</v>
       </c>
       <c r="H938" t="s">
         <v>8</v>
@@ -24783,7 +24783,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G939" t="n">
-        <v>4.44871520996094</v>
+        <v>4.44871473312378</v>
       </c>
       <c r="H939" t="s">
         <v>8</v>
@@ -24939,7 +24939,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G945" t="n">
-        <v>4.39240169525146</v>
+        <v>4.39240217208862</v>
       </c>
       <c r="H945" t="s">
         <v>8</v>
@@ -24965,7 +24965,7 @@
         <v>4.63000011444092</v>
       </c>
       <c r="G946" t="n">
-        <v>4.34547472000122</v>
+        <v>4.34547519683838</v>
       </c>
       <c r="H946" t="s">
         <v>8</v>
@@ -25017,7 +25017,7 @@
         <v>4.63000011444092</v>
       </c>
       <c r="G948" t="n">
-        <v>4.34547472000122</v>
+        <v>4.34547519683838</v>
       </c>
       <c r="H948" t="s">
         <v>8</v>
@@ -25043,7 +25043,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G949" t="n">
-        <v>4.39240169525146</v>
+        <v>4.39240217208862</v>
       </c>
       <c r="H949" t="s">
         <v>8</v>
@@ -25121,7 +25121,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G952" t="n">
-        <v>4.24223470687866</v>
+        <v>4.2422342300415</v>
       </c>
       <c r="H952" t="s">
         <v>8</v>
@@ -25147,7 +25147,7 @@
         <v>4.59000015258789</v>
       </c>
       <c r="G953" t="n">
-        <v>4.30793333053589</v>
+        <v>4.30793285369873</v>
       </c>
       <c r="H953" t="s">
         <v>8</v>
@@ -25459,7 +25459,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G965" t="n">
-        <v>4.61765336990356</v>
+        <v>4.61765384674072</v>
       </c>
       <c r="H965" t="s">
         <v>8</v>
@@ -25511,7 +25511,7 @@
         <v>4.86999988555908</v>
       </c>
       <c r="G967" t="n">
-        <v>4.57072591781616</v>
+        <v>4.57072639465332</v>
       </c>
       <c r="H967" t="s">
         <v>8</v>
@@ -25563,7 +25563,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G969" t="n">
-        <v>4.80536270141602</v>
+        <v>4.80536317825317</v>
       </c>
       <c r="H969" t="s">
         <v>8</v>
@@ -25615,7 +25615,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G971" t="n">
-        <v>4.86167621612549</v>
+        <v>4.86167573928833</v>
       </c>
       <c r="H971" t="s">
         <v>8</v>
@@ -25641,7 +25641,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G972" t="n">
-        <v>4.84290504455566</v>
+        <v>4.84290456771851</v>
       </c>
       <c r="H972" t="s">
         <v>8</v>
@@ -25693,7 +25693,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G974" t="n">
-        <v>4.86167621612549</v>
+        <v>4.86167573928833</v>
       </c>
       <c r="H974" t="s">
         <v>8</v>
@@ -25719,7 +25719,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G975" t="n">
-        <v>4.86167621612549</v>
+        <v>4.86167573928833</v>
       </c>
       <c r="H975" t="s">
         <v>8</v>
@@ -25745,7 +25745,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G976" t="n">
-        <v>4.80536270141602</v>
+        <v>4.80536317825317</v>
       </c>
       <c r="H976" t="s">
         <v>8</v>
@@ -25823,7 +25823,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G979" t="n">
-        <v>4.84290504455566</v>
+        <v>4.84290456771851</v>
       </c>
       <c r="H979" t="s">
         <v>8</v>
@@ -25901,7 +25901,7 @@
         <v>4.82999992370605</v>
       </c>
       <c r="G982" t="n">
-        <v>4.53318405151367</v>
+        <v>4.53318452835083</v>
       </c>
       <c r="H982" t="s">
         <v>8</v>
@@ -25927,7 +25927,7 @@
         <v>4.78999996185303</v>
       </c>
       <c r="G983" t="n">
-        <v>4.49564266204834</v>
+        <v>4.49564218521118</v>
       </c>
       <c r="H983" t="s">
         <v>8</v>
@@ -25953,7 +25953,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G984" t="n">
-        <v>4.58011150360107</v>
+        <v>4.58011198043823</v>
       </c>
       <c r="H984" t="s">
         <v>8</v>
@@ -26031,7 +26031,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G987" t="n">
-        <v>4.73027944564819</v>
+        <v>4.73027896881104</v>
       </c>
       <c r="H987" t="s">
         <v>8</v>
@@ -26083,7 +26083,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G989" t="n">
-        <v>4.71150827407837</v>
+        <v>4.71150875091553</v>
       </c>
       <c r="H989" t="s">
         <v>8</v>
@@ -26213,7 +26213,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G994" t="n">
-        <v>4.84290504455566</v>
+        <v>4.84290456771851</v>
       </c>
       <c r="H994" t="s">
         <v>8</v>
@@ -26343,7 +26343,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G999" t="n">
-        <v>4.73027944564819</v>
+        <v>4.73027896881104</v>
       </c>
       <c r="H999" t="s">
         <v>8</v>
@@ -26395,7 +26395,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G1001" t="n">
-        <v>4.71150827407837</v>
+        <v>4.71150875091553</v>
       </c>
       <c r="H1001" t="s">
         <v>8</v>
@@ -26421,7 +26421,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G1002" t="n">
-        <v>4.73027944564819</v>
+        <v>4.73027896881104</v>
       </c>
       <c r="H1002" t="s">
         <v>8</v>
@@ -26447,7 +26447,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G1003" t="n">
-        <v>4.80536270141602</v>
+        <v>4.80536317825317</v>
       </c>
       <c r="H1003" t="s">
         <v>8</v>
@@ -26473,7 +26473,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G1004" t="n">
-        <v>4.95553112030029</v>
+        <v>4.95553064346313</v>
       </c>
       <c r="H1004" t="s">
         <v>8</v>
@@ -26525,7 +26525,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G1006" t="n">
-        <v>4.95553112030029</v>
+        <v>4.95553064346313</v>
       </c>
       <c r="H1006" t="s">
         <v>8</v>
@@ -26629,7 +26629,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G1010" t="n">
-        <v>4.99307250976562</v>
+        <v>4.99307298660278</v>
       </c>
       <c r="H1010" t="s">
         <v>8</v>
@@ -26655,7 +26655,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G1011" t="n">
-        <v>4.95553112030029</v>
+        <v>4.95553064346313</v>
       </c>
       <c r="H1011" t="s">
         <v>8</v>
@@ -26681,7 +26681,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G1012" t="n">
-        <v>4.99307250976562</v>
+        <v>4.99307298660278</v>
       </c>
       <c r="H1012" t="s">
         <v>8</v>
@@ -26759,7 +26759,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G1015" t="n">
-        <v>4.84290504455566</v>
+        <v>4.84290456771851</v>
       </c>
       <c r="H1015" t="s">
         <v>8</v>
@@ -26811,7 +26811,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G1017" t="n">
-        <v>4.86167621612549</v>
+        <v>4.86167573928833</v>
       </c>
       <c r="H1017" t="s">
         <v>8</v>
@@ -26837,7 +26837,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G1018" t="n">
-        <v>4.80536270141602</v>
+        <v>4.80536317825317</v>
       </c>
       <c r="H1018" t="s">
         <v>8</v>
@@ -26941,7 +26941,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G1022" t="n">
-        <v>4.84290504455566</v>
+        <v>4.84290456771851</v>
       </c>
       <c r="H1022" t="s">
         <v>8</v>
@@ -26967,7 +26967,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G1023" t="n">
-        <v>4.86167621612549</v>
+        <v>4.86167573928833</v>
       </c>
       <c r="H1023" t="s">
         <v>8</v>
@@ -26993,7 +26993,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G1024" t="n">
-        <v>4.84290504455566</v>
+        <v>4.84290456771851</v>
       </c>
       <c r="H1024" t="s">
         <v>8</v>
@@ -27019,7 +27019,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G1025" t="n">
-        <v>4.84290504455566</v>
+        <v>4.84290456771851</v>
       </c>
       <c r="H1025" t="s">
         <v>8</v>
@@ -27045,7 +27045,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G1026" t="n">
-        <v>4.84290504455566</v>
+        <v>4.84290456771851</v>
       </c>
       <c r="H1026" t="s">
         <v>8</v>
@@ -27071,7 +27071,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G1027" t="n">
-        <v>4.99307250976562</v>
+        <v>4.99307298660278</v>
       </c>
       <c r="H1027" t="s">
         <v>8</v>
@@ -27175,7 +27175,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G1031" t="n">
-        <v>6.28826808929443</v>
+        <v>6.28826761245728</v>
       </c>
       <c r="H1031" t="s">
         <v>8</v>
@@ -27305,7 +27305,7 @@
         <v>6.07999992370605</v>
       </c>
       <c r="G1036" t="n">
-        <v>5.70636892318726</v>
+        <v>5.7063684463501</v>
       </c>
       <c r="H1036" t="s">
         <v>8</v>
@@ -27487,7 +27487,7 @@
         <v>6.03999996185303</v>
       </c>
       <c r="G1043" t="n">
-        <v>5.66882658004761</v>
+        <v>5.66882705688477</v>
       </c>
       <c r="H1043" t="s">
         <v>8</v>
@@ -27513,7 +27513,7 @@
         <v>6.05999994277954</v>
       </c>
       <c r="G1044" t="n">
-        <v>5.68759727478027</v>
+        <v>5.68759775161743</v>
       </c>
       <c r="H1044" t="s">
         <v>8</v>
@@ -27591,7 +27591,7 @@
         <v>6.07999992370605</v>
       </c>
       <c r="G1047" t="n">
-        <v>5.70636892318726</v>
+        <v>5.7063684463501</v>
       </c>
       <c r="H1047" t="s">
         <v>8</v>
@@ -27617,7 +27617,7 @@
         <v>5.96000003814697</v>
       </c>
       <c r="G1048" t="n">
-        <v>5.59374284744263</v>
+        <v>5.59374332427979</v>
       </c>
       <c r="H1048" t="s">
         <v>8</v>
@@ -27747,7 +27747,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G1053" t="n">
-        <v>4.71150827407837</v>
+        <v>4.71150875091553</v>
       </c>
       <c r="H1053" t="s">
         <v>8</v>
@@ -27773,7 +27773,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G1054" t="n">
-        <v>4.86167621612549</v>
+        <v>4.86167573928833</v>
       </c>
       <c r="H1054" t="s">
         <v>8</v>
@@ -27851,7 +27851,7 @@
         <v>4.98999977111816</v>
       </c>
       <c r="G1057" t="n">
-        <v>4.68335199356079</v>
+        <v>4.68335151672363</v>
       </c>
       <c r="H1057" t="s">
         <v>8</v>
@@ -27903,7 +27903,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G1059" t="n">
-        <v>4.73027944564819</v>
+        <v>4.73027896881104</v>
       </c>
       <c r="H1059" t="s">
         <v>8</v>
@@ -27929,7 +27929,7 @@
         <v>4.78999996185303</v>
       </c>
       <c r="G1060" t="n">
-        <v>4.49564266204834</v>
+        <v>4.49564218521118</v>
       </c>
       <c r="H1060" t="s">
         <v>8</v>
@@ -27981,7 +27981,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G1062" t="n">
-        <v>3.85743021965027</v>
+        <v>3.85743045806885</v>
       </c>
       <c r="H1062" t="s">
         <v>8</v>
@@ -28033,7 +28033,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G1064" t="n">
-        <v>3.94189953804016</v>
+        <v>3.941899061203</v>
       </c>
       <c r="H1064" t="s">
         <v>8</v>
@@ -28137,7 +28137,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G1068" t="n">
-        <v>3.55709481239319</v>
+        <v>3.55709505081177</v>
       </c>
       <c r="H1068" t="s">
         <v>8</v>
@@ -28189,7 +28189,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G1070" t="n">
-        <v>3.37877082824707</v>
+        <v>3.37877106666565</v>
       </c>
       <c r="H1070" t="s">
         <v>8</v>
@@ -28215,7 +28215,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G1071" t="n">
-        <v>3.50078225135803</v>
+        <v>3.50078201293945</v>
       </c>
       <c r="H1071" t="s">
         <v>8</v>
@@ -28345,7 +28345,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G1076" t="n">
-        <v>3.81988835334778</v>
+        <v>3.81988859176636</v>
       </c>
       <c r="H1076" t="s">
         <v>8</v>
@@ -28475,7 +28475,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G1081" t="n">
-        <v>3.70726251602173</v>
+        <v>3.70726275444031</v>
       </c>
       <c r="H1081" t="s">
         <v>8</v>
@@ -28553,7 +28553,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G1084" t="n">
-        <v>3.85743021965027</v>
+        <v>3.85743045806885</v>
       </c>
       <c r="H1084" t="s">
         <v>8</v>
@@ -28579,7 +28579,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G1085" t="n">
-        <v>3.8386595249176</v>
+        <v>3.83865928649902</v>
       </c>
       <c r="H1085" t="s">
         <v>8</v>
@@ -28683,7 +28683,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G1089" t="n">
-        <v>3.94189953804016</v>
+        <v>3.941899061203</v>
       </c>
       <c r="H1089" t="s">
         <v>8</v>
@@ -28917,7 +28917,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G1098" t="n">
-        <v>4.16715049743652</v>
+        <v>4.16715097427368</v>
       </c>
       <c r="H1098" t="s">
         <v>8</v>
@@ -28943,7 +28943,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G1099" t="n">
-        <v>4.05452537536621</v>
+        <v>4.05452489852905</v>
       </c>
       <c r="H1099" t="s">
         <v>8</v>
@@ -29021,7 +29021,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G1102" t="n">
-        <v>3.97944092750549</v>
+        <v>3.97944116592407</v>
       </c>
       <c r="H1102" t="s">
         <v>8</v>
@@ -29047,7 +29047,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G1103" t="n">
-        <v>3.89497232437134</v>
+        <v>3.89497208595276</v>
       </c>
       <c r="H1103" t="s">
         <v>8</v>
@@ -29099,7 +29099,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G1105" t="n">
-        <v>3.85743021965027</v>
+        <v>3.85743045806885</v>
       </c>
       <c r="H1105" t="s">
         <v>8</v>
@@ -29125,7 +29125,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G1106" t="n">
-        <v>3.76357555389404</v>
+        <v>3.76357579231262</v>
       </c>
       <c r="H1106" t="s">
         <v>8</v>
@@ -29177,7 +29177,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G1108" t="n">
-        <v>3.7448046207428</v>
+        <v>3.74480438232422</v>
       </c>
       <c r="H1108" t="s">
         <v>8</v>
@@ -29203,7 +29203,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G1109" t="n">
-        <v>3.66972064971924</v>
+        <v>3.66972088813782</v>
       </c>
       <c r="H1109" t="s">
         <v>8</v>
@@ -29229,7 +29229,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G1110" t="n">
-        <v>3.76357555389404</v>
+        <v>3.76357579231262</v>
       </c>
       <c r="H1110" t="s">
         <v>8</v>
@@ -29307,7 +29307,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G1113" t="n">
-        <v>3.65094995498657</v>
+        <v>3.65094971656799</v>
       </c>
       <c r="H1113" t="s">
         <v>8</v>
@@ -29437,7 +29437,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G1118" t="n">
-        <v>3.95128512382507</v>
+        <v>3.95128488540649</v>
       </c>
       <c r="H1118" t="s">
         <v>8</v>
@@ -29463,7 +29463,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G1119" t="n">
-        <v>3.94189953804016</v>
+        <v>3.941899061203</v>
       </c>
       <c r="H1119" t="s">
         <v>8</v>
@@ -29489,7 +29489,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G1120" t="n">
-        <v>4.16715049743652</v>
+        <v>4.16715097427368</v>
       </c>
       <c r="H1120" t="s">
         <v>8</v>
@@ -29593,7 +29593,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G1124" t="n">
-        <v>4.24223470687866</v>
+        <v>4.2422342300415</v>
       </c>
       <c r="H1124" t="s">
         <v>8</v>
@@ -29723,7 +29723,7 @@
         <v>4.59000015258789</v>
       </c>
       <c r="G1129" t="n">
-        <v>4.30793333053589</v>
+        <v>4.30793285369873</v>
       </c>
       <c r="H1129" t="s">
         <v>8</v>
@@ -29853,7 +29853,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G1134" t="n">
-        <v>4.39240169525146</v>
+        <v>4.39240217208862</v>
       </c>
       <c r="H1134" t="s">
         <v>8</v>
@@ -29879,7 +29879,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G1135" t="n">
-        <v>4.24223470687866</v>
+        <v>4.2422342300415</v>
       </c>
       <c r="H1135" t="s">
         <v>8</v>
@@ -30009,7 +30009,7 @@
         <v>4.42999982833862</v>
       </c>
       <c r="G1140" t="n">
-        <v>4.15776491165161</v>
+        <v>4.15776538848877</v>
       </c>
       <c r="H1140" t="s">
         <v>8</v>
@@ -30035,7 +30035,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G1141" t="n">
-        <v>4.19530725479126</v>
+        <v>4.1953067779541</v>
       </c>
       <c r="H1141" t="s">
         <v>8</v>
@@ -30165,7 +30165,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G1146" t="n">
-        <v>3.94189953804016</v>
+        <v>3.941899061203</v>
       </c>
       <c r="H1146" t="s">
         <v>8</v>
@@ -30269,7 +30269,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G1150" t="n">
-        <v>3.81050252914429</v>
+        <v>3.81050276756287</v>
       </c>
       <c r="H1150" t="s">
         <v>8</v>
@@ -30373,7 +30373,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G1154" t="n">
-        <v>4.44871520996094</v>
+        <v>4.44871473312378</v>
       </c>
       <c r="H1154" t="s">
         <v>8</v>
@@ -30503,7 +30503,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G1159" t="n">
-        <v>3.97944092750549</v>
+        <v>3.97944116592407</v>
       </c>
       <c r="H1159" t="s">
         <v>8</v>
@@ -30529,7 +30529,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G1160" t="n">
-        <v>3.99821257591248</v>
+        <v>3.9982123374939</v>
       </c>
       <c r="H1160" t="s">
         <v>8</v>
@@ -30685,7 +30685,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G1166" t="n">
-        <v>3.88558626174927</v>
+        <v>3.88558650016785</v>
       </c>
       <c r="H1166" t="s">
         <v>8</v>
@@ -30737,7 +30737,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G1168" t="n">
-        <v>3.94189953804016</v>
+        <v>3.941899061203</v>
       </c>
       <c r="H1168" t="s">
         <v>8</v>
@@ -30815,7 +30815,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G1171" t="n">
-        <v>4.39240169525146</v>
+        <v>4.39240217208862</v>
       </c>
       <c r="H1171" t="s">
         <v>8</v>
@@ -30867,7 +30867,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G1173" t="n">
-        <v>4.26100587844849</v>
+        <v>4.26100540161133</v>
       </c>
       <c r="H1173" t="s">
         <v>8</v>
@@ -30919,7 +30919,7 @@
         <v>4.42999982833862</v>
       </c>
       <c r="G1175" t="n">
-        <v>4.15776491165161</v>
+        <v>4.15776538848877</v>
       </c>
       <c r="H1175" t="s">
         <v>8</v>
@@ -30997,7 +30997,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G1178" t="n">
-        <v>4.05452537536621</v>
+        <v>4.05452489852905</v>
       </c>
       <c r="H1178" t="s">
         <v>8</v>
@@ -31049,7 +31049,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G1180" t="n">
-        <v>4.00759792327881</v>
+        <v>4.00759744644165</v>
       </c>
       <c r="H1180" t="s">
         <v>8</v>
@@ -31153,7 +31153,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G1184" t="n">
-        <v>3.95128512382507</v>
+        <v>3.95128488540649</v>
       </c>
       <c r="H1184" t="s">
         <v>8</v>
@@ -31205,7 +31205,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G1186" t="n">
-        <v>3.93251395225525</v>
+        <v>3.93251419067383</v>
       </c>
       <c r="H1186" t="s">
         <v>8</v>
@@ -31231,7 +31231,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G1187" t="n">
-        <v>3.8386595249176</v>
+        <v>3.83865928649902</v>
       </c>
       <c r="H1187" t="s">
         <v>8</v>
@@ -31309,7 +31309,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G1190" t="n">
-        <v>3.88558626174927</v>
+        <v>3.88558650016785</v>
       </c>
       <c r="H1190" t="s">
         <v>8</v>
@@ -31335,7 +31335,7 @@
         <v>4.17000007629395</v>
       </c>
       <c r="G1191" t="n">
-        <v>3.913743019104</v>
+        <v>3.91374325752258</v>
       </c>
       <c r="H1191" t="s">
         <v>8</v>
@@ -31413,7 +31413,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G1194" t="n">
-        <v>3.97944092750549</v>
+        <v>3.97944116592407</v>
       </c>
       <c r="H1194" t="s">
         <v>8</v>
@@ -31465,7 +31465,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G1196" t="n">
-        <v>3.95128512382507</v>
+        <v>3.95128488540649</v>
       </c>
       <c r="H1196" t="s">
         <v>8</v>
@@ -31517,7 +31517,7 @@
         <v>4.17000007629395</v>
       </c>
       <c r="G1198" t="n">
-        <v>3.913743019104</v>
+        <v>3.91374325752258</v>
       </c>
       <c r="H1198" t="s">
         <v>8</v>
@@ -31543,7 +31543,7 @@
         <v>4.17000007629395</v>
       </c>
       <c r="G1199" t="n">
-        <v>3.913743019104</v>
+        <v>3.91374325752258</v>
       </c>
       <c r="H1199" t="s">
         <v>8</v>
@@ -31569,7 +31569,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G1200" t="n">
-        <v>3.76357555389404</v>
+        <v>3.76357579231262</v>
       </c>
       <c r="H1200" t="s">
         <v>8</v>
@@ -31595,7 +31595,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G1201" t="n">
-        <v>3.66972064971924</v>
+        <v>3.66972088813782</v>
       </c>
       <c r="H1201" t="s">
         <v>8</v>
@@ -31621,7 +31621,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G1202" t="n">
-        <v>3.70726251602173</v>
+        <v>3.70726275444031</v>
       </c>
       <c r="H1202" t="s">
         <v>8</v>
@@ -31907,7 +31907,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G1213" t="n">
-        <v>3.7448046207428</v>
+        <v>3.74480438232422</v>
       </c>
       <c r="H1213" t="s">
         <v>8</v>
@@ -31933,7 +31933,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G1214" t="n">
-        <v>3.67910623550415</v>
+        <v>3.67910599708557</v>
       </c>
       <c r="H1214" t="s">
         <v>8</v>
@@ -31959,7 +31959,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G1215" t="n">
-        <v>3.7448046207428</v>
+        <v>3.74480438232422</v>
       </c>
       <c r="H1215" t="s">
         <v>8</v>
@@ -32037,7 +32037,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G1218" t="n">
-        <v>3.50078225135803</v>
+        <v>3.50078201293945</v>
       </c>
       <c r="H1218" t="s">
         <v>8</v>
@@ -32063,7 +32063,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G1219" t="n">
-        <v>3.38815641403198</v>
+        <v>3.3881561756134</v>
       </c>
       <c r="H1219" t="s">
         <v>8</v>
@@ -32141,7 +32141,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G1222" t="n">
-        <v>3.38815641403198</v>
+        <v>3.3881561756134</v>
       </c>
       <c r="H1222" t="s">
         <v>8</v>
@@ -32219,7 +32219,7 @@
         <v>3.41000008583069</v>
       </c>
       <c r="G1225" t="n">
-        <v>3.20044708251953</v>
+        <v>3.20044684410095</v>
       </c>
       <c r="H1225" t="s">
         <v>8</v>
@@ -32401,7 +32401,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G1232" t="n">
-        <v>3.65094995498657</v>
+        <v>3.65094971656799</v>
       </c>
       <c r="H1232" t="s">
         <v>8</v>
@@ -32505,7 +32505,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G1236" t="n">
-        <v>3.57586574554443</v>
+        <v>3.57586598396301</v>
       </c>
       <c r="H1236" t="s">
         <v>8</v>
@@ -32531,7 +32531,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G1237" t="n">
-        <v>3.67910623550415</v>
+        <v>3.67910599708557</v>
       </c>
       <c r="H1237" t="s">
         <v>8</v>
@@ -32583,7 +32583,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G1239" t="n">
-        <v>3.70726251602173</v>
+        <v>3.70726275444031</v>
       </c>
       <c r="H1239" t="s">
         <v>8</v>
@@ -32661,7 +32661,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G1242" t="n">
-        <v>3.89497232437134</v>
+        <v>3.89497208595276</v>
       </c>
       <c r="H1242" t="s">
         <v>8</v>
@@ -32687,7 +32687,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G1243" t="n">
-        <v>3.89497232437134</v>
+        <v>3.89497208595276</v>
       </c>
       <c r="H1243" t="s">
         <v>8</v>
@@ -32713,7 +32713,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G1244" t="n">
-        <v>3.8386595249176</v>
+        <v>3.83865928649902</v>
       </c>
       <c r="H1244" t="s">
         <v>8</v>
@@ -32765,7 +32765,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G1246" t="n">
-        <v>3.7448046207428</v>
+        <v>3.74480438232422</v>
       </c>
       <c r="H1246" t="s">
         <v>8</v>
@@ -32791,7 +32791,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G1247" t="n">
-        <v>3.70726251602173</v>
+        <v>3.70726275444031</v>
       </c>
       <c r="H1247" t="s">
         <v>8</v>
@@ -32921,7 +32921,7 @@
         <v>4.17000007629395</v>
       </c>
       <c r="G1252" t="n">
-        <v>3.913743019104</v>
+        <v>3.91374325752258</v>
       </c>
       <c r="H1252" t="s">
         <v>8</v>
@@ -32947,7 +32947,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G1253" t="n">
-        <v>3.89497232437134</v>
+        <v>3.89497208595276</v>
       </c>
       <c r="H1253" t="s">
         <v>8</v>
@@ -33103,7 +33103,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G1259" t="n">
-        <v>3.70726251602173</v>
+        <v>3.70726275444031</v>
       </c>
       <c r="H1259" t="s">
         <v>8</v>
@@ -33129,7 +33129,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G1260" t="n">
-        <v>3.70726251602173</v>
+        <v>3.70726275444031</v>
       </c>
       <c r="H1260" t="s">
         <v>8</v>
@@ -33181,7 +33181,7 @@
         <v>3.97000002861023</v>
       </c>
       <c r="G1262" t="n">
-        <v>3.72603368759155</v>
+        <v>3.72603344917297</v>
       </c>
       <c r="H1262" t="s">
         <v>8</v>
@@ -33207,7 +33207,7 @@
         <v>3.97000002861023</v>
       </c>
       <c r="G1263" t="n">
-        <v>3.72603368759155</v>
+        <v>3.72603344917297</v>
       </c>
       <c r="H1263" t="s">
         <v>8</v>
@@ -33259,7 +33259,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G1265" t="n">
-        <v>3.70726251602173</v>
+        <v>3.70726275444031</v>
       </c>
       <c r="H1265" t="s">
         <v>8</v>
@@ -33285,7 +33285,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G1266" t="n">
-        <v>3.70726251602173</v>
+        <v>3.70726275444031</v>
       </c>
       <c r="H1266" t="s">
         <v>8</v>
@@ -33311,7 +33311,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G1267" t="n">
-        <v>3.70726251602173</v>
+        <v>3.70726275444031</v>
       </c>
       <c r="H1267" t="s">
         <v>8</v>
@@ -33337,7 +33337,7 @@
         <v>3.97000002861023</v>
       </c>
       <c r="G1268" t="n">
-        <v>3.72603368759155</v>
+        <v>3.72603344917297</v>
       </c>
       <c r="H1268" t="s">
         <v>8</v>
@@ -33363,7 +33363,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G1269" t="n">
-        <v>3.7448046207428</v>
+        <v>3.74480438232422</v>
       </c>
       <c r="H1269" t="s">
         <v>8</v>
@@ -33389,7 +33389,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G1270" t="n">
-        <v>3.52893853187561</v>
+        <v>3.52893877029419</v>
       </c>
       <c r="H1270" t="s">
         <v>8</v>
@@ -33415,7 +33415,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G1271" t="n">
-        <v>3.65094995498657</v>
+        <v>3.65094971656799</v>
       </c>
       <c r="H1271" t="s">
         <v>8</v>
@@ -33519,7 +33519,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G1275" t="n">
-        <v>3.66972064971924</v>
+        <v>3.66972088813782</v>
       </c>
       <c r="H1275" t="s">
         <v>8</v>
@@ -33545,7 +33545,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G1276" t="n">
-        <v>3.66972064971924</v>
+        <v>3.66972088813782</v>
       </c>
       <c r="H1276" t="s">
         <v>8</v>
@@ -33571,7 +33571,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G1277" t="n">
-        <v>3.70726251602173</v>
+        <v>3.70726275444031</v>
       </c>
       <c r="H1277" t="s">
         <v>8</v>
@@ -33597,7 +33597,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G1278" t="n">
-        <v>3.63217878341675</v>
+        <v>3.63217854499817</v>
       </c>
       <c r="H1278" t="s">
         <v>8</v>
@@ -33649,7 +33649,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G1280" t="n">
-        <v>3.57586574554443</v>
+        <v>3.57586598396301</v>
       </c>
       <c r="H1280" t="s">
         <v>8</v>
@@ -33753,7 +33753,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G1284" t="n">
-        <v>3.57586574554443</v>
+        <v>3.57586598396301</v>
       </c>
       <c r="H1284" t="s">
         <v>8</v>
@@ -33779,7 +33779,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G1285" t="n">
-        <v>3.55709481239319</v>
+        <v>3.55709505081177</v>
       </c>
       <c r="H1285" t="s">
         <v>8</v>
@@ -33987,7 +33987,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G1293" t="n">
-        <v>3.63217878341675</v>
+        <v>3.63217854499817</v>
       </c>
       <c r="H1293" t="s">
         <v>8</v>
@@ -34065,7 +34065,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G1296" t="n">
-        <v>3.63217878341675</v>
+        <v>3.63217854499817</v>
       </c>
       <c r="H1296" t="s">
         <v>8</v>
@@ -34247,7 +34247,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G1303" t="n">
-        <v>3.63217878341675</v>
+        <v>3.63217854499817</v>
       </c>
       <c r="H1303" t="s">
         <v>8</v>
@@ -34611,7 +34611,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G1317" t="n">
-        <v>3.55709481239319</v>
+        <v>3.55709505081177</v>
       </c>
       <c r="H1317" t="s">
         <v>8</v>
@@ -34689,7 +34689,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G1320" t="n">
-        <v>3.52893853187561</v>
+        <v>3.52893877029419</v>
       </c>
       <c r="H1320" t="s">
         <v>8</v>
@@ -34741,7 +34741,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G1322" t="n">
-        <v>3.53832411766052</v>
+        <v>3.53832387924194</v>
       </c>
       <c r="H1322" t="s">
         <v>8</v>
@@ -34767,7 +34767,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G1323" t="n">
-        <v>3.52893853187561</v>
+        <v>3.52893877029419</v>
       </c>
       <c r="H1323" t="s">
         <v>8</v>
@@ -34819,7 +34819,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G1325" t="n">
-        <v>3.55709481239319</v>
+        <v>3.55709505081177</v>
       </c>
       <c r="H1325" t="s">
         <v>8</v>
@@ -34845,7 +34845,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G1326" t="n">
-        <v>3.55709481239319</v>
+        <v>3.55709505081177</v>
       </c>
       <c r="H1326" t="s">
         <v>8</v>
@@ -34897,7 +34897,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G1328" t="n">
-        <v>3.89497232437134</v>
+        <v>3.89497208595276</v>
       </c>
       <c r="H1328" t="s">
         <v>8</v>
@@ -34975,7 +34975,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G1331" t="n">
-        <v>3.88558626174927</v>
+        <v>3.88558650016785</v>
       </c>
       <c r="H1331" t="s">
         <v>8</v>
@@ -35027,7 +35027,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G1333" t="n">
-        <v>3.81050252914429</v>
+        <v>3.81050276756287</v>
       </c>
       <c r="H1333" t="s">
         <v>8</v>
@@ -35079,7 +35079,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G1335" t="n">
-        <v>3.81050252914429</v>
+        <v>3.81050276756287</v>
       </c>
       <c r="H1335" t="s">
         <v>8</v>
@@ -35105,7 +35105,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G1336" t="n">
-        <v>3.76357555389404</v>
+        <v>3.76357579231262</v>
       </c>
       <c r="H1336" t="s">
         <v>8</v>
@@ -35183,7 +35183,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G1339" t="n">
-        <v>3.76357555389404</v>
+        <v>3.76357579231262</v>
       </c>
       <c r="H1339" t="s">
         <v>8</v>
@@ -35209,7 +35209,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G1340" t="n">
-        <v>3.81050252914429</v>
+        <v>3.81050276756287</v>
       </c>
       <c r="H1340" t="s">
         <v>8</v>
@@ -35235,7 +35235,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G1341" t="n">
-        <v>3.85743021965027</v>
+        <v>3.85743045806885</v>
       </c>
       <c r="H1341" t="s">
         <v>8</v>
@@ -35287,7 +35287,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G1343" t="n">
-        <v>3.81050252914429</v>
+        <v>3.81050276756287</v>
       </c>
       <c r="H1343" t="s">
         <v>8</v>
@@ -35313,7 +35313,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G1344" t="n">
-        <v>3.81050252914429</v>
+        <v>3.81050276756287</v>
       </c>
       <c r="H1344" t="s">
         <v>8</v>
@@ -35625,7 +35625,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G1356" t="n">
-        <v>3.70726251602173</v>
+        <v>3.70726275444031</v>
       </c>
       <c r="H1356" t="s">
         <v>8</v>
@@ -35651,7 +35651,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G1357" t="n">
-        <v>3.76357555389404</v>
+        <v>3.76357579231262</v>
       </c>
       <c r="H1357" t="s">
         <v>8</v>
@@ -35677,7 +35677,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G1358" t="n">
-        <v>3.76357555389404</v>
+        <v>3.76357579231262</v>
       </c>
       <c r="H1358" t="s">
         <v>8</v>
@@ -35729,7 +35729,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G1360" t="n">
-        <v>3.70726251602173</v>
+        <v>3.70726275444031</v>
       </c>
       <c r="H1360" t="s">
         <v>8</v>
@@ -35937,7 +35937,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G1368" t="n">
-        <v>3.70726251602173</v>
+        <v>3.70726275444031</v>
       </c>
       <c r="H1368" t="s">
         <v>8</v>
@@ -35963,7 +35963,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G1369" t="n">
-        <v>3.70726251602173</v>
+        <v>3.70726275444031</v>
       </c>
       <c r="H1369" t="s">
         <v>8</v>
@@ -36015,7 +36015,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G1371" t="n">
-        <v>3.66972064971924</v>
+        <v>3.66972088813782</v>
       </c>
       <c r="H1371" t="s">
         <v>8</v>
@@ -36041,7 +36041,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G1372" t="n">
-        <v>3.67910623550415</v>
+        <v>3.67910599708557</v>
       </c>
       <c r="H1372" t="s">
         <v>8</v>
@@ -36067,7 +36067,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G1373" t="n">
-        <v>3.70726251602173</v>
+        <v>3.70726275444031</v>
       </c>
       <c r="H1373" t="s">
         <v>8</v>
@@ -36301,7 +36301,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G1382" t="n">
-        <v>3.70726251602173</v>
+        <v>3.70726275444031</v>
       </c>
       <c r="H1382" t="s">
         <v>8</v>
@@ -36327,7 +36327,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G1383" t="n">
-        <v>3.66972064971924</v>
+        <v>3.66972088813782</v>
       </c>
       <c r="H1383" t="s">
         <v>8</v>
@@ -36353,7 +36353,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G1384" t="n">
-        <v>3.67910623550415</v>
+        <v>3.67910599708557</v>
       </c>
       <c r="H1384" t="s">
         <v>8</v>
@@ -36483,7 +36483,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G1389" t="n">
-        <v>3.70726251602173</v>
+        <v>3.70726275444031</v>
       </c>
       <c r="H1389" t="s">
         <v>8</v>
@@ -36509,7 +36509,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G1390" t="n">
-        <v>3.70726251602173</v>
+        <v>3.70726275444031</v>
       </c>
       <c r="H1390" t="s">
         <v>8</v>
@@ -36535,7 +36535,7 @@
         <v>3.97000002861023</v>
       </c>
       <c r="G1391" t="n">
-        <v>3.72603368759155</v>
+        <v>3.72603344917297</v>
       </c>
       <c r="H1391" t="s">
         <v>8</v>
@@ -36639,7 +36639,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G1395" t="n">
-        <v>3.70726251602173</v>
+        <v>3.70726275444031</v>
       </c>
       <c r="H1395" t="s">
         <v>8</v>
@@ -36665,7 +36665,7 @@
         <v>3.97000002861023</v>
       </c>
       <c r="G1396" t="n">
-        <v>3.72603368759155</v>
+        <v>3.72603344917297</v>
       </c>
       <c r="H1396" t="s">
         <v>8</v>
@@ -36821,7 +36821,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G1402" t="n">
-        <v>3.57586574554443</v>
+        <v>3.57586598396301</v>
       </c>
       <c r="H1402" t="s">
         <v>8</v>
@@ -36925,7 +36925,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G1406" t="n">
-        <v>3.63217878341675</v>
+        <v>3.63217854499817</v>
       </c>
       <c r="H1406" t="s">
         <v>8</v>
@@ -37029,7 +37029,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G1410" t="n">
-        <v>3.55709481239319</v>
+        <v>3.55709505081177</v>
       </c>
       <c r="H1410" t="s">
         <v>8</v>
@@ -37107,7 +37107,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G1413" t="n">
-        <v>3.63217878341675</v>
+        <v>3.63217854499817</v>
       </c>
       <c r="H1413" t="s">
         <v>8</v>
@@ -37133,7 +37133,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G1414" t="n">
-        <v>3.57586574554443</v>
+        <v>3.57586598396301</v>
       </c>
       <c r="H1414" t="s">
         <v>8</v>
@@ -37185,7 +37185,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G1416" t="n">
-        <v>3.53832411766052</v>
+        <v>3.53832387924194</v>
       </c>
       <c r="H1416" t="s">
         <v>8</v>
@@ -37211,7 +37211,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G1417" t="n">
-        <v>3.53832411766052</v>
+        <v>3.53832387924194</v>
       </c>
       <c r="H1417" t="s">
         <v>8</v>
@@ -37341,7 +37341,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G1422" t="n">
-        <v>3.63217878341675</v>
+        <v>3.63217854499817</v>
       </c>
       <c r="H1422" t="s">
         <v>8</v>
@@ -37393,7 +37393,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G1424" t="n">
-        <v>3.66972064971924</v>
+        <v>3.66972088813782</v>
       </c>
       <c r="H1424" t="s">
         <v>8</v>
@@ -37419,7 +37419,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G1425" t="n">
-        <v>3.66972064971924</v>
+        <v>3.66972088813782</v>
       </c>
       <c r="H1425" t="s">
         <v>8</v>
@@ -37549,7 +37549,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G1430" t="n">
-        <v>3.67910623550415</v>
+        <v>3.67910599708557</v>
       </c>
       <c r="H1430" t="s">
         <v>8</v>
@@ -37575,7 +37575,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G1431" t="n">
-        <v>3.65094995498657</v>
+        <v>3.65094971656799</v>
       </c>
       <c r="H1431" t="s">
         <v>8</v>
@@ -37601,7 +37601,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G1432" t="n">
-        <v>3.65094995498657</v>
+        <v>3.65094971656799</v>
       </c>
       <c r="H1432" t="s">
         <v>8</v>
@@ -37627,7 +37627,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G1433" t="n">
-        <v>3.65094995498657</v>
+        <v>3.65094971656799</v>
       </c>
       <c r="H1433" t="s">
         <v>8</v>
@@ -37679,7 +37679,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G1435" t="n">
-        <v>3.63217878341675</v>
+        <v>3.63217854499817</v>
       </c>
       <c r="H1435" t="s">
         <v>8</v>
@@ -37731,7 +37731,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G1437" t="n">
-        <v>3.63217878341675</v>
+        <v>3.63217854499817</v>
       </c>
       <c r="H1437" t="s">
         <v>8</v>
@@ -37757,7 +37757,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G1438" t="n">
-        <v>3.66972064971924</v>
+        <v>3.66972088813782</v>
       </c>
       <c r="H1438" t="s">
         <v>8</v>
@@ -37783,7 +37783,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G1439" t="n">
-        <v>3.65094995498657</v>
+        <v>3.65094971656799</v>
       </c>
       <c r="H1439" t="s">
         <v>8</v>
@@ -38069,7 +38069,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G1450" t="n">
-        <v>3.55709481239319</v>
+        <v>3.55709505081177</v>
       </c>
       <c r="H1450" t="s">
         <v>8</v>
@@ -38121,7 +38121,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G1452" t="n">
-        <v>3.57586574554443</v>
+        <v>3.57586598396301</v>
       </c>
       <c r="H1452" t="s">
         <v>8</v>
@@ -38147,7 +38147,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G1453" t="n">
-        <v>3.57586574554443</v>
+        <v>3.57586598396301</v>
       </c>
       <c r="H1453" t="s">
         <v>8</v>
@@ -38173,7 +38173,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G1454" t="n">
-        <v>3.52893853187561</v>
+        <v>3.52893877029419</v>
       </c>
       <c r="H1454" t="s">
         <v>8</v>
@@ -38251,7 +38251,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G1457" t="n">
-        <v>3.57586574554443</v>
+        <v>3.57586598396301</v>
       </c>
       <c r="H1457" t="s">
         <v>8</v>
@@ -38329,7 +38329,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G1460" t="n">
-        <v>3.50078225135803</v>
+        <v>3.50078201293945</v>
       </c>
       <c r="H1460" t="s">
         <v>8</v>
@@ -38511,7 +38511,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G1467" t="n">
-        <v>3.53832411766052</v>
+        <v>3.53832387924194</v>
       </c>
       <c r="H1467" t="s">
         <v>8</v>
@@ -38537,7 +38537,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G1468" t="n">
-        <v>3.52893853187561</v>
+        <v>3.52893877029419</v>
       </c>
       <c r="H1468" t="s">
         <v>8</v>
@@ -38693,7 +38693,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G1474" t="n">
-        <v>3.55709481239319</v>
+        <v>3.55709505081177</v>
       </c>
       <c r="H1474" t="s">
         <v>8</v>
@@ -38745,7 +38745,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G1476" t="n">
-        <v>3.52893853187561</v>
+        <v>3.52893877029419</v>
       </c>
       <c r="H1476" t="s">
         <v>8</v>
@@ -38849,7 +38849,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G1480" t="n">
-        <v>3.50078225135803</v>
+        <v>3.50078201293945</v>
       </c>
       <c r="H1480" t="s">
         <v>8</v>
@@ -38875,7 +38875,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G1481" t="n">
-        <v>3.50078225135803</v>
+        <v>3.50078201293945</v>
       </c>
       <c r="H1481" t="s">
         <v>8</v>
@@ -38953,7 +38953,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G1484" t="n">
-        <v>3.52893853187561</v>
+        <v>3.52893877029419</v>
       </c>
       <c r="H1484" t="s">
         <v>8</v>
@@ -39005,7 +39005,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G1486" t="n">
-        <v>3.46324014663696</v>
+        <v>3.46324038505554</v>
       </c>
       <c r="H1486" t="s">
         <v>8</v>
@@ -39083,7 +39083,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G1489" t="n">
-        <v>3.4444694519043</v>
+        <v>3.44446921348572</v>
       </c>
       <c r="H1489" t="s">
         <v>8</v>
@@ -39213,7 +39213,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G1494" t="n">
-        <v>3.46324014663696</v>
+        <v>3.46324038505554</v>
       </c>
       <c r="H1494" t="s">
         <v>8</v>
@@ -39239,7 +39239,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G1495" t="n">
-        <v>3.50078225135803</v>
+        <v>3.50078201293945</v>
       </c>
       <c r="H1495" t="s">
         <v>8</v>
@@ -39265,7 +39265,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G1496" t="n">
-        <v>3.50078225135803</v>
+        <v>3.50078201293945</v>
       </c>
       <c r="H1496" t="s">
         <v>8</v>
@@ -39317,7 +39317,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G1498" t="n">
-        <v>3.52893853187561</v>
+        <v>3.52893877029419</v>
       </c>
       <c r="H1498" t="s">
         <v>8</v>
@@ -39395,7 +39395,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G1501" t="n">
-        <v>3.50078225135803</v>
+        <v>3.50078201293945</v>
       </c>
       <c r="H1501" t="s">
         <v>8</v>
@@ -39499,7 +39499,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G1505" t="n">
-        <v>3.46324014663696</v>
+        <v>3.46324038505554</v>
       </c>
       <c r="H1505" t="s">
         <v>8</v>
@@ -39525,7 +39525,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G1506" t="n">
-        <v>3.39754199981689</v>
+        <v>3.39754176139832</v>
       </c>
       <c r="H1506" t="s">
         <v>8</v>
@@ -39603,7 +39603,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G1509" t="n">
-        <v>3.1910617351532</v>
+        <v>3.19106149673462</v>
       </c>
       <c r="H1509" t="s">
         <v>8</v>
@@ -39785,7 +39785,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G1516" t="n">
-        <v>3.14413404464722</v>
+        <v>3.14413380622864</v>
       </c>
       <c r="H1516" t="s">
         <v>8</v>
@@ -39811,7 +39811,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G1517" t="n">
-        <v>3.25675964355469</v>
+        <v>3.25675988197327</v>
       </c>
       <c r="H1517" t="s">
         <v>8</v>
@@ -39837,7 +39837,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G1518" t="n">
-        <v>3.46324014663696</v>
+        <v>3.46324038505554</v>
       </c>
       <c r="H1518" t="s">
         <v>8</v>
@@ -39863,7 +39863,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G1519" t="n">
-        <v>3.55709481239319</v>
+        <v>3.55709505081177</v>
       </c>
       <c r="H1519" t="s">
         <v>8</v>
@@ -39889,7 +39889,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G1520" t="n">
-        <v>3.57586574554443</v>
+        <v>3.57586598396301</v>
       </c>
       <c r="H1520" t="s">
         <v>8</v>
@@ -40019,7 +40019,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G1525" t="n">
-        <v>3.39754199981689</v>
+        <v>3.39754176139832</v>
       </c>
       <c r="H1525" t="s">
         <v>8</v>
@@ -40227,7 +40227,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G1533" t="n">
-        <v>3.37877082824707</v>
+        <v>3.37877106666565</v>
       </c>
       <c r="H1533" t="s">
         <v>8</v>
@@ -40305,7 +40305,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G1536" t="n">
-        <v>3.36938524246216</v>
+        <v>3.36938548088074</v>
       </c>
       <c r="H1536" t="s">
         <v>8</v>
@@ -40331,7 +40331,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G1537" t="n">
-        <v>3.25675964355469</v>
+        <v>3.25675988197327</v>
       </c>
       <c r="H1537" t="s">
         <v>8</v>
@@ -40409,7 +40409,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G1540" t="n">
-        <v>3.29430174827576</v>
+        <v>3.29430150985718</v>
       </c>
       <c r="H1540" t="s">
         <v>8</v>
@@ -40435,7 +40435,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G1541" t="n">
-        <v>3.25675964355469</v>
+        <v>3.25675988197327</v>
       </c>
       <c r="H1541" t="s">
         <v>8</v>
@@ -40487,7 +40487,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G1543" t="n">
-        <v>3.25675964355469</v>
+        <v>3.25675988197327</v>
       </c>
       <c r="H1543" t="s">
         <v>8</v>
@@ -40513,7 +40513,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G1544" t="n">
-        <v>3.1910617351532</v>
+        <v>3.19106149673462</v>
       </c>
       <c r="H1544" t="s">
         <v>8</v>
@@ -40539,7 +40539,7 @@
         <v>3.41000008583069</v>
       </c>
       <c r="G1545" t="n">
-        <v>3.20044708251953</v>
+        <v>3.20044684410095</v>
       </c>
       <c r="H1545" t="s">
         <v>8</v>
@@ -40643,7 +40643,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G1549" t="n">
-        <v>3.1910617351532</v>
+        <v>3.19106149673462</v>
       </c>
       <c r="H1549" t="s">
         <v>8</v>
@@ -40721,7 +40721,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G1552" t="n">
-        <v>3.04089379310608</v>
+        <v>3.04089403152466</v>
       </c>
       <c r="H1552" t="s">
         <v>8</v>
@@ -40903,7 +40903,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G1559" t="n">
-        <v>3.52893853187561</v>
+        <v>3.52893877029419</v>
       </c>
       <c r="H1559" t="s">
         <v>8</v>
@@ -41085,7 +41085,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G1566" t="n">
-        <v>3.37877082824707</v>
+        <v>3.37877106666565</v>
       </c>
       <c r="H1566" t="s">
         <v>8</v>
@@ -41163,7 +41163,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G1569" t="n">
-        <v>3.37877082824707</v>
+        <v>3.37877106666565</v>
       </c>
       <c r="H1569" t="s">
         <v>8</v>
@@ -41189,7 +41189,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G1570" t="n">
-        <v>3.4444694519043</v>
+        <v>3.44446921348572</v>
       </c>
       <c r="H1570" t="s">
         <v>8</v>
@@ -41293,7 +41293,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G1574" t="n">
-        <v>2.95642447471619</v>
+        <v>2.95642471313477</v>
       </c>
       <c r="H1574" t="s">
         <v>8</v>
@@ -41397,7 +41397,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G1578" t="n">
-        <v>2.92826795578003</v>
+        <v>2.92826819419861</v>
       </c>
       <c r="H1578" t="s">
         <v>8</v>
@@ -41449,7 +41449,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G1580" t="n">
-        <v>2.90011167526245</v>
+        <v>2.90011143684387</v>
       </c>
       <c r="H1580" t="s">
         <v>8</v>
@@ -41475,7 +41475,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G1581" t="n">
-        <v>2.92826795578003</v>
+        <v>2.92826819419861</v>
       </c>
       <c r="H1581" t="s">
         <v>8</v>
@@ -41527,7 +41527,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G1583" t="n">
-        <v>3.27553057670593</v>
+        <v>3.27553081512451</v>
       </c>
       <c r="H1583" t="s">
         <v>8</v>
@@ -41553,7 +41553,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G1584" t="n">
-        <v>3.55709481239319</v>
+        <v>3.55709505081177</v>
       </c>
       <c r="H1584" t="s">
         <v>8</v>
@@ -41605,7 +41605,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G1586" t="n">
-        <v>3.66972064971924</v>
+        <v>3.66972088813782</v>
       </c>
       <c r="H1586" t="s">
         <v>8</v>
@@ -41631,7 +41631,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G1587" t="n">
-        <v>3.65094995498657</v>
+        <v>3.65094971656799</v>
       </c>
       <c r="H1587" t="s">
         <v>8</v>
@@ -41657,7 +41657,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G1588" t="n">
-        <v>3.4444694519043</v>
+        <v>3.44446921348572</v>
       </c>
       <c r="H1588" t="s">
         <v>8</v>
@@ -41735,7 +41735,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G1591" t="n">
-        <v>3.55709481239319</v>
+        <v>3.55709505081177</v>
       </c>
       <c r="H1591" t="s">
         <v>8</v>
@@ -41787,7 +41787,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G1593" t="n">
-        <v>3.52893853187561</v>
+        <v>3.52893877029419</v>
       </c>
       <c r="H1593" t="s">
         <v>8</v>
@@ -41813,7 +41813,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G1594" t="n">
-        <v>3.55709481239319</v>
+        <v>3.55709505081177</v>
       </c>
       <c r="H1594" t="s">
         <v>8</v>
@@ -41839,7 +41839,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G1595" t="n">
-        <v>3.55709481239319</v>
+        <v>3.55709505081177</v>
       </c>
       <c r="H1595" t="s">
         <v>8</v>
@@ -41865,7 +41865,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G1596" t="n">
-        <v>3.57586574554443</v>
+        <v>3.57586598396301</v>
       </c>
       <c r="H1596" t="s">
         <v>8</v>
@@ -41969,7 +41969,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G1600" t="n">
-        <v>3.46324014663696</v>
+        <v>3.46324038505554</v>
       </c>
       <c r="H1600" t="s">
         <v>8</v>
@@ -42203,7 +42203,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G1609" t="n">
-        <v>3.46324014663696</v>
+        <v>3.46324038505554</v>
       </c>
       <c r="H1609" t="s">
         <v>8</v>
@@ -42255,7 +42255,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G1611" t="n">
-        <v>3.39754199981689</v>
+        <v>3.39754176139832</v>
       </c>
       <c r="H1611" t="s">
         <v>8</v>
@@ -42281,7 +42281,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G1612" t="n">
-        <v>3.39754199981689</v>
+        <v>3.39754176139832</v>
       </c>
       <c r="H1612" t="s">
         <v>8</v>
@@ -42333,7 +42333,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G1614" t="n">
-        <v>3.38815641403198</v>
+        <v>3.3881561756134</v>
       </c>
       <c r="H1614" t="s">
         <v>8</v>
@@ -42359,7 +42359,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G1615" t="n">
-        <v>3.1910617351532</v>
+        <v>3.19106149673462</v>
       </c>
       <c r="H1615" t="s">
         <v>8</v>
@@ -42411,7 +42411,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G1617" t="n">
-        <v>3.25675964355469</v>
+        <v>3.25675988197327</v>
       </c>
       <c r="H1617" t="s">
         <v>8</v>
@@ -42437,7 +42437,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G1618" t="n">
-        <v>3.25675964355469</v>
+        <v>3.25675988197327</v>
       </c>
       <c r="H1618" t="s">
         <v>8</v>
@@ -71274,6 +71274,32 @@
         <v>1.0900000333786</v>
       </c>
       <c r="H2727" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2728">
+      <c r="A2728" s="1" t="n">
+        <v>46289.2916666667</v>
+      </c>
+      <c r="B2728" t="n">
+        <v>689</v>
+      </c>
+      <c r="C2728" t="n">
+        <v>1.04999995231628</v>
+      </c>
+      <c r="D2728" t="n">
+        <v>1.02999997138977</v>
+      </c>
+      <c r="E2728" t="n">
+        <v>1.04999995231628</v>
+      </c>
+      <c r="F2728" t="n">
+        <v>1.04999995231628</v>
+      </c>
+      <c r="G2728" t="n">
+        <v>1.04999995231628</v>
+      </c>
+      <c r="H2728" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/RAT.MI.xlsx
+++ b/data/RAT.MI.xlsx
@@ -421,7 +421,7 @@
         <v>2.3659999370575</v>
       </c>
       <c r="G2" t="n">
-        <v>1.8582592010498</v>
+        <v>1.85825955867767</v>
       </c>
       <c r="H2" t="s">
         <v>8</v>
@@ -447,7 +447,7 @@
         <v>2.43600010871887</v>
       </c>
       <c r="G3" t="n">
-        <v>1.91323781013489</v>
+        <v>1.91323792934418</v>
       </c>
       <c r="H3" t="s">
         <v>8</v>
@@ -473,7 +473,7 @@
         <v>2.44600009918213</v>
       </c>
       <c r="G4" t="n">
-        <v>1.92109143733978</v>
+        <v>1.92109167575836</v>
       </c>
       <c r="H4" t="s">
         <v>8</v>
@@ -499,7 +499,7 @@
         <v>2.44600009918213</v>
       </c>
       <c r="G5" t="n">
-        <v>1.92109143733978</v>
+        <v>1.92109167575836</v>
       </c>
       <c r="H5" t="s">
         <v>8</v>
@@ -525,7 +525,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G6" t="n">
-        <v>1.8849630355835</v>
+        <v>1.88496315479279</v>
       </c>
       <c r="H6" t="s">
         <v>8</v>
@@ -551,7 +551,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G7" t="n">
-        <v>1.8849630355835</v>
+        <v>1.88496315479279</v>
       </c>
       <c r="H7" t="s">
         <v>8</v>
@@ -577,7 +577,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G8" t="n">
-        <v>1.9242330789566</v>
+        <v>1.92423319816589</v>
       </c>
       <c r="H8" t="s">
         <v>8</v>
@@ -603,7 +603,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G9" t="n">
-        <v>1.8849630355835</v>
+        <v>1.88496315479279</v>
       </c>
       <c r="H9" t="s">
         <v>8</v>
@@ -629,7 +629,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G10" t="n">
-        <v>1.8849630355835</v>
+        <v>1.88496315479279</v>
       </c>
       <c r="H10" t="s">
         <v>8</v>
@@ -655,7 +655,7 @@
         <v>2.3659999370575</v>
       </c>
       <c r="G11" t="n">
-        <v>1.8582592010498</v>
+        <v>1.85825955867767</v>
       </c>
       <c r="H11" t="s">
         <v>8</v>
@@ -681,7 +681,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G12" t="n">
-        <v>1.80642306804657</v>
+        <v>1.80642294883728</v>
       </c>
       <c r="H12" t="s">
         <v>8</v>
@@ -707,7 +707,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G13" t="n">
-        <v>1.80642306804657</v>
+        <v>1.80642294883728</v>
       </c>
       <c r="H13" t="s">
         <v>8</v>
@@ -733,7 +733,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G14" t="n">
-        <v>1.82998490333557</v>
+        <v>1.82998502254486</v>
       </c>
       <c r="H14" t="s">
         <v>8</v>
@@ -759,7 +759,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G15" t="n">
-        <v>1.79856872558594</v>
+        <v>1.79856896400452</v>
       </c>
       <c r="H15" t="s">
         <v>8</v>
@@ -785,7 +785,7 @@
         <v>2.25</v>
       </c>
       <c r="G16" t="n">
-        <v>1.76715302467346</v>
+        <v>1.76715314388275</v>
       </c>
       <c r="H16" t="s">
         <v>8</v>
@@ -811,7 +811,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G17" t="n">
-        <v>1.85354685783386</v>
+        <v>1.85354709625244</v>
       </c>
       <c r="H17" t="s">
         <v>8</v>
@@ -837,7 +837,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G18" t="n">
-        <v>1.85354685783386</v>
+        <v>1.85354709625244</v>
       </c>
       <c r="H18" t="s">
         <v>8</v>
@@ -863,7 +863,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G19" t="n">
-        <v>1.86925542354584</v>
+        <v>1.86925530433655</v>
       </c>
       <c r="H19" t="s">
         <v>8</v>
@@ -967,7 +967,7 @@
         <v>2.31200003623962</v>
       </c>
       <c r="G23" t="n">
-        <v>1.81584811210632</v>
+        <v>1.81584763526917</v>
       </c>
       <c r="H23" t="s">
         <v>8</v>
@@ -993,7 +993,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G24" t="n">
-        <v>1.83783900737762</v>
+        <v>1.83783888816833</v>
       </c>
       <c r="H24" t="s">
         <v>8</v>
@@ -1019,7 +1019,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G25" t="n">
-        <v>1.83783900737762</v>
+        <v>1.83783888816833</v>
       </c>
       <c r="H25" t="s">
         <v>8</v>
@@ -1045,7 +1045,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G26" t="n">
-        <v>1.8849630355835</v>
+        <v>1.88496315479279</v>
       </c>
       <c r="H26" t="s">
         <v>8</v>
@@ -1071,7 +1071,7 @@
         <v>2.38800001144409</v>
       </c>
       <c r="G27" t="n">
-        <v>1.8755384683609</v>
+        <v>1.87553811073303</v>
       </c>
       <c r="H27" t="s">
         <v>8</v>
@@ -1097,7 +1097,7 @@
         <v>2.38800001144409</v>
       </c>
       <c r="G28" t="n">
-        <v>1.8755384683609</v>
+        <v>1.87553811073303</v>
       </c>
       <c r="H28" t="s">
         <v>8</v>
@@ -1123,7 +1123,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G29" t="n">
-        <v>1.8849630355835</v>
+        <v>1.88496315479279</v>
       </c>
       <c r="H29" t="s">
         <v>8</v>
@@ -1149,7 +1149,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G30" t="n">
-        <v>1.80642306804657</v>
+        <v>1.80642294883728</v>
       </c>
       <c r="H30" t="s">
         <v>8</v>
@@ -1175,7 +1175,7 @@
         <v>2.32599997520447</v>
       </c>
       <c r="G31" t="n">
-        <v>1.82684326171875</v>
+        <v>1.82684350013733</v>
       </c>
       <c r="H31" t="s">
         <v>8</v>
@@ -1201,7 +1201,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G32" t="n">
-        <v>1.84569299221039</v>
+        <v>1.84569275379181</v>
       </c>
       <c r="H32" t="s">
         <v>8</v>
@@ -1227,7 +1227,7 @@
         <v>2.31599998474121</v>
       </c>
       <c r="G33" t="n">
-        <v>1.81898939609528</v>
+        <v>1.81898951530457</v>
       </c>
       <c r="H33" t="s">
         <v>8</v>
@@ -1253,7 +1253,7 @@
         <v>2.33800005912781</v>
       </c>
       <c r="G34" t="n">
-        <v>1.8362683057785</v>
+        <v>1.83626818656921</v>
       </c>
       <c r="H34" t="s">
         <v>8</v>
@@ -1279,7 +1279,7 @@
         <v>2.36800003051758</v>
       </c>
       <c r="G35" t="n">
-        <v>1.85983037948608</v>
+        <v>1.85983049869537</v>
       </c>
       <c r="H35" t="s">
         <v>8</v>
@@ -1305,7 +1305,7 @@
         <v>2.36800003051758</v>
       </c>
       <c r="G36" t="n">
-        <v>1.85983037948608</v>
+        <v>1.85983049869537</v>
       </c>
       <c r="H36" t="s">
         <v>8</v>
@@ -1331,7 +1331,7 @@
         <v>2.36800003051758</v>
       </c>
       <c r="G37" t="n">
-        <v>1.85983037948608</v>
+        <v>1.85983049869537</v>
       </c>
       <c r="H37" t="s">
         <v>8</v>
@@ -1357,7 +1357,7 @@
         <v>2.29800009727478</v>
       </c>
       <c r="G38" t="n">
-        <v>1.80485200881958</v>
+        <v>1.80485212802887</v>
       </c>
       <c r="H38" t="s">
         <v>8</v>
@@ -1383,7 +1383,7 @@
         <v>2.31800007820129</v>
       </c>
       <c r="G39" t="n">
-        <v>1.82056033611298</v>
+        <v>1.82056045532227</v>
       </c>
       <c r="H39" t="s">
         <v>8</v>
@@ -1487,7 +1487,7 @@
         <v>2.33800005912781</v>
       </c>
       <c r="G43" t="n">
-        <v>1.8362683057785</v>
+        <v>1.83626818656921</v>
       </c>
       <c r="H43" t="s">
         <v>8</v>
@@ -1513,7 +1513,7 @@
         <v>2.36800003051758</v>
       </c>
       <c r="G44" t="n">
-        <v>1.85983037948608</v>
+        <v>1.85983049869537</v>
       </c>
       <c r="H44" t="s">
         <v>8</v>
@@ -1643,7 +1643,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G49" t="n">
-        <v>1.81427681446075</v>
+        <v>1.81427669525146</v>
       </c>
       <c r="H49" t="s">
         <v>8</v>
@@ -1669,7 +1669,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G50" t="n">
-        <v>1.84569299221039</v>
+        <v>1.84569275379181</v>
       </c>
       <c r="H50" t="s">
         <v>8</v>
@@ -1695,7 +1695,7 @@
         <v>2.33800005912781</v>
       </c>
       <c r="G51" t="n">
-        <v>1.8362683057785</v>
+        <v>1.83626818656921</v>
       </c>
       <c r="H51" t="s">
         <v>8</v>
@@ -1721,7 +1721,7 @@
         <v>2.35800004005432</v>
       </c>
       <c r="G52" t="n">
-        <v>1.85197627544403</v>
+        <v>1.85197651386261</v>
       </c>
       <c r="H52" t="s">
         <v>8</v>
@@ -1747,7 +1747,7 @@
         <v>2.34800004959106</v>
       </c>
       <c r="G53" t="n">
-        <v>1.84412240982056</v>
+        <v>1.84412217140198</v>
       </c>
       <c r="H53" t="s">
         <v>8</v>
@@ -1773,7 +1773,7 @@
         <v>2.34400010108948</v>
       </c>
       <c r="G54" t="n">
-        <v>1.84098076820374</v>
+        <v>1.84098064899445</v>
       </c>
       <c r="H54" t="s">
         <v>8</v>
@@ -1799,7 +1799,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G55" t="n">
-        <v>1.84569299221039</v>
+        <v>1.84569275379181</v>
       </c>
       <c r="H55" t="s">
         <v>8</v>
@@ -1825,7 +1825,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G56" t="n">
-        <v>1.84569299221039</v>
+        <v>1.84569275379181</v>
       </c>
       <c r="H56" t="s">
         <v>8</v>
@@ -1851,7 +1851,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G57" t="n">
-        <v>1.85354685783386</v>
+        <v>1.85354709625244</v>
       </c>
       <c r="H57" t="s">
         <v>8</v>
@@ -1877,7 +1877,7 @@
         <v>2.32200002670288</v>
       </c>
       <c r="G58" t="n">
-        <v>1.82370162010193</v>
+        <v>1.82370185852051</v>
       </c>
       <c r="H58" t="s">
         <v>8</v>
@@ -1903,7 +1903,7 @@
         <v>2.32200002670288</v>
       </c>
       <c r="G59" t="n">
-        <v>1.82370162010193</v>
+        <v>1.82370185852051</v>
       </c>
       <c r="H59" t="s">
         <v>8</v>
@@ -1955,7 +1955,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G61" t="n">
-        <v>1.81427681446075</v>
+        <v>1.81427669525146</v>
       </c>
       <c r="H61" t="s">
         <v>8</v>
@@ -1981,7 +1981,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G62" t="n">
-        <v>1.82213091850281</v>
+        <v>1.8221310377121</v>
       </c>
       <c r="H62" t="s">
         <v>8</v>
@@ -2033,7 +2033,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G64" t="n">
-        <v>1.84569299221039</v>
+        <v>1.84569275379181</v>
       </c>
       <c r="H64" t="s">
         <v>8</v>
@@ -2059,7 +2059,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G65" t="n">
-        <v>1.9242330789566</v>
+        <v>1.92423319816589</v>
       </c>
       <c r="H65" t="s">
         <v>8</v>
@@ -2085,7 +2085,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G66" t="n">
-        <v>1.9242330789566</v>
+        <v>1.92423319816589</v>
       </c>
       <c r="H66" t="s">
         <v>8</v>
@@ -2137,7 +2137,7 @@
         <v>2.4779999256134</v>
       </c>
       <c r="G68" t="n">
-        <v>1.94622457027435</v>
+        <v>1.94622433185577</v>
       </c>
       <c r="H68" t="s">
         <v>8</v>
@@ -2163,7 +2163,7 @@
         <v>2.48799991607666</v>
       </c>
       <c r="G69" t="n">
-        <v>1.95407819747925</v>
+        <v>1.95407843589783</v>
       </c>
       <c r="H69" t="s">
         <v>8</v>
@@ -2215,7 +2215,7 @@
         <v>2.50200009346008</v>
       </c>
       <c r="G71" t="n">
-        <v>1.9650741815567</v>
+        <v>1.96507394313812</v>
       </c>
       <c r="H71" t="s">
         <v>8</v>
@@ -2241,7 +2241,7 @@
         <v>2.53800010681152</v>
       </c>
       <c r="G72" t="n">
-        <v>1.99334836006165</v>
+        <v>1.99334859848022</v>
       </c>
       <c r="H72" t="s">
         <v>8</v>
@@ -2267,7 +2267,7 @@
         <v>2.55200004577637</v>
       </c>
       <c r="G73" t="n">
-        <v>2.00434422492981</v>
+        <v>2.00434398651123</v>
       </c>
       <c r="H73" t="s">
         <v>8</v>
@@ -2345,7 +2345,7 @@
         <v>2.50200009346008</v>
       </c>
       <c r="G76" t="n">
-        <v>1.9650741815567</v>
+        <v>1.96507394313812</v>
       </c>
       <c r="H76" t="s">
         <v>8</v>
@@ -2371,7 +2371,7 @@
         <v>2.55800008773804</v>
       </c>
       <c r="G77" t="n">
-        <v>2.00905656814575</v>
+        <v>2.00905680656433</v>
       </c>
       <c r="H77" t="s">
         <v>8</v>
@@ -2397,7 +2397,7 @@
         <v>2.57800006866455</v>
       </c>
       <c r="G78" t="n">
-        <v>2.0247642993927</v>
+        <v>2.02476453781128</v>
       </c>
       <c r="H78" t="s">
         <v>8</v>
@@ -2423,7 +2423,7 @@
         <v>2.45799994468689</v>
       </c>
       <c r="G79" t="n">
-        <v>1.93051612377167</v>
+        <v>1.93051636219025</v>
       </c>
       <c r="H79" t="s">
         <v>8</v>
@@ -2449,7 +2449,7 @@
         <v>2.45799994468689</v>
       </c>
       <c r="G80" t="n">
-        <v>1.93051612377167</v>
+        <v>1.93051636219025</v>
       </c>
       <c r="H80" t="s">
         <v>8</v>
@@ -2527,7 +2527,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G83" t="n">
-        <v>1.93994128704071</v>
+        <v>1.93994116783142</v>
       </c>
       <c r="H83" t="s">
         <v>8</v>
@@ -2553,7 +2553,7 @@
         <v>2.48799991607666</v>
       </c>
       <c r="G84" t="n">
-        <v>1.95407819747925</v>
+        <v>1.95407843589783</v>
       </c>
       <c r="H84" t="s">
         <v>8</v>
@@ -2579,7 +2579,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G85" t="n">
-        <v>1.95564901828766</v>
+        <v>1.95564925670624</v>
       </c>
       <c r="H85" t="s">
         <v>8</v>
@@ -2605,7 +2605,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G86" t="n">
-        <v>1.95564901828766</v>
+        <v>1.95564925670624</v>
       </c>
       <c r="H86" t="s">
         <v>8</v>
@@ -2631,7 +2631,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G87" t="n">
-        <v>1.93994128704071</v>
+        <v>1.93994116783142</v>
       </c>
       <c r="H87" t="s">
         <v>8</v>
@@ -2657,7 +2657,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G88" t="n">
-        <v>1.91637933254242</v>
+        <v>1.91637909412384</v>
       </c>
       <c r="H88" t="s">
         <v>8</v>
@@ -2683,7 +2683,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G89" t="n">
-        <v>1.8849630355835</v>
+        <v>1.88496315479279</v>
       </c>
       <c r="H89" t="s">
         <v>8</v>
@@ -2709,7 +2709,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G90" t="n">
-        <v>1.91637933254242</v>
+        <v>1.91637909412384</v>
       </c>
       <c r="H90" t="s">
         <v>8</v>
@@ -2735,7 +2735,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G91" t="n">
-        <v>1.91637933254242</v>
+        <v>1.91637909412384</v>
       </c>
       <c r="H91" t="s">
         <v>8</v>
@@ -2813,7 +2813,7 @@
         <v>2.38599991798401</v>
       </c>
       <c r="G94" t="n">
-        <v>1.87396740913391</v>
+        <v>1.87396728992462</v>
       </c>
       <c r="H94" t="s">
         <v>8</v>
@@ -2839,7 +2839,7 @@
         <v>2.38599991798401</v>
       </c>
       <c r="G95" t="n">
-        <v>1.87396740913391</v>
+        <v>1.87396728992462</v>
       </c>
       <c r="H95" t="s">
         <v>8</v>
@@ -2865,7 +2865,7 @@
         <v>2.29800009727478</v>
       </c>
       <c r="G96" t="n">
-        <v>1.80485200881958</v>
+        <v>1.80485212802887</v>
       </c>
       <c r="H96" t="s">
         <v>8</v>
@@ -2891,7 +2891,7 @@
         <v>2.29800009727478</v>
       </c>
       <c r="G97" t="n">
-        <v>1.80485200881958</v>
+        <v>1.80485212802887</v>
       </c>
       <c r="H97" t="s">
         <v>8</v>
@@ -2917,7 +2917,7 @@
         <v>2.34800004959106</v>
       </c>
       <c r="G98" t="n">
-        <v>1.84412240982056</v>
+        <v>1.84412217140198</v>
       </c>
       <c r="H98" t="s">
         <v>8</v>
@@ -2969,7 +2969,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G100" t="n">
-        <v>1.93378710746765</v>
+        <v>1.93378722667694</v>
       </c>
       <c r="H100" t="s">
         <v>8</v>
@@ -2995,7 +2995,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G101" t="n">
-        <v>1.95017564296722</v>
+        <v>1.95017540454865</v>
       </c>
       <c r="H101" t="s">
         <v>8</v>
@@ -3047,7 +3047,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G103" t="n">
-        <v>1.93378710746765</v>
+        <v>1.93378722667694</v>
       </c>
       <c r="H103" t="s">
         <v>8</v>
@@ -3151,7 +3151,7 @@
         <v>2.38599991798401</v>
       </c>
       <c r="G107" t="n">
-        <v>1.95509171485901</v>
+        <v>1.95509147644043</v>
       </c>
       <c r="H107" t="s">
         <v>8</v>
@@ -3229,7 +3229,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G110" t="n">
-        <v>1.95017564296722</v>
+        <v>1.95017540454865</v>
       </c>
       <c r="H110" t="s">
         <v>8</v>
@@ -3255,7 +3255,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G111" t="n">
-        <v>1.95017564296722</v>
+        <v>1.95017540454865</v>
       </c>
       <c r="H111" t="s">
         <v>8</v>
@@ -3281,7 +3281,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G112" t="n">
-        <v>1.91739916801453</v>
+        <v>1.91739904880524</v>
       </c>
       <c r="H112" t="s">
         <v>8</v>
@@ -3307,7 +3307,7 @@
         <v>2.36199998855591</v>
       </c>
       <c r="G113" t="n">
-        <v>1.9354259967804</v>
+        <v>1.93542611598969</v>
       </c>
       <c r="H113" t="s">
         <v>8</v>
@@ -3333,7 +3333,7 @@
         <v>2.36199998855591</v>
       </c>
       <c r="G114" t="n">
-        <v>1.9354259967804</v>
+        <v>1.93542611598969</v>
       </c>
       <c r="H114" t="s">
         <v>8</v>
@@ -3359,7 +3359,7 @@
         <v>2.36199998855591</v>
       </c>
       <c r="G115" t="n">
-        <v>1.9354259967804</v>
+        <v>1.93542611598969</v>
       </c>
       <c r="H115" t="s">
         <v>8</v>
@@ -3385,7 +3385,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G116" t="n">
-        <v>1.94198095798492</v>
+        <v>1.9419811964035</v>
       </c>
       <c r="H116" t="s">
         <v>8</v>
@@ -3411,7 +3411,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G117" t="n">
-        <v>1.94198095798492</v>
+        <v>1.9419811964035</v>
       </c>
       <c r="H117" t="s">
         <v>8</v>
@@ -3437,7 +3437,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G118" t="n">
-        <v>1.91739916801453</v>
+        <v>1.91739904880524</v>
       </c>
       <c r="H118" t="s">
         <v>8</v>
@@ -3489,7 +3489,7 @@
         <v>2.33200001716614</v>
       </c>
       <c r="G120" t="n">
-        <v>1.91084420681</v>
+        <v>1.91084396839142</v>
       </c>
       <c r="H120" t="s">
         <v>8</v>
@@ -3515,7 +3515,7 @@
         <v>2.33200001716614</v>
       </c>
       <c r="G121" t="n">
-        <v>1.91084420681</v>
+        <v>1.91084396839142</v>
       </c>
       <c r="H121" t="s">
         <v>8</v>
@@ -3593,7 +3593,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G124" t="n">
-        <v>1.83545899391174</v>
+        <v>1.83545887470245</v>
       </c>
       <c r="H124" t="s">
         <v>8</v>
@@ -3645,7 +3645,7 @@
         <v>2.24799990653992</v>
       </c>
       <c r="G126" t="n">
-        <v>1.84201407432556</v>
+        <v>1.84201431274414</v>
       </c>
       <c r="H126" t="s">
         <v>8</v>
@@ -3671,7 +3671,7 @@
         <v>2.23600006103516</v>
       </c>
       <c r="G127" t="n">
-        <v>1.83218145370483</v>
+        <v>1.83218133449554</v>
       </c>
       <c r="H127" t="s">
         <v>8</v>
@@ -3697,7 +3697,7 @@
         <v>2.24799990653992</v>
       </c>
       <c r="G128" t="n">
-        <v>1.84201407432556</v>
+        <v>1.84201431274414</v>
       </c>
       <c r="H128" t="s">
         <v>8</v>
@@ -3723,7 +3723,7 @@
         <v>2.29800009727478</v>
       </c>
       <c r="G129" t="n">
-        <v>1.88298416137695</v>
+        <v>1.88298428058624</v>
       </c>
       <c r="H129" t="s">
         <v>8</v>
@@ -3749,7 +3749,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G130" t="n">
-        <v>1.86823523044586</v>
+        <v>1.86823511123657</v>
       </c>
       <c r="H130" t="s">
         <v>8</v>
@@ -3775,7 +3775,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G131" t="n">
-        <v>1.94198095798492</v>
+        <v>1.9419811964035</v>
       </c>
       <c r="H131" t="s">
         <v>8</v>
@@ -3801,7 +3801,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G132" t="n">
-        <v>1.94198095798492</v>
+        <v>1.9419811964035</v>
       </c>
       <c r="H132" t="s">
         <v>8</v>
@@ -3827,7 +3827,7 @@
         <v>2.32800006866455</v>
       </c>
       <c r="G133" t="n">
-        <v>1.90756630897522</v>
+        <v>1.9075665473938</v>
       </c>
       <c r="H133" t="s">
         <v>8</v>
@@ -3853,7 +3853,7 @@
         <v>2.32800006866455</v>
       </c>
       <c r="G134" t="n">
-        <v>1.90756630897522</v>
+        <v>1.9075665473938</v>
       </c>
       <c r="H134" t="s">
         <v>8</v>
@@ -3879,7 +3879,7 @@
         <v>2.32800006866455</v>
       </c>
       <c r="G135" t="n">
-        <v>1.90756630897522</v>
+        <v>1.9075665473938</v>
       </c>
       <c r="H135" t="s">
         <v>8</v>
@@ -3905,7 +3905,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G136" t="n">
-        <v>1.89281702041626</v>
+        <v>1.89281678199768</v>
       </c>
       <c r="H136" t="s">
         <v>8</v>
@@ -3931,7 +3931,7 @@
         <v>2.32599997520447</v>
       </c>
       <c r="G137" t="n">
-        <v>1.90592741966248</v>
+        <v>1.90592765808105</v>
       </c>
       <c r="H137" t="s">
         <v>8</v>
@@ -3957,7 +3957,7 @@
         <v>2.32599997520447</v>
       </c>
       <c r="G138" t="n">
-        <v>1.90592741966248</v>
+        <v>1.90592765808105</v>
       </c>
       <c r="H138" t="s">
         <v>8</v>
@@ -3983,7 +3983,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G139" t="n">
-        <v>1.88462316989899</v>
+        <v>1.88462293148041</v>
       </c>
       <c r="H139" t="s">
         <v>8</v>
@@ -4009,7 +4009,7 @@
         <v>2.32599997520447</v>
       </c>
       <c r="G140" t="n">
-        <v>1.90592741966248</v>
+        <v>1.90592765808105</v>
       </c>
       <c r="H140" t="s">
         <v>8</v>
@@ -4035,7 +4035,7 @@
         <v>2.32599997520447</v>
       </c>
       <c r="G141" t="n">
-        <v>1.90592741966248</v>
+        <v>1.90592765808105</v>
       </c>
       <c r="H141" t="s">
         <v>8</v>
@@ -4061,7 +4061,7 @@
         <v>2.32800006866455</v>
       </c>
       <c r="G142" t="n">
-        <v>1.90756630897522</v>
+        <v>1.9075665473938</v>
       </c>
       <c r="H142" t="s">
         <v>8</v>
@@ -4087,7 +4087,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G143" t="n">
-        <v>1.90920507907867</v>
+        <v>1.90920519828796</v>
       </c>
       <c r="H143" t="s">
         <v>8</v>
@@ -4113,7 +4113,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G144" t="n">
-        <v>1.90920507907867</v>
+        <v>1.90920519828796</v>
       </c>
       <c r="H144" t="s">
         <v>8</v>
@@ -4139,7 +4139,7 @@
         <v>2.28399991989136</v>
       </c>
       <c r="G145" t="n">
-        <v>1.87151253223419</v>
+        <v>1.87151265144348</v>
       </c>
       <c r="H145" t="s">
         <v>8</v>
@@ -4165,7 +4165,7 @@
         <v>2.31599998474121</v>
       </c>
       <c r="G146" t="n">
-        <v>1.8977335691452</v>
+        <v>1.89773368835449</v>
       </c>
       <c r="H146" t="s">
         <v>8</v>
@@ -4191,7 +4191,7 @@
         <v>2.32599997520447</v>
       </c>
       <c r="G147" t="n">
-        <v>1.90592741966248</v>
+        <v>1.90592765808105</v>
       </c>
       <c r="H147" t="s">
         <v>8</v>
@@ -4217,7 +4217,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G148" t="n">
-        <v>1.90920507907867</v>
+        <v>1.90920519828796</v>
       </c>
       <c r="H148" t="s">
         <v>8</v>
@@ -4321,7 +4321,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G152" t="n">
-        <v>1.7862948179245</v>
+        <v>1.78629493713379</v>
       </c>
       <c r="H152" t="s">
         <v>8</v>
@@ -4347,7 +4347,7 @@
         <v>2.16799998283386</v>
       </c>
       <c r="G153" t="n">
-        <v>1.77646195888519</v>
+        <v>1.77646219730377</v>
       </c>
       <c r="H153" t="s">
         <v>8</v>
@@ -4373,7 +4373,7 @@
         <v>2.13800001144409</v>
       </c>
       <c r="G154" t="n">
-        <v>1.75188004970551</v>
+        <v>1.75188016891479</v>
       </c>
       <c r="H154" t="s">
         <v>8</v>
@@ -4477,7 +4477,7 @@
         <v>2.13599991798401</v>
       </c>
       <c r="G158" t="n">
-        <v>1.75024116039276</v>
+        <v>1.75024127960205</v>
       </c>
       <c r="H158" t="s">
         <v>8</v>
@@ -4503,7 +4503,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G159" t="n">
-        <v>1.72074270248413</v>
+        <v>1.72074282169342</v>
       </c>
       <c r="H159" t="s">
         <v>8</v>
@@ -4529,7 +4529,7 @@
         <v>2.03800010681152</v>
       </c>
       <c r="G160" t="n">
-        <v>1.66993999481201</v>
+        <v>1.6699401140213</v>
       </c>
       <c r="H160" t="s">
         <v>8</v>
@@ -4555,7 +4555,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G161" t="n">
-        <v>1.72893679141998</v>
+        <v>1.72893691062927</v>
       </c>
       <c r="H161" t="s">
         <v>8</v>
@@ -4581,7 +4581,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G162" t="n">
-        <v>1.72893679141998</v>
+        <v>1.72893691062927</v>
       </c>
       <c r="H162" t="s">
         <v>8</v>
@@ -4633,7 +4633,7 @@
         <v>2.14800000190735</v>
       </c>
       <c r="G164" t="n">
-        <v>1.76007401943207</v>
+        <v>1.76007413864136</v>
       </c>
       <c r="H164" t="s">
         <v>8</v>
@@ -4659,7 +4659,7 @@
         <v>2.14800000190735</v>
       </c>
       <c r="G165" t="n">
-        <v>1.76007401943207</v>
+        <v>1.76007413864136</v>
       </c>
       <c r="H165" t="s">
         <v>8</v>
@@ -4685,7 +4685,7 @@
         <v>2.14800000190735</v>
       </c>
       <c r="G166" t="n">
-        <v>1.76007401943207</v>
+        <v>1.76007413864136</v>
       </c>
       <c r="H166" t="s">
         <v>8</v>
@@ -4711,7 +4711,7 @@
         <v>2.14800000190735</v>
       </c>
       <c r="G167" t="n">
-        <v>1.76007401943207</v>
+        <v>1.76007413864136</v>
       </c>
       <c r="H167" t="s">
         <v>8</v>
@@ -4737,7 +4737,7 @@
         <v>2.14800000190735</v>
       </c>
       <c r="G168" t="n">
-        <v>1.76007401943207</v>
+        <v>1.76007413864136</v>
       </c>
       <c r="H168" t="s">
         <v>8</v>
@@ -4763,7 +4763,7 @@
         <v>2.14800000190735</v>
       </c>
       <c r="G169" t="n">
-        <v>1.76007401943207</v>
+        <v>1.76007413864136</v>
       </c>
       <c r="H169" t="s">
         <v>8</v>
@@ -4789,7 +4789,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G170" t="n">
-        <v>1.70435476303101</v>
+        <v>1.70435464382172</v>
       </c>
       <c r="H170" t="s">
         <v>8</v>
@@ -4815,7 +4815,7 @@
         <v>2.11800003051758</v>
       </c>
       <c r="G171" t="n">
-        <v>1.73549211025238</v>
+        <v>1.73549199104309</v>
       </c>
       <c r="H171" t="s">
         <v>8</v>
@@ -4841,7 +4841,7 @@
         <v>2.1159999370575</v>
       </c>
       <c r="G172" t="n">
-        <v>1.73385322093964</v>
+        <v>1.73385310173035</v>
       </c>
       <c r="H172" t="s">
         <v>8</v>
@@ -4867,7 +4867,7 @@
         <v>2.1159999370575</v>
       </c>
       <c r="G173" t="n">
-        <v>1.73385322093964</v>
+        <v>1.73385310173035</v>
       </c>
       <c r="H173" t="s">
         <v>8</v>
@@ -4893,7 +4893,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G174" t="n">
-        <v>1.71254873275757</v>
+        <v>1.71254885196686</v>
       </c>
       <c r="H174" t="s">
         <v>8</v>
@@ -4919,7 +4919,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G175" t="n">
-        <v>1.63060879707336</v>
+        <v>1.63060867786407</v>
       </c>
       <c r="H175" t="s">
         <v>8</v>
@@ -5023,7 +5023,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G179" t="n">
-        <v>1.62241458892822</v>
+        <v>1.62241470813751</v>
       </c>
       <c r="H179" t="s">
         <v>8</v>
@@ -5049,7 +5049,7 @@
         <v>2.03800010681152</v>
       </c>
       <c r="G180" t="n">
-        <v>1.66993999481201</v>
+        <v>1.6699401140213</v>
       </c>
       <c r="H180" t="s">
         <v>8</v>
@@ -5075,7 +5075,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G181" t="n">
-        <v>1.66338467597961</v>
+        <v>1.6633847951889</v>
       </c>
       <c r="H181" t="s">
         <v>8</v>
@@ -5153,7 +5153,7 @@
         <v>2.04200005531311</v>
       </c>
       <c r="G184" t="n">
-        <v>1.67321765422821</v>
+        <v>1.67321753501892</v>
       </c>
       <c r="H184" t="s">
         <v>8</v>
@@ -5205,7 +5205,7 @@
         <v>2.03800010681152</v>
       </c>
       <c r="G186" t="n">
-        <v>1.66993999481201</v>
+        <v>1.6699401140213</v>
       </c>
       <c r="H186" t="s">
         <v>8</v>
@@ -5231,7 +5231,7 @@
         <v>2.03800010681152</v>
       </c>
       <c r="G187" t="n">
-        <v>1.66993999481201</v>
+        <v>1.6699401140213</v>
       </c>
       <c r="H187" t="s">
         <v>8</v>
@@ -5257,7 +5257,7 @@
         <v>2.03800010681152</v>
       </c>
       <c r="G188" t="n">
-        <v>1.66993999481201</v>
+        <v>1.6699401140213</v>
       </c>
       <c r="H188" t="s">
         <v>8</v>
@@ -5309,7 +5309,7 @@
         <v>2</v>
       </c>
       <c r="G190" t="n">
-        <v>1.63880276679993</v>
+        <v>1.63880264759064</v>
       </c>
       <c r="H190" t="s">
         <v>8</v>
@@ -5361,7 +5361,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G192" t="n">
-        <v>1.66338467597961</v>
+        <v>1.6633847951889</v>
       </c>
       <c r="H192" t="s">
         <v>8</v>
@@ -5413,7 +5413,7 @@
         <v>2.03800010681152</v>
       </c>
       <c r="G194" t="n">
-        <v>1.66993999481201</v>
+        <v>1.6699401140213</v>
       </c>
       <c r="H194" t="s">
         <v>8</v>
@@ -5491,7 +5491,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G197" t="n">
-        <v>1.65519070625305</v>
+        <v>1.65519058704376</v>
       </c>
       <c r="H197" t="s">
         <v>8</v>
@@ -5517,7 +5517,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G198" t="n">
-        <v>1.65519070625305</v>
+        <v>1.65519058704376</v>
       </c>
       <c r="H198" t="s">
         <v>8</v>
@@ -5543,7 +5543,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G199" t="n">
-        <v>1.65519070625305</v>
+        <v>1.65519058704376</v>
       </c>
       <c r="H199" t="s">
         <v>8</v>
@@ -5569,7 +5569,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G200" t="n">
-        <v>1.65519070625305</v>
+        <v>1.65519058704376</v>
       </c>
       <c r="H200" t="s">
         <v>8</v>
@@ -5595,7 +5595,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G201" t="n">
-        <v>1.65519070625305</v>
+        <v>1.65519058704376</v>
       </c>
       <c r="H201" t="s">
         <v>8</v>
@@ -5621,7 +5621,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G202" t="n">
-        <v>1.6469966173172</v>
+        <v>1.64699673652649</v>
       </c>
       <c r="H202" t="s">
         <v>8</v>
@@ -5647,7 +5647,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G203" t="n">
-        <v>1.6469966173172</v>
+        <v>1.64699673652649</v>
       </c>
       <c r="H203" t="s">
         <v>8</v>
@@ -5673,7 +5673,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G204" t="n">
-        <v>1.6469966173172</v>
+        <v>1.64699673652649</v>
       </c>
       <c r="H204" t="s">
         <v>8</v>
@@ -5699,7 +5699,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G205" t="n">
-        <v>1.6469966173172</v>
+        <v>1.64699673652649</v>
       </c>
       <c r="H205" t="s">
         <v>8</v>
@@ -5725,7 +5725,7 @@
         <v>1.99899995326996</v>
       </c>
       <c r="G206" t="n">
-        <v>1.63798308372498</v>
+        <v>1.63798320293427</v>
       </c>
       <c r="H206" t="s">
         <v>8</v>
@@ -5803,7 +5803,7 @@
         <v>1.932000041008</v>
       </c>
       <c r="G209" t="n">
-        <v>1.58308351039886</v>
+        <v>1.58308339118958</v>
       </c>
       <c r="H209" t="s">
         <v>8</v>
@@ -5933,7 +5933,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G214" t="n">
-        <v>1.54047465324402</v>
+        <v>1.54047453403473</v>
       </c>
       <c r="H214" t="s">
         <v>8</v>
@@ -6011,7 +6011,7 @@
         <v>1.91199994087219</v>
       </c>
       <c r="G217" t="n">
-        <v>1.56669521331787</v>
+        <v>1.56669533252716</v>
       </c>
       <c r="H217" t="s">
         <v>8</v>
@@ -6037,7 +6037,7 @@
         <v>1.90199995040894</v>
       </c>
       <c r="G218" t="n">
-        <v>1.5585013628006</v>
+        <v>1.55850124359131</v>
       </c>
       <c r="H218" t="s">
         <v>8</v>
@@ -6219,7 +6219,7 @@
         <v>1.85399997234344</v>
       </c>
       <c r="G225" t="n">
-        <v>1.51916992664337</v>
+        <v>1.51917004585266</v>
       </c>
       <c r="H225" t="s">
         <v>8</v>
@@ -6271,7 +6271,7 @@
         <v>1.8860000371933</v>
       </c>
       <c r="G227" t="n">
-        <v>1.54539108276367</v>
+        <v>1.54539096355438</v>
       </c>
       <c r="H227" t="s">
         <v>8</v>
@@ -6349,7 +6349,7 @@
         <v>1.70200002193451</v>
       </c>
       <c r="G230" t="n">
-        <v>1.39462101459503</v>
+        <v>1.39462113380432</v>
       </c>
       <c r="H230" t="s">
         <v>8</v>
@@ -6427,7 +6427,7 @@
         <v>1.87199997901917</v>
       </c>
       <c r="G233" t="n">
-        <v>1.53391945362091</v>
+        <v>1.53391933441162</v>
       </c>
       <c r="H233" t="s">
         <v>8</v>
@@ -6661,7 +6661,7 @@
         <v>1.89800000190735</v>
       </c>
       <c r="G242" t="n">
-        <v>1.55522382259369</v>
+        <v>1.5552237033844</v>
       </c>
       <c r="H242" t="s">
         <v>8</v>
@@ -6687,7 +6687,7 @@
         <v>1.89800000190735</v>
       </c>
       <c r="G243" t="n">
-        <v>1.55522382259369</v>
+        <v>1.5552237033844</v>
       </c>
       <c r="H243" t="s">
         <v>8</v>
@@ -6739,7 +6739,7 @@
         <v>1.90900003910065</v>
       </c>
       <c r="G245" t="n">
-        <v>1.56423711776733</v>
+        <v>1.56423723697662</v>
       </c>
       <c r="H245" t="s">
         <v>8</v>
@@ -6765,7 +6765,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G246" t="n">
-        <v>1.54047465324402</v>
+        <v>1.54047453403473</v>
       </c>
       <c r="H246" t="s">
         <v>8</v>
@@ -6869,7 +6869,7 @@
         <v>1.85699999332428</v>
       </c>
       <c r="G250" t="n">
-        <v>1.52162826061249</v>
+        <v>1.52162837982178</v>
       </c>
       <c r="H250" t="s">
         <v>8</v>
@@ -6895,7 +6895,7 @@
         <v>1.88100004196167</v>
       </c>
       <c r="G251" t="n">
-        <v>1.54129385948181</v>
+        <v>1.5412939786911</v>
       </c>
       <c r="H251" t="s">
         <v>8</v>
@@ -6999,7 +6999,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G255" t="n">
-        <v>1.51589250564575</v>
+        <v>1.51589238643646</v>
       </c>
       <c r="H255" t="s">
         <v>8</v>
@@ -7051,7 +7051,7 @@
         <v>1.84099996089935</v>
       </c>
       <c r="G257" t="n">
-        <v>1.50851786136627</v>
+        <v>1.50851774215698</v>
       </c>
       <c r="H257" t="s">
         <v>8</v>
@@ -7077,7 +7077,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G258" t="n">
-        <v>1.53228044509888</v>
+        <v>1.53228056430817</v>
       </c>
       <c r="H258" t="s">
         <v>8</v>
@@ -7103,7 +7103,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G259" t="n">
-        <v>1.53228044509888</v>
+        <v>1.53228056430817</v>
       </c>
       <c r="H259" t="s">
         <v>8</v>
@@ -7155,7 +7155,7 @@
         <v>1.84099996089935</v>
       </c>
       <c r="G261" t="n">
-        <v>1.50851786136627</v>
+        <v>1.50851774215698</v>
       </c>
       <c r="H261" t="s">
         <v>8</v>
@@ -7259,7 +7259,7 @@
         <v>1.83399999141693</v>
       </c>
       <c r="G265" t="n">
-        <v>1.50278222560883</v>
+        <v>1.50278210639954</v>
       </c>
       <c r="H265" t="s">
         <v>8</v>
@@ -7311,7 +7311,7 @@
         <v>1.84300005435944</v>
       </c>
       <c r="G267" t="n">
-        <v>1.51015663146973</v>
+        <v>1.51015675067902</v>
       </c>
       <c r="H267" t="s">
         <v>8</v>
@@ -7337,7 +7337,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G268" t="n">
-        <v>1.54047465324402</v>
+        <v>1.54047453403473</v>
       </c>
       <c r="H268" t="s">
         <v>8</v>
@@ -7363,7 +7363,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G269" t="n">
-        <v>1.57325053215027</v>
+        <v>1.57325065135956</v>
       </c>
       <c r="H269" t="s">
         <v>8</v>
@@ -7441,7 +7441,7 @@
         <v>1.94599997997284</v>
       </c>
       <c r="G272" t="n">
-        <v>1.59455502033234</v>
+        <v>1.59455490112305</v>
       </c>
       <c r="H272" t="s">
         <v>8</v>
@@ -7467,7 +7467,7 @@
         <v>1.96099996566772</v>
       </c>
       <c r="G273" t="n">
-        <v>1.60684585571289</v>
+        <v>1.60684597492218</v>
       </c>
       <c r="H273" t="s">
         <v>8</v>
@@ -7571,7 +7571,7 @@
         <v>1.91799998283386</v>
       </c>
       <c r="G277" t="n">
-        <v>1.57161176204681</v>
+        <v>1.5716118812561</v>
       </c>
       <c r="H277" t="s">
         <v>8</v>
@@ -7623,7 +7623,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G279" t="n">
-        <v>1.53228044509888</v>
+        <v>1.53228056430817</v>
       </c>
       <c r="H279" t="s">
         <v>8</v>
@@ -7649,7 +7649,7 @@
         <v>1.9190000295639</v>
       </c>
       <c r="G280" t="n">
-        <v>1.57243120670319</v>
+        <v>1.57243132591248</v>
       </c>
       <c r="H280" t="s">
         <v>8</v>
@@ -7701,7 +7701,7 @@
         <v>1.88699996471405</v>
       </c>
       <c r="G282" t="n">
-        <v>1.54621028900146</v>
+        <v>1.54621016979218</v>
       </c>
       <c r="H282" t="s">
         <v>8</v>
@@ -7727,7 +7727,7 @@
         <v>1.90100002288818</v>
       </c>
       <c r="G283" t="n">
-        <v>1.55768191814423</v>
+        <v>1.55768203735352</v>
       </c>
       <c r="H283" t="s">
         <v>8</v>
@@ -7831,7 +7831,7 @@
         <v>1.93099999427795</v>
       </c>
       <c r="G287" t="n">
-        <v>1.58226382732391</v>
+        <v>1.5822639465332</v>
       </c>
       <c r="H287" t="s">
         <v>8</v>
@@ -7857,7 +7857,7 @@
         <v>1.88699996471405</v>
       </c>
       <c r="G288" t="n">
-        <v>1.54621028900146</v>
+        <v>1.54621016979218</v>
       </c>
       <c r="H288" t="s">
         <v>8</v>
@@ -7883,7 +7883,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G289" t="n">
-        <v>1.54047465324402</v>
+        <v>1.54047453403473</v>
       </c>
       <c r="H289" t="s">
         <v>8</v>
@@ -7961,7 +7961,7 @@
         <v>1.87800002098083</v>
       </c>
       <c r="G292" t="n">
-        <v>1.53883588314056</v>
+        <v>1.53883564472198</v>
       </c>
       <c r="H292" t="s">
         <v>8</v>
@@ -8039,7 +8039,7 @@
         <v>1.88900005817413</v>
       </c>
       <c r="G295" t="n">
-        <v>1.54784917831421</v>
+        <v>1.54784905910492</v>
       </c>
       <c r="H295" t="s">
         <v>8</v>
@@ -8065,7 +8065,7 @@
         <v>1.88900005817413</v>
       </c>
       <c r="G296" t="n">
-        <v>1.54784917831421</v>
+        <v>1.54784905910492</v>
       </c>
       <c r="H296" t="s">
         <v>8</v>
@@ -8195,7 +8195,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G301" t="n">
-        <v>1.53228044509888</v>
+        <v>1.53228056430817</v>
       </c>
       <c r="H301" t="s">
         <v>8</v>
@@ -8273,7 +8273,7 @@
         <v>1.875</v>
       </c>
       <c r="G304" t="n">
-        <v>1.53637754917145</v>
+        <v>1.53637742996216</v>
       </c>
       <c r="H304" t="s">
         <v>8</v>
@@ -8403,7 +8403,7 @@
         <v>2</v>
       </c>
       <c r="G309" t="n">
-        <v>1.63880276679993</v>
+        <v>1.63880264759064</v>
       </c>
       <c r="H309" t="s">
         <v>8</v>
@@ -8429,7 +8429,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G310" t="n">
-        <v>1.63060879707336</v>
+        <v>1.63060867786407</v>
       </c>
       <c r="H310" t="s">
         <v>8</v>
@@ -8455,7 +8455,7 @@
         <v>2.01600003242493</v>
       </c>
       <c r="G311" t="n">
-        <v>1.65191304683685</v>
+        <v>1.65191316604614</v>
       </c>
       <c r="H311" t="s">
         <v>8</v>
@@ -8481,7 +8481,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G312" t="n">
-        <v>1.6469966173172</v>
+        <v>1.64699673652649</v>
       </c>
       <c r="H312" t="s">
         <v>8</v>
@@ -8533,7 +8533,7 @@
         <v>2.04200005531311</v>
       </c>
       <c r="G314" t="n">
-        <v>1.67321765422821</v>
+        <v>1.67321753501892</v>
       </c>
       <c r="H314" t="s">
         <v>8</v>
@@ -8559,7 +8559,7 @@
         <v>2.01799988746643</v>
       </c>
       <c r="G315" t="n">
-        <v>1.65355169773102</v>
+        <v>1.65355181694031</v>
       </c>
       <c r="H315" t="s">
         <v>8</v>
@@ -8585,7 +8585,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G316" t="n">
-        <v>1.65519070625305</v>
+        <v>1.65519058704376</v>
       </c>
       <c r="H316" t="s">
         <v>8</v>
@@ -8611,7 +8611,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G317" t="n">
-        <v>1.66338467597961</v>
+        <v>1.6633847951889</v>
       </c>
       <c r="H317" t="s">
         <v>8</v>
@@ -8637,7 +8637,7 @@
         <v>2.29800009727478</v>
       </c>
       <c r="G318" t="n">
-        <v>1.88298416137695</v>
+        <v>1.88298428058624</v>
       </c>
       <c r="H318" t="s">
         <v>8</v>
@@ -8689,7 +8689,7 @@
         <v>2.23200011253357</v>
       </c>
       <c r="G320" t="n">
-        <v>1.82890379428864</v>
+        <v>1.82890391349792</v>
       </c>
       <c r="H320" t="s">
         <v>8</v>
@@ -8715,7 +8715,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G321" t="n">
-        <v>1.7862948179245</v>
+        <v>1.78629493713379</v>
       </c>
       <c r="H321" t="s">
         <v>8</v>
@@ -8741,7 +8741,7 @@
         <v>2.21799993515015</v>
       </c>
       <c r="G322" t="n">
-        <v>1.81743204593658</v>
+        <v>1.81743216514587</v>
       </c>
       <c r="H322" t="s">
         <v>8</v>
@@ -8767,7 +8767,7 @@
         <v>2.21600008010864</v>
       </c>
       <c r="G323" t="n">
-        <v>1.81579327583313</v>
+        <v>1.81579351425171</v>
       </c>
       <c r="H323" t="s">
         <v>8</v>
@@ -8819,7 +8819,7 @@
         <v>2.29399991035461</v>
       </c>
       <c r="G325" t="n">
-        <v>1.87970662117004</v>
+        <v>1.87970650196075</v>
       </c>
       <c r="H325" t="s">
         <v>8</v>
@@ -8845,7 +8845,7 @@
         <v>2.24799990653992</v>
       </c>
       <c r="G326" t="n">
-        <v>1.84201407432556</v>
+        <v>1.84201431274414</v>
       </c>
       <c r="H326" t="s">
         <v>8</v>
@@ -8871,7 +8871,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G327" t="n">
-        <v>1.79448914527893</v>
+        <v>1.79448890686035</v>
       </c>
       <c r="H327" t="s">
         <v>8</v>
@@ -8897,7 +8897,7 @@
         <v>2.19799995422363</v>
       </c>
       <c r="G328" t="n">
-        <v>1.80104410648346</v>
+        <v>1.80104398727417</v>
       </c>
       <c r="H328" t="s">
         <v>8</v>
@@ -8949,7 +8949,7 @@
         <v>2.21600008010864</v>
       </c>
       <c r="G330" t="n">
-        <v>1.81579327583313</v>
+        <v>1.81579351425171</v>
       </c>
       <c r="H330" t="s">
         <v>8</v>
@@ -8975,7 +8975,7 @@
         <v>2.19799995422363</v>
       </c>
       <c r="G331" t="n">
-        <v>1.80104410648346</v>
+        <v>1.80104398727417</v>
       </c>
       <c r="H331" t="s">
         <v>8</v>
@@ -9027,7 +9027,7 @@
         <v>2.10800004005432</v>
       </c>
       <c r="G333" t="n">
-        <v>1.72729802131653</v>
+        <v>1.72729814052582</v>
       </c>
       <c r="H333" t="s">
         <v>8</v>
@@ -9053,7 +9053,7 @@
         <v>2.13199996948242</v>
       </c>
       <c r="G334" t="n">
-        <v>1.74696362018585</v>
+        <v>1.74696373939514</v>
       </c>
       <c r="H334" t="s">
         <v>8</v>
@@ -9079,7 +9079,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G335" t="n">
-        <v>1.72893679141998</v>
+        <v>1.72893691062927</v>
       </c>
       <c r="H335" t="s">
         <v>8</v>
@@ -9105,7 +9105,7 @@
         <v>2.15199995040894</v>
       </c>
       <c r="G336" t="n">
-        <v>1.76335179805756</v>
+        <v>1.76335167884827</v>
       </c>
       <c r="H336" t="s">
         <v>8</v>
@@ -9183,7 +9183,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G339" t="n">
-        <v>1.83545899391174</v>
+        <v>1.83545887470245</v>
       </c>
       <c r="H339" t="s">
         <v>8</v>
@@ -9209,7 +9209,7 @@
         <v>2.25399994850159</v>
       </c>
       <c r="G340" t="n">
-        <v>1.84693038463593</v>
+        <v>1.84693074226379</v>
       </c>
       <c r="H340" t="s">
         <v>8</v>
@@ -9235,7 +9235,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G341" t="n">
-        <v>1.81087684631348</v>
+        <v>1.81087708473206</v>
       </c>
       <c r="H341" t="s">
         <v>8</v>
@@ -9261,7 +9261,7 @@
         <v>2.20799994468689</v>
       </c>
       <c r="G342" t="n">
-        <v>1.80923807621002</v>
+        <v>1.8092383146286</v>
       </c>
       <c r="H342" t="s">
         <v>8</v>
@@ -9313,7 +9313,7 @@
         <v>2.2720000743866</v>
       </c>
       <c r="G344" t="n">
-        <v>1.86168003082275</v>
+        <v>1.86167979240417</v>
       </c>
       <c r="H344" t="s">
         <v>8</v>
@@ -9339,7 +9339,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G345" t="n">
-        <v>1.83545899391174</v>
+        <v>1.83545887470245</v>
       </c>
       <c r="H345" t="s">
         <v>8</v>
@@ -9365,7 +9365,7 @@
         <v>2.27600002288818</v>
       </c>
       <c r="G346" t="n">
-        <v>1.86495757102966</v>
+        <v>1.86495733261108</v>
       </c>
       <c r="H346" t="s">
         <v>8</v>
@@ -9417,7 +9417,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G348" t="n">
-        <v>1.87642872333527</v>
+        <v>1.87642896175385</v>
       </c>
       <c r="H348" t="s">
         <v>8</v>
@@ -9443,7 +9443,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G349" t="n">
-        <v>1.88462316989899</v>
+        <v>1.88462293148041</v>
       </c>
       <c r="H349" t="s">
         <v>8</v>
@@ -9469,7 +9469,7 @@
         <v>2.31800007820129</v>
       </c>
       <c r="G350" t="n">
-        <v>1.89937245845795</v>
+        <v>1.89937257766724</v>
       </c>
       <c r="H350" t="s">
         <v>8</v>
@@ -9495,7 +9495,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G351" t="n">
-        <v>1.91739916801453</v>
+        <v>1.91739904880524</v>
       </c>
       <c r="H351" t="s">
         <v>8</v>
@@ -9521,7 +9521,7 @@
         <v>2.25600004196167</v>
       </c>
       <c r="G352" t="n">
-        <v>1.84856951236725</v>
+        <v>1.84856963157654</v>
       </c>
       <c r="H352" t="s">
         <v>8</v>
@@ -9547,7 +9547,7 @@
         <v>2.27600002288818</v>
       </c>
       <c r="G353" t="n">
-        <v>1.86495757102966</v>
+        <v>1.86495733261108</v>
       </c>
       <c r="H353" t="s">
         <v>8</v>
@@ -9573,7 +9573,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G354" t="n">
-        <v>1.86823523044586</v>
+        <v>1.86823511123657</v>
       </c>
       <c r="H354" t="s">
         <v>8</v>
@@ -9599,7 +9599,7 @@
         <v>2.24600005149841</v>
       </c>
       <c r="G355" t="n">
-        <v>1.92479634284973</v>
+        <v>1.92479646205902</v>
       </c>
       <c r="H355" t="s">
         <v>8</v>
@@ -9625,7 +9625,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G356" t="n">
-        <v>1.93679392337799</v>
+        <v>1.93679428100586</v>
       </c>
       <c r="H356" t="s">
         <v>8</v>
@@ -9651,7 +9651,7 @@
         <v>2.26200008392334</v>
       </c>
       <c r="G357" t="n">
-        <v>1.93850815296173</v>
+        <v>1.93850803375244</v>
       </c>
       <c r="H357" t="s">
         <v>8</v>
@@ -9677,7 +9677,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G358" t="n">
-        <v>1.97107374668121</v>
+        <v>1.97107350826263</v>
       </c>
       <c r="H358" t="s">
         <v>8</v>
@@ -9703,7 +9703,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G359" t="n">
-        <v>1.97107374668121</v>
+        <v>1.97107350826263</v>
       </c>
       <c r="H359" t="s">
         <v>8</v>
@@ -9729,7 +9729,7 @@
         <v>2.25</v>
       </c>
       <c r="G360" t="n">
-        <v>1.92822432518005</v>
+        <v>1.92822444438934</v>
       </c>
       <c r="H360" t="s">
         <v>8</v>
@@ -9755,7 +9755,7 @@
         <v>2.26600003242493</v>
       </c>
       <c r="G361" t="n">
-        <v>1.94193613529205</v>
+        <v>1.94193601608276</v>
       </c>
       <c r="H361" t="s">
         <v>8</v>
@@ -9885,7 +9885,7 @@
         <v>2.25</v>
       </c>
       <c r="G366" t="n">
-        <v>1.92822432518005</v>
+        <v>1.92822444438934</v>
       </c>
       <c r="H366" t="s">
         <v>8</v>
@@ -9911,7 +9911,7 @@
         <v>2.24799990653992</v>
       </c>
       <c r="G367" t="n">
-        <v>1.92651009559631</v>
+        <v>1.92651033401489</v>
       </c>
       <c r="H367" t="s">
         <v>8</v>
@@ -9937,7 +9937,7 @@
         <v>2.24799990653992</v>
       </c>
       <c r="G368" t="n">
-        <v>1.92651009559631</v>
+        <v>1.92651033401489</v>
       </c>
       <c r="H368" t="s">
         <v>8</v>
@@ -10015,7 +10015,7 @@
         <v>2.25600004196167</v>
       </c>
       <c r="G371" t="n">
-        <v>1.93336629867554</v>
+        <v>1.93336641788483</v>
       </c>
       <c r="H371" t="s">
         <v>8</v>
@@ -10041,7 +10041,7 @@
         <v>2.22399997711182</v>
       </c>
       <c r="G372" t="n">
-        <v>1.90594244003296</v>
+        <v>1.90594255924225</v>
       </c>
       <c r="H372" t="s">
         <v>8</v>
@@ -10067,7 +10067,7 @@
         <v>2.22399997711182</v>
       </c>
       <c r="G373" t="n">
-        <v>1.90594244003296</v>
+        <v>1.90594255924225</v>
       </c>
       <c r="H373" t="s">
         <v>8</v>
@@ -10093,7 +10093,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G374" t="n">
-        <v>1.89394462108612</v>
+        <v>1.8939448595047</v>
       </c>
       <c r="H374" t="s">
         <v>8</v>
@@ -10145,7 +10145,7 @@
         <v>2.25200009346008</v>
       </c>
       <c r="G376" t="n">
-        <v>1.92993831634521</v>
+        <v>1.92993855476379</v>
       </c>
       <c r="H376" t="s">
         <v>8</v>
@@ -10171,7 +10171,7 @@
         <v>2.21799993515015</v>
       </c>
       <c r="G377" t="n">
-        <v>1.90080058574677</v>
+        <v>1.90080070495605</v>
       </c>
       <c r="H377" t="s">
         <v>8</v>
@@ -10197,7 +10197,7 @@
         <v>2.23399996757507</v>
       </c>
       <c r="G378" t="n">
-        <v>1.91451251506805</v>
+        <v>1.91451239585876</v>
       </c>
       <c r="H378" t="s">
         <v>8</v>
@@ -10223,7 +10223,7 @@
         <v>2.20199990272522</v>
       </c>
       <c r="G379" t="n">
-        <v>1.88708877563477</v>
+        <v>1.88708865642548</v>
       </c>
       <c r="H379" t="s">
         <v>8</v>
@@ -10249,7 +10249,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G380" t="n">
-        <v>1.87680518627167</v>
+        <v>1.87680494785309</v>
       </c>
       <c r="H380" t="s">
         <v>8</v>
@@ -10327,7 +10327,7 @@
         <v>2.18199992179871</v>
       </c>
       <c r="G383" t="n">
-        <v>1.86994898319244</v>
+        <v>1.86994886398315</v>
       </c>
       <c r="H383" t="s">
         <v>8</v>
@@ -10353,7 +10353,7 @@
         <v>2.2039999961853</v>
       </c>
       <c r="G384" t="n">
-        <v>1.88880276679993</v>
+        <v>1.88880300521851</v>
       </c>
       <c r="H384" t="s">
         <v>8</v>
@@ -10379,7 +10379,7 @@
         <v>2.2279999256134</v>
       </c>
       <c r="G385" t="n">
-        <v>1.90937066078186</v>
+        <v>1.90937054157257</v>
       </c>
       <c r="H385" t="s">
         <v>8</v>
@@ -10431,7 +10431,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G387" t="n">
-        <v>1.89394462108612</v>
+        <v>1.8939448595047</v>
       </c>
       <c r="H387" t="s">
         <v>8</v>
@@ -10457,7 +10457,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G388" t="n">
-        <v>1.89394462108612</v>
+        <v>1.8939448595047</v>
       </c>
       <c r="H388" t="s">
         <v>8</v>
@@ -10483,7 +10483,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G389" t="n">
-        <v>1.89394462108612</v>
+        <v>1.8939448595047</v>
       </c>
       <c r="H389" t="s">
         <v>8</v>
@@ -10509,7 +10509,7 @@
         <v>2.23399996757507</v>
       </c>
       <c r="G390" t="n">
-        <v>1.91451251506805</v>
+        <v>1.91451239585876</v>
       </c>
       <c r="H390" t="s">
         <v>8</v>
@@ -10561,7 +10561,7 @@
         <v>2.25600004196167</v>
       </c>
       <c r="G392" t="n">
-        <v>1.93336629867554</v>
+        <v>1.93336641788483</v>
       </c>
       <c r="H392" t="s">
         <v>8</v>
@@ -10639,7 +10639,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G395" t="n">
-        <v>1.96250355243683</v>
+        <v>1.96250379085541</v>
       </c>
       <c r="H395" t="s">
         <v>8</v>
@@ -10665,7 +10665,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G396" t="n">
-        <v>1.97107374668121</v>
+        <v>1.97107350826263</v>
       </c>
       <c r="H396" t="s">
         <v>8</v>
@@ -10899,7 +10899,7 @@
         <v>2.42600011825562</v>
       </c>
       <c r="G405" t="n">
-        <v>2.07905435562134</v>
+        <v>2.07905411720276</v>
       </c>
       <c r="H405" t="s">
         <v>8</v>
@@ -10951,7 +10951,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G407" t="n">
-        <v>2.06534266471863</v>
+        <v>2.06534242630005</v>
       </c>
       <c r="H407" t="s">
         <v>8</v>
@@ -10977,7 +10977,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G408" t="n">
-        <v>2.06534266471863</v>
+        <v>2.06534242630005</v>
       </c>
       <c r="H408" t="s">
         <v>8</v>
@@ -11133,7 +11133,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G414" t="n">
-        <v>2.1081919670105</v>
+        <v>2.10819172859192</v>
       </c>
       <c r="H414" t="s">
         <v>8</v>
@@ -11159,7 +11159,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G415" t="n">
-        <v>2.09962177276611</v>
+        <v>2.09962201118469</v>
       </c>
       <c r="H415" t="s">
         <v>8</v>
@@ -11211,7 +11211,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G417" t="n">
-        <v>2.03963303565979</v>
+        <v>2.03963279724121</v>
       </c>
       <c r="H417" t="s">
         <v>8</v>
@@ -11263,7 +11263,7 @@
         <v>2.46799993515015</v>
       </c>
       <c r="G419" t="n">
-        <v>2.11504769325256</v>
+        <v>2.11504793167114</v>
       </c>
       <c r="H419" t="s">
         <v>8</v>
@@ -11289,7 +11289,7 @@
         <v>2.46799993515015</v>
       </c>
       <c r="G420" t="n">
-        <v>2.11504769325256</v>
+        <v>2.11504793167114</v>
       </c>
       <c r="H420" t="s">
         <v>8</v>
@@ -11341,7 +11341,7 @@
         <v>2.44799995422363</v>
       </c>
       <c r="G422" t="n">
-        <v>2.09790825843811</v>
+        <v>2.09790802001953</v>
       </c>
       <c r="H422" t="s">
         <v>8</v>
@@ -11367,7 +11367,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G423" t="n">
-        <v>2.11676168441772</v>
+        <v>2.1167619228363</v>
       </c>
       <c r="H423" t="s">
         <v>8</v>
@@ -11419,7 +11419,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G425" t="n">
-        <v>2.09962177276611</v>
+        <v>2.09962201118469</v>
       </c>
       <c r="H425" t="s">
         <v>8</v>
@@ -11445,7 +11445,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G426" t="n">
-        <v>2.08248209953308</v>
+        <v>2.08248233795166</v>
       </c>
       <c r="H426" t="s">
         <v>8</v>
@@ -11471,7 +11471,7 @@
         <v>2.46799993515015</v>
       </c>
       <c r="G427" t="n">
-        <v>2.11504769325256</v>
+        <v>2.11504793167114</v>
       </c>
       <c r="H427" t="s">
         <v>8</v>
@@ -11601,7 +11601,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G432" t="n">
-        <v>2.1081919670105</v>
+        <v>2.10819172859192</v>
       </c>
       <c r="H432" t="s">
         <v>8</v>
@@ -11627,7 +11627,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G433" t="n">
-        <v>2.09962177276611</v>
+        <v>2.09962201118469</v>
       </c>
       <c r="H433" t="s">
         <v>8</v>
@@ -11679,7 +11679,7 @@
         <v>2.43799996376038</v>
       </c>
       <c r="G435" t="n">
-        <v>2.08933806419373</v>
+        <v>2.0893383026123</v>
       </c>
       <c r="H435" t="s">
         <v>8</v>
@@ -11731,7 +11731,7 @@
         <v>2.44799995422363</v>
       </c>
       <c r="G437" t="n">
-        <v>2.09790825843811</v>
+        <v>2.09790802001953</v>
       </c>
       <c r="H437" t="s">
         <v>8</v>
@@ -11757,7 +11757,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G438" t="n">
-        <v>2.08248209953308</v>
+        <v>2.08248233795166</v>
       </c>
       <c r="H438" t="s">
         <v>8</v>
@@ -11783,7 +11783,7 @@
         <v>2.44799995422363</v>
       </c>
       <c r="G439" t="n">
-        <v>2.09790825843811</v>
+        <v>2.09790802001953</v>
       </c>
       <c r="H439" t="s">
         <v>8</v>
@@ -11835,7 +11835,7 @@
         <v>2.5</v>
       </c>
       <c r="G441" t="n">
-        <v>2.14247155189514</v>
+        <v>2.14247179031372</v>
       </c>
       <c r="H441" t="s">
         <v>8</v>
@@ -11887,7 +11887,7 @@
         <v>2.48600006103516</v>
       </c>
       <c r="G443" t="n">
-        <v>2.13047361373901</v>
+        <v>2.13047385215759</v>
       </c>
       <c r="H443" t="s">
         <v>8</v>
@@ -11939,7 +11939,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G445" t="n">
-        <v>2.15961122512817</v>
+        <v>2.15961098670959</v>
       </c>
       <c r="H445" t="s">
         <v>8</v>
@@ -11965,7 +11965,7 @@
         <v>2.47199988365173</v>
       </c>
       <c r="G446" t="n">
-        <v>2.11847591400146</v>
+        <v>2.11847567558289</v>
       </c>
       <c r="H446" t="s">
         <v>8</v>
@@ -11991,7 +11991,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G447" t="n">
-        <v>2.11676168441772</v>
+        <v>2.1167619228363</v>
       </c>
       <c r="H447" t="s">
         <v>8</v>
@@ -12017,7 +12017,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G448" t="n">
-        <v>2.09105229377747</v>
+        <v>2.09105205535889</v>
       </c>
       <c r="H448" t="s">
         <v>8</v>
@@ -12043,7 +12043,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G449" t="n">
-        <v>2.09962177276611</v>
+        <v>2.09962201118469</v>
       </c>
       <c r="H449" t="s">
         <v>8</v>
@@ -12121,7 +12121,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G452" t="n">
-        <v>2.09105229377747</v>
+        <v>2.09105205535889</v>
       </c>
       <c r="H452" t="s">
         <v>8</v>
@@ -12147,7 +12147,7 @@
         <v>2.46799993515015</v>
       </c>
       <c r="G453" t="n">
-        <v>2.11504769325256</v>
+        <v>2.11504793167114</v>
       </c>
       <c r="H453" t="s">
         <v>8</v>
@@ -12381,7 +12381,7 @@
         <v>2.49799990653992</v>
       </c>
       <c r="G462" t="n">
-        <v>2.14075708389282</v>
+        <v>2.1407573223114</v>
       </c>
       <c r="H462" t="s">
         <v>8</v>
@@ -12459,7 +12459,7 @@
         <v>2.50799989700317</v>
       </c>
       <c r="G465" t="n">
-        <v>2.14932727813721</v>
+        <v>2.14932703971863</v>
       </c>
       <c r="H465" t="s">
         <v>8</v>
@@ -12615,7 +12615,7 @@
         <v>2.49799990653992</v>
       </c>
       <c r="G471" t="n">
-        <v>2.14075708389282</v>
+        <v>2.1407573223114</v>
       </c>
       <c r="H471" t="s">
         <v>8</v>
@@ -12745,7 +12745,7 @@
         <v>2.47399997711182</v>
       </c>
       <c r="G476" t="n">
-        <v>2.12018942832947</v>
+        <v>2.12018966674805</v>
       </c>
       <c r="H476" t="s">
         <v>8</v>
@@ -12771,7 +12771,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G477" t="n">
-        <v>2.09962177276611</v>
+        <v>2.09962201118469</v>
       </c>
       <c r="H477" t="s">
         <v>8</v>
@@ -12797,7 +12797,7 @@
         <v>2.45600008964539</v>
       </c>
       <c r="G478" t="n">
-        <v>2.10476398468018</v>
+        <v>2.1047637462616</v>
       </c>
       <c r="H478" t="s">
         <v>8</v>
@@ -12823,7 +12823,7 @@
         <v>2.40799999237061</v>
       </c>
       <c r="G479" t="n">
-        <v>2.06362843513489</v>
+        <v>2.06362819671631</v>
       </c>
       <c r="H479" t="s">
         <v>8</v>
@@ -12901,7 +12901,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G482" t="n">
-        <v>2.04820275306702</v>
+        <v>2.0482029914856</v>
       </c>
       <c r="H482" t="s">
         <v>8</v>
@@ -12927,7 +12927,7 @@
         <v>2.42600011825562</v>
       </c>
       <c r="G483" t="n">
-        <v>2.07905435562134</v>
+        <v>2.07905411720276</v>
       </c>
       <c r="H483" t="s">
         <v>8</v>
@@ -12953,7 +12953,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G484" t="n">
-        <v>2.04820275306702</v>
+        <v>2.0482029914856</v>
       </c>
       <c r="H484" t="s">
         <v>8</v>
@@ -12979,7 +12979,7 @@
         <v>2.41599988937378</v>
       </c>
       <c r="G485" t="n">
-        <v>2.07048439979553</v>
+        <v>2.07048416137695</v>
       </c>
       <c r="H485" t="s">
         <v>8</v>
@@ -13031,7 +13031,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G487" t="n">
-        <v>2.06534266471863</v>
+        <v>2.06534242630005</v>
       </c>
       <c r="H487" t="s">
         <v>8</v>
@@ -13057,7 +13057,7 @@
         <v>2.39199995994568</v>
       </c>
       <c r="G488" t="n">
-        <v>2.04991674423218</v>
+        <v>2.0499165058136</v>
       </c>
       <c r="H488" t="s">
         <v>8</v>
@@ -13083,7 +13083,7 @@
         <v>2.49799990653992</v>
       </c>
       <c r="G489" t="n">
-        <v>2.14075708389282</v>
+        <v>2.1407573223114</v>
       </c>
       <c r="H489" t="s">
         <v>8</v>
@@ -13135,7 +13135,7 @@
         <v>2.44799995422363</v>
       </c>
       <c r="G491" t="n">
-        <v>2.09790825843811</v>
+        <v>2.09790802001953</v>
       </c>
       <c r="H491" t="s">
         <v>8</v>
@@ -13187,7 +13187,7 @@
         <v>2.45600008964539</v>
       </c>
       <c r="G493" t="n">
-        <v>2.10476398468018</v>
+        <v>2.1047637462616</v>
       </c>
       <c r="H493" t="s">
         <v>8</v>
@@ -13265,7 +13265,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G496" t="n">
-        <v>2.11676168441772</v>
+        <v>2.1167619228363</v>
       </c>
       <c r="H496" t="s">
         <v>8</v>
@@ -13291,7 +13291,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G497" t="n">
-        <v>2.11676168441772</v>
+        <v>2.1167619228363</v>
       </c>
       <c r="H497" t="s">
         <v>8</v>
@@ -13317,7 +13317,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G498" t="n">
-        <v>2.11676168441772</v>
+        <v>2.1167619228363</v>
       </c>
       <c r="H498" t="s">
         <v>8</v>
@@ -13343,7 +13343,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G499" t="n">
-        <v>2.11676168441772</v>
+        <v>2.1167619228363</v>
       </c>
       <c r="H499" t="s">
         <v>8</v>
@@ -13369,7 +13369,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G500" t="n">
-        <v>2.08248209953308</v>
+        <v>2.08248233795166</v>
       </c>
       <c r="H500" t="s">
         <v>8</v>
@@ -13421,7 +13421,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G502" t="n">
-        <v>2.03963303565979</v>
+        <v>2.03963279724121</v>
       </c>
       <c r="H502" t="s">
         <v>8</v>
@@ -13447,7 +13447,7 @@
         <v>2.35800004005432</v>
       </c>
       <c r="G503" t="n">
-        <v>2.02077913284302</v>
+        <v>2.0207793712616</v>
       </c>
       <c r="H503" t="s">
         <v>8</v>
@@ -13499,7 +13499,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G505" t="n">
-        <v>2.08248209953308</v>
+        <v>2.08248233795166</v>
       </c>
       <c r="H505" t="s">
         <v>8</v>
@@ -13551,7 +13551,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G507" t="n">
-        <v>2.09962177276611</v>
+        <v>2.09962201118469</v>
       </c>
       <c r="H507" t="s">
         <v>8</v>
@@ -13577,7 +13577,7 @@
         <v>2.44799995422363</v>
       </c>
       <c r="G508" t="n">
-        <v>2.09790825843811</v>
+        <v>2.09790802001953</v>
       </c>
       <c r="H508" t="s">
         <v>8</v>
@@ -13603,7 +13603,7 @@
         <v>2.44799995422363</v>
       </c>
       <c r="G509" t="n">
-        <v>2.09790825843811</v>
+        <v>2.09790802001953</v>
       </c>
       <c r="H509" t="s">
         <v>8</v>
@@ -13629,7 +13629,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G510" t="n">
-        <v>2.09962177276611</v>
+        <v>2.09962201118469</v>
       </c>
       <c r="H510" t="s">
         <v>8</v>
@@ -13655,7 +13655,7 @@
         <v>2.41599988937378</v>
       </c>
       <c r="G511" t="n">
-        <v>2.07048439979553</v>
+        <v>2.07048416137695</v>
       </c>
       <c r="H511" t="s">
         <v>8</v>
@@ -13707,7 +13707,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G513" t="n">
-        <v>2.09962177276611</v>
+        <v>2.09962201118469</v>
       </c>
       <c r="H513" t="s">
         <v>8</v>
@@ -13785,7 +13785,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G516" t="n">
-        <v>2.08248209953308</v>
+        <v>2.08248233795166</v>
       </c>
       <c r="H516" t="s">
         <v>8</v>
@@ -13811,7 +13811,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G517" t="n">
-        <v>2.09105229377747</v>
+        <v>2.09105205535889</v>
       </c>
       <c r="H517" t="s">
         <v>8</v>
@@ -13837,7 +13837,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G518" t="n">
-        <v>2.09105229377747</v>
+        <v>2.09105205535889</v>
       </c>
       <c r="H518" t="s">
         <v>8</v>
@@ -13863,7 +13863,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G519" t="n">
-        <v>2.08248209953308</v>
+        <v>2.08248233795166</v>
       </c>
       <c r="H519" t="s">
         <v>8</v>
@@ -13889,7 +13889,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G520" t="n">
-        <v>2.08248209953308</v>
+        <v>2.08248233795166</v>
       </c>
       <c r="H520" t="s">
         <v>8</v>
@@ -13915,7 +13915,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G521" t="n">
-        <v>2.03963303565979</v>
+        <v>2.03963279724121</v>
       </c>
       <c r="H521" t="s">
         <v>8</v>
@@ -13941,7 +13941,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G522" t="n">
-        <v>2.03963303565979</v>
+        <v>2.03963279724121</v>
       </c>
       <c r="H522" t="s">
         <v>8</v>
@@ -13967,7 +13967,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G523" t="n">
-        <v>2.03963303565979</v>
+        <v>2.03963279724121</v>
       </c>
       <c r="H523" t="s">
         <v>8</v>
@@ -13993,7 +13993,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G524" t="n">
-        <v>2.03963303565979</v>
+        <v>2.03963279724121</v>
       </c>
       <c r="H524" t="s">
         <v>8</v>
@@ -14149,7 +14149,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G530" t="n">
-        <v>2.09962177276611</v>
+        <v>2.09962201118469</v>
       </c>
       <c r="H530" t="s">
         <v>8</v>
@@ -14305,7 +14305,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G536" t="n">
-        <v>2.04820275306702</v>
+        <v>2.0482029914856</v>
       </c>
       <c r="H536" t="s">
         <v>8</v>
@@ -14331,7 +14331,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G537" t="n">
-        <v>2.01392316818237</v>
+        <v>2.01392292976379</v>
       </c>
       <c r="H537" t="s">
         <v>8</v>
@@ -14435,7 +14435,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G541" t="n">
-        <v>2.09105229377747</v>
+        <v>2.09105205535889</v>
       </c>
       <c r="H541" t="s">
         <v>8</v>
@@ -14461,7 +14461,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G542" t="n">
-        <v>2.09105229377747</v>
+        <v>2.09105205535889</v>
       </c>
       <c r="H542" t="s">
         <v>8</v>
@@ -14487,7 +14487,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G543" t="n">
-        <v>2.09962177276611</v>
+        <v>2.09962201118469</v>
       </c>
       <c r="H543" t="s">
         <v>8</v>
@@ -14513,7 +14513,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G544" t="n">
-        <v>2.09962177276611</v>
+        <v>2.09962201118469</v>
       </c>
       <c r="H544" t="s">
         <v>8</v>
@@ -14539,7 +14539,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G545" t="n">
-        <v>2.09962177276611</v>
+        <v>2.09962201118469</v>
       </c>
       <c r="H545" t="s">
         <v>8</v>
@@ -14591,7 +14591,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G547" t="n">
-        <v>2.08248209953308</v>
+        <v>2.08248233795166</v>
       </c>
       <c r="H547" t="s">
         <v>8</v>
@@ -14617,7 +14617,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G548" t="n">
-        <v>2.04820275306702</v>
+        <v>2.0482029914856</v>
       </c>
       <c r="H548" t="s">
         <v>8</v>
@@ -14643,7 +14643,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G549" t="n">
-        <v>2.03963303565979</v>
+        <v>2.03963279724121</v>
       </c>
       <c r="H549" t="s">
         <v>8</v>
@@ -14669,7 +14669,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G550" t="n">
-        <v>2.08248209953308</v>
+        <v>2.08248233795166</v>
       </c>
       <c r="H550" t="s">
         <v>8</v>
@@ -14695,7 +14695,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G551" t="n">
-        <v>2.03963303565979</v>
+        <v>2.03963279724121</v>
       </c>
       <c r="H551" t="s">
         <v>8</v>
@@ -14721,7 +14721,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G552" t="n">
-        <v>2.03963303565979</v>
+        <v>2.03963279724121</v>
       </c>
       <c r="H552" t="s">
         <v>8</v>
@@ -14747,7 +14747,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G553" t="n">
-        <v>2.08248209953308</v>
+        <v>2.08248233795166</v>
       </c>
       <c r="H553" t="s">
         <v>8</v>
@@ -14799,7 +14799,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G555" t="n">
-        <v>2.06534266471863</v>
+        <v>2.06534242630005</v>
       </c>
       <c r="H555" t="s">
         <v>8</v>
@@ -14825,7 +14825,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G556" t="n">
-        <v>2.03963303565979</v>
+        <v>2.03963279724121</v>
       </c>
       <c r="H556" t="s">
         <v>8</v>
@@ -14851,7 +14851,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G557" t="n">
-        <v>2.11676168441772</v>
+        <v>2.1167619228363</v>
       </c>
       <c r="H557" t="s">
         <v>8</v>
@@ -14877,7 +14877,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G558" t="n">
-        <v>2.1081919670105</v>
+        <v>2.10819172859192</v>
       </c>
       <c r="H558" t="s">
         <v>8</v>
@@ -14903,7 +14903,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G559" t="n">
-        <v>2.06534266471863</v>
+        <v>2.06534242630005</v>
       </c>
       <c r="H559" t="s">
         <v>8</v>
@@ -14929,7 +14929,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G560" t="n">
-        <v>2.06534266471863</v>
+        <v>2.06534242630005</v>
       </c>
       <c r="H560" t="s">
         <v>8</v>
@@ -14955,7 +14955,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G561" t="n">
-        <v>2.09105229377747</v>
+        <v>2.09105205535889</v>
       </c>
       <c r="H561" t="s">
         <v>8</v>
@@ -14981,7 +14981,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G562" t="n">
-        <v>2.08248209953308</v>
+        <v>2.08248233795166</v>
       </c>
       <c r="H562" t="s">
         <v>8</v>
@@ -15007,7 +15007,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G563" t="n">
-        <v>2.08248209953308</v>
+        <v>2.08248233795166</v>
       </c>
       <c r="H563" t="s">
         <v>8</v>
@@ -15033,7 +15033,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G564" t="n">
-        <v>2.1081919670105</v>
+        <v>2.10819172859192</v>
       </c>
       <c r="H564" t="s">
         <v>8</v>
@@ -15059,7 +15059,7 @@
         <v>2.5</v>
       </c>
       <c r="G565" t="n">
-        <v>2.14247155189514</v>
+        <v>2.14247179031372</v>
       </c>
       <c r="H565" t="s">
         <v>8</v>
@@ -15111,7 +15111,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G567" t="n">
-        <v>2.1081919670105</v>
+        <v>2.10819172859192</v>
       </c>
       <c r="H567" t="s">
         <v>8</v>
@@ -15137,7 +15137,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G568" t="n">
-        <v>2.1081919670105</v>
+        <v>2.10819172859192</v>
       </c>
       <c r="H568" t="s">
         <v>8</v>
@@ -15189,7 +15189,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G570" t="n">
-        <v>2.09962177276611</v>
+        <v>2.09962201118469</v>
       </c>
       <c r="H570" t="s">
         <v>8</v>
@@ -15215,7 +15215,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G571" t="n">
-        <v>2.1081919670105</v>
+        <v>2.10819172859192</v>
       </c>
       <c r="H571" t="s">
         <v>8</v>
@@ -15241,7 +15241,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G572" t="n">
-        <v>2.09105229377747</v>
+        <v>2.09105205535889</v>
       </c>
       <c r="H572" t="s">
         <v>8</v>
@@ -15267,7 +15267,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G573" t="n">
-        <v>2.09105229377747</v>
+        <v>2.09105205535889</v>
       </c>
       <c r="H573" t="s">
         <v>8</v>
@@ -15293,7 +15293,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G574" t="n">
-        <v>2.09962177276611</v>
+        <v>2.09962201118469</v>
       </c>
       <c r="H574" t="s">
         <v>8</v>
@@ -15319,7 +15319,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G575" t="n">
-        <v>2.1081919670105</v>
+        <v>2.10819172859192</v>
       </c>
       <c r="H575" t="s">
         <v>8</v>
@@ -15345,7 +15345,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G576" t="n">
-        <v>2.09962177276611</v>
+        <v>2.09962201118469</v>
       </c>
       <c r="H576" t="s">
         <v>8</v>
@@ -15397,7 +15397,7 @@
         <v>2.5</v>
       </c>
       <c r="G578" t="n">
-        <v>2.14247155189514</v>
+        <v>2.14247179031372</v>
       </c>
       <c r="H578" t="s">
         <v>8</v>
@@ -15423,7 +15423,7 @@
         <v>2.5</v>
       </c>
       <c r="G579" t="n">
-        <v>2.14247155189514</v>
+        <v>2.14247179031372</v>
       </c>
       <c r="H579" t="s">
         <v>8</v>
@@ -15475,7 +15475,7 @@
         <v>2.5</v>
       </c>
       <c r="G581" t="n">
-        <v>2.14247155189514</v>
+        <v>2.14247179031372</v>
       </c>
       <c r="H581" t="s">
         <v>8</v>
@@ -15553,7 +15553,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G584" t="n">
-        <v>2.15961122512817</v>
+        <v>2.15961098670959</v>
       </c>
       <c r="H584" t="s">
         <v>8</v>
@@ -15579,7 +15579,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G585" t="n">
-        <v>2.15961122512817</v>
+        <v>2.15961098670959</v>
       </c>
       <c r="H585" t="s">
         <v>8</v>
@@ -15631,7 +15631,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G587" t="n">
-        <v>2.15961122512817</v>
+        <v>2.15961098670959</v>
       </c>
       <c r="H587" t="s">
         <v>8</v>
@@ -15657,7 +15657,7 @@
         <v>2.5</v>
       </c>
       <c r="G588" t="n">
-        <v>2.14247155189514</v>
+        <v>2.14247179031372</v>
       </c>
       <c r="H588" t="s">
         <v>8</v>
@@ -15683,7 +15683,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G589" t="n">
-        <v>2.15961122512817</v>
+        <v>2.15961098670959</v>
       </c>
       <c r="H589" t="s">
         <v>8</v>
@@ -15735,7 +15735,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G591" t="n">
-        <v>2.18532061576843</v>
+        <v>2.18532085418701</v>
       </c>
       <c r="H591" t="s">
         <v>8</v>
@@ -15761,7 +15761,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G592" t="n">
-        <v>2.29672956466675</v>
+        <v>2.29672932624817</v>
       </c>
       <c r="H592" t="s">
         <v>8</v>
@@ -15787,7 +15787,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G593" t="n">
-        <v>2.29672956466675</v>
+        <v>2.29672932624817</v>
       </c>
       <c r="H593" t="s">
         <v>8</v>
@@ -15969,7 +15969,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G600" t="n">
-        <v>2.47669720649719</v>
+        <v>2.47669696807861</v>
       </c>
       <c r="H600" t="s">
         <v>8</v>
@@ -16047,7 +16047,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G603" t="n">
-        <v>2.53668618202209</v>
+        <v>2.53668642044067</v>
       </c>
       <c r="H603" t="s">
         <v>8</v>
@@ -16073,7 +16073,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G604" t="n">
-        <v>2.57953572273254</v>
+        <v>2.57953548431396</v>
       </c>
       <c r="H604" t="s">
         <v>8</v>
@@ -16125,7 +16125,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G606" t="n">
-        <v>2.61381530761719</v>
+        <v>2.61381506919861</v>
       </c>
       <c r="H606" t="s">
         <v>8</v>
@@ -16151,7 +16151,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G607" t="n">
-        <v>2.55382609367371</v>
+        <v>2.55382585525513</v>
       </c>
       <c r="H607" t="s">
         <v>8</v>
@@ -16177,7 +16177,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G608" t="n">
-        <v>2.63447308540344</v>
+        <v>2.63447332382202</v>
       </c>
       <c r="H608" t="s">
         <v>8</v>
@@ -16255,7 +16255,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G611" t="n">
-        <v>2.61655163764954</v>
+        <v>2.61655139923096</v>
       </c>
       <c r="H611" t="s">
         <v>8</v>
@@ -16593,7 +16593,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G624" t="n">
-        <v>2.57174730300903</v>
+        <v>2.57174754142761</v>
       </c>
       <c r="H624" t="s">
         <v>8</v>
@@ -16619,7 +16619,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G625" t="n">
-        <v>2.57174730300903</v>
+        <v>2.57174754142761</v>
       </c>
       <c r="H625" t="s">
         <v>8</v>
@@ -16775,7 +16775,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G631" t="n">
-        <v>2.53590440750122</v>
+        <v>2.53590416908264</v>
       </c>
       <c r="H631" t="s">
         <v>8</v>
@@ -16801,7 +16801,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G632" t="n">
-        <v>2.4911003112793</v>
+        <v>2.49110054969788</v>
       </c>
       <c r="H632" t="s">
         <v>8</v>
@@ -16983,7 +16983,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G639" t="n">
-        <v>2.53590440750122</v>
+        <v>2.53590416908264</v>
       </c>
       <c r="H639" t="s">
         <v>8</v>
@@ -17009,7 +17009,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G640" t="n">
-        <v>2.53590440750122</v>
+        <v>2.53590416908264</v>
       </c>
       <c r="H640" t="s">
         <v>8</v>
@@ -17035,7 +17035,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G641" t="n">
-        <v>2.53590440750122</v>
+        <v>2.53590416908264</v>
       </c>
       <c r="H641" t="s">
         <v>8</v>
@@ -17061,7 +17061,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G642" t="n">
-        <v>2.53590440750122</v>
+        <v>2.53590416908264</v>
       </c>
       <c r="H642" t="s">
         <v>8</v>
@@ -17087,7 +17087,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G643" t="n">
-        <v>2.53590440750122</v>
+        <v>2.53590416908264</v>
       </c>
       <c r="H643" t="s">
         <v>8</v>
@@ -17139,7 +17139,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G645" t="n">
-        <v>2.53590440750122</v>
+        <v>2.53590416908264</v>
       </c>
       <c r="H645" t="s">
         <v>8</v>
@@ -17477,7 +17477,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G658" t="n">
-        <v>2.77784562110901</v>
+        <v>2.77784585952759</v>
       </c>
       <c r="H658" t="s">
         <v>8</v>
@@ -17503,7 +17503,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G659" t="n">
-        <v>2.77784562110901</v>
+        <v>2.77784585952759</v>
       </c>
       <c r="H659" t="s">
         <v>8</v>
@@ -17659,7 +17659,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G665" t="n">
-        <v>2.76888489723206</v>
+        <v>2.76888513565063</v>
       </c>
       <c r="H665" t="s">
         <v>8</v>
@@ -17685,7 +17685,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G666" t="n">
-        <v>2.71512007713318</v>
+        <v>2.71512031555176</v>
       </c>
       <c r="H666" t="s">
         <v>8</v>
@@ -17711,7 +17711,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G667" t="n">
-        <v>2.75096344947815</v>
+        <v>2.75096321105957</v>
       </c>
       <c r="H667" t="s">
         <v>8</v>
@@ -17737,7 +17737,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G668" t="n">
-        <v>2.67031645774841</v>
+        <v>2.67031621932983</v>
       </c>
       <c r="H668" t="s">
         <v>8</v>
@@ -17763,7 +17763,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G669" t="n">
-        <v>2.63447308540344</v>
+        <v>2.63447332382202</v>
       </c>
       <c r="H669" t="s">
         <v>8</v>
@@ -17815,7 +17815,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G671" t="n">
-        <v>2.75096344947815</v>
+        <v>2.75096321105957</v>
       </c>
       <c r="H671" t="s">
         <v>8</v>
@@ -17893,7 +17893,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G674" t="n">
-        <v>2.65239453315735</v>
+        <v>2.65239477157593</v>
       </c>
       <c r="H674" t="s">
         <v>8</v>
@@ -17919,7 +17919,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G675" t="n">
-        <v>2.65239453315735</v>
+        <v>2.65239477157593</v>
       </c>
       <c r="H675" t="s">
         <v>8</v>
@@ -17971,7 +17971,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G677" t="n">
-        <v>2.67031645774841</v>
+        <v>2.67031621932983</v>
       </c>
       <c r="H677" t="s">
         <v>8</v>
@@ -17997,7 +17997,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G678" t="n">
-        <v>2.67031645774841</v>
+        <v>2.67031621932983</v>
       </c>
       <c r="H678" t="s">
         <v>8</v>
@@ -18101,7 +18101,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G682" t="n">
-        <v>2.75096344947815</v>
+        <v>2.75096321105957</v>
       </c>
       <c r="H682" t="s">
         <v>8</v>
@@ -18127,7 +18127,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G683" t="n">
-        <v>2.73304200172424</v>
+        <v>2.73304176330566</v>
       </c>
       <c r="H683" t="s">
         <v>8</v>
@@ -18231,7 +18231,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G687" t="n">
-        <v>2.71512007713318</v>
+        <v>2.71512031555176</v>
       </c>
       <c r="H687" t="s">
         <v>8</v>
@@ -18257,7 +18257,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G688" t="n">
-        <v>2.75096344947815</v>
+        <v>2.75096321105957</v>
       </c>
       <c r="H688" t="s">
         <v>8</v>
@@ -18283,7 +18283,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G689" t="n">
-        <v>2.71512007713318</v>
+        <v>2.71512031555176</v>
       </c>
       <c r="H689" t="s">
         <v>8</v>
@@ -18309,7 +18309,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G690" t="n">
-        <v>2.69719862937927</v>
+        <v>2.69719886779785</v>
       </c>
       <c r="H690" t="s">
         <v>8</v>
@@ -18335,7 +18335,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G691" t="n">
-        <v>2.67927718162537</v>
+        <v>2.67927694320679</v>
       </c>
       <c r="H691" t="s">
         <v>8</v>
@@ -18465,7 +18465,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G696" t="n">
-        <v>2.73304200172424</v>
+        <v>2.73304176330566</v>
       </c>
       <c r="H696" t="s">
         <v>8</v>
@@ -18491,7 +18491,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G697" t="n">
-        <v>2.75096344947815</v>
+        <v>2.75096321105957</v>
       </c>
       <c r="H697" t="s">
         <v>8</v>
@@ -18569,7 +18569,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G700" t="n">
-        <v>2.75096344947815</v>
+        <v>2.75096321105957</v>
       </c>
       <c r="H700" t="s">
         <v>8</v>
@@ -18595,7 +18595,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G701" t="n">
-        <v>2.75096344947815</v>
+        <v>2.75096321105957</v>
       </c>
       <c r="H701" t="s">
         <v>8</v>
@@ -18621,7 +18621,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G702" t="n">
-        <v>2.75096344947815</v>
+        <v>2.75096321105957</v>
       </c>
       <c r="H702" t="s">
         <v>8</v>
@@ -18673,7 +18673,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G704" t="n">
-        <v>2.65239453315735</v>
+        <v>2.65239477157593</v>
       </c>
       <c r="H704" t="s">
         <v>8</v>
@@ -18699,7 +18699,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G705" t="n">
-        <v>2.69719862937927</v>
+        <v>2.69719886779785</v>
       </c>
       <c r="H705" t="s">
         <v>8</v>
@@ -18725,7 +18725,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G706" t="n">
-        <v>2.67927718162537</v>
+        <v>2.67927694320679</v>
       </c>
       <c r="H706" t="s">
         <v>8</v>
@@ -18777,7 +18777,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G708" t="n">
-        <v>2.63447308540344</v>
+        <v>2.63447332382202</v>
       </c>
       <c r="H708" t="s">
         <v>8</v>
@@ -18803,7 +18803,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G709" t="n">
-        <v>2.62551236152649</v>
+        <v>2.62551259994507</v>
       </c>
       <c r="H709" t="s">
         <v>8</v>
@@ -18907,7 +18907,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G713" t="n">
-        <v>2.61655163764954</v>
+        <v>2.61655139923096</v>
       </c>
       <c r="H713" t="s">
         <v>8</v>
@@ -19037,7 +19037,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G718" t="n">
-        <v>2.57174730300903</v>
+        <v>2.57174754142761</v>
       </c>
       <c r="H718" t="s">
         <v>8</v>
@@ -19089,7 +19089,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G720" t="n">
-        <v>2.61655163764954</v>
+        <v>2.61655139923096</v>
       </c>
       <c r="H720" t="s">
         <v>8</v>
@@ -19115,7 +19115,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G721" t="n">
-        <v>2.61655163764954</v>
+        <v>2.61655139923096</v>
       </c>
       <c r="H721" t="s">
         <v>8</v>
@@ -19245,7 +19245,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G726" t="n">
-        <v>2.62551236152649</v>
+        <v>2.62551259994507</v>
       </c>
       <c r="H726" t="s">
         <v>8</v>
@@ -19271,7 +19271,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G727" t="n">
-        <v>2.61655163764954</v>
+        <v>2.61655139923096</v>
       </c>
       <c r="H727" t="s">
         <v>8</v>
@@ -19297,7 +19297,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G728" t="n">
-        <v>2.61655163764954</v>
+        <v>2.61655139923096</v>
       </c>
       <c r="H728" t="s">
         <v>8</v>
@@ -19323,7 +19323,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G729" t="n">
-        <v>2.61655163764954</v>
+        <v>2.61655139923096</v>
       </c>
       <c r="H729" t="s">
         <v>8</v>
@@ -19349,7 +19349,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G730" t="n">
-        <v>2.60759091377258</v>
+        <v>2.607590675354</v>
       </c>
       <c r="H730" t="s">
         <v>8</v>
@@ -19375,7 +19375,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G731" t="n">
-        <v>2.61655163764954</v>
+        <v>2.61655139923096</v>
       </c>
       <c r="H731" t="s">
         <v>8</v>
@@ -19557,7 +19557,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G738" t="n">
-        <v>2.57174730300903</v>
+        <v>2.57174754142761</v>
       </c>
       <c r="H738" t="s">
         <v>8</v>
@@ -19765,7 +19765,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G746" t="n">
-        <v>2.41941428184509</v>
+        <v>2.41941404342651</v>
       </c>
       <c r="H746" t="s">
         <v>8</v>
@@ -19817,7 +19817,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G748" t="n">
-        <v>2.57174730300903</v>
+        <v>2.57174754142761</v>
       </c>
       <c r="H748" t="s">
         <v>8</v>
@@ -19869,7 +19869,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G750" t="n">
-        <v>2.57174730300903</v>
+        <v>2.57174754142761</v>
       </c>
       <c r="H750" t="s">
         <v>8</v>
@@ -19895,7 +19895,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G751" t="n">
-        <v>2.57174730300903</v>
+        <v>2.57174754142761</v>
       </c>
       <c r="H751" t="s">
         <v>8</v>
@@ -19921,7 +19921,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G752" t="n">
-        <v>2.57174730300903</v>
+        <v>2.57174754142761</v>
       </c>
       <c r="H752" t="s">
         <v>8</v>
@@ -20025,7 +20025,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G756" t="n">
-        <v>2.53590440750122</v>
+        <v>2.53590416908264</v>
       </c>
       <c r="H756" t="s">
         <v>8</v>
@@ -20051,7 +20051,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G757" t="n">
-        <v>2.53590440750122</v>
+        <v>2.53590416908264</v>
       </c>
       <c r="H757" t="s">
         <v>8</v>
@@ -20077,7 +20077,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G758" t="n">
-        <v>2.53590440750122</v>
+        <v>2.53590416908264</v>
       </c>
       <c r="H758" t="s">
         <v>8</v>
@@ -20207,7 +20207,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G763" t="n">
-        <v>2.53590440750122</v>
+        <v>2.53590416908264</v>
       </c>
       <c r="H763" t="s">
         <v>8</v>
@@ -20233,7 +20233,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G764" t="n">
-        <v>2.53590440750122</v>
+        <v>2.53590416908264</v>
       </c>
       <c r="H764" t="s">
         <v>8</v>
@@ -20259,7 +20259,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G765" t="n">
-        <v>2.60759091377258</v>
+        <v>2.607590675354</v>
       </c>
       <c r="H765" t="s">
         <v>8</v>
@@ -20285,7 +20285,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G766" t="n">
-        <v>2.63447308540344</v>
+        <v>2.63447332382202</v>
       </c>
       <c r="H766" t="s">
         <v>8</v>
@@ -20311,7 +20311,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G767" t="n">
-        <v>2.67031645774841</v>
+        <v>2.67031621932983</v>
       </c>
       <c r="H767" t="s">
         <v>8</v>
@@ -20363,7 +20363,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G769" t="n">
-        <v>2.67031645774841</v>
+        <v>2.67031621932983</v>
       </c>
       <c r="H769" t="s">
         <v>8</v>
@@ -20389,7 +20389,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G770" t="n">
-        <v>2.69719862937927</v>
+        <v>2.69719886779785</v>
       </c>
       <c r="H770" t="s">
         <v>8</v>
@@ -20415,7 +20415,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G771" t="n">
-        <v>2.67927718162537</v>
+        <v>2.67927694320679</v>
       </c>
       <c r="H771" t="s">
         <v>8</v>
@@ -20441,7 +20441,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G772" t="n">
-        <v>2.67031645774841</v>
+        <v>2.67031621932983</v>
       </c>
       <c r="H772" t="s">
         <v>8</v>
@@ -20467,7 +20467,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G773" t="n">
-        <v>2.71512007713318</v>
+        <v>2.71512031555176</v>
       </c>
       <c r="H773" t="s">
         <v>8</v>
@@ -20519,7 +20519,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G775" t="n">
-        <v>2.69719862937927</v>
+        <v>2.69719886779785</v>
       </c>
       <c r="H775" t="s">
         <v>8</v>
@@ -20545,7 +20545,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G776" t="n">
-        <v>2.67927718162537</v>
+        <v>2.67927694320679</v>
       </c>
       <c r="H776" t="s">
         <v>8</v>
@@ -20571,7 +20571,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G777" t="n">
-        <v>2.75096344947815</v>
+        <v>2.75096321105957</v>
       </c>
       <c r="H777" t="s">
         <v>8</v>
@@ -20597,7 +20597,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G778" t="n">
-        <v>2.81368923187256</v>
+        <v>2.81368899345398</v>
       </c>
       <c r="H778" t="s">
         <v>8</v>
@@ -20623,7 +20623,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G779" t="n">
-        <v>2.84057140350342</v>
+        <v>2.840571641922</v>
       </c>
       <c r="H779" t="s">
         <v>8</v>
@@ -20649,7 +20649,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G780" t="n">
-        <v>2.93914031982422</v>
+        <v>2.93914008140564</v>
       </c>
       <c r="H780" t="s">
         <v>8</v>
@@ -20675,7 +20675,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G781" t="n">
-        <v>2.87641477584839</v>
+        <v>2.87641453742981</v>
       </c>
       <c r="H781" t="s">
         <v>8</v>
@@ -20727,7 +20727,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G783" t="n">
-        <v>2.82264995574951</v>
+        <v>2.82264971733093</v>
       </c>
       <c r="H783" t="s">
         <v>8</v>
@@ -20805,7 +20805,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G786" t="n">
-        <v>2.82264995574951</v>
+        <v>2.82264971733093</v>
       </c>
       <c r="H786" t="s">
         <v>8</v>
@@ -20831,7 +20831,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G787" t="n">
-        <v>2.77784562110901</v>
+        <v>2.77784585952759</v>
       </c>
       <c r="H787" t="s">
         <v>8</v>
@@ -20857,7 +20857,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G788" t="n">
-        <v>2.84057140350342</v>
+        <v>2.840571641922</v>
       </c>
       <c r="H788" t="s">
         <v>8</v>
@@ -20883,7 +20883,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G789" t="n">
-        <v>2.77784562110901</v>
+        <v>2.77784585952759</v>
       </c>
       <c r="H789" t="s">
         <v>8</v>
@@ -20909,7 +20909,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G790" t="n">
-        <v>2.76888489723206</v>
+        <v>2.76888513565063</v>
       </c>
       <c r="H790" t="s">
         <v>8</v>
@@ -20961,7 +20961,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G792" t="n">
-        <v>2.77784562110901</v>
+        <v>2.77784585952759</v>
       </c>
       <c r="H792" t="s">
         <v>8</v>
@@ -21013,7 +21013,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G794" t="n">
-        <v>2.87641477584839</v>
+        <v>2.87641453742981</v>
       </c>
       <c r="H794" t="s">
         <v>8</v>
@@ -21039,7 +21039,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G795" t="n">
-        <v>2.87641477584839</v>
+        <v>2.87641453742981</v>
       </c>
       <c r="H795" t="s">
         <v>8</v>
@@ -21117,7 +21117,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G798" t="n">
-        <v>3.16315984725952</v>
+        <v>3.16315960884094</v>
       </c>
       <c r="H798" t="s">
         <v>8</v>
@@ -21195,7 +21195,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G801" t="n">
-        <v>3.25276803970337</v>
+        <v>3.25276780128479</v>
       </c>
       <c r="H801" t="s">
         <v>8</v>
@@ -21247,7 +21247,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G803" t="n">
-        <v>3.25276803970337</v>
+        <v>3.25276780128479</v>
       </c>
       <c r="H803" t="s">
         <v>8</v>
@@ -21403,7 +21403,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G809" t="n">
-        <v>3.33341503143311</v>
+        <v>3.33341479301453</v>
       </c>
       <c r="H809" t="s">
         <v>8</v>
@@ -21455,7 +21455,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G811" t="n">
-        <v>3.33341503143311</v>
+        <v>3.33341479301453</v>
       </c>
       <c r="H811" t="s">
         <v>8</v>
@@ -21481,7 +21481,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G812" t="n">
-        <v>3.34237551689148</v>
+        <v>3.34237575531006</v>
       </c>
       <c r="H812" t="s">
         <v>8</v>
@@ -21559,7 +21559,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G815" t="n">
-        <v>3.40510106086731</v>
+        <v>3.40510129928589</v>
       </c>
       <c r="H815" t="s">
         <v>8</v>
@@ -21611,7 +21611,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G817" t="n">
-        <v>3.3692581653595</v>
+        <v>3.36925792694092</v>
       </c>
       <c r="H817" t="s">
         <v>8</v>
@@ -21663,7 +21663,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G819" t="n">
-        <v>3.40510106086731</v>
+        <v>3.40510129928589</v>
       </c>
       <c r="H819" t="s">
         <v>8</v>
@@ -21741,7 +21741,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G822" t="n">
-        <v>3.48574829101562</v>
+        <v>3.4857485294342</v>
       </c>
       <c r="H822" t="s">
         <v>8</v>
@@ -21767,7 +21767,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G823" t="n">
-        <v>3.47678780555725</v>
+        <v>3.47678756713867</v>
       </c>
       <c r="H823" t="s">
         <v>8</v>
@@ -22053,7 +22053,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G834" t="n">
-        <v>3.51263070106506</v>
+        <v>3.51263093948364</v>
       </c>
       <c r="H834" t="s">
         <v>8</v>
@@ -22079,7 +22079,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G835" t="n">
-        <v>3.51263070106506</v>
+        <v>3.51263093948364</v>
       </c>
       <c r="H835" t="s">
         <v>8</v>
@@ -22131,7 +22131,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G837" t="n">
-        <v>3.51263070106506</v>
+        <v>3.51263093948364</v>
       </c>
       <c r="H837" t="s">
         <v>8</v>
@@ -22157,7 +22157,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G838" t="n">
-        <v>3.53951334953308</v>
+        <v>3.5395131111145</v>
       </c>
       <c r="H838" t="s">
         <v>8</v>
@@ -22209,7 +22209,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G840" t="n">
-        <v>3.51263070106506</v>
+        <v>3.51263093948364</v>
       </c>
       <c r="H840" t="s">
         <v>8</v>
@@ -22365,7 +22365,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G846" t="n">
-        <v>3.71872901916504</v>
+        <v>3.71872925758362</v>
       </c>
       <c r="H846" t="s">
         <v>8</v>
@@ -22391,7 +22391,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G847" t="n">
-        <v>3.69184637069702</v>
+        <v>3.6918466091156</v>
       </c>
       <c r="H847" t="s">
         <v>8</v>
@@ -22417,7 +22417,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G848" t="n">
-        <v>3.70976829528809</v>
+        <v>3.70976805686951</v>
       </c>
       <c r="H848" t="s">
         <v>8</v>
@@ -22443,7 +22443,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G849" t="n">
-        <v>3.68288612365723</v>
+        <v>3.68288588523865</v>
       </c>
       <c r="H849" t="s">
         <v>8</v>
@@ -22495,7 +22495,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G851" t="n">
-        <v>3.70976829528809</v>
+        <v>3.70976805686951</v>
       </c>
       <c r="H851" t="s">
         <v>8</v>
@@ -22599,7 +22599,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G855" t="n">
-        <v>3.7904155254364</v>
+        <v>3.79041528701782</v>
       </c>
       <c r="H855" t="s">
         <v>8</v>
@@ -71300,6 +71300,32 @@
         <v>1.04999995231628</v>
       </c>
       <c r="H2728" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2729">
+      <c r="A2729" s="1" t="n">
+        <v>46290.2916666667</v>
+      </c>
+      <c r="B2729" t="n">
+        <v>23530</v>
+      </c>
+      <c r="C2729" t="n">
+        <v>1.03999996185303</v>
+      </c>
+      <c r="D2729" t="n">
+        <v>1</v>
+      </c>
+      <c r="E2729" t="n">
+        <v>1</v>
+      </c>
+      <c r="F2729" t="n">
+        <v>1.03999996185303</v>
+      </c>
+      <c r="G2729" t="n">
+        <v>1.03999996185303</v>
+      </c>
+      <c r="H2729" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/RAT.MI.xlsx
+++ b/data/RAT.MI.xlsx
@@ -63155,7 +63155,9 @@
       <c r="E2730" t="n">
         <v>1.02999997138977</v>
       </c>
-      <c r="F2730"/>
+      <c r="F2730" t="n">
+        <v>1.04999995231628</v>
+      </c>
       <c r="G2730" t="s">
         <v>7</v>
       </c>

--- a/data/RAT.MI.xlsx
+++ b/data/RAT.MI.xlsx
@@ -63270,8 +63270,31 @@
       <c r="E2735" t="n">
         <v>1.01999998092651</v>
       </c>
-      <c r="F2735"/>
+      <c r="F2735" t="n">
+        <v>1.03999996185303</v>
+      </c>
       <c r="G2735" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2736">
+      <c r="A2736" s="1" t="n">
+        <v>46301.2916666667</v>
+      </c>
+      <c r="B2736" t="n">
+        <v>1920</v>
+      </c>
+      <c r="C2736" t="n">
+        <v>1.02999997138977</v>
+      </c>
+      <c r="D2736" t="n">
+        <v>1.00999999046326</v>
+      </c>
+      <c r="E2736" t="n">
+        <v>1.02999997138977</v>
+      </c>
+      <c r="F2736"/>
+      <c r="G2736" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/RAT.MI.xlsx
+++ b/data/RAT.MI.xlsx
@@ -63293,8 +63293,31 @@
       <c r="E2736" t="n">
         <v>1.02999997138977</v>
       </c>
-      <c r="F2736"/>
+      <c r="F2736" t="n">
+        <v>1.02999997138977</v>
+      </c>
       <c r="G2736" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2737">
+      <c r="A2737" s="1" t="n">
+        <v>46302.2916666667</v>
+      </c>
+      <c r="B2737" t="n">
+        <v>112</v>
+      </c>
+      <c r="C2737" t="n">
+        <v>1.03999996185303</v>
+      </c>
+      <c r="D2737" t="n">
+        <v>1.00999999046326</v>
+      </c>
+      <c r="E2737" t="n">
+        <v>1.03999996185303</v>
+      </c>
+      <c r="F2737"/>
+      <c r="G2737" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/RAT.MI.xlsx
+++ b/data/RAT.MI.xlsx
@@ -63316,8 +63316,31 @@
       <c r="E2737" t="n">
         <v>1.03999996185303</v>
       </c>
-      <c r="F2737"/>
+      <c r="F2737" t="n">
+        <v>1.02999997138977</v>
+      </c>
       <c r="G2737" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2738">
+      <c r="A2738" s="1" t="n">
+        <v>46303.2916666667</v>
+      </c>
+      <c r="B2738" t="n">
+        <v>5150</v>
+      </c>
+      <c r="C2738" t="n">
+        <v>1.04999995231628</v>
+      </c>
+      <c r="D2738" t="n">
+        <v>1</v>
+      </c>
+      <c r="E2738" t="n">
+        <v>1.00999999046326</v>
+      </c>
+      <c r="F2738"/>
+      <c r="G2738" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/RAT.MI.xlsx
+++ b/data/RAT.MI.xlsx
@@ -63339,8 +63339,31 @@
       <c r="E2738" t="n">
         <v>1.00999999046326</v>
       </c>
-      <c r="F2738"/>
+      <c r="F2738" t="n">
+        <v>1.04999995231628</v>
+      </c>
       <c r="G2738" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2739">
+      <c r="A2739" s="1" t="n">
+        <v>46304.2916666667</v>
+      </c>
+      <c r="B2739" t="n">
+        <v>18207</v>
+      </c>
+      <c r="C2739" t="n">
+        <v>1.03999996185303</v>
+      </c>
+      <c r="D2739" t="n">
+        <v>1</v>
+      </c>
+      <c r="E2739" t="n">
+        <v>1.01999998092651</v>
+      </c>
+      <c r="F2739"/>
+      <c r="G2739" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/RAT.MI.xlsx
+++ b/data/RAT.MI.xlsx
@@ -63369,6 +63369,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2740">
+      <c r="A2740" s="1" t="n">
+        <v>46307.2916666667</v>
+      </c>
+      <c r="B2740" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2740" t="n">
+        <v>1</v>
+      </c>
+      <c r="D2740" t="n">
+        <v>1</v>
+      </c>
+      <c r="E2740" t="n">
+        <v>1</v>
+      </c>
+      <c r="F2740" t="n">
+        <v>1</v>
+      </c>
+      <c r="G2740" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/RAT.MI.xlsx
+++ b/data/RAT.MI.xlsx
@@ -447,7 +447,7 @@
         <v>2.43600010871887</v>
       </c>
       <c r="G3" t="n">
-        <v>1.91323757171631</v>
+        <v>1.91323781013489</v>
       </c>
       <c r="H3" t="s">
         <v>8</v>
@@ -473,7 +473,7 @@
         <v>2.44600009918213</v>
       </c>
       <c r="G4" t="n">
-        <v>1.92109167575836</v>
+        <v>1.92109143733978</v>
       </c>
       <c r="H4" t="s">
         <v>8</v>
@@ -499,7 +499,7 @@
         <v>2.44600009918213</v>
       </c>
       <c r="G5" t="n">
-        <v>1.92109167575836</v>
+        <v>1.92109143733978</v>
       </c>
       <c r="H5" t="s">
         <v>8</v>
@@ -525,7 +525,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G6" t="n">
-        <v>1.8849630355835</v>
+        <v>1.88496327400208</v>
       </c>
       <c r="H6" t="s">
         <v>8</v>
@@ -551,7 +551,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G7" t="n">
-        <v>1.8849630355835</v>
+        <v>1.88496327400208</v>
       </c>
       <c r="H7" t="s">
         <v>8</v>
@@ -577,7 +577,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G8" t="n">
-        <v>1.92423331737518</v>
+        <v>1.9242330789566</v>
       </c>
       <c r="H8" t="s">
         <v>8</v>
@@ -603,7 +603,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G9" t="n">
-        <v>1.8849630355835</v>
+        <v>1.88496327400208</v>
       </c>
       <c r="H9" t="s">
         <v>8</v>
@@ -629,7 +629,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G10" t="n">
-        <v>1.8849630355835</v>
+        <v>1.88496327400208</v>
       </c>
       <c r="H10" t="s">
         <v>8</v>
@@ -681,7 +681,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G12" t="n">
-        <v>1.80642306804657</v>
+        <v>1.80642282962799</v>
       </c>
       <c r="H12" t="s">
         <v>8</v>
@@ -707,7 +707,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G13" t="n">
-        <v>1.80642306804657</v>
+        <v>1.80642282962799</v>
       </c>
       <c r="H13" t="s">
         <v>8</v>
@@ -733,7 +733,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G14" t="n">
-        <v>1.82998478412628</v>
+        <v>1.82998502254486</v>
       </c>
       <c r="H14" t="s">
         <v>8</v>
@@ -759,7 +759,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G15" t="n">
-        <v>1.79856908321381</v>
+        <v>1.79856884479523</v>
       </c>
       <c r="H15" t="s">
         <v>8</v>
@@ -785,7 +785,7 @@
         <v>2.25</v>
       </c>
       <c r="G16" t="n">
-        <v>1.76715290546417</v>
+        <v>1.76715314388275</v>
       </c>
       <c r="H16" t="s">
         <v>8</v>
@@ -863,7 +863,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G19" t="n">
-        <v>1.86925518512726</v>
+        <v>1.86925506591797</v>
       </c>
       <c r="H19" t="s">
         <v>8</v>
@@ -941,7 +941,7 @@
         <v>2.37800002098083</v>
       </c>
       <c r="G22" t="n">
-        <v>1.86768424510956</v>
+        <v>1.86768436431885</v>
       </c>
       <c r="H22" t="s">
         <v>8</v>
@@ -993,7 +993,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G24" t="n">
-        <v>1.83783900737762</v>
+        <v>1.83783888816833</v>
       </c>
       <c r="H24" t="s">
         <v>8</v>
@@ -1019,7 +1019,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G25" t="n">
-        <v>1.83783900737762</v>
+        <v>1.83783888816833</v>
       </c>
       <c r="H25" t="s">
         <v>8</v>
@@ -1045,7 +1045,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G26" t="n">
-        <v>1.8849630355835</v>
+        <v>1.88496327400208</v>
       </c>
       <c r="H26" t="s">
         <v>8</v>
@@ -1071,7 +1071,7 @@
         <v>2.38800001144409</v>
       </c>
       <c r="G27" t="n">
-        <v>1.87553799152374</v>
+        <v>1.87553834915161</v>
       </c>
       <c r="H27" t="s">
         <v>8</v>
@@ -1097,7 +1097,7 @@
         <v>2.38800001144409</v>
       </c>
       <c r="G28" t="n">
-        <v>1.87553799152374</v>
+        <v>1.87553834915161</v>
       </c>
       <c r="H28" t="s">
         <v>8</v>
@@ -1123,7 +1123,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G29" t="n">
-        <v>1.8849630355835</v>
+        <v>1.88496327400208</v>
       </c>
       <c r="H29" t="s">
         <v>8</v>
@@ -1149,7 +1149,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G30" t="n">
-        <v>1.80642306804657</v>
+        <v>1.80642282962799</v>
       </c>
       <c r="H30" t="s">
         <v>8</v>
@@ -1175,7 +1175,7 @@
         <v>2.32599997520447</v>
       </c>
       <c r="G31" t="n">
-        <v>1.82684326171875</v>
+        <v>1.82684361934662</v>
       </c>
       <c r="H31" t="s">
         <v>8</v>
@@ -1201,7 +1201,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G32" t="n">
-        <v>1.84569263458252</v>
+        <v>1.84569299221039</v>
       </c>
       <c r="H32" t="s">
         <v>8</v>
@@ -1227,7 +1227,7 @@
         <v>2.31599998474121</v>
       </c>
       <c r="G33" t="n">
-        <v>1.81898927688599</v>
+        <v>1.8189891576767</v>
       </c>
       <c r="H33" t="s">
         <v>8</v>
@@ -1253,7 +1253,7 @@
         <v>2.33800005912781</v>
       </c>
       <c r="G34" t="n">
-        <v>1.8362683057785</v>
+        <v>1.83626806735992</v>
       </c>
       <c r="H34" t="s">
         <v>8</v>
@@ -1279,7 +1279,7 @@
         <v>2.36800003051758</v>
       </c>
       <c r="G35" t="n">
-        <v>1.8598301410675</v>
+        <v>1.85983002185822</v>
       </c>
       <c r="H35" t="s">
         <v>8</v>
@@ -1305,7 +1305,7 @@
         <v>2.36800003051758</v>
       </c>
       <c r="G36" t="n">
-        <v>1.8598301410675</v>
+        <v>1.85983002185822</v>
       </c>
       <c r="H36" t="s">
         <v>8</v>
@@ -1331,7 +1331,7 @@
         <v>2.36800003051758</v>
       </c>
       <c r="G37" t="n">
-        <v>1.8598301410675</v>
+        <v>1.85983002185822</v>
       </c>
       <c r="H37" t="s">
         <v>8</v>
@@ -1357,7 +1357,7 @@
         <v>2.29800009727478</v>
       </c>
       <c r="G38" t="n">
-        <v>1.80485212802887</v>
+        <v>1.80485224723816</v>
       </c>
       <c r="H38" t="s">
         <v>8</v>
@@ -1383,7 +1383,7 @@
         <v>2.31800007820129</v>
       </c>
       <c r="G39" t="n">
-        <v>1.82056045532227</v>
+        <v>1.82056033611298</v>
       </c>
       <c r="H39" t="s">
         <v>8</v>
@@ -1409,7 +1409,7 @@
         <v>2.31399989128113</v>
       </c>
       <c r="G40" t="n">
-        <v>1.81741845607758</v>
+        <v>1.81741833686829</v>
       </c>
       <c r="H40" t="s">
         <v>8</v>
@@ -1435,7 +1435,7 @@
         <v>2.31399989128113</v>
       </c>
       <c r="G41" t="n">
-        <v>1.81741845607758</v>
+        <v>1.81741833686829</v>
       </c>
       <c r="H41" t="s">
         <v>8</v>
@@ -1461,7 +1461,7 @@
         <v>2.31399989128113</v>
       </c>
       <c r="G42" t="n">
-        <v>1.81741845607758</v>
+        <v>1.81741833686829</v>
       </c>
       <c r="H42" t="s">
         <v>8</v>
@@ -1487,7 +1487,7 @@
         <v>2.33800005912781</v>
       </c>
       <c r="G43" t="n">
-        <v>1.8362683057785</v>
+        <v>1.83626806735992</v>
       </c>
       <c r="H43" t="s">
         <v>8</v>
@@ -1513,7 +1513,7 @@
         <v>2.36800003051758</v>
       </c>
       <c r="G44" t="n">
-        <v>1.8598301410675</v>
+        <v>1.85983002185822</v>
       </c>
       <c r="H44" t="s">
         <v>8</v>
@@ -1539,7 +1539,7 @@
         <v>2.37800002098083</v>
       </c>
       <c r="G45" t="n">
-        <v>1.86768424510956</v>
+        <v>1.86768436431885</v>
       </c>
       <c r="H45" t="s">
         <v>8</v>
@@ -1565,7 +1565,7 @@
         <v>2.35599994659424</v>
       </c>
       <c r="G46" t="n">
-        <v>1.85040545463562</v>
+        <v>1.85040533542633</v>
       </c>
       <c r="H46" t="s">
         <v>8</v>
@@ -1591,7 +1591,7 @@
         <v>2.39400005340576</v>
       </c>
       <c r="G47" t="n">
-        <v>1.88025081157684</v>
+        <v>1.88025069236755</v>
       </c>
       <c r="H47" t="s">
         <v>8</v>
@@ -1617,7 +1617,7 @@
         <v>2.39400005340576</v>
       </c>
       <c r="G48" t="n">
-        <v>1.88025081157684</v>
+        <v>1.88025069236755</v>
       </c>
       <c r="H48" t="s">
         <v>8</v>
@@ -1669,7 +1669,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G50" t="n">
-        <v>1.84569263458252</v>
+        <v>1.84569299221039</v>
       </c>
       <c r="H50" t="s">
         <v>8</v>
@@ -1695,7 +1695,7 @@
         <v>2.33800005912781</v>
       </c>
       <c r="G51" t="n">
-        <v>1.8362683057785</v>
+        <v>1.83626806735992</v>
       </c>
       <c r="H51" t="s">
         <v>8</v>
@@ -1721,7 +1721,7 @@
         <v>2.35800004005432</v>
       </c>
       <c r="G52" t="n">
-        <v>1.85197639465332</v>
+        <v>1.85197651386261</v>
       </c>
       <c r="H52" t="s">
         <v>8</v>
@@ -1773,7 +1773,7 @@
         <v>2.34400010108948</v>
       </c>
       <c r="G54" t="n">
-        <v>1.84098064899445</v>
+        <v>1.84098041057587</v>
       </c>
       <c r="H54" t="s">
         <v>8</v>
@@ -1799,7 +1799,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G55" t="n">
-        <v>1.84569263458252</v>
+        <v>1.84569299221039</v>
       </c>
       <c r="H55" t="s">
         <v>8</v>
@@ -1825,7 +1825,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G56" t="n">
-        <v>1.84569263458252</v>
+        <v>1.84569299221039</v>
       </c>
       <c r="H56" t="s">
         <v>8</v>
@@ -1877,7 +1877,7 @@
         <v>2.32200002670288</v>
       </c>
       <c r="G58" t="n">
-        <v>1.82370185852051</v>
+        <v>1.82370173931122</v>
       </c>
       <c r="H58" t="s">
         <v>8</v>
@@ -1903,7 +1903,7 @@
         <v>2.32200002670288</v>
       </c>
       <c r="G59" t="n">
-        <v>1.82370185852051</v>
+        <v>1.82370173931122</v>
       </c>
       <c r="H59" t="s">
         <v>8</v>
@@ -2007,7 +2007,7 @@
         <v>2.35599994659424</v>
       </c>
       <c r="G63" t="n">
-        <v>1.85040545463562</v>
+        <v>1.85040533542633</v>
       </c>
       <c r="H63" t="s">
         <v>8</v>
@@ -2033,7 +2033,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G64" t="n">
-        <v>1.84569263458252</v>
+        <v>1.84569299221039</v>
       </c>
       <c r="H64" t="s">
         <v>8</v>
@@ -2059,7 +2059,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G65" t="n">
-        <v>1.92423331737518</v>
+        <v>1.9242330789566</v>
       </c>
       <c r="H65" t="s">
         <v>8</v>
@@ -2085,7 +2085,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G66" t="n">
-        <v>1.92423331737518</v>
+        <v>1.9242330789566</v>
       </c>
       <c r="H66" t="s">
         <v>8</v>
@@ -2111,7 +2111,7 @@
         <v>2.46600008010864</v>
       </c>
       <c r="G67" t="n">
-        <v>1.93679964542389</v>
+        <v>1.93679976463318</v>
       </c>
       <c r="H67" t="s">
         <v>8</v>
@@ -2137,7 +2137,7 @@
         <v>2.4779999256134</v>
       </c>
       <c r="G68" t="n">
-        <v>1.94622433185577</v>
+        <v>1.94622421264648</v>
       </c>
       <c r="H68" t="s">
         <v>8</v>
@@ -2163,7 +2163,7 @@
         <v>2.48799991607666</v>
       </c>
       <c r="G69" t="n">
-        <v>1.95407843589783</v>
+        <v>1.95407855510712</v>
       </c>
       <c r="H69" t="s">
         <v>8</v>
@@ -2189,7 +2189,7 @@
         <v>2.5</v>
       </c>
       <c r="G70" t="n">
-        <v>1.96350336074829</v>
+        <v>1.963503241539</v>
       </c>
       <c r="H70" t="s">
         <v>8</v>
@@ -2215,7 +2215,7 @@
         <v>2.50200009346008</v>
       </c>
       <c r="G71" t="n">
-        <v>1.9650741815567</v>
+        <v>1.96507394313812</v>
       </c>
       <c r="H71" t="s">
         <v>8</v>
@@ -2241,7 +2241,7 @@
         <v>2.53800010681152</v>
       </c>
       <c r="G72" t="n">
-        <v>1.99334859848022</v>
+        <v>1.99334847927094</v>
       </c>
       <c r="H72" t="s">
         <v>8</v>
@@ -2293,7 +2293,7 @@
         <v>2.5</v>
       </c>
       <c r="G74" t="n">
-        <v>1.96350336074829</v>
+        <v>1.963503241539</v>
       </c>
       <c r="H74" t="s">
         <v>8</v>
@@ -2319,7 +2319,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G75" t="n">
-        <v>1.98706531524658</v>
+        <v>1.98706519603729</v>
       </c>
       <c r="H75" t="s">
         <v>8</v>
@@ -2345,7 +2345,7 @@
         <v>2.50200009346008</v>
       </c>
       <c r="G76" t="n">
-        <v>1.9650741815567</v>
+        <v>1.96507394313812</v>
       </c>
       <c r="H76" t="s">
         <v>8</v>
@@ -2397,7 +2397,7 @@
         <v>2.57800006866455</v>
       </c>
       <c r="G78" t="n">
-        <v>2.02476453781128</v>
+        <v>2.02476477622986</v>
       </c>
       <c r="H78" t="s">
         <v>8</v>
@@ -2475,7 +2475,7 @@
         <v>2.5</v>
       </c>
       <c r="G81" t="n">
-        <v>1.96350336074829</v>
+        <v>1.963503241539</v>
       </c>
       <c r="H81" t="s">
         <v>8</v>
@@ -2501,7 +2501,7 @@
         <v>2.49799990653992</v>
       </c>
       <c r="G82" t="n">
-        <v>1.9619323015213</v>
+        <v>1.96193218231201</v>
       </c>
       <c r="H82" t="s">
         <v>8</v>
@@ -2527,7 +2527,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G83" t="n">
-        <v>1.93994140625</v>
+        <v>1.93994092941284</v>
       </c>
       <c r="H83" t="s">
         <v>8</v>
@@ -2553,7 +2553,7 @@
         <v>2.48799991607666</v>
       </c>
       <c r="G84" t="n">
-        <v>1.95407843589783</v>
+        <v>1.95407855510712</v>
       </c>
       <c r="H84" t="s">
         <v>8</v>
@@ -2579,7 +2579,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G85" t="n">
-        <v>1.95564901828766</v>
+        <v>1.95564913749695</v>
       </c>
       <c r="H85" t="s">
         <v>8</v>
@@ -2605,7 +2605,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G86" t="n">
-        <v>1.95564901828766</v>
+        <v>1.95564913749695</v>
       </c>
       <c r="H86" t="s">
         <v>8</v>
@@ -2631,7 +2631,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G87" t="n">
-        <v>1.93994140625</v>
+        <v>1.93994092941284</v>
       </c>
       <c r="H87" t="s">
         <v>8</v>
@@ -2657,7 +2657,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G88" t="n">
-        <v>1.91637909412384</v>
+        <v>1.91637921333313</v>
       </c>
       <c r="H88" t="s">
         <v>8</v>
@@ -2683,7 +2683,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G89" t="n">
-        <v>1.8849630355835</v>
+        <v>1.88496327400208</v>
       </c>
       <c r="H89" t="s">
         <v>8</v>
@@ -2709,7 +2709,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G90" t="n">
-        <v>1.91637909412384</v>
+        <v>1.91637921333313</v>
       </c>
       <c r="H90" t="s">
         <v>8</v>
@@ -2735,7 +2735,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G91" t="n">
-        <v>1.91637909412384</v>
+        <v>1.91637921333313</v>
       </c>
       <c r="H91" t="s">
         <v>8</v>
@@ -2761,7 +2761,7 @@
         <v>2.39400005340576</v>
       </c>
       <c r="G92" t="n">
-        <v>1.88025081157684</v>
+        <v>1.88025069236755</v>
       </c>
       <c r="H92" t="s">
         <v>8</v>
@@ -2865,7 +2865,7 @@
         <v>2.29800009727478</v>
       </c>
       <c r="G96" t="n">
-        <v>1.80485212802887</v>
+        <v>1.80485224723816</v>
       </c>
       <c r="H96" t="s">
         <v>8</v>
@@ -2891,7 +2891,7 @@
         <v>2.29800009727478</v>
       </c>
       <c r="G97" t="n">
-        <v>1.80485212802887</v>
+        <v>1.80485224723816</v>
       </c>
       <c r="H97" t="s">
         <v>8</v>
@@ -2969,7 +2969,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G100" t="n">
-        <v>1.93378710746765</v>
+        <v>1.93378698825836</v>
       </c>
       <c r="H100" t="s">
         <v>8</v>
@@ -2995,7 +2995,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G101" t="n">
-        <v>1.95017540454865</v>
+        <v>1.95017528533936</v>
       </c>
       <c r="H101" t="s">
         <v>8</v>
@@ -3047,7 +3047,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G103" t="n">
-        <v>1.93378710746765</v>
+        <v>1.93378698825836</v>
       </c>
       <c r="H103" t="s">
         <v>8</v>
@@ -3099,7 +3099,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G105" t="n">
-        <v>1.96656322479248</v>
+        <v>1.96656346321106</v>
       </c>
       <c r="H105" t="s">
         <v>8</v>
@@ -3125,7 +3125,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G106" t="n">
-        <v>1.96656322479248</v>
+        <v>1.96656346321106</v>
       </c>
       <c r="H106" t="s">
         <v>8</v>
@@ -3151,7 +3151,7 @@
         <v>2.38599991798401</v>
       </c>
       <c r="G107" t="n">
-        <v>1.95509171485901</v>
+        <v>1.95509135723114</v>
       </c>
       <c r="H107" t="s">
         <v>8</v>
@@ -3177,7 +3177,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G108" t="n">
-        <v>1.9583694934845</v>
+        <v>1.95836937427521</v>
       </c>
       <c r="H108" t="s">
         <v>8</v>
@@ -3203,7 +3203,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G109" t="n">
-        <v>1.9583694934845</v>
+        <v>1.95836937427521</v>
       </c>
       <c r="H109" t="s">
         <v>8</v>
@@ -3229,7 +3229,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G110" t="n">
-        <v>1.95017540454865</v>
+        <v>1.95017528533936</v>
       </c>
       <c r="H110" t="s">
         <v>8</v>
@@ -3255,7 +3255,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G111" t="n">
-        <v>1.95017540454865</v>
+        <v>1.95017528533936</v>
       </c>
       <c r="H111" t="s">
         <v>8</v>
@@ -3281,7 +3281,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G112" t="n">
-        <v>1.91739916801453</v>
+        <v>1.91739940643311</v>
       </c>
       <c r="H112" t="s">
         <v>8</v>
@@ -3385,7 +3385,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G116" t="n">
-        <v>1.9419811964035</v>
+        <v>1.94198107719421</v>
       </c>
       <c r="H116" t="s">
         <v>8</v>
@@ -3411,7 +3411,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G117" t="n">
-        <v>1.9419811964035</v>
+        <v>1.94198107719421</v>
       </c>
       <c r="H117" t="s">
         <v>8</v>
@@ -3437,7 +3437,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G118" t="n">
-        <v>1.91739916801453</v>
+        <v>1.91739940643311</v>
       </c>
       <c r="H118" t="s">
         <v>8</v>
@@ -3463,7 +3463,7 @@
         <v>2.33400011062622</v>
       </c>
       <c r="G119" t="n">
-        <v>1.91248285770416</v>
+        <v>1.91248273849487</v>
       </c>
       <c r="H119" t="s">
         <v>8</v>
@@ -3489,7 +3489,7 @@
         <v>2.33200001716614</v>
       </c>
       <c r="G120" t="n">
-        <v>1.91084396839142</v>
+        <v>1.91084408760071</v>
       </c>
       <c r="H120" t="s">
         <v>8</v>
@@ -3515,7 +3515,7 @@
         <v>2.33200001716614</v>
       </c>
       <c r="G121" t="n">
-        <v>1.91084396839142</v>
+        <v>1.91084408760071</v>
       </c>
       <c r="H121" t="s">
         <v>8</v>
@@ -3541,7 +3541,7 @@
         <v>2.33400011062622</v>
       </c>
       <c r="G122" t="n">
-        <v>1.91248285770416</v>
+        <v>1.91248273849487</v>
       </c>
       <c r="H122" t="s">
         <v>8</v>
@@ -3567,7 +3567,7 @@
         <v>2.33400011062622</v>
       </c>
       <c r="G123" t="n">
-        <v>1.91248285770416</v>
+        <v>1.91248273849487</v>
       </c>
       <c r="H123" t="s">
         <v>8</v>
@@ -3619,7 +3619,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G125" t="n">
-        <v>1.80268287658691</v>
+        <v>1.8026829957962</v>
       </c>
       <c r="H125" t="s">
         <v>8</v>
@@ -3645,7 +3645,7 @@
         <v>2.24799990653992</v>
       </c>
       <c r="G126" t="n">
-        <v>1.84201419353485</v>
+        <v>1.84201407432556</v>
       </c>
       <c r="H126" t="s">
         <v>8</v>
@@ -3671,7 +3671,7 @@
         <v>2.23600006103516</v>
       </c>
       <c r="G127" t="n">
-        <v>1.83218145370483</v>
+        <v>1.83218157291412</v>
       </c>
       <c r="H127" t="s">
         <v>8</v>
@@ -3697,7 +3697,7 @@
         <v>2.24799990653992</v>
       </c>
       <c r="G128" t="n">
-        <v>1.84201419353485</v>
+        <v>1.84201407432556</v>
       </c>
       <c r="H128" t="s">
         <v>8</v>
@@ -3723,7 +3723,7 @@
         <v>2.29800009727478</v>
       </c>
       <c r="G129" t="n">
-        <v>1.88298416137695</v>
+        <v>1.88298439979553</v>
       </c>
       <c r="H129" t="s">
         <v>8</v>
@@ -3775,7 +3775,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G131" t="n">
-        <v>1.9419811964035</v>
+        <v>1.94198107719421</v>
       </c>
       <c r="H131" t="s">
         <v>8</v>
@@ -3801,7 +3801,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G132" t="n">
-        <v>1.9419811964035</v>
+        <v>1.94198107719421</v>
       </c>
       <c r="H132" t="s">
         <v>8</v>
@@ -3827,7 +3827,7 @@
         <v>2.32800006866455</v>
       </c>
       <c r="G133" t="n">
-        <v>1.90756630897522</v>
+        <v>1.90756618976593</v>
       </c>
       <c r="H133" t="s">
         <v>8</v>
@@ -3853,7 +3853,7 @@
         <v>2.32800006866455</v>
       </c>
       <c r="G134" t="n">
-        <v>1.90756630897522</v>
+        <v>1.90756618976593</v>
       </c>
       <c r="H134" t="s">
         <v>8</v>
@@ -3879,7 +3879,7 @@
         <v>2.32800006866455</v>
       </c>
       <c r="G135" t="n">
-        <v>1.90756630897522</v>
+        <v>1.90756618976593</v>
       </c>
       <c r="H135" t="s">
         <v>8</v>
@@ -3905,7 +3905,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G136" t="n">
-        <v>1.89281725883484</v>
+        <v>1.89281702041626</v>
       </c>
       <c r="H136" t="s">
         <v>8</v>
@@ -3931,7 +3931,7 @@
         <v>2.32599997520447</v>
       </c>
       <c r="G137" t="n">
-        <v>1.90592765808105</v>
+        <v>1.90592753887177</v>
       </c>
       <c r="H137" t="s">
         <v>8</v>
@@ -3957,7 +3957,7 @@
         <v>2.32599997520447</v>
       </c>
       <c r="G138" t="n">
-        <v>1.90592765808105</v>
+        <v>1.90592753887177</v>
       </c>
       <c r="H138" t="s">
         <v>8</v>
@@ -3983,7 +3983,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G139" t="n">
-        <v>1.88462316989899</v>
+        <v>1.88462293148041</v>
       </c>
       <c r="H139" t="s">
         <v>8</v>
@@ -4009,7 +4009,7 @@
         <v>2.32599997520447</v>
       </c>
       <c r="G140" t="n">
-        <v>1.90592765808105</v>
+        <v>1.90592753887177</v>
       </c>
       <c r="H140" t="s">
         <v>8</v>
@@ -4035,7 +4035,7 @@
         <v>2.32599997520447</v>
       </c>
       <c r="G141" t="n">
-        <v>1.90592765808105</v>
+        <v>1.90592753887177</v>
       </c>
       <c r="H141" t="s">
         <v>8</v>
@@ -4061,7 +4061,7 @@
         <v>2.32800006866455</v>
       </c>
       <c r="G142" t="n">
-        <v>1.90756630897522</v>
+        <v>1.90756618976593</v>
       </c>
       <c r="H142" t="s">
         <v>8</v>
@@ -4139,7 +4139,7 @@
         <v>2.28399991989136</v>
       </c>
       <c r="G145" t="n">
-        <v>1.87151253223419</v>
+        <v>1.8715124130249</v>
       </c>
       <c r="H145" t="s">
         <v>8</v>
@@ -4191,7 +4191,7 @@
         <v>2.32599997520447</v>
       </c>
       <c r="G147" t="n">
-        <v>1.90592765808105</v>
+        <v>1.90592753887177</v>
       </c>
       <c r="H147" t="s">
         <v>8</v>
@@ -4269,7 +4269,7 @@
         <v>2.14599990844727</v>
       </c>
       <c r="G150" t="n">
-        <v>1.75843524932861</v>
+        <v>1.75843513011932</v>
       </c>
       <c r="H150" t="s">
         <v>8</v>
@@ -4295,7 +4295,7 @@
         <v>2.15599989891052</v>
       </c>
       <c r="G151" t="n">
-        <v>1.76662921905518</v>
+        <v>1.76662909984589</v>
       </c>
       <c r="H151" t="s">
         <v>8</v>
@@ -4347,7 +4347,7 @@
         <v>2.16799998283386</v>
       </c>
       <c r="G153" t="n">
-        <v>1.77646219730377</v>
+        <v>1.77646207809448</v>
       </c>
       <c r="H153" t="s">
         <v>8</v>
@@ -4399,7 +4399,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G155" t="n">
-        <v>1.75351905822754</v>
+        <v>1.75351893901825</v>
       </c>
       <c r="H155" t="s">
         <v>8</v>
@@ -4425,7 +4425,7 @@
         <v>2.17199993133545</v>
       </c>
       <c r="G156" t="n">
-        <v>1.77973985671997</v>
+        <v>1.77973961830139</v>
       </c>
       <c r="H156" t="s">
         <v>8</v>
@@ -4451,7 +4451,7 @@
         <v>2.17199993133545</v>
       </c>
       <c r="G157" t="n">
-        <v>1.77973985671997</v>
+        <v>1.77973961830139</v>
       </c>
       <c r="H157" t="s">
         <v>8</v>
@@ -4477,7 +4477,7 @@
         <v>2.13599991798401</v>
       </c>
       <c r="G158" t="n">
-        <v>1.75024116039276</v>
+        <v>1.75024127960205</v>
       </c>
       <c r="H158" t="s">
         <v>8</v>
@@ -4503,7 +4503,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G159" t="n">
-        <v>1.72074282169342</v>
+        <v>1.72074270248413</v>
       </c>
       <c r="H159" t="s">
         <v>8</v>
@@ -4555,7 +4555,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G161" t="n">
-        <v>1.72893667221069</v>
+        <v>1.72893679141998</v>
       </c>
       <c r="H161" t="s">
         <v>8</v>
@@ -4581,7 +4581,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G162" t="n">
-        <v>1.72893667221069</v>
+        <v>1.72893679141998</v>
       </c>
       <c r="H162" t="s">
         <v>8</v>
@@ -4607,7 +4607,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G163" t="n">
-        <v>1.69616067409515</v>
+        <v>1.69616079330444</v>
       </c>
       <c r="H163" t="s">
         <v>8</v>
@@ -4789,7 +4789,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G170" t="n">
-        <v>1.70435464382172</v>
+        <v>1.70435476303101</v>
       </c>
       <c r="H170" t="s">
         <v>8</v>
@@ -4815,7 +4815,7 @@
         <v>2.11800003051758</v>
       </c>
       <c r="G171" t="n">
-        <v>1.73549211025238</v>
+        <v>1.73549199104309</v>
       </c>
       <c r="H171" t="s">
         <v>8</v>
@@ -4841,7 +4841,7 @@
         <v>2.1159999370575</v>
       </c>
       <c r="G172" t="n">
-        <v>1.73385334014893</v>
+        <v>1.73385310173035</v>
       </c>
       <c r="H172" t="s">
         <v>8</v>
@@ -4867,7 +4867,7 @@
         <v>2.1159999370575</v>
       </c>
       <c r="G173" t="n">
-        <v>1.73385334014893</v>
+        <v>1.73385310173035</v>
       </c>
       <c r="H173" t="s">
         <v>8</v>
@@ -4893,7 +4893,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G174" t="n">
-        <v>1.71254861354828</v>
+        <v>1.71254873275757</v>
       </c>
       <c r="H174" t="s">
         <v>8</v>
@@ -4945,7 +4945,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G176" t="n">
-        <v>1.67157864570618</v>
+        <v>1.67157888412476</v>
       </c>
       <c r="H176" t="s">
         <v>8</v>
@@ -4997,7 +4997,7 @@
         <v>1.9650000333786</v>
       </c>
       <c r="G178" t="n">
-        <v>1.61012375354767</v>
+        <v>1.61012351512909</v>
       </c>
       <c r="H178" t="s">
         <v>8</v>
@@ -5023,7 +5023,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G179" t="n">
-        <v>1.62241458892822</v>
+        <v>1.62241470813751</v>
       </c>
       <c r="H179" t="s">
         <v>8</v>
@@ -5075,7 +5075,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G181" t="n">
-        <v>1.6633847951889</v>
+        <v>1.66338467597961</v>
       </c>
       <c r="H181" t="s">
         <v>8</v>
@@ -5101,7 +5101,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G182" t="n">
-        <v>1.67157864570618</v>
+        <v>1.67157888412476</v>
       </c>
       <c r="H182" t="s">
         <v>8</v>
@@ -5127,7 +5127,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G183" t="n">
-        <v>1.67157864570618</v>
+        <v>1.67157888412476</v>
       </c>
       <c r="H183" t="s">
         <v>8</v>
@@ -5153,7 +5153,7 @@
         <v>2.04200005531311</v>
       </c>
       <c r="G184" t="n">
-        <v>1.67321765422821</v>
+        <v>1.67321753501892</v>
       </c>
       <c r="H184" t="s">
         <v>8</v>
@@ -5179,7 +5179,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G185" t="n">
-        <v>1.67157864570618</v>
+        <v>1.67157888412476</v>
       </c>
       <c r="H185" t="s">
         <v>8</v>
@@ -5283,7 +5283,7 @@
         <v>2.00799989700317</v>
       </c>
       <c r="G189" t="n">
-        <v>1.64535772800446</v>
+        <v>1.64535784721375</v>
       </c>
       <c r="H189" t="s">
         <v>8</v>
@@ -5361,7 +5361,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G192" t="n">
-        <v>1.6633847951889</v>
+        <v>1.66338467597961</v>
       </c>
       <c r="H192" t="s">
         <v>8</v>
@@ -5491,7 +5491,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G197" t="n">
-        <v>1.65519082546234</v>
+        <v>1.65519070625305</v>
       </c>
       <c r="H197" t="s">
         <v>8</v>
@@ -5517,7 +5517,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G198" t="n">
-        <v>1.65519082546234</v>
+        <v>1.65519070625305</v>
       </c>
       <c r="H198" t="s">
         <v>8</v>
@@ -5543,7 +5543,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G199" t="n">
-        <v>1.65519082546234</v>
+        <v>1.65519070625305</v>
       </c>
       <c r="H199" t="s">
         <v>8</v>
@@ -5569,7 +5569,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G200" t="n">
-        <v>1.65519082546234</v>
+        <v>1.65519070625305</v>
       </c>
       <c r="H200" t="s">
         <v>8</v>
@@ -5595,7 +5595,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G201" t="n">
-        <v>1.65519082546234</v>
+        <v>1.65519070625305</v>
       </c>
       <c r="H201" t="s">
         <v>8</v>
@@ -5751,7 +5751,7 @@
         <v>1.95099997520447</v>
       </c>
       <c r="G207" t="n">
-        <v>1.59865188598633</v>
+        <v>1.59865200519562</v>
       </c>
       <c r="H207" t="s">
         <v>8</v>
@@ -5829,7 +5829,7 @@
         <v>1.94700002670288</v>
       </c>
       <c r="G210" t="n">
-        <v>1.59537434577942</v>
+        <v>1.59537446498871</v>
       </c>
       <c r="H210" t="s">
         <v>8</v>
@@ -5855,7 +5855,7 @@
         <v>1.92700004577637</v>
       </c>
       <c r="G211" t="n">
-        <v>1.57898640632629</v>
+        <v>1.578986287117</v>
       </c>
       <c r="H211" t="s">
         <v>8</v>
@@ -6011,7 +6011,7 @@
         <v>1.91199994087219</v>
       </c>
       <c r="G217" t="n">
-        <v>1.56669521331787</v>
+        <v>1.56669533252716</v>
       </c>
       <c r="H217" t="s">
         <v>8</v>
@@ -6037,7 +6037,7 @@
         <v>1.90199995040894</v>
       </c>
       <c r="G218" t="n">
-        <v>1.55850124359131</v>
+        <v>1.5585013628006</v>
       </c>
       <c r="H218" t="s">
         <v>8</v>
@@ -6089,7 +6089,7 @@
         <v>1.95700001716614</v>
       </c>
       <c r="G220" t="n">
-        <v>1.60356855392456</v>
+        <v>1.60356831550598</v>
       </c>
       <c r="H220" t="s">
         <v>8</v>
@@ -6193,7 +6193,7 @@
         <v>2.00799989700317</v>
       </c>
       <c r="G224" t="n">
-        <v>1.64535772800446</v>
+        <v>1.64535784721375</v>
       </c>
       <c r="H224" t="s">
         <v>8</v>
@@ -6245,7 +6245,7 @@
         <v>1.90600001811981</v>
       </c>
       <c r="G226" t="n">
-        <v>1.56177890300751</v>
+        <v>1.5617790222168</v>
       </c>
       <c r="H226" t="s">
         <v>8</v>
@@ -6271,7 +6271,7 @@
         <v>1.8860000371933</v>
       </c>
       <c r="G227" t="n">
-        <v>1.54539108276367</v>
+        <v>1.54539096355438</v>
       </c>
       <c r="H227" t="s">
         <v>8</v>
@@ -6297,7 +6297,7 @@
         <v>1.67999994754791</v>
       </c>
       <c r="G228" t="n">
-        <v>1.37659418582916</v>
+        <v>1.37659406661987</v>
       </c>
       <c r="H228" t="s">
         <v>8</v>
@@ -6349,7 +6349,7 @@
         <v>1.70200002193451</v>
       </c>
       <c r="G230" t="n">
-        <v>1.39462113380432</v>
+        <v>1.39462125301361</v>
       </c>
       <c r="H230" t="s">
         <v>8</v>
@@ -6479,7 +6479,7 @@
         <v>1.96700000762939</v>
       </c>
       <c r="G235" t="n">
-        <v>1.61176240444183</v>
+        <v>1.61176252365112</v>
       </c>
       <c r="H235" t="s">
         <v>8</v>
@@ -6505,7 +6505,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G236" t="n">
-        <v>1.59783279895782</v>
+        <v>1.59783267974854</v>
       </c>
       <c r="H236" t="s">
         <v>8</v>
@@ -6531,7 +6531,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G237" t="n">
-        <v>1.59783279895782</v>
+        <v>1.59783267974854</v>
       </c>
       <c r="H237" t="s">
         <v>8</v>
@@ -6557,7 +6557,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G238" t="n">
-        <v>1.59783279895782</v>
+        <v>1.59783267974854</v>
       </c>
       <c r="H238" t="s">
         <v>8</v>
@@ -6583,7 +6583,7 @@
         <v>1.96700000762939</v>
       </c>
       <c r="G239" t="n">
-        <v>1.61176240444183</v>
+        <v>1.61176252365112</v>
       </c>
       <c r="H239" t="s">
         <v>8</v>
@@ -6635,7 +6635,7 @@
         <v>1.84500002861023</v>
       </c>
       <c r="G241" t="n">
-        <v>1.51179552078247</v>
+        <v>1.51179540157318</v>
       </c>
       <c r="H241" t="s">
         <v>8</v>
@@ -6739,7 +6739,7 @@
         <v>1.90900003910065</v>
       </c>
       <c r="G245" t="n">
-        <v>1.56423723697662</v>
+        <v>1.56423711776733</v>
       </c>
       <c r="H245" t="s">
         <v>8</v>
@@ -6791,7 +6791,7 @@
         <v>1.94400000572205</v>
       </c>
       <c r="G247" t="n">
-        <v>1.59291613101959</v>
+        <v>1.59291625022888</v>
       </c>
       <c r="H247" t="s">
         <v>8</v>
@@ -6817,7 +6817,7 @@
         <v>1.94400000572205</v>
       </c>
       <c r="G248" t="n">
-        <v>1.59291613101959</v>
+        <v>1.59291625022888</v>
       </c>
       <c r="H248" t="s">
         <v>8</v>
@@ -6843,7 +6843,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G249" t="n">
-        <v>1.55686259269714</v>
+        <v>1.55686247348785</v>
       </c>
       <c r="H249" t="s">
         <v>8</v>
@@ -6869,7 +6869,7 @@
         <v>1.85699999332428</v>
       </c>
       <c r="G250" t="n">
-        <v>1.52162826061249</v>
+        <v>1.52162837982178</v>
       </c>
       <c r="H250" t="s">
         <v>8</v>
@@ -6895,7 +6895,7 @@
         <v>1.88100004196167</v>
       </c>
       <c r="G251" t="n">
-        <v>1.54129374027252</v>
+        <v>1.5412939786911</v>
       </c>
       <c r="H251" t="s">
         <v>8</v>
@@ -6921,7 +6921,7 @@
         <v>1.83599996566772</v>
       </c>
       <c r="G252" t="n">
-        <v>1.50442087650299</v>
+        <v>1.5044207572937</v>
       </c>
       <c r="H252" t="s">
         <v>8</v>
@@ -6973,7 +6973,7 @@
         <v>1.89300000667572</v>
       </c>
       <c r="G254" t="n">
-        <v>1.55112683773041</v>
+        <v>1.55112671852112</v>
       </c>
       <c r="H254" t="s">
         <v>8</v>
@@ -6999,7 +6999,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G255" t="n">
-        <v>1.51589238643646</v>
+        <v>1.51589250564575</v>
       </c>
       <c r="H255" t="s">
         <v>8</v>
@@ -7051,7 +7051,7 @@
         <v>1.84099996089935</v>
       </c>
       <c r="G257" t="n">
-        <v>1.50851774215698</v>
+        <v>1.50851786136627</v>
       </c>
       <c r="H257" t="s">
         <v>8</v>
@@ -7077,7 +7077,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G258" t="n">
-        <v>1.53228056430817</v>
+        <v>1.53228044509888</v>
       </c>
       <c r="H258" t="s">
         <v>8</v>
@@ -7103,7 +7103,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G259" t="n">
-        <v>1.53228056430817</v>
+        <v>1.53228044509888</v>
       </c>
       <c r="H259" t="s">
         <v>8</v>
@@ -7129,7 +7129,7 @@
         <v>1.84200000762939</v>
       </c>
       <c r="G260" t="n">
-        <v>1.50933730602264</v>
+        <v>1.50933718681335</v>
       </c>
       <c r="H260" t="s">
         <v>8</v>
@@ -7155,7 +7155,7 @@
         <v>1.84099996089935</v>
       </c>
       <c r="G261" t="n">
-        <v>1.50851774215698</v>
+        <v>1.50851786136627</v>
       </c>
       <c r="H261" t="s">
         <v>8</v>
@@ -7207,7 +7207,7 @@
         <v>1.84200000762939</v>
       </c>
       <c r="G263" t="n">
-        <v>1.50933730602264</v>
+        <v>1.50933718681335</v>
       </c>
       <c r="H263" t="s">
         <v>8</v>
@@ -7285,7 +7285,7 @@
         <v>1.82500004768372</v>
       </c>
       <c r="G266" t="n">
-        <v>1.49540746212006</v>
+        <v>1.49540758132935</v>
       </c>
       <c r="H266" t="s">
         <v>8</v>
@@ -7311,7 +7311,7 @@
         <v>1.84300005435944</v>
       </c>
       <c r="G267" t="n">
-        <v>1.51015663146973</v>
+        <v>1.51015675067902</v>
       </c>
       <c r="H267" t="s">
         <v>8</v>
@@ -7363,7 +7363,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G269" t="n">
-        <v>1.57325041294098</v>
+        <v>1.57325065135956</v>
       </c>
       <c r="H269" t="s">
         <v>8</v>
@@ -7415,7 +7415,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G271" t="n">
-        <v>1.55686259269714</v>
+        <v>1.55686247348785</v>
       </c>
       <c r="H271" t="s">
         <v>8</v>
@@ -7441,7 +7441,7 @@
         <v>1.94599997997284</v>
       </c>
       <c r="G272" t="n">
-        <v>1.59455502033234</v>
+        <v>1.59455490112305</v>
       </c>
       <c r="H272" t="s">
         <v>8</v>
@@ -7467,7 +7467,7 @@
         <v>1.96099996566772</v>
       </c>
       <c r="G273" t="n">
-        <v>1.60684585571289</v>
+        <v>1.60684597492218</v>
       </c>
       <c r="H273" t="s">
         <v>8</v>
@@ -7493,7 +7493,7 @@
         <v>1.95700001716614</v>
       </c>
       <c r="G274" t="n">
-        <v>1.60356855392456</v>
+        <v>1.60356831550598</v>
       </c>
       <c r="H274" t="s">
         <v>8</v>
@@ -7545,7 +7545,7 @@
         <v>1.97899997234344</v>
       </c>
       <c r="G276" t="n">
-        <v>1.62159526348114</v>
+        <v>1.62159538269043</v>
       </c>
       <c r="H276" t="s">
         <v>8</v>
@@ -7597,7 +7597,7 @@
         <v>1.88399994373322</v>
       </c>
       <c r="G278" t="n">
-        <v>1.54375207424164</v>
+        <v>1.54375195503235</v>
       </c>
       <c r="H278" t="s">
         <v>8</v>
@@ -7623,7 +7623,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G279" t="n">
-        <v>1.53228056430817</v>
+        <v>1.53228044509888</v>
       </c>
       <c r="H279" t="s">
         <v>8</v>
@@ -7649,7 +7649,7 @@
         <v>1.9190000295639</v>
       </c>
       <c r="G280" t="n">
-        <v>1.57243132591248</v>
+        <v>1.57243120670319</v>
       </c>
       <c r="H280" t="s">
         <v>8</v>
@@ -7675,7 +7675,7 @@
         <v>1.93700003623962</v>
       </c>
       <c r="G281" t="n">
-        <v>1.58718037605286</v>
+        <v>1.58718049526215</v>
       </c>
       <c r="H281" t="s">
         <v>8</v>
@@ -7727,7 +7727,7 @@
         <v>1.90100002288818</v>
       </c>
       <c r="G283" t="n">
-        <v>1.55768203735352</v>
+        <v>1.55768191814423</v>
       </c>
       <c r="H283" t="s">
         <v>8</v>
@@ -7753,7 +7753,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G284" t="n">
-        <v>1.55686259269714</v>
+        <v>1.55686247348785</v>
       </c>
       <c r="H284" t="s">
         <v>8</v>
@@ -7779,7 +7779,7 @@
         <v>1.93799996376038</v>
       </c>
       <c r="G285" t="n">
-        <v>1.58799982070923</v>
+        <v>1.58799970149994</v>
       </c>
       <c r="H285" t="s">
         <v>8</v>
@@ -8091,7 +8091,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G297" t="n">
-        <v>1.55686259269714</v>
+        <v>1.55686247348785</v>
       </c>
       <c r="H297" t="s">
         <v>8</v>
@@ -8117,7 +8117,7 @@
         <v>1.89499998092651</v>
       </c>
       <c r="G298" t="n">
-        <v>1.55276548862457</v>
+        <v>1.55276560783386</v>
       </c>
       <c r="H298" t="s">
         <v>8</v>
@@ -8143,7 +8143,7 @@
         <v>1.89100003242493</v>
       </c>
       <c r="G299" t="n">
-        <v>1.54948794841766</v>
+        <v>1.54948806762695</v>
       </c>
       <c r="H299" t="s">
         <v>8</v>
@@ -8169,7 +8169,7 @@
         <v>1.87699997425079</v>
       </c>
       <c r="G300" t="n">
-        <v>1.5380163192749</v>
+        <v>1.53801620006561</v>
       </c>
       <c r="H300" t="s">
         <v>8</v>
@@ -8195,7 +8195,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G301" t="n">
-        <v>1.53228056430817</v>
+        <v>1.53228044509888</v>
       </c>
       <c r="H301" t="s">
         <v>8</v>
@@ -8247,7 +8247,7 @@
         <v>1.89100003242493</v>
       </c>
       <c r="G303" t="n">
-        <v>1.54948794841766</v>
+        <v>1.54948806762695</v>
       </c>
       <c r="H303" t="s">
         <v>8</v>
@@ -8377,7 +8377,7 @@
         <v>1.89300000667572</v>
       </c>
       <c r="G308" t="n">
-        <v>1.55112683773041</v>
+        <v>1.55112671852112</v>
       </c>
       <c r="H308" t="s">
         <v>8</v>
@@ -8455,7 +8455,7 @@
         <v>2.01600003242493</v>
       </c>
       <c r="G311" t="n">
-        <v>1.65191304683685</v>
+        <v>1.65191316604614</v>
       </c>
       <c r="H311" t="s">
         <v>8</v>
@@ -8533,7 +8533,7 @@
         <v>2.04200005531311</v>
       </c>
       <c r="G314" t="n">
-        <v>1.67321765422821</v>
+        <v>1.67321753501892</v>
       </c>
       <c r="H314" t="s">
         <v>8</v>
@@ -8559,7 +8559,7 @@
         <v>2.01799988746643</v>
       </c>
       <c r="G315" t="n">
-        <v>1.65355169773102</v>
+        <v>1.65355181694031</v>
       </c>
       <c r="H315" t="s">
         <v>8</v>
@@ -8585,7 +8585,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G316" t="n">
-        <v>1.65519082546234</v>
+        <v>1.65519070625305</v>
       </c>
       <c r="H316" t="s">
         <v>8</v>
@@ -8611,7 +8611,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G317" t="n">
-        <v>1.6633847951889</v>
+        <v>1.66338467597961</v>
       </c>
       <c r="H317" t="s">
         <v>8</v>
@@ -8637,7 +8637,7 @@
         <v>2.29800009727478</v>
       </c>
       <c r="G318" t="n">
-        <v>1.88298416137695</v>
+        <v>1.88298439979553</v>
       </c>
       <c r="H318" t="s">
         <v>8</v>
@@ -8663,7 +8663,7 @@
         <v>2.22199988365173</v>
       </c>
       <c r="G319" t="n">
-        <v>1.82070970535278</v>
+        <v>1.8207094669342</v>
       </c>
       <c r="H319" t="s">
         <v>8</v>
@@ -8689,7 +8689,7 @@
         <v>2.23200011253357</v>
       </c>
       <c r="G320" t="n">
-        <v>1.82890379428864</v>
+        <v>1.82890391349792</v>
       </c>
       <c r="H320" t="s">
         <v>8</v>
@@ -8741,7 +8741,7 @@
         <v>2.21799993515015</v>
       </c>
       <c r="G322" t="n">
-        <v>1.81743204593658</v>
+        <v>1.81743228435516</v>
       </c>
       <c r="H322" t="s">
         <v>8</v>
@@ -8767,7 +8767,7 @@
         <v>2.21600008010864</v>
       </c>
       <c r="G323" t="n">
-        <v>1.81579351425171</v>
+        <v>1.81579339504242</v>
       </c>
       <c r="H323" t="s">
         <v>8</v>
@@ -8793,7 +8793,7 @@
         <v>2.17199993133545</v>
       </c>
       <c r="G324" t="n">
-        <v>1.77973985671997</v>
+        <v>1.77973961830139</v>
       </c>
       <c r="H324" t="s">
         <v>8</v>
@@ -8845,7 +8845,7 @@
         <v>2.24799990653992</v>
       </c>
       <c r="G326" t="n">
-        <v>1.84201419353485</v>
+        <v>1.84201407432556</v>
       </c>
       <c r="H326" t="s">
         <v>8</v>
@@ -8871,7 +8871,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G327" t="n">
-        <v>1.79448890686035</v>
+        <v>1.79448902606964</v>
       </c>
       <c r="H327" t="s">
         <v>8</v>
@@ -8897,7 +8897,7 @@
         <v>2.19799995422363</v>
       </c>
       <c r="G328" t="n">
-        <v>1.80104398727417</v>
+        <v>1.80104422569275</v>
       </c>
       <c r="H328" t="s">
         <v>8</v>
@@ -8949,7 +8949,7 @@
         <v>2.21600008010864</v>
       </c>
       <c r="G330" t="n">
-        <v>1.81579351425171</v>
+        <v>1.81579339504242</v>
       </c>
       <c r="H330" t="s">
         <v>8</v>
@@ -8975,7 +8975,7 @@
         <v>2.19799995422363</v>
       </c>
       <c r="G331" t="n">
-        <v>1.80104398727417</v>
+        <v>1.80104422569275</v>
       </c>
       <c r="H331" t="s">
         <v>8</v>
@@ -9027,7 +9027,7 @@
         <v>2.10800004005432</v>
       </c>
       <c r="G333" t="n">
-        <v>1.72729814052582</v>
+        <v>1.72729802131653</v>
       </c>
       <c r="H333" t="s">
         <v>8</v>
@@ -9079,7 +9079,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G335" t="n">
-        <v>1.72893667221069</v>
+        <v>1.72893679141998</v>
       </c>
       <c r="H335" t="s">
         <v>8</v>
@@ -9105,7 +9105,7 @@
         <v>2.15199995040894</v>
       </c>
       <c r="G336" t="n">
-        <v>1.76335155963898</v>
+        <v>1.76335167884827</v>
       </c>
       <c r="H336" t="s">
         <v>8</v>
@@ -9131,7 +9131,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G337" t="n">
-        <v>1.80268287658691</v>
+        <v>1.8026829957962</v>
       </c>
       <c r="H337" t="s">
         <v>8</v>
@@ -9157,7 +9157,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G338" t="n">
-        <v>1.80268287658691</v>
+        <v>1.8026829957962</v>
       </c>
       <c r="H338" t="s">
         <v>8</v>
@@ -9209,7 +9209,7 @@
         <v>2.25399994850159</v>
       </c>
       <c r="G340" t="n">
-        <v>1.84693038463593</v>
+        <v>1.8469306230545</v>
       </c>
       <c r="H340" t="s">
         <v>8</v>
@@ -9235,7 +9235,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G341" t="n">
-        <v>1.81087708473206</v>
+        <v>1.81087696552277</v>
       </c>
       <c r="H341" t="s">
         <v>8</v>
@@ -9261,7 +9261,7 @@
         <v>2.20799994468689</v>
       </c>
       <c r="G342" t="n">
-        <v>1.80923795700073</v>
+        <v>1.80923807621002</v>
       </c>
       <c r="H342" t="s">
         <v>8</v>
@@ -9287,7 +9287,7 @@
         <v>2.21199989318848</v>
       </c>
       <c r="G343" t="n">
-        <v>1.81251585483551</v>
+        <v>1.81251573562622</v>
       </c>
       <c r="H343" t="s">
         <v>8</v>
@@ -9365,7 +9365,7 @@
         <v>2.27600002288818</v>
       </c>
       <c r="G346" t="n">
-        <v>1.86495757102966</v>
+        <v>1.86495745182037</v>
       </c>
       <c r="H346" t="s">
         <v>8</v>
@@ -9391,7 +9391,7 @@
         <v>2.26799988746643</v>
       </c>
       <c r="G347" t="n">
-        <v>1.85840225219727</v>
+        <v>1.85840201377869</v>
       </c>
       <c r="H347" t="s">
         <v>8</v>
@@ -9417,7 +9417,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G348" t="n">
-        <v>1.87642896175385</v>
+        <v>1.87642884254456</v>
       </c>
       <c r="H348" t="s">
         <v>8</v>
@@ -9443,7 +9443,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G349" t="n">
-        <v>1.88462316989899</v>
+        <v>1.88462293148041</v>
       </c>
       <c r="H349" t="s">
         <v>8</v>
@@ -9469,7 +9469,7 @@
         <v>2.31800007820129</v>
       </c>
       <c r="G350" t="n">
-        <v>1.89937245845795</v>
+        <v>1.89937233924866</v>
       </c>
       <c r="H350" t="s">
         <v>8</v>
@@ -9495,7 +9495,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G351" t="n">
-        <v>1.91739916801453</v>
+        <v>1.91739940643311</v>
       </c>
       <c r="H351" t="s">
         <v>8</v>
@@ -9521,7 +9521,7 @@
         <v>2.25600004196167</v>
       </c>
       <c r="G352" t="n">
-        <v>1.84856939315796</v>
+        <v>1.84856951236725</v>
       </c>
       <c r="H352" t="s">
         <v>8</v>
@@ -9547,7 +9547,7 @@
         <v>2.27600002288818</v>
       </c>
       <c r="G353" t="n">
-        <v>1.86495757102966</v>
+        <v>1.86495745182037</v>
       </c>
       <c r="H353" t="s">
         <v>8</v>
@@ -9625,7 +9625,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G356" t="n">
-        <v>1.93679404258728</v>
+        <v>1.93679392337799</v>
       </c>
       <c r="H356" t="s">
         <v>8</v>
@@ -9651,7 +9651,7 @@
         <v>2.26200008392334</v>
       </c>
       <c r="G357" t="n">
-        <v>1.93850827217102</v>
+        <v>1.93850815296173</v>
       </c>
       <c r="H357" t="s">
         <v>8</v>
@@ -9677,7 +9677,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G358" t="n">
-        <v>1.97107374668121</v>
+        <v>1.97107362747192</v>
       </c>
       <c r="H358" t="s">
         <v>8</v>
@@ -9703,7 +9703,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G359" t="n">
-        <v>1.97107374668121</v>
+        <v>1.97107362747192</v>
       </c>
       <c r="H359" t="s">
         <v>8</v>
@@ -9729,7 +9729,7 @@
         <v>2.25</v>
       </c>
       <c r="G360" t="n">
-        <v>1.92822420597076</v>
+        <v>1.92822456359863</v>
       </c>
       <c r="H360" t="s">
         <v>8</v>
@@ -9755,7 +9755,7 @@
         <v>2.26600003242493</v>
       </c>
       <c r="G361" t="n">
-        <v>1.94193625450134</v>
+        <v>1.94193637371063</v>
       </c>
       <c r="H361" t="s">
         <v>8</v>
@@ -9781,7 +9781,7 @@
         <v>2.26799988746643</v>
       </c>
       <c r="G362" t="n">
-        <v>1.94365012645721</v>
+        <v>1.94364988803864</v>
       </c>
       <c r="H362" t="s">
         <v>8</v>
@@ -9885,7 +9885,7 @@
         <v>2.25</v>
       </c>
       <c r="G366" t="n">
-        <v>1.92822420597076</v>
+        <v>1.92822456359863</v>
       </c>
       <c r="H366" t="s">
         <v>8</v>
@@ -9911,7 +9911,7 @@
         <v>2.24799990653992</v>
       </c>
       <c r="G367" t="n">
-        <v>1.92651033401489</v>
+        <v>1.9265102148056</v>
       </c>
       <c r="H367" t="s">
         <v>8</v>
@@ -9937,7 +9937,7 @@
         <v>2.24799990653992</v>
       </c>
       <c r="G368" t="n">
-        <v>1.92651033401489</v>
+        <v>1.9265102148056</v>
       </c>
       <c r="H368" t="s">
         <v>8</v>
@@ -9963,7 +9963,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G369" t="n">
-        <v>1.95393407344818</v>
+        <v>1.95393395423889</v>
       </c>
       <c r="H369" t="s">
         <v>8</v>
@@ -9989,7 +9989,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G370" t="n">
-        <v>1.95393407344818</v>
+        <v>1.95393395423889</v>
       </c>
       <c r="H370" t="s">
         <v>8</v>
@@ -10015,7 +10015,7 @@
         <v>2.25600004196167</v>
       </c>
       <c r="G371" t="n">
-        <v>1.93336617946625</v>
+        <v>1.93336629867554</v>
       </c>
       <c r="H371" t="s">
         <v>8</v>
@@ -10093,7 +10093,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G374" t="n">
-        <v>1.8939448595047</v>
+        <v>1.89394462108612</v>
       </c>
       <c r="H374" t="s">
         <v>8</v>
@@ -10119,7 +10119,7 @@
         <v>2.18400001525879</v>
       </c>
       <c r="G375" t="n">
-        <v>1.8716629743576</v>
+        <v>1.87166309356689</v>
       </c>
       <c r="H375" t="s">
         <v>8</v>
@@ -10145,7 +10145,7 @@
         <v>2.25200009346008</v>
       </c>
       <c r="G376" t="n">
-        <v>1.92993855476379</v>
+        <v>1.92993807792664</v>
       </c>
       <c r="H376" t="s">
         <v>8</v>
@@ -10197,7 +10197,7 @@
         <v>2.23399996757507</v>
       </c>
       <c r="G378" t="n">
-        <v>1.91451239585876</v>
+        <v>1.91451263427734</v>
       </c>
       <c r="H378" t="s">
         <v>8</v>
@@ -10223,7 +10223,7 @@
         <v>2.20199990272522</v>
       </c>
       <c r="G379" t="n">
-        <v>1.88708889484406</v>
+        <v>1.88708865642548</v>
       </c>
       <c r="H379" t="s">
         <v>8</v>
@@ -10249,7 +10249,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G380" t="n">
-        <v>1.87680494785309</v>
+        <v>1.87680518627167</v>
       </c>
       <c r="H380" t="s">
         <v>8</v>
@@ -10275,7 +10275,7 @@
         <v>2.23799991607666</v>
       </c>
       <c r="G381" t="n">
-        <v>1.91794049739838</v>
+        <v>1.9179402589798</v>
       </c>
       <c r="H381" t="s">
         <v>8</v>
@@ -10301,7 +10301,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G382" t="n">
-        <v>1.8853747844696</v>
+        <v>1.88537490367889</v>
       </c>
       <c r="H382" t="s">
         <v>8</v>
@@ -10327,7 +10327,7 @@
         <v>2.18199992179871</v>
       </c>
       <c r="G383" t="n">
-        <v>1.86994898319244</v>
+        <v>1.86994910240173</v>
       </c>
       <c r="H383" t="s">
         <v>8</v>
@@ -10353,7 +10353,7 @@
         <v>2.2039999961853</v>
       </c>
       <c r="G384" t="n">
-        <v>1.88880276679993</v>
+        <v>1.88880288600922</v>
       </c>
       <c r="H384" t="s">
         <v>8</v>
@@ -10431,7 +10431,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G387" t="n">
-        <v>1.8939448595047</v>
+        <v>1.89394462108612</v>
       </c>
       <c r="H387" t="s">
         <v>8</v>
@@ -10457,7 +10457,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G388" t="n">
-        <v>1.8939448595047</v>
+        <v>1.89394462108612</v>
       </c>
       <c r="H388" t="s">
         <v>8</v>
@@ -10483,7 +10483,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G389" t="n">
-        <v>1.8939448595047</v>
+        <v>1.89394462108612</v>
       </c>
       <c r="H389" t="s">
         <v>8</v>
@@ -10509,7 +10509,7 @@
         <v>2.23399996757507</v>
       </c>
       <c r="G390" t="n">
-        <v>1.91451239585876</v>
+        <v>1.91451263427734</v>
       </c>
       <c r="H390" t="s">
         <v>8</v>
@@ -10535,7 +10535,7 @@
         <v>2.23799991607666</v>
       </c>
       <c r="G391" t="n">
-        <v>1.91794049739838</v>
+        <v>1.9179402589798</v>
       </c>
       <c r="H391" t="s">
         <v>8</v>
@@ -10561,7 +10561,7 @@
         <v>2.25600004196167</v>
       </c>
       <c r="G392" t="n">
-        <v>1.93336617946625</v>
+        <v>1.93336629867554</v>
       </c>
       <c r="H392" t="s">
         <v>8</v>
@@ -10613,7 +10613,7 @@
         <v>2.29200005531311</v>
       </c>
       <c r="G394" t="n">
-        <v>1.96421790122986</v>
+        <v>1.96421778202057</v>
       </c>
       <c r="H394" t="s">
         <v>8</v>
@@ -10665,7 +10665,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G396" t="n">
-        <v>1.97107374668121</v>
+        <v>1.97107362747192</v>
       </c>
       <c r="H396" t="s">
         <v>8</v>
@@ -10691,7 +10691,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G397" t="n">
-        <v>1.98821353912354</v>
+        <v>1.98821341991425</v>
       </c>
       <c r="H397" t="s">
         <v>8</v>
@@ -10717,7 +10717,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G398" t="n">
-        <v>1.98821353912354</v>
+        <v>1.98821341991425</v>
       </c>
       <c r="H398" t="s">
         <v>8</v>
@@ -10769,7 +10769,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G400" t="n">
-        <v>1.97964370250702</v>
+        <v>1.97964346408844</v>
       </c>
       <c r="H400" t="s">
         <v>8</v>
@@ -10795,7 +10795,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G401" t="n">
-        <v>1.97964370250702</v>
+        <v>1.97964346408844</v>
       </c>
       <c r="H401" t="s">
         <v>8</v>
@@ -10821,7 +10821,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G402" t="n">
-        <v>2.12533164024353</v>
+        <v>2.12533140182495</v>
       </c>
       <c r="H402" t="s">
         <v>8</v>
@@ -10899,7 +10899,7 @@
         <v>2.42600011825562</v>
       </c>
       <c r="G405" t="n">
-        <v>2.07905435562134</v>
+        <v>2.07905459403992</v>
       </c>
       <c r="H405" t="s">
         <v>8</v>
@@ -10925,7 +10925,7 @@
         <v>2.42799997329712</v>
       </c>
       <c r="G406" t="n">
-        <v>2.0807683467865</v>
+        <v>2.08076810836792</v>
       </c>
       <c r="H406" t="s">
         <v>8</v>
@@ -10951,7 +10951,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G407" t="n">
-        <v>2.06534242630005</v>
+        <v>2.06534266471863</v>
       </c>
       <c r="H407" t="s">
         <v>8</v>
@@ -10977,7 +10977,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G408" t="n">
-        <v>2.06534242630005</v>
+        <v>2.06534266471863</v>
       </c>
       <c r="H408" t="s">
         <v>8</v>
@@ -11029,7 +11029,7 @@
         <v>2.41799998283386</v>
       </c>
       <c r="G410" t="n">
-        <v>2.07219839096069</v>
+        <v>2.07219862937927</v>
       </c>
       <c r="H410" t="s">
         <v>8</v>
@@ -11055,7 +11055,7 @@
         <v>2.41799998283386</v>
       </c>
       <c r="G411" t="n">
-        <v>2.07219839096069</v>
+        <v>2.07219862937927</v>
       </c>
       <c r="H411" t="s">
         <v>8</v>
@@ -11081,7 +11081,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G412" t="n">
-        <v>2.12533164024353</v>
+        <v>2.12533140182495</v>
       </c>
       <c r="H412" t="s">
         <v>8</v>
@@ -11133,7 +11133,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G414" t="n">
-        <v>2.1081919670105</v>
+        <v>2.10819220542908</v>
       </c>
       <c r="H414" t="s">
         <v>8</v>
@@ -11185,7 +11185,7 @@
         <v>2.4539999961853</v>
       </c>
       <c r="G416" t="n">
-        <v>2.10304999351501</v>
+        <v>2.10304975509644</v>
       </c>
       <c r="H416" t="s">
         <v>8</v>
@@ -11263,7 +11263,7 @@
         <v>2.46799993515015</v>
       </c>
       <c r="G419" t="n">
-        <v>2.11504769325256</v>
+        <v>2.11504793167114</v>
       </c>
       <c r="H419" t="s">
         <v>8</v>
@@ -11289,7 +11289,7 @@
         <v>2.46799993515015</v>
       </c>
       <c r="G420" t="n">
-        <v>2.11504769325256</v>
+        <v>2.11504793167114</v>
       </c>
       <c r="H420" t="s">
         <v>8</v>
@@ -11367,7 +11367,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G423" t="n">
-        <v>2.1167619228363</v>
+        <v>2.11676168441772</v>
       </c>
       <c r="H423" t="s">
         <v>8</v>
@@ -11471,7 +11471,7 @@
         <v>2.46799993515015</v>
       </c>
       <c r="G427" t="n">
-        <v>2.11504769325256</v>
+        <v>2.11504793167114</v>
       </c>
       <c r="H427" t="s">
         <v>8</v>
@@ -11523,7 +11523,7 @@
         <v>2.4760000705719</v>
       </c>
       <c r="G429" t="n">
-        <v>2.12190365791321</v>
+        <v>2.12190389633179</v>
       </c>
       <c r="H429" t="s">
         <v>8</v>
@@ -11601,7 +11601,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G432" t="n">
-        <v>2.1081919670105</v>
+        <v>2.10819220542908</v>
       </c>
       <c r="H432" t="s">
         <v>8</v>
@@ -11679,7 +11679,7 @@
         <v>2.43799996376038</v>
       </c>
       <c r="G435" t="n">
-        <v>2.0893383026123</v>
+        <v>2.08933806419373</v>
       </c>
       <c r="H435" t="s">
         <v>8</v>
@@ -11705,7 +11705,7 @@
         <v>2.39400005340576</v>
       </c>
       <c r="G436" t="n">
-        <v>2.05163049697876</v>
+        <v>2.05163073539734</v>
       </c>
       <c r="H436" t="s">
         <v>8</v>
@@ -11809,7 +11809,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G440" t="n">
-        <v>2.17675089836121</v>
+        <v>2.17675113677979</v>
       </c>
       <c r="H440" t="s">
         <v>8</v>
@@ -11887,7 +11887,7 @@
         <v>2.48600006103516</v>
       </c>
       <c r="G443" t="n">
-        <v>2.13047385215759</v>
+        <v>2.13047361373901</v>
       </c>
       <c r="H443" t="s">
         <v>8</v>
@@ -11939,7 +11939,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G445" t="n">
-        <v>2.15961122512817</v>
+        <v>2.15961098670959</v>
       </c>
       <c r="H445" t="s">
         <v>8</v>
@@ -11965,7 +11965,7 @@
         <v>2.47199988365173</v>
       </c>
       <c r="G446" t="n">
-        <v>2.11847543716431</v>
+        <v>2.11847567558289</v>
       </c>
       <c r="H446" t="s">
         <v>8</v>
@@ -11991,7 +11991,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G447" t="n">
-        <v>2.1167619228363</v>
+        <v>2.11676168441772</v>
       </c>
       <c r="H447" t="s">
         <v>8</v>
@@ -12017,7 +12017,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G448" t="n">
-        <v>2.09105181694031</v>
+        <v>2.09105229377747</v>
       </c>
       <c r="H448" t="s">
         <v>8</v>
@@ -12069,7 +12069,7 @@
         <v>2.4779999256134</v>
       </c>
       <c r="G450" t="n">
-        <v>2.12361764907837</v>
+        <v>2.12361741065979</v>
       </c>
       <c r="H450" t="s">
         <v>8</v>
@@ -12121,7 +12121,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G452" t="n">
-        <v>2.09105181694031</v>
+        <v>2.09105229377747</v>
       </c>
       <c r="H452" t="s">
         <v>8</v>
@@ -12147,7 +12147,7 @@
         <v>2.46799993515015</v>
       </c>
       <c r="G453" t="n">
-        <v>2.11504769325256</v>
+        <v>2.11504793167114</v>
       </c>
       <c r="H453" t="s">
         <v>8</v>
@@ -12173,7 +12173,7 @@
         <v>2.4539999961853</v>
       </c>
       <c r="G454" t="n">
-        <v>2.10304999351501</v>
+        <v>2.10304975509644</v>
       </c>
       <c r="H454" t="s">
         <v>8</v>
@@ -12225,7 +12225,7 @@
         <v>2.4779999256134</v>
       </c>
       <c r="G456" t="n">
-        <v>2.12361764907837</v>
+        <v>2.12361741065979</v>
       </c>
       <c r="H456" t="s">
         <v>8</v>
@@ -12459,7 +12459,7 @@
         <v>2.50799989700317</v>
       </c>
       <c r="G465" t="n">
-        <v>2.14932703971863</v>
+        <v>2.14932751655579</v>
       </c>
       <c r="H465" t="s">
         <v>8</v>
@@ -12485,7 +12485,7 @@
         <v>2.49600005149841</v>
       </c>
       <c r="G466" t="n">
-        <v>2.13904356956482</v>
+        <v>2.13904333114624</v>
       </c>
       <c r="H466" t="s">
         <v>8</v>
@@ -12511,7 +12511,7 @@
         <v>2.49600005149841</v>
       </c>
       <c r="G467" t="n">
-        <v>2.13904356956482</v>
+        <v>2.13904333114624</v>
       </c>
       <c r="H467" t="s">
         <v>8</v>
@@ -12589,7 +12589,7 @@
         <v>2.4760000705719</v>
       </c>
       <c r="G470" t="n">
-        <v>2.12190365791321</v>
+        <v>2.12190389633179</v>
       </c>
       <c r="H470" t="s">
         <v>8</v>
@@ -12641,7 +12641,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G472" t="n">
-        <v>2.12533164024353</v>
+        <v>2.12533140182495</v>
       </c>
       <c r="H472" t="s">
         <v>8</v>
@@ -12667,7 +12667,7 @@
         <v>2.53800010681152</v>
       </c>
       <c r="G473" t="n">
-        <v>2.17503690719604</v>
+        <v>2.17503714561462</v>
       </c>
       <c r="H473" t="s">
         <v>8</v>
@@ -12693,7 +12693,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G474" t="n">
-        <v>2.15104126930237</v>
+        <v>2.15104150772095</v>
       </c>
       <c r="H474" t="s">
         <v>8</v>
@@ -12797,7 +12797,7 @@
         <v>2.45600008964539</v>
       </c>
       <c r="G478" t="n">
-        <v>2.1047637462616</v>
+        <v>2.10476398468018</v>
       </c>
       <c r="H478" t="s">
         <v>8</v>
@@ -12875,7 +12875,7 @@
         <v>2.37199997901917</v>
       </c>
       <c r="G481" t="n">
-        <v>2.03277707099915</v>
+        <v>2.03277683258057</v>
       </c>
       <c r="H481" t="s">
         <v>8</v>
@@ -12901,7 +12901,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G482" t="n">
-        <v>2.0482029914856</v>
+        <v>2.04820275306702</v>
       </c>
       <c r="H482" t="s">
         <v>8</v>
@@ -12927,7 +12927,7 @@
         <v>2.42600011825562</v>
       </c>
       <c r="G483" t="n">
-        <v>2.07905435562134</v>
+        <v>2.07905459403992</v>
       </c>
       <c r="H483" t="s">
         <v>8</v>
@@ -12953,7 +12953,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G484" t="n">
-        <v>2.0482029914856</v>
+        <v>2.04820275306702</v>
       </c>
       <c r="H484" t="s">
         <v>8</v>
@@ -12979,7 +12979,7 @@
         <v>2.41599988937378</v>
       </c>
       <c r="G485" t="n">
-        <v>2.07048416137695</v>
+        <v>2.07048439979553</v>
       </c>
       <c r="H485" t="s">
         <v>8</v>
@@ -13005,7 +13005,7 @@
         <v>2.37199997901917</v>
       </c>
       <c r="G486" t="n">
-        <v>2.03277707099915</v>
+        <v>2.03277683258057</v>
       </c>
       <c r="H486" t="s">
         <v>8</v>
@@ -13031,7 +13031,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G487" t="n">
-        <v>2.06534242630005</v>
+        <v>2.06534266471863</v>
       </c>
       <c r="H487" t="s">
         <v>8</v>
@@ -13057,7 +13057,7 @@
         <v>2.39199995994568</v>
       </c>
       <c r="G488" t="n">
-        <v>2.0499165058136</v>
+        <v>2.04991674423218</v>
       </c>
       <c r="H488" t="s">
         <v>8</v>
@@ -13109,7 +13109,7 @@
         <v>2.49600005149841</v>
       </c>
       <c r="G490" t="n">
-        <v>2.13904356956482</v>
+        <v>2.13904333114624</v>
       </c>
       <c r="H490" t="s">
         <v>8</v>
@@ -13161,7 +13161,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G492" t="n">
-        <v>2.12533164024353</v>
+        <v>2.12533140182495</v>
       </c>
       <c r="H492" t="s">
         <v>8</v>
@@ -13187,7 +13187,7 @@
         <v>2.45600008964539</v>
       </c>
       <c r="G493" t="n">
-        <v>2.1047637462616</v>
+        <v>2.10476398468018</v>
       </c>
       <c r="H493" t="s">
         <v>8</v>
@@ -13213,7 +13213,7 @@
         <v>2.48399996757507</v>
       </c>
       <c r="G494" t="n">
-        <v>2.12875962257385</v>
+        <v>2.12875986099243</v>
       </c>
       <c r="H494" t="s">
         <v>8</v>
@@ -13239,7 +13239,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G495" t="n">
-        <v>2.12533164024353</v>
+        <v>2.12533140182495</v>
       </c>
       <c r="H495" t="s">
         <v>8</v>
@@ -13265,7 +13265,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G496" t="n">
-        <v>2.1167619228363</v>
+        <v>2.11676168441772</v>
       </c>
       <c r="H496" t="s">
         <v>8</v>
@@ -13291,7 +13291,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G497" t="n">
-        <v>2.1167619228363</v>
+        <v>2.11676168441772</v>
       </c>
       <c r="H497" t="s">
         <v>8</v>
@@ -13317,7 +13317,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G498" t="n">
-        <v>2.1167619228363</v>
+        <v>2.11676168441772</v>
       </c>
       <c r="H498" t="s">
         <v>8</v>
@@ -13343,7 +13343,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G499" t="n">
-        <v>2.1167619228363</v>
+        <v>2.11676168441772</v>
       </c>
       <c r="H499" t="s">
         <v>8</v>
@@ -13655,7 +13655,7 @@
         <v>2.41599988937378</v>
       </c>
       <c r="G511" t="n">
-        <v>2.07048416137695</v>
+        <v>2.07048439979553</v>
       </c>
       <c r="H511" t="s">
         <v>8</v>
@@ -13681,7 +13681,7 @@
         <v>2.4760000705719</v>
       </c>
       <c r="G512" t="n">
-        <v>2.12190365791321</v>
+        <v>2.12190389633179</v>
       </c>
       <c r="H512" t="s">
         <v>8</v>
@@ -13811,7 +13811,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G517" t="n">
-        <v>2.09105181694031</v>
+        <v>2.09105229377747</v>
       </c>
       <c r="H517" t="s">
         <v>8</v>
@@ -13837,7 +13837,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G518" t="n">
-        <v>2.09105181694031</v>
+        <v>2.09105229377747</v>
       </c>
       <c r="H518" t="s">
         <v>8</v>
@@ -14305,7 +14305,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G536" t="n">
-        <v>2.0482029914856</v>
+        <v>2.04820275306702</v>
       </c>
       <c r="H536" t="s">
         <v>8</v>
@@ -14331,7 +14331,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G537" t="n">
-        <v>2.01392292976379</v>
+        <v>2.01392316818237</v>
       </c>
       <c r="H537" t="s">
         <v>8</v>
@@ -14435,7 +14435,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G541" t="n">
-        <v>2.09105181694031</v>
+        <v>2.09105229377747</v>
       </c>
       <c r="H541" t="s">
         <v>8</v>
@@ -14461,7 +14461,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G542" t="n">
-        <v>2.09105181694031</v>
+        <v>2.09105229377747</v>
       </c>
       <c r="H542" t="s">
         <v>8</v>
@@ -14617,7 +14617,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G548" t="n">
-        <v>2.0482029914856</v>
+        <v>2.04820275306702</v>
       </c>
       <c r="H548" t="s">
         <v>8</v>
@@ -14799,7 +14799,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G555" t="n">
-        <v>2.06534242630005</v>
+        <v>2.06534266471863</v>
       </c>
       <c r="H555" t="s">
         <v>8</v>
@@ -14851,7 +14851,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G557" t="n">
-        <v>2.1167619228363</v>
+        <v>2.11676168441772</v>
       </c>
       <c r="H557" t="s">
         <v>8</v>
@@ -14877,7 +14877,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G558" t="n">
-        <v>2.1081919670105</v>
+        <v>2.10819220542908</v>
       </c>
       <c r="H558" t="s">
         <v>8</v>
@@ -14903,7 +14903,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G559" t="n">
-        <v>2.06534242630005</v>
+        <v>2.06534266471863</v>
       </c>
       <c r="H559" t="s">
         <v>8</v>
@@ -14929,7 +14929,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G560" t="n">
-        <v>2.06534242630005</v>
+        <v>2.06534266471863</v>
       </c>
       <c r="H560" t="s">
         <v>8</v>
@@ -14955,7 +14955,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G561" t="n">
-        <v>2.09105181694031</v>
+        <v>2.09105229377747</v>
       </c>
       <c r="H561" t="s">
         <v>8</v>
@@ -15033,7 +15033,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G564" t="n">
-        <v>2.1081919670105</v>
+        <v>2.10819220542908</v>
       </c>
       <c r="H564" t="s">
         <v>8</v>
@@ -15085,7 +15085,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G566" t="n">
-        <v>2.12533164024353</v>
+        <v>2.12533140182495</v>
       </c>
       <c r="H566" t="s">
         <v>8</v>
@@ -15111,7 +15111,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G567" t="n">
-        <v>2.1081919670105</v>
+        <v>2.10819220542908</v>
       </c>
       <c r="H567" t="s">
         <v>8</v>
@@ -15137,7 +15137,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G568" t="n">
-        <v>2.1081919670105</v>
+        <v>2.10819220542908</v>
       </c>
       <c r="H568" t="s">
         <v>8</v>
@@ -15215,7 +15215,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G571" t="n">
-        <v>2.1081919670105</v>
+        <v>2.10819220542908</v>
       </c>
       <c r="H571" t="s">
         <v>8</v>
@@ -15241,7 +15241,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G572" t="n">
-        <v>2.09105181694031</v>
+        <v>2.09105229377747</v>
       </c>
       <c r="H572" t="s">
         <v>8</v>
@@ -15267,7 +15267,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G573" t="n">
-        <v>2.09105181694031</v>
+        <v>2.09105229377747</v>
       </c>
       <c r="H573" t="s">
         <v>8</v>
@@ -15319,7 +15319,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G575" t="n">
-        <v>2.1081919670105</v>
+        <v>2.10819220542908</v>
       </c>
       <c r="H575" t="s">
         <v>8</v>
@@ -15501,7 +15501,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G582" t="n">
-        <v>2.16818118095398</v>
+        <v>2.1681809425354</v>
       </c>
       <c r="H582" t="s">
         <v>8</v>
@@ -15527,7 +15527,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G583" t="n">
-        <v>2.16818118095398</v>
+        <v>2.1681809425354</v>
       </c>
       <c r="H583" t="s">
         <v>8</v>
@@ -15553,7 +15553,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G584" t="n">
-        <v>2.15961122512817</v>
+        <v>2.15961098670959</v>
       </c>
       <c r="H584" t="s">
         <v>8</v>
@@ -15579,7 +15579,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G585" t="n">
-        <v>2.15961122512817</v>
+        <v>2.15961098670959</v>
       </c>
       <c r="H585" t="s">
         <v>8</v>
@@ -15605,7 +15605,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G586" t="n">
-        <v>2.16818118095398</v>
+        <v>2.1681809425354</v>
       </c>
       <c r="H586" t="s">
         <v>8</v>
@@ -15631,7 +15631,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G587" t="n">
-        <v>2.15961122512817</v>
+        <v>2.15961098670959</v>
       </c>
       <c r="H587" t="s">
         <v>8</v>
@@ -15683,7 +15683,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G589" t="n">
-        <v>2.15961122512817</v>
+        <v>2.15961098670959</v>
       </c>
       <c r="H589" t="s">
         <v>8</v>
@@ -15709,7 +15709,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G590" t="n">
-        <v>2.17675089836121</v>
+        <v>2.17675113677979</v>
       </c>
       <c r="H590" t="s">
         <v>8</v>
@@ -15735,7 +15735,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G591" t="n">
-        <v>2.18532085418701</v>
+        <v>2.18532061576843</v>
       </c>
       <c r="H591" t="s">
         <v>8</v>
@@ -15865,7 +15865,7 @@
         <v>2.75</v>
       </c>
       <c r="G596" t="n">
-        <v>2.35671830177307</v>
+        <v>2.35671854019165</v>
       </c>
       <c r="H596" t="s">
         <v>8</v>
@@ -15943,7 +15943,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G599" t="n">
-        <v>2.46812725067139</v>
+        <v>2.46812701225281</v>
       </c>
       <c r="H599" t="s">
         <v>8</v>
@@ -16021,7 +16021,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G602" t="n">
-        <v>2.46812725067139</v>
+        <v>2.46812701225281</v>
       </c>
       <c r="H602" t="s">
         <v>8</v>
@@ -16047,7 +16047,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G603" t="n">
-        <v>2.53668642044067</v>
+        <v>2.53668594360352</v>
       </c>
       <c r="H603" t="s">
         <v>8</v>
@@ -16073,7 +16073,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G604" t="n">
-        <v>2.57953572273254</v>
+        <v>2.57953548431396</v>
       </c>
       <c r="H604" t="s">
         <v>8</v>
@@ -16099,7 +16099,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G605" t="n">
-        <v>2.596675157547</v>
+        <v>2.59667539596558</v>
       </c>
       <c r="H605" t="s">
         <v>8</v>
@@ -16151,7 +16151,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G607" t="n">
-        <v>2.55382585525513</v>
+        <v>2.55382609367371</v>
       </c>
       <c r="H607" t="s">
         <v>8</v>
@@ -16177,7 +16177,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G608" t="n">
-        <v>2.63447332382202</v>
+        <v>2.63447308540344</v>
       </c>
       <c r="H608" t="s">
         <v>8</v>
@@ -16255,7 +16255,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G611" t="n">
-        <v>2.61655139923096</v>
+        <v>2.61655163764954</v>
       </c>
       <c r="H611" t="s">
         <v>8</v>
@@ -16307,7 +16307,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G613" t="n">
-        <v>2.52694344520569</v>
+        <v>2.52694368362427</v>
       </c>
       <c r="H613" t="s">
         <v>8</v>
@@ -16385,7 +16385,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G616" t="n">
-        <v>2.50006127357483</v>
+        <v>2.50006103515625</v>
       </c>
       <c r="H616" t="s">
         <v>8</v>
@@ -16541,7 +16541,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G622" t="n">
-        <v>2.54486513137817</v>
+        <v>2.54486489295959</v>
       </c>
       <c r="H622" t="s">
         <v>8</v>
@@ -16593,7 +16593,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G624" t="n">
-        <v>2.57174754142761</v>
+        <v>2.57174730300903</v>
       </c>
       <c r="H624" t="s">
         <v>8</v>
@@ -16619,7 +16619,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G625" t="n">
-        <v>2.57174754142761</v>
+        <v>2.57174730300903</v>
       </c>
       <c r="H625" t="s">
         <v>8</v>
@@ -16723,7 +16723,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G629" t="n">
-        <v>2.54486513137817</v>
+        <v>2.54486489295959</v>
       </c>
       <c r="H629" t="s">
         <v>8</v>
@@ -16801,7 +16801,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G632" t="n">
-        <v>2.49110054969788</v>
+        <v>2.4911003112793</v>
       </c>
       <c r="H632" t="s">
         <v>8</v>
@@ -16905,7 +16905,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G636" t="n">
-        <v>2.54486513137817</v>
+        <v>2.54486489295959</v>
       </c>
       <c r="H636" t="s">
         <v>8</v>
@@ -17113,7 +17113,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G644" t="n">
-        <v>2.52694344520569</v>
+        <v>2.52694368362427</v>
       </c>
       <c r="H644" t="s">
         <v>8</v>
@@ -17295,7 +17295,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G651" t="n">
-        <v>2.54486513137817</v>
+        <v>2.54486489295959</v>
       </c>
       <c r="H651" t="s">
         <v>8</v>
@@ -17347,7 +17347,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G653" t="n">
-        <v>2.52694344520569</v>
+        <v>2.52694368362427</v>
       </c>
       <c r="H653" t="s">
         <v>8</v>
@@ -17477,7 +17477,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G658" t="n">
-        <v>2.77784585952759</v>
+        <v>2.77784562110901</v>
       </c>
       <c r="H658" t="s">
         <v>8</v>
@@ -17503,7 +17503,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G659" t="n">
-        <v>2.77784585952759</v>
+        <v>2.77784562110901</v>
       </c>
       <c r="H659" t="s">
         <v>8</v>
@@ -17659,7 +17659,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G665" t="n">
-        <v>2.76888513565063</v>
+        <v>2.76888465881348</v>
       </c>
       <c r="H665" t="s">
         <v>8</v>
@@ -17711,7 +17711,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G667" t="n">
-        <v>2.75096321105957</v>
+        <v>2.75096344947815</v>
       </c>
       <c r="H667" t="s">
         <v>8</v>
@@ -17737,7 +17737,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G668" t="n">
-        <v>2.67031621932983</v>
+        <v>2.67031645774841</v>
       </c>
       <c r="H668" t="s">
         <v>8</v>
@@ -17763,7 +17763,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G669" t="n">
-        <v>2.63447332382202</v>
+        <v>2.63447308540344</v>
       </c>
       <c r="H669" t="s">
         <v>8</v>
@@ -17789,7 +17789,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G670" t="n">
-        <v>2.72408103942871</v>
+        <v>2.72408080101013</v>
       </c>
       <c r="H670" t="s">
         <v>8</v>
@@ -17815,7 +17815,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G671" t="n">
-        <v>2.75096321105957</v>
+        <v>2.75096344947815</v>
       </c>
       <c r="H671" t="s">
         <v>8</v>
@@ -17893,7 +17893,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G674" t="n">
-        <v>2.65239477157593</v>
+        <v>2.65239453315735</v>
       </c>
       <c r="H674" t="s">
         <v>8</v>
@@ -17919,7 +17919,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G675" t="n">
-        <v>2.65239477157593</v>
+        <v>2.65239453315735</v>
       </c>
       <c r="H675" t="s">
         <v>8</v>
@@ -17945,7 +17945,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G676" t="n">
-        <v>2.72408103942871</v>
+        <v>2.72408080101013</v>
       </c>
       <c r="H676" t="s">
         <v>8</v>
@@ -17971,7 +17971,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G677" t="n">
-        <v>2.67031621932983</v>
+        <v>2.67031645774841</v>
       </c>
       <c r="H677" t="s">
         <v>8</v>
@@ -17997,7 +17997,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G678" t="n">
-        <v>2.67031621932983</v>
+        <v>2.67031645774841</v>
       </c>
       <c r="H678" t="s">
         <v>8</v>
@@ -18049,7 +18049,7 @@
         <v>3</v>
       </c>
       <c r="G680" t="n">
-        <v>2.68823790550232</v>
+        <v>2.68823766708374</v>
       </c>
       <c r="H680" t="s">
         <v>8</v>
@@ -18075,7 +18075,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G681" t="n">
-        <v>2.72408103942871</v>
+        <v>2.72408080101013</v>
       </c>
       <c r="H681" t="s">
         <v>8</v>
@@ -18101,7 +18101,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G682" t="n">
-        <v>2.75096321105957</v>
+        <v>2.75096344947815</v>
       </c>
       <c r="H682" t="s">
         <v>8</v>
@@ -18153,7 +18153,7 @@
         <v>3</v>
       </c>
       <c r="G684" t="n">
-        <v>2.68823790550232</v>
+        <v>2.68823766708374</v>
       </c>
       <c r="H684" t="s">
         <v>8</v>
@@ -18179,7 +18179,7 @@
         <v>3</v>
       </c>
       <c r="G685" t="n">
-        <v>2.68823790550232</v>
+        <v>2.68823766708374</v>
       </c>
       <c r="H685" t="s">
         <v>8</v>
@@ -18205,7 +18205,7 @@
         <v>3</v>
       </c>
       <c r="G686" t="n">
-        <v>2.68823790550232</v>
+        <v>2.68823766708374</v>
       </c>
       <c r="H686" t="s">
         <v>8</v>
@@ -18257,7 +18257,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G688" t="n">
-        <v>2.75096321105957</v>
+        <v>2.75096344947815</v>
       </c>
       <c r="H688" t="s">
         <v>8</v>
@@ -18309,7 +18309,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G690" t="n">
-        <v>2.69719886779785</v>
+        <v>2.69719862937927</v>
       </c>
       <c r="H690" t="s">
         <v>8</v>
@@ -18413,7 +18413,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G694" t="n">
-        <v>2.86745381355286</v>
+        <v>2.86745357513428</v>
       </c>
       <c r="H694" t="s">
         <v>8</v>
@@ -18439,7 +18439,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G695" t="n">
-        <v>2.83161067962646</v>
+        <v>2.83161044120789</v>
       </c>
       <c r="H695" t="s">
         <v>8</v>
@@ -18491,7 +18491,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G697" t="n">
-        <v>2.75096321105957</v>
+        <v>2.75096344947815</v>
       </c>
       <c r="H697" t="s">
         <v>8</v>
@@ -18517,7 +18517,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G698" t="n">
-        <v>2.72408103942871</v>
+        <v>2.72408080101013</v>
       </c>
       <c r="H698" t="s">
         <v>8</v>
@@ -18569,7 +18569,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G700" t="n">
-        <v>2.75096321105957</v>
+        <v>2.75096344947815</v>
       </c>
       <c r="H700" t="s">
         <v>8</v>
@@ -18595,7 +18595,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G701" t="n">
-        <v>2.75096321105957</v>
+        <v>2.75096344947815</v>
       </c>
       <c r="H701" t="s">
         <v>8</v>
@@ -18621,7 +18621,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G702" t="n">
-        <v>2.75096321105957</v>
+        <v>2.75096344947815</v>
       </c>
       <c r="H702" t="s">
         <v>8</v>
@@ -18647,7 +18647,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G703" t="n">
-        <v>2.72408103942871</v>
+        <v>2.72408080101013</v>
       </c>
       <c r="H703" t="s">
         <v>8</v>
@@ -18673,7 +18673,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G704" t="n">
-        <v>2.65239477157593</v>
+        <v>2.65239453315735</v>
       </c>
       <c r="H704" t="s">
         <v>8</v>
@@ -18699,7 +18699,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G705" t="n">
-        <v>2.69719886779785</v>
+        <v>2.69719862937927</v>
       </c>
       <c r="H705" t="s">
         <v>8</v>
@@ -18751,7 +18751,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G707" t="n">
-        <v>2.64343404769897</v>
+        <v>2.6434338092804</v>
       </c>
       <c r="H707" t="s">
         <v>8</v>
@@ -18777,7 +18777,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G708" t="n">
-        <v>2.63447332382202</v>
+        <v>2.63447308540344</v>
       </c>
       <c r="H708" t="s">
         <v>8</v>
@@ -18803,7 +18803,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G709" t="n">
-        <v>2.62551259994507</v>
+        <v>2.62551236152649</v>
       </c>
       <c r="H709" t="s">
         <v>8</v>
@@ -18829,7 +18829,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G710" t="n">
-        <v>2.58070850372314</v>
+        <v>2.58070826530457</v>
       </c>
       <c r="H710" t="s">
         <v>8</v>
@@ -18855,7 +18855,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G711" t="n">
-        <v>2.58070850372314</v>
+        <v>2.58070826530457</v>
       </c>
       <c r="H711" t="s">
         <v>8</v>
@@ -18907,7 +18907,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G713" t="n">
-        <v>2.61655139923096</v>
+        <v>2.61655163764954</v>
       </c>
       <c r="H713" t="s">
         <v>8</v>
@@ -19011,7 +19011,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G717" t="n">
-        <v>2.58070850372314</v>
+        <v>2.58070826530457</v>
       </c>
       <c r="H717" t="s">
         <v>8</v>
@@ -19037,7 +19037,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G718" t="n">
-        <v>2.57174754142761</v>
+        <v>2.57174730300903</v>
       </c>
       <c r="H718" t="s">
         <v>8</v>
@@ -19089,7 +19089,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G720" t="n">
-        <v>2.61655139923096</v>
+        <v>2.61655163764954</v>
       </c>
       <c r="H720" t="s">
         <v>8</v>
@@ -19115,7 +19115,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G721" t="n">
-        <v>2.61655139923096</v>
+        <v>2.61655163764954</v>
       </c>
       <c r="H721" t="s">
         <v>8</v>
@@ -19245,7 +19245,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G726" t="n">
-        <v>2.62551259994507</v>
+        <v>2.62551236152649</v>
       </c>
       <c r="H726" t="s">
         <v>8</v>
@@ -19271,7 +19271,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G727" t="n">
-        <v>2.61655139923096</v>
+        <v>2.61655163764954</v>
       </c>
       <c r="H727" t="s">
         <v>8</v>
@@ -19297,7 +19297,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G728" t="n">
-        <v>2.61655139923096</v>
+        <v>2.61655163764954</v>
       </c>
       <c r="H728" t="s">
         <v>8</v>
@@ -19323,7 +19323,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G729" t="n">
-        <v>2.61655139923096</v>
+        <v>2.61655163764954</v>
       </c>
       <c r="H729" t="s">
         <v>8</v>
@@ -19375,7 +19375,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G731" t="n">
-        <v>2.61655139923096</v>
+        <v>2.61655163764954</v>
       </c>
       <c r="H731" t="s">
         <v>8</v>
@@ -19557,7 +19557,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G738" t="n">
-        <v>2.57174754142761</v>
+        <v>2.57174730300903</v>
       </c>
       <c r="H738" t="s">
         <v>8</v>
@@ -19765,7 +19765,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G746" t="n">
-        <v>2.41941404342651</v>
+        <v>2.41941428184509</v>
       </c>
       <c r="H746" t="s">
         <v>8</v>
@@ -19791,7 +19791,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G747" t="n">
-        <v>2.50006127357483</v>
+        <v>2.50006103515625</v>
       </c>
       <c r="H747" t="s">
         <v>8</v>
@@ -19817,7 +19817,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G748" t="n">
-        <v>2.57174754142761</v>
+        <v>2.57174730300903</v>
       </c>
       <c r="H748" t="s">
         <v>8</v>
@@ -19869,7 +19869,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G750" t="n">
-        <v>2.57174754142761</v>
+        <v>2.57174730300903</v>
       </c>
       <c r="H750" t="s">
         <v>8</v>
@@ -19895,7 +19895,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G751" t="n">
-        <v>2.57174754142761</v>
+        <v>2.57174730300903</v>
       </c>
       <c r="H751" t="s">
         <v>8</v>
@@ -19921,7 +19921,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G752" t="n">
-        <v>2.57174754142761</v>
+        <v>2.57174730300903</v>
       </c>
       <c r="H752" t="s">
         <v>8</v>
@@ -20285,7 +20285,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G766" t="n">
-        <v>2.63447332382202</v>
+        <v>2.63447308540344</v>
       </c>
       <c r="H766" t="s">
         <v>8</v>
@@ -20311,7 +20311,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G767" t="n">
-        <v>2.67031621932983</v>
+        <v>2.67031645774841</v>
       </c>
       <c r="H767" t="s">
         <v>8</v>
@@ -20363,7 +20363,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G769" t="n">
-        <v>2.67031621932983</v>
+        <v>2.67031645774841</v>
       </c>
       <c r="H769" t="s">
         <v>8</v>
@@ -20389,7 +20389,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G770" t="n">
-        <v>2.69719886779785</v>
+        <v>2.69719862937927</v>
       </c>
       <c r="H770" t="s">
         <v>8</v>
@@ -20441,7 +20441,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G772" t="n">
-        <v>2.67031621932983</v>
+        <v>2.67031645774841</v>
       </c>
       <c r="H772" t="s">
         <v>8</v>
@@ -20493,7 +20493,7 @@
         <v>3</v>
       </c>
       <c r="G774" t="n">
-        <v>2.68823790550232</v>
+        <v>2.68823766708374</v>
       </c>
       <c r="H774" t="s">
         <v>8</v>
@@ -20519,7 +20519,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G775" t="n">
-        <v>2.69719886779785</v>
+        <v>2.69719862937927</v>
       </c>
       <c r="H775" t="s">
         <v>8</v>
@@ -20571,7 +20571,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G777" t="n">
-        <v>2.75096321105957</v>
+        <v>2.75096344947815</v>
       </c>
       <c r="H777" t="s">
         <v>8</v>
@@ -20623,7 +20623,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G779" t="n">
-        <v>2.840571641922</v>
+        <v>2.84057140350342</v>
       </c>
       <c r="H779" t="s">
         <v>8</v>
@@ -20727,7 +20727,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G783" t="n">
-        <v>2.82264971733093</v>
+        <v>2.82264995574951</v>
       </c>
       <c r="H783" t="s">
         <v>8</v>
@@ -20779,7 +20779,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G785" t="n">
-        <v>2.83161067962646</v>
+        <v>2.83161044120789</v>
       </c>
       <c r="H785" t="s">
         <v>8</v>
@@ -20805,7 +20805,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G786" t="n">
-        <v>2.82264971733093</v>
+        <v>2.82264995574951</v>
       </c>
       <c r="H786" t="s">
         <v>8</v>
@@ -20831,7 +20831,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G787" t="n">
-        <v>2.77784585952759</v>
+        <v>2.77784562110901</v>
       </c>
       <c r="H787" t="s">
         <v>8</v>
@@ -20857,7 +20857,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G788" t="n">
-        <v>2.840571641922</v>
+        <v>2.84057140350342</v>
       </c>
       <c r="H788" t="s">
         <v>8</v>
@@ -20883,7 +20883,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G789" t="n">
-        <v>2.77784585952759</v>
+        <v>2.77784562110901</v>
       </c>
       <c r="H789" t="s">
         <v>8</v>
@@ -20909,7 +20909,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G790" t="n">
-        <v>2.76888513565063</v>
+        <v>2.76888465881348</v>
       </c>
       <c r="H790" t="s">
         <v>8</v>
@@ -20935,7 +20935,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G791" t="n">
-        <v>2.83161067962646</v>
+        <v>2.83161044120789</v>
       </c>
       <c r="H791" t="s">
         <v>8</v>
@@ -20961,7 +20961,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G792" t="n">
-        <v>2.77784585952759</v>
+        <v>2.77784562110901</v>
       </c>
       <c r="H792" t="s">
         <v>8</v>
@@ -21117,7 +21117,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G798" t="n">
-        <v>3.16315960884094</v>
+        <v>3.16315984725952</v>
       </c>
       <c r="H798" t="s">
         <v>8</v>
@@ -21143,7 +21143,7 @@
         <v>3.5</v>
       </c>
       <c r="G799" t="n">
-        <v>3.13627743721008</v>
+        <v>3.13627767562866</v>
       </c>
       <c r="H799" t="s">
         <v>8</v>
@@ -21195,7 +21195,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G801" t="n">
-        <v>3.25276780128479</v>
+        <v>3.25276803970337</v>
       </c>
       <c r="H801" t="s">
         <v>8</v>
@@ -21221,7 +21221,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G802" t="n">
-        <v>3.26172852516174</v>
+        <v>3.26172876358032</v>
       </c>
       <c r="H802" t="s">
         <v>8</v>
@@ -21247,7 +21247,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G803" t="n">
-        <v>3.25276780128479</v>
+        <v>3.25276803970337</v>
       </c>
       <c r="H803" t="s">
         <v>8</v>
@@ -21325,7 +21325,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G806" t="n">
-        <v>3.29757165908813</v>
+        <v>3.29757189750671</v>
       </c>
       <c r="H806" t="s">
         <v>8</v>
@@ -21403,7 +21403,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G809" t="n">
-        <v>3.33341479301453</v>
+        <v>3.33341503143311</v>
       </c>
       <c r="H809" t="s">
         <v>8</v>
@@ -21455,7 +21455,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G811" t="n">
-        <v>3.33341479301453</v>
+        <v>3.33341503143311</v>
       </c>
       <c r="H811" t="s">
         <v>8</v>
@@ -21481,7 +21481,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G812" t="n">
-        <v>3.34237575531006</v>
+        <v>3.34237551689148</v>
       </c>
       <c r="H812" t="s">
         <v>8</v>
@@ -21611,7 +21611,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G817" t="n">
-        <v>3.36925792694092</v>
+        <v>3.36925840377808</v>
       </c>
       <c r="H817" t="s">
         <v>8</v>
@@ -21689,7 +21689,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G820" t="n">
-        <v>3.37821888923645</v>
+        <v>3.37821865081787</v>
       </c>
       <c r="H820" t="s">
         <v>8</v>
@@ -21741,7 +21741,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G822" t="n">
-        <v>3.4857485294342</v>
+        <v>3.48574829101562</v>
       </c>
       <c r="H822" t="s">
         <v>8</v>
@@ -21767,7 +21767,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G823" t="n">
-        <v>3.47678756713867</v>
+        <v>3.47678780555725</v>
       </c>
       <c r="H823" t="s">
         <v>8</v>
@@ -21949,7 +21949,7 @@
         <v>3.97000002861023</v>
       </c>
       <c r="G830" t="n">
-        <v>3.55743479728699</v>
+        <v>3.55743455886841</v>
       </c>
       <c r="H830" t="s">
         <v>8</v>
@@ -22027,7 +22027,7 @@
         <v>3.9300000667572</v>
       </c>
       <c r="G833" t="n">
-        <v>3.5215916633606</v>
+        <v>3.52159142494202</v>
       </c>
       <c r="H833" t="s">
         <v>8</v>
@@ -22053,7 +22053,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G834" t="n">
-        <v>3.51263093948364</v>
+        <v>3.51263070106506</v>
       </c>
       <c r="H834" t="s">
         <v>8</v>
@@ -22079,7 +22079,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G835" t="n">
-        <v>3.51263093948364</v>
+        <v>3.51263070106506</v>
       </c>
       <c r="H835" t="s">
         <v>8</v>
@@ -22105,7 +22105,7 @@
         <v>3.97000002861023</v>
       </c>
       <c r="G836" t="n">
-        <v>3.55743479728699</v>
+        <v>3.55743455886841</v>
       </c>
       <c r="H836" t="s">
         <v>8</v>
@@ -22131,7 +22131,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G837" t="n">
-        <v>3.51263093948364</v>
+        <v>3.51263070106506</v>
       </c>
       <c r="H837" t="s">
         <v>8</v>
@@ -22157,7 +22157,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G838" t="n">
-        <v>3.5395131111145</v>
+        <v>3.53951334953308</v>
       </c>
       <c r="H838" t="s">
         <v>8</v>
@@ -22209,7 +22209,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G840" t="n">
-        <v>3.51263093948364</v>
+        <v>3.51263070106506</v>
       </c>
       <c r="H840" t="s">
         <v>8</v>
@@ -22313,7 +22313,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G844" t="n">
-        <v>3.66496443748474</v>
+        <v>3.66496419906616</v>
       </c>
       <c r="H844" t="s">
         <v>8</v>
@@ -22365,7 +22365,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G846" t="n">
-        <v>3.71872925758362</v>
+        <v>3.71872901916504</v>
       </c>
       <c r="H846" t="s">
         <v>8</v>
@@ -22443,7 +22443,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G849" t="n">
-        <v>3.68288588523865</v>
+        <v>3.68288612365723</v>
       </c>
       <c r="H849" t="s">
         <v>8</v>
@@ -22573,7 +22573,7 @@
         <v>4.25</v>
       </c>
       <c r="G854" t="n">
-        <v>3.80833721160889</v>
+        <v>3.80833697319031</v>
       </c>
       <c r="H854" t="s">
         <v>8</v>
@@ -22625,7 +22625,7 @@
         <v>4.25</v>
       </c>
       <c r="G856" t="n">
-        <v>3.80833721160889</v>
+        <v>3.80833697319031</v>
       </c>
       <c r="H856" t="s">
         <v>8</v>
@@ -22677,7 +22677,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G858" t="n">
-        <v>3.96067070960999</v>
+        <v>3.96067023277283</v>
       </c>
       <c r="H858" t="s">
         <v>8</v>
@@ -71664,6 +71664,32 @@
         <v>0.990000009536743</v>
       </c>
       <c r="H2742" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2743">
+      <c r="A2743" s="1" t="n">
+        <v>46310.2916666667</v>
+      </c>
+      <c r="B2743" t="n">
+        <v>674</v>
+      </c>
+      <c r="C2743" t="n">
+        <v>0.980000019073486</v>
+      </c>
+      <c r="D2743" t="n">
+        <v>0.975000023841858</v>
+      </c>
+      <c r="E2743" t="n">
+        <v>0.975000023841858</v>
+      </c>
+      <c r="F2743" t="n">
+        <v>0.980000019073486</v>
+      </c>
+      <c r="G2743" t="n">
+        <v>0.980000019073486</v>
+      </c>
+      <c r="H2743" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/RAT.MI.xlsx
+++ b/data/RAT.MI.xlsx
@@ -421,7 +421,7 @@
         <v>2.3659999370575</v>
       </c>
       <c r="G2" t="n">
-        <v>1.85825955867767</v>
+        <v>1.85825932025909</v>
       </c>
       <c r="H2" t="s">
         <v>8</v>
@@ -447,7 +447,7 @@
         <v>2.43600010871887</v>
       </c>
       <c r="G3" t="n">
-        <v>1.91323781013489</v>
+        <v>1.9132376909256</v>
       </c>
       <c r="H3" t="s">
         <v>8</v>
@@ -473,7 +473,7 @@
         <v>2.44600009918213</v>
       </c>
       <c r="G4" t="n">
-        <v>1.92109143733978</v>
+        <v>1.92109167575836</v>
       </c>
       <c r="H4" t="s">
         <v>8</v>
@@ -499,7 +499,7 @@
         <v>2.44600009918213</v>
       </c>
       <c r="G5" t="n">
-        <v>1.92109143733978</v>
+        <v>1.92109167575836</v>
       </c>
       <c r="H5" t="s">
         <v>8</v>
@@ -525,7 +525,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G6" t="n">
-        <v>1.88496327400208</v>
+        <v>1.88496291637421</v>
       </c>
       <c r="H6" t="s">
         <v>8</v>
@@ -551,7 +551,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G7" t="n">
-        <v>1.88496327400208</v>
+        <v>1.88496291637421</v>
       </c>
       <c r="H7" t="s">
         <v>8</v>
@@ -577,7 +577,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G8" t="n">
-        <v>1.9242330789566</v>
+        <v>1.92423319816589</v>
       </c>
       <c r="H8" t="s">
         <v>8</v>
@@ -603,7 +603,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G9" t="n">
-        <v>1.88496327400208</v>
+        <v>1.88496291637421</v>
       </c>
       <c r="H9" t="s">
         <v>8</v>
@@ -629,7 +629,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G10" t="n">
-        <v>1.88496327400208</v>
+        <v>1.88496291637421</v>
       </c>
       <c r="H10" t="s">
         <v>8</v>
@@ -655,7 +655,7 @@
         <v>2.3659999370575</v>
       </c>
       <c r="G11" t="n">
-        <v>1.85825955867767</v>
+        <v>1.85825932025909</v>
       </c>
       <c r="H11" t="s">
         <v>8</v>
@@ -785,7 +785,7 @@
         <v>2.25</v>
       </c>
       <c r="G16" t="n">
-        <v>1.76715314388275</v>
+        <v>1.76715278625488</v>
       </c>
       <c r="H16" t="s">
         <v>8</v>
@@ -811,7 +811,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G17" t="n">
-        <v>1.85354697704315</v>
+        <v>1.85354709625244</v>
       </c>
       <c r="H17" t="s">
         <v>8</v>
@@ -837,7 +837,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G18" t="n">
-        <v>1.85354697704315</v>
+        <v>1.85354709625244</v>
       </c>
       <c r="H18" t="s">
         <v>8</v>
@@ -889,7 +889,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G20" t="n">
-        <v>1.87710905075073</v>
+        <v>1.87710916996002</v>
       </c>
       <c r="H20" t="s">
         <v>8</v>
@@ -915,7 +915,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G21" t="n">
-        <v>1.89281725883484</v>
+        <v>1.89281713962555</v>
       </c>
       <c r="H21" t="s">
         <v>8</v>
@@ -941,7 +941,7 @@
         <v>2.37800002098083</v>
       </c>
       <c r="G22" t="n">
-        <v>1.86768436431885</v>
+        <v>1.86768424510956</v>
       </c>
       <c r="H22" t="s">
         <v>8</v>
@@ -993,7 +993,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G24" t="n">
-        <v>1.83783888816833</v>
+        <v>1.83783900737762</v>
       </c>
       <c r="H24" t="s">
         <v>8</v>
@@ -1019,7 +1019,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G25" t="n">
-        <v>1.83783888816833</v>
+        <v>1.83783900737762</v>
       </c>
       <c r="H25" t="s">
         <v>8</v>
@@ -1045,7 +1045,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G26" t="n">
-        <v>1.88496327400208</v>
+        <v>1.88496291637421</v>
       </c>
       <c r="H26" t="s">
         <v>8</v>
@@ -1071,7 +1071,7 @@
         <v>2.38800001144409</v>
       </c>
       <c r="G27" t="n">
-        <v>1.87553834915161</v>
+        <v>1.87553858757019</v>
       </c>
       <c r="H27" t="s">
         <v>8</v>
@@ -1097,7 +1097,7 @@
         <v>2.38800001144409</v>
       </c>
       <c r="G28" t="n">
-        <v>1.87553834915161</v>
+        <v>1.87553858757019</v>
       </c>
       <c r="H28" t="s">
         <v>8</v>
@@ -1123,7 +1123,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G29" t="n">
-        <v>1.88496327400208</v>
+        <v>1.88496291637421</v>
       </c>
       <c r="H29" t="s">
         <v>8</v>
@@ -1175,7 +1175,7 @@
         <v>2.32599997520447</v>
       </c>
       <c r="G31" t="n">
-        <v>1.82684361934662</v>
+        <v>1.82684350013733</v>
       </c>
       <c r="H31" t="s">
         <v>8</v>
@@ -1227,7 +1227,7 @@
         <v>2.31599998474121</v>
       </c>
       <c r="G33" t="n">
-        <v>1.8189891576767</v>
+        <v>1.81898951530457</v>
       </c>
       <c r="H33" t="s">
         <v>8</v>
@@ -1253,7 +1253,7 @@
         <v>2.33800005912781</v>
       </c>
       <c r="G34" t="n">
-        <v>1.83626806735992</v>
+        <v>1.8362683057785</v>
       </c>
       <c r="H34" t="s">
         <v>8</v>
@@ -1279,7 +1279,7 @@
         <v>2.36800003051758</v>
       </c>
       <c r="G35" t="n">
-        <v>1.85983002185822</v>
+        <v>1.85983037948608</v>
       </c>
       <c r="H35" t="s">
         <v>8</v>
@@ -1305,7 +1305,7 @@
         <v>2.36800003051758</v>
       </c>
       <c r="G36" t="n">
-        <v>1.85983002185822</v>
+        <v>1.85983037948608</v>
       </c>
       <c r="H36" t="s">
         <v>8</v>
@@ -1331,7 +1331,7 @@
         <v>2.36800003051758</v>
       </c>
       <c r="G37" t="n">
-        <v>1.85983002185822</v>
+        <v>1.85983037948608</v>
       </c>
       <c r="H37" t="s">
         <v>8</v>
@@ -1357,7 +1357,7 @@
         <v>2.29800009727478</v>
       </c>
       <c r="G38" t="n">
-        <v>1.80485224723816</v>
+        <v>1.80485212802887</v>
       </c>
       <c r="H38" t="s">
         <v>8</v>
@@ -1383,7 +1383,7 @@
         <v>2.31800007820129</v>
       </c>
       <c r="G39" t="n">
-        <v>1.82056033611298</v>
+        <v>1.82056021690369</v>
       </c>
       <c r="H39" t="s">
         <v>8</v>
@@ -1409,7 +1409,7 @@
         <v>2.31399989128113</v>
       </c>
       <c r="G40" t="n">
-        <v>1.81741833686829</v>
+        <v>1.81741845607758</v>
       </c>
       <c r="H40" t="s">
         <v>8</v>
@@ -1435,7 +1435,7 @@
         <v>2.31399989128113</v>
       </c>
       <c r="G41" t="n">
-        <v>1.81741833686829</v>
+        <v>1.81741845607758</v>
       </c>
       <c r="H41" t="s">
         <v>8</v>
@@ -1461,7 +1461,7 @@
         <v>2.31399989128113</v>
       </c>
       <c r="G42" t="n">
-        <v>1.81741833686829</v>
+        <v>1.81741845607758</v>
       </c>
       <c r="H42" t="s">
         <v>8</v>
@@ -1487,7 +1487,7 @@
         <v>2.33800005912781</v>
       </c>
       <c r="G43" t="n">
-        <v>1.83626806735992</v>
+        <v>1.8362683057785</v>
       </c>
       <c r="H43" t="s">
         <v>8</v>
@@ -1513,7 +1513,7 @@
         <v>2.36800003051758</v>
       </c>
       <c r="G44" t="n">
-        <v>1.85983002185822</v>
+        <v>1.85983037948608</v>
       </c>
       <c r="H44" t="s">
         <v>8</v>
@@ -1539,7 +1539,7 @@
         <v>2.37800002098083</v>
       </c>
       <c r="G45" t="n">
-        <v>1.86768436431885</v>
+        <v>1.86768424510956</v>
       </c>
       <c r="H45" t="s">
         <v>8</v>
@@ -1565,7 +1565,7 @@
         <v>2.35599994659424</v>
       </c>
       <c r="G46" t="n">
-        <v>1.85040533542633</v>
+        <v>1.85040521621704</v>
       </c>
       <c r="H46" t="s">
         <v>8</v>
@@ -1591,7 +1591,7 @@
         <v>2.39400005340576</v>
       </c>
       <c r="G47" t="n">
-        <v>1.88025069236755</v>
+        <v>1.88025081157684</v>
       </c>
       <c r="H47" t="s">
         <v>8</v>
@@ -1617,7 +1617,7 @@
         <v>2.39400005340576</v>
       </c>
       <c r="G48" t="n">
-        <v>1.88025069236755</v>
+        <v>1.88025081157684</v>
       </c>
       <c r="H48" t="s">
         <v>8</v>
@@ -1643,7 +1643,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G49" t="n">
-        <v>1.81427693367004</v>
+        <v>1.81427705287933</v>
       </c>
       <c r="H49" t="s">
         <v>8</v>
@@ -1695,7 +1695,7 @@
         <v>2.33800005912781</v>
       </c>
       <c r="G51" t="n">
-        <v>1.83626806735992</v>
+        <v>1.8362683057785</v>
       </c>
       <c r="H51" t="s">
         <v>8</v>
@@ -1721,7 +1721,7 @@
         <v>2.35800004005432</v>
       </c>
       <c r="G52" t="n">
-        <v>1.85197651386261</v>
+        <v>1.85197615623474</v>
       </c>
       <c r="H52" t="s">
         <v>8</v>
@@ -1773,7 +1773,7 @@
         <v>2.34400010108948</v>
       </c>
       <c r="G54" t="n">
-        <v>1.84098041057587</v>
+        <v>1.84098052978516</v>
       </c>
       <c r="H54" t="s">
         <v>8</v>
@@ -1851,7 +1851,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G57" t="n">
-        <v>1.85354697704315</v>
+        <v>1.85354709625244</v>
       </c>
       <c r="H57" t="s">
         <v>8</v>
@@ -1929,7 +1929,7 @@
         <v>2.30599999427795</v>
       </c>
       <c r="G60" t="n">
-        <v>1.81113541126251</v>
+        <v>1.8111355304718</v>
       </c>
       <c r="H60" t="s">
         <v>8</v>
@@ -1955,7 +1955,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G61" t="n">
-        <v>1.81427693367004</v>
+        <v>1.81427705287933</v>
       </c>
       <c r="H61" t="s">
         <v>8</v>
@@ -2007,7 +2007,7 @@
         <v>2.35599994659424</v>
       </c>
       <c r="G63" t="n">
-        <v>1.85040533542633</v>
+        <v>1.85040521621704</v>
       </c>
       <c r="H63" t="s">
         <v>8</v>
@@ -2059,7 +2059,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G65" t="n">
-        <v>1.9242330789566</v>
+        <v>1.92423319816589</v>
       </c>
       <c r="H65" t="s">
         <v>8</v>
@@ -2085,7 +2085,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G66" t="n">
-        <v>1.9242330789566</v>
+        <v>1.92423319816589</v>
       </c>
       <c r="H66" t="s">
         <v>8</v>
@@ -2111,7 +2111,7 @@
         <v>2.46600008010864</v>
       </c>
       <c r="G67" t="n">
-        <v>1.93679976463318</v>
+        <v>1.9367995262146</v>
       </c>
       <c r="H67" t="s">
         <v>8</v>
@@ -2163,7 +2163,7 @@
         <v>2.48799991607666</v>
       </c>
       <c r="G69" t="n">
-        <v>1.95407855510712</v>
+        <v>1.95407819747925</v>
       </c>
       <c r="H69" t="s">
         <v>8</v>
@@ -2215,7 +2215,7 @@
         <v>2.50200009346008</v>
       </c>
       <c r="G71" t="n">
-        <v>1.96507394313812</v>
+        <v>1.9650741815567</v>
       </c>
       <c r="H71" t="s">
         <v>8</v>
@@ -2241,7 +2241,7 @@
         <v>2.53800010681152</v>
       </c>
       <c r="G72" t="n">
-        <v>1.99334847927094</v>
+        <v>1.99334871768951</v>
       </c>
       <c r="H72" t="s">
         <v>8</v>
@@ -2267,7 +2267,7 @@
         <v>2.55200004577637</v>
       </c>
       <c r="G73" t="n">
-        <v>2.00434398651123</v>
+        <v>2.00434422492981</v>
       </c>
       <c r="H73" t="s">
         <v>8</v>
@@ -2319,7 +2319,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G75" t="n">
-        <v>1.98706519603729</v>
+        <v>1.98706543445587</v>
       </c>
       <c r="H75" t="s">
         <v>8</v>
@@ -2345,7 +2345,7 @@
         <v>2.50200009346008</v>
       </c>
       <c r="G76" t="n">
-        <v>1.96507394313812</v>
+        <v>1.9650741815567</v>
       </c>
       <c r="H76" t="s">
         <v>8</v>
@@ -2371,7 +2371,7 @@
         <v>2.55800008773804</v>
       </c>
       <c r="G77" t="n">
-        <v>2.00905656814575</v>
+        <v>2.00905632972717</v>
       </c>
       <c r="H77" t="s">
         <v>8</v>
@@ -2397,7 +2397,7 @@
         <v>2.57800006866455</v>
       </c>
       <c r="G78" t="n">
-        <v>2.02476477622986</v>
+        <v>2.02476453781128</v>
       </c>
       <c r="H78" t="s">
         <v>8</v>
@@ -2423,7 +2423,7 @@
         <v>2.45799994468689</v>
       </c>
       <c r="G79" t="n">
-        <v>1.93051636219025</v>
+        <v>1.93051624298096</v>
       </c>
       <c r="H79" t="s">
         <v>8</v>
@@ -2449,7 +2449,7 @@
         <v>2.45799994468689</v>
       </c>
       <c r="G80" t="n">
-        <v>1.93051636219025</v>
+        <v>1.93051624298096</v>
       </c>
       <c r="H80" t="s">
         <v>8</v>
@@ -2501,7 +2501,7 @@
         <v>2.49799990653992</v>
       </c>
       <c r="G82" t="n">
-        <v>1.96193218231201</v>
+        <v>1.96193242073059</v>
       </c>
       <c r="H82" t="s">
         <v>8</v>
@@ -2527,7 +2527,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G83" t="n">
-        <v>1.93994092941284</v>
+        <v>1.93994116783142</v>
       </c>
       <c r="H83" t="s">
         <v>8</v>
@@ -2553,7 +2553,7 @@
         <v>2.48799991607666</v>
       </c>
       <c r="G84" t="n">
-        <v>1.95407855510712</v>
+        <v>1.95407819747925</v>
       </c>
       <c r="H84" t="s">
         <v>8</v>
@@ -2579,7 +2579,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G85" t="n">
-        <v>1.95564913749695</v>
+        <v>1.95564925670624</v>
       </c>
       <c r="H85" t="s">
         <v>8</v>
@@ -2605,7 +2605,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G86" t="n">
-        <v>1.95564913749695</v>
+        <v>1.95564925670624</v>
       </c>
       <c r="H86" t="s">
         <v>8</v>
@@ -2631,7 +2631,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G87" t="n">
-        <v>1.93994092941284</v>
+        <v>1.93994116783142</v>
       </c>
       <c r="H87" t="s">
         <v>8</v>
@@ -2683,7 +2683,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G89" t="n">
-        <v>1.88496327400208</v>
+        <v>1.88496291637421</v>
       </c>
       <c r="H89" t="s">
         <v>8</v>
@@ -2761,7 +2761,7 @@
         <v>2.39400005340576</v>
       </c>
       <c r="G92" t="n">
-        <v>1.88025069236755</v>
+        <v>1.88025081157684</v>
       </c>
       <c r="H92" t="s">
         <v>8</v>
@@ -2787,7 +2787,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G93" t="n">
-        <v>1.87710905075073</v>
+        <v>1.87710916996002</v>
       </c>
       <c r="H93" t="s">
         <v>8</v>
@@ -2865,7 +2865,7 @@
         <v>2.29800009727478</v>
       </c>
       <c r="G96" t="n">
-        <v>1.80485224723816</v>
+        <v>1.80485212802887</v>
       </c>
       <c r="H96" t="s">
         <v>8</v>
@@ -2891,7 +2891,7 @@
         <v>2.29800009727478</v>
       </c>
       <c r="G97" t="n">
-        <v>1.80485224723816</v>
+        <v>1.80485212802887</v>
       </c>
       <c r="H97" t="s">
         <v>8</v>
@@ -2943,7 +2943,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G99" t="n">
-        <v>1.89281725883484</v>
+        <v>1.89281713962555</v>
       </c>
       <c r="H99" t="s">
         <v>8</v>
@@ -2969,7 +2969,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G100" t="n">
-        <v>1.93378698825836</v>
+        <v>1.93378722667694</v>
       </c>
       <c r="H100" t="s">
         <v>8</v>
@@ -2995,7 +2995,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G101" t="n">
-        <v>1.95017528533936</v>
+        <v>1.95017516613007</v>
       </c>
       <c r="H101" t="s">
         <v>8</v>
@@ -3021,7 +3021,7 @@
         <v>2.34599995613098</v>
       </c>
       <c r="G102" t="n">
-        <v>1.92231559753418</v>
+        <v>1.9223153591156</v>
       </c>
       <c r="H102" t="s">
         <v>8</v>
@@ -3047,7 +3047,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G103" t="n">
-        <v>1.93378698825836</v>
+        <v>1.93378722667694</v>
       </c>
       <c r="H103" t="s">
         <v>8</v>
@@ -3073,7 +3073,7 @@
         <v>2.35599994659424</v>
       </c>
       <c r="G104" t="n">
-        <v>1.93050968647003</v>
+        <v>1.93050932884216</v>
       </c>
       <c r="H104" t="s">
         <v>8</v>
@@ -3099,7 +3099,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G105" t="n">
-        <v>1.96656346321106</v>
+        <v>1.9665629863739</v>
       </c>
       <c r="H105" t="s">
         <v>8</v>
@@ -3125,7 +3125,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G106" t="n">
-        <v>1.96656346321106</v>
+        <v>1.9665629863739</v>
       </c>
       <c r="H106" t="s">
         <v>8</v>
@@ -3151,7 +3151,7 @@
         <v>2.38599991798401</v>
       </c>
       <c r="G107" t="n">
-        <v>1.95509135723114</v>
+        <v>1.95509147644043</v>
       </c>
       <c r="H107" t="s">
         <v>8</v>
@@ -3177,7 +3177,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G108" t="n">
-        <v>1.95836937427521</v>
+        <v>1.95836925506592</v>
       </c>
       <c r="H108" t="s">
         <v>8</v>
@@ -3203,7 +3203,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G109" t="n">
-        <v>1.95836937427521</v>
+        <v>1.95836925506592</v>
       </c>
       <c r="H109" t="s">
         <v>8</v>
@@ -3229,7 +3229,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G110" t="n">
-        <v>1.95017528533936</v>
+        <v>1.95017516613007</v>
       </c>
       <c r="H110" t="s">
         <v>8</v>
@@ -3255,7 +3255,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G111" t="n">
-        <v>1.95017528533936</v>
+        <v>1.95017516613007</v>
       </c>
       <c r="H111" t="s">
         <v>8</v>
@@ -3281,7 +3281,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G112" t="n">
-        <v>1.91739940643311</v>
+        <v>1.91739916801453</v>
       </c>
       <c r="H112" t="s">
         <v>8</v>
@@ -3307,7 +3307,7 @@
         <v>2.36199998855591</v>
       </c>
       <c r="G113" t="n">
-        <v>1.9354259967804</v>
+        <v>1.93542587757111</v>
       </c>
       <c r="H113" t="s">
         <v>8</v>
@@ -3333,7 +3333,7 @@
         <v>2.36199998855591</v>
       </c>
       <c r="G114" t="n">
-        <v>1.9354259967804</v>
+        <v>1.93542587757111</v>
       </c>
       <c r="H114" t="s">
         <v>8</v>
@@ -3359,7 +3359,7 @@
         <v>2.36199998855591</v>
       </c>
       <c r="G115" t="n">
-        <v>1.9354259967804</v>
+        <v>1.93542587757111</v>
       </c>
       <c r="H115" t="s">
         <v>8</v>
@@ -3385,7 +3385,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G116" t="n">
-        <v>1.94198107719421</v>
+        <v>1.9419811964035</v>
       </c>
       <c r="H116" t="s">
         <v>8</v>
@@ -3411,7 +3411,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G117" t="n">
-        <v>1.94198107719421</v>
+        <v>1.9419811964035</v>
       </c>
       <c r="H117" t="s">
         <v>8</v>
@@ -3437,7 +3437,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G118" t="n">
-        <v>1.91739940643311</v>
+        <v>1.91739916801453</v>
       </c>
       <c r="H118" t="s">
         <v>8</v>
@@ -3463,7 +3463,7 @@
         <v>2.33400011062622</v>
       </c>
       <c r="G119" t="n">
-        <v>1.91248273849487</v>
+        <v>1.91248285770416</v>
       </c>
       <c r="H119" t="s">
         <v>8</v>
@@ -3541,7 +3541,7 @@
         <v>2.33400011062622</v>
       </c>
       <c r="G122" t="n">
-        <v>1.91248273849487</v>
+        <v>1.91248285770416</v>
       </c>
       <c r="H122" t="s">
         <v>8</v>
@@ -3567,7 +3567,7 @@
         <v>2.33400011062622</v>
       </c>
       <c r="G123" t="n">
-        <v>1.91248273849487</v>
+        <v>1.91248285770416</v>
       </c>
       <c r="H123" t="s">
         <v>8</v>
@@ -3593,7 +3593,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G124" t="n">
-        <v>1.83545887470245</v>
+        <v>1.83545899391174</v>
       </c>
       <c r="H124" t="s">
         <v>8</v>
@@ -3619,7 +3619,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G125" t="n">
-        <v>1.8026829957962</v>
+        <v>1.80268287658691</v>
       </c>
       <c r="H125" t="s">
         <v>8</v>
@@ -3645,7 +3645,7 @@
         <v>2.24799990653992</v>
       </c>
       <c r="G126" t="n">
-        <v>1.84201407432556</v>
+        <v>1.84201395511627</v>
       </c>
       <c r="H126" t="s">
         <v>8</v>
@@ -3697,7 +3697,7 @@
         <v>2.24799990653992</v>
       </c>
       <c r="G128" t="n">
-        <v>1.84201407432556</v>
+        <v>1.84201395511627</v>
       </c>
       <c r="H128" t="s">
         <v>8</v>
@@ -3723,7 +3723,7 @@
         <v>2.29800009727478</v>
       </c>
       <c r="G129" t="n">
-        <v>1.88298439979553</v>
+        <v>1.88298428058624</v>
       </c>
       <c r="H129" t="s">
         <v>8</v>
@@ -3749,7 +3749,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G130" t="n">
-        <v>1.86823523044586</v>
+        <v>1.86823499202728</v>
       </c>
       <c r="H130" t="s">
         <v>8</v>
@@ -3775,7 +3775,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G131" t="n">
-        <v>1.94198107719421</v>
+        <v>1.9419811964035</v>
       </c>
       <c r="H131" t="s">
         <v>8</v>
@@ -3801,7 +3801,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G132" t="n">
-        <v>1.94198107719421</v>
+        <v>1.9419811964035</v>
       </c>
       <c r="H132" t="s">
         <v>8</v>
@@ -3827,7 +3827,7 @@
         <v>2.32800006866455</v>
       </c>
       <c r="G133" t="n">
-        <v>1.90756618976593</v>
+        <v>1.90756630897522</v>
       </c>
       <c r="H133" t="s">
         <v>8</v>
@@ -3853,7 +3853,7 @@
         <v>2.32800006866455</v>
       </c>
       <c r="G134" t="n">
-        <v>1.90756618976593</v>
+        <v>1.90756630897522</v>
       </c>
       <c r="H134" t="s">
         <v>8</v>
@@ -3879,7 +3879,7 @@
         <v>2.32800006866455</v>
       </c>
       <c r="G135" t="n">
-        <v>1.90756618976593</v>
+        <v>1.90756630897522</v>
       </c>
       <c r="H135" t="s">
         <v>8</v>
@@ -3905,7 +3905,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G136" t="n">
-        <v>1.89281702041626</v>
+        <v>1.89281713962555</v>
       </c>
       <c r="H136" t="s">
         <v>8</v>
@@ -3931,7 +3931,7 @@
         <v>2.32599997520447</v>
       </c>
       <c r="G137" t="n">
-        <v>1.90592753887177</v>
+        <v>1.90592765808105</v>
       </c>
       <c r="H137" t="s">
         <v>8</v>
@@ -3957,7 +3957,7 @@
         <v>2.32599997520447</v>
       </c>
       <c r="G138" t="n">
-        <v>1.90592753887177</v>
+        <v>1.90592765808105</v>
       </c>
       <c r="H138" t="s">
         <v>8</v>
@@ -4009,7 +4009,7 @@
         <v>2.32599997520447</v>
       </c>
       <c r="G140" t="n">
-        <v>1.90592753887177</v>
+        <v>1.90592765808105</v>
       </c>
       <c r="H140" t="s">
         <v>8</v>
@@ -4035,7 +4035,7 @@
         <v>2.32599997520447</v>
       </c>
       <c r="G141" t="n">
-        <v>1.90592753887177</v>
+        <v>1.90592765808105</v>
       </c>
       <c r="H141" t="s">
         <v>8</v>
@@ -4061,7 +4061,7 @@
         <v>2.32800006866455</v>
       </c>
       <c r="G142" t="n">
-        <v>1.90756618976593</v>
+        <v>1.90756630897522</v>
       </c>
       <c r="H142" t="s">
         <v>8</v>
@@ -4087,7 +4087,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G143" t="n">
-        <v>1.90920507907867</v>
+        <v>1.90920519828796</v>
       </c>
       <c r="H143" t="s">
         <v>8</v>
@@ -4113,7 +4113,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G144" t="n">
-        <v>1.90920507907867</v>
+        <v>1.90920519828796</v>
       </c>
       <c r="H144" t="s">
         <v>8</v>
@@ -4139,7 +4139,7 @@
         <v>2.28399991989136</v>
       </c>
       <c r="G145" t="n">
-        <v>1.8715124130249</v>
+        <v>1.87151277065277</v>
       </c>
       <c r="H145" t="s">
         <v>8</v>
@@ -4165,7 +4165,7 @@
         <v>2.31599998474121</v>
       </c>
       <c r="G146" t="n">
-        <v>1.89773333072662</v>
+        <v>1.89773368835449</v>
       </c>
       <c r="H146" t="s">
         <v>8</v>
@@ -4191,7 +4191,7 @@
         <v>2.32599997520447</v>
       </c>
       <c r="G147" t="n">
-        <v>1.90592753887177</v>
+        <v>1.90592765808105</v>
       </c>
       <c r="H147" t="s">
         <v>8</v>
@@ -4217,7 +4217,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G148" t="n">
-        <v>1.90920507907867</v>
+        <v>1.90920519828796</v>
       </c>
       <c r="H148" t="s">
         <v>8</v>
@@ -4243,7 +4243,7 @@
         <v>2.2260000705719</v>
       </c>
       <c r="G149" t="n">
-        <v>1.82398748397827</v>
+        <v>1.82398724555969</v>
       </c>
       <c r="H149" t="s">
         <v>8</v>
@@ -4295,7 +4295,7 @@
         <v>2.15599989891052</v>
       </c>
       <c r="G151" t="n">
-        <v>1.76662909984589</v>
+        <v>1.76662921905518</v>
       </c>
       <c r="H151" t="s">
         <v>8</v>
@@ -4321,7 +4321,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G152" t="n">
-        <v>1.78629493713379</v>
+        <v>1.78629505634308</v>
       </c>
       <c r="H152" t="s">
         <v>8</v>
@@ -4425,7 +4425,7 @@
         <v>2.17199993133545</v>
       </c>
       <c r="G156" t="n">
-        <v>1.77973961830139</v>
+        <v>1.77973973751068</v>
       </c>
       <c r="H156" t="s">
         <v>8</v>
@@ -4451,7 +4451,7 @@
         <v>2.17199993133545</v>
       </c>
       <c r="G157" t="n">
-        <v>1.77973961830139</v>
+        <v>1.77973973751068</v>
       </c>
       <c r="H157" t="s">
         <v>8</v>
@@ -4477,7 +4477,7 @@
         <v>2.13599991798401</v>
       </c>
       <c r="G158" t="n">
-        <v>1.75024127960205</v>
+        <v>1.75024116039276</v>
       </c>
       <c r="H158" t="s">
         <v>8</v>
@@ -4503,7 +4503,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G159" t="n">
-        <v>1.72074270248413</v>
+        <v>1.72074258327484</v>
       </c>
       <c r="H159" t="s">
         <v>8</v>
@@ -4633,7 +4633,7 @@
         <v>2.14800000190735</v>
       </c>
       <c r="G164" t="n">
-        <v>1.76007401943207</v>
+        <v>1.76007413864136</v>
       </c>
       <c r="H164" t="s">
         <v>8</v>
@@ -4659,7 +4659,7 @@
         <v>2.14800000190735</v>
       </c>
       <c r="G165" t="n">
-        <v>1.76007401943207</v>
+        <v>1.76007413864136</v>
       </c>
       <c r="H165" t="s">
         <v>8</v>
@@ -4685,7 +4685,7 @@
         <v>2.14800000190735</v>
       </c>
       <c r="G166" t="n">
-        <v>1.76007401943207</v>
+        <v>1.76007413864136</v>
       </c>
       <c r="H166" t="s">
         <v>8</v>
@@ -4711,7 +4711,7 @@
         <v>2.14800000190735</v>
       </c>
       <c r="G167" t="n">
-        <v>1.76007401943207</v>
+        <v>1.76007413864136</v>
       </c>
       <c r="H167" t="s">
         <v>8</v>
@@ -4737,7 +4737,7 @@
         <v>2.14800000190735</v>
       </c>
       <c r="G168" t="n">
-        <v>1.76007401943207</v>
+        <v>1.76007413864136</v>
       </c>
       <c r="H168" t="s">
         <v>8</v>
@@ -4763,7 +4763,7 @@
         <v>2.14800000190735</v>
       </c>
       <c r="G169" t="n">
-        <v>1.76007401943207</v>
+        <v>1.76007413864136</v>
       </c>
       <c r="H169" t="s">
         <v>8</v>
@@ -4815,7 +4815,7 @@
         <v>2.11800003051758</v>
       </c>
       <c r="G171" t="n">
-        <v>1.73549199104309</v>
+        <v>1.73549211025238</v>
       </c>
       <c r="H171" t="s">
         <v>8</v>
@@ -4841,7 +4841,7 @@
         <v>2.1159999370575</v>
       </c>
       <c r="G172" t="n">
-        <v>1.73385310173035</v>
+        <v>1.73385322093964</v>
       </c>
       <c r="H172" t="s">
         <v>8</v>
@@ -4867,7 +4867,7 @@
         <v>2.1159999370575</v>
       </c>
       <c r="G173" t="n">
-        <v>1.73385310173035</v>
+        <v>1.73385322093964</v>
       </c>
       <c r="H173" t="s">
         <v>8</v>
@@ -4893,7 +4893,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G174" t="n">
-        <v>1.71254873275757</v>
+        <v>1.71254861354828</v>
       </c>
       <c r="H174" t="s">
         <v>8</v>
@@ -4945,7 +4945,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G176" t="n">
-        <v>1.67157888412476</v>
+        <v>1.67157864570618</v>
       </c>
       <c r="H176" t="s">
         <v>8</v>
@@ -4971,7 +4971,7 @@
         <v>2.03399991989136</v>
       </c>
       <c r="G177" t="n">
-        <v>1.66666221618652</v>
+        <v>1.66666233539581</v>
       </c>
       <c r="H177" t="s">
         <v>8</v>
@@ -4997,7 +4997,7 @@
         <v>1.9650000333786</v>
       </c>
       <c r="G178" t="n">
-        <v>1.61012351512909</v>
+        <v>1.61012363433838</v>
       </c>
       <c r="H178" t="s">
         <v>8</v>
@@ -5023,7 +5023,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G179" t="n">
-        <v>1.62241470813751</v>
+        <v>1.62241458892822</v>
       </c>
       <c r="H179" t="s">
         <v>8</v>
@@ -5101,7 +5101,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G182" t="n">
-        <v>1.67157888412476</v>
+        <v>1.67157864570618</v>
       </c>
       <c r="H182" t="s">
         <v>8</v>
@@ -5127,7 +5127,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G183" t="n">
-        <v>1.67157888412476</v>
+        <v>1.67157864570618</v>
       </c>
       <c r="H183" t="s">
         <v>8</v>
@@ -5179,7 +5179,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G185" t="n">
-        <v>1.67157888412476</v>
+        <v>1.67157864570618</v>
       </c>
       <c r="H185" t="s">
         <v>8</v>
@@ -5309,7 +5309,7 @@
         <v>2</v>
       </c>
       <c r="G190" t="n">
-        <v>1.63880264759064</v>
+        <v>1.63880276679993</v>
       </c>
       <c r="H190" t="s">
         <v>8</v>
@@ -5387,7 +5387,7 @@
         <v>2.03399991989136</v>
       </c>
       <c r="G193" t="n">
-        <v>1.66666221618652</v>
+        <v>1.66666233539581</v>
       </c>
       <c r="H193" t="s">
         <v>8</v>
@@ -5439,7 +5439,7 @@
         <v>2.03600001335144</v>
       </c>
       <c r="G195" t="n">
-        <v>1.66830110549927</v>
+        <v>1.66830122470856</v>
       </c>
       <c r="H195" t="s">
         <v>8</v>
@@ -5465,7 +5465,7 @@
         <v>2.03600001335144</v>
       </c>
       <c r="G196" t="n">
-        <v>1.66830110549927</v>
+        <v>1.66830122470856</v>
       </c>
       <c r="H196" t="s">
         <v>8</v>
@@ -5491,7 +5491,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G197" t="n">
-        <v>1.65519070625305</v>
+        <v>1.65519058704376</v>
       </c>
       <c r="H197" t="s">
         <v>8</v>
@@ -5517,7 +5517,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G198" t="n">
-        <v>1.65519070625305</v>
+        <v>1.65519058704376</v>
       </c>
       <c r="H198" t="s">
         <v>8</v>
@@ -5543,7 +5543,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G199" t="n">
-        <v>1.65519070625305</v>
+        <v>1.65519058704376</v>
       </c>
       <c r="H199" t="s">
         <v>8</v>
@@ -5569,7 +5569,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G200" t="n">
-        <v>1.65519070625305</v>
+        <v>1.65519058704376</v>
       </c>
       <c r="H200" t="s">
         <v>8</v>
@@ -5595,7 +5595,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G201" t="n">
-        <v>1.65519070625305</v>
+        <v>1.65519058704376</v>
       </c>
       <c r="H201" t="s">
         <v>8</v>
@@ -5621,7 +5621,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G202" t="n">
-        <v>1.6469966173172</v>
+        <v>1.64699673652649</v>
       </c>
       <c r="H202" t="s">
         <v>8</v>
@@ -5647,7 +5647,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G203" t="n">
-        <v>1.6469966173172</v>
+        <v>1.64699673652649</v>
       </c>
       <c r="H203" t="s">
         <v>8</v>
@@ -5673,7 +5673,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G204" t="n">
-        <v>1.6469966173172</v>
+        <v>1.64699673652649</v>
       </c>
       <c r="H204" t="s">
         <v>8</v>
@@ -5699,7 +5699,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G205" t="n">
-        <v>1.6469966173172</v>
+        <v>1.64699673652649</v>
       </c>
       <c r="H205" t="s">
         <v>8</v>
@@ -5777,7 +5777,7 @@
         <v>1.9889999628067</v>
       </c>
       <c r="G208" t="n">
-        <v>1.6297892332077</v>
+        <v>1.62978911399841</v>
       </c>
       <c r="H208" t="s">
         <v>8</v>
@@ -5829,7 +5829,7 @@
         <v>1.94700002670288</v>
       </c>
       <c r="G210" t="n">
-        <v>1.59537446498871</v>
+        <v>1.59537434577942</v>
       </c>
       <c r="H210" t="s">
         <v>8</v>
@@ -5855,7 +5855,7 @@
         <v>1.92700004577637</v>
       </c>
       <c r="G211" t="n">
-        <v>1.578986287117</v>
+        <v>1.57898640632629</v>
       </c>
       <c r="H211" t="s">
         <v>8</v>
@@ -5881,7 +5881,7 @@
         <v>1.94200003147125</v>
       </c>
       <c r="G212" t="n">
-        <v>1.59127748012543</v>
+        <v>1.59127736091614</v>
       </c>
       <c r="H212" t="s">
         <v>8</v>
@@ -5907,7 +5907,7 @@
         <v>1.94200003147125</v>
       </c>
       <c r="G213" t="n">
-        <v>1.59127748012543</v>
+        <v>1.59127736091614</v>
       </c>
       <c r="H213" t="s">
         <v>8</v>
@@ -5985,7 +5985,7 @@
         <v>1.91600000858307</v>
       </c>
       <c r="G216" t="n">
-        <v>1.56997299194336</v>
+        <v>1.56997287273407</v>
       </c>
       <c r="H216" t="s">
         <v>8</v>
@@ -6037,7 +6037,7 @@
         <v>1.90199995040894</v>
       </c>
       <c r="G218" t="n">
-        <v>1.5585013628006</v>
+        <v>1.55850124359131</v>
       </c>
       <c r="H218" t="s">
         <v>8</v>
@@ -6089,7 +6089,7 @@
         <v>1.95700001716614</v>
       </c>
       <c r="G220" t="n">
-        <v>1.60356831550598</v>
+        <v>1.60356855392456</v>
       </c>
       <c r="H220" t="s">
         <v>8</v>
@@ -6219,7 +6219,7 @@
         <v>1.85399997234344</v>
       </c>
       <c r="G225" t="n">
-        <v>1.51917004585266</v>
+        <v>1.51917016506195</v>
       </c>
       <c r="H225" t="s">
         <v>8</v>
@@ -6245,7 +6245,7 @@
         <v>1.90600001811981</v>
       </c>
       <c r="G226" t="n">
-        <v>1.5617790222168</v>
+        <v>1.56177890300751</v>
       </c>
       <c r="H226" t="s">
         <v>8</v>
@@ -6297,7 +6297,7 @@
         <v>1.67999994754791</v>
       </c>
       <c r="G228" t="n">
-        <v>1.37659406661987</v>
+        <v>1.37659418582916</v>
       </c>
       <c r="H228" t="s">
         <v>8</v>
@@ -6323,7 +6323,7 @@
         <v>1.72399997711182</v>
       </c>
       <c r="G229" t="n">
-        <v>1.41264796257019</v>
+        <v>1.4126478433609</v>
       </c>
       <c r="H229" t="s">
         <v>8</v>
@@ -6349,7 +6349,7 @@
         <v>1.70200002193451</v>
       </c>
       <c r="G230" t="n">
-        <v>1.39462125301361</v>
+        <v>1.39462101459503</v>
       </c>
       <c r="H230" t="s">
         <v>8</v>
@@ -6479,7 +6479,7 @@
         <v>1.96700000762939</v>
       </c>
       <c r="G235" t="n">
-        <v>1.61176252365112</v>
+        <v>1.61176240444183</v>
       </c>
       <c r="H235" t="s">
         <v>8</v>
@@ -6583,7 +6583,7 @@
         <v>1.96700000762939</v>
       </c>
       <c r="G239" t="n">
-        <v>1.61176252365112</v>
+        <v>1.61176240444183</v>
       </c>
       <c r="H239" t="s">
         <v>8</v>
@@ -6661,7 +6661,7 @@
         <v>1.89800000190735</v>
       </c>
       <c r="G242" t="n">
-        <v>1.55522382259369</v>
+        <v>1.55522394180298</v>
       </c>
       <c r="H242" t="s">
         <v>8</v>
@@ -6687,7 +6687,7 @@
         <v>1.89800000190735</v>
       </c>
       <c r="G243" t="n">
-        <v>1.55522382259369</v>
+        <v>1.55522394180298</v>
       </c>
       <c r="H243" t="s">
         <v>8</v>
@@ -6739,7 +6739,7 @@
         <v>1.90900003910065</v>
       </c>
       <c r="G245" t="n">
-        <v>1.56423711776733</v>
+        <v>1.56423723697662</v>
       </c>
       <c r="H245" t="s">
         <v>8</v>
@@ -6791,7 +6791,7 @@
         <v>1.94400000572205</v>
       </c>
       <c r="G247" t="n">
-        <v>1.59291625022888</v>
+        <v>1.59291636943817</v>
       </c>
       <c r="H247" t="s">
         <v>8</v>
@@ -6817,7 +6817,7 @@
         <v>1.94400000572205</v>
       </c>
       <c r="G248" t="n">
-        <v>1.59291625022888</v>
+        <v>1.59291636943817</v>
       </c>
       <c r="H248" t="s">
         <v>8</v>
@@ -6843,7 +6843,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G249" t="n">
-        <v>1.55686247348785</v>
+        <v>1.55686259269714</v>
       </c>
       <c r="H249" t="s">
         <v>8</v>
@@ -6869,7 +6869,7 @@
         <v>1.85699999332428</v>
       </c>
       <c r="G250" t="n">
-        <v>1.52162837982178</v>
+        <v>1.52162826061249</v>
       </c>
       <c r="H250" t="s">
         <v>8</v>
@@ -6999,7 +6999,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G255" t="n">
-        <v>1.51589250564575</v>
+        <v>1.51589238643646</v>
       </c>
       <c r="H255" t="s">
         <v>8</v>
@@ -7077,7 +7077,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G258" t="n">
-        <v>1.53228044509888</v>
+        <v>1.53228056430817</v>
       </c>
       <c r="H258" t="s">
         <v>8</v>
@@ -7103,7 +7103,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G259" t="n">
-        <v>1.53228044509888</v>
+        <v>1.53228056430817</v>
       </c>
       <c r="H259" t="s">
         <v>8</v>
@@ -7129,7 +7129,7 @@
         <v>1.84200000762939</v>
       </c>
       <c r="G260" t="n">
-        <v>1.50933718681335</v>
+        <v>1.50933742523193</v>
       </c>
       <c r="H260" t="s">
         <v>8</v>
@@ -7207,7 +7207,7 @@
         <v>1.84200000762939</v>
       </c>
       <c r="G263" t="n">
-        <v>1.50933718681335</v>
+        <v>1.50933742523193</v>
       </c>
       <c r="H263" t="s">
         <v>8</v>
@@ -7259,7 +7259,7 @@
         <v>1.83399999141693</v>
       </c>
       <c r="G265" t="n">
-        <v>1.50278210639954</v>
+        <v>1.50278198719025</v>
       </c>
       <c r="H265" t="s">
         <v>8</v>
@@ -7285,7 +7285,7 @@
         <v>1.82500004768372</v>
       </c>
       <c r="G266" t="n">
-        <v>1.49540758132935</v>
+        <v>1.49540746212006</v>
       </c>
       <c r="H266" t="s">
         <v>8</v>
@@ -7415,7 +7415,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G271" t="n">
-        <v>1.55686247348785</v>
+        <v>1.55686259269714</v>
       </c>
       <c r="H271" t="s">
         <v>8</v>
@@ -7441,7 +7441,7 @@
         <v>1.94599997997284</v>
       </c>
       <c r="G272" t="n">
-        <v>1.59455490112305</v>
+        <v>1.59455513954163</v>
       </c>
       <c r="H272" t="s">
         <v>8</v>
@@ -7493,7 +7493,7 @@
         <v>1.95700001716614</v>
       </c>
       <c r="G274" t="n">
-        <v>1.60356831550598</v>
+        <v>1.60356855392456</v>
       </c>
       <c r="H274" t="s">
         <v>8</v>
@@ -7545,7 +7545,7 @@
         <v>1.97899997234344</v>
       </c>
       <c r="G276" t="n">
-        <v>1.62159538269043</v>
+        <v>1.62159526348114</v>
       </c>
       <c r="H276" t="s">
         <v>8</v>
@@ -7597,7 +7597,7 @@
         <v>1.88399994373322</v>
       </c>
       <c r="G278" t="n">
-        <v>1.54375195503235</v>
+        <v>1.54375207424164</v>
       </c>
       <c r="H278" t="s">
         <v>8</v>
@@ -7623,7 +7623,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G279" t="n">
-        <v>1.53228044509888</v>
+        <v>1.53228056430817</v>
       </c>
       <c r="H279" t="s">
         <v>8</v>
@@ -7649,7 +7649,7 @@
         <v>1.9190000295639</v>
       </c>
       <c r="G280" t="n">
-        <v>1.57243120670319</v>
+        <v>1.57243132591248</v>
       </c>
       <c r="H280" t="s">
         <v>8</v>
@@ -7675,7 +7675,7 @@
         <v>1.93700003623962</v>
       </c>
       <c r="G281" t="n">
-        <v>1.58718049526215</v>
+        <v>1.58718025684357</v>
       </c>
       <c r="H281" t="s">
         <v>8</v>
@@ -7753,7 +7753,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G284" t="n">
-        <v>1.55686247348785</v>
+        <v>1.55686259269714</v>
       </c>
       <c r="H284" t="s">
         <v>8</v>
@@ -7779,7 +7779,7 @@
         <v>1.93799996376038</v>
       </c>
       <c r="G285" t="n">
-        <v>1.58799970149994</v>
+        <v>1.58799982070923</v>
       </c>
       <c r="H285" t="s">
         <v>8</v>
@@ -7831,7 +7831,7 @@
         <v>1.93099999427795</v>
       </c>
       <c r="G287" t="n">
-        <v>1.5822639465332</v>
+        <v>1.58226406574249</v>
       </c>
       <c r="H287" t="s">
         <v>8</v>
@@ -7961,7 +7961,7 @@
         <v>1.87800002098083</v>
       </c>
       <c r="G292" t="n">
-        <v>1.53883588314056</v>
+        <v>1.53883576393127</v>
       </c>
       <c r="H292" t="s">
         <v>8</v>
@@ -8091,7 +8091,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G297" t="n">
-        <v>1.55686247348785</v>
+        <v>1.55686259269714</v>
       </c>
       <c r="H297" t="s">
         <v>8</v>
@@ -8117,7 +8117,7 @@
         <v>1.89499998092651</v>
       </c>
       <c r="G298" t="n">
-        <v>1.55276560783386</v>
+        <v>1.55276548862457</v>
       </c>
       <c r="H298" t="s">
         <v>8</v>
@@ -8143,7 +8143,7 @@
         <v>1.89100003242493</v>
       </c>
       <c r="G299" t="n">
-        <v>1.54948806762695</v>
+        <v>1.54948782920837</v>
       </c>
       <c r="H299" t="s">
         <v>8</v>
@@ -8195,7 +8195,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G301" t="n">
-        <v>1.53228044509888</v>
+        <v>1.53228056430817</v>
       </c>
       <c r="H301" t="s">
         <v>8</v>
@@ -8247,7 +8247,7 @@
         <v>1.89100003242493</v>
       </c>
       <c r="G303" t="n">
-        <v>1.54948806762695</v>
+        <v>1.54948782920837</v>
       </c>
       <c r="H303" t="s">
         <v>8</v>
@@ -8273,7 +8273,7 @@
         <v>1.875</v>
       </c>
       <c r="G304" t="n">
-        <v>1.53637754917145</v>
+        <v>1.53637742996216</v>
       </c>
       <c r="H304" t="s">
         <v>8</v>
@@ -8403,7 +8403,7 @@
         <v>2</v>
       </c>
       <c r="G309" t="n">
-        <v>1.63880264759064</v>
+        <v>1.63880276679993</v>
       </c>
       <c r="H309" t="s">
         <v>8</v>
@@ -8455,7 +8455,7 @@
         <v>2.01600003242493</v>
       </c>
       <c r="G311" t="n">
-        <v>1.65191316604614</v>
+        <v>1.65191304683685</v>
       </c>
       <c r="H311" t="s">
         <v>8</v>
@@ -8481,7 +8481,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G312" t="n">
-        <v>1.6469966173172</v>
+        <v>1.64699673652649</v>
       </c>
       <c r="H312" t="s">
         <v>8</v>
@@ -8559,7 +8559,7 @@
         <v>2.01799988746643</v>
       </c>
       <c r="G315" t="n">
-        <v>1.65355181694031</v>
+        <v>1.65355169773102</v>
       </c>
       <c r="H315" t="s">
         <v>8</v>
@@ -8585,7 +8585,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G316" t="n">
-        <v>1.65519070625305</v>
+        <v>1.65519058704376</v>
       </c>
       <c r="H316" t="s">
         <v>8</v>
@@ -8637,7 +8637,7 @@
         <v>2.29800009727478</v>
       </c>
       <c r="G318" t="n">
-        <v>1.88298439979553</v>
+        <v>1.88298428058624</v>
       </c>
       <c r="H318" t="s">
         <v>8</v>
@@ -8663,7 +8663,7 @@
         <v>2.22199988365173</v>
       </c>
       <c r="G319" t="n">
-        <v>1.8207094669342</v>
+        <v>1.82070970535278</v>
       </c>
       <c r="H319" t="s">
         <v>8</v>
@@ -8689,7 +8689,7 @@
         <v>2.23200011253357</v>
       </c>
       <c r="G320" t="n">
-        <v>1.82890391349792</v>
+        <v>1.82890403270721</v>
       </c>
       <c r="H320" t="s">
         <v>8</v>
@@ -8715,7 +8715,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G321" t="n">
-        <v>1.78629493713379</v>
+        <v>1.78629505634308</v>
       </c>
       <c r="H321" t="s">
         <v>8</v>
@@ -8793,7 +8793,7 @@
         <v>2.17199993133545</v>
       </c>
       <c r="G324" t="n">
-        <v>1.77973961830139</v>
+        <v>1.77973973751068</v>
       </c>
       <c r="H324" t="s">
         <v>8</v>
@@ -8819,7 +8819,7 @@
         <v>2.29399991035461</v>
       </c>
       <c r="G325" t="n">
-        <v>1.87970662117004</v>
+        <v>1.87970650196075</v>
       </c>
       <c r="H325" t="s">
         <v>8</v>
@@ -8845,7 +8845,7 @@
         <v>2.24799990653992</v>
       </c>
       <c r="G326" t="n">
-        <v>1.84201407432556</v>
+        <v>1.84201395511627</v>
       </c>
       <c r="H326" t="s">
         <v>8</v>
@@ -8897,7 +8897,7 @@
         <v>2.19799995422363</v>
       </c>
       <c r="G328" t="n">
-        <v>1.80104422569275</v>
+        <v>1.80104398727417</v>
       </c>
       <c r="H328" t="s">
         <v>8</v>
@@ -8923,7 +8923,7 @@
         <v>2.2260000705719</v>
       </c>
       <c r="G329" t="n">
-        <v>1.82398748397827</v>
+        <v>1.82398724555969</v>
       </c>
       <c r="H329" t="s">
         <v>8</v>
@@ -8975,7 +8975,7 @@
         <v>2.19799995422363</v>
       </c>
       <c r="G331" t="n">
-        <v>1.80104422569275</v>
+        <v>1.80104398727417</v>
       </c>
       <c r="H331" t="s">
         <v>8</v>
@@ -9027,7 +9027,7 @@
         <v>2.10800004005432</v>
       </c>
       <c r="G333" t="n">
-        <v>1.72729802131653</v>
+        <v>1.72729814052582</v>
       </c>
       <c r="H333" t="s">
         <v>8</v>
@@ -9105,7 +9105,7 @@
         <v>2.15199995040894</v>
       </c>
       <c r="G336" t="n">
-        <v>1.76335167884827</v>
+        <v>1.76335155963898</v>
       </c>
       <c r="H336" t="s">
         <v>8</v>
@@ -9131,7 +9131,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G337" t="n">
-        <v>1.8026829957962</v>
+        <v>1.80268287658691</v>
       </c>
       <c r="H337" t="s">
         <v>8</v>
@@ -9157,7 +9157,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G338" t="n">
-        <v>1.8026829957962</v>
+        <v>1.80268287658691</v>
       </c>
       <c r="H338" t="s">
         <v>8</v>
@@ -9183,7 +9183,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G339" t="n">
-        <v>1.83545887470245</v>
+        <v>1.83545899391174</v>
       </c>
       <c r="H339" t="s">
         <v>8</v>
@@ -9209,7 +9209,7 @@
         <v>2.25399994850159</v>
       </c>
       <c r="G340" t="n">
-        <v>1.8469306230545</v>
+        <v>1.84693038463593</v>
       </c>
       <c r="H340" t="s">
         <v>8</v>
@@ -9235,7 +9235,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G341" t="n">
-        <v>1.81087696552277</v>
+        <v>1.81087708473206</v>
       </c>
       <c r="H341" t="s">
         <v>8</v>
@@ -9261,7 +9261,7 @@
         <v>2.20799994468689</v>
       </c>
       <c r="G342" t="n">
-        <v>1.80923807621002</v>
+        <v>1.8092383146286</v>
       </c>
       <c r="H342" t="s">
         <v>8</v>
@@ -9287,7 +9287,7 @@
         <v>2.21199989318848</v>
       </c>
       <c r="G343" t="n">
-        <v>1.81251573562622</v>
+        <v>1.81251561641693</v>
       </c>
       <c r="H343" t="s">
         <v>8</v>
@@ -9313,7 +9313,7 @@
         <v>2.2720000743866</v>
       </c>
       <c r="G344" t="n">
-        <v>1.86168003082275</v>
+        <v>1.86167991161346</v>
       </c>
       <c r="H344" t="s">
         <v>8</v>
@@ -9339,7 +9339,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G345" t="n">
-        <v>1.83545887470245</v>
+        <v>1.83545899391174</v>
       </c>
       <c r="H345" t="s">
         <v>8</v>
@@ -9417,7 +9417,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G348" t="n">
-        <v>1.87642884254456</v>
+        <v>1.87642896175385</v>
       </c>
       <c r="H348" t="s">
         <v>8</v>
@@ -9495,7 +9495,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G351" t="n">
-        <v>1.91739940643311</v>
+        <v>1.91739916801453</v>
       </c>
       <c r="H351" t="s">
         <v>8</v>
@@ -9521,7 +9521,7 @@
         <v>2.25600004196167</v>
       </c>
       <c r="G352" t="n">
-        <v>1.84856951236725</v>
+        <v>1.84856963157654</v>
       </c>
       <c r="H352" t="s">
         <v>8</v>
@@ -9573,7 +9573,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G354" t="n">
-        <v>1.86823523044586</v>
+        <v>1.86823499202728</v>
       </c>
       <c r="H354" t="s">
         <v>8</v>
@@ -9625,7 +9625,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G356" t="n">
-        <v>1.93679392337799</v>
+        <v>1.93679416179657</v>
       </c>
       <c r="H356" t="s">
         <v>8</v>
@@ -9677,7 +9677,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G358" t="n">
-        <v>1.97107362747192</v>
+        <v>1.97107374668121</v>
       </c>
       <c r="H358" t="s">
         <v>8</v>
@@ -9703,7 +9703,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G359" t="n">
-        <v>1.97107362747192</v>
+        <v>1.97107374668121</v>
       </c>
       <c r="H359" t="s">
         <v>8</v>
@@ -9729,7 +9729,7 @@
         <v>2.25</v>
       </c>
       <c r="G360" t="n">
-        <v>1.92822456359863</v>
+        <v>1.92822432518005</v>
       </c>
       <c r="H360" t="s">
         <v>8</v>
@@ -9755,7 +9755,7 @@
         <v>2.26600003242493</v>
       </c>
       <c r="G361" t="n">
-        <v>1.94193637371063</v>
+        <v>1.94193625450134</v>
       </c>
       <c r="H361" t="s">
         <v>8</v>
@@ -9781,7 +9781,7 @@
         <v>2.26799988746643</v>
       </c>
       <c r="G362" t="n">
-        <v>1.94364988803864</v>
+        <v>1.94365000724792</v>
       </c>
       <c r="H362" t="s">
         <v>8</v>
@@ -9885,7 +9885,7 @@
         <v>2.25</v>
       </c>
       <c r="G366" t="n">
-        <v>1.92822456359863</v>
+        <v>1.92822432518005</v>
       </c>
       <c r="H366" t="s">
         <v>8</v>
@@ -9911,7 +9911,7 @@
         <v>2.24799990653992</v>
       </c>
       <c r="G367" t="n">
-        <v>1.9265102148056</v>
+        <v>1.92651033401489</v>
       </c>
       <c r="H367" t="s">
         <v>8</v>
@@ -9937,7 +9937,7 @@
         <v>2.24799990653992</v>
       </c>
       <c r="G368" t="n">
-        <v>1.9265102148056</v>
+        <v>1.92651033401489</v>
       </c>
       <c r="H368" t="s">
         <v>8</v>
@@ -9963,7 +9963,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G369" t="n">
-        <v>1.95393395423889</v>
+        <v>1.95393407344818</v>
       </c>
       <c r="H369" t="s">
         <v>8</v>
@@ -9989,7 +9989,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G370" t="n">
-        <v>1.95393395423889</v>
+        <v>1.95393407344818</v>
       </c>
       <c r="H370" t="s">
         <v>8</v>
@@ -10015,7 +10015,7 @@
         <v>2.25600004196167</v>
       </c>
       <c r="G371" t="n">
-        <v>1.93336629867554</v>
+        <v>1.93336641788483</v>
       </c>
       <c r="H371" t="s">
         <v>8</v>
@@ -10041,7 +10041,7 @@
         <v>2.22399997711182</v>
       </c>
       <c r="G372" t="n">
-        <v>1.90594255924225</v>
+        <v>1.90594244003296</v>
       </c>
       <c r="H372" t="s">
         <v>8</v>
@@ -10067,7 +10067,7 @@
         <v>2.22399997711182</v>
       </c>
       <c r="G373" t="n">
-        <v>1.90594255924225</v>
+        <v>1.90594244003296</v>
       </c>
       <c r="H373" t="s">
         <v>8</v>
@@ -10093,7 +10093,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G374" t="n">
-        <v>1.89394462108612</v>
+        <v>1.8939448595047</v>
       </c>
       <c r="H374" t="s">
         <v>8</v>
@@ -10119,7 +10119,7 @@
         <v>2.18400001525879</v>
       </c>
       <c r="G375" t="n">
-        <v>1.87166309356689</v>
+        <v>1.8716629743576</v>
       </c>
       <c r="H375" t="s">
         <v>8</v>
@@ -10145,7 +10145,7 @@
         <v>2.25200009346008</v>
       </c>
       <c r="G376" t="n">
-        <v>1.92993807792664</v>
+        <v>1.92993831634521</v>
       </c>
       <c r="H376" t="s">
         <v>8</v>
@@ -10171,7 +10171,7 @@
         <v>2.21799993515015</v>
       </c>
       <c r="G377" t="n">
-        <v>1.90080046653748</v>
+        <v>1.90080070495605</v>
       </c>
       <c r="H377" t="s">
         <v>8</v>
@@ -10197,7 +10197,7 @@
         <v>2.23399996757507</v>
       </c>
       <c r="G378" t="n">
-        <v>1.91451263427734</v>
+        <v>1.91451251506805</v>
       </c>
       <c r="H378" t="s">
         <v>8</v>
@@ -10223,7 +10223,7 @@
         <v>2.20199990272522</v>
       </c>
       <c r="G379" t="n">
-        <v>1.88708865642548</v>
+        <v>1.88708877563477</v>
       </c>
       <c r="H379" t="s">
         <v>8</v>
@@ -10301,7 +10301,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G382" t="n">
-        <v>1.88537490367889</v>
+        <v>1.8853747844696</v>
       </c>
       <c r="H382" t="s">
         <v>8</v>
@@ -10405,7 +10405,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G386" t="n">
-        <v>1.90251469612122</v>
+        <v>1.90251457691193</v>
       </c>
       <c r="H386" t="s">
         <v>8</v>
@@ -10431,7 +10431,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G387" t="n">
-        <v>1.89394462108612</v>
+        <v>1.8939448595047</v>
       </c>
       <c r="H387" t="s">
         <v>8</v>
@@ -10457,7 +10457,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G388" t="n">
-        <v>1.89394462108612</v>
+        <v>1.8939448595047</v>
       </c>
       <c r="H388" t="s">
         <v>8</v>
@@ -10483,7 +10483,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G389" t="n">
-        <v>1.89394462108612</v>
+        <v>1.8939448595047</v>
       </c>
       <c r="H389" t="s">
         <v>8</v>
@@ -10509,7 +10509,7 @@
         <v>2.23399996757507</v>
       </c>
       <c r="G390" t="n">
-        <v>1.91451263427734</v>
+        <v>1.91451251506805</v>
       </c>
       <c r="H390" t="s">
         <v>8</v>
@@ -10561,7 +10561,7 @@
         <v>2.25600004196167</v>
       </c>
       <c r="G392" t="n">
-        <v>1.93336629867554</v>
+        <v>1.93336641788483</v>
       </c>
       <c r="H392" t="s">
         <v>8</v>
@@ -10613,7 +10613,7 @@
         <v>2.29200005531311</v>
       </c>
       <c r="G394" t="n">
-        <v>1.96421778202057</v>
+        <v>1.96421790122986</v>
       </c>
       <c r="H394" t="s">
         <v>8</v>
@@ -10639,7 +10639,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G395" t="n">
-        <v>1.96250379085541</v>
+        <v>1.96250355243683</v>
       </c>
       <c r="H395" t="s">
         <v>8</v>
@@ -10665,7 +10665,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G396" t="n">
-        <v>1.97107362747192</v>
+        <v>1.97107374668121</v>
       </c>
       <c r="H396" t="s">
         <v>8</v>
@@ -10691,7 +10691,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G397" t="n">
-        <v>1.98821341991425</v>
+        <v>1.98821353912354</v>
       </c>
       <c r="H397" t="s">
         <v>8</v>
@@ -10717,7 +10717,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G398" t="n">
-        <v>1.98821341991425</v>
+        <v>1.98821353912354</v>
       </c>
       <c r="H398" t="s">
         <v>8</v>
@@ -10821,7 +10821,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G402" t="n">
-        <v>2.12533140182495</v>
+        <v>2.12533164024353</v>
       </c>
       <c r="H402" t="s">
         <v>8</v>
@@ -10873,7 +10873,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G404" t="n">
-        <v>2.05677270889282</v>
+        <v>2.0567729473114</v>
       </c>
       <c r="H404" t="s">
         <v>8</v>
@@ -10899,7 +10899,7 @@
         <v>2.42600011825562</v>
       </c>
       <c r="G405" t="n">
-        <v>2.07905459403992</v>
+        <v>2.07905435562134</v>
       </c>
       <c r="H405" t="s">
         <v>8</v>
@@ -10925,7 +10925,7 @@
         <v>2.42799997329712</v>
       </c>
       <c r="G406" t="n">
-        <v>2.08076810836792</v>
+        <v>2.0807683467865</v>
       </c>
       <c r="H406" t="s">
         <v>8</v>
@@ -11029,7 +11029,7 @@
         <v>2.41799998283386</v>
       </c>
       <c r="G410" t="n">
-        <v>2.07219862937927</v>
+        <v>2.07219839096069</v>
       </c>
       <c r="H410" t="s">
         <v>8</v>
@@ -11055,7 +11055,7 @@
         <v>2.41799998283386</v>
       </c>
       <c r="G411" t="n">
-        <v>2.07219862937927</v>
+        <v>2.07219839096069</v>
       </c>
       <c r="H411" t="s">
         <v>8</v>
@@ -11081,7 +11081,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G412" t="n">
-        <v>2.12533140182495</v>
+        <v>2.12533164024353</v>
       </c>
       <c r="H412" t="s">
         <v>8</v>
@@ -11133,7 +11133,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G414" t="n">
-        <v>2.10819220542908</v>
+        <v>2.10819172859192</v>
       </c>
       <c r="H414" t="s">
         <v>8</v>
@@ -11159,7 +11159,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G415" t="n">
-        <v>2.09962201118469</v>
+        <v>2.09962177276611</v>
       </c>
       <c r="H415" t="s">
         <v>8</v>
@@ -11263,7 +11263,7 @@
         <v>2.46799993515015</v>
       </c>
       <c r="G419" t="n">
-        <v>2.11504793167114</v>
+        <v>2.11504769325256</v>
       </c>
       <c r="H419" t="s">
         <v>8</v>
@@ -11289,7 +11289,7 @@
         <v>2.46799993515015</v>
       </c>
       <c r="G420" t="n">
-        <v>2.11504793167114</v>
+        <v>2.11504769325256</v>
       </c>
       <c r="H420" t="s">
         <v>8</v>
@@ -11367,7 +11367,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G423" t="n">
-        <v>2.11676168441772</v>
+        <v>2.1167619228363</v>
       </c>
       <c r="H423" t="s">
         <v>8</v>
@@ -11419,7 +11419,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G425" t="n">
-        <v>2.09962201118469</v>
+        <v>2.09962177276611</v>
       </c>
       <c r="H425" t="s">
         <v>8</v>
@@ -11471,7 +11471,7 @@
         <v>2.46799993515015</v>
       </c>
       <c r="G427" t="n">
-        <v>2.11504793167114</v>
+        <v>2.11504769325256</v>
       </c>
       <c r="H427" t="s">
         <v>8</v>
@@ -11601,7 +11601,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G432" t="n">
-        <v>2.10819220542908</v>
+        <v>2.10819172859192</v>
       </c>
       <c r="H432" t="s">
         <v>8</v>
@@ -11627,7 +11627,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G433" t="n">
-        <v>2.09962201118469</v>
+        <v>2.09962177276611</v>
       </c>
       <c r="H433" t="s">
         <v>8</v>
@@ -11887,7 +11887,7 @@
         <v>2.48600006103516</v>
       </c>
       <c r="G443" t="n">
-        <v>2.13047361373901</v>
+        <v>2.13047385215759</v>
       </c>
       <c r="H443" t="s">
         <v>8</v>
@@ -11991,7 +11991,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G447" t="n">
-        <v>2.11676168441772</v>
+        <v>2.1167619228363</v>
       </c>
       <c r="H447" t="s">
         <v>8</v>
@@ -12043,7 +12043,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G449" t="n">
-        <v>2.09962201118469</v>
+        <v>2.09962177276611</v>
       </c>
       <c r="H449" t="s">
         <v>8</v>
@@ -12069,7 +12069,7 @@
         <v>2.4779999256134</v>
       </c>
       <c r="G450" t="n">
-        <v>2.12361741065979</v>
+        <v>2.12361764907837</v>
       </c>
       <c r="H450" t="s">
         <v>8</v>
@@ -12147,7 +12147,7 @@
         <v>2.46799993515015</v>
       </c>
       <c r="G453" t="n">
-        <v>2.11504793167114</v>
+        <v>2.11504769325256</v>
       </c>
       <c r="H453" t="s">
         <v>8</v>
@@ -12225,7 +12225,7 @@
         <v>2.4779999256134</v>
       </c>
       <c r="G456" t="n">
-        <v>2.12361741065979</v>
+        <v>2.12361764907837</v>
       </c>
       <c r="H456" t="s">
         <v>8</v>
@@ -12329,7 +12329,7 @@
         <v>2.51600003242493</v>
       </c>
       <c r="G460" t="n">
-        <v>2.15618348121643</v>
+        <v>2.15618324279785</v>
       </c>
       <c r="H460" t="s">
         <v>8</v>
@@ -12459,7 +12459,7 @@
         <v>2.50799989700317</v>
       </c>
       <c r="G465" t="n">
-        <v>2.14932751655579</v>
+        <v>2.14932703971863</v>
       </c>
       <c r="H465" t="s">
         <v>8</v>
@@ -12537,7 +12537,7 @@
         <v>2.51600003242493</v>
       </c>
       <c r="G468" t="n">
-        <v>2.15618348121643</v>
+        <v>2.15618324279785</v>
       </c>
       <c r="H468" t="s">
         <v>8</v>
@@ -12641,7 +12641,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G472" t="n">
-        <v>2.12533140182495</v>
+        <v>2.12533164024353</v>
       </c>
       <c r="H472" t="s">
         <v>8</v>
@@ -12771,7 +12771,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G477" t="n">
-        <v>2.09962201118469</v>
+        <v>2.09962177276611</v>
       </c>
       <c r="H477" t="s">
         <v>8</v>
@@ -12849,7 +12849,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G480" t="n">
-        <v>2.05677270889282</v>
+        <v>2.0567729473114</v>
       </c>
       <c r="H480" t="s">
         <v>8</v>
@@ -12927,7 +12927,7 @@
         <v>2.42600011825562</v>
       </c>
       <c r="G483" t="n">
-        <v>2.07905459403992</v>
+        <v>2.07905435562134</v>
       </c>
       <c r="H483" t="s">
         <v>8</v>
@@ -13161,7 +13161,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G492" t="n">
-        <v>2.12533140182495</v>
+        <v>2.12533164024353</v>
       </c>
       <c r="H492" t="s">
         <v>8</v>
@@ -13213,7 +13213,7 @@
         <v>2.48399996757507</v>
       </c>
       <c r="G494" t="n">
-        <v>2.12875986099243</v>
+        <v>2.12875938415527</v>
       </c>
       <c r="H494" t="s">
         <v>8</v>
@@ -13239,7 +13239,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G495" t="n">
-        <v>2.12533140182495</v>
+        <v>2.12533164024353</v>
       </c>
       <c r="H495" t="s">
         <v>8</v>
@@ -13265,7 +13265,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G496" t="n">
-        <v>2.11676168441772</v>
+        <v>2.1167619228363</v>
       </c>
       <c r="H496" t="s">
         <v>8</v>
@@ -13291,7 +13291,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G497" t="n">
-        <v>2.11676168441772</v>
+        <v>2.1167619228363</v>
       </c>
       <c r="H497" t="s">
         <v>8</v>
@@ -13317,7 +13317,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G498" t="n">
-        <v>2.11676168441772</v>
+        <v>2.1167619228363</v>
       </c>
       <c r="H498" t="s">
         <v>8</v>
@@ -13343,7 +13343,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G499" t="n">
-        <v>2.11676168441772</v>
+        <v>2.1167619228363</v>
       </c>
       <c r="H499" t="s">
         <v>8</v>
@@ -13395,7 +13395,7 @@
         <v>2.43600010871887</v>
       </c>
       <c r="G501" t="n">
-        <v>2.08762431144714</v>
+        <v>2.08762407302856</v>
       </c>
       <c r="H501" t="s">
         <v>8</v>
@@ -13447,7 +13447,7 @@
         <v>2.35800004005432</v>
       </c>
       <c r="G503" t="n">
-        <v>2.02077913284302</v>
+        <v>2.0207793712616</v>
       </c>
       <c r="H503" t="s">
         <v>8</v>
@@ -13551,7 +13551,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G507" t="n">
-        <v>2.09962201118469</v>
+        <v>2.09962177276611</v>
       </c>
       <c r="H507" t="s">
         <v>8</v>
@@ -13629,7 +13629,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G510" t="n">
-        <v>2.09962201118469</v>
+        <v>2.09962177276611</v>
       </c>
       <c r="H510" t="s">
         <v>8</v>
@@ -13707,7 +13707,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G513" t="n">
-        <v>2.09962201118469</v>
+        <v>2.09962177276611</v>
       </c>
       <c r="H513" t="s">
         <v>8</v>
@@ -13759,7 +13759,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G515" t="n">
-        <v>2.05677270889282</v>
+        <v>2.0567729473114</v>
       </c>
       <c r="H515" t="s">
         <v>8</v>
@@ -14019,7 +14019,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G525" t="n">
-        <v>2.05677270889282</v>
+        <v>2.0567729473114</v>
       </c>
       <c r="H525" t="s">
         <v>8</v>
@@ -14045,7 +14045,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G526" t="n">
-        <v>2.05677270889282</v>
+        <v>2.0567729473114</v>
       </c>
       <c r="H526" t="s">
         <v>8</v>
@@ -14071,7 +14071,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G527" t="n">
-        <v>2.0224928855896</v>
+        <v>2.02249264717102</v>
       </c>
       <c r="H527" t="s">
         <v>8</v>
@@ -14097,7 +14097,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G528" t="n">
-        <v>2.0224928855896</v>
+        <v>2.02249264717102</v>
       </c>
       <c r="H528" t="s">
         <v>8</v>
@@ -14123,7 +14123,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G529" t="n">
-        <v>2.0224928855896</v>
+        <v>2.02249264717102</v>
       </c>
       <c r="H529" t="s">
         <v>8</v>
@@ -14149,7 +14149,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G530" t="n">
-        <v>2.09962201118469</v>
+        <v>2.09962177276611</v>
       </c>
       <c r="H530" t="s">
         <v>8</v>
@@ -14253,7 +14253,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G534" t="n">
-        <v>2.05677270889282</v>
+        <v>2.0567729473114</v>
       </c>
       <c r="H534" t="s">
         <v>8</v>
@@ -14279,7 +14279,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G535" t="n">
-        <v>2.05677270889282</v>
+        <v>2.0567729473114</v>
       </c>
       <c r="H535" t="s">
         <v>8</v>
@@ -14409,7 +14409,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G540" t="n">
-        <v>2.05677270889282</v>
+        <v>2.0567729473114</v>
       </c>
       <c r="H540" t="s">
         <v>8</v>
@@ -14487,7 +14487,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G543" t="n">
-        <v>2.09962201118469</v>
+        <v>2.09962177276611</v>
       </c>
       <c r="H543" t="s">
         <v>8</v>
@@ -14513,7 +14513,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G544" t="n">
-        <v>2.09962201118469</v>
+        <v>2.09962177276611</v>
       </c>
       <c r="H544" t="s">
         <v>8</v>
@@ -14539,7 +14539,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G545" t="n">
-        <v>2.09962201118469</v>
+        <v>2.09962177276611</v>
       </c>
       <c r="H545" t="s">
         <v>8</v>
@@ -14565,7 +14565,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G546" t="n">
-        <v>2.0224928855896</v>
+        <v>2.02249264717102</v>
       </c>
       <c r="H546" t="s">
         <v>8</v>
@@ -14851,7 +14851,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G557" t="n">
-        <v>2.11676168441772</v>
+        <v>2.1167619228363</v>
       </c>
       <c r="H557" t="s">
         <v>8</v>
@@ -14877,7 +14877,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G558" t="n">
-        <v>2.10819220542908</v>
+        <v>2.10819172859192</v>
       </c>
       <c r="H558" t="s">
         <v>8</v>
@@ -15033,7 +15033,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G564" t="n">
-        <v>2.10819220542908</v>
+        <v>2.10819172859192</v>
       </c>
       <c r="H564" t="s">
         <v>8</v>
@@ -15085,7 +15085,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G566" t="n">
-        <v>2.12533140182495</v>
+        <v>2.12533164024353</v>
       </c>
       <c r="H566" t="s">
         <v>8</v>
@@ -15111,7 +15111,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G567" t="n">
-        <v>2.10819220542908</v>
+        <v>2.10819172859192</v>
       </c>
       <c r="H567" t="s">
         <v>8</v>
@@ -15137,7 +15137,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G568" t="n">
-        <v>2.10819220542908</v>
+        <v>2.10819172859192</v>
       </c>
       <c r="H568" t="s">
         <v>8</v>
@@ -15189,7 +15189,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G570" t="n">
-        <v>2.09962201118469</v>
+        <v>2.09962177276611</v>
       </c>
       <c r="H570" t="s">
         <v>8</v>
@@ -15215,7 +15215,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G571" t="n">
-        <v>2.10819220542908</v>
+        <v>2.10819172859192</v>
       </c>
       <c r="H571" t="s">
         <v>8</v>
@@ -15293,7 +15293,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G574" t="n">
-        <v>2.09962201118469</v>
+        <v>2.09962177276611</v>
       </c>
       <c r="H574" t="s">
         <v>8</v>
@@ -15319,7 +15319,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G575" t="n">
-        <v>2.10819220542908</v>
+        <v>2.10819172859192</v>
       </c>
       <c r="H575" t="s">
         <v>8</v>
@@ -15345,7 +15345,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G576" t="n">
-        <v>2.09962201118469</v>
+        <v>2.09962177276611</v>
       </c>
       <c r="H576" t="s">
         <v>8</v>
@@ -15501,7 +15501,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G582" t="n">
-        <v>2.1681809425354</v>
+        <v>2.16818118095398</v>
       </c>
       <c r="H582" t="s">
         <v>8</v>
@@ -15527,7 +15527,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G583" t="n">
-        <v>2.1681809425354</v>
+        <v>2.16818118095398</v>
       </c>
       <c r="H583" t="s">
         <v>8</v>
@@ -15605,7 +15605,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G586" t="n">
-        <v>2.1681809425354</v>
+        <v>2.16818118095398</v>
       </c>
       <c r="H586" t="s">
         <v>8</v>
@@ -15865,7 +15865,7 @@
         <v>2.75</v>
       </c>
       <c r="G596" t="n">
-        <v>2.35671854019165</v>
+        <v>2.35671830177307</v>
       </c>
       <c r="H596" t="s">
         <v>8</v>
@@ -15891,7 +15891,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G597" t="n">
-        <v>2.44241738319397</v>
+        <v>2.44241714477539</v>
       </c>
       <c r="H597" t="s">
         <v>8</v>
@@ -15917,7 +15917,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G598" t="n">
-        <v>2.49383664131165</v>
+        <v>2.49383687973022</v>
       </c>
       <c r="H598" t="s">
         <v>8</v>
@@ -15943,7 +15943,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G599" t="n">
-        <v>2.46812701225281</v>
+        <v>2.46812725067139</v>
       </c>
       <c r="H599" t="s">
         <v>8</v>
@@ -16021,7 +16021,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G602" t="n">
-        <v>2.46812701225281</v>
+        <v>2.46812725067139</v>
       </c>
       <c r="H602" t="s">
         <v>8</v>
@@ -16047,7 +16047,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G603" t="n">
-        <v>2.53668594360352</v>
+        <v>2.53668618202209</v>
       </c>
       <c r="H603" t="s">
         <v>8</v>
@@ -16099,7 +16099,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G605" t="n">
-        <v>2.59667539596558</v>
+        <v>2.596675157547</v>
       </c>
       <c r="H605" t="s">
         <v>8</v>
@@ -16125,7 +16125,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G606" t="n">
-        <v>2.61381506919861</v>
+        <v>2.61381530761719</v>
       </c>
       <c r="H606" t="s">
         <v>8</v>
@@ -16307,7 +16307,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G613" t="n">
-        <v>2.52694368362427</v>
+        <v>2.52694344520569</v>
       </c>
       <c r="H613" t="s">
         <v>8</v>
@@ -16385,7 +16385,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G616" t="n">
-        <v>2.50006103515625</v>
+        <v>2.50006127357483</v>
       </c>
       <c r="H616" t="s">
         <v>8</v>
@@ -16541,7 +16541,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G622" t="n">
-        <v>2.54486489295959</v>
+        <v>2.54486513137817</v>
       </c>
       <c r="H622" t="s">
         <v>8</v>
@@ -16723,7 +16723,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G629" t="n">
-        <v>2.54486489295959</v>
+        <v>2.54486513137817</v>
       </c>
       <c r="H629" t="s">
         <v>8</v>
@@ -16775,7 +16775,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G631" t="n">
-        <v>2.53590416908264</v>
+        <v>2.53590440750122</v>
       </c>
       <c r="H631" t="s">
         <v>8</v>
@@ -16905,7 +16905,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G636" t="n">
-        <v>2.54486489295959</v>
+        <v>2.54486513137817</v>
       </c>
       <c r="H636" t="s">
         <v>8</v>
@@ -16983,7 +16983,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G639" t="n">
-        <v>2.53590416908264</v>
+        <v>2.53590440750122</v>
       </c>
       <c r="H639" t="s">
         <v>8</v>
@@ -17009,7 +17009,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G640" t="n">
-        <v>2.53590416908264</v>
+        <v>2.53590440750122</v>
       </c>
       <c r="H640" t="s">
         <v>8</v>
@@ -17035,7 +17035,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G641" t="n">
-        <v>2.53590416908264</v>
+        <v>2.53590440750122</v>
       </c>
       <c r="H641" t="s">
         <v>8</v>
@@ -17061,7 +17061,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G642" t="n">
-        <v>2.53590416908264</v>
+        <v>2.53590440750122</v>
       </c>
       <c r="H642" t="s">
         <v>8</v>
@@ -17087,7 +17087,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G643" t="n">
-        <v>2.53590416908264</v>
+        <v>2.53590440750122</v>
       </c>
       <c r="H643" t="s">
         <v>8</v>
@@ -17113,7 +17113,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G644" t="n">
-        <v>2.52694368362427</v>
+        <v>2.52694344520569</v>
       </c>
       <c r="H644" t="s">
         <v>8</v>
@@ -17139,7 +17139,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G645" t="n">
-        <v>2.53590416908264</v>
+        <v>2.53590440750122</v>
       </c>
       <c r="H645" t="s">
         <v>8</v>
@@ -17295,7 +17295,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G651" t="n">
-        <v>2.54486489295959</v>
+        <v>2.54486513137817</v>
       </c>
       <c r="H651" t="s">
         <v>8</v>
@@ -17347,7 +17347,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G653" t="n">
-        <v>2.52694368362427</v>
+        <v>2.52694344520569</v>
       </c>
       <c r="H653" t="s">
         <v>8</v>
@@ -17659,7 +17659,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G665" t="n">
-        <v>2.76888465881348</v>
+        <v>2.76888489723206</v>
       </c>
       <c r="H665" t="s">
         <v>8</v>
@@ -17685,7 +17685,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G666" t="n">
-        <v>2.71512031555176</v>
+        <v>2.71512007713318</v>
       </c>
       <c r="H666" t="s">
         <v>8</v>
@@ -17789,7 +17789,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G670" t="n">
-        <v>2.72408080101013</v>
+        <v>2.72408103942871</v>
       </c>
       <c r="H670" t="s">
         <v>8</v>
@@ -17945,7 +17945,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G676" t="n">
-        <v>2.72408080101013</v>
+        <v>2.72408103942871</v>
       </c>
       <c r="H676" t="s">
         <v>8</v>
@@ -18049,7 +18049,7 @@
         <v>3</v>
       </c>
       <c r="G680" t="n">
-        <v>2.68823766708374</v>
+        <v>2.68823790550232</v>
       </c>
       <c r="H680" t="s">
         <v>8</v>
@@ -18075,7 +18075,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G681" t="n">
-        <v>2.72408080101013</v>
+        <v>2.72408103942871</v>
       </c>
       <c r="H681" t="s">
         <v>8</v>
@@ -18127,7 +18127,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G683" t="n">
-        <v>2.73304176330566</v>
+        <v>2.73304200172424</v>
       </c>
       <c r="H683" t="s">
         <v>8</v>
@@ -18153,7 +18153,7 @@
         <v>3</v>
       </c>
       <c r="G684" t="n">
-        <v>2.68823766708374</v>
+        <v>2.68823790550232</v>
       </c>
       <c r="H684" t="s">
         <v>8</v>
@@ -18179,7 +18179,7 @@
         <v>3</v>
       </c>
       <c r="G685" t="n">
-        <v>2.68823766708374</v>
+        <v>2.68823790550232</v>
       </c>
       <c r="H685" t="s">
         <v>8</v>
@@ -18205,7 +18205,7 @@
         <v>3</v>
       </c>
       <c r="G686" t="n">
-        <v>2.68823766708374</v>
+        <v>2.68823790550232</v>
       </c>
       <c r="H686" t="s">
         <v>8</v>
@@ -18231,7 +18231,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G687" t="n">
-        <v>2.71512031555176</v>
+        <v>2.71512007713318</v>
       </c>
       <c r="H687" t="s">
         <v>8</v>
@@ -18283,7 +18283,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G689" t="n">
-        <v>2.71512031555176</v>
+        <v>2.71512007713318</v>
       </c>
       <c r="H689" t="s">
         <v>8</v>
@@ -18335,7 +18335,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G691" t="n">
-        <v>2.67927694320679</v>
+        <v>2.67927718162537</v>
       </c>
       <c r="H691" t="s">
         <v>8</v>
@@ -18413,7 +18413,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G694" t="n">
-        <v>2.86745357513428</v>
+        <v>2.86745381355286</v>
       </c>
       <c r="H694" t="s">
         <v>8</v>
@@ -18439,7 +18439,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G695" t="n">
-        <v>2.83161044120789</v>
+        <v>2.83161067962646</v>
       </c>
       <c r="H695" t="s">
         <v>8</v>
@@ -18465,7 +18465,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G696" t="n">
-        <v>2.73304176330566</v>
+        <v>2.73304200172424</v>
       </c>
       <c r="H696" t="s">
         <v>8</v>
@@ -18517,7 +18517,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G698" t="n">
-        <v>2.72408080101013</v>
+        <v>2.72408103942871</v>
       </c>
       <c r="H698" t="s">
         <v>8</v>
@@ -18647,7 +18647,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G703" t="n">
-        <v>2.72408080101013</v>
+        <v>2.72408103942871</v>
       </c>
       <c r="H703" t="s">
         <v>8</v>
@@ -18725,7 +18725,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G706" t="n">
-        <v>2.67927694320679</v>
+        <v>2.67927718162537</v>
       </c>
       <c r="H706" t="s">
         <v>8</v>
@@ -18751,7 +18751,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G707" t="n">
-        <v>2.6434338092804</v>
+        <v>2.64343404769897</v>
       </c>
       <c r="H707" t="s">
         <v>8</v>
@@ -18829,7 +18829,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G710" t="n">
-        <v>2.58070826530457</v>
+        <v>2.58070850372314</v>
       </c>
       <c r="H710" t="s">
         <v>8</v>
@@ -18855,7 +18855,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G711" t="n">
-        <v>2.58070826530457</v>
+        <v>2.58070850372314</v>
       </c>
       <c r="H711" t="s">
         <v>8</v>
@@ -19011,7 +19011,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G717" t="n">
-        <v>2.58070826530457</v>
+        <v>2.58070850372314</v>
       </c>
       <c r="H717" t="s">
         <v>8</v>
@@ -19349,7 +19349,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G730" t="n">
-        <v>2.607590675354</v>
+        <v>2.60759091377258</v>
       </c>
       <c r="H730" t="s">
         <v>8</v>
@@ -19791,7 +19791,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G747" t="n">
-        <v>2.50006103515625</v>
+        <v>2.50006127357483</v>
       </c>
       <c r="H747" t="s">
         <v>8</v>
@@ -20025,7 +20025,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G756" t="n">
-        <v>2.53590416908264</v>
+        <v>2.53590440750122</v>
       </c>
       <c r="H756" t="s">
         <v>8</v>
@@ -20051,7 +20051,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G757" t="n">
-        <v>2.53590416908264</v>
+        <v>2.53590440750122</v>
       </c>
       <c r="H757" t="s">
         <v>8</v>
@@ -20077,7 +20077,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G758" t="n">
-        <v>2.53590416908264</v>
+        <v>2.53590440750122</v>
       </c>
       <c r="H758" t="s">
         <v>8</v>
@@ -20207,7 +20207,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G763" t="n">
-        <v>2.53590416908264</v>
+        <v>2.53590440750122</v>
       </c>
       <c r="H763" t="s">
         <v>8</v>
@@ -20233,7 +20233,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G764" t="n">
-        <v>2.53590416908264</v>
+        <v>2.53590440750122</v>
       </c>
       <c r="H764" t="s">
         <v>8</v>
@@ -20259,7 +20259,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G765" t="n">
-        <v>2.607590675354</v>
+        <v>2.60759091377258</v>
       </c>
       <c r="H765" t="s">
         <v>8</v>
@@ -20415,7 +20415,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G771" t="n">
-        <v>2.67927694320679</v>
+        <v>2.67927718162537</v>
       </c>
       <c r="H771" t="s">
         <v>8</v>
@@ -20467,7 +20467,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G773" t="n">
-        <v>2.71512031555176</v>
+        <v>2.71512007713318</v>
       </c>
       <c r="H773" t="s">
         <v>8</v>
@@ -20493,7 +20493,7 @@
         <v>3</v>
       </c>
       <c r="G774" t="n">
-        <v>2.68823766708374</v>
+        <v>2.68823790550232</v>
       </c>
       <c r="H774" t="s">
         <v>8</v>
@@ -20545,7 +20545,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G776" t="n">
-        <v>2.67927694320679</v>
+        <v>2.67927718162537</v>
       </c>
       <c r="H776" t="s">
         <v>8</v>
@@ -20597,7 +20597,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G778" t="n">
-        <v>2.81368899345398</v>
+        <v>2.81368923187256</v>
       </c>
       <c r="H778" t="s">
         <v>8</v>
@@ -20649,7 +20649,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G780" t="n">
-        <v>2.93914008140564</v>
+        <v>2.93914031982422</v>
       </c>
       <c r="H780" t="s">
         <v>8</v>
@@ -20675,7 +20675,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G781" t="n">
-        <v>2.87641453742981</v>
+        <v>2.87641477584839</v>
       </c>
       <c r="H781" t="s">
         <v>8</v>
@@ -20779,7 +20779,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G785" t="n">
-        <v>2.83161044120789</v>
+        <v>2.83161067962646</v>
       </c>
       <c r="H785" t="s">
         <v>8</v>
@@ -20909,7 +20909,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G790" t="n">
-        <v>2.76888465881348</v>
+        <v>2.76888489723206</v>
       </c>
       <c r="H790" t="s">
         <v>8</v>
@@ -20935,7 +20935,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G791" t="n">
-        <v>2.83161044120789</v>
+        <v>2.83161067962646</v>
       </c>
       <c r="H791" t="s">
         <v>8</v>
@@ -21013,7 +21013,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G794" t="n">
-        <v>2.87641453742981</v>
+        <v>2.87641477584839</v>
       </c>
       <c r="H794" t="s">
         <v>8</v>
@@ -21039,7 +21039,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G795" t="n">
-        <v>2.87641453742981</v>
+        <v>2.87641477584839</v>
       </c>
       <c r="H795" t="s">
         <v>8</v>
@@ -21143,7 +21143,7 @@
         <v>3.5</v>
       </c>
       <c r="G799" t="n">
-        <v>3.13627767562866</v>
+        <v>3.13627743721008</v>
       </c>
       <c r="H799" t="s">
         <v>8</v>
@@ -21221,7 +21221,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G802" t="n">
-        <v>3.26172876358032</v>
+        <v>3.26172852516174</v>
       </c>
       <c r="H802" t="s">
         <v>8</v>
@@ -21325,7 +21325,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G806" t="n">
-        <v>3.29757189750671</v>
+        <v>3.29757165908813</v>
       </c>
       <c r="H806" t="s">
         <v>8</v>
@@ -21559,7 +21559,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G815" t="n">
-        <v>3.40510129928589</v>
+        <v>3.40510106086731</v>
       </c>
       <c r="H815" t="s">
         <v>8</v>
@@ -21611,7 +21611,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G817" t="n">
-        <v>3.36925840377808</v>
+        <v>3.3692581653595</v>
       </c>
       <c r="H817" t="s">
         <v>8</v>
@@ -21663,7 +21663,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G819" t="n">
-        <v>3.40510129928589</v>
+        <v>3.40510106086731</v>
       </c>
       <c r="H819" t="s">
         <v>8</v>
@@ -21689,7 +21689,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G820" t="n">
-        <v>3.37821865081787</v>
+        <v>3.37821888923645</v>
       </c>
       <c r="H820" t="s">
         <v>8</v>
@@ -21949,7 +21949,7 @@
         <v>3.97000002861023</v>
       </c>
       <c r="G830" t="n">
-        <v>3.55743455886841</v>
+        <v>3.55743479728699</v>
       </c>
       <c r="H830" t="s">
         <v>8</v>
@@ -22027,7 +22027,7 @@
         <v>3.9300000667572</v>
       </c>
       <c r="G833" t="n">
-        <v>3.52159142494202</v>
+        <v>3.5215916633606</v>
       </c>
       <c r="H833" t="s">
         <v>8</v>
@@ -22105,7 +22105,7 @@
         <v>3.97000002861023</v>
       </c>
       <c r="G836" t="n">
-        <v>3.55743455886841</v>
+        <v>3.55743479728699</v>
       </c>
       <c r="H836" t="s">
         <v>8</v>
@@ -22313,7 +22313,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G844" t="n">
-        <v>3.66496419906616</v>
+        <v>3.66496443748474</v>
       </c>
       <c r="H844" t="s">
         <v>8</v>
@@ -22391,7 +22391,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G847" t="n">
-        <v>3.6918466091156</v>
+        <v>3.69184637069702</v>
       </c>
       <c r="H847" t="s">
         <v>8</v>
@@ -22417,7 +22417,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G848" t="n">
-        <v>3.70976805686951</v>
+        <v>3.70976829528809</v>
       </c>
       <c r="H848" t="s">
         <v>8</v>
@@ -22495,7 +22495,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G851" t="n">
-        <v>3.70976805686951</v>
+        <v>3.70976829528809</v>
       </c>
       <c r="H851" t="s">
         <v>8</v>
@@ -22573,7 +22573,7 @@
         <v>4.25</v>
       </c>
       <c r="G854" t="n">
-        <v>3.80833697319031</v>
+        <v>3.80833721160889</v>
       </c>
       <c r="H854" t="s">
         <v>8</v>
@@ -22599,7 +22599,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G855" t="n">
-        <v>3.79041528701782</v>
+        <v>3.7904155254364</v>
       </c>
       <c r="H855" t="s">
         <v>8</v>
@@ -22625,7 +22625,7 @@
         <v>4.25</v>
       </c>
       <c r="G856" t="n">
-        <v>3.80833697319031</v>
+        <v>3.80833721160889</v>
       </c>
       <c r="H856" t="s">
         <v>8</v>
@@ -22677,7 +22677,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G858" t="n">
-        <v>3.96067023277283</v>
+        <v>3.96067070960999</v>
       </c>
       <c r="H858" t="s">
         <v>8</v>
@@ -71690,6 +71690,32 @@
         <v>0.980000019073486</v>
       </c>
       <c r="H2743" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2744">
+      <c r="A2744" s="1" t="n">
+        <v>46311.2916666667</v>
+      </c>
+      <c r="B2744" t="n">
+        <v>2400</v>
+      </c>
+      <c r="C2744" t="n">
+        <v>1.00999999046326</v>
+      </c>
+      <c r="D2744" t="n">
+        <v>0.985000014305115</v>
+      </c>
+      <c r="E2744" t="n">
+        <v>0.985000014305115</v>
+      </c>
+      <c r="F2744" t="n">
+        <v>1.00999999046326</v>
+      </c>
+      <c r="G2744" t="n">
+        <v>1.00999999046326</v>
+      </c>
+      <c r="H2744" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/RAT.MI.xlsx
+++ b/data/RAT.MI.xlsx
@@ -427,7 +427,7 @@
         <v>2.3659999370575</v>
       </c>
       <c r="G2" t="n">
-        <v>1.85825955867767</v>
+        <v>1.85825932025909</v>
       </c>
       <c r="H2" t="n">
         <v>1350</v>
@@ -485,7 +485,7 @@
         <v>2.44600009918213</v>
       </c>
       <c r="G4" t="n">
-        <v>1.92109167575836</v>
+        <v>1.92109143733978</v>
       </c>
       <c r="H4" t="n">
         <v>365</v>
@@ -514,7 +514,7 @@
         <v>2.44600009918213</v>
       </c>
       <c r="G5" t="n">
-        <v>1.92109167575836</v>
+        <v>1.92109143733978</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -543,7 +543,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G6" t="n">
-        <v>1.88496315479279</v>
+        <v>1.88496327400208</v>
       </c>
       <c r="H6" t="n">
         <v>5635</v>
@@ -572,7 +572,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G7" t="n">
-        <v>1.88496315479279</v>
+        <v>1.88496327400208</v>
       </c>
       <c r="H7" t="n">
         <v>1000</v>
@@ -601,7 +601,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G8" t="n">
-        <v>1.92423319816589</v>
+        <v>1.92423331737518</v>
       </c>
       <c r="H8" t="n">
         <v>4000</v>
@@ -630,7 +630,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G9" t="n">
-        <v>1.88496315479279</v>
+        <v>1.88496327400208</v>
       </c>
       <c r="H9" t="n">
         <v>155</v>
@@ -659,7 +659,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G10" t="n">
-        <v>1.88496315479279</v>
+        <v>1.88496327400208</v>
       </c>
       <c r="H10" t="n">
         <v>559</v>
@@ -688,7 +688,7 @@
         <v>2.3659999370575</v>
       </c>
       <c r="G11" t="n">
-        <v>1.85825955867767</v>
+        <v>1.85825932025909</v>
       </c>
       <c r="H11" t="n">
         <v>1414</v>
@@ -717,7 +717,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G12" t="n">
-        <v>1.80642306804657</v>
+        <v>1.80642294883728</v>
       </c>
       <c r="H12" t="n">
         <v>270</v>
@@ -746,7 +746,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G13" t="n">
-        <v>1.80642306804657</v>
+        <v>1.80642294883728</v>
       </c>
       <c r="H13" t="n">
         <v>1200</v>
@@ -775,7 +775,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G14" t="n">
-        <v>1.82998490333557</v>
+        <v>1.82998502254486</v>
       </c>
       <c r="H14" t="n">
         <v>193</v>
@@ -833,7 +833,7 @@
         <v>2.25</v>
       </c>
       <c r="G16" t="n">
-        <v>1.76715278625488</v>
+        <v>1.76715302467346</v>
       </c>
       <c r="H16" t="n">
         <v>2070</v>
@@ -862,7 +862,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G17" t="n">
-        <v>1.85354685783386</v>
+        <v>1.85354709625244</v>
       </c>
       <c r="H17" t="n">
         <v>4705</v>
@@ -891,7 +891,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G18" t="n">
-        <v>1.85354685783386</v>
+        <v>1.85354709625244</v>
       </c>
       <c r="H18" t="n">
         <v>2000</v>
@@ -920,7 +920,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G19" t="n">
-        <v>1.86925518512726</v>
+        <v>1.86925506591797</v>
       </c>
       <c r="H19" t="n">
         <v>3200</v>
@@ -978,7 +978,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G21" t="n">
-        <v>1.89281713962555</v>
+        <v>1.89281737804413</v>
       </c>
       <c r="H21" t="n">
         <v>100</v>
@@ -1123,7 +1123,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G26" t="n">
-        <v>1.88496315479279</v>
+        <v>1.88496327400208</v>
       </c>
       <c r="H26" t="n">
         <v>330</v>
@@ -1152,7 +1152,7 @@
         <v>2.38800001144409</v>
       </c>
       <c r="G27" t="n">
-        <v>1.8755384683609</v>
+        <v>1.87553811073303</v>
       </c>
       <c r="H27" t="n">
         <v>2173</v>
@@ -1181,7 +1181,7 @@
         <v>2.38800001144409</v>
       </c>
       <c r="G28" t="n">
-        <v>1.8755384683609</v>
+        <v>1.87553811073303</v>
       </c>
       <c r="H28" t="n">
         <v>0</v>
@@ -1210,7 +1210,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G29" t="n">
-        <v>1.88496315479279</v>
+        <v>1.88496327400208</v>
       </c>
       <c r="H29" t="n">
         <v>1810</v>
@@ -1239,7 +1239,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G30" t="n">
-        <v>1.80642306804657</v>
+        <v>1.80642294883728</v>
       </c>
       <c r="H30" t="n">
         <v>10919</v>
@@ -1297,7 +1297,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G32" t="n">
-        <v>1.84569311141968</v>
+        <v>1.84569299221039</v>
       </c>
       <c r="H32" t="n">
         <v>250</v>
@@ -1355,7 +1355,7 @@
         <v>2.33800005912781</v>
       </c>
       <c r="G34" t="n">
-        <v>1.83626842498779</v>
+        <v>1.8362683057785</v>
       </c>
       <c r="H34" t="n">
         <v>9221</v>
@@ -1384,7 +1384,7 @@
         <v>2.36800003051758</v>
       </c>
       <c r="G35" t="n">
-        <v>1.8598301410675</v>
+        <v>1.85983026027679</v>
       </c>
       <c r="H35" t="n">
         <v>100</v>
@@ -1413,7 +1413,7 @@
         <v>2.36800003051758</v>
       </c>
       <c r="G36" t="n">
-        <v>1.8598301410675</v>
+        <v>1.85983026027679</v>
       </c>
       <c r="H36" t="n">
         <v>0</v>
@@ -1442,7 +1442,7 @@
         <v>2.36800003051758</v>
       </c>
       <c r="G37" t="n">
-        <v>1.8598301410675</v>
+        <v>1.85983026027679</v>
       </c>
       <c r="H37" t="n">
         <v>100</v>
@@ -1471,7 +1471,7 @@
         <v>2.29800009727478</v>
       </c>
       <c r="G38" t="n">
-        <v>1.80485236644745</v>
+        <v>1.80485212802887</v>
       </c>
       <c r="H38" t="n">
         <v>7831</v>
@@ -1500,7 +1500,7 @@
         <v>2.31800007820129</v>
       </c>
       <c r="G39" t="n">
-        <v>1.8205600976944</v>
+        <v>1.82056033611298</v>
       </c>
       <c r="H39" t="n">
         <v>330</v>
@@ -1616,7 +1616,7 @@
         <v>2.33800005912781</v>
       </c>
       <c r="G43" t="n">
-        <v>1.83626842498779</v>
+        <v>1.8362683057785</v>
       </c>
       <c r="H43" t="n">
         <v>950</v>
@@ -1645,7 +1645,7 @@
         <v>2.36800003051758</v>
       </c>
       <c r="G44" t="n">
-        <v>1.8598301410675</v>
+        <v>1.85983026027679</v>
       </c>
       <c r="H44" t="n">
         <v>540</v>
@@ -1703,7 +1703,7 @@
         <v>2.35599994659424</v>
       </c>
       <c r="G46" t="n">
-        <v>1.85040545463562</v>
+        <v>1.85040533542633</v>
       </c>
       <c r="H46" t="n">
         <v>253</v>
@@ -1732,7 +1732,7 @@
         <v>2.39400005340576</v>
       </c>
       <c r="G47" t="n">
-        <v>1.88025081157684</v>
+        <v>1.88025057315826</v>
       </c>
       <c r="H47" t="n">
         <v>110</v>
@@ -1761,7 +1761,7 @@
         <v>2.39400005340576</v>
       </c>
       <c r="G48" t="n">
-        <v>1.88025081157684</v>
+        <v>1.88025057315826</v>
       </c>
       <c r="H48" t="n">
         <v>0</v>
@@ -1790,7 +1790,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G49" t="n">
-        <v>1.81427693367004</v>
+        <v>1.81427705287933</v>
       </c>
       <c r="H49" t="n">
         <v>1530</v>
@@ -1819,7 +1819,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G50" t="n">
-        <v>1.84569311141968</v>
+        <v>1.84569299221039</v>
       </c>
       <c r="H50" t="n">
         <v>396</v>
@@ -1848,7 +1848,7 @@
         <v>2.33800005912781</v>
       </c>
       <c r="G51" t="n">
-        <v>1.83626842498779</v>
+        <v>1.8362683057785</v>
       </c>
       <c r="H51" t="n">
         <v>1660</v>
@@ -1877,7 +1877,7 @@
         <v>2.35800004005432</v>
       </c>
       <c r="G52" t="n">
-        <v>1.85197615623474</v>
+        <v>1.85197603702545</v>
       </c>
       <c r="H52" t="n">
         <v>3419</v>
@@ -1906,7 +1906,7 @@
         <v>2.34800004959106</v>
       </c>
       <c r="G53" t="n">
-        <v>1.84412240982056</v>
+        <v>1.84412217140198</v>
       </c>
       <c r="H53" t="n">
         <v>3348</v>
@@ -1964,7 +1964,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G55" t="n">
-        <v>1.84569311141968</v>
+        <v>1.84569299221039</v>
       </c>
       <c r="H55" t="n">
         <v>386</v>
@@ -1993,7 +1993,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G56" t="n">
-        <v>1.84569311141968</v>
+        <v>1.84569299221039</v>
       </c>
       <c r="H56" t="n">
         <v>5025</v>
@@ -2022,7 +2022,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G57" t="n">
-        <v>1.85354685783386</v>
+        <v>1.85354709625244</v>
       </c>
       <c r="H57" t="n">
         <v>50</v>
@@ -2109,7 +2109,7 @@
         <v>2.30599999427795</v>
       </c>
       <c r="G60" t="n">
-        <v>1.81113541126251</v>
+        <v>1.81113529205322</v>
       </c>
       <c r="H60" t="n">
         <v>6820</v>
@@ -2138,7 +2138,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G61" t="n">
-        <v>1.81427693367004</v>
+        <v>1.81427705287933</v>
       </c>
       <c r="H61" t="n">
         <v>150</v>
@@ -2196,7 +2196,7 @@
         <v>2.35599994659424</v>
       </c>
       <c r="G63" t="n">
-        <v>1.85040545463562</v>
+        <v>1.85040533542633</v>
       </c>
       <c r="H63" t="n">
         <v>100</v>
@@ -2225,7 +2225,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G64" t="n">
-        <v>1.84569311141968</v>
+        <v>1.84569299221039</v>
       </c>
       <c r="H64" t="n">
         <v>1054</v>
@@ -2254,7 +2254,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G65" t="n">
-        <v>1.92423319816589</v>
+        <v>1.92423331737518</v>
       </c>
       <c r="H65" t="n">
         <v>19358</v>
@@ -2283,7 +2283,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G66" t="n">
-        <v>1.92423319816589</v>
+        <v>1.92423331737518</v>
       </c>
       <c r="H66" t="n">
         <v>0</v>
@@ -2312,7 +2312,7 @@
         <v>2.46600008010864</v>
       </c>
       <c r="G67" t="n">
-        <v>1.93679940700531</v>
+        <v>1.93679976463318</v>
       </c>
       <c r="H67" t="n">
         <v>1695</v>
@@ -2341,7 +2341,7 @@
         <v>2.4779999256134</v>
       </c>
       <c r="G68" t="n">
-        <v>1.94622421264648</v>
+        <v>1.94622397422791</v>
       </c>
       <c r="H68" t="n">
         <v>120</v>
@@ -2370,7 +2370,7 @@
         <v>2.48799991607666</v>
       </c>
       <c r="G69" t="n">
-        <v>1.95407843589783</v>
+        <v>1.95407807826996</v>
       </c>
       <c r="H69" t="n">
         <v>16224</v>
@@ -2399,7 +2399,7 @@
         <v>2.5</v>
       </c>
       <c r="G70" t="n">
-        <v>1.963503241539</v>
+        <v>1.96350336074829</v>
       </c>
       <c r="H70" t="n">
         <v>23697</v>
@@ -2457,7 +2457,7 @@
         <v>2.53800010681152</v>
       </c>
       <c r="G72" t="n">
-        <v>1.99334871768951</v>
+        <v>1.99334836006165</v>
       </c>
       <c r="H72" t="n">
         <v>1951</v>
@@ -2515,7 +2515,7 @@
         <v>2.5</v>
       </c>
       <c r="G74" t="n">
-        <v>1.963503241539</v>
+        <v>1.96350336074829</v>
       </c>
       <c r="H74" t="n">
         <v>1853</v>
@@ -2544,7 +2544,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G75" t="n">
-        <v>1.98706543445587</v>
+        <v>1.98706519603729</v>
       </c>
       <c r="H75" t="n">
         <v>41607</v>
@@ -2660,7 +2660,7 @@
         <v>2.45799994468689</v>
       </c>
       <c r="G79" t="n">
-        <v>1.93051648139954</v>
+        <v>1.93051636219025</v>
       </c>
       <c r="H79" t="n">
         <v>9175</v>
@@ -2689,7 +2689,7 @@
         <v>2.45799994468689</v>
       </c>
       <c r="G80" t="n">
-        <v>1.93051648139954</v>
+        <v>1.93051636219025</v>
       </c>
       <c r="H80" t="n">
         <v>1464</v>
@@ -2718,7 +2718,7 @@
         <v>2.5</v>
       </c>
       <c r="G81" t="n">
-        <v>1.963503241539</v>
+        <v>1.96350336074829</v>
       </c>
       <c r="H81" t="n">
         <v>50</v>
@@ -2747,7 +2747,7 @@
         <v>2.49799990653992</v>
       </c>
       <c r="G82" t="n">
-        <v>1.96193242073059</v>
+        <v>1.96193218231201</v>
       </c>
       <c r="H82" t="n">
         <v>2294</v>
@@ -2776,7 +2776,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G83" t="n">
-        <v>1.93994140625</v>
+        <v>1.93994152545929</v>
       </c>
       <c r="H83" t="n">
         <v>1443</v>
@@ -2805,7 +2805,7 @@
         <v>2.48799991607666</v>
       </c>
       <c r="G84" t="n">
-        <v>1.95407843589783</v>
+        <v>1.95407807826996</v>
       </c>
       <c r="H84" t="n">
         <v>371</v>
@@ -2892,7 +2892,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G87" t="n">
-        <v>1.93994140625</v>
+        <v>1.93994152545929</v>
       </c>
       <c r="H87" t="n">
         <v>303</v>
@@ -2950,7 +2950,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G89" t="n">
-        <v>1.88496315479279</v>
+        <v>1.88496327400208</v>
       </c>
       <c r="H89" t="n">
         <v>4181</v>
@@ -3037,7 +3037,7 @@
         <v>2.39400005340576</v>
       </c>
       <c r="G92" t="n">
-        <v>1.88025081157684</v>
+        <v>1.88025057315826</v>
       </c>
       <c r="H92" t="n">
         <v>260</v>
@@ -3153,7 +3153,7 @@
         <v>2.29800009727478</v>
       </c>
       <c r="G96" t="n">
-        <v>1.80485236644745</v>
+        <v>1.80485212802887</v>
       </c>
       <c r="H96" t="n">
         <v>5665</v>
@@ -3182,7 +3182,7 @@
         <v>2.29800009727478</v>
       </c>
       <c r="G97" t="n">
-        <v>1.80485236644745</v>
+        <v>1.80485212802887</v>
       </c>
       <c r="H97" t="n">
         <v>50</v>
@@ -3211,7 +3211,7 @@
         <v>2.34800004959106</v>
       </c>
       <c r="G98" t="n">
-        <v>1.84412240982056</v>
+        <v>1.84412217140198</v>
       </c>
       <c r="H98" t="n">
         <v>8904</v>
@@ -3240,7 +3240,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G99" t="n">
-        <v>1.89281713962555</v>
+        <v>1.89281737804413</v>
       </c>
       <c r="H99" t="n">
         <v>14550</v>
@@ -3269,7 +3269,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G100" t="n">
-        <v>1.93378698825836</v>
+        <v>1.93378710746765</v>
       </c>
       <c r="H100" t="n">
         <v>1125</v>
@@ -3298,7 +3298,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G101" t="n">
-        <v>1.95017528533936</v>
+        <v>1.95017516613007</v>
       </c>
       <c r="H101" t="n">
         <v>176</v>
@@ -3356,7 +3356,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G103" t="n">
-        <v>1.93378698825836</v>
+        <v>1.93378710746765</v>
       </c>
       <c r="H103" t="n">
         <v>3800</v>
@@ -3385,7 +3385,7 @@
         <v>2.35599994659424</v>
       </c>
       <c r="G104" t="n">
-        <v>1.93050956726074</v>
+        <v>1.93050944805145</v>
       </c>
       <c r="H104" t="n">
         <v>3779</v>
@@ -3472,7 +3472,7 @@
         <v>2.38599991798401</v>
       </c>
       <c r="G107" t="n">
-        <v>1.95509135723114</v>
+        <v>1.95509147644043</v>
       </c>
       <c r="H107" t="n">
         <v>523</v>
@@ -3559,7 +3559,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G110" t="n">
-        <v>1.95017528533936</v>
+        <v>1.95017516613007</v>
       </c>
       <c r="H110" t="n">
         <v>403</v>
@@ -3588,7 +3588,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G111" t="n">
-        <v>1.95017528533936</v>
+        <v>1.95017516613007</v>
       </c>
       <c r="H111" t="n">
         <v>0</v>
@@ -3617,7 +3617,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G112" t="n">
-        <v>1.91739904880524</v>
+        <v>1.91739892959595</v>
       </c>
       <c r="H112" t="n">
         <v>778</v>
@@ -3646,7 +3646,7 @@
         <v>2.36199998855591</v>
       </c>
       <c r="G113" t="n">
-        <v>1.9354259967804</v>
+        <v>1.93542611598969</v>
       </c>
       <c r="H113" t="n">
         <v>1461</v>
@@ -3675,7 +3675,7 @@
         <v>2.36199998855591</v>
       </c>
       <c r="G114" t="n">
-        <v>1.9354259967804</v>
+        <v>1.93542611598969</v>
       </c>
       <c r="H114" t="n">
         <v>0</v>
@@ -3704,7 +3704,7 @@
         <v>2.36199998855591</v>
       </c>
       <c r="G115" t="n">
-        <v>1.9354259967804</v>
+        <v>1.93542611598969</v>
       </c>
       <c r="H115" t="n">
         <v>635</v>
@@ -3733,7 +3733,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G116" t="n">
-        <v>1.94198107719421</v>
+        <v>1.9419811964035</v>
       </c>
       <c r="H116" t="n">
         <v>5088</v>
@@ -3762,7 +3762,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G117" t="n">
-        <v>1.94198107719421</v>
+        <v>1.9419811964035</v>
       </c>
       <c r="H117" t="n">
         <v>0</v>
@@ -3791,7 +3791,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G118" t="n">
-        <v>1.91739904880524</v>
+        <v>1.91739892959595</v>
       </c>
       <c r="H118" t="n">
         <v>2740</v>
@@ -3849,7 +3849,7 @@
         <v>2.33200001716614</v>
       </c>
       <c r="G120" t="n">
-        <v>1.91084420681</v>
+        <v>1.91084396839142</v>
       </c>
       <c r="H120" t="n">
         <v>1532</v>
@@ -3878,7 +3878,7 @@
         <v>2.33200001716614</v>
       </c>
       <c r="G121" t="n">
-        <v>1.91084420681</v>
+        <v>1.91084396839142</v>
       </c>
       <c r="H121" t="n">
         <v>0</v>
@@ -3994,7 +3994,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G125" t="n">
-        <v>1.8026829957962</v>
+        <v>1.80268323421478</v>
       </c>
       <c r="H125" t="n">
         <v>3159</v>
@@ -4052,7 +4052,7 @@
         <v>2.23600006103516</v>
       </c>
       <c r="G127" t="n">
-        <v>1.83218157291412</v>
+        <v>1.83218133449554</v>
       </c>
       <c r="H127" t="n">
         <v>773</v>
@@ -4110,7 +4110,7 @@
         <v>2.29800009727478</v>
       </c>
       <c r="G129" t="n">
-        <v>1.88298451900482</v>
+        <v>1.88298428058624</v>
       </c>
       <c r="H129" t="n">
         <v>100</v>
@@ -4139,7 +4139,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G130" t="n">
-        <v>1.86823499202728</v>
+        <v>1.86823523044586</v>
       </c>
       <c r="H130" t="n">
         <v>2288</v>
@@ -4168,7 +4168,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G131" t="n">
-        <v>1.94198107719421</v>
+        <v>1.9419811964035</v>
       </c>
       <c r="H131" t="n">
         <v>150</v>
@@ -4197,7 +4197,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G132" t="n">
-        <v>1.94198107719421</v>
+        <v>1.9419811964035</v>
       </c>
       <c r="H132" t="n">
         <v>0</v>
@@ -4313,7 +4313,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G136" t="n">
-        <v>1.89281702041626</v>
+        <v>1.89281713962555</v>
       </c>
       <c r="H136" t="n">
         <v>6553</v>
@@ -4400,7 +4400,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G139" t="n">
-        <v>1.88462316989899</v>
+        <v>1.8846230506897</v>
       </c>
       <c r="H139" t="n">
         <v>110</v>
@@ -4690,7 +4690,7 @@
         <v>2.2260000705719</v>
       </c>
       <c r="G149" t="n">
-        <v>1.82398760318756</v>
+        <v>1.82398748397827</v>
       </c>
       <c r="H149" t="n">
         <v>2820</v>
@@ -4777,7 +4777,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G152" t="n">
-        <v>1.78629517555237</v>
+        <v>1.78629505634308</v>
       </c>
       <c r="H152" t="n">
         <v>7134</v>
@@ -4806,7 +4806,7 @@
         <v>2.16799998283386</v>
       </c>
       <c r="G153" t="n">
-        <v>1.77646195888519</v>
+        <v>1.77646219730377</v>
       </c>
       <c r="H153" t="n">
         <v>1600</v>
@@ -4835,7 +4835,7 @@
         <v>2.13800001144409</v>
       </c>
       <c r="G154" t="n">
-        <v>1.75188016891479</v>
+        <v>1.75188004970551</v>
       </c>
       <c r="H154" t="n">
         <v>6911</v>
@@ -4893,7 +4893,7 @@
         <v>2.17199993133545</v>
       </c>
       <c r="G156" t="n">
-        <v>1.77973961830139</v>
+        <v>1.77973973751068</v>
       </c>
       <c r="H156" t="n">
         <v>975</v>
@@ -4922,7 +4922,7 @@
         <v>2.17199993133545</v>
       </c>
       <c r="G157" t="n">
-        <v>1.77973961830139</v>
+        <v>1.77973973751068</v>
       </c>
       <c r="H157" t="n">
         <v>0</v>
@@ -4951,7 +4951,7 @@
         <v>2.13599991798401</v>
       </c>
       <c r="G158" t="n">
-        <v>1.75024127960205</v>
+        <v>1.75024104118347</v>
       </c>
       <c r="H158" t="n">
         <v>4584</v>
@@ -4980,7 +4980,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G159" t="n">
-        <v>1.72074294090271</v>
+        <v>1.72074282169342</v>
       </c>
       <c r="H159" t="n">
         <v>2791</v>
@@ -5009,7 +5009,7 @@
         <v>2.03800010681152</v>
       </c>
       <c r="G160" t="n">
-        <v>1.66993999481201</v>
+        <v>1.66993987560272</v>
       </c>
       <c r="H160" t="n">
         <v>1226</v>
@@ -5038,7 +5038,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G161" t="n">
-        <v>1.7289365530014</v>
+        <v>1.72893679141998</v>
       </c>
       <c r="H161" t="n">
         <v>12639</v>
@@ -5067,7 +5067,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G162" t="n">
-        <v>1.7289365530014</v>
+        <v>1.72893679141998</v>
       </c>
       <c r="H162" t="n">
         <v>0</v>
@@ -5096,7 +5096,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G163" t="n">
-        <v>1.69616055488586</v>
+        <v>1.69616067409515</v>
       </c>
       <c r="H163" t="n">
         <v>4541</v>
@@ -5299,7 +5299,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G170" t="n">
-        <v>1.70435476303101</v>
+        <v>1.7043548822403</v>
       </c>
       <c r="H170" t="n">
         <v>12329</v>
@@ -5357,7 +5357,7 @@
         <v>2.1159999370575</v>
       </c>
       <c r="G172" t="n">
-        <v>1.73385334014893</v>
+        <v>1.73385310173035</v>
       </c>
       <c r="H172" t="n">
         <v>5150</v>
@@ -5386,7 +5386,7 @@
         <v>2.1159999370575</v>
       </c>
       <c r="G173" t="n">
-        <v>1.73385334014893</v>
+        <v>1.73385310173035</v>
       </c>
       <c r="H173" t="n">
         <v>0</v>
@@ -5444,7 +5444,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G175" t="n">
-        <v>1.63060867786407</v>
+        <v>1.63060879707336</v>
       </c>
       <c r="H175" t="n">
         <v>32041</v>
@@ -5473,7 +5473,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G176" t="n">
-        <v>1.67157876491547</v>
+        <v>1.67157864570618</v>
       </c>
       <c r="H176" t="n">
         <v>12255</v>
@@ -5502,7 +5502,7 @@
         <v>2.03399991989136</v>
       </c>
       <c r="G177" t="n">
-        <v>1.66666233539581</v>
+        <v>1.66666221618652</v>
       </c>
       <c r="H177" t="n">
         <v>7268</v>
@@ -5531,7 +5531,7 @@
         <v>1.9650000333786</v>
       </c>
       <c r="G178" t="n">
-        <v>1.61012363433838</v>
+        <v>1.61012375354767</v>
       </c>
       <c r="H178" t="n">
         <v>11222</v>
@@ -5589,7 +5589,7 @@
         <v>2.03800010681152</v>
       </c>
       <c r="G180" t="n">
-        <v>1.66993999481201</v>
+        <v>1.66993987560272</v>
       </c>
       <c r="H180" t="n">
         <v>9799</v>
@@ -5647,7 +5647,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G182" t="n">
-        <v>1.67157876491547</v>
+        <v>1.67157864570618</v>
       </c>
       <c r="H182" t="n">
         <v>1012</v>
@@ -5676,7 +5676,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G183" t="n">
-        <v>1.67157876491547</v>
+        <v>1.67157864570618</v>
       </c>
       <c r="H183" t="n">
         <v>0</v>
@@ -5705,7 +5705,7 @@
         <v>2.04200005531311</v>
       </c>
       <c r="G184" t="n">
-        <v>1.67321765422821</v>
+        <v>1.67321753501892</v>
       </c>
       <c r="H184" t="n">
         <v>14480</v>
@@ -5734,7 +5734,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G185" t="n">
-        <v>1.67157876491547</v>
+        <v>1.67157864570618</v>
       </c>
       <c r="H185" t="n">
         <v>1394</v>
@@ -5763,7 +5763,7 @@
         <v>2.03800010681152</v>
       </c>
       <c r="G186" t="n">
-        <v>1.66993999481201</v>
+        <v>1.66993987560272</v>
       </c>
       <c r="H186" t="n">
         <v>1116</v>
@@ -5792,7 +5792,7 @@
         <v>2.03800010681152</v>
       </c>
       <c r="G187" t="n">
-        <v>1.66993999481201</v>
+        <v>1.66993987560272</v>
       </c>
       <c r="H187" t="n">
         <v>0</v>
@@ -5821,7 +5821,7 @@
         <v>2.03800010681152</v>
       </c>
       <c r="G188" t="n">
-        <v>1.66993999481201</v>
+        <v>1.66993987560272</v>
       </c>
       <c r="H188" t="n">
         <v>0</v>
@@ -5879,7 +5879,7 @@
         <v>2</v>
       </c>
       <c r="G190" t="n">
-        <v>1.63880264759064</v>
+        <v>1.63880276679993</v>
       </c>
       <c r="H190" t="n">
         <v>288</v>
@@ -5908,7 +5908,7 @@
         <v>1.98399996757507</v>
       </c>
       <c r="G191" t="n">
-        <v>1.62569236755371</v>
+        <v>1.62569212913513</v>
       </c>
       <c r="H191" t="n">
         <v>9477</v>
@@ -5966,7 +5966,7 @@
         <v>2.03399991989136</v>
       </c>
       <c r="G193" t="n">
-        <v>1.66666233539581</v>
+        <v>1.66666221618652</v>
       </c>
       <c r="H193" t="n">
         <v>2852</v>
@@ -5995,7 +5995,7 @@
         <v>2.03800010681152</v>
       </c>
       <c r="G194" t="n">
-        <v>1.66993999481201</v>
+        <v>1.66993987560272</v>
       </c>
       <c r="H194" t="n">
         <v>204</v>
@@ -6024,7 +6024,7 @@
         <v>2.03600001335144</v>
       </c>
       <c r="G195" t="n">
-        <v>1.66830110549927</v>
+        <v>1.66830122470856</v>
       </c>
       <c r="H195" t="n">
         <v>6290</v>
@@ -6053,7 +6053,7 @@
         <v>2.03600001335144</v>
       </c>
       <c r="G196" t="n">
-        <v>1.66830110549927</v>
+        <v>1.66830122470856</v>
       </c>
       <c r="H196" t="n">
         <v>0</v>
@@ -6082,7 +6082,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G197" t="n">
-        <v>1.65519058704376</v>
+        <v>1.65519070625305</v>
       </c>
       <c r="H197" t="n">
         <v>4191</v>
@@ -6111,7 +6111,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G198" t="n">
-        <v>1.65519058704376</v>
+        <v>1.65519070625305</v>
       </c>
       <c r="H198" t="n">
         <v>0</v>
@@ -6140,7 +6140,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G199" t="n">
-        <v>1.65519058704376</v>
+        <v>1.65519070625305</v>
       </c>
       <c r="H199" t="n">
         <v>1000</v>
@@ -6169,7 +6169,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G200" t="n">
-        <v>1.65519058704376</v>
+        <v>1.65519070625305</v>
       </c>
       <c r="H200" t="n">
         <v>0</v>
@@ -6198,7 +6198,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G201" t="n">
-        <v>1.65519058704376</v>
+        <v>1.65519070625305</v>
       </c>
       <c r="H201" t="n">
         <v>100</v>
@@ -6372,7 +6372,7 @@
         <v>1.95099997520447</v>
       </c>
       <c r="G207" t="n">
-        <v>1.59865212440491</v>
+        <v>1.59865200519562</v>
       </c>
       <c r="H207" t="n">
         <v>3446</v>
@@ -6401,7 +6401,7 @@
         <v>1.9889999628067</v>
       </c>
       <c r="G208" t="n">
-        <v>1.6297892332077</v>
+        <v>1.62978935241699</v>
       </c>
       <c r="H208" t="n">
         <v>50</v>
@@ -6430,7 +6430,7 @@
         <v>1.932000041008</v>
       </c>
       <c r="G209" t="n">
-        <v>1.58308339118958</v>
+        <v>1.58308351039886</v>
       </c>
       <c r="H209" t="n">
         <v>10501</v>
@@ -6459,7 +6459,7 @@
         <v>1.94700002670288</v>
       </c>
       <c r="G210" t="n">
-        <v>1.59537434577942</v>
+        <v>1.59537446498871</v>
       </c>
       <c r="H210" t="n">
         <v>7151</v>
@@ -6604,7 +6604,7 @@
         <v>1.91299998760223</v>
       </c>
       <c r="G215" t="n">
-        <v>1.56751465797424</v>
+        <v>1.56751477718353</v>
       </c>
       <c r="H215" t="n">
         <v>8016</v>
@@ -6633,7 +6633,7 @@
         <v>1.91600000858307</v>
       </c>
       <c r="G216" t="n">
-        <v>1.56997299194336</v>
+        <v>1.56997311115265</v>
       </c>
       <c r="H216" t="n">
         <v>8053</v>
@@ -6662,7 +6662,7 @@
         <v>1.91199994087219</v>
       </c>
       <c r="G217" t="n">
-        <v>1.56669533252716</v>
+        <v>1.56669545173645</v>
       </c>
       <c r="H217" t="n">
         <v>1680</v>
@@ -6749,7 +6749,7 @@
         <v>1.95700001716614</v>
       </c>
       <c r="G220" t="n">
-        <v>1.60356843471527</v>
+        <v>1.60356855392456</v>
       </c>
       <c r="H220" t="n">
         <v>5560</v>
@@ -6952,7 +6952,7 @@
         <v>1.8860000371933</v>
       </c>
       <c r="G227" t="n">
-        <v>1.54539108276367</v>
+        <v>1.54539084434509</v>
       </c>
       <c r="H227" t="n">
         <v>11268</v>
@@ -6981,7 +6981,7 @@
         <v>1.67999994754791</v>
       </c>
       <c r="G228" t="n">
-        <v>1.37659418582916</v>
+        <v>1.37659430503845</v>
       </c>
       <c r="H228" t="n">
         <v>40640</v>
@@ -7010,7 +7010,7 @@
         <v>1.72399997711182</v>
       </c>
       <c r="G229" t="n">
-        <v>1.4126478433609</v>
+        <v>1.41264796257019</v>
       </c>
       <c r="H229" t="n">
         <v>18656</v>
@@ -7039,7 +7039,7 @@
         <v>1.70200002193451</v>
       </c>
       <c r="G230" t="n">
-        <v>1.39462101459503</v>
+        <v>1.39462125301361</v>
       </c>
       <c r="H230" t="n">
         <v>23064</v>
@@ -7126,7 +7126,7 @@
         <v>1.87199997901917</v>
       </c>
       <c r="G233" t="n">
-        <v>1.53391921520233</v>
+        <v>1.53391945362091</v>
       </c>
       <c r="H233" t="n">
         <v>4000</v>
@@ -7155,7 +7155,7 @@
         <v>1.96800005435944</v>
       </c>
       <c r="G234" t="n">
-        <v>1.6125819683075</v>
+        <v>1.61258172988892</v>
       </c>
       <c r="H234" t="n">
         <v>5088</v>
@@ -7358,7 +7358,7 @@
         <v>1.84500002861023</v>
       </c>
       <c r="G241" t="n">
-        <v>1.51179552078247</v>
+        <v>1.51179540157318</v>
       </c>
       <c r="H241" t="n">
         <v>3642</v>
@@ -7387,7 +7387,7 @@
         <v>1.89800000190735</v>
       </c>
       <c r="G242" t="n">
-        <v>1.5552237033844</v>
+        <v>1.55522358417511</v>
       </c>
       <c r="H242" t="n">
         <v>6374</v>
@@ -7416,7 +7416,7 @@
         <v>1.89800000190735</v>
       </c>
       <c r="G243" t="n">
-        <v>1.5552237033844</v>
+        <v>1.55522358417511</v>
       </c>
       <c r="H243" t="n">
         <v>3380</v>
@@ -7445,7 +7445,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G244" t="n">
-        <v>1.56505656242371</v>
+        <v>1.565056681633</v>
       </c>
       <c r="H244" t="n">
         <v>627</v>
@@ -7590,7 +7590,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G249" t="n">
-        <v>1.55686259269714</v>
+        <v>1.55686247348785</v>
       </c>
       <c r="H249" t="n">
         <v>17229</v>
@@ -7851,7 +7851,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G258" t="n">
-        <v>1.53228056430817</v>
+        <v>1.53228044509888</v>
       </c>
       <c r="H258" t="n">
         <v>900</v>
@@ -7880,7 +7880,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G259" t="n">
-        <v>1.53228056430817</v>
+        <v>1.53228044509888</v>
       </c>
       <c r="H259" t="n">
         <v>10450</v>
@@ -7909,7 +7909,7 @@
         <v>1.84200000762939</v>
       </c>
       <c r="G260" t="n">
-        <v>1.50933718681335</v>
+        <v>1.50933730602264</v>
       </c>
       <c r="H260" t="n">
         <v>15155</v>
@@ -7967,7 +7967,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G262" t="n">
-        <v>1.5076984167099</v>
+        <v>1.50769853591919</v>
       </c>
       <c r="H262" t="n">
         <v>110</v>
@@ -7996,7 +7996,7 @@
         <v>1.84200000762939</v>
       </c>
       <c r="G263" t="n">
-        <v>1.50933718681335</v>
+        <v>1.50933730602264</v>
       </c>
       <c r="H263" t="n">
         <v>8077</v>
@@ -8025,7 +8025,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G264" t="n">
-        <v>1.5076984167099</v>
+        <v>1.50769853591919</v>
       </c>
       <c r="H264" t="n">
         <v>10670</v>
@@ -8054,7 +8054,7 @@
         <v>1.83399999141693</v>
       </c>
       <c r="G265" t="n">
-        <v>1.50278198719025</v>
+        <v>1.50278210639954</v>
       </c>
       <c r="H265" t="n">
         <v>16963</v>
@@ -8083,7 +8083,7 @@
         <v>1.82500004768372</v>
       </c>
       <c r="G266" t="n">
-        <v>1.49540746212006</v>
+        <v>1.49540758132935</v>
       </c>
       <c r="H266" t="n">
         <v>6063</v>
@@ -8170,7 +8170,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G269" t="n">
-        <v>1.57325053215027</v>
+        <v>1.57325065135956</v>
       </c>
       <c r="H269" t="n">
         <v>3905</v>
@@ -8228,7 +8228,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G271" t="n">
-        <v>1.55686259269714</v>
+        <v>1.55686247348785</v>
       </c>
       <c r="H271" t="n">
         <v>15130</v>
@@ -8315,7 +8315,7 @@
         <v>1.95700001716614</v>
       </c>
       <c r="G274" t="n">
-        <v>1.60356843471527</v>
+        <v>1.60356855392456</v>
       </c>
       <c r="H274" t="n">
         <v>6671</v>
@@ -8344,7 +8344,7 @@
         <v>1.96800005435944</v>
       </c>
       <c r="G275" t="n">
-        <v>1.6125819683075</v>
+        <v>1.61258172988892</v>
       </c>
       <c r="H275" t="n">
         <v>19986</v>
@@ -8460,7 +8460,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G279" t="n">
-        <v>1.53228056430817</v>
+        <v>1.53228044509888</v>
       </c>
       <c r="H279" t="n">
         <v>9806</v>
@@ -8489,7 +8489,7 @@
         <v>1.9190000295639</v>
       </c>
       <c r="G280" t="n">
-        <v>1.57243120670319</v>
+        <v>1.57243132591248</v>
       </c>
       <c r="H280" t="n">
         <v>3432</v>
@@ -8518,7 +8518,7 @@
         <v>1.93700003623962</v>
       </c>
       <c r="G281" t="n">
-        <v>1.58718037605286</v>
+        <v>1.58718049526215</v>
       </c>
       <c r="H281" t="n">
         <v>5183</v>
@@ -8547,7 +8547,7 @@
         <v>1.88699996471405</v>
       </c>
       <c r="G282" t="n">
-        <v>1.54621028900146</v>
+        <v>1.54621040821075</v>
       </c>
       <c r="H282" t="n">
         <v>3939</v>
@@ -8605,7 +8605,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G284" t="n">
-        <v>1.55686259269714</v>
+        <v>1.55686247348785</v>
       </c>
       <c r="H284" t="n">
         <v>6242</v>
@@ -8634,7 +8634,7 @@
         <v>1.93799996376038</v>
       </c>
       <c r="G285" t="n">
-        <v>1.58799970149994</v>
+        <v>1.58799982070923</v>
       </c>
       <c r="H285" t="n">
         <v>2632</v>
@@ -8663,7 +8663,7 @@
         <v>1.87300002574921</v>
       </c>
       <c r="G286" t="n">
-        <v>1.5347386598587</v>
+        <v>1.53473877906799</v>
       </c>
       <c r="H286" t="n">
         <v>168</v>
@@ -8721,7 +8721,7 @@
         <v>1.88699996471405</v>
       </c>
       <c r="G288" t="n">
-        <v>1.54621028900146</v>
+        <v>1.54621040821075</v>
       </c>
       <c r="H288" t="n">
         <v>1302</v>
@@ -8779,7 +8779,7 @@
         <v>1.88800001144409</v>
       </c>
       <c r="G290" t="n">
-        <v>1.54702961444855</v>
+        <v>1.54702973365784</v>
       </c>
       <c r="H290" t="n">
         <v>3926</v>
@@ -8808,7 +8808,7 @@
         <v>1.88800001144409</v>
       </c>
       <c r="G291" t="n">
-        <v>1.54702961444855</v>
+        <v>1.54702973365784</v>
       </c>
       <c r="H291" t="n">
         <v>0</v>
@@ -8837,7 +8837,7 @@
         <v>1.87800002098083</v>
       </c>
       <c r="G292" t="n">
-        <v>1.53883588314056</v>
+        <v>1.53883564472198</v>
       </c>
       <c r="H292" t="n">
         <v>1219</v>
@@ -8866,7 +8866,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G293" t="n">
-        <v>1.56505656242371</v>
+        <v>1.565056681633</v>
       </c>
       <c r="H293" t="n">
         <v>3832</v>
@@ -8924,7 +8924,7 @@
         <v>1.88900005817413</v>
       </c>
       <c r="G295" t="n">
-        <v>1.54784905910492</v>
+        <v>1.54784917831421</v>
       </c>
       <c r="H295" t="n">
         <v>658</v>
@@ -8953,7 +8953,7 @@
         <v>1.88900005817413</v>
       </c>
       <c r="G296" t="n">
-        <v>1.54784905910492</v>
+        <v>1.54784917831421</v>
       </c>
       <c r="H296" t="n">
         <v>0</v>
@@ -8982,7 +8982,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G297" t="n">
-        <v>1.55686259269714</v>
+        <v>1.55686247348785</v>
       </c>
       <c r="H297" t="n">
         <v>1280</v>
@@ -9011,7 +9011,7 @@
         <v>1.89499998092651</v>
       </c>
       <c r="G298" t="n">
-        <v>1.55276560783386</v>
+        <v>1.55276548862457</v>
       </c>
       <c r="H298" t="n">
         <v>1397</v>
@@ -9040,7 +9040,7 @@
         <v>1.89100003242493</v>
       </c>
       <c r="G299" t="n">
-        <v>1.54948794841766</v>
+        <v>1.54948806762695</v>
       </c>
       <c r="H299" t="n">
         <v>50</v>
@@ -9069,7 +9069,7 @@
         <v>1.87699997425079</v>
       </c>
       <c r="G300" t="n">
-        <v>1.53801643848419</v>
+        <v>1.5380163192749</v>
       </c>
       <c r="H300" t="n">
         <v>1972</v>
@@ -9098,7 +9098,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G301" t="n">
-        <v>1.53228056430817</v>
+        <v>1.53228044509888</v>
       </c>
       <c r="H301" t="n">
         <v>3558</v>
@@ -9156,7 +9156,7 @@
         <v>1.89100003242493</v>
       </c>
       <c r="G303" t="n">
-        <v>1.54948794841766</v>
+        <v>1.54948806762695</v>
       </c>
       <c r="H303" t="n">
         <v>4699</v>
@@ -9214,7 +9214,7 @@
         <v>1.87899994850159</v>
       </c>
       <c r="G305" t="n">
-        <v>1.53965508937836</v>
+        <v>1.53965520858765</v>
       </c>
       <c r="H305" t="n">
         <v>5851</v>
@@ -9330,7 +9330,7 @@
         <v>2</v>
       </c>
       <c r="G309" t="n">
-        <v>1.63880264759064</v>
+        <v>1.63880276679993</v>
       </c>
       <c r="H309" t="n">
         <v>57906</v>
@@ -9359,7 +9359,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G310" t="n">
-        <v>1.63060867786407</v>
+        <v>1.63060879707336</v>
       </c>
       <c r="H310" t="n">
         <v>16096</v>
@@ -9388,7 +9388,7 @@
         <v>2.01600003242493</v>
       </c>
       <c r="G311" t="n">
-        <v>1.65191316604614</v>
+        <v>1.65191304683685</v>
       </c>
       <c r="H311" t="n">
         <v>43485</v>
@@ -9446,7 +9446,7 @@
         <v>2.06599998474121</v>
       </c>
       <c r="G313" t="n">
-        <v>1.69288325309753</v>
+        <v>1.69288313388824</v>
       </c>
       <c r="H313" t="n">
         <v>12262</v>
@@ -9475,7 +9475,7 @@
         <v>2.04200005531311</v>
       </c>
       <c r="G314" t="n">
-        <v>1.67321765422821</v>
+        <v>1.67321753501892</v>
       </c>
       <c r="H314" t="n">
         <v>5821</v>
@@ -9504,7 +9504,7 @@
         <v>2.01799988746643</v>
       </c>
       <c r="G315" t="n">
-        <v>1.6535519361496</v>
+        <v>1.65355169773102</v>
       </c>
       <c r="H315" t="n">
         <v>15632</v>
@@ -9533,7 +9533,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G316" t="n">
-        <v>1.65519058704376</v>
+        <v>1.65519070625305</v>
       </c>
       <c r="H316" t="n">
         <v>11483</v>
@@ -9591,7 +9591,7 @@
         <v>2.29800009727478</v>
       </c>
       <c r="G318" t="n">
-        <v>1.88298451900482</v>
+        <v>1.88298428058624</v>
       </c>
       <c r="H318" t="n">
         <v>94367</v>
@@ -9620,7 +9620,7 @@
         <v>2.22199988365173</v>
       </c>
       <c r="G319" t="n">
-        <v>1.82070970535278</v>
+        <v>1.82070982456207</v>
       </c>
       <c r="H319" t="n">
         <v>37358</v>
@@ -9649,7 +9649,7 @@
         <v>2.23200011253357</v>
       </c>
       <c r="G320" t="n">
-        <v>1.82890391349792</v>
+        <v>1.82890403270721</v>
       </c>
       <c r="H320" t="n">
         <v>71318</v>
@@ -9678,7 +9678,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G321" t="n">
-        <v>1.78629517555237</v>
+        <v>1.78629505634308</v>
       </c>
       <c r="H321" t="n">
         <v>16351</v>
@@ -9707,7 +9707,7 @@
         <v>2.21799993515015</v>
       </c>
       <c r="G322" t="n">
-        <v>1.81743204593658</v>
+        <v>1.81743216514587</v>
       </c>
       <c r="H322" t="n">
         <v>3920</v>
@@ -9736,7 +9736,7 @@
         <v>2.21600008010864</v>
       </c>
       <c r="G323" t="n">
-        <v>1.81579327583313</v>
+        <v>1.81579339504242</v>
       </c>
       <c r="H323" t="n">
         <v>40297</v>
@@ -9765,7 +9765,7 @@
         <v>2.17199993133545</v>
       </c>
       <c r="G324" t="n">
-        <v>1.77973961830139</v>
+        <v>1.77973973751068</v>
       </c>
       <c r="H324" t="n">
         <v>11729</v>
@@ -9794,7 +9794,7 @@
         <v>2.29399991035461</v>
       </c>
       <c r="G325" t="n">
-        <v>1.87970674037933</v>
+        <v>1.87970662117004</v>
       </c>
       <c r="H325" t="n">
         <v>82545</v>
@@ -9881,7 +9881,7 @@
         <v>2.19799995422363</v>
       </c>
       <c r="G328" t="n">
-        <v>1.80104422569275</v>
+        <v>1.80104410648346</v>
       </c>
       <c r="H328" t="n">
         <v>10476</v>
@@ -9910,7 +9910,7 @@
         <v>2.2260000705719</v>
       </c>
       <c r="G329" t="n">
-        <v>1.82398760318756</v>
+        <v>1.82398748397827</v>
       </c>
       <c r="H329" t="n">
         <v>4573</v>
@@ -9939,7 +9939,7 @@
         <v>2.21600008010864</v>
       </c>
       <c r="G330" t="n">
-        <v>1.81579327583313</v>
+        <v>1.81579339504242</v>
       </c>
       <c r="H330" t="n">
         <v>2603</v>
@@ -9968,7 +9968,7 @@
         <v>2.19799995422363</v>
       </c>
       <c r="G331" t="n">
-        <v>1.80104422569275</v>
+        <v>1.80104410648346</v>
       </c>
       <c r="H331" t="n">
         <v>14355</v>
@@ -10026,7 +10026,7 @@
         <v>2.10800004005432</v>
       </c>
       <c r="G333" t="n">
-        <v>1.72729814052582</v>
+        <v>1.72729802131653</v>
       </c>
       <c r="H333" t="n">
         <v>5276</v>
@@ -10055,7 +10055,7 @@
         <v>2.13199996948242</v>
       </c>
       <c r="G334" t="n">
-        <v>1.74696362018585</v>
+        <v>1.74696350097656</v>
       </c>
       <c r="H334" t="n">
         <v>2476</v>
@@ -10084,7 +10084,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G335" t="n">
-        <v>1.7289365530014</v>
+        <v>1.72893679141998</v>
       </c>
       <c r="H335" t="n">
         <v>3195</v>
@@ -10113,7 +10113,7 @@
         <v>2.15199995040894</v>
       </c>
       <c r="G336" t="n">
-        <v>1.76335155963898</v>
+        <v>1.76335167884827</v>
       </c>
       <c r="H336" t="n">
         <v>6305</v>
@@ -10142,7 +10142,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G337" t="n">
-        <v>1.8026829957962</v>
+        <v>1.80268323421478</v>
       </c>
       <c r="H337" t="n">
         <v>8773</v>
@@ -10171,7 +10171,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G338" t="n">
-        <v>1.8026829957962</v>
+        <v>1.80268323421478</v>
       </c>
       <c r="H338" t="n">
         <v>13339</v>
@@ -10287,7 +10287,7 @@
         <v>2.20799994468689</v>
       </c>
       <c r="G342" t="n">
-        <v>1.80923795700073</v>
+        <v>1.80923807621002</v>
       </c>
       <c r="H342" t="n">
         <v>10083</v>
@@ -10461,7 +10461,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G348" t="n">
-        <v>1.87642896175385</v>
+        <v>1.87642884254456</v>
       </c>
       <c r="H348" t="n">
         <v>15563</v>
@@ -10490,7 +10490,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G349" t="n">
-        <v>1.88462316989899</v>
+        <v>1.8846230506897</v>
       </c>
       <c r="H349" t="n">
         <v>33981</v>
@@ -10519,7 +10519,7 @@
         <v>2.31800007820129</v>
       </c>
       <c r="G350" t="n">
-        <v>1.89937222003937</v>
+        <v>1.89937257766724</v>
       </c>
       <c r="H350" t="n">
         <v>4160</v>
@@ -10548,7 +10548,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G351" t="n">
-        <v>1.91739904880524</v>
+        <v>1.91739892959595</v>
       </c>
       <c r="H351" t="n">
         <v>6240</v>
@@ -10577,7 +10577,7 @@
         <v>2.25600004196167</v>
       </c>
       <c r="G352" t="n">
-        <v>1.84856951236725</v>
+        <v>1.84856939315796</v>
       </c>
       <c r="H352" t="n">
         <v>9093</v>
@@ -10635,7 +10635,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G354" t="n">
-        <v>1.86823499202728</v>
+        <v>1.86823523044586</v>
       </c>
       <c r="H354" t="n">
         <v>9851</v>
@@ -10693,7 +10693,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G356" t="n">
-        <v>1.93679428100586</v>
+        <v>1.93679416179657</v>
       </c>
       <c r="H356" t="n">
         <v>8052</v>
@@ -10751,7 +10751,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G358" t="n">
-        <v>1.97107350826263</v>
+        <v>1.97107362747192</v>
       </c>
       <c r="H358" t="n">
         <v>23455</v>
@@ -10780,7 +10780,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G359" t="n">
-        <v>1.97107350826263</v>
+        <v>1.97107362747192</v>
       </c>
       <c r="H359" t="n">
         <v>18785</v>
@@ -10867,7 +10867,7 @@
         <v>2.26799988746643</v>
       </c>
       <c r="G362" t="n">
-        <v>1.94365000724792</v>
+        <v>1.94364988803864</v>
       </c>
       <c r="H362" t="n">
         <v>9505</v>
@@ -10896,7 +10896,7 @@
         <v>2.28600001335144</v>
       </c>
       <c r="G363" t="n">
-        <v>1.95907580852509</v>
+        <v>1.9590756893158</v>
       </c>
       <c r="H363" t="n">
         <v>13959</v>
@@ -10925,7 +10925,7 @@
         <v>2.28600001335144</v>
       </c>
       <c r="G364" t="n">
-        <v>1.95907580852509</v>
+        <v>1.9590756893158</v>
       </c>
       <c r="H364" t="n">
         <v>0</v>
@@ -10954,7 +10954,7 @@
         <v>2.2960000038147</v>
       </c>
       <c r="G365" t="n">
-        <v>1.9676456451416</v>
+        <v>1.96764576435089</v>
       </c>
       <c r="H365" t="n">
         <v>6191</v>
@@ -11070,7 +11070,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G369" t="n">
-        <v>1.95393407344818</v>
+        <v>1.95393395423889</v>
       </c>
       <c r="H369" t="n">
         <v>20269</v>
@@ -11099,7 +11099,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G370" t="n">
-        <v>1.95393407344818</v>
+        <v>1.95393395423889</v>
       </c>
       <c r="H370" t="n">
         <v>0</v>
@@ -11244,7 +11244,7 @@
         <v>2.18400001525879</v>
       </c>
       <c r="G375" t="n">
-        <v>1.8716629743576</v>
+        <v>1.87166285514832</v>
       </c>
       <c r="H375" t="n">
         <v>10669</v>
@@ -11273,7 +11273,7 @@
         <v>2.25200009346008</v>
       </c>
       <c r="G376" t="n">
-        <v>1.92993819713593</v>
+        <v>1.92993831634521</v>
       </c>
       <c r="H376" t="n">
         <v>2547</v>
@@ -11766,7 +11766,7 @@
         <v>2.2960000038147</v>
       </c>
       <c r="G393" t="n">
-        <v>1.9676456451416</v>
+        <v>1.96764576435089</v>
       </c>
       <c r="H393" t="n">
         <v>11250</v>
@@ -11853,7 +11853,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G396" t="n">
-        <v>1.97107350826263</v>
+        <v>1.97107362747192</v>
       </c>
       <c r="H396" t="n">
         <v>2881</v>
@@ -11882,7 +11882,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G397" t="n">
-        <v>1.98821341991425</v>
+        <v>1.98821365833282</v>
       </c>
       <c r="H397" t="n">
         <v>4950</v>
@@ -11911,7 +11911,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G398" t="n">
-        <v>1.98821341991425</v>
+        <v>1.98821365833282</v>
       </c>
       <c r="H398" t="n">
         <v>1201</v>
@@ -11940,7 +11940,7 @@
         <v>2.31800007820129</v>
       </c>
       <c r="G399" t="n">
-        <v>1.98649966716766</v>
+        <v>1.98649954795837</v>
       </c>
       <c r="H399" t="n">
         <v>506</v>
@@ -12027,7 +12027,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G402" t="n">
-        <v>2.12533164024353</v>
+        <v>2.12533140182495</v>
       </c>
       <c r="H402" t="n">
         <v>107928</v>
@@ -12056,7 +12056,7 @@
         <v>2.43400001525879</v>
       </c>
       <c r="G403" t="n">
-        <v>2.0859100818634</v>
+        <v>2.08591032028198</v>
       </c>
       <c r="H403" t="n">
         <v>66474</v>
@@ -12085,7 +12085,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G404" t="n">
-        <v>2.05677270889282</v>
+        <v>2.05677247047424</v>
       </c>
       <c r="H404" t="n">
         <v>20365</v>
@@ -12259,7 +12259,7 @@
         <v>2.41799998283386</v>
       </c>
       <c r="G410" t="n">
-        <v>2.07219839096069</v>
+        <v>2.07219862937927</v>
       </c>
       <c r="H410" t="n">
         <v>1517</v>
@@ -12288,7 +12288,7 @@
         <v>2.41799998283386</v>
       </c>
       <c r="G411" t="n">
-        <v>2.07219839096069</v>
+        <v>2.07219862937927</v>
       </c>
       <c r="H411" t="n">
         <v>22152</v>
@@ -12317,7 +12317,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G412" t="n">
-        <v>2.12533164024353</v>
+        <v>2.12533140182495</v>
       </c>
       <c r="H412" t="n">
         <v>13189</v>
@@ -12346,7 +12346,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G413" t="n">
-        <v>2.13390135765076</v>
+        <v>2.13390159606934</v>
       </c>
       <c r="H413" t="n">
         <v>51781</v>
@@ -12520,7 +12520,7 @@
         <v>2.46799993515015</v>
       </c>
       <c r="G419" t="n">
-        <v>2.11504769325256</v>
+        <v>2.11504793167114</v>
       </c>
       <c r="H419" t="n">
         <v>13804</v>
@@ -12549,7 +12549,7 @@
         <v>2.46799993515015</v>
       </c>
       <c r="G420" t="n">
-        <v>2.11504769325256</v>
+        <v>2.11504793167114</v>
       </c>
       <c r="H420" t="n">
         <v>0</v>
@@ -12578,7 +12578,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G421" t="n">
-        <v>2.07391238212585</v>
+        <v>2.07391262054443</v>
       </c>
       <c r="H421" t="n">
         <v>13845</v>
@@ -12607,7 +12607,7 @@
         <v>2.44799995422363</v>
       </c>
       <c r="G422" t="n">
-        <v>2.09790802001953</v>
+        <v>2.09790778160095</v>
       </c>
       <c r="H422" t="n">
         <v>3874</v>
@@ -12665,7 +12665,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G424" t="n">
-        <v>2.07391238212585</v>
+        <v>2.07391262054443</v>
       </c>
       <c r="H424" t="n">
         <v>2466</v>
@@ -12723,7 +12723,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G426" t="n">
-        <v>2.08248233795166</v>
+        <v>2.08248209953308</v>
       </c>
       <c r="H426" t="n">
         <v>2302</v>
@@ -12752,7 +12752,7 @@
         <v>2.46799993515015</v>
       </c>
       <c r="G427" t="n">
-        <v>2.11504769325256</v>
+        <v>2.11504793167114</v>
       </c>
       <c r="H427" t="n">
         <v>15505</v>
@@ -12955,7 +12955,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G434" t="n">
-        <v>2.13390135765076</v>
+        <v>2.13390159606934</v>
       </c>
       <c r="H434" t="n">
         <v>13299</v>
@@ -13013,7 +13013,7 @@
         <v>2.39400005340576</v>
       </c>
       <c r="G436" t="n">
-        <v>2.05163049697876</v>
+        <v>2.05163073539734</v>
       </c>
       <c r="H436" t="n">
         <v>6502</v>
@@ -13042,7 +13042,7 @@
         <v>2.44799995422363</v>
       </c>
       <c r="G437" t="n">
-        <v>2.09790802001953</v>
+        <v>2.09790778160095</v>
       </c>
       <c r="H437" t="n">
         <v>5750</v>
@@ -13071,7 +13071,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G438" t="n">
-        <v>2.08248233795166</v>
+        <v>2.08248209953308</v>
       </c>
       <c r="H438" t="n">
         <v>13950</v>
@@ -13100,7 +13100,7 @@
         <v>2.44799995422363</v>
       </c>
       <c r="G439" t="n">
-        <v>2.09790802001953</v>
+        <v>2.09790778160095</v>
       </c>
       <c r="H439" t="n">
         <v>10563</v>
@@ -13274,7 +13274,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G445" t="n">
-        <v>2.15961146354675</v>
+        <v>2.15961122512817</v>
       </c>
       <c r="H445" t="n">
         <v>3123</v>
@@ -13303,7 +13303,7 @@
         <v>2.47199988365173</v>
       </c>
       <c r="G446" t="n">
-        <v>2.11847567558289</v>
+        <v>2.11847543716431</v>
       </c>
       <c r="H446" t="n">
         <v>7321</v>
@@ -13419,7 +13419,7 @@
         <v>2.4779999256134</v>
       </c>
       <c r="G450" t="n">
-        <v>2.12361764907837</v>
+        <v>2.12361741065979</v>
       </c>
       <c r="H450" t="n">
         <v>13080</v>
@@ -13448,7 +13448,7 @@
         <v>2.46399998664856</v>
       </c>
       <c r="G451" t="n">
-        <v>2.11161994934082</v>
+        <v>2.11161971092224</v>
       </c>
       <c r="H451" t="n">
         <v>6894</v>
@@ -13506,7 +13506,7 @@
         <v>2.46799993515015</v>
       </c>
       <c r="G453" t="n">
-        <v>2.11504769325256</v>
+        <v>2.11504793167114</v>
       </c>
       <c r="H453" t="n">
         <v>3583</v>
@@ -13564,7 +13564,7 @@
         <v>2.46399998664856</v>
       </c>
       <c r="G455" t="n">
-        <v>2.11161994934082</v>
+        <v>2.11161971092224</v>
       </c>
       <c r="H455" t="n">
         <v>1095</v>
@@ -13593,7 +13593,7 @@
         <v>2.4779999256134</v>
       </c>
       <c r="G456" t="n">
-        <v>2.12361764907837</v>
+        <v>2.12361741065979</v>
       </c>
       <c r="H456" t="n">
         <v>1700</v>
@@ -13680,7 +13680,7 @@
         <v>2.51799988746643</v>
       </c>
       <c r="G459" t="n">
-        <v>2.15789723396301</v>
+        <v>2.15789699554443</v>
       </c>
       <c r="H459" t="n">
         <v>1</v>
@@ -13709,7 +13709,7 @@
         <v>2.51600003242493</v>
       </c>
       <c r="G460" t="n">
-        <v>2.15618300437927</v>
+        <v>2.15618324279785</v>
       </c>
       <c r="H460" t="n">
         <v>633</v>
@@ -13796,7 +13796,7 @@
         <v>2.46399998664856</v>
       </c>
       <c r="G463" t="n">
-        <v>2.11161994934082</v>
+        <v>2.11161971092224</v>
       </c>
       <c r="H463" t="n">
         <v>801</v>
@@ -13825,7 +13825,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G464" t="n">
-        <v>2.13390135765076</v>
+        <v>2.13390159606934</v>
       </c>
       <c r="H464" t="n">
         <v>2100</v>
@@ -13883,7 +13883,7 @@
         <v>2.49600005149841</v>
       </c>
       <c r="G466" t="n">
-        <v>2.13904356956482</v>
+        <v>2.13904333114624</v>
       </c>
       <c r="H466" t="n">
         <v>763</v>
@@ -13912,7 +13912,7 @@
         <v>2.49600005149841</v>
       </c>
       <c r="G467" t="n">
-        <v>2.13904356956482</v>
+        <v>2.13904333114624</v>
       </c>
       <c r="H467" t="n">
         <v>1434</v>
@@ -13941,7 +13941,7 @@
         <v>2.51600003242493</v>
       </c>
       <c r="G468" t="n">
-        <v>2.15618300437927</v>
+        <v>2.15618324279785</v>
       </c>
       <c r="H468" t="n">
         <v>1033</v>
@@ -13970,7 +13970,7 @@
         <v>2.51799988746643</v>
       </c>
       <c r="G469" t="n">
-        <v>2.15789723396301</v>
+        <v>2.15789699554443</v>
       </c>
       <c r="H469" t="n">
         <v>3027</v>
@@ -14057,7 +14057,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G472" t="n">
-        <v>2.12533164024353</v>
+        <v>2.12533140182495</v>
       </c>
       <c r="H472" t="n">
         <v>8551</v>
@@ -14086,7 +14086,7 @@
         <v>2.53800010681152</v>
       </c>
       <c r="G473" t="n">
-        <v>2.17503690719604</v>
+        <v>2.17503714561462</v>
       </c>
       <c r="H473" t="n">
         <v>2512</v>
@@ -14144,7 +14144,7 @@
         <v>2.51799988746643</v>
       </c>
       <c r="G475" t="n">
-        <v>2.15789723396301</v>
+        <v>2.15789699554443</v>
       </c>
       <c r="H475" t="n">
         <v>1188</v>
@@ -14289,7 +14289,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G480" t="n">
-        <v>2.05677270889282</v>
+        <v>2.05677247047424</v>
       </c>
       <c r="H480" t="n">
         <v>6507</v>
@@ -14318,7 +14318,7 @@
         <v>2.37199997901917</v>
       </c>
       <c r="G481" t="n">
-        <v>2.03277659416199</v>
+        <v>2.03277683258057</v>
       </c>
       <c r="H481" t="n">
         <v>6951</v>
@@ -14463,7 +14463,7 @@
         <v>2.37199997901917</v>
       </c>
       <c r="G486" t="n">
-        <v>2.03277659416199</v>
+        <v>2.03277683258057</v>
       </c>
       <c r="H486" t="n">
         <v>1218</v>
@@ -14579,7 +14579,7 @@
         <v>2.49600005149841</v>
       </c>
       <c r="G490" t="n">
-        <v>2.13904356956482</v>
+        <v>2.13904333114624</v>
       </c>
       <c r="H490" t="n">
         <v>1802</v>
@@ -14608,7 +14608,7 @@
         <v>2.44799995422363</v>
       </c>
       <c r="G491" t="n">
-        <v>2.09790802001953</v>
+        <v>2.09790778160095</v>
       </c>
       <c r="H491" t="n">
         <v>2342</v>
@@ -14637,7 +14637,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G492" t="n">
-        <v>2.12533164024353</v>
+        <v>2.12533140182495</v>
       </c>
       <c r="H492" t="n">
         <v>182</v>
@@ -14724,7 +14724,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G495" t="n">
-        <v>2.12533164024353</v>
+        <v>2.12533140182495</v>
       </c>
       <c r="H495" t="n">
         <v>1145</v>
@@ -14869,7 +14869,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G500" t="n">
-        <v>2.08248233795166</v>
+        <v>2.08248209953308</v>
       </c>
       <c r="H500" t="n">
         <v>6624</v>
@@ -14985,7 +14985,7 @@
         <v>2.43199992179871</v>
       </c>
       <c r="G504" t="n">
-        <v>2.08419632911682</v>
+        <v>2.08419609069824</v>
       </c>
       <c r="H504" t="n">
         <v>6818</v>
@@ -15014,7 +15014,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G505" t="n">
-        <v>2.08248233795166</v>
+        <v>2.08248209953308</v>
       </c>
       <c r="H505" t="n">
         <v>608</v>
@@ -15043,7 +15043,7 @@
         <v>2.43199992179871</v>
       </c>
       <c r="G506" t="n">
-        <v>2.08419632911682</v>
+        <v>2.08419609069824</v>
       </c>
       <c r="H506" t="n">
         <v>1196</v>
@@ -15101,7 +15101,7 @@
         <v>2.44799995422363</v>
       </c>
       <c r="G508" t="n">
-        <v>2.09790802001953</v>
+        <v>2.09790778160095</v>
       </c>
       <c r="H508" t="n">
         <v>2286</v>
@@ -15130,7 +15130,7 @@
         <v>2.44799995422363</v>
       </c>
       <c r="G509" t="n">
-        <v>2.09790802001953</v>
+        <v>2.09790778160095</v>
       </c>
       <c r="H509" t="n">
         <v>0</v>
@@ -15275,7 +15275,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G514" t="n">
-        <v>2.07391238212585</v>
+        <v>2.07391262054443</v>
       </c>
       <c r="H514" t="n">
         <v>7736</v>
@@ -15304,7 +15304,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G515" t="n">
-        <v>2.05677270889282</v>
+        <v>2.05677247047424</v>
       </c>
       <c r="H515" t="n">
         <v>7000</v>
@@ -15333,7 +15333,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G516" t="n">
-        <v>2.08248233795166</v>
+        <v>2.08248209953308</v>
       </c>
       <c r="H516" t="n">
         <v>1125</v>
@@ -15420,7 +15420,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G519" t="n">
-        <v>2.08248233795166</v>
+        <v>2.08248209953308</v>
       </c>
       <c r="H519" t="n">
         <v>8541</v>
@@ -15449,7 +15449,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G520" t="n">
-        <v>2.08248233795166</v>
+        <v>2.08248209953308</v>
       </c>
       <c r="H520" t="n">
         <v>321</v>
@@ -15594,7 +15594,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G525" t="n">
-        <v>2.05677270889282</v>
+        <v>2.05677247047424</v>
       </c>
       <c r="H525" t="n">
         <v>398</v>
@@ -15623,7 +15623,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G526" t="n">
-        <v>2.05677270889282</v>
+        <v>2.05677247047424</v>
       </c>
       <c r="H526" t="n">
         <v>5700</v>
@@ -15768,7 +15768,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G531" t="n">
-        <v>2.07391238212585</v>
+        <v>2.07391262054443</v>
       </c>
       <c r="H531" t="n">
         <v>7994</v>
@@ -15797,7 +15797,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G532" t="n">
-        <v>2.07391238212585</v>
+        <v>2.07391262054443</v>
       </c>
       <c r="H532" t="n">
         <v>23272</v>
@@ -15826,7 +15826,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G533" t="n">
-        <v>2.07391238212585</v>
+        <v>2.07391262054443</v>
       </c>
       <c r="H533" t="n">
         <v>0</v>
@@ -15855,7 +15855,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G534" t="n">
-        <v>2.05677270889282</v>
+        <v>2.05677247047424</v>
       </c>
       <c r="H534" t="n">
         <v>361</v>
@@ -15884,7 +15884,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G535" t="n">
-        <v>2.05677270889282</v>
+        <v>2.05677247047424</v>
       </c>
       <c r="H535" t="n">
         <v>1190</v>
@@ -16029,7 +16029,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G540" t="n">
-        <v>2.05677270889282</v>
+        <v>2.05677247047424</v>
       </c>
       <c r="H540" t="n">
         <v>910</v>
@@ -16232,7 +16232,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G547" t="n">
-        <v>2.08248233795166</v>
+        <v>2.08248209953308</v>
       </c>
       <c r="H547" t="n">
         <v>3430</v>
@@ -16319,7 +16319,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G550" t="n">
-        <v>2.08248233795166</v>
+        <v>2.08248209953308</v>
       </c>
       <c r="H550" t="n">
         <v>678</v>
@@ -16406,7 +16406,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G553" t="n">
-        <v>2.08248233795166</v>
+        <v>2.08248209953308</v>
       </c>
       <c r="H553" t="n">
         <v>290</v>
@@ -16435,7 +16435,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G554" t="n">
-        <v>2.07391238212585</v>
+        <v>2.07391262054443</v>
       </c>
       <c r="H554" t="n">
         <v>1580</v>
@@ -16667,7 +16667,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G562" t="n">
-        <v>2.08248233795166</v>
+        <v>2.08248209953308</v>
       </c>
       <c r="H562" t="n">
         <v>10</v>
@@ -16696,7 +16696,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G563" t="n">
-        <v>2.08248233795166</v>
+        <v>2.08248209953308</v>
       </c>
       <c r="H563" t="n">
         <v>0</v>
@@ -16783,7 +16783,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G566" t="n">
-        <v>2.12533164024353</v>
+        <v>2.12533140182495</v>
       </c>
       <c r="H566" t="n">
         <v>11930</v>
@@ -16870,7 +16870,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G569" t="n">
-        <v>2.07391238212585</v>
+        <v>2.07391262054443</v>
       </c>
       <c r="H569" t="n">
         <v>6674</v>
@@ -17102,7 +17102,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G577" t="n">
-        <v>2.13390135765076</v>
+        <v>2.13390159606934</v>
       </c>
       <c r="H577" t="n">
         <v>18463</v>
@@ -17189,7 +17189,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G580" t="n">
-        <v>2.13390135765076</v>
+        <v>2.13390159606934</v>
       </c>
       <c r="H580" t="n">
         <v>5118</v>
@@ -17247,7 +17247,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G582" t="n">
-        <v>2.1681809425354</v>
+        <v>2.16818118095398</v>
       </c>
       <c r="H582" t="n">
         <v>1455</v>
@@ -17276,7 +17276,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G583" t="n">
-        <v>2.1681809425354</v>
+        <v>2.16818118095398</v>
       </c>
       <c r="H583" t="n">
         <v>2779</v>
@@ -17305,7 +17305,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G584" t="n">
-        <v>2.15961146354675</v>
+        <v>2.15961122512817</v>
       </c>
       <c r="H584" t="n">
         <v>21594</v>
@@ -17334,7 +17334,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G585" t="n">
-        <v>2.15961146354675</v>
+        <v>2.15961122512817</v>
       </c>
       <c r="H585" t="n">
         <v>4446</v>
@@ -17363,7 +17363,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G586" t="n">
-        <v>2.1681809425354</v>
+        <v>2.16818118095398</v>
       </c>
       <c r="H586" t="n">
         <v>6585</v>
@@ -17392,7 +17392,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G587" t="n">
-        <v>2.15961146354675</v>
+        <v>2.15961122512817</v>
       </c>
       <c r="H587" t="n">
         <v>17966</v>
@@ -17450,7 +17450,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G589" t="n">
-        <v>2.15961146354675</v>
+        <v>2.15961122512817</v>
       </c>
       <c r="H589" t="n">
         <v>5280</v>
@@ -17537,7 +17537,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G592" t="n">
-        <v>2.29672932624817</v>
+        <v>2.29672956466675</v>
       </c>
       <c r="H592" t="n">
         <v>109129</v>
@@ -17566,7 +17566,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G593" t="n">
-        <v>2.29672932624817</v>
+        <v>2.29672956466675</v>
       </c>
       <c r="H593" t="n">
         <v>67369</v>
@@ -17624,7 +17624,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G595" t="n">
-        <v>2.32243919372559</v>
+        <v>2.32243895530701</v>
       </c>
       <c r="H595" t="n">
         <v>49282</v>
@@ -17798,7 +17798,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G601" t="n">
-        <v>2.48526692390442</v>
+        <v>2.48526668548584</v>
       </c>
       <c r="H601" t="n">
         <v>7487</v>
@@ -17914,7 +17914,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G605" t="n">
-        <v>2.596675157547</v>
+        <v>2.59667539596558</v>
       </c>
       <c r="H605" t="n">
         <v>23766</v>
@@ -17972,7 +17972,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G607" t="n">
-        <v>2.55382585525513</v>
+        <v>2.55382561683655</v>
       </c>
       <c r="H607" t="n">
         <v>22011</v>
@@ -18117,7 +18117,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G612" t="n">
-        <v>2.55382585525513</v>
+        <v>2.55382561683655</v>
       </c>
       <c r="H612" t="n">
         <v>19084</v>
@@ -18146,7 +18146,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G613" t="n">
-        <v>2.52694368362427</v>
+        <v>2.52694344520569</v>
       </c>
       <c r="H613" t="n">
         <v>7434</v>
@@ -18233,7 +18233,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G616" t="n">
-        <v>2.50006103515625</v>
+        <v>2.50006127357483</v>
       </c>
       <c r="H616" t="n">
         <v>13877</v>
@@ -18436,7 +18436,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G623" t="n">
-        <v>2.55382585525513</v>
+        <v>2.55382561683655</v>
       </c>
       <c r="H623" t="n">
         <v>4765</v>
@@ -18465,7 +18465,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G624" t="n">
-        <v>2.57174730300903</v>
+        <v>2.57174754142761</v>
       </c>
       <c r="H624" t="n">
         <v>2231</v>
@@ -18494,7 +18494,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G625" t="n">
-        <v>2.57174730300903</v>
+        <v>2.57174754142761</v>
       </c>
       <c r="H625" t="n">
         <v>3450</v>
@@ -18523,7 +18523,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G626" t="n">
-        <v>2.55382585525513</v>
+        <v>2.55382561683655</v>
       </c>
       <c r="H626" t="n">
         <v>2320</v>
@@ -18755,7 +18755,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G634" t="n">
-        <v>2.5090217590332</v>
+        <v>2.50902199745178</v>
       </c>
       <c r="H634" t="n">
         <v>5371</v>
@@ -18842,7 +18842,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G637" t="n">
-        <v>2.55382585525513</v>
+        <v>2.55382561683655</v>
       </c>
       <c r="H637" t="n">
         <v>198</v>
@@ -18871,7 +18871,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G638" t="n">
-        <v>2.55382585525513</v>
+        <v>2.55382561683655</v>
       </c>
       <c r="H638" t="n">
         <v>0</v>
@@ -19045,7 +19045,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G644" t="n">
-        <v>2.52694368362427</v>
+        <v>2.52694344520569</v>
       </c>
       <c r="H644" t="n">
         <v>3990</v>
@@ -19219,7 +19219,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G650" t="n">
-        <v>2.5090217590332</v>
+        <v>2.50902199745178</v>
       </c>
       <c r="H650" t="n">
         <v>6483</v>
@@ -19306,7 +19306,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G653" t="n">
-        <v>2.52694368362427</v>
+        <v>2.52694344520569</v>
       </c>
       <c r="H653" t="n">
         <v>3121</v>
@@ -19364,7 +19364,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G655" t="n">
-        <v>2.55382585525513</v>
+        <v>2.55382561683655</v>
       </c>
       <c r="H655" t="n">
         <v>1321</v>
@@ -19422,7 +19422,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G657" t="n">
-        <v>2.7599241733551</v>
+        <v>2.75992441177368</v>
       </c>
       <c r="H657" t="n">
         <v>25425</v>
@@ -19509,7 +19509,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G660" t="n">
-        <v>2.7599241733551</v>
+        <v>2.75992441177368</v>
       </c>
       <c r="H660" t="n">
         <v>11991</v>
@@ -19538,7 +19538,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G661" t="n">
-        <v>2.7420027256012</v>
+        <v>2.74200248718262</v>
       </c>
       <c r="H661" t="n">
         <v>11421</v>
@@ -19567,7 +19567,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G662" t="n">
-        <v>2.7420027256012</v>
+        <v>2.74200248718262</v>
       </c>
       <c r="H662" t="n">
         <v>2357</v>
@@ -19596,7 +19596,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G663" t="n">
-        <v>2.7420027256012</v>
+        <v>2.74200248718262</v>
       </c>
       <c r="H663" t="n">
         <v>0</v>
@@ -19625,7 +19625,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G664" t="n">
-        <v>2.7420027256012</v>
+        <v>2.74200248718262</v>
       </c>
       <c r="H664" t="n">
         <v>3014</v>
@@ -19712,7 +19712,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G667" t="n">
-        <v>2.75096344947815</v>
+        <v>2.75096321105957</v>
       </c>
       <c r="H667" t="n">
         <v>2365</v>
@@ -19828,7 +19828,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G671" t="n">
-        <v>2.75096344947815</v>
+        <v>2.75096321105957</v>
       </c>
       <c r="H671" t="n">
         <v>1370</v>
@@ -19857,7 +19857,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G672" t="n">
-        <v>2.7420027256012</v>
+        <v>2.74200248718262</v>
       </c>
       <c r="H672" t="n">
         <v>508</v>
@@ -19886,7 +19886,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G673" t="n">
-        <v>2.7420027256012</v>
+        <v>2.74200248718262</v>
       </c>
       <c r="H673" t="n">
         <v>567</v>
@@ -20060,7 +20060,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G679" t="n">
-        <v>2.7420027256012</v>
+        <v>2.74200248718262</v>
       </c>
       <c r="H679" t="n">
         <v>345</v>
@@ -20147,7 +20147,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G682" t="n">
-        <v>2.75096344947815</v>
+        <v>2.75096321105957</v>
       </c>
       <c r="H682" t="n">
         <v>10777</v>
@@ -20321,7 +20321,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G688" t="n">
-        <v>2.75096344947815</v>
+        <v>2.75096321105957</v>
       </c>
       <c r="H688" t="n">
         <v>5155</v>
@@ -20379,7 +20379,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G690" t="n">
-        <v>2.69719862937927</v>
+        <v>2.69719886779785</v>
       </c>
       <c r="H690" t="n">
         <v>5352</v>
@@ -20437,7 +20437,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G692" t="n">
-        <v>2.7599241733551</v>
+        <v>2.75992441177368</v>
       </c>
       <c r="H692" t="n">
         <v>1966</v>
@@ -20582,7 +20582,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G697" t="n">
-        <v>2.75096344947815</v>
+        <v>2.75096321105957</v>
       </c>
       <c r="H697" t="n">
         <v>927</v>
@@ -20640,7 +20640,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G699" t="n">
-        <v>2.7599241733551</v>
+        <v>2.75992441177368</v>
       </c>
       <c r="H699" t="n">
         <v>7749</v>
@@ -20669,7 +20669,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G700" t="n">
-        <v>2.75096344947815</v>
+        <v>2.75096321105957</v>
       </c>
       <c r="H700" t="n">
         <v>3068</v>
@@ -20698,7 +20698,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G701" t="n">
-        <v>2.75096344947815</v>
+        <v>2.75096321105957</v>
       </c>
       <c r="H701" t="n">
         <v>1928</v>
@@ -20727,7 +20727,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G702" t="n">
-        <v>2.75096344947815</v>
+        <v>2.75096321105957</v>
       </c>
       <c r="H702" t="n">
         <v>0</v>
@@ -20814,7 +20814,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G705" t="n">
-        <v>2.69719862937927</v>
+        <v>2.69719886779785</v>
       </c>
       <c r="H705" t="n">
         <v>193</v>
@@ -20959,7 +20959,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G710" t="n">
-        <v>2.58070826530457</v>
+        <v>2.58070850372314</v>
       </c>
       <c r="H710" t="n">
         <v>9964</v>
@@ -20988,7 +20988,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G711" t="n">
-        <v>2.58070826530457</v>
+        <v>2.58070850372314</v>
       </c>
       <c r="H711" t="n">
         <v>401</v>
@@ -21017,7 +21017,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G712" t="n">
-        <v>2.55382585525513</v>
+        <v>2.55382561683655</v>
       </c>
       <c r="H712" t="n">
         <v>13458</v>
@@ -21162,7 +21162,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G717" t="n">
-        <v>2.58070826530457</v>
+        <v>2.58070850372314</v>
       </c>
       <c r="H717" t="n">
         <v>3201</v>
@@ -21191,7 +21191,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G718" t="n">
-        <v>2.57174730300903</v>
+        <v>2.57174754142761</v>
       </c>
       <c r="H718" t="n">
         <v>1700</v>
@@ -21539,7 +21539,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G730" t="n">
-        <v>2.607590675354</v>
+        <v>2.60759091377258</v>
       </c>
       <c r="H730" t="n">
         <v>5732</v>
@@ -21655,7 +21655,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G734" t="n">
-        <v>2.5090217590332</v>
+        <v>2.50902199745178</v>
       </c>
       <c r="H734" t="n">
         <v>700</v>
@@ -21713,7 +21713,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G736" t="n">
-        <v>2.5090217590332</v>
+        <v>2.50902199745178</v>
       </c>
       <c r="H736" t="n">
         <v>10571</v>
@@ -21771,7 +21771,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G738" t="n">
-        <v>2.57174730300903</v>
+        <v>2.57174754142761</v>
       </c>
       <c r="H738" t="n">
         <v>2354</v>
@@ -21829,7 +21829,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G740" t="n">
-        <v>2.5090217590332</v>
+        <v>2.50902199745178</v>
       </c>
       <c r="H740" t="n">
         <v>670</v>
@@ -21858,7 +21858,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G741" t="n">
-        <v>2.5090217590332</v>
+        <v>2.50902199745178</v>
       </c>
       <c r="H741" t="n">
         <v>0</v>
@@ -21887,7 +21887,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G742" t="n">
-        <v>2.5090217590332</v>
+        <v>2.50902199745178</v>
       </c>
       <c r="H742" t="n">
         <v>0</v>
@@ -21916,7 +21916,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G743" t="n">
-        <v>2.5090217590332</v>
+        <v>2.50902199745178</v>
       </c>
       <c r="H743" t="n">
         <v>300</v>
@@ -21945,7 +21945,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G744" t="n">
-        <v>2.5090217590332</v>
+        <v>2.50902199745178</v>
       </c>
       <c r="H744" t="n">
         <v>2716</v>
@@ -21974,7 +21974,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G745" t="n">
-        <v>2.5090217590332</v>
+        <v>2.50902199745178</v>
       </c>
       <c r="H745" t="n">
         <v>430</v>
@@ -22003,7 +22003,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G746" t="n">
-        <v>2.41941428184509</v>
+        <v>2.41941404342651</v>
       </c>
       <c r="H746" t="n">
         <v>10198</v>
@@ -22032,7 +22032,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G747" t="n">
-        <v>2.50006103515625</v>
+        <v>2.50006127357483</v>
       </c>
       <c r="H747" t="n">
         <v>11156</v>
@@ -22061,7 +22061,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G748" t="n">
-        <v>2.57174730300903</v>
+        <v>2.57174754142761</v>
       </c>
       <c r="H748" t="n">
         <v>2700</v>
@@ -22119,7 +22119,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G750" t="n">
-        <v>2.57174730300903</v>
+        <v>2.57174754142761</v>
       </c>
       <c r="H750" t="n">
         <v>1555</v>
@@ -22148,7 +22148,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G751" t="n">
-        <v>2.57174730300903</v>
+        <v>2.57174754142761</v>
       </c>
       <c r="H751" t="n">
         <v>0</v>
@@ -22177,7 +22177,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G752" t="n">
-        <v>2.57174730300903</v>
+        <v>2.57174754142761</v>
       </c>
       <c r="H752" t="n">
         <v>0</v>
@@ -22206,7 +22206,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G753" t="n">
-        <v>2.5090217590332</v>
+        <v>2.50902199745178</v>
       </c>
       <c r="H753" t="n">
         <v>4583</v>
@@ -22235,7 +22235,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G754" t="n">
-        <v>2.55382585525513</v>
+        <v>2.55382561683655</v>
       </c>
       <c r="H754" t="n">
         <v>1</v>
@@ -22264,7 +22264,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G755" t="n">
-        <v>2.55382585525513</v>
+        <v>2.55382561683655</v>
       </c>
       <c r="H755" t="n">
         <v>0</v>
@@ -22380,7 +22380,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G759" t="n">
-        <v>2.5090217590332</v>
+        <v>2.50902199745178</v>
       </c>
       <c r="H759" t="n">
         <v>2900</v>
@@ -22438,7 +22438,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G761" t="n">
-        <v>2.5090217590332</v>
+        <v>2.50902199745178</v>
       </c>
       <c r="H761" t="n">
         <v>2040</v>
@@ -22554,7 +22554,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G765" t="n">
-        <v>2.607590675354</v>
+        <v>2.60759091377258</v>
       </c>
       <c r="H765" t="n">
         <v>2167</v>
@@ -22699,7 +22699,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G770" t="n">
-        <v>2.69719862937927</v>
+        <v>2.69719886779785</v>
       </c>
       <c r="H770" t="n">
         <v>753</v>
@@ -22844,7 +22844,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G775" t="n">
-        <v>2.69719862937927</v>
+        <v>2.69719886779785</v>
       </c>
       <c r="H775" t="n">
         <v>12499</v>
@@ -22902,7 +22902,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G777" t="n">
-        <v>2.75096344947815</v>
+        <v>2.75096321105957</v>
       </c>
       <c r="H777" t="n">
         <v>1940</v>
@@ -23453,7 +23453,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G796" t="n">
-        <v>2.90329670906067</v>
+        <v>2.90329694747925</v>
       </c>
       <c r="H796" t="n">
         <v>1573</v>
@@ -23540,7 +23540,7 @@
         <v>3.5</v>
       </c>
       <c r="G799" t="n">
-        <v>3.13627767562866</v>
+        <v>3.13627743721008</v>
       </c>
       <c r="H799" t="n">
         <v>4784</v>
@@ -23569,7 +23569,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G800" t="n">
-        <v>3.19004225730896</v>
+        <v>3.19004201889038</v>
       </c>
       <c r="H800" t="n">
         <v>12016</v>
@@ -23598,7 +23598,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G801" t="n">
-        <v>3.25276803970337</v>
+        <v>3.25276780128479</v>
       </c>
       <c r="H801" t="n">
         <v>35656</v>
@@ -23627,7 +23627,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G802" t="n">
-        <v>3.26172876358032</v>
+        <v>3.26172852516174</v>
       </c>
       <c r="H802" t="n">
         <v>84823</v>
@@ -23656,7 +23656,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G803" t="n">
-        <v>3.25276803970337</v>
+        <v>3.25276780128479</v>
       </c>
       <c r="H803" t="n">
         <v>24537</v>
@@ -23685,7 +23685,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G804" t="n">
-        <v>3.19004225730896</v>
+        <v>3.19004201889038</v>
       </c>
       <c r="H804" t="n">
         <v>11994</v>
@@ -23946,7 +23946,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G813" t="n">
-        <v>3.42302274703979</v>
+        <v>3.42302298545837</v>
       </c>
       <c r="H813" t="n">
         <v>37852</v>
@@ -24033,7 +24033,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G816" t="n">
-        <v>3.41406178474426</v>
+        <v>3.41406202316284</v>
       </c>
       <c r="H816" t="n">
         <v>31655</v>
@@ -24062,7 +24062,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G817" t="n">
-        <v>3.3692581653595</v>
+        <v>3.36925792694092</v>
       </c>
       <c r="H817" t="n">
         <v>26326</v>
@@ -24178,7 +24178,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G821" t="n">
-        <v>3.45886588096619</v>
+        <v>3.45886564254761</v>
       </c>
       <c r="H821" t="n">
         <v>39609</v>
@@ -24207,7 +24207,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G822" t="n">
-        <v>3.4857485294342</v>
+        <v>3.48574876785278</v>
       </c>
       <c r="H822" t="n">
         <v>8734</v>
@@ -24323,7 +24323,7 @@
         <v>4</v>
       </c>
       <c r="G826" t="n">
-        <v>3.58431720733643</v>
+        <v>3.58431696891785</v>
       </c>
       <c r="H826" t="n">
         <v>34994</v>
@@ -24468,7 +24468,7 @@
         <v>4</v>
       </c>
       <c r="G831" t="n">
-        <v>3.58431720733643</v>
+        <v>3.58431696891785</v>
       </c>
       <c r="H831" t="n">
         <v>6782</v>
@@ -24497,7 +24497,7 @@
         <v>4</v>
       </c>
       <c r="G832" t="n">
-        <v>3.58431720733643</v>
+        <v>3.58431696891785</v>
       </c>
       <c r="H832" t="n">
         <v>21082</v>
@@ -24671,7 +24671,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G838" t="n">
-        <v>3.5395131111145</v>
+        <v>3.53951334953308</v>
       </c>
       <c r="H838" t="n">
         <v>9297</v>
@@ -24700,7 +24700,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G839" t="n">
-        <v>3.45886588096619</v>
+        <v>3.45886564254761</v>
       </c>
       <c r="H839" t="n">
         <v>1361</v>
@@ -24758,7 +24758,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G841" t="n">
-        <v>3.60223865509033</v>
+        <v>3.60223889350891</v>
       </c>
       <c r="H841" t="n">
         <v>17694</v>
@@ -24787,7 +24787,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G842" t="n">
-        <v>3.65600347518921</v>
+        <v>3.65600323677063</v>
       </c>
       <c r="H842" t="n">
         <v>57918</v>
@@ -24816,7 +24816,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G843" t="n">
-        <v>3.65600347518921</v>
+        <v>3.65600323677063</v>
       </c>
       <c r="H843" t="n">
         <v>7977</v>
@@ -24874,7 +24874,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G845" t="n">
-        <v>3.72768974304199</v>
+        <v>3.72768998146057</v>
       </c>
       <c r="H845" t="n">
         <v>6921</v>
@@ -25077,7 +25077,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G852" t="n">
-        <v>3.76353311538696</v>
+        <v>3.76353287696838</v>
       </c>
       <c r="H852" t="n">
         <v>27687</v>
@@ -25135,7 +25135,7 @@
         <v>4.25</v>
       </c>
       <c r="G854" t="n">
-        <v>3.80833697319031</v>
+        <v>3.80833721160889</v>
       </c>
       <c r="H854" t="n">
         <v>30581</v>
@@ -25164,7 +25164,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G855" t="n">
-        <v>3.79041528701782</v>
+        <v>3.79041504859924</v>
       </c>
       <c r="H855" t="n">
         <v>50118</v>
@@ -25193,7 +25193,7 @@
         <v>4.25</v>
       </c>
       <c r="G856" t="n">
-        <v>3.80833697319031</v>
+        <v>3.80833721160889</v>
       </c>
       <c r="H856" t="n">
         <v>29263</v>
@@ -25251,7 +25251,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G858" t="n">
-        <v>3.96067023277283</v>
+        <v>3.96067070960999</v>
       </c>
       <c r="H858" t="n">
         <v>45171</v>
@@ -79951,6 +79951,64 @@
         <v>2400</v>
       </c>
       <c r="I2744" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2745">
+      <c r="A2745" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2745" s="1" t="n">
+        <v>46314.2916666667</v>
+      </c>
+      <c r="C2745" t="n">
+        <v>1.00999999046326</v>
+      </c>
+      <c r="D2745" t="n">
+        <v>1.00999999046326</v>
+      </c>
+      <c r="E2745" t="n">
+        <v>1.00999999046326</v>
+      </c>
+      <c r="F2745" t="n">
+        <v>1.00999999046326</v>
+      </c>
+      <c r="G2745" t="n">
+        <v>1.00999999046326</v>
+      </c>
+      <c r="H2745" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2745" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2746">
+      <c r="A2746" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2746" s="1" t="n">
+        <v>46315.2916666667</v>
+      </c>
+      <c r="C2746" t="n">
+        <v>0.970000028610229</v>
+      </c>
+      <c r="D2746" t="n">
+        <v>0.970000028610229</v>
+      </c>
+      <c r="E2746" t="n">
+        <v>0.959999978542328</v>
+      </c>
+      <c r="F2746" t="n">
+        <v>1.01999998092651</v>
+      </c>
+      <c r="G2746" t="n">
+        <v>1.01999998092651</v>
+      </c>
+      <c r="H2746" t="n">
+        <v>1759</v>
+      </c>
+      <c r="I2746" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/RAT.MI.xlsx
+++ b/data/RAT.MI.xlsx
@@ -601,7 +601,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G8" t="n">
-        <v>1.92423331737518</v>
+        <v>1.9242330789566</v>
       </c>
       <c r="H8" t="n">
         <v>4000</v>
@@ -717,7 +717,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G12" t="n">
-        <v>1.80642294883728</v>
+        <v>1.80642306804657</v>
       </c>
       <c r="H12" t="n">
         <v>270</v>
@@ -746,7 +746,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G13" t="n">
-        <v>1.80642294883728</v>
+        <v>1.80642306804657</v>
       </c>
       <c r="H13" t="n">
         <v>1200</v>
@@ -804,7 +804,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G15" t="n">
-        <v>1.79856884479523</v>
+        <v>1.79856908321381</v>
       </c>
       <c r="H15" t="n">
         <v>2788</v>
@@ -833,7 +833,7 @@
         <v>2.25</v>
       </c>
       <c r="G16" t="n">
-        <v>1.76715302467346</v>
+        <v>1.76715314388275</v>
       </c>
       <c r="H16" t="n">
         <v>2070</v>
@@ -920,7 +920,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G19" t="n">
-        <v>1.86925506591797</v>
+        <v>1.86925530433655</v>
       </c>
       <c r="H19" t="n">
         <v>3200</v>
@@ -1007,7 +1007,7 @@
         <v>2.37800002098083</v>
       </c>
       <c r="G22" t="n">
-        <v>1.86768412590027</v>
+        <v>1.86768448352814</v>
       </c>
       <c r="H22" t="n">
         <v>2858</v>
@@ -1036,7 +1036,7 @@
         <v>2.31200003623962</v>
       </c>
       <c r="G23" t="n">
-        <v>1.81584787368774</v>
+        <v>1.81584763526917</v>
       </c>
       <c r="H23" t="n">
         <v>750</v>
@@ -1239,7 +1239,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G30" t="n">
-        <v>1.80642294883728</v>
+        <v>1.80642306804657</v>
       </c>
       <c r="H30" t="n">
         <v>10919</v>
@@ -1268,7 +1268,7 @@
         <v>2.32599997520447</v>
       </c>
       <c r="G31" t="n">
-        <v>1.82684350013733</v>
+        <v>1.82684326171875</v>
       </c>
       <c r="H31" t="n">
         <v>9925</v>
@@ -1326,7 +1326,7 @@
         <v>2.31599998474121</v>
       </c>
       <c r="G33" t="n">
-        <v>1.81898939609528</v>
+        <v>1.81898927688599</v>
       </c>
       <c r="H33" t="n">
         <v>1023</v>
@@ -1355,7 +1355,7 @@
         <v>2.33800005912781</v>
       </c>
       <c r="G34" t="n">
-        <v>1.8362683057785</v>
+        <v>1.83626818656921</v>
       </c>
       <c r="H34" t="n">
         <v>9221</v>
@@ -1384,7 +1384,7 @@
         <v>2.36800003051758</v>
       </c>
       <c r="G35" t="n">
-        <v>1.85983026027679</v>
+        <v>1.85983037948608</v>
       </c>
       <c r="H35" t="n">
         <v>100</v>
@@ -1413,7 +1413,7 @@
         <v>2.36800003051758</v>
       </c>
       <c r="G36" t="n">
-        <v>1.85983026027679</v>
+        <v>1.85983037948608</v>
       </c>
       <c r="H36" t="n">
         <v>0</v>
@@ -1442,7 +1442,7 @@
         <v>2.36800003051758</v>
       </c>
       <c r="G37" t="n">
-        <v>1.85983026027679</v>
+        <v>1.85983037948608</v>
       </c>
       <c r="H37" t="n">
         <v>100</v>
@@ -1471,7 +1471,7 @@
         <v>2.29800009727478</v>
       </c>
       <c r="G38" t="n">
-        <v>1.80485212802887</v>
+        <v>1.80485224723816</v>
       </c>
       <c r="H38" t="n">
         <v>7831</v>
@@ -1500,7 +1500,7 @@
         <v>2.31800007820129</v>
       </c>
       <c r="G39" t="n">
-        <v>1.82056033611298</v>
+        <v>1.82056021690369</v>
       </c>
       <c r="H39" t="n">
         <v>330</v>
@@ -1616,7 +1616,7 @@
         <v>2.33800005912781</v>
       </c>
       <c r="G43" t="n">
-        <v>1.8362683057785</v>
+        <v>1.83626818656921</v>
       </c>
       <c r="H43" t="n">
         <v>950</v>
@@ -1645,7 +1645,7 @@
         <v>2.36800003051758</v>
       </c>
       <c r="G44" t="n">
-        <v>1.85983026027679</v>
+        <v>1.85983037948608</v>
       </c>
       <c r="H44" t="n">
         <v>540</v>
@@ -1674,7 +1674,7 @@
         <v>2.37800002098083</v>
       </c>
       <c r="G45" t="n">
-        <v>1.86768412590027</v>
+        <v>1.86768448352814</v>
       </c>
       <c r="H45" t="n">
         <v>2230</v>
@@ -1703,7 +1703,7 @@
         <v>2.35599994659424</v>
       </c>
       <c r="G46" t="n">
-        <v>1.85040533542633</v>
+        <v>1.85040545463562</v>
       </c>
       <c r="H46" t="n">
         <v>253</v>
@@ -1790,7 +1790,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G49" t="n">
-        <v>1.81427705287933</v>
+        <v>1.81427693367004</v>
       </c>
       <c r="H49" t="n">
         <v>1530</v>
@@ -1848,7 +1848,7 @@
         <v>2.33800005912781</v>
       </c>
       <c r="G51" t="n">
-        <v>1.8362683057785</v>
+        <v>1.83626818656921</v>
       </c>
       <c r="H51" t="n">
         <v>1660</v>
@@ -1877,7 +1877,7 @@
         <v>2.35800004005432</v>
       </c>
       <c r="G52" t="n">
-        <v>1.85197603702545</v>
+        <v>1.85197639465332</v>
       </c>
       <c r="H52" t="n">
         <v>3419</v>
@@ -1906,7 +1906,7 @@
         <v>2.34800004959106</v>
       </c>
       <c r="G53" t="n">
-        <v>1.84412217140198</v>
+        <v>1.84412240982056</v>
       </c>
       <c r="H53" t="n">
         <v>3348</v>
@@ -2109,7 +2109,7 @@
         <v>2.30599999427795</v>
       </c>
       <c r="G60" t="n">
-        <v>1.81113529205322</v>
+        <v>1.81113541126251</v>
       </c>
       <c r="H60" t="n">
         <v>6820</v>
@@ -2138,7 +2138,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G61" t="n">
-        <v>1.81427705287933</v>
+        <v>1.81427693367004</v>
       </c>
       <c r="H61" t="n">
         <v>150</v>
@@ -2167,7 +2167,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G62" t="n">
-        <v>1.82213115692139</v>
+        <v>1.82213091850281</v>
       </c>
       <c r="H62" t="n">
         <v>7700</v>
@@ -2196,7 +2196,7 @@
         <v>2.35599994659424</v>
       </c>
       <c r="G63" t="n">
-        <v>1.85040533542633</v>
+        <v>1.85040545463562</v>
       </c>
       <c r="H63" t="n">
         <v>100</v>
@@ -2254,7 +2254,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G65" t="n">
-        <v>1.92423331737518</v>
+        <v>1.9242330789566</v>
       </c>
       <c r="H65" t="n">
         <v>19358</v>
@@ -2283,7 +2283,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G66" t="n">
-        <v>1.92423331737518</v>
+        <v>1.9242330789566</v>
       </c>
       <c r="H66" t="n">
         <v>0</v>
@@ -2341,7 +2341,7 @@
         <v>2.4779999256134</v>
       </c>
       <c r="G68" t="n">
-        <v>1.94622397422791</v>
+        <v>1.94622421264648</v>
       </c>
       <c r="H68" t="n">
         <v>120</v>
@@ -2370,7 +2370,7 @@
         <v>2.48799991607666</v>
       </c>
       <c r="G69" t="n">
-        <v>1.95407807826996</v>
+        <v>1.95407831668854</v>
       </c>
       <c r="H69" t="n">
         <v>16224</v>
@@ -2399,7 +2399,7 @@
         <v>2.5</v>
       </c>
       <c r="G70" t="n">
-        <v>1.96350336074829</v>
+        <v>1.96350312232971</v>
       </c>
       <c r="H70" t="n">
         <v>23697</v>
@@ -2457,7 +2457,7 @@
         <v>2.53800010681152</v>
       </c>
       <c r="G72" t="n">
-        <v>1.99334836006165</v>
+        <v>1.99334859848022</v>
       </c>
       <c r="H72" t="n">
         <v>1951</v>
@@ -2515,7 +2515,7 @@
         <v>2.5</v>
       </c>
       <c r="G74" t="n">
-        <v>1.96350336074829</v>
+        <v>1.96350312232971</v>
       </c>
       <c r="H74" t="n">
         <v>1853</v>
@@ -2602,7 +2602,7 @@
         <v>2.55800008773804</v>
       </c>
       <c r="G77" t="n">
-        <v>2.00905656814575</v>
+        <v>2.00905632972717</v>
       </c>
       <c r="H77" t="n">
         <v>1892</v>
@@ -2631,7 +2631,7 @@
         <v>2.57800006866455</v>
       </c>
       <c r="G78" t="n">
-        <v>2.0247642993927</v>
+        <v>2.02476453781128</v>
       </c>
       <c r="H78" t="n">
         <v>1952</v>
@@ -2660,7 +2660,7 @@
         <v>2.45799994468689</v>
       </c>
       <c r="G79" t="n">
-        <v>1.93051636219025</v>
+        <v>1.93051660060883</v>
       </c>
       <c r="H79" t="n">
         <v>9175</v>
@@ -2689,7 +2689,7 @@
         <v>2.45799994468689</v>
       </c>
       <c r="G80" t="n">
-        <v>1.93051636219025</v>
+        <v>1.93051660060883</v>
       </c>
       <c r="H80" t="n">
         <v>1464</v>
@@ -2718,7 +2718,7 @@
         <v>2.5</v>
       </c>
       <c r="G81" t="n">
-        <v>1.96350336074829</v>
+        <v>1.96350312232971</v>
       </c>
       <c r="H81" t="n">
         <v>50</v>
@@ -2776,7 +2776,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G83" t="n">
-        <v>1.93994152545929</v>
+        <v>1.93994128704071</v>
       </c>
       <c r="H83" t="n">
         <v>1443</v>
@@ -2805,7 +2805,7 @@
         <v>2.48799991607666</v>
       </c>
       <c r="G84" t="n">
-        <v>1.95407807826996</v>
+        <v>1.95407831668854</v>
       </c>
       <c r="H84" t="n">
         <v>371</v>
@@ -2892,7 +2892,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G87" t="n">
-        <v>1.93994152545929</v>
+        <v>1.93994128704071</v>
       </c>
       <c r="H87" t="n">
         <v>303</v>
@@ -2921,7 +2921,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G88" t="n">
-        <v>1.91637921333313</v>
+        <v>1.91637897491455</v>
       </c>
       <c r="H88" t="n">
         <v>1187</v>
@@ -2979,7 +2979,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G90" t="n">
-        <v>1.91637921333313</v>
+        <v>1.91637897491455</v>
       </c>
       <c r="H90" t="n">
         <v>65</v>
@@ -3008,7 +3008,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G91" t="n">
-        <v>1.91637921333313</v>
+        <v>1.91637897491455</v>
       </c>
       <c r="H91" t="n">
         <v>0</v>
@@ -3153,7 +3153,7 @@
         <v>2.29800009727478</v>
       </c>
       <c r="G96" t="n">
-        <v>1.80485212802887</v>
+        <v>1.80485224723816</v>
       </c>
       <c r="H96" t="n">
         <v>5665</v>
@@ -3182,7 +3182,7 @@
         <v>2.29800009727478</v>
       </c>
       <c r="G97" t="n">
-        <v>1.80485212802887</v>
+        <v>1.80485224723816</v>
       </c>
       <c r="H97" t="n">
         <v>50</v>
@@ -3211,7 +3211,7 @@
         <v>2.34800004959106</v>
       </c>
       <c r="G98" t="n">
-        <v>1.84412217140198</v>
+        <v>1.84412240982056</v>
       </c>
       <c r="H98" t="n">
         <v>8904</v>
@@ -79994,7 +79994,7 @@
         <v>0.970000028610229</v>
       </c>
       <c r="D2746" t="n">
-        <v>0.970000028610229</v>
+        <v>1.01999998092651</v>
       </c>
       <c r="E2746" t="n">
         <v>0.959999978542328</v>
@@ -80009,6 +80009,35 @@
         <v>1759</v>
       </c>
       <c r="I2746" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2747">
+      <c r="A2747" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2747" s="1" t="n">
+        <v>46316.2916666667</v>
+      </c>
+      <c r="C2747" t="n">
+        <v>0.964999973773956</v>
+      </c>
+      <c r="D2747" t="n">
+        <v>0.985000014305115</v>
+      </c>
+      <c r="E2747" t="n">
+        <v>0.964999973773956</v>
+      </c>
+      <c r="F2747" t="n">
+        <v>0.980000019073486</v>
+      </c>
+      <c r="G2747" t="n">
+        <v>0.980000019073486</v>
+      </c>
+      <c r="H2747" t="n">
+        <v>100805</v>
+      </c>
+      <c r="I2747" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/RAT.MI.xlsx
+++ b/data/RAT.MI.xlsx
@@ -427,7 +427,7 @@
         <v>2.3659999370575</v>
       </c>
       <c r="G2" t="n">
-        <v>1.85825932025909</v>
+        <v>1.85825943946838</v>
       </c>
       <c r="H2" t="n">
         <v>1350</v>
@@ -456,7 +456,7 @@
         <v>2.43600010871887</v>
       </c>
       <c r="G3" t="n">
-        <v>1.91323757171631</v>
+        <v>1.9132376909256</v>
       </c>
       <c r="H3" t="n">
         <v>3199</v>
@@ -485,7 +485,7 @@
         <v>2.44600009918213</v>
       </c>
       <c r="G4" t="n">
-        <v>1.92109143733978</v>
+        <v>1.92109155654907</v>
       </c>
       <c r="H4" t="n">
         <v>365</v>
@@ -514,7 +514,7 @@
         <v>2.44600009918213</v>
       </c>
       <c r="G5" t="n">
-        <v>1.92109143733978</v>
+        <v>1.92109155654907</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -543,7 +543,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G6" t="n">
-        <v>1.88496327400208</v>
+        <v>1.8849630355835</v>
       </c>
       <c r="H6" t="n">
         <v>5635</v>
@@ -572,7 +572,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G7" t="n">
-        <v>1.88496327400208</v>
+        <v>1.8849630355835</v>
       </c>
       <c r="H7" t="n">
         <v>1000</v>
@@ -630,7 +630,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G9" t="n">
-        <v>1.88496327400208</v>
+        <v>1.8849630355835</v>
       </c>
       <c r="H9" t="n">
         <v>155</v>
@@ -659,7 +659,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G10" t="n">
-        <v>1.88496327400208</v>
+        <v>1.8849630355835</v>
       </c>
       <c r="H10" t="n">
         <v>559</v>
@@ -688,7 +688,7 @@
         <v>2.3659999370575</v>
       </c>
       <c r="G11" t="n">
-        <v>1.85825932025909</v>
+        <v>1.85825943946838</v>
       </c>
       <c r="H11" t="n">
         <v>1414</v>
@@ -775,7 +775,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G14" t="n">
-        <v>1.82998502254486</v>
+        <v>1.82998514175415</v>
       </c>
       <c r="H14" t="n">
         <v>193</v>
@@ -804,7 +804,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G15" t="n">
-        <v>1.79856908321381</v>
+        <v>1.79856896400452</v>
       </c>
       <c r="H15" t="n">
         <v>2788</v>
@@ -833,7 +833,7 @@
         <v>2.25</v>
       </c>
       <c r="G16" t="n">
-        <v>1.76715314388275</v>
+        <v>1.76715302467346</v>
       </c>
       <c r="H16" t="n">
         <v>2070</v>
@@ -862,7 +862,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G17" t="n">
-        <v>1.85354709625244</v>
+        <v>1.85354697704315</v>
       </c>
       <c r="H17" t="n">
         <v>4705</v>
@@ -891,7 +891,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G18" t="n">
-        <v>1.85354709625244</v>
+        <v>1.85354697704315</v>
       </c>
       <c r="H18" t="n">
         <v>2000</v>
@@ -920,7 +920,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G19" t="n">
-        <v>1.86925530433655</v>
+        <v>1.86925518512726</v>
       </c>
       <c r="H19" t="n">
         <v>3200</v>
@@ -978,7 +978,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G21" t="n">
-        <v>1.89281737804413</v>
+        <v>1.89281725883484</v>
       </c>
       <c r="H21" t="n">
         <v>100</v>
@@ -1007,7 +1007,7 @@
         <v>2.37800002098083</v>
       </c>
       <c r="G22" t="n">
-        <v>1.86768448352814</v>
+        <v>1.86768412590027</v>
       </c>
       <c r="H22" t="n">
         <v>2858</v>
@@ -1036,7 +1036,7 @@
         <v>2.31200003623962</v>
       </c>
       <c r="G23" t="n">
-        <v>1.81584763526917</v>
+        <v>1.81584787368774</v>
       </c>
       <c r="H23" t="n">
         <v>750</v>
@@ -1123,7 +1123,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G26" t="n">
-        <v>1.88496327400208</v>
+        <v>1.8849630355835</v>
       </c>
       <c r="H26" t="n">
         <v>330</v>
@@ -1152,7 +1152,7 @@
         <v>2.38800001144409</v>
       </c>
       <c r="G27" t="n">
-        <v>1.87553811073303</v>
+        <v>1.87553834915161</v>
       </c>
       <c r="H27" t="n">
         <v>2173</v>
@@ -1181,7 +1181,7 @@
         <v>2.38800001144409</v>
       </c>
       <c r="G28" t="n">
-        <v>1.87553811073303</v>
+        <v>1.87553834915161</v>
       </c>
       <c r="H28" t="n">
         <v>0</v>
@@ -1210,7 +1210,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G29" t="n">
-        <v>1.88496327400208</v>
+        <v>1.8849630355835</v>
       </c>
       <c r="H29" t="n">
         <v>1810</v>
@@ -1326,7 +1326,7 @@
         <v>2.31599998474121</v>
       </c>
       <c r="G33" t="n">
-        <v>1.81898927688599</v>
+        <v>1.81898939609528</v>
       </c>
       <c r="H33" t="n">
         <v>1023</v>
@@ -1355,7 +1355,7 @@
         <v>2.33800005912781</v>
       </c>
       <c r="G34" t="n">
-        <v>1.83626818656921</v>
+        <v>1.83626806735992</v>
       </c>
       <c r="H34" t="n">
         <v>9221</v>
@@ -1500,7 +1500,7 @@
         <v>2.31800007820129</v>
       </c>
       <c r="G39" t="n">
-        <v>1.82056021690369</v>
+        <v>1.82056045532227</v>
       </c>
       <c r="H39" t="n">
         <v>330</v>
@@ -1616,7 +1616,7 @@
         <v>2.33800005912781</v>
       </c>
       <c r="G43" t="n">
-        <v>1.83626818656921</v>
+        <v>1.83626806735992</v>
       </c>
       <c r="H43" t="n">
         <v>950</v>
@@ -1674,7 +1674,7 @@
         <v>2.37800002098083</v>
       </c>
       <c r="G45" t="n">
-        <v>1.86768448352814</v>
+        <v>1.86768412590027</v>
       </c>
       <c r="H45" t="n">
         <v>2230</v>
@@ -1703,7 +1703,7 @@
         <v>2.35599994659424</v>
       </c>
       <c r="G46" t="n">
-        <v>1.85040545463562</v>
+        <v>1.85040533542633</v>
       </c>
       <c r="H46" t="n">
         <v>253</v>
@@ -1732,7 +1732,7 @@
         <v>2.39400005340576</v>
       </c>
       <c r="G47" t="n">
-        <v>1.88025057315826</v>
+        <v>1.88025081157684</v>
       </c>
       <c r="H47" t="n">
         <v>110</v>
@@ -1761,7 +1761,7 @@
         <v>2.39400005340576</v>
       </c>
       <c r="G48" t="n">
-        <v>1.88025057315826</v>
+        <v>1.88025081157684</v>
       </c>
       <c r="H48" t="n">
         <v>0</v>
@@ -1790,7 +1790,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G49" t="n">
-        <v>1.81427693367004</v>
+        <v>1.81427669525146</v>
       </c>
       <c r="H49" t="n">
         <v>1530</v>
@@ -1848,7 +1848,7 @@
         <v>2.33800005912781</v>
       </c>
       <c r="G51" t="n">
-        <v>1.83626818656921</v>
+        <v>1.83626806735992</v>
       </c>
       <c r="H51" t="n">
         <v>1660</v>
@@ -1906,7 +1906,7 @@
         <v>2.34800004959106</v>
       </c>
       <c r="G53" t="n">
-        <v>1.84412240982056</v>
+        <v>1.84412229061127</v>
       </c>
       <c r="H53" t="n">
         <v>3348</v>
@@ -2022,7 +2022,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G57" t="n">
-        <v>1.85354709625244</v>
+        <v>1.85354697704315</v>
       </c>
       <c r="H57" t="n">
         <v>50</v>
@@ -2051,7 +2051,7 @@
         <v>2.32200002670288</v>
       </c>
       <c r="G58" t="n">
-        <v>1.82370173931122</v>
+        <v>1.8237019777298</v>
       </c>
       <c r="H58" t="n">
         <v>1606</v>
@@ -2080,7 +2080,7 @@
         <v>2.32200002670288</v>
       </c>
       <c r="G59" t="n">
-        <v>1.82370173931122</v>
+        <v>1.8237019777298</v>
       </c>
       <c r="H59" t="n">
         <v>0</v>
@@ -2109,7 +2109,7 @@
         <v>2.30599999427795</v>
       </c>
       <c r="G60" t="n">
-        <v>1.81113541126251</v>
+        <v>1.81113529205322</v>
       </c>
       <c r="H60" t="n">
         <v>6820</v>
@@ -2138,7 +2138,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G61" t="n">
-        <v>1.81427693367004</v>
+        <v>1.81427669525146</v>
       </c>
       <c r="H61" t="n">
         <v>150</v>
@@ -2167,7 +2167,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G62" t="n">
-        <v>1.82213091850281</v>
+        <v>1.8221310377121</v>
       </c>
       <c r="H62" t="n">
         <v>7700</v>
@@ -2196,7 +2196,7 @@
         <v>2.35599994659424</v>
       </c>
       <c r="G63" t="n">
-        <v>1.85040545463562</v>
+        <v>1.85040533542633</v>
       </c>
       <c r="H63" t="n">
         <v>100</v>
@@ -2341,7 +2341,7 @@
         <v>2.4779999256134</v>
       </c>
       <c r="G68" t="n">
-        <v>1.94622421264648</v>
+        <v>1.94622457027435</v>
       </c>
       <c r="H68" t="n">
         <v>120</v>
@@ -2370,7 +2370,7 @@
         <v>2.48799991607666</v>
       </c>
       <c r="G69" t="n">
-        <v>1.95407831668854</v>
+        <v>1.95407819747925</v>
       </c>
       <c r="H69" t="n">
         <v>16224</v>
@@ -2399,7 +2399,7 @@
         <v>2.5</v>
       </c>
       <c r="G70" t="n">
-        <v>1.96350312232971</v>
+        <v>1.96350359916687</v>
       </c>
       <c r="H70" t="n">
         <v>23697</v>
@@ -2457,7 +2457,7 @@
         <v>2.53800010681152</v>
       </c>
       <c r="G72" t="n">
-        <v>1.99334859848022</v>
+        <v>1.9933488368988</v>
       </c>
       <c r="H72" t="n">
         <v>1951</v>
@@ -2515,7 +2515,7 @@
         <v>2.5</v>
       </c>
       <c r="G74" t="n">
-        <v>1.96350312232971</v>
+        <v>1.96350359916687</v>
       </c>
       <c r="H74" t="n">
         <v>1853</v>
@@ -2544,7 +2544,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G75" t="n">
-        <v>1.98706519603729</v>
+        <v>1.987065076828</v>
       </c>
       <c r="H75" t="n">
         <v>41607</v>
@@ -2602,7 +2602,7 @@
         <v>2.55800008773804</v>
       </c>
       <c r="G77" t="n">
-        <v>2.00905632972717</v>
+        <v>2.00905656814575</v>
       </c>
       <c r="H77" t="n">
         <v>1892</v>
@@ -2660,7 +2660,7 @@
         <v>2.45799994468689</v>
       </c>
       <c r="G79" t="n">
-        <v>1.93051660060883</v>
+        <v>1.93051636219025</v>
       </c>
       <c r="H79" t="n">
         <v>9175</v>
@@ -2689,7 +2689,7 @@
         <v>2.45799994468689</v>
       </c>
       <c r="G80" t="n">
-        <v>1.93051660060883</v>
+        <v>1.93051636219025</v>
       </c>
       <c r="H80" t="n">
         <v>1464</v>
@@ -2718,7 +2718,7 @@
         <v>2.5</v>
       </c>
       <c r="G81" t="n">
-        <v>1.96350312232971</v>
+        <v>1.96350359916687</v>
       </c>
       <c r="H81" t="n">
         <v>50</v>
@@ -2747,7 +2747,7 @@
         <v>2.49799990653992</v>
       </c>
       <c r="G82" t="n">
-        <v>1.96193218231201</v>
+        <v>1.9619323015213</v>
       </c>
       <c r="H82" t="n">
         <v>2294</v>
@@ -2776,7 +2776,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G83" t="n">
-        <v>1.93994128704071</v>
+        <v>1.93994140625</v>
       </c>
       <c r="H83" t="n">
         <v>1443</v>
@@ -2805,7 +2805,7 @@
         <v>2.48799991607666</v>
       </c>
       <c r="G84" t="n">
-        <v>1.95407831668854</v>
+        <v>1.95407819747925</v>
       </c>
       <c r="H84" t="n">
         <v>371</v>
@@ -2834,7 +2834,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G85" t="n">
-        <v>1.95564925670624</v>
+        <v>1.95564901828766</v>
       </c>
       <c r="H85" t="n">
         <v>2700</v>
@@ -2863,7 +2863,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G86" t="n">
-        <v>1.95564925670624</v>
+        <v>1.95564901828766</v>
       </c>
       <c r="H86" t="n">
         <v>0</v>
@@ -2892,7 +2892,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G87" t="n">
-        <v>1.93994128704071</v>
+        <v>1.93994140625</v>
       </c>
       <c r="H87" t="n">
         <v>303</v>
@@ -2921,7 +2921,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G88" t="n">
-        <v>1.91637897491455</v>
+        <v>1.91637945175171</v>
       </c>
       <c r="H88" t="n">
         <v>1187</v>
@@ -2950,7 +2950,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G89" t="n">
-        <v>1.88496327400208</v>
+        <v>1.8849630355835</v>
       </c>
       <c r="H89" t="n">
         <v>4181</v>
@@ -2979,7 +2979,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G90" t="n">
-        <v>1.91637897491455</v>
+        <v>1.91637945175171</v>
       </c>
       <c r="H90" t="n">
         <v>65</v>
@@ -3008,7 +3008,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G91" t="n">
-        <v>1.91637897491455</v>
+        <v>1.91637945175171</v>
       </c>
       <c r="H91" t="n">
         <v>0</v>
@@ -3037,7 +3037,7 @@
         <v>2.39400005340576</v>
       </c>
       <c r="G92" t="n">
-        <v>1.88025057315826</v>
+        <v>1.88025081157684</v>
       </c>
       <c r="H92" t="n">
         <v>260</v>
@@ -3095,7 +3095,7 @@
         <v>2.38599991798401</v>
       </c>
       <c r="G94" t="n">
-        <v>1.87396728992462</v>
+        <v>1.87396740913391</v>
       </c>
       <c r="H94" t="n">
         <v>11190</v>
@@ -3124,7 +3124,7 @@
         <v>2.38599991798401</v>
       </c>
       <c r="G95" t="n">
-        <v>1.87396728992462</v>
+        <v>1.87396740913391</v>
       </c>
       <c r="H95" t="n">
         <v>0</v>
@@ -3211,7 +3211,7 @@
         <v>2.34800004959106</v>
       </c>
       <c r="G98" t="n">
-        <v>1.84412240982056</v>
+        <v>1.84412229061127</v>
       </c>
       <c r="H98" t="n">
         <v>8904</v>
@@ -3240,7 +3240,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G99" t="n">
-        <v>1.89281737804413</v>
+        <v>1.89281725883484</v>
       </c>
       <c r="H99" t="n">
         <v>14550</v>
@@ -3327,7 +3327,7 @@
         <v>2.34599995613098</v>
       </c>
       <c r="G102" t="n">
-        <v>1.9223153591156</v>
+        <v>1.92231547832489</v>
       </c>
       <c r="H102" t="n">
         <v>195</v>
@@ -3385,7 +3385,7 @@
         <v>2.35599994659424</v>
       </c>
       <c r="G104" t="n">
-        <v>1.93050944805145</v>
+        <v>1.93050968647003</v>
       </c>
       <c r="H104" t="n">
         <v>3779</v>
@@ -3414,7 +3414,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G105" t="n">
-        <v>1.96656334400177</v>
+        <v>1.96656322479248</v>
       </c>
       <c r="H105" t="n">
         <v>160</v>
@@ -3443,7 +3443,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G106" t="n">
-        <v>1.96656334400177</v>
+        <v>1.96656322479248</v>
       </c>
       <c r="H106" t="n">
         <v>0</v>
@@ -3501,7 +3501,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G108" t="n">
-        <v>1.95836925506592</v>
+        <v>1.9583694934845</v>
       </c>
       <c r="H108" t="n">
         <v>668</v>
@@ -3530,7 +3530,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G109" t="n">
-        <v>1.95836925506592</v>
+        <v>1.9583694934845</v>
       </c>
       <c r="H109" t="n">
         <v>0</v>
@@ -3617,7 +3617,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G112" t="n">
-        <v>1.91739892959595</v>
+        <v>1.91739916801453</v>
       </c>
       <c r="H112" t="n">
         <v>778</v>
@@ -3646,7 +3646,7 @@
         <v>2.36199998855591</v>
       </c>
       <c r="G113" t="n">
-        <v>1.93542611598969</v>
+        <v>1.93542587757111</v>
       </c>
       <c r="H113" t="n">
         <v>1461</v>
@@ -3675,7 +3675,7 @@
         <v>2.36199998855591</v>
       </c>
       <c r="G114" t="n">
-        <v>1.93542611598969</v>
+        <v>1.93542587757111</v>
       </c>
       <c r="H114" t="n">
         <v>0</v>
@@ -3704,7 +3704,7 @@
         <v>2.36199998855591</v>
       </c>
       <c r="G115" t="n">
-        <v>1.93542611598969</v>
+        <v>1.93542587757111</v>
       </c>
       <c r="H115" t="n">
         <v>635</v>
@@ -3733,7 +3733,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G116" t="n">
-        <v>1.9419811964035</v>
+        <v>1.94198107719421</v>
       </c>
       <c r="H116" t="n">
         <v>5088</v>
@@ -3762,7 +3762,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G117" t="n">
-        <v>1.9419811964035</v>
+        <v>1.94198107719421</v>
       </c>
       <c r="H117" t="n">
         <v>0</v>
@@ -3791,7 +3791,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G118" t="n">
-        <v>1.91739892959595</v>
+        <v>1.91739916801453</v>
       </c>
       <c r="H118" t="n">
         <v>2740</v>
@@ -3820,7 +3820,7 @@
         <v>2.33400011062622</v>
       </c>
       <c r="G119" t="n">
-        <v>1.91248261928558</v>
+        <v>1.91248285770416</v>
       </c>
       <c r="H119" t="n">
         <v>2002</v>
@@ -3907,7 +3907,7 @@
         <v>2.33400011062622</v>
       </c>
       <c r="G122" t="n">
-        <v>1.91248261928558</v>
+        <v>1.91248285770416</v>
       </c>
       <c r="H122" t="n">
         <v>1260</v>
@@ -3936,7 +3936,7 @@
         <v>2.33400011062622</v>
       </c>
       <c r="G123" t="n">
-        <v>1.91248261928558</v>
+        <v>1.91248285770416</v>
       </c>
       <c r="H123" t="n">
         <v>0</v>
@@ -3965,7 +3965,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G124" t="n">
-        <v>1.83545899391174</v>
+        <v>1.83545875549316</v>
       </c>
       <c r="H124" t="n">
         <v>348</v>
@@ -3994,7 +3994,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G125" t="n">
-        <v>1.80268323421478</v>
+        <v>1.8026829957962</v>
       </c>
       <c r="H125" t="n">
         <v>3159</v>
@@ -4110,7 +4110,7 @@
         <v>2.29800009727478</v>
       </c>
       <c r="G129" t="n">
-        <v>1.88298428058624</v>
+        <v>1.88298439979553</v>
       </c>
       <c r="H129" t="n">
         <v>100</v>
@@ -4139,7 +4139,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G130" t="n">
-        <v>1.86823523044586</v>
+        <v>1.86823511123657</v>
       </c>
       <c r="H130" t="n">
         <v>2288</v>
@@ -4168,7 +4168,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G131" t="n">
-        <v>1.9419811964035</v>
+        <v>1.94198107719421</v>
       </c>
       <c r="H131" t="n">
         <v>150</v>
@@ -4197,7 +4197,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G132" t="n">
-        <v>1.9419811964035</v>
+        <v>1.94198107719421</v>
       </c>
       <c r="H132" t="n">
         <v>0</v>
@@ -4313,7 +4313,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G136" t="n">
-        <v>1.89281713962555</v>
+        <v>1.89281702041626</v>
       </c>
       <c r="H136" t="n">
         <v>6553</v>
@@ -4400,7 +4400,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G139" t="n">
-        <v>1.8846230506897</v>
+        <v>1.88462293148041</v>
       </c>
       <c r="H139" t="n">
         <v>110</v>
@@ -4516,7 +4516,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G143" t="n">
-        <v>1.90920507907867</v>
+        <v>1.90920519828796</v>
       </c>
       <c r="H143" t="n">
         <v>1045</v>
@@ -4545,7 +4545,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G144" t="n">
-        <v>1.90920507907867</v>
+        <v>1.90920519828796</v>
       </c>
       <c r="H144" t="n">
         <v>1250</v>
@@ -4574,7 +4574,7 @@
         <v>2.28399991989136</v>
       </c>
       <c r="G145" t="n">
-        <v>1.87151253223419</v>
+        <v>1.87151265144348</v>
       </c>
       <c r="H145" t="n">
         <v>10583</v>
@@ -4661,7 +4661,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G148" t="n">
-        <v>1.90920507907867</v>
+        <v>1.90920519828796</v>
       </c>
       <c r="H148" t="n">
         <v>1371</v>
@@ -4690,7 +4690,7 @@
         <v>2.2260000705719</v>
       </c>
       <c r="G149" t="n">
-        <v>1.82398748397827</v>
+        <v>1.82398736476898</v>
       </c>
       <c r="H149" t="n">
         <v>2820</v>
@@ -4864,7 +4864,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G155" t="n">
-        <v>1.75351893901825</v>
+        <v>1.75351905822754</v>
       </c>
       <c r="H155" t="n">
         <v>606</v>
@@ -4893,7 +4893,7 @@
         <v>2.17199993133545</v>
       </c>
       <c r="G156" t="n">
-        <v>1.77973973751068</v>
+        <v>1.77973985671997</v>
       </c>
       <c r="H156" t="n">
         <v>975</v>
@@ -4922,7 +4922,7 @@
         <v>2.17199993133545</v>
       </c>
       <c r="G157" t="n">
-        <v>1.77973973751068</v>
+        <v>1.77973985671997</v>
       </c>
       <c r="H157" t="n">
         <v>0</v>
@@ -4951,7 +4951,7 @@
         <v>2.13599991798401</v>
       </c>
       <c r="G158" t="n">
-        <v>1.75024104118347</v>
+        <v>1.75024116039276</v>
       </c>
       <c r="H158" t="n">
         <v>4584</v>
@@ -5009,7 +5009,7 @@
         <v>2.03800010681152</v>
       </c>
       <c r="G160" t="n">
-        <v>1.66993987560272</v>
+        <v>1.66993999481201</v>
       </c>
       <c r="H160" t="n">
         <v>1226</v>
@@ -5038,7 +5038,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G161" t="n">
-        <v>1.72893679141998</v>
+        <v>1.72893691062927</v>
       </c>
       <c r="H161" t="n">
         <v>12639</v>
@@ -5067,7 +5067,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G162" t="n">
-        <v>1.72893679141998</v>
+        <v>1.72893691062927</v>
       </c>
       <c r="H162" t="n">
         <v>0</v>
@@ -5096,7 +5096,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G163" t="n">
-        <v>1.69616067409515</v>
+        <v>1.69616079330444</v>
       </c>
       <c r="H163" t="n">
         <v>4541</v>
@@ -5299,7 +5299,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G170" t="n">
-        <v>1.7043548822403</v>
+        <v>1.70435464382172</v>
       </c>
       <c r="H170" t="n">
         <v>12329</v>
@@ -5328,7 +5328,7 @@
         <v>2.11800003051758</v>
       </c>
       <c r="G171" t="n">
-        <v>1.73549199104309</v>
+        <v>1.73549211025238</v>
       </c>
       <c r="H171" t="n">
         <v>263</v>
@@ -5357,7 +5357,7 @@
         <v>2.1159999370575</v>
       </c>
       <c r="G172" t="n">
-        <v>1.73385310173035</v>
+        <v>1.73385322093964</v>
       </c>
       <c r="H172" t="n">
         <v>5150</v>
@@ -5386,7 +5386,7 @@
         <v>2.1159999370575</v>
       </c>
       <c r="G173" t="n">
-        <v>1.73385310173035</v>
+        <v>1.73385322093964</v>
       </c>
       <c r="H173" t="n">
         <v>0</v>
@@ -5444,7 +5444,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G175" t="n">
-        <v>1.63060879707336</v>
+        <v>1.63060867786407</v>
       </c>
       <c r="H175" t="n">
         <v>32041</v>
@@ -5560,7 +5560,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G179" t="n">
-        <v>1.62241458892822</v>
+        <v>1.62241470813751</v>
       </c>
       <c r="H179" t="n">
         <v>20086</v>
@@ -5589,7 +5589,7 @@
         <v>2.03800010681152</v>
       </c>
       <c r="G180" t="n">
-        <v>1.66993987560272</v>
+        <v>1.66993999481201</v>
       </c>
       <c r="H180" t="n">
         <v>9799</v>
@@ -5763,7 +5763,7 @@
         <v>2.03800010681152</v>
       </c>
       <c r="G186" t="n">
-        <v>1.66993987560272</v>
+        <v>1.66993999481201</v>
       </c>
       <c r="H186" t="n">
         <v>1116</v>
@@ -5792,7 +5792,7 @@
         <v>2.03800010681152</v>
       </c>
       <c r="G187" t="n">
-        <v>1.66993987560272</v>
+        <v>1.66993999481201</v>
       </c>
       <c r="H187" t="n">
         <v>0</v>
@@ -5821,7 +5821,7 @@
         <v>2.03800010681152</v>
       </c>
       <c r="G188" t="n">
-        <v>1.66993987560272</v>
+        <v>1.66993999481201</v>
       </c>
       <c r="H188" t="n">
         <v>0</v>
@@ -5850,7 +5850,7 @@
         <v>2.00799989700317</v>
       </c>
       <c r="G189" t="n">
-        <v>1.64535772800446</v>
+        <v>1.64535784721375</v>
       </c>
       <c r="H189" t="n">
         <v>2513</v>
@@ -5995,7 +5995,7 @@
         <v>2.03800010681152</v>
       </c>
       <c r="G194" t="n">
-        <v>1.66993987560272</v>
+        <v>1.66993999481201</v>
       </c>
       <c r="H194" t="n">
         <v>204</v>
@@ -6024,7 +6024,7 @@
         <v>2.03600001335144</v>
       </c>
       <c r="G195" t="n">
-        <v>1.66830122470856</v>
+        <v>1.66830110549927</v>
       </c>
       <c r="H195" t="n">
         <v>6290</v>
@@ -6053,7 +6053,7 @@
         <v>2.03600001335144</v>
       </c>
       <c r="G196" t="n">
-        <v>1.66830122470856</v>
+        <v>1.66830110549927</v>
       </c>
       <c r="H196" t="n">
         <v>0</v>
@@ -6082,7 +6082,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G197" t="n">
-        <v>1.65519070625305</v>
+        <v>1.65519058704376</v>
       </c>
       <c r="H197" t="n">
         <v>4191</v>
@@ -6111,7 +6111,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G198" t="n">
-        <v>1.65519070625305</v>
+        <v>1.65519058704376</v>
       </c>
       <c r="H198" t="n">
         <v>0</v>
@@ -6140,7 +6140,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G199" t="n">
-        <v>1.65519070625305</v>
+        <v>1.65519058704376</v>
       </c>
       <c r="H199" t="n">
         <v>1000</v>
@@ -6169,7 +6169,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G200" t="n">
-        <v>1.65519070625305</v>
+        <v>1.65519058704376</v>
       </c>
       <c r="H200" t="n">
         <v>0</v>
@@ -6198,7 +6198,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G201" t="n">
-        <v>1.65519070625305</v>
+        <v>1.65519058704376</v>
       </c>
       <c r="H201" t="n">
         <v>100</v>
@@ -6227,7 +6227,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G202" t="n">
-        <v>1.64699685573578</v>
+        <v>1.64699673652649</v>
       </c>
       <c r="H202" t="n">
         <v>487</v>
@@ -6256,7 +6256,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G203" t="n">
-        <v>1.64699685573578</v>
+        <v>1.64699673652649</v>
       </c>
       <c r="H203" t="n">
         <v>4278</v>
@@ -6285,7 +6285,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G204" t="n">
-        <v>1.64699685573578</v>
+        <v>1.64699673652649</v>
       </c>
       <c r="H204" t="n">
         <v>180</v>
@@ -6314,7 +6314,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G205" t="n">
-        <v>1.64699685573578</v>
+        <v>1.64699673652649</v>
       </c>
       <c r="H205" t="n">
         <v>0</v>
@@ -6401,7 +6401,7 @@
         <v>1.9889999628067</v>
       </c>
       <c r="G208" t="n">
-        <v>1.62978935241699</v>
+        <v>1.62978911399841</v>
       </c>
       <c r="H208" t="n">
         <v>50</v>
@@ -6430,7 +6430,7 @@
         <v>1.932000041008</v>
       </c>
       <c r="G209" t="n">
-        <v>1.58308351039886</v>
+        <v>1.58308339118958</v>
       </c>
       <c r="H209" t="n">
         <v>10501</v>
@@ -6575,7 +6575,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G214" t="n">
-        <v>1.54047441482544</v>
+        <v>1.54047453403473</v>
       </c>
       <c r="H214" t="n">
         <v>2780</v>
@@ -6604,7 +6604,7 @@
         <v>1.91299998760223</v>
       </c>
       <c r="G215" t="n">
-        <v>1.56751477718353</v>
+        <v>1.56751465797424</v>
       </c>
       <c r="H215" t="n">
         <v>8016</v>
@@ -6633,7 +6633,7 @@
         <v>1.91600000858307</v>
       </c>
       <c r="G216" t="n">
-        <v>1.56997311115265</v>
+        <v>1.56997299194336</v>
       </c>
       <c r="H216" t="n">
         <v>8053</v>
@@ -6662,7 +6662,7 @@
         <v>1.91199994087219</v>
       </c>
       <c r="G217" t="n">
-        <v>1.56669545173645</v>
+        <v>1.56669521331787</v>
       </c>
       <c r="H217" t="n">
         <v>1680</v>
@@ -6691,7 +6691,7 @@
         <v>1.90199995040894</v>
       </c>
       <c r="G218" t="n">
-        <v>1.55850124359131</v>
+        <v>1.5585013628006</v>
       </c>
       <c r="H218" t="n">
         <v>2601</v>
@@ -6836,7 +6836,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G223" t="n">
-        <v>1.60602676868439</v>
+        <v>1.60602653026581</v>
       </c>
       <c r="H223" t="n">
         <v>3500</v>
@@ -6865,7 +6865,7 @@
         <v>2.00799989700317</v>
       </c>
       <c r="G224" t="n">
-        <v>1.64535772800446</v>
+        <v>1.64535784721375</v>
       </c>
       <c r="H224" t="n">
         <v>100</v>
@@ -6894,7 +6894,7 @@
         <v>1.85399997234344</v>
       </c>
       <c r="G225" t="n">
-        <v>1.51917016506195</v>
+        <v>1.51917004585266</v>
       </c>
       <c r="H225" t="n">
         <v>20310</v>
@@ -6952,7 +6952,7 @@
         <v>1.8860000371933</v>
       </c>
       <c r="G227" t="n">
-        <v>1.54539084434509</v>
+        <v>1.54539108276367</v>
       </c>
       <c r="H227" t="n">
         <v>11268</v>
@@ -6981,7 +6981,7 @@
         <v>1.67999994754791</v>
       </c>
       <c r="G228" t="n">
-        <v>1.37659430503845</v>
+        <v>1.37659418582916</v>
       </c>
       <c r="H228" t="n">
         <v>40640</v>
@@ -7010,7 +7010,7 @@
         <v>1.72399997711182</v>
       </c>
       <c r="G229" t="n">
-        <v>1.41264796257019</v>
+        <v>1.4126478433609</v>
       </c>
       <c r="H229" t="n">
         <v>18656</v>
@@ -7039,7 +7039,7 @@
         <v>1.70200002193451</v>
       </c>
       <c r="G230" t="n">
-        <v>1.39462125301361</v>
+        <v>1.39462113380432</v>
       </c>
       <c r="H230" t="n">
         <v>23064</v>
@@ -7068,7 +7068,7 @@
         <v>1.77900004386902</v>
       </c>
       <c r="G231" t="n">
-        <v>1.45771503448486</v>
+        <v>1.45771491527557</v>
       </c>
       <c r="H231" t="n">
         <v>4259</v>
@@ -7126,7 +7126,7 @@
         <v>1.87199997901917</v>
       </c>
       <c r="G233" t="n">
-        <v>1.53391945362091</v>
+        <v>1.53391933441162</v>
       </c>
       <c r="H233" t="n">
         <v>4000</v>
@@ -7358,7 +7358,7 @@
         <v>1.84500002861023</v>
       </c>
       <c r="G241" t="n">
-        <v>1.51179540157318</v>
+        <v>1.51179563999176</v>
       </c>
       <c r="H241" t="n">
         <v>3642</v>
@@ -7387,7 +7387,7 @@
         <v>1.89800000190735</v>
       </c>
       <c r="G242" t="n">
-        <v>1.55522358417511</v>
+        <v>1.5552237033844</v>
       </c>
       <c r="H242" t="n">
         <v>6374</v>
@@ -7416,7 +7416,7 @@
         <v>1.89800000190735</v>
       </c>
       <c r="G243" t="n">
-        <v>1.55522358417511</v>
+        <v>1.5552237033844</v>
       </c>
       <c r="H243" t="n">
         <v>3380</v>
@@ -7445,7 +7445,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G244" t="n">
-        <v>1.565056681633</v>
+        <v>1.56505656242371</v>
       </c>
       <c r="H244" t="n">
         <v>627</v>
@@ -7503,7 +7503,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G246" t="n">
-        <v>1.54047441482544</v>
+        <v>1.54047453403473</v>
       </c>
       <c r="H246" t="n">
         <v>430</v>
@@ -7532,7 +7532,7 @@
         <v>1.94400000572205</v>
       </c>
       <c r="G247" t="n">
-        <v>1.59291625022888</v>
+        <v>1.59291613101959</v>
       </c>
       <c r="H247" t="n">
         <v>10</v>
@@ -7561,7 +7561,7 @@
         <v>1.94400000572205</v>
       </c>
       <c r="G248" t="n">
-        <v>1.59291625022888</v>
+        <v>1.59291613101959</v>
       </c>
       <c r="H248" t="n">
         <v>5280</v>
@@ -7590,7 +7590,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G249" t="n">
-        <v>1.55686247348785</v>
+        <v>1.55686259269714</v>
       </c>
       <c r="H249" t="n">
         <v>17229</v>
@@ -7648,7 +7648,7 @@
         <v>1.88100004196167</v>
       </c>
       <c r="G251" t="n">
-        <v>1.5412939786911</v>
+        <v>1.54129385948181</v>
       </c>
       <c r="H251" t="n">
         <v>33196</v>
@@ -7677,7 +7677,7 @@
         <v>1.83599996566772</v>
       </c>
       <c r="G252" t="n">
-        <v>1.50442087650299</v>
+        <v>1.5044207572937</v>
       </c>
       <c r="H252" t="n">
         <v>920</v>
@@ -7706,7 +7706,7 @@
         <v>1.84399998188019</v>
       </c>
       <c r="G253" t="n">
-        <v>1.51097619533539</v>
+        <v>1.5109760761261</v>
       </c>
       <c r="H253" t="n">
         <v>15268</v>
@@ -7764,7 +7764,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G255" t="n">
-        <v>1.51589250564575</v>
+        <v>1.51589238643646</v>
       </c>
       <c r="H255" t="n">
         <v>3734</v>
@@ -7822,7 +7822,7 @@
         <v>1.84099996089935</v>
       </c>
       <c r="G257" t="n">
-        <v>1.50851786136627</v>
+        <v>1.50851774215698</v>
       </c>
       <c r="H257" t="n">
         <v>9</v>
@@ -7851,7 +7851,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G258" t="n">
-        <v>1.53228044509888</v>
+        <v>1.53228056430817</v>
       </c>
       <c r="H258" t="n">
         <v>900</v>
@@ -7880,7 +7880,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G259" t="n">
-        <v>1.53228044509888</v>
+        <v>1.53228056430817</v>
       </c>
       <c r="H259" t="n">
         <v>10450</v>
@@ -7909,7 +7909,7 @@
         <v>1.84200000762939</v>
       </c>
       <c r="G260" t="n">
-        <v>1.50933730602264</v>
+        <v>1.50933718681335</v>
       </c>
       <c r="H260" t="n">
         <v>15155</v>
@@ -7938,7 +7938,7 @@
         <v>1.84099996089935</v>
       </c>
       <c r="G261" t="n">
-        <v>1.50851786136627</v>
+        <v>1.50851774215698</v>
       </c>
       <c r="H261" t="n">
         <v>9819</v>
@@ -7996,7 +7996,7 @@
         <v>1.84200000762939</v>
       </c>
       <c r="G263" t="n">
-        <v>1.50933730602264</v>
+        <v>1.50933718681335</v>
       </c>
       <c r="H263" t="n">
         <v>8077</v>
@@ -8054,7 +8054,7 @@
         <v>1.83399999141693</v>
       </c>
       <c r="G265" t="n">
-        <v>1.50278210639954</v>
+        <v>1.50278198719025</v>
       </c>
       <c r="H265" t="n">
         <v>16963</v>
@@ -8083,7 +8083,7 @@
         <v>1.82500004768372</v>
       </c>
       <c r="G266" t="n">
-        <v>1.49540758132935</v>
+        <v>1.49540746212006</v>
       </c>
       <c r="H266" t="n">
         <v>6063</v>
@@ -8141,7 +8141,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G268" t="n">
-        <v>1.54047441482544</v>
+        <v>1.54047453403473</v>
       </c>
       <c r="H268" t="n">
         <v>27145</v>
@@ -8170,7 +8170,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G269" t="n">
-        <v>1.57325065135956</v>
+        <v>1.57325041294098</v>
       </c>
       <c r="H269" t="n">
         <v>3905</v>
@@ -8228,7 +8228,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G271" t="n">
-        <v>1.55686247348785</v>
+        <v>1.55686259269714</v>
       </c>
       <c r="H271" t="n">
         <v>15130</v>
@@ -8257,7 +8257,7 @@
         <v>1.94599997997284</v>
       </c>
       <c r="G272" t="n">
-        <v>1.59455490112305</v>
+        <v>1.59455502033234</v>
       </c>
       <c r="H272" t="n">
         <v>20610</v>
@@ -8286,7 +8286,7 @@
         <v>1.96099996566772</v>
       </c>
       <c r="G273" t="n">
-        <v>1.60684597492218</v>
+        <v>1.60684609413147</v>
       </c>
       <c r="H273" t="n">
         <v>4589</v>
@@ -8431,7 +8431,7 @@
         <v>1.88399994373322</v>
       </c>
       <c r="G278" t="n">
-        <v>1.54375207424164</v>
+        <v>1.54375219345093</v>
       </c>
       <c r="H278" t="n">
         <v>4401</v>
@@ -8460,7 +8460,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G279" t="n">
-        <v>1.53228044509888</v>
+        <v>1.53228056430817</v>
       </c>
       <c r="H279" t="n">
         <v>9806</v>
@@ -8518,7 +8518,7 @@
         <v>1.93700003623962</v>
       </c>
       <c r="G281" t="n">
-        <v>1.58718049526215</v>
+        <v>1.58718037605286</v>
       </c>
       <c r="H281" t="n">
         <v>5183</v>
@@ -8547,7 +8547,7 @@
         <v>1.88699996471405</v>
       </c>
       <c r="G282" t="n">
-        <v>1.54621040821075</v>
+        <v>1.54621028900146</v>
       </c>
       <c r="H282" t="n">
         <v>3939</v>
@@ -8605,7 +8605,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G284" t="n">
-        <v>1.55686247348785</v>
+        <v>1.55686259269714</v>
       </c>
       <c r="H284" t="n">
         <v>6242</v>
@@ -8663,7 +8663,7 @@
         <v>1.87300002574921</v>
       </c>
       <c r="G286" t="n">
-        <v>1.53473877906799</v>
+        <v>1.5347386598587</v>
       </c>
       <c r="H286" t="n">
         <v>168</v>
@@ -8721,7 +8721,7 @@
         <v>1.88699996471405</v>
       </c>
       <c r="G288" t="n">
-        <v>1.54621040821075</v>
+        <v>1.54621028900146</v>
       </c>
       <c r="H288" t="n">
         <v>1302</v>
@@ -8750,7 +8750,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G289" t="n">
-        <v>1.54047441482544</v>
+        <v>1.54047453403473</v>
       </c>
       <c r="H289" t="n">
         <v>1385</v>
@@ -8837,7 +8837,7 @@
         <v>1.87800002098083</v>
       </c>
       <c r="G292" t="n">
-        <v>1.53883564472198</v>
+        <v>1.53883576393127</v>
       </c>
       <c r="H292" t="n">
         <v>1219</v>
@@ -8866,7 +8866,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G293" t="n">
-        <v>1.565056681633</v>
+        <v>1.56505656242371</v>
       </c>
       <c r="H293" t="n">
         <v>3832</v>
@@ -8924,7 +8924,7 @@
         <v>1.88900005817413</v>
       </c>
       <c r="G295" t="n">
-        <v>1.54784917831421</v>
+        <v>1.54784905910492</v>
       </c>
       <c r="H295" t="n">
         <v>658</v>
@@ -8953,7 +8953,7 @@
         <v>1.88900005817413</v>
       </c>
       <c r="G296" t="n">
-        <v>1.54784917831421</v>
+        <v>1.54784905910492</v>
       </c>
       <c r="H296" t="n">
         <v>0</v>
@@ -8982,7 +8982,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G297" t="n">
-        <v>1.55686247348785</v>
+        <v>1.55686259269714</v>
       </c>
       <c r="H297" t="n">
         <v>1280</v>
@@ -9040,7 +9040,7 @@
         <v>1.89100003242493</v>
       </c>
       <c r="G299" t="n">
-        <v>1.54948806762695</v>
+        <v>1.54948782920837</v>
       </c>
       <c r="H299" t="n">
         <v>50</v>
@@ -9069,7 +9069,7 @@
         <v>1.87699997425079</v>
       </c>
       <c r="G300" t="n">
-        <v>1.5380163192749</v>
+        <v>1.53801620006561</v>
       </c>
       <c r="H300" t="n">
         <v>1972</v>
@@ -9098,7 +9098,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G301" t="n">
-        <v>1.53228044509888</v>
+        <v>1.53228056430817</v>
       </c>
       <c r="H301" t="n">
         <v>3558</v>
@@ -9156,7 +9156,7 @@
         <v>1.89100003242493</v>
       </c>
       <c r="G303" t="n">
-        <v>1.54948806762695</v>
+        <v>1.54948782920837</v>
       </c>
       <c r="H303" t="n">
         <v>4699</v>
@@ -9185,7 +9185,7 @@
         <v>1.875</v>
       </c>
       <c r="G304" t="n">
-        <v>1.53637754917145</v>
+        <v>1.53637731075287</v>
       </c>
       <c r="H304" t="n">
         <v>4192</v>
@@ -9214,7 +9214,7 @@
         <v>1.87899994850159</v>
       </c>
       <c r="G305" t="n">
-        <v>1.53965520858765</v>
+        <v>1.53965497016907</v>
       </c>
       <c r="H305" t="n">
         <v>5851</v>
@@ -9359,7 +9359,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G310" t="n">
-        <v>1.63060879707336</v>
+        <v>1.63060867786407</v>
       </c>
       <c r="H310" t="n">
         <v>16096</v>
@@ -9417,7 +9417,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G312" t="n">
-        <v>1.64699685573578</v>
+        <v>1.64699673652649</v>
       </c>
       <c r="H312" t="n">
         <v>18453</v>
@@ -9504,7 +9504,7 @@
         <v>2.01799988746643</v>
       </c>
       <c r="G315" t="n">
-        <v>1.65355169773102</v>
+        <v>1.65355181694031</v>
       </c>
       <c r="H315" t="n">
         <v>15632</v>
@@ -9533,7 +9533,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G316" t="n">
-        <v>1.65519070625305</v>
+        <v>1.65519058704376</v>
       </c>
       <c r="H316" t="n">
         <v>11483</v>
@@ -9591,7 +9591,7 @@
         <v>2.29800009727478</v>
       </c>
       <c r="G318" t="n">
-        <v>1.88298428058624</v>
+        <v>1.88298439979553</v>
       </c>
       <c r="H318" t="n">
         <v>94367</v>
@@ -9620,7 +9620,7 @@
         <v>2.22199988365173</v>
       </c>
       <c r="G319" t="n">
-        <v>1.82070982456207</v>
+        <v>1.82070970535278</v>
       </c>
       <c r="H319" t="n">
         <v>37358</v>
@@ -9649,7 +9649,7 @@
         <v>2.23200011253357</v>
       </c>
       <c r="G320" t="n">
-        <v>1.82890403270721</v>
+        <v>1.82890379428864</v>
       </c>
       <c r="H320" t="n">
         <v>71318</v>
@@ -9736,7 +9736,7 @@
         <v>2.21600008010864</v>
       </c>
       <c r="G323" t="n">
-        <v>1.81579339504242</v>
+        <v>1.81579351425171</v>
       </c>
       <c r="H323" t="n">
         <v>40297</v>
@@ -9765,7 +9765,7 @@
         <v>2.17199993133545</v>
       </c>
       <c r="G324" t="n">
-        <v>1.77973973751068</v>
+        <v>1.77973985671997</v>
       </c>
       <c r="H324" t="n">
         <v>11729</v>
@@ -9910,7 +9910,7 @@
         <v>2.2260000705719</v>
       </c>
       <c r="G329" t="n">
-        <v>1.82398748397827</v>
+        <v>1.82398736476898</v>
       </c>
       <c r="H329" t="n">
         <v>4573</v>
@@ -9939,7 +9939,7 @@
         <v>2.21600008010864</v>
       </c>
       <c r="G330" t="n">
-        <v>1.81579339504242</v>
+        <v>1.81579351425171</v>
       </c>
       <c r="H330" t="n">
         <v>2603</v>
@@ -9997,7 +9997,7 @@
         <v>2.12199997901917</v>
       </c>
       <c r="G332" t="n">
-        <v>1.73876965045929</v>
+        <v>1.73876953125</v>
       </c>
       <c r="H332" t="n">
         <v>4555</v>
@@ -10026,7 +10026,7 @@
         <v>2.10800004005432</v>
       </c>
       <c r="G333" t="n">
-        <v>1.72729802131653</v>
+        <v>1.72729814052582</v>
       </c>
       <c r="H333" t="n">
         <v>5276</v>
@@ -10055,7 +10055,7 @@
         <v>2.13199996948242</v>
       </c>
       <c r="G334" t="n">
-        <v>1.74696350097656</v>
+        <v>1.74696373939514</v>
       </c>
       <c r="H334" t="n">
         <v>2476</v>
@@ -10084,7 +10084,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G335" t="n">
-        <v>1.72893679141998</v>
+        <v>1.72893691062927</v>
       </c>
       <c r="H335" t="n">
         <v>3195</v>
@@ -10113,7 +10113,7 @@
         <v>2.15199995040894</v>
       </c>
       <c r="G336" t="n">
-        <v>1.76335167884827</v>
+        <v>1.76335155963898</v>
       </c>
       <c r="H336" t="n">
         <v>6305</v>
@@ -10142,7 +10142,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G337" t="n">
-        <v>1.80268323421478</v>
+        <v>1.8026829957962</v>
       </c>
       <c r="H337" t="n">
         <v>8773</v>
@@ -10171,7 +10171,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G338" t="n">
-        <v>1.80268323421478</v>
+        <v>1.8026829957962</v>
       </c>
       <c r="H338" t="n">
         <v>13339</v>
@@ -10200,7 +10200,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G339" t="n">
-        <v>1.83545899391174</v>
+        <v>1.83545875549316</v>
       </c>
       <c r="H339" t="n">
         <v>10440</v>
@@ -10258,7 +10258,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G341" t="n">
-        <v>1.81087696552277</v>
+        <v>1.81087708473206</v>
       </c>
       <c r="H341" t="n">
         <v>19150</v>
@@ -10287,7 +10287,7 @@
         <v>2.20799994468689</v>
       </c>
       <c r="G342" t="n">
-        <v>1.80923807621002</v>
+        <v>1.80923819541931</v>
       </c>
       <c r="H342" t="n">
         <v>10083</v>
@@ -10316,7 +10316,7 @@
         <v>2.21199989318848</v>
       </c>
       <c r="G343" t="n">
-        <v>1.81251561641693</v>
+        <v>1.81251573562622</v>
       </c>
       <c r="H343" t="n">
         <v>17654</v>
@@ -10345,7 +10345,7 @@
         <v>2.2720000743866</v>
       </c>
       <c r="G344" t="n">
-        <v>1.86167979240417</v>
+        <v>1.86167967319489</v>
       </c>
       <c r="H344" t="n">
         <v>19071</v>
@@ -10374,7 +10374,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G345" t="n">
-        <v>1.83545899391174</v>
+        <v>1.83545875549316</v>
       </c>
       <c r="H345" t="n">
         <v>20200</v>
@@ -10403,7 +10403,7 @@
         <v>2.27600002288818</v>
       </c>
       <c r="G346" t="n">
-        <v>1.86495757102966</v>
+        <v>1.86495745182037</v>
       </c>
       <c r="H346" t="n">
         <v>12118</v>
@@ -10432,7 +10432,7 @@
         <v>2.26799988746643</v>
       </c>
       <c r="G347" t="n">
-        <v>1.85840225219727</v>
+        <v>1.85840201377869</v>
       </c>
       <c r="H347" t="n">
         <v>10030</v>
@@ -10461,7 +10461,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G348" t="n">
-        <v>1.87642884254456</v>
+        <v>1.87642896175385</v>
       </c>
       <c r="H348" t="n">
         <v>15563</v>
@@ -10490,7 +10490,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G349" t="n">
-        <v>1.8846230506897</v>
+        <v>1.88462293148041</v>
       </c>
       <c r="H349" t="n">
         <v>33981</v>
@@ -10519,7 +10519,7 @@
         <v>2.31800007820129</v>
       </c>
       <c r="G350" t="n">
-        <v>1.89937257766724</v>
+        <v>1.89937245845795</v>
       </c>
       <c r="H350" t="n">
         <v>4160</v>
@@ -10548,7 +10548,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G351" t="n">
-        <v>1.91739892959595</v>
+        <v>1.91739916801453</v>
       </c>
       <c r="H351" t="n">
         <v>6240</v>
@@ -10606,7 +10606,7 @@
         <v>2.27600002288818</v>
       </c>
       <c r="G353" t="n">
-        <v>1.86495757102966</v>
+        <v>1.86495745182037</v>
       </c>
       <c r="H353" t="n">
         <v>5451</v>
@@ -10635,7 +10635,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G354" t="n">
-        <v>1.86823523044586</v>
+        <v>1.86823511123657</v>
       </c>
       <c r="H354" t="n">
         <v>9851</v>
@@ -10722,7 +10722,7 @@
         <v>2.26200008392334</v>
       </c>
       <c r="G357" t="n">
-        <v>1.93850827217102</v>
+        <v>1.93850815296173</v>
       </c>
       <c r="H357" t="n">
         <v>47650</v>
@@ -10751,7 +10751,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G358" t="n">
-        <v>1.97107362747192</v>
+        <v>1.97107374668121</v>
       </c>
       <c r="H358" t="n">
         <v>23455</v>
@@ -10780,7 +10780,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G359" t="n">
-        <v>1.97107362747192</v>
+        <v>1.97107374668121</v>
       </c>
       <c r="H359" t="n">
         <v>18785</v>
@@ -10809,7 +10809,7 @@
         <v>2.25</v>
       </c>
       <c r="G360" t="n">
-        <v>1.92822420597076</v>
+        <v>1.92822432518005</v>
       </c>
       <c r="H360" t="n">
         <v>25228</v>
@@ -10896,7 +10896,7 @@
         <v>2.28600001335144</v>
       </c>
       <c r="G363" t="n">
-        <v>1.9590756893158</v>
+        <v>1.95907580852509</v>
       </c>
       <c r="H363" t="n">
         <v>13959</v>
@@ -10925,7 +10925,7 @@
         <v>2.28600001335144</v>
       </c>
       <c r="G364" t="n">
-        <v>1.9590756893158</v>
+        <v>1.95907580852509</v>
       </c>
       <c r="H364" t="n">
         <v>0</v>
@@ -10983,7 +10983,7 @@
         <v>2.25</v>
       </c>
       <c r="G366" t="n">
-        <v>1.92822420597076</v>
+        <v>1.92822432518005</v>
       </c>
       <c r="H366" t="n">
         <v>799</v>
@@ -11012,7 +11012,7 @@
         <v>2.24799990653992</v>
       </c>
       <c r="G367" t="n">
-        <v>1.92651009559631</v>
+        <v>1.92651033401489</v>
       </c>
       <c r="H367" t="n">
         <v>1585</v>
@@ -11041,7 +11041,7 @@
         <v>2.24799990653992</v>
       </c>
       <c r="G368" t="n">
-        <v>1.92651009559631</v>
+        <v>1.92651033401489</v>
       </c>
       <c r="H368" t="n">
         <v>0</v>
@@ -11070,7 +11070,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G369" t="n">
-        <v>1.95393395423889</v>
+        <v>1.95393407344818</v>
       </c>
       <c r="H369" t="n">
         <v>20269</v>
@@ -11099,7 +11099,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G370" t="n">
-        <v>1.95393395423889</v>
+        <v>1.95393407344818</v>
       </c>
       <c r="H370" t="n">
         <v>0</v>
@@ -11157,7 +11157,7 @@
         <v>2.22399997711182</v>
       </c>
       <c r="G372" t="n">
-        <v>1.90594255924225</v>
+        <v>1.90594244003296</v>
       </c>
       <c r="H372" t="n">
         <v>8910</v>
@@ -11186,7 +11186,7 @@
         <v>2.22399997711182</v>
       </c>
       <c r="G373" t="n">
-        <v>1.90594255924225</v>
+        <v>1.90594244003296</v>
       </c>
       <c r="H373" t="n">
         <v>0</v>
@@ -11215,7 +11215,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G374" t="n">
-        <v>1.89394474029541</v>
+        <v>1.8939448595047</v>
       </c>
       <c r="H374" t="n">
         <v>3200</v>
@@ -11244,7 +11244,7 @@
         <v>2.18400001525879</v>
       </c>
       <c r="G375" t="n">
-        <v>1.87166285514832</v>
+        <v>1.8716629743576</v>
       </c>
       <c r="H375" t="n">
         <v>10669</v>
@@ -11331,7 +11331,7 @@
         <v>2.23399996757507</v>
       </c>
       <c r="G378" t="n">
-        <v>1.91451239585876</v>
+        <v>1.91451227664948</v>
       </c>
       <c r="H378" t="n">
         <v>12050</v>
@@ -11360,7 +11360,7 @@
         <v>2.20199990272522</v>
       </c>
       <c r="G379" t="n">
-        <v>1.88708877563477</v>
+        <v>1.88708853721619</v>
       </c>
       <c r="H379" t="n">
         <v>17691</v>
@@ -11418,7 +11418,7 @@
         <v>2.23799991607666</v>
       </c>
       <c r="G381" t="n">
-        <v>1.91794049739838</v>
+        <v>1.9179402589798</v>
       </c>
       <c r="H381" t="n">
         <v>6850</v>
@@ -11447,7 +11447,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G382" t="n">
-        <v>1.88537502288818</v>
+        <v>1.8853747844696</v>
       </c>
       <c r="H382" t="n">
         <v>1450</v>
@@ -11476,7 +11476,7 @@
         <v>2.18199992179871</v>
       </c>
       <c r="G383" t="n">
-        <v>1.86994910240173</v>
+        <v>1.86994898319244</v>
       </c>
       <c r="H383" t="n">
         <v>1040</v>
@@ -11505,7 +11505,7 @@
         <v>2.2039999961853</v>
       </c>
       <c r="G384" t="n">
-        <v>1.88880276679993</v>
+        <v>1.88880300521851</v>
       </c>
       <c r="H384" t="n">
         <v>6700</v>
@@ -11534,7 +11534,7 @@
         <v>2.2279999256134</v>
       </c>
       <c r="G385" t="n">
-        <v>1.90937030315399</v>
+        <v>1.90937042236328</v>
       </c>
       <c r="H385" t="n">
         <v>9416</v>
@@ -11563,7 +11563,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G386" t="n">
-        <v>1.90251445770264</v>
+        <v>1.90251469612122</v>
       </c>
       <c r="H386" t="n">
         <v>12328</v>
@@ -11592,7 +11592,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G387" t="n">
-        <v>1.89394474029541</v>
+        <v>1.8939448595047</v>
       </c>
       <c r="H387" t="n">
         <v>391</v>
@@ -11621,7 +11621,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G388" t="n">
-        <v>1.89394474029541</v>
+        <v>1.8939448595047</v>
       </c>
       <c r="H388" t="n">
         <v>0</v>
@@ -11650,7 +11650,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G389" t="n">
-        <v>1.89394474029541</v>
+        <v>1.8939448595047</v>
       </c>
       <c r="H389" t="n">
         <v>3804</v>
@@ -11679,7 +11679,7 @@
         <v>2.23399996757507</v>
       </c>
       <c r="G390" t="n">
-        <v>1.91451239585876</v>
+        <v>1.91451227664948</v>
       </c>
       <c r="H390" t="n">
         <v>7104</v>
@@ -11708,7 +11708,7 @@
         <v>2.23799991607666</v>
       </c>
       <c r="G391" t="n">
-        <v>1.91794049739838</v>
+        <v>1.9179402589798</v>
       </c>
       <c r="H391" t="n">
         <v>125</v>
@@ -11795,7 +11795,7 @@
         <v>2.29200005531311</v>
       </c>
       <c r="G394" t="n">
-        <v>1.96421778202057</v>
+        <v>1.96421790122986</v>
       </c>
       <c r="H394" t="n">
         <v>3374</v>
@@ -11853,7 +11853,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G396" t="n">
-        <v>1.97107362747192</v>
+        <v>1.97107374668121</v>
       </c>
       <c r="H396" t="n">
         <v>2881</v>
@@ -11882,7 +11882,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G397" t="n">
-        <v>1.98821365833282</v>
+        <v>1.98821353912354</v>
       </c>
       <c r="H397" t="n">
         <v>4950</v>
@@ -11911,7 +11911,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G398" t="n">
-        <v>1.98821365833282</v>
+        <v>1.98821353912354</v>
       </c>
       <c r="H398" t="n">
         <v>1201</v>
@@ -11940,7 +11940,7 @@
         <v>2.31800007820129</v>
       </c>
       <c r="G399" t="n">
-        <v>1.98649954795837</v>
+        <v>1.98649966716766</v>
       </c>
       <c r="H399" t="n">
         <v>506</v>
@@ -11969,7 +11969,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G400" t="n">
-        <v>1.97964358329773</v>
+        <v>1.97964346408844</v>
       </c>
       <c r="H400" t="n">
         <v>5628</v>
@@ -11998,7 +11998,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G401" t="n">
-        <v>1.97964358329773</v>
+        <v>1.97964346408844</v>
       </c>
       <c r="H401" t="n">
         <v>0</v>
@@ -12027,7 +12027,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G402" t="n">
-        <v>2.12533140182495</v>
+        <v>2.12533164024353</v>
       </c>
       <c r="H402" t="n">
         <v>107928</v>
@@ -12085,7 +12085,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G404" t="n">
-        <v>2.05677247047424</v>
+        <v>2.0567729473114</v>
       </c>
       <c r="H404" t="n">
         <v>20365</v>
@@ -12114,7 +12114,7 @@
         <v>2.42600011825562</v>
       </c>
       <c r="G405" t="n">
-        <v>2.07905459403992</v>
+        <v>2.07905411720276</v>
       </c>
       <c r="H405" t="n">
         <v>6400</v>
@@ -12143,7 +12143,7 @@
         <v>2.42799997329712</v>
       </c>
       <c r="G406" t="n">
-        <v>2.08076810836792</v>
+        <v>2.08076858520508</v>
       </c>
       <c r="H406" t="n">
         <v>5713</v>
@@ -12172,7 +12172,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G407" t="n">
-        <v>2.06534266471863</v>
+        <v>2.06534242630005</v>
       </c>
       <c r="H407" t="n">
         <v>8713</v>
@@ -12201,7 +12201,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G408" t="n">
-        <v>2.06534266471863</v>
+        <v>2.06534242630005</v>
       </c>
       <c r="H408" t="n">
         <v>0</v>
@@ -12230,7 +12230,7 @@
         <v>2.40400004386902</v>
       </c>
       <c r="G409" t="n">
-        <v>2.06020069122314</v>
+        <v>2.06020045280457</v>
       </c>
       <c r="H409" t="n">
         <v>10784</v>
@@ -12259,7 +12259,7 @@
         <v>2.41799998283386</v>
       </c>
       <c r="G410" t="n">
-        <v>2.07219862937927</v>
+        <v>2.07219815254211</v>
       </c>
       <c r="H410" t="n">
         <v>1517</v>
@@ -12288,7 +12288,7 @@
         <v>2.41799998283386</v>
       </c>
       <c r="G411" t="n">
-        <v>2.07219862937927</v>
+        <v>2.07219815254211</v>
       </c>
       <c r="H411" t="n">
         <v>22152</v>
@@ -12317,7 +12317,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G412" t="n">
-        <v>2.12533140182495</v>
+        <v>2.12533164024353</v>
       </c>
       <c r="H412" t="n">
         <v>13189</v>
@@ -12404,7 +12404,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G415" t="n">
-        <v>2.09962224960327</v>
+        <v>2.09962201118469</v>
       </c>
       <c r="H415" t="n">
         <v>3641</v>
@@ -12433,7 +12433,7 @@
         <v>2.4539999961853</v>
       </c>
       <c r="G416" t="n">
-        <v>2.10304999351501</v>
+        <v>2.10304975509644</v>
       </c>
       <c r="H416" t="n">
         <v>4434</v>
@@ -12578,7 +12578,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G421" t="n">
-        <v>2.07391262054443</v>
+        <v>2.07391238212585</v>
       </c>
       <c r="H421" t="n">
         <v>13845</v>
@@ -12607,7 +12607,7 @@
         <v>2.44799995422363</v>
       </c>
       <c r="G422" t="n">
-        <v>2.09790778160095</v>
+        <v>2.09790802001953</v>
       </c>
       <c r="H422" t="n">
         <v>3874</v>
@@ -12636,7 +12636,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G423" t="n">
-        <v>2.1167619228363</v>
+        <v>2.11676168441772</v>
       </c>
       <c r="H423" t="n">
         <v>2588</v>
@@ -12665,7 +12665,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G424" t="n">
-        <v>2.07391262054443</v>
+        <v>2.07391238212585</v>
       </c>
       <c r="H424" t="n">
         <v>2466</v>
@@ -12694,7 +12694,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G425" t="n">
-        <v>2.09962224960327</v>
+        <v>2.09962201118469</v>
       </c>
       <c r="H425" t="n">
         <v>5724</v>
@@ -12723,7 +12723,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G426" t="n">
-        <v>2.08248209953308</v>
+        <v>2.08248233795166</v>
       </c>
       <c r="H426" t="n">
         <v>2302</v>
@@ -12839,7 +12839,7 @@
         <v>2.45799994468689</v>
       </c>
       <c r="G430" t="n">
-        <v>2.10647797584534</v>
+        <v>2.10647773742676</v>
       </c>
       <c r="H430" t="n">
         <v>4919</v>
@@ -12868,7 +12868,7 @@
         <v>2.45799994468689</v>
       </c>
       <c r="G431" t="n">
-        <v>2.10647797584534</v>
+        <v>2.10647773742676</v>
       </c>
       <c r="H431" t="n">
         <v>0</v>
@@ -12926,7 +12926,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G433" t="n">
-        <v>2.09962224960327</v>
+        <v>2.09962201118469</v>
       </c>
       <c r="H433" t="n">
         <v>1120</v>
@@ -13042,7 +13042,7 @@
         <v>2.44799995422363</v>
       </c>
       <c r="G437" t="n">
-        <v>2.09790778160095</v>
+        <v>2.09790802001953</v>
       </c>
       <c r="H437" t="n">
         <v>5750</v>
@@ -13071,7 +13071,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G438" t="n">
-        <v>2.08248209953308</v>
+        <v>2.08248233795166</v>
       </c>
       <c r="H438" t="n">
         <v>13950</v>
@@ -13100,7 +13100,7 @@
         <v>2.44799995422363</v>
       </c>
       <c r="G439" t="n">
-        <v>2.09790778160095</v>
+        <v>2.09790802001953</v>
       </c>
       <c r="H439" t="n">
         <v>10563</v>
@@ -13129,7 +13129,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G440" t="n">
-        <v>2.17675089836121</v>
+        <v>2.17675113677979</v>
       </c>
       <c r="H440" t="n">
         <v>17588</v>
@@ -13303,7 +13303,7 @@
         <v>2.47199988365173</v>
       </c>
       <c r="G446" t="n">
-        <v>2.11847543716431</v>
+        <v>2.11847567558289</v>
       </c>
       <c r="H446" t="n">
         <v>7321</v>
@@ -13332,7 +13332,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G447" t="n">
-        <v>2.1167619228363</v>
+        <v>2.11676168441772</v>
       </c>
       <c r="H447" t="n">
         <v>3053</v>
@@ -13361,7 +13361,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G448" t="n">
-        <v>2.09105205535889</v>
+        <v>2.09105229377747</v>
       </c>
       <c r="H448" t="n">
         <v>6572</v>
@@ -13390,7 +13390,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G449" t="n">
-        <v>2.09962224960327</v>
+        <v>2.09962201118469</v>
       </c>
       <c r="H449" t="n">
         <v>450</v>
@@ -13419,7 +13419,7 @@
         <v>2.4779999256134</v>
       </c>
       <c r="G450" t="n">
-        <v>2.12361741065979</v>
+        <v>2.12361764907837</v>
       </c>
       <c r="H450" t="n">
         <v>13080</v>
@@ -13448,7 +13448,7 @@
         <v>2.46399998664856</v>
       </c>
       <c r="G451" t="n">
-        <v>2.11161971092224</v>
+        <v>2.11161994934082</v>
       </c>
       <c r="H451" t="n">
         <v>6894</v>
@@ -13477,7 +13477,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G452" t="n">
-        <v>2.09105205535889</v>
+        <v>2.09105229377747</v>
       </c>
       <c r="H452" t="n">
         <v>5134</v>
@@ -13535,7 +13535,7 @@
         <v>2.4539999961853</v>
       </c>
       <c r="G454" t="n">
-        <v>2.10304999351501</v>
+        <v>2.10304975509644</v>
       </c>
       <c r="H454" t="n">
         <v>7892</v>
@@ -13564,7 +13564,7 @@
         <v>2.46399998664856</v>
       </c>
       <c r="G455" t="n">
-        <v>2.11161971092224</v>
+        <v>2.11161994934082</v>
       </c>
       <c r="H455" t="n">
         <v>1095</v>
@@ -13593,7 +13593,7 @@
         <v>2.4779999256134</v>
       </c>
       <c r="G456" t="n">
-        <v>2.12361741065979</v>
+        <v>2.12361764907837</v>
       </c>
       <c r="H456" t="n">
         <v>1700</v>
@@ -13680,7 +13680,7 @@
         <v>2.51799988746643</v>
       </c>
       <c r="G459" t="n">
-        <v>2.15789699554443</v>
+        <v>2.15789723396301</v>
       </c>
       <c r="H459" t="n">
         <v>1</v>
@@ -13767,7 +13767,7 @@
         <v>2.49799990653992</v>
       </c>
       <c r="G462" t="n">
-        <v>2.14075756072998</v>
+        <v>2.14075708389282</v>
       </c>
       <c r="H462" t="n">
         <v>6700</v>
@@ -13796,7 +13796,7 @@
         <v>2.46399998664856</v>
       </c>
       <c r="G463" t="n">
-        <v>2.11161971092224</v>
+        <v>2.11161994934082</v>
       </c>
       <c r="H463" t="n">
         <v>801</v>
@@ -13883,7 +13883,7 @@
         <v>2.49600005149841</v>
       </c>
       <c r="G466" t="n">
-        <v>2.13904333114624</v>
+        <v>2.13904356956482</v>
       </c>
       <c r="H466" t="n">
         <v>763</v>
@@ -13912,7 +13912,7 @@
         <v>2.49600005149841</v>
       </c>
       <c r="G467" t="n">
-        <v>2.13904333114624</v>
+        <v>2.13904356956482</v>
       </c>
       <c r="H467" t="n">
         <v>1434</v>
@@ -13970,7 +13970,7 @@
         <v>2.51799988746643</v>
       </c>
       <c r="G469" t="n">
-        <v>2.15789699554443</v>
+        <v>2.15789723396301</v>
       </c>
       <c r="H469" t="n">
         <v>3027</v>
@@ -14028,7 +14028,7 @@
         <v>2.49799990653992</v>
       </c>
       <c r="G471" t="n">
-        <v>2.14075756072998</v>
+        <v>2.14075708389282</v>
       </c>
       <c r="H471" t="n">
         <v>150</v>
@@ -14057,7 +14057,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G472" t="n">
-        <v>2.12533140182495</v>
+        <v>2.12533164024353</v>
       </c>
       <c r="H472" t="n">
         <v>8551</v>
@@ -14115,7 +14115,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G474" t="n">
-        <v>2.15104103088379</v>
+        <v>2.15104126930237</v>
       </c>
       <c r="H474" t="n">
         <v>6956</v>
@@ -14144,7 +14144,7 @@
         <v>2.51799988746643</v>
       </c>
       <c r="G475" t="n">
-        <v>2.15789699554443</v>
+        <v>2.15789723396301</v>
       </c>
       <c r="H475" t="n">
         <v>1188</v>
@@ -14202,7 +14202,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G477" t="n">
-        <v>2.09962224960327</v>
+        <v>2.09962201118469</v>
       </c>
       <c r="H477" t="n">
         <v>893</v>
@@ -14289,7 +14289,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G480" t="n">
-        <v>2.05677247047424</v>
+        <v>2.0567729473114</v>
       </c>
       <c r="H480" t="n">
         <v>6507</v>
@@ -14318,7 +14318,7 @@
         <v>2.37199997901917</v>
       </c>
       <c r="G481" t="n">
-        <v>2.03277683258057</v>
+        <v>2.03277707099915</v>
       </c>
       <c r="H481" t="n">
         <v>6951</v>
@@ -14347,7 +14347,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G482" t="n">
-        <v>2.04820275306702</v>
+        <v>2.0482029914856</v>
       </c>
       <c r="H482" t="n">
         <v>5071</v>
@@ -14376,7 +14376,7 @@
         <v>2.42600011825562</v>
       </c>
       <c r="G483" t="n">
-        <v>2.07905459403992</v>
+        <v>2.07905411720276</v>
       </c>
       <c r="H483" t="n">
         <v>2813</v>
@@ -14405,7 +14405,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G484" t="n">
-        <v>2.04820275306702</v>
+        <v>2.0482029914856</v>
       </c>
       <c r="H484" t="n">
         <v>355</v>
@@ -14463,7 +14463,7 @@
         <v>2.37199997901917</v>
       </c>
       <c r="G486" t="n">
-        <v>2.03277683258057</v>
+        <v>2.03277707099915</v>
       </c>
       <c r="H486" t="n">
         <v>1218</v>
@@ -14492,7 +14492,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G487" t="n">
-        <v>2.06534266471863</v>
+        <v>2.06534242630005</v>
       </c>
       <c r="H487" t="n">
         <v>3267</v>
@@ -14521,7 +14521,7 @@
         <v>2.39199995994568</v>
       </c>
       <c r="G488" t="n">
-        <v>2.0499165058136</v>
+        <v>2.04991674423218</v>
       </c>
       <c r="H488" t="n">
         <v>1156</v>
@@ -14550,7 +14550,7 @@
         <v>2.49799990653992</v>
       </c>
       <c r="G489" t="n">
-        <v>2.14075756072998</v>
+        <v>2.14075708389282</v>
       </c>
       <c r="H489" t="n">
         <v>2763</v>
@@ -14579,7 +14579,7 @@
         <v>2.49600005149841</v>
       </c>
       <c r="G490" t="n">
-        <v>2.13904333114624</v>
+        <v>2.13904356956482</v>
       </c>
       <c r="H490" t="n">
         <v>1802</v>
@@ -14608,7 +14608,7 @@
         <v>2.44799995422363</v>
       </c>
       <c r="G491" t="n">
-        <v>2.09790778160095</v>
+        <v>2.09790802001953</v>
       </c>
       <c r="H491" t="n">
         <v>2342</v>
@@ -14637,7 +14637,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G492" t="n">
-        <v>2.12533140182495</v>
+        <v>2.12533164024353</v>
       </c>
       <c r="H492" t="n">
         <v>182</v>
@@ -14724,7 +14724,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G495" t="n">
-        <v>2.12533140182495</v>
+        <v>2.12533164024353</v>
       </c>
       <c r="H495" t="n">
         <v>1145</v>
@@ -14753,7 +14753,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G496" t="n">
-        <v>2.1167619228363</v>
+        <v>2.11676168441772</v>
       </c>
       <c r="H496" t="n">
         <v>950</v>
@@ -14782,7 +14782,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G497" t="n">
-        <v>2.1167619228363</v>
+        <v>2.11676168441772</v>
       </c>
       <c r="H497" t="n">
         <v>0</v>
@@ -14811,7 +14811,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G498" t="n">
-        <v>2.1167619228363</v>
+        <v>2.11676168441772</v>
       </c>
       <c r="H498" t="n">
         <v>0</v>
@@ -14840,7 +14840,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G499" t="n">
-        <v>2.1167619228363</v>
+        <v>2.11676168441772</v>
       </c>
       <c r="H499" t="n">
         <v>0</v>
@@ -14869,7 +14869,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G500" t="n">
-        <v>2.08248209953308</v>
+        <v>2.08248233795166</v>
       </c>
       <c r="H500" t="n">
         <v>6624</v>
@@ -14956,7 +14956,7 @@
         <v>2.35800004005432</v>
       </c>
       <c r="G503" t="n">
-        <v>2.02077889442444</v>
+        <v>2.02077913284302</v>
       </c>
       <c r="H503" t="n">
         <v>2564</v>
@@ -15014,7 +15014,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G505" t="n">
-        <v>2.08248209953308</v>
+        <v>2.08248233795166</v>
       </c>
       <c r="H505" t="n">
         <v>608</v>
@@ -15072,7 +15072,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G507" t="n">
-        <v>2.09962224960327</v>
+        <v>2.09962201118469</v>
       </c>
       <c r="H507" t="n">
         <v>2401</v>
@@ -15101,7 +15101,7 @@
         <v>2.44799995422363</v>
       </c>
       <c r="G508" t="n">
-        <v>2.09790778160095</v>
+        <v>2.09790802001953</v>
       </c>
       <c r="H508" t="n">
         <v>2286</v>
@@ -15130,7 +15130,7 @@
         <v>2.44799995422363</v>
       </c>
       <c r="G509" t="n">
-        <v>2.09790778160095</v>
+        <v>2.09790802001953</v>
       </c>
       <c r="H509" t="n">
         <v>0</v>
@@ -15159,7 +15159,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G510" t="n">
-        <v>2.09962224960327</v>
+        <v>2.09962201118469</v>
       </c>
       <c r="H510" t="n">
         <v>370</v>
@@ -15246,7 +15246,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G513" t="n">
-        <v>2.09962224960327</v>
+        <v>2.09962201118469</v>
       </c>
       <c r="H513" t="n">
         <v>8107</v>
@@ -15275,7 +15275,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G514" t="n">
-        <v>2.07391262054443</v>
+        <v>2.07391238212585</v>
       </c>
       <c r="H514" t="n">
         <v>7736</v>
@@ -15304,7 +15304,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G515" t="n">
-        <v>2.05677247047424</v>
+        <v>2.0567729473114</v>
       </c>
       <c r="H515" t="n">
         <v>7000</v>
@@ -15333,7 +15333,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G516" t="n">
-        <v>2.08248209953308</v>
+        <v>2.08248233795166</v>
       </c>
       <c r="H516" t="n">
         <v>1125</v>
@@ -15362,7 +15362,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G517" t="n">
-        <v>2.09105205535889</v>
+        <v>2.09105229377747</v>
       </c>
       <c r="H517" t="n">
         <v>5717</v>
@@ -15391,7 +15391,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G518" t="n">
-        <v>2.09105205535889</v>
+        <v>2.09105229377747</v>
       </c>
       <c r="H518" t="n">
         <v>10837</v>
@@ -15420,7 +15420,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G519" t="n">
-        <v>2.08248209953308</v>
+        <v>2.08248233795166</v>
       </c>
       <c r="H519" t="n">
         <v>8541</v>
@@ -15449,7 +15449,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G520" t="n">
-        <v>2.08248209953308</v>
+        <v>2.08248233795166</v>
       </c>
       <c r="H520" t="n">
         <v>321</v>
@@ -15594,7 +15594,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G525" t="n">
-        <v>2.05677247047424</v>
+        <v>2.0567729473114</v>
       </c>
       <c r="H525" t="n">
         <v>398</v>
@@ -15623,7 +15623,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G526" t="n">
-        <v>2.05677247047424</v>
+        <v>2.0567729473114</v>
       </c>
       <c r="H526" t="n">
         <v>5700</v>
@@ -15739,7 +15739,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G530" t="n">
-        <v>2.09962224960327</v>
+        <v>2.09962201118469</v>
       </c>
       <c r="H530" t="n">
         <v>9824</v>
@@ -15768,7 +15768,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G531" t="n">
-        <v>2.07391262054443</v>
+        <v>2.07391238212585</v>
       </c>
       <c r="H531" t="n">
         <v>7994</v>
@@ -15797,7 +15797,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G532" t="n">
-        <v>2.07391262054443</v>
+        <v>2.07391238212585</v>
       </c>
       <c r="H532" t="n">
         <v>23272</v>
@@ -15826,7 +15826,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G533" t="n">
-        <v>2.07391262054443</v>
+        <v>2.07391238212585</v>
       </c>
       <c r="H533" t="n">
         <v>0</v>
@@ -15855,7 +15855,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G534" t="n">
-        <v>2.05677247047424</v>
+        <v>2.0567729473114</v>
       </c>
       <c r="H534" t="n">
         <v>361</v>
@@ -15884,7 +15884,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G535" t="n">
-        <v>2.05677247047424</v>
+        <v>2.0567729473114</v>
       </c>
       <c r="H535" t="n">
         <v>1190</v>
@@ -15913,7 +15913,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G536" t="n">
-        <v>2.04820275306702</v>
+        <v>2.0482029914856</v>
       </c>
       <c r="H536" t="n">
         <v>1440</v>
@@ -16029,7 +16029,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G540" t="n">
-        <v>2.05677247047424</v>
+        <v>2.0567729473114</v>
       </c>
       <c r="H540" t="n">
         <v>910</v>
@@ -16058,7 +16058,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G541" t="n">
-        <v>2.09105205535889</v>
+        <v>2.09105229377747</v>
       </c>
       <c r="H541" t="n">
         <v>6273</v>
@@ -16087,7 +16087,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G542" t="n">
-        <v>2.09105205535889</v>
+        <v>2.09105229377747</v>
       </c>
       <c r="H542" t="n">
         <v>0</v>
@@ -16116,7 +16116,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G543" t="n">
-        <v>2.09962224960327</v>
+        <v>2.09962201118469</v>
       </c>
       <c r="H543" t="n">
         <v>100</v>
@@ -16145,7 +16145,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G544" t="n">
-        <v>2.09962224960327</v>
+        <v>2.09962201118469</v>
       </c>
       <c r="H544" t="n">
         <v>2265</v>
@@ -16174,7 +16174,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G545" t="n">
-        <v>2.09962224960327</v>
+        <v>2.09962201118469</v>
       </c>
       <c r="H545" t="n">
         <v>0</v>
@@ -16232,7 +16232,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G547" t="n">
-        <v>2.08248209953308</v>
+        <v>2.08248233795166</v>
       </c>
       <c r="H547" t="n">
         <v>3430</v>
@@ -16261,7 +16261,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G548" t="n">
-        <v>2.04820275306702</v>
+        <v>2.0482029914856</v>
       </c>
       <c r="H548" t="n">
         <v>110</v>
@@ -16319,7 +16319,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G550" t="n">
-        <v>2.08248209953308</v>
+        <v>2.08248233795166</v>
       </c>
       <c r="H550" t="n">
         <v>678</v>
@@ -16406,7 +16406,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G553" t="n">
-        <v>2.08248209953308</v>
+        <v>2.08248233795166</v>
       </c>
       <c r="H553" t="n">
         <v>290</v>
@@ -16435,7 +16435,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G554" t="n">
-        <v>2.07391262054443</v>
+        <v>2.07391238212585</v>
       </c>
       <c r="H554" t="n">
         <v>1580</v>
@@ -16464,7 +16464,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G555" t="n">
-        <v>2.06534266471863</v>
+        <v>2.06534242630005</v>
       </c>
       <c r="H555" t="n">
         <v>1952</v>
@@ -16522,7 +16522,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G557" t="n">
-        <v>2.1167619228363</v>
+        <v>2.11676168441772</v>
       </c>
       <c r="H557" t="n">
         <v>24020</v>
@@ -16580,7 +16580,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G559" t="n">
-        <v>2.06534266471863</v>
+        <v>2.06534242630005</v>
       </c>
       <c r="H559" t="n">
         <v>459</v>
@@ -16609,7 +16609,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G560" t="n">
-        <v>2.06534266471863</v>
+        <v>2.06534242630005</v>
       </c>
       <c r="H560" t="n">
         <v>2100</v>
@@ -16638,7 +16638,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G561" t="n">
-        <v>2.09105205535889</v>
+        <v>2.09105229377747</v>
       </c>
       <c r="H561" t="n">
         <v>8100</v>
@@ -16667,7 +16667,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G562" t="n">
-        <v>2.08248209953308</v>
+        <v>2.08248233795166</v>
       </c>
       <c r="H562" t="n">
         <v>10</v>
@@ -16696,7 +16696,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G563" t="n">
-        <v>2.08248209953308</v>
+        <v>2.08248233795166</v>
       </c>
       <c r="H563" t="n">
         <v>0</v>
@@ -16783,7 +16783,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G566" t="n">
-        <v>2.12533140182495</v>
+        <v>2.12533164024353</v>
       </c>
       <c r="H566" t="n">
         <v>11930</v>
@@ -16870,7 +16870,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G569" t="n">
-        <v>2.07391262054443</v>
+        <v>2.07391238212585</v>
       </c>
       <c r="H569" t="n">
         <v>6674</v>
@@ -16899,7 +16899,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G570" t="n">
-        <v>2.09962224960327</v>
+        <v>2.09962201118469</v>
       </c>
       <c r="H570" t="n">
         <v>1093</v>
@@ -16957,7 +16957,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G572" t="n">
-        <v>2.09105205535889</v>
+        <v>2.09105229377747</v>
       </c>
       <c r="H572" t="n">
         <v>2665</v>
@@ -16986,7 +16986,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G573" t="n">
-        <v>2.09105205535889</v>
+        <v>2.09105229377747</v>
       </c>
       <c r="H573" t="n">
         <v>2589</v>
@@ -17015,7 +17015,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G574" t="n">
-        <v>2.09962224960327</v>
+        <v>2.09962201118469</v>
       </c>
       <c r="H574" t="n">
         <v>7837</v>
@@ -17073,7 +17073,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G576" t="n">
-        <v>2.09962224960327</v>
+        <v>2.09962201118469</v>
       </c>
       <c r="H576" t="n">
         <v>7199</v>
@@ -17247,7 +17247,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G582" t="n">
-        <v>2.16818118095398</v>
+        <v>2.1681809425354</v>
       </c>
       <c r="H582" t="n">
         <v>1455</v>
@@ -17276,7 +17276,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G583" t="n">
-        <v>2.16818118095398</v>
+        <v>2.1681809425354</v>
       </c>
       <c r="H583" t="n">
         <v>2779</v>
@@ -17363,7 +17363,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G586" t="n">
-        <v>2.16818118095398</v>
+        <v>2.1681809425354</v>
       </c>
       <c r="H586" t="n">
         <v>6585</v>
@@ -17479,7 +17479,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G590" t="n">
-        <v>2.17675089836121</v>
+        <v>2.17675113677979</v>
       </c>
       <c r="H590" t="n">
         <v>47108</v>
@@ -17508,7 +17508,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G591" t="n">
-        <v>2.18532085418701</v>
+        <v>2.18532061576843</v>
       </c>
       <c r="H591" t="n">
         <v>11111</v>
@@ -17537,7 +17537,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G592" t="n">
-        <v>2.29672956466675</v>
+        <v>2.29672932624817</v>
       </c>
       <c r="H592" t="n">
         <v>109129</v>
@@ -17566,7 +17566,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G593" t="n">
-        <v>2.29672956466675</v>
+        <v>2.29672932624817</v>
       </c>
       <c r="H593" t="n">
         <v>67369</v>
@@ -17653,7 +17653,7 @@
         <v>2.75</v>
       </c>
       <c r="G596" t="n">
-        <v>2.35671830177307</v>
+        <v>2.35671854019165</v>
       </c>
       <c r="H596" t="n">
         <v>31138</v>
@@ -17682,7 +17682,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G597" t="n">
-        <v>2.44241714477539</v>
+        <v>2.44241738319397</v>
       </c>
       <c r="H597" t="n">
         <v>71018</v>
@@ -17740,7 +17740,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G599" t="n">
-        <v>2.46812701225281</v>
+        <v>2.46812725067139</v>
       </c>
       <c r="H599" t="n">
         <v>10346</v>
@@ -17798,7 +17798,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G601" t="n">
-        <v>2.48526668548584</v>
+        <v>2.48526692390442</v>
       </c>
       <c r="H601" t="n">
         <v>7487</v>
@@ -17827,7 +17827,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G602" t="n">
-        <v>2.46812701225281</v>
+        <v>2.46812725067139</v>
       </c>
       <c r="H602" t="n">
         <v>7243</v>
@@ -17972,7 +17972,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G607" t="n">
-        <v>2.55382561683655</v>
+        <v>2.55382585525513</v>
       </c>
       <c r="H607" t="n">
         <v>22011</v>
@@ -18001,7 +18001,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G608" t="n">
-        <v>2.63447332382202</v>
+        <v>2.63447308540344</v>
       </c>
       <c r="H608" t="n">
         <v>30164</v>
@@ -18088,7 +18088,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G611" t="n">
-        <v>2.61655139923096</v>
+        <v>2.61655163764954</v>
       </c>
       <c r="H611" t="n">
         <v>13758</v>
@@ -18117,7 +18117,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G612" t="n">
-        <v>2.55382561683655</v>
+        <v>2.55382585525513</v>
       </c>
       <c r="H612" t="n">
         <v>19084</v>
@@ -18320,7 +18320,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G619" t="n">
-        <v>2.45525741577148</v>
+        <v>2.45525717735291</v>
       </c>
       <c r="H619" t="n">
         <v>4749</v>
@@ -18349,7 +18349,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G620" t="n">
-        <v>2.45525741577148</v>
+        <v>2.45525717735291</v>
       </c>
       <c r="H620" t="n">
         <v>4193</v>
@@ -18436,7 +18436,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G623" t="n">
-        <v>2.55382561683655</v>
+        <v>2.55382585525513</v>
       </c>
       <c r="H623" t="n">
         <v>4765</v>
@@ -18465,7 +18465,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G624" t="n">
-        <v>2.57174754142761</v>
+        <v>2.57174730300903</v>
       </c>
       <c r="H624" t="n">
         <v>2231</v>
@@ -18494,7 +18494,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G625" t="n">
-        <v>2.57174754142761</v>
+        <v>2.57174730300903</v>
       </c>
       <c r="H625" t="n">
         <v>3450</v>
@@ -18523,7 +18523,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G626" t="n">
-        <v>2.55382561683655</v>
+        <v>2.55382585525513</v>
       </c>
       <c r="H626" t="n">
         <v>2320</v>
@@ -18552,7 +18552,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G627" t="n">
-        <v>2.51798295974731</v>
+        <v>2.51798272132874</v>
       </c>
       <c r="H627" t="n">
         <v>191</v>
@@ -18639,7 +18639,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G630" t="n">
-        <v>2.51798295974731</v>
+        <v>2.51798272132874</v>
       </c>
       <c r="H630" t="n">
         <v>1232</v>
@@ -18668,7 +18668,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G631" t="n">
-        <v>2.53590416908264</v>
+        <v>2.53590440750122</v>
       </c>
       <c r="H631" t="n">
         <v>519</v>
@@ -18784,7 +18784,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G635" t="n">
-        <v>2.51798295974731</v>
+        <v>2.51798272132874</v>
       </c>
       <c r="H635" t="n">
         <v>19029</v>
@@ -18842,7 +18842,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G637" t="n">
-        <v>2.55382561683655</v>
+        <v>2.55382585525513</v>
       </c>
       <c r="H637" t="n">
         <v>198</v>
@@ -18871,7 +18871,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G638" t="n">
-        <v>2.55382561683655</v>
+        <v>2.55382585525513</v>
       </c>
       <c r="H638" t="n">
         <v>0</v>
@@ -18900,7 +18900,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G639" t="n">
-        <v>2.53590416908264</v>
+        <v>2.53590440750122</v>
       </c>
       <c r="H639" t="n">
         <v>2002</v>
@@ -18929,7 +18929,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G640" t="n">
-        <v>2.53590416908264</v>
+        <v>2.53590440750122</v>
       </c>
       <c r="H640" t="n">
         <v>1371</v>
@@ -18958,7 +18958,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G641" t="n">
-        <v>2.53590416908264</v>
+        <v>2.53590440750122</v>
       </c>
       <c r="H641" t="n">
         <v>230</v>
@@ -18987,7 +18987,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G642" t="n">
-        <v>2.53590416908264</v>
+        <v>2.53590440750122</v>
       </c>
       <c r="H642" t="n">
         <v>418</v>
@@ -19016,7 +19016,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G643" t="n">
-        <v>2.53590416908264</v>
+        <v>2.53590440750122</v>
       </c>
       <c r="H643" t="n">
         <v>0</v>
@@ -19074,7 +19074,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G645" t="n">
-        <v>2.53590416908264</v>
+        <v>2.53590440750122</v>
       </c>
       <c r="H645" t="n">
         <v>2500</v>
@@ -19103,7 +19103,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G646" t="n">
-        <v>2.47317862510681</v>
+        <v>2.47317886352539</v>
       </c>
       <c r="H646" t="n">
         <v>1829</v>
@@ -19132,7 +19132,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G647" t="n">
-        <v>2.51798295974731</v>
+        <v>2.51798272132874</v>
       </c>
       <c r="H647" t="n">
         <v>16631</v>
@@ -19161,7 +19161,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G648" t="n">
-        <v>2.51798295974731</v>
+        <v>2.51798272132874</v>
       </c>
       <c r="H648" t="n">
         <v>6390</v>
@@ -19190,7 +19190,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G649" t="n">
-        <v>2.51798295974731</v>
+        <v>2.51798272132874</v>
       </c>
       <c r="H649" t="n">
         <v>0</v>
@@ -19364,7 +19364,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G655" t="n">
-        <v>2.55382561683655</v>
+        <v>2.55382585525513</v>
       </c>
       <c r="H655" t="n">
         <v>1321</v>
@@ -19422,7 +19422,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G657" t="n">
-        <v>2.75992441177368</v>
+        <v>2.7599241733551</v>
       </c>
       <c r="H657" t="n">
         <v>25425</v>
@@ -19509,7 +19509,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G660" t="n">
-        <v>2.75992441177368</v>
+        <v>2.7599241733551</v>
       </c>
       <c r="H660" t="n">
         <v>11991</v>
@@ -19712,7 +19712,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G667" t="n">
-        <v>2.75096321105957</v>
+        <v>2.75096344947815</v>
       </c>
       <c r="H667" t="n">
         <v>2365</v>
@@ -19741,7 +19741,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G668" t="n">
-        <v>2.67031621932983</v>
+        <v>2.67031645774841</v>
       </c>
       <c r="H668" t="n">
         <v>16566</v>
@@ -19770,7 +19770,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G669" t="n">
-        <v>2.63447332382202</v>
+        <v>2.63447308540344</v>
       </c>
       <c r="H669" t="n">
         <v>764</v>
@@ -19828,7 +19828,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G671" t="n">
-        <v>2.75096321105957</v>
+        <v>2.75096344947815</v>
       </c>
       <c r="H671" t="n">
         <v>1370</v>
@@ -19915,7 +19915,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G674" t="n">
-        <v>2.65239477157593</v>
+        <v>2.65239453315735</v>
       </c>
       <c r="H674" t="n">
         <v>1869</v>
@@ -19944,7 +19944,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G675" t="n">
-        <v>2.65239477157593</v>
+        <v>2.65239453315735</v>
       </c>
       <c r="H675" t="n">
         <v>0</v>
@@ -20002,7 +20002,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G677" t="n">
-        <v>2.67031621932983</v>
+        <v>2.67031645774841</v>
       </c>
       <c r="H677" t="n">
         <v>1645</v>
@@ -20031,7 +20031,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G678" t="n">
-        <v>2.67031621932983</v>
+        <v>2.67031645774841</v>
       </c>
       <c r="H678" t="n">
         <v>0</v>
@@ -20089,7 +20089,7 @@
         <v>3</v>
       </c>
       <c r="G680" t="n">
-        <v>2.68823766708374</v>
+        <v>2.68823790550232</v>
       </c>
       <c r="H680" t="n">
         <v>1900</v>
@@ -20147,7 +20147,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G682" t="n">
-        <v>2.75096321105957</v>
+        <v>2.75096344947815</v>
       </c>
       <c r="H682" t="n">
         <v>10777</v>
@@ -20176,7 +20176,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G683" t="n">
-        <v>2.73304176330566</v>
+        <v>2.73304200172424</v>
       </c>
       <c r="H683" t="n">
         <v>1575</v>
@@ -20205,7 +20205,7 @@
         <v>3</v>
       </c>
       <c r="G684" t="n">
-        <v>2.68823766708374</v>
+        <v>2.68823790550232</v>
       </c>
       <c r="H684" t="n">
         <v>795</v>
@@ -20234,7 +20234,7 @@
         <v>3</v>
       </c>
       <c r="G685" t="n">
-        <v>2.68823766708374</v>
+        <v>2.68823790550232</v>
       </c>
       <c r="H685" t="n">
         <v>9614</v>
@@ -20263,7 +20263,7 @@
         <v>3</v>
       </c>
       <c r="G686" t="n">
-        <v>2.68823766708374</v>
+        <v>2.68823790550232</v>
       </c>
       <c r="H686" t="n">
         <v>669</v>
@@ -20321,7 +20321,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G688" t="n">
-        <v>2.75096321105957</v>
+        <v>2.75096344947815</v>
       </c>
       <c r="H688" t="n">
         <v>5155</v>
@@ -20379,7 +20379,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G690" t="n">
-        <v>2.69719886779785</v>
+        <v>2.69719862937927</v>
       </c>
       <c r="H690" t="n">
         <v>5352</v>
@@ -20408,7 +20408,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G691" t="n">
-        <v>2.67927694320679</v>
+        <v>2.67927718162537</v>
       </c>
       <c r="H691" t="n">
         <v>996</v>
@@ -20437,7 +20437,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G692" t="n">
-        <v>2.75992441177368</v>
+        <v>2.7599241733551</v>
       </c>
       <c r="H692" t="n">
         <v>1966</v>
@@ -20495,7 +20495,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G694" t="n">
-        <v>2.86745357513428</v>
+        <v>2.86745381355286</v>
       </c>
       <c r="H694" t="n">
         <v>9450</v>
@@ -20553,7 +20553,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G696" t="n">
-        <v>2.73304176330566</v>
+        <v>2.73304200172424</v>
       </c>
       <c r="H696" t="n">
         <v>20211</v>
@@ -20582,7 +20582,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G697" t="n">
-        <v>2.75096321105957</v>
+        <v>2.75096344947815</v>
       </c>
       <c r="H697" t="n">
         <v>927</v>
@@ -20640,7 +20640,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G699" t="n">
-        <v>2.75992441177368</v>
+        <v>2.7599241733551</v>
       </c>
       <c r="H699" t="n">
         <v>7749</v>
@@ -20669,7 +20669,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G700" t="n">
-        <v>2.75096321105957</v>
+        <v>2.75096344947815</v>
       </c>
       <c r="H700" t="n">
         <v>3068</v>
@@ -20698,7 +20698,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G701" t="n">
-        <v>2.75096321105957</v>
+        <v>2.75096344947815</v>
       </c>
       <c r="H701" t="n">
         <v>1928</v>
@@ -20727,7 +20727,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G702" t="n">
-        <v>2.75096321105957</v>
+        <v>2.75096344947815</v>
       </c>
       <c r="H702" t="n">
         <v>0</v>
@@ -20785,7 +20785,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G704" t="n">
-        <v>2.65239477157593</v>
+        <v>2.65239453315735</v>
       </c>
       <c r="H704" t="n">
         <v>4663</v>
@@ -20814,7 +20814,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G705" t="n">
-        <v>2.69719886779785</v>
+        <v>2.69719862937927</v>
       </c>
       <c r="H705" t="n">
         <v>193</v>
@@ -20843,7 +20843,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G706" t="n">
-        <v>2.67927694320679</v>
+        <v>2.67927718162537</v>
       </c>
       <c r="H706" t="n">
         <v>6101</v>
@@ -20872,7 +20872,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G707" t="n">
-        <v>2.6434338092804</v>
+        <v>2.64343404769897</v>
       </c>
       <c r="H707" t="n">
         <v>9896</v>
@@ -20901,7 +20901,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G708" t="n">
-        <v>2.63447332382202</v>
+        <v>2.63447308540344</v>
       </c>
       <c r="H708" t="n">
         <v>4328</v>
@@ -21017,7 +21017,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G712" t="n">
-        <v>2.55382561683655</v>
+        <v>2.55382585525513</v>
       </c>
       <c r="H712" t="n">
         <v>13458</v>
@@ -21046,7 +21046,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G713" t="n">
-        <v>2.61655139923096</v>
+        <v>2.61655163764954</v>
       </c>
       <c r="H713" t="n">
         <v>1</v>
@@ -21191,7 +21191,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G718" t="n">
-        <v>2.57174754142761</v>
+        <v>2.57174730300903</v>
       </c>
       <c r="H718" t="n">
         <v>1700</v>
@@ -21249,7 +21249,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G720" t="n">
-        <v>2.61655139923096</v>
+        <v>2.61655163764954</v>
       </c>
       <c r="H720" t="n">
         <v>1330</v>
@@ -21278,7 +21278,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G721" t="n">
-        <v>2.61655139923096</v>
+        <v>2.61655163764954</v>
       </c>
       <c r="H721" t="n">
         <v>2</v>
@@ -21452,7 +21452,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G727" t="n">
-        <v>2.61655139923096</v>
+        <v>2.61655163764954</v>
       </c>
       <c r="H727" t="n">
         <v>3600</v>
@@ -21481,7 +21481,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G728" t="n">
-        <v>2.61655139923096</v>
+        <v>2.61655163764954</v>
       </c>
       <c r="H728" t="n">
         <v>343</v>
@@ -21510,7 +21510,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G729" t="n">
-        <v>2.61655139923096</v>
+        <v>2.61655163764954</v>
       </c>
       <c r="H729" t="n">
         <v>0</v>
@@ -21568,7 +21568,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G731" t="n">
-        <v>2.61655139923096</v>
+        <v>2.61655163764954</v>
       </c>
       <c r="H731" t="n">
         <v>3102</v>
@@ -21684,7 +21684,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G735" t="n">
-        <v>2.45525741577148</v>
+        <v>2.45525717735291</v>
       </c>
       <c r="H735" t="n">
         <v>2301</v>
@@ -21771,7 +21771,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G738" t="n">
-        <v>2.57174754142761</v>
+        <v>2.57174730300903</v>
       </c>
       <c r="H738" t="n">
         <v>2354</v>
@@ -21800,7 +21800,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G739" t="n">
-        <v>2.45525741577148</v>
+        <v>2.45525717735291</v>
       </c>
       <c r="H739" t="n">
         <v>1210</v>
@@ -22003,7 +22003,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G746" t="n">
-        <v>2.41941404342651</v>
+        <v>2.41941428184509</v>
       </c>
       <c r="H746" t="n">
         <v>10198</v>
@@ -22061,7 +22061,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G748" t="n">
-        <v>2.57174754142761</v>
+        <v>2.57174730300903</v>
       </c>
       <c r="H748" t="n">
         <v>2700</v>
@@ -22119,7 +22119,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G750" t="n">
-        <v>2.57174754142761</v>
+        <v>2.57174730300903</v>
       </c>
       <c r="H750" t="n">
         <v>1555</v>
@@ -22148,7 +22148,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G751" t="n">
-        <v>2.57174754142761</v>
+        <v>2.57174730300903</v>
       </c>
       <c r="H751" t="n">
         <v>0</v>
@@ -22177,7 +22177,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G752" t="n">
-        <v>2.57174754142761</v>
+        <v>2.57174730300903</v>
       </c>
       <c r="H752" t="n">
         <v>0</v>
@@ -22235,7 +22235,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G754" t="n">
-        <v>2.55382561683655</v>
+        <v>2.55382585525513</v>
       </c>
       <c r="H754" t="n">
         <v>1</v>
@@ -22264,7 +22264,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G755" t="n">
-        <v>2.55382561683655</v>
+        <v>2.55382585525513</v>
       </c>
       <c r="H755" t="n">
         <v>0</v>
@@ -22293,7 +22293,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G756" t="n">
-        <v>2.53590416908264</v>
+        <v>2.53590440750122</v>
       </c>
       <c r="H756" t="n">
         <v>50</v>
@@ -22322,7 +22322,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G757" t="n">
-        <v>2.53590416908264</v>
+        <v>2.53590440750122</v>
       </c>
       <c r="H757" t="n">
         <v>0</v>
@@ -22351,7 +22351,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G758" t="n">
-        <v>2.53590416908264</v>
+        <v>2.53590440750122</v>
       </c>
       <c r="H758" t="n">
         <v>0</v>
@@ -22496,7 +22496,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G763" t="n">
-        <v>2.53590416908264</v>
+        <v>2.53590440750122</v>
       </c>
       <c r="H763" t="n">
         <v>1110</v>
@@ -22525,7 +22525,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G764" t="n">
-        <v>2.53590416908264</v>
+        <v>2.53590440750122</v>
       </c>
       <c r="H764" t="n">
         <v>2491</v>
@@ -22583,7 +22583,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G766" t="n">
-        <v>2.63447332382202</v>
+        <v>2.63447308540344</v>
       </c>
       <c r="H766" t="n">
         <v>1525</v>
@@ -22612,7 +22612,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G767" t="n">
-        <v>2.67031621932983</v>
+        <v>2.67031645774841</v>
       </c>
       <c r="H767" t="n">
         <v>1992</v>
@@ -22670,7 +22670,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G769" t="n">
-        <v>2.67031621932983</v>
+        <v>2.67031645774841</v>
       </c>
       <c r="H769" t="n">
         <v>2001</v>
@@ -22699,7 +22699,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G770" t="n">
-        <v>2.69719886779785</v>
+        <v>2.69719862937927</v>
       </c>
       <c r="H770" t="n">
         <v>753</v>
@@ -22728,7 +22728,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G771" t="n">
-        <v>2.67927694320679</v>
+        <v>2.67927718162537</v>
       </c>
       <c r="H771" t="n">
         <v>2755</v>
@@ -22757,7 +22757,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G772" t="n">
-        <v>2.67031621932983</v>
+        <v>2.67031645774841</v>
       </c>
       <c r="H772" t="n">
         <v>1014</v>
@@ -22815,7 +22815,7 @@
         <v>3</v>
       </c>
       <c r="G774" t="n">
-        <v>2.68823766708374</v>
+        <v>2.68823790550232</v>
       </c>
       <c r="H774" t="n">
         <v>22062</v>
@@ -22844,7 +22844,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G775" t="n">
-        <v>2.69719886779785</v>
+        <v>2.69719862937927</v>
       </c>
       <c r="H775" t="n">
         <v>12499</v>
@@ -22873,7 +22873,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G776" t="n">
-        <v>2.67927694320679</v>
+        <v>2.67927718162537</v>
       </c>
       <c r="H776" t="n">
         <v>5677</v>
@@ -22902,7 +22902,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G777" t="n">
-        <v>2.75096321105957</v>
+        <v>2.75096344947815</v>
       </c>
       <c r="H777" t="n">
         <v>1940</v>
@@ -22931,7 +22931,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G778" t="n">
-        <v>2.81368899345398</v>
+        <v>2.81368923187256</v>
       </c>
       <c r="H778" t="n">
         <v>12625</v>
@@ -22989,7 +22989,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G780" t="n">
-        <v>2.93914008140564</v>
+        <v>2.93914031982422</v>
       </c>
       <c r="H780" t="n">
         <v>37762</v>
@@ -23018,7 +23018,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G781" t="n">
-        <v>2.87641453742981</v>
+        <v>2.87641477584839</v>
       </c>
       <c r="H781" t="n">
         <v>16941</v>
@@ -23076,7 +23076,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G783" t="n">
-        <v>2.82264971733093</v>
+        <v>2.82264995574951</v>
       </c>
       <c r="H783" t="n">
         <v>3132</v>
@@ -23163,7 +23163,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G786" t="n">
-        <v>2.82264971733093</v>
+        <v>2.82264995574951</v>
       </c>
       <c r="H786" t="n">
         <v>757</v>
@@ -23395,7 +23395,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G794" t="n">
-        <v>2.87641453742981</v>
+        <v>2.87641477584839</v>
       </c>
       <c r="H794" t="n">
         <v>5745</v>
@@ -23424,7 +23424,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G795" t="n">
-        <v>2.87641453742981</v>
+        <v>2.87641477584839</v>
       </c>
       <c r="H795" t="n">
         <v>10690</v>
@@ -23482,7 +23482,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G797" t="n">
-        <v>3.12731647491455</v>
+        <v>3.12731671333313</v>
       </c>
       <c r="H797" t="n">
         <v>113615</v>
@@ -23569,7 +23569,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G800" t="n">
-        <v>3.19004201889038</v>
+        <v>3.19004225730896</v>
       </c>
       <c r="H800" t="n">
         <v>12016</v>
@@ -23598,7 +23598,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G801" t="n">
-        <v>3.25276780128479</v>
+        <v>3.25276803970337</v>
       </c>
       <c r="H801" t="n">
         <v>35656</v>
@@ -23656,7 +23656,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G803" t="n">
-        <v>3.25276780128479</v>
+        <v>3.25276803970337</v>
       </c>
       <c r="H803" t="n">
         <v>24537</v>
@@ -23685,7 +23685,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G804" t="n">
-        <v>3.19004201889038</v>
+        <v>3.19004225730896</v>
       </c>
       <c r="H804" t="n">
         <v>11994</v>
@@ -23714,7 +23714,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G805" t="n">
-        <v>3.28861117362976</v>
+        <v>3.28861093521118</v>
       </c>
       <c r="H805" t="n">
         <v>11063</v>
@@ -23743,7 +23743,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G806" t="n">
-        <v>3.29757189750671</v>
+        <v>3.29757165908813</v>
       </c>
       <c r="H806" t="n">
         <v>24295</v>
@@ -23917,7 +23917,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G812" t="n">
-        <v>3.34237575531006</v>
+        <v>3.34237551689148</v>
       </c>
       <c r="H812" t="n">
         <v>14717</v>
@@ -23946,7 +23946,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G813" t="n">
-        <v>3.42302298545837</v>
+        <v>3.42302274703979</v>
       </c>
       <c r="H813" t="n">
         <v>37852</v>
@@ -24004,7 +24004,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G815" t="n">
-        <v>3.40510129928589</v>
+        <v>3.40510106086731</v>
       </c>
       <c r="H815" t="n">
         <v>25970</v>
@@ -24062,7 +24062,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G817" t="n">
-        <v>3.36925792694092</v>
+        <v>3.3692581653595</v>
       </c>
       <c r="H817" t="n">
         <v>26326</v>
@@ -24120,7 +24120,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G819" t="n">
-        <v>3.40510129928589</v>
+        <v>3.40510106086731</v>
       </c>
       <c r="H819" t="n">
         <v>2828</v>
@@ -24178,7 +24178,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G821" t="n">
-        <v>3.45886564254761</v>
+        <v>3.45886588096619</v>
       </c>
       <c r="H821" t="n">
         <v>39609</v>
@@ -24207,7 +24207,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G822" t="n">
-        <v>3.48574876785278</v>
+        <v>3.48574829101562</v>
       </c>
       <c r="H822" t="n">
         <v>8734</v>
@@ -24323,7 +24323,7 @@
         <v>4</v>
       </c>
       <c r="G826" t="n">
-        <v>3.58431696891785</v>
+        <v>3.58431720733643</v>
       </c>
       <c r="H826" t="n">
         <v>34994</v>
@@ -24410,7 +24410,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G829" t="n">
-        <v>3.59327793121338</v>
+        <v>3.59327816963196</v>
       </c>
       <c r="H829" t="n">
         <v>26135</v>
@@ -24468,7 +24468,7 @@
         <v>4</v>
       </c>
       <c r="G831" t="n">
-        <v>3.58431696891785</v>
+        <v>3.58431720733643</v>
       </c>
       <c r="H831" t="n">
         <v>6782</v>
@@ -24497,7 +24497,7 @@
         <v>4</v>
       </c>
       <c r="G832" t="n">
-        <v>3.58431696891785</v>
+        <v>3.58431720733643</v>
       </c>
       <c r="H832" t="n">
         <v>21082</v>
@@ -24526,7 +24526,7 @@
         <v>3.9300000667572</v>
       </c>
       <c r="G833" t="n">
-        <v>3.52159142494202</v>
+        <v>3.5215916633606</v>
       </c>
       <c r="H833" t="n">
         <v>15187</v>
@@ -24555,7 +24555,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G834" t="n">
-        <v>3.51263093948364</v>
+        <v>3.51263070106506</v>
       </c>
       <c r="H834" t="n">
         <v>17785</v>
@@ -24584,7 +24584,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G835" t="n">
-        <v>3.51263093948364</v>
+        <v>3.51263070106506</v>
       </c>
       <c r="H835" t="n">
         <v>9370</v>
@@ -24642,7 +24642,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G837" t="n">
-        <v>3.51263093948364</v>
+        <v>3.51263070106506</v>
       </c>
       <c r="H837" t="n">
         <v>3704</v>
@@ -24700,7 +24700,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G839" t="n">
-        <v>3.45886564254761</v>
+        <v>3.45886588096619</v>
       </c>
       <c r="H839" t="n">
         <v>1361</v>
@@ -24729,7 +24729,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G840" t="n">
-        <v>3.51263093948364</v>
+        <v>3.51263070106506</v>
       </c>
       <c r="H840" t="n">
         <v>9839</v>
@@ -24758,7 +24758,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G841" t="n">
-        <v>3.60223889350891</v>
+        <v>3.60223865509033</v>
       </c>
       <c r="H841" t="n">
         <v>17694</v>
@@ -24787,7 +24787,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G842" t="n">
-        <v>3.65600323677063</v>
+        <v>3.65600347518921</v>
       </c>
       <c r="H842" t="n">
         <v>57918</v>
@@ -24816,7 +24816,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G843" t="n">
-        <v>3.65600323677063</v>
+        <v>3.65600347518921</v>
       </c>
       <c r="H843" t="n">
         <v>7977</v>
@@ -24874,7 +24874,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G845" t="n">
-        <v>3.72768998146057</v>
+        <v>3.72768974304199</v>
       </c>
       <c r="H845" t="n">
         <v>6921</v>
@@ -24903,7 +24903,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G846" t="n">
-        <v>3.71872925758362</v>
+        <v>3.71872901916504</v>
       </c>
       <c r="H846" t="n">
         <v>10814</v>
@@ -24932,7 +24932,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G847" t="n">
-        <v>3.6918466091156</v>
+        <v>3.69184637069702</v>
       </c>
       <c r="H847" t="n">
         <v>15171</v>
@@ -24961,7 +24961,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G848" t="n">
-        <v>3.70976781845093</v>
+        <v>3.70976829528809</v>
       </c>
       <c r="H848" t="n">
         <v>16414</v>
@@ -24990,7 +24990,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G849" t="n">
-        <v>3.68288588523865</v>
+        <v>3.68288612365723</v>
       </c>
       <c r="H849" t="n">
         <v>10497</v>
@@ -25048,7 +25048,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G851" t="n">
-        <v>3.70976781845093</v>
+        <v>3.70976829528809</v>
       </c>
       <c r="H851" t="n">
         <v>3613</v>
@@ -25077,7 +25077,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G852" t="n">
-        <v>3.76353287696838</v>
+        <v>3.7635326385498</v>
       </c>
       <c r="H852" t="n">
         <v>27687</v>
@@ -25164,7 +25164,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G855" t="n">
-        <v>3.79041504859924</v>
+        <v>3.7904155254364</v>
       </c>
       <c r="H855" t="n">
         <v>50118</v>
@@ -25309,7 +25309,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G860" t="n">
-        <v>4.00759792327881</v>
+        <v>4.00759744644165</v>
       </c>
       <c r="H860" t="n">
         <v>14479</v>
@@ -25367,7 +25367,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G862" t="n">
-        <v>3.81988835334778</v>
+        <v>3.81988859176636</v>
       </c>
       <c r="H862" t="n">
         <v>85637</v>
@@ -25860,7 +25860,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G879" t="n">
-        <v>3.99821257591248</v>
+        <v>3.9982123374939</v>
       </c>
       <c r="H879" t="n">
         <v>2396</v>
@@ -25889,7 +25889,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G880" t="n">
-        <v>3.99821257591248</v>
+        <v>3.9982123374939</v>
       </c>
       <c r="H880" t="n">
         <v>4689</v>
@@ -25918,7 +25918,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G881" t="n">
-        <v>3.99821257591248</v>
+        <v>3.9982123374939</v>
       </c>
       <c r="H881" t="n">
         <v>930</v>
@@ -25947,7 +25947,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G882" t="n">
-        <v>3.99821257591248</v>
+        <v>3.9982123374939</v>
       </c>
       <c r="H882" t="n">
         <v>6492</v>
@@ -25976,7 +25976,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G883" t="n">
-        <v>3.97944092750549</v>
+        <v>3.97944116592407</v>
       </c>
       <c r="H883" t="n">
         <v>118</v>
@@ -26005,7 +26005,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G884" t="n">
-        <v>3.85743021965027</v>
+        <v>3.85743045806885</v>
       </c>
       <c r="H884" t="n">
         <v>10925</v>
@@ -26063,7 +26063,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G886" t="n">
-        <v>3.85743021965027</v>
+        <v>3.85743045806885</v>
       </c>
       <c r="H886" t="n">
         <v>14918</v>
@@ -26092,7 +26092,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G887" t="n">
-        <v>3.81050252914429</v>
+        <v>3.81050276756287</v>
       </c>
       <c r="H887" t="n">
         <v>11271</v>
@@ -26121,7 +26121,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G888" t="n">
-        <v>3.7448046207428</v>
+        <v>3.74480438232422</v>
       </c>
       <c r="H888" t="n">
         <v>7435</v>
@@ -26150,7 +26150,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G889" t="n">
-        <v>3.89497232437134</v>
+        <v>3.89497208595276</v>
       </c>
       <c r="H889" t="n">
         <v>31861</v>
@@ -26179,7 +26179,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G890" t="n">
-        <v>3.94189953804016</v>
+        <v>3.941899061203</v>
       </c>
       <c r="H890" t="n">
         <v>18047</v>
@@ -26208,7 +26208,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G891" t="n">
-        <v>3.99821257591248</v>
+        <v>3.9982123374939</v>
       </c>
       <c r="H891" t="n">
         <v>23527</v>
@@ -26237,7 +26237,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G892" t="n">
-        <v>4.00759792327881</v>
+        <v>4.00759744644165</v>
       </c>
       <c r="H892" t="n">
         <v>7461</v>
@@ -26353,7 +26353,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G896" t="n">
-        <v>3.93251395225525</v>
+        <v>3.93251419067383</v>
       </c>
       <c r="H896" t="n">
         <v>5116</v>
@@ -26382,7 +26382,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G897" t="n">
-        <v>3.93251395225525</v>
+        <v>3.93251419067383</v>
       </c>
       <c r="H897" t="n">
         <v>8757</v>
@@ -26498,7 +26498,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G901" t="n">
-        <v>4.11083793640137</v>
+        <v>4.11083841323853</v>
       </c>
       <c r="H901" t="n">
         <v>2430</v>
@@ -26527,7 +26527,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G902" t="n">
-        <v>4.11083793640137</v>
+        <v>4.11083841323853</v>
       </c>
       <c r="H902" t="n">
         <v>5958</v>
@@ -26730,7 +26730,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G909" t="n">
-        <v>4.19530725479126</v>
+        <v>4.1953067779541</v>
       </c>
       <c r="H909" t="n">
         <v>26343</v>
@@ -26846,7 +26846,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G913" t="n">
-        <v>4.26100587844849</v>
+        <v>4.26100540161133</v>
       </c>
       <c r="H913" t="n">
         <v>12580</v>
@@ -26904,7 +26904,7 @@
         <v>4.63000011444092</v>
       </c>
       <c r="G915" t="n">
-        <v>4.34547472000122</v>
+        <v>4.34547519683838</v>
       </c>
       <c r="H915" t="n">
         <v>15972</v>
@@ -27020,7 +27020,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G919" t="n">
-        <v>4.26100587844849</v>
+        <v>4.26100540161133</v>
       </c>
       <c r="H919" t="n">
         <v>3999</v>
@@ -27194,7 +27194,7 @@
         <v>4.78999996185303</v>
       </c>
       <c r="G925" t="n">
-        <v>4.49564266204834</v>
+        <v>4.49564218521118</v>
       </c>
       <c r="H925" t="n">
         <v>32339</v>
@@ -27310,7 +27310,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G929" t="n">
-        <v>4.54257011413574</v>
+        <v>4.54256963729858</v>
       </c>
       <c r="H929" t="n">
         <v>3268</v>
@@ -27397,7 +27397,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G932" t="n">
-        <v>4.44871520996094</v>
+        <v>4.44871473312378</v>
       </c>
       <c r="H932" t="n">
         <v>2596</v>
@@ -27513,7 +27513,7 @@
         <v>4.78999996185303</v>
       </c>
       <c r="G936" t="n">
-        <v>4.49564266204834</v>
+        <v>4.49564218521118</v>
       </c>
       <c r="H936" t="n">
         <v>11834</v>
@@ -27571,7 +27571,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G938" t="n">
-        <v>4.44871520996094</v>
+        <v>4.44871473312378</v>
       </c>
       <c r="H938" t="n">
         <v>11168</v>
@@ -27600,7 +27600,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G939" t="n">
-        <v>4.44871520996094</v>
+        <v>4.44871473312378</v>
       </c>
       <c r="H939" t="n">
         <v>11433</v>
@@ -27774,7 +27774,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G945" t="n">
-        <v>4.39240169525146</v>
+        <v>4.39240217208862</v>
       </c>
       <c r="H945" t="n">
         <v>13922</v>
@@ -27803,7 +27803,7 @@
         <v>4.63000011444092</v>
       </c>
       <c r="G946" t="n">
-        <v>4.34547472000122</v>
+        <v>4.34547519683838</v>
       </c>
       <c r="H946" t="n">
         <v>810</v>
@@ -27861,7 +27861,7 @@
         <v>4.63000011444092</v>
       </c>
       <c r="G948" t="n">
-        <v>4.34547472000122</v>
+        <v>4.34547519683838</v>
       </c>
       <c r="H948" t="n">
         <v>641</v>
@@ -27890,7 +27890,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G949" t="n">
-        <v>4.39240169525146</v>
+        <v>4.39240217208862</v>
       </c>
       <c r="H949" t="n">
         <v>27724</v>
@@ -27977,7 +27977,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G952" t="n">
-        <v>4.24223470687866</v>
+        <v>4.2422342300415</v>
       </c>
       <c r="H952" t="n">
         <v>7693</v>
@@ -28006,7 +28006,7 @@
         <v>4.59000015258789</v>
       </c>
       <c r="G953" t="n">
-        <v>4.30793333053589</v>
+        <v>4.30793285369873</v>
       </c>
       <c r="H953" t="n">
         <v>13450</v>
@@ -28354,7 +28354,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G965" t="n">
-        <v>4.61765336990356</v>
+        <v>4.61765384674072</v>
       </c>
       <c r="H965" t="n">
         <v>10122</v>
@@ -28412,7 +28412,7 @@
         <v>4.86999988555908</v>
       </c>
       <c r="G967" t="n">
-        <v>4.57072591781616</v>
+        <v>4.57072639465332</v>
       </c>
       <c r="H967" t="n">
         <v>14636</v>
@@ -28470,7 +28470,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G969" t="n">
-        <v>4.80536270141602</v>
+        <v>4.80536317825317</v>
       </c>
       <c r="H969" t="n">
         <v>76657</v>
@@ -28528,7 +28528,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G971" t="n">
-        <v>4.86167621612549</v>
+        <v>4.86167573928833</v>
       </c>
       <c r="H971" t="n">
         <v>41217</v>
@@ -28557,7 +28557,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G972" t="n">
-        <v>4.84290504455566</v>
+        <v>4.84290456771851</v>
       </c>
       <c r="H972" t="n">
         <v>39106</v>
@@ -28615,7 +28615,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G974" t="n">
-        <v>4.86167621612549</v>
+        <v>4.86167573928833</v>
       </c>
       <c r="H974" t="n">
         <v>28236</v>
@@ -28644,7 +28644,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G975" t="n">
-        <v>4.86167621612549</v>
+        <v>4.86167573928833</v>
       </c>
       <c r="H975" t="n">
         <v>22913</v>
@@ -28673,7 +28673,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G976" t="n">
-        <v>4.80536270141602</v>
+        <v>4.80536317825317</v>
       </c>
       <c r="H976" t="n">
         <v>3201</v>
@@ -28760,7 +28760,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G979" t="n">
-        <v>4.84290504455566</v>
+        <v>4.84290456771851</v>
       </c>
       <c r="H979" t="n">
         <v>19735</v>
@@ -28847,7 +28847,7 @@
         <v>4.82999992370605</v>
       </c>
       <c r="G982" t="n">
-        <v>4.53318405151367</v>
+        <v>4.53318452835083</v>
       </c>
       <c r="H982" t="n">
         <v>36516</v>
@@ -28876,7 +28876,7 @@
         <v>4.78999996185303</v>
       </c>
       <c r="G983" t="n">
-        <v>4.49564266204834</v>
+        <v>4.49564218521118</v>
       </c>
       <c r="H983" t="n">
         <v>7469</v>
@@ -28905,7 +28905,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G984" t="n">
-        <v>4.58011150360107</v>
+        <v>4.58011198043823</v>
       </c>
       <c r="H984" t="n">
         <v>27741</v>
@@ -28992,7 +28992,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G987" t="n">
-        <v>4.73027944564819</v>
+        <v>4.73027896881104</v>
       </c>
       <c r="H987" t="n">
         <v>2459</v>
@@ -29050,7 +29050,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G989" t="n">
-        <v>4.71150827407837</v>
+        <v>4.71150875091553</v>
       </c>
       <c r="H989" t="n">
         <v>7841</v>
@@ -29195,7 +29195,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G994" t="n">
-        <v>4.84290504455566</v>
+        <v>4.84290456771851</v>
       </c>
       <c r="H994" t="n">
         <v>5142</v>
@@ -29340,7 +29340,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G999" t="n">
-        <v>4.73027944564819</v>
+        <v>4.73027896881104</v>
       </c>
       <c r="H999" t="n">
         <v>20631</v>
@@ -29398,7 +29398,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G1001" t="n">
-        <v>4.71150827407837</v>
+        <v>4.71150875091553</v>
       </c>
       <c r="H1001" t="n">
         <v>3676</v>
@@ -29427,7 +29427,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G1002" t="n">
-        <v>4.73027944564819</v>
+        <v>4.73027896881104</v>
       </c>
       <c r="H1002" t="n">
         <v>1299</v>
@@ -29456,7 +29456,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G1003" t="n">
-        <v>4.80536270141602</v>
+        <v>4.80536317825317</v>
       </c>
       <c r="H1003" t="n">
         <v>6210</v>
@@ -29485,7 +29485,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G1004" t="n">
-        <v>4.95553112030029</v>
+        <v>4.95553064346313</v>
       </c>
       <c r="H1004" t="n">
         <v>22236</v>
@@ -29543,7 +29543,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G1006" t="n">
-        <v>4.95553112030029</v>
+        <v>4.95553064346313</v>
       </c>
       <c r="H1006" t="n">
         <v>17242</v>
@@ -29659,7 +29659,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G1010" t="n">
-        <v>4.99307250976562</v>
+        <v>4.99307298660278</v>
       </c>
       <c r="H1010" t="n">
         <v>4517</v>
@@ -29688,7 +29688,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G1011" t="n">
-        <v>4.95553112030029</v>
+        <v>4.95553064346313</v>
       </c>
       <c r="H1011" t="n">
         <v>12051</v>
@@ -29717,7 +29717,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G1012" t="n">
-        <v>4.99307250976562</v>
+        <v>4.99307298660278</v>
       </c>
       <c r="H1012" t="n">
         <v>13162</v>
@@ -29804,7 +29804,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G1015" t="n">
-        <v>4.84290504455566</v>
+        <v>4.84290456771851</v>
       </c>
       <c r="H1015" t="n">
         <v>4359</v>
@@ -29862,7 +29862,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G1017" t="n">
-        <v>4.86167621612549</v>
+        <v>4.86167573928833</v>
       </c>
       <c r="H1017" t="n">
         <v>8973</v>
@@ -29891,7 +29891,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G1018" t="n">
-        <v>4.80536270141602</v>
+        <v>4.80536317825317</v>
       </c>
       <c r="H1018" t="n">
         <v>5043</v>
@@ -30007,7 +30007,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G1022" t="n">
-        <v>4.84290504455566</v>
+        <v>4.84290456771851</v>
       </c>
       <c r="H1022" t="n">
         <v>4235</v>
@@ -30036,7 +30036,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G1023" t="n">
-        <v>4.86167621612549</v>
+        <v>4.86167573928833</v>
       </c>
       <c r="H1023" t="n">
         <v>1208</v>
@@ -30065,7 +30065,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G1024" t="n">
-        <v>4.84290504455566</v>
+        <v>4.84290456771851</v>
       </c>
       <c r="H1024" t="n">
         <v>1337</v>
@@ -30094,7 +30094,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G1025" t="n">
-        <v>4.84290504455566</v>
+        <v>4.84290456771851</v>
       </c>
       <c r="H1025" t="n">
         <v>4590</v>
@@ -30123,7 +30123,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G1026" t="n">
-        <v>4.84290504455566</v>
+        <v>4.84290456771851</v>
       </c>
       <c r="H1026" t="n">
         <v>2573</v>
@@ -30152,7 +30152,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G1027" t="n">
-        <v>4.99307250976562</v>
+        <v>4.99307298660278</v>
       </c>
       <c r="H1027" t="n">
         <v>34186</v>
@@ -30268,7 +30268,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G1031" t="n">
-        <v>6.28826808929443</v>
+        <v>6.28826761245728</v>
       </c>
       <c r="H1031" t="n">
         <v>103442</v>
@@ -30413,7 +30413,7 @@
         <v>6.07999992370605</v>
       </c>
       <c r="G1036" t="n">
-        <v>5.70636892318726</v>
+        <v>5.7063684463501</v>
       </c>
       <c r="H1036" t="n">
         <v>30034</v>
@@ -30616,7 +30616,7 @@
         <v>6.03999996185303</v>
       </c>
       <c r="G1043" t="n">
-        <v>5.66882658004761</v>
+        <v>5.66882705688477</v>
       </c>
       <c r="H1043" t="n">
         <v>49809</v>
@@ -30645,7 +30645,7 @@
         <v>6.05999994277954</v>
       </c>
       <c r="G1044" t="n">
-        <v>5.68759727478027</v>
+        <v>5.68759775161743</v>
       </c>
       <c r="H1044" t="n">
         <v>21058</v>
@@ -30732,7 +30732,7 @@
         <v>6.07999992370605</v>
       </c>
       <c r="G1047" t="n">
-        <v>5.70636892318726</v>
+        <v>5.7063684463501</v>
       </c>
       <c r="H1047" t="n">
         <v>8347</v>
@@ -30761,7 +30761,7 @@
         <v>5.96000003814697</v>
       </c>
       <c r="G1048" t="n">
-        <v>5.59374284744263</v>
+        <v>5.59374332427979</v>
       </c>
       <c r="H1048" t="n">
         <v>22781</v>
@@ -30906,7 +30906,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G1053" t="n">
-        <v>4.71150827407837</v>
+        <v>4.71150875091553</v>
       </c>
       <c r="H1053" t="n">
         <v>57902</v>
@@ -30935,7 +30935,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G1054" t="n">
-        <v>4.86167621612549</v>
+        <v>4.86167573928833</v>
       </c>
       <c r="H1054" t="n">
         <v>38882</v>
@@ -31022,7 +31022,7 @@
         <v>4.98999977111816</v>
       </c>
       <c r="G1057" t="n">
-        <v>4.68335199356079</v>
+        <v>4.68335151672363</v>
       </c>
       <c r="H1057" t="n">
         <v>36128</v>
@@ -31080,7 +31080,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G1059" t="n">
-        <v>4.73027944564819</v>
+        <v>4.73027896881104</v>
       </c>
       <c r="H1059" t="n">
         <v>7986</v>
@@ -31109,7 +31109,7 @@
         <v>4.78999996185303</v>
       </c>
       <c r="G1060" t="n">
-        <v>4.49564266204834</v>
+        <v>4.49564218521118</v>
       </c>
       <c r="H1060" t="n">
         <v>13924</v>
@@ -31167,7 +31167,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G1062" t="n">
-        <v>3.85743021965027</v>
+        <v>3.85743045806885</v>
       </c>
       <c r="H1062" t="n">
         <v>44030</v>
@@ -31225,7 +31225,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G1064" t="n">
-        <v>3.94189953804016</v>
+        <v>3.941899061203</v>
       </c>
       <c r="H1064" t="n">
         <v>37120</v>
@@ -31341,7 +31341,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G1068" t="n">
-        <v>3.55709481239319</v>
+        <v>3.55709505081177</v>
       </c>
       <c r="H1068" t="n">
         <v>40177</v>
@@ -31399,7 +31399,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G1070" t="n">
-        <v>3.37877082824707</v>
+        <v>3.37877106666565</v>
       </c>
       <c r="H1070" t="n">
         <v>6066</v>
@@ -31428,7 +31428,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G1071" t="n">
-        <v>3.50078225135803</v>
+        <v>3.50078201293945</v>
       </c>
       <c r="H1071" t="n">
         <v>9632</v>
@@ -31573,7 +31573,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G1076" t="n">
-        <v>3.81988835334778</v>
+        <v>3.81988859176636</v>
       </c>
       <c r="H1076" t="n">
         <v>1676</v>
@@ -31718,7 +31718,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G1081" t="n">
-        <v>3.70726251602173</v>
+        <v>3.70726275444031</v>
       </c>
       <c r="H1081" t="n">
         <v>8487</v>
@@ -31805,7 +31805,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G1084" t="n">
-        <v>3.85743021965027</v>
+        <v>3.85743045806885</v>
       </c>
       <c r="H1084" t="n">
         <v>19626</v>
@@ -31834,7 +31834,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G1085" t="n">
-        <v>3.8386595249176</v>
+        <v>3.83865928649902</v>
       </c>
       <c r="H1085" t="n">
         <v>2650</v>
@@ -31950,7 +31950,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G1089" t="n">
-        <v>3.94189953804016</v>
+        <v>3.941899061203</v>
       </c>
       <c r="H1089" t="n">
         <v>22490</v>
@@ -32211,7 +32211,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G1098" t="n">
-        <v>4.16715049743652</v>
+        <v>4.16715097427368</v>
       </c>
       <c r="H1098" t="n">
         <v>6343</v>
@@ -32240,7 +32240,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G1099" t="n">
-        <v>4.05452537536621</v>
+        <v>4.05452489852905</v>
       </c>
       <c r="H1099" t="n">
         <v>8645</v>
@@ -32327,7 +32327,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G1102" t="n">
-        <v>3.97944092750549</v>
+        <v>3.97944116592407</v>
       </c>
       <c r="H1102" t="n">
         <v>4361</v>
@@ -32356,7 +32356,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G1103" t="n">
-        <v>3.89497232437134</v>
+        <v>3.89497208595276</v>
       </c>
       <c r="H1103" t="n">
         <v>1661</v>
@@ -32414,7 +32414,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G1105" t="n">
-        <v>3.85743021965027</v>
+        <v>3.85743045806885</v>
       </c>
       <c r="H1105" t="n">
         <v>11057</v>
@@ -32443,7 +32443,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G1106" t="n">
-        <v>3.76357555389404</v>
+        <v>3.76357579231262</v>
       </c>
       <c r="H1106" t="n">
         <v>3773</v>
@@ -32501,7 +32501,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G1108" t="n">
-        <v>3.7448046207428</v>
+        <v>3.74480438232422</v>
       </c>
       <c r="H1108" t="n">
         <v>6737</v>
@@ -32530,7 +32530,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G1109" t="n">
-        <v>3.66972064971924</v>
+        <v>3.66972088813782</v>
       </c>
       <c r="H1109" t="n">
         <v>4826</v>
@@ -32559,7 +32559,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G1110" t="n">
-        <v>3.76357555389404</v>
+        <v>3.76357579231262</v>
       </c>
       <c r="H1110" t="n">
         <v>2597</v>
@@ -32646,7 +32646,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G1113" t="n">
-        <v>3.65094995498657</v>
+        <v>3.65094971656799</v>
       </c>
       <c r="H1113" t="n">
         <v>229</v>
@@ -32791,7 +32791,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G1118" t="n">
-        <v>3.95128512382507</v>
+        <v>3.95128488540649</v>
       </c>
       <c r="H1118" t="n">
         <v>11818</v>
@@ -32820,7 +32820,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G1119" t="n">
-        <v>3.94189953804016</v>
+        <v>3.941899061203</v>
       </c>
       <c r="H1119" t="n">
         <v>8936</v>
@@ -32849,7 +32849,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G1120" t="n">
-        <v>4.16715049743652</v>
+        <v>4.16715097427368</v>
       </c>
       <c r="H1120" t="n">
         <v>3306</v>
@@ -32965,7 +32965,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G1124" t="n">
-        <v>4.24223470687866</v>
+        <v>4.2422342300415</v>
       </c>
       <c r="H1124" t="n">
         <v>17104</v>
@@ -33110,7 +33110,7 @@
         <v>4.59000015258789</v>
       </c>
       <c r="G1129" t="n">
-        <v>4.30793333053589</v>
+        <v>4.30793285369873</v>
       </c>
       <c r="H1129" t="n">
         <v>18140</v>
@@ -33255,7 +33255,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G1134" t="n">
-        <v>4.39240169525146</v>
+        <v>4.39240217208862</v>
       </c>
       <c r="H1134" t="n">
         <v>7995</v>
@@ -33284,7 +33284,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G1135" t="n">
-        <v>4.24223470687866</v>
+        <v>4.2422342300415</v>
       </c>
       <c r="H1135" t="n">
         <v>16906</v>
@@ -33429,7 +33429,7 @@
         <v>4.42999982833862</v>
       </c>
       <c r="G1140" t="n">
-        <v>4.15776491165161</v>
+        <v>4.15776538848877</v>
       </c>
       <c r="H1140" t="n">
         <v>977</v>
@@ -33458,7 +33458,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G1141" t="n">
-        <v>4.19530725479126</v>
+        <v>4.1953067779541</v>
       </c>
       <c r="H1141" t="n">
         <v>3970</v>
@@ -33603,7 +33603,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G1146" t="n">
-        <v>3.94189953804016</v>
+        <v>3.941899061203</v>
       </c>
       <c r="H1146" t="n">
         <v>10440</v>
@@ -33719,7 +33719,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G1150" t="n">
-        <v>3.81050252914429</v>
+        <v>3.81050276756287</v>
       </c>
       <c r="H1150" t="n">
         <v>1400</v>
@@ -33835,7 +33835,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G1154" t="n">
-        <v>4.44871520996094</v>
+        <v>4.44871473312378</v>
       </c>
       <c r="H1154" t="n">
         <v>44144</v>
@@ -33980,7 +33980,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G1159" t="n">
-        <v>3.97944092750549</v>
+        <v>3.97944116592407</v>
       </c>
       <c r="H1159" t="n">
         <v>20766</v>
@@ -34009,7 +34009,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G1160" t="n">
-        <v>3.99821257591248</v>
+        <v>3.9982123374939</v>
       </c>
       <c r="H1160" t="n">
         <v>9039</v>
@@ -34183,7 +34183,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G1166" t="n">
-        <v>3.88558626174927</v>
+        <v>3.88558650016785</v>
       </c>
       <c r="H1166" t="n">
         <v>3504</v>
@@ -34241,7 +34241,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G1168" t="n">
-        <v>3.94189953804016</v>
+        <v>3.941899061203</v>
       </c>
       <c r="H1168" t="n">
         <v>7781</v>
@@ -34328,7 +34328,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G1171" t="n">
-        <v>4.39240169525146</v>
+        <v>4.39240217208862</v>
       </c>
       <c r="H1171" t="n">
         <v>38443</v>
@@ -34386,7 +34386,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G1173" t="n">
-        <v>4.26100587844849</v>
+        <v>4.26100540161133</v>
       </c>
       <c r="H1173" t="n">
         <v>7903</v>
@@ -34444,7 +34444,7 @@
         <v>4.42999982833862</v>
       </c>
       <c r="G1175" t="n">
-        <v>4.15776491165161</v>
+        <v>4.15776538848877</v>
       </c>
       <c r="H1175" t="n">
         <v>8074</v>
@@ -34531,7 +34531,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G1178" t="n">
-        <v>4.05452537536621</v>
+        <v>4.05452489852905</v>
       </c>
       <c r="H1178" t="n">
         <v>2862</v>
@@ -34589,7 +34589,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G1180" t="n">
-        <v>4.00759792327881</v>
+        <v>4.00759744644165</v>
       </c>
       <c r="H1180" t="n">
         <v>7820</v>
@@ -34705,7 +34705,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G1184" t="n">
-        <v>3.95128512382507</v>
+        <v>3.95128488540649</v>
       </c>
       <c r="H1184" t="n">
         <v>6509</v>
@@ -34763,7 +34763,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G1186" t="n">
-        <v>3.93251395225525</v>
+        <v>3.93251419067383</v>
       </c>
       <c r="H1186" t="n">
         <v>1195</v>
@@ -34792,7 +34792,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G1187" t="n">
-        <v>3.8386595249176</v>
+        <v>3.83865928649902</v>
       </c>
       <c r="H1187" t="n">
         <v>14833</v>
@@ -34879,7 +34879,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G1190" t="n">
-        <v>3.88558626174927</v>
+        <v>3.88558650016785</v>
       </c>
       <c r="H1190" t="n">
         <v>6046</v>
@@ -34908,7 +34908,7 @@
         <v>4.17000007629395</v>
       </c>
       <c r="G1191" t="n">
-        <v>3.913743019104</v>
+        <v>3.91374325752258</v>
       </c>
       <c r="H1191" t="n">
         <v>3042</v>
@@ -34995,7 +34995,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G1194" t="n">
-        <v>3.97944092750549</v>
+        <v>3.97944116592407</v>
       </c>
       <c r="H1194" t="n">
         <v>9588</v>
@@ -35053,7 +35053,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G1196" t="n">
-        <v>3.95128512382507</v>
+        <v>3.95128488540649</v>
       </c>
       <c r="H1196" t="n">
         <v>8614</v>
@@ -35111,7 +35111,7 @@
         <v>4.17000007629395</v>
       </c>
       <c r="G1198" t="n">
-        <v>3.913743019104</v>
+        <v>3.91374325752258</v>
       </c>
       <c r="H1198" t="n">
         <v>3221</v>
@@ -35140,7 +35140,7 @@
         <v>4.17000007629395</v>
       </c>
       <c r="G1199" t="n">
-        <v>3.913743019104</v>
+        <v>3.91374325752258</v>
       </c>
       <c r="H1199" t="n">
         <v>4048</v>
@@ -35169,7 +35169,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G1200" t="n">
-        <v>3.76357555389404</v>
+        <v>3.76357579231262</v>
       </c>
       <c r="H1200" t="n">
         <v>21925</v>
@@ -35198,7 +35198,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G1201" t="n">
-        <v>3.66972064971924</v>
+        <v>3.66972088813782</v>
       </c>
       <c r="H1201" t="n">
         <v>10719</v>
@@ -35227,7 +35227,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G1202" t="n">
-        <v>3.70726251602173</v>
+        <v>3.70726275444031</v>
       </c>
       <c r="H1202" t="n">
         <v>6557</v>
@@ -35546,7 +35546,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G1213" t="n">
-        <v>3.7448046207428</v>
+        <v>3.74480438232422</v>
       </c>
       <c r="H1213" t="n">
         <v>13310</v>
@@ -35575,7 +35575,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G1214" t="n">
-        <v>3.67910623550415</v>
+        <v>3.67910599708557</v>
       </c>
       <c r="H1214" t="n">
         <v>3204</v>
@@ -35604,7 +35604,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G1215" t="n">
-        <v>3.7448046207428</v>
+        <v>3.74480438232422</v>
       </c>
       <c r="H1215" t="n">
         <v>20889</v>
@@ -35691,7 +35691,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G1218" t="n">
-        <v>3.50078225135803</v>
+        <v>3.50078201293945</v>
       </c>
       <c r="H1218" t="n">
         <v>7191</v>
@@ -35720,7 +35720,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G1219" t="n">
-        <v>3.38815641403198</v>
+        <v>3.3881561756134</v>
       </c>
       <c r="H1219" t="n">
         <v>10556</v>
@@ -35807,7 +35807,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G1222" t="n">
-        <v>3.38815641403198</v>
+        <v>3.3881561756134</v>
       </c>
       <c r="H1222" t="n">
         <v>9690</v>
@@ -35894,7 +35894,7 @@
         <v>3.41000008583069</v>
       </c>
       <c r="G1225" t="n">
-        <v>3.20044708251953</v>
+        <v>3.20044684410095</v>
       </c>
       <c r="H1225" t="n">
         <v>8882</v>
@@ -36097,7 +36097,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G1232" t="n">
-        <v>3.65094995498657</v>
+        <v>3.65094971656799</v>
       </c>
       <c r="H1232" t="n">
         <v>14970</v>
@@ -36213,7 +36213,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G1236" t="n">
-        <v>3.57586574554443</v>
+        <v>3.57586598396301</v>
       </c>
       <c r="H1236" t="n">
         <v>1829</v>
@@ -36242,7 +36242,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G1237" t="n">
-        <v>3.67910623550415</v>
+        <v>3.67910599708557</v>
       </c>
       <c r="H1237" t="n">
         <v>4650</v>
@@ -36300,7 +36300,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G1239" t="n">
-        <v>3.70726251602173</v>
+        <v>3.70726275444031</v>
       </c>
       <c r="H1239" t="n">
         <v>34864</v>
@@ -36387,7 +36387,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G1242" t="n">
-        <v>3.89497232437134</v>
+        <v>3.89497208595276</v>
       </c>
       <c r="H1242" t="n">
         <v>54144</v>
@@ -36416,7 +36416,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G1243" t="n">
-        <v>3.89497232437134</v>
+        <v>3.89497208595276</v>
       </c>
       <c r="H1243" t="n">
         <v>8113</v>
@@ -36445,7 +36445,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G1244" t="n">
-        <v>3.8386595249176</v>
+        <v>3.83865928649902</v>
       </c>
       <c r="H1244" t="n">
         <v>8928</v>
@@ -36503,7 +36503,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G1246" t="n">
-        <v>3.7448046207428</v>
+        <v>3.74480438232422</v>
       </c>
       <c r="H1246" t="n">
         <v>15117</v>
@@ -36532,7 +36532,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G1247" t="n">
-        <v>3.70726251602173</v>
+        <v>3.70726275444031</v>
       </c>
       <c r="H1247" t="n">
         <v>7302</v>
@@ -36677,7 +36677,7 @@
         <v>4.17000007629395</v>
       </c>
       <c r="G1252" t="n">
-        <v>3.913743019104</v>
+        <v>3.91374325752258</v>
       </c>
       <c r="H1252" t="n">
         <v>17785</v>
@@ -36706,7 +36706,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G1253" t="n">
-        <v>3.89497232437134</v>
+        <v>3.89497208595276</v>
       </c>
       <c r="H1253" t="n">
         <v>28710</v>
@@ -36880,7 +36880,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G1259" t="n">
-        <v>3.70726251602173</v>
+        <v>3.70726275444031</v>
       </c>
       <c r="H1259" t="n">
         <v>4961</v>
@@ -36909,7 +36909,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G1260" t="n">
-        <v>3.70726251602173</v>
+        <v>3.70726275444031</v>
       </c>
       <c r="H1260" t="n">
         <v>3838</v>
@@ -36967,7 +36967,7 @@
         <v>3.97000002861023</v>
       </c>
       <c r="G1262" t="n">
-        <v>3.72603368759155</v>
+        <v>3.72603344917297</v>
       </c>
       <c r="H1262" t="n">
         <v>6000</v>
@@ -36996,7 +36996,7 @@
         <v>3.97000002861023</v>
       </c>
       <c r="G1263" t="n">
-        <v>3.72603368759155</v>
+        <v>3.72603344917297</v>
       </c>
       <c r="H1263" t="n">
         <v>3245</v>
@@ -37054,7 +37054,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G1265" t="n">
-        <v>3.70726251602173</v>
+        <v>3.70726275444031</v>
       </c>
       <c r="H1265" t="n">
         <v>9568</v>
@@ -37083,7 +37083,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G1266" t="n">
-        <v>3.70726251602173</v>
+        <v>3.70726275444031</v>
       </c>
       <c r="H1266" t="n">
         <v>4860</v>
@@ -37112,7 +37112,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G1267" t="n">
-        <v>3.70726251602173</v>
+        <v>3.70726275444031</v>
       </c>
       <c r="H1267" t="n">
         <v>2386</v>
@@ -37141,7 +37141,7 @@
         <v>3.97000002861023</v>
       </c>
       <c r="G1268" t="n">
-        <v>3.72603368759155</v>
+        <v>3.72603344917297</v>
       </c>
       <c r="H1268" t="n">
         <v>6034</v>
@@ -37170,7 +37170,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G1269" t="n">
-        <v>3.7448046207428</v>
+        <v>3.74480438232422</v>
       </c>
       <c r="H1269" t="n">
         <v>4265</v>
@@ -37199,7 +37199,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G1270" t="n">
-        <v>3.52893853187561</v>
+        <v>3.52893877029419</v>
       </c>
       <c r="H1270" t="n">
         <v>20500</v>
@@ -37228,7 +37228,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G1271" t="n">
-        <v>3.65094995498657</v>
+        <v>3.65094971656799</v>
       </c>
       <c r="H1271" t="n">
         <v>10268</v>
@@ -37344,7 +37344,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G1275" t="n">
-        <v>3.66972064971924</v>
+        <v>3.66972088813782</v>
       </c>
       <c r="H1275" t="n">
         <v>8840</v>
@@ -37373,7 +37373,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G1276" t="n">
-        <v>3.66972064971924</v>
+        <v>3.66972088813782</v>
       </c>
       <c r="H1276" t="n">
         <v>3526</v>
@@ -37402,7 +37402,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G1277" t="n">
-        <v>3.70726251602173</v>
+        <v>3.70726275444031</v>
       </c>
       <c r="H1277" t="n">
         <v>11778</v>
@@ -37431,7 +37431,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G1278" t="n">
-        <v>3.63217878341675</v>
+        <v>3.63217854499817</v>
       </c>
       <c r="H1278" t="n">
         <v>10400</v>
@@ -37489,7 +37489,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G1280" t="n">
-        <v>3.57586574554443</v>
+        <v>3.57586598396301</v>
       </c>
       <c r="H1280" t="n">
         <v>903</v>
@@ -37605,7 +37605,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G1284" t="n">
-        <v>3.57586574554443</v>
+        <v>3.57586598396301</v>
       </c>
       <c r="H1284" t="n">
         <v>17627</v>
@@ -37634,7 +37634,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G1285" t="n">
-        <v>3.55709481239319</v>
+        <v>3.55709505081177</v>
       </c>
       <c r="H1285" t="n">
         <v>2645</v>
@@ -37866,7 +37866,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G1293" t="n">
-        <v>3.63217878341675</v>
+        <v>3.63217854499817</v>
       </c>
       <c r="H1293" t="n">
         <v>6267</v>
@@ -37953,7 +37953,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G1296" t="n">
-        <v>3.63217878341675</v>
+        <v>3.63217854499817</v>
       </c>
       <c r="H1296" t="n">
         <v>21822</v>
@@ -38156,7 +38156,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G1303" t="n">
-        <v>3.63217878341675</v>
+        <v>3.63217854499817</v>
       </c>
       <c r="H1303" t="n">
         <v>2047</v>
@@ -38562,7 +38562,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G1317" t="n">
-        <v>3.55709481239319</v>
+        <v>3.55709505081177</v>
       </c>
       <c r="H1317" t="n">
         <v>7529</v>
@@ -38649,7 +38649,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G1320" t="n">
-        <v>3.52893853187561</v>
+        <v>3.52893877029419</v>
       </c>
       <c r="H1320" t="n">
         <v>8713</v>
@@ -38707,7 +38707,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G1322" t="n">
-        <v>3.53832411766052</v>
+        <v>3.53832387924194</v>
       </c>
       <c r="H1322" t="n">
         <v>4391</v>
@@ -38736,7 +38736,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G1323" t="n">
-        <v>3.52893853187561</v>
+        <v>3.52893877029419</v>
       </c>
       <c r="H1323" t="n">
         <v>10305</v>
@@ -38794,7 +38794,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G1325" t="n">
-        <v>3.55709481239319</v>
+        <v>3.55709505081177</v>
       </c>
       <c r="H1325" t="n">
         <v>10336</v>
@@ -38823,7 +38823,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G1326" t="n">
-        <v>3.55709481239319</v>
+        <v>3.55709505081177</v>
       </c>
       <c r="H1326" t="n">
         <v>3135</v>
@@ -38881,7 +38881,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G1328" t="n">
-        <v>3.89497232437134</v>
+        <v>3.89497208595276</v>
       </c>
       <c r="H1328" t="n">
         <v>94205</v>
@@ -38968,7 +38968,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G1331" t="n">
-        <v>3.88558626174927</v>
+        <v>3.88558650016785</v>
       </c>
       <c r="H1331" t="n">
         <v>34293</v>
@@ -39026,7 +39026,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G1333" t="n">
-        <v>3.81050252914429</v>
+        <v>3.81050276756287</v>
       </c>
       <c r="H1333" t="n">
         <v>13284</v>
@@ -39084,7 +39084,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G1335" t="n">
-        <v>3.81050252914429</v>
+        <v>3.81050276756287</v>
       </c>
       <c r="H1335" t="n">
         <v>19980</v>
@@ -39113,7 +39113,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G1336" t="n">
-        <v>3.76357555389404</v>
+        <v>3.76357579231262</v>
       </c>
       <c r="H1336" t="n">
         <v>10453</v>
@@ -39200,7 +39200,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G1339" t="n">
-        <v>3.76357555389404</v>
+        <v>3.76357579231262</v>
       </c>
       <c r="H1339" t="n">
         <v>2281</v>
@@ -39229,7 +39229,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G1340" t="n">
-        <v>3.81050252914429</v>
+        <v>3.81050276756287</v>
       </c>
       <c r="H1340" t="n">
         <v>7947</v>
@@ -39258,7 +39258,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G1341" t="n">
-        <v>3.85743021965027</v>
+        <v>3.85743045806885</v>
       </c>
       <c r="H1341" t="n">
         <v>16294</v>
@@ -39316,7 +39316,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G1343" t="n">
-        <v>3.81050252914429</v>
+        <v>3.81050276756287</v>
       </c>
       <c r="H1343" t="n">
         <v>7887</v>
@@ -39345,7 +39345,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G1344" t="n">
-        <v>3.81050252914429</v>
+        <v>3.81050276756287</v>
       </c>
       <c r="H1344" t="n">
         <v>3994</v>
@@ -39693,7 +39693,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G1356" t="n">
-        <v>3.70726251602173</v>
+        <v>3.70726275444031</v>
       </c>
       <c r="H1356" t="n">
         <v>20494</v>
@@ -39722,7 +39722,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G1357" t="n">
-        <v>3.76357555389404</v>
+        <v>3.76357579231262</v>
       </c>
       <c r="H1357" t="n">
         <v>2322</v>
@@ -39751,7 +39751,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G1358" t="n">
-        <v>3.76357555389404</v>
+        <v>3.76357579231262</v>
       </c>
       <c r="H1358" t="n">
         <v>1404</v>
@@ -39809,7 +39809,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G1360" t="n">
-        <v>3.70726251602173</v>
+        <v>3.70726275444031</v>
       </c>
       <c r="H1360" t="n">
         <v>2733</v>
@@ -40041,7 +40041,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G1368" t="n">
-        <v>3.70726251602173</v>
+        <v>3.70726275444031</v>
       </c>
       <c r="H1368" t="n">
         <v>2800</v>
@@ -40070,7 +40070,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G1369" t="n">
-        <v>3.70726251602173</v>
+        <v>3.70726275444031</v>
       </c>
       <c r="H1369" t="n">
         <v>901</v>
@@ -40128,7 +40128,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G1371" t="n">
-        <v>3.66972064971924</v>
+        <v>3.66972088813782</v>
       </c>
       <c r="H1371" t="n">
         <v>4058</v>
@@ -40157,7 +40157,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G1372" t="n">
-        <v>3.67910623550415</v>
+        <v>3.67910599708557</v>
       </c>
       <c r="H1372" t="n">
         <v>5324</v>
@@ -40186,7 +40186,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G1373" t="n">
-        <v>3.70726251602173</v>
+        <v>3.70726275444031</v>
       </c>
       <c r="H1373" t="n">
         <v>1977</v>
@@ -40447,7 +40447,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G1382" t="n">
-        <v>3.70726251602173</v>
+        <v>3.70726275444031</v>
       </c>
       <c r="H1382" t="n">
         <v>4052</v>
@@ -40476,7 +40476,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G1383" t="n">
-        <v>3.66972064971924</v>
+        <v>3.66972088813782</v>
       </c>
       <c r="H1383" t="n">
         <v>10163</v>
@@ -40505,7 +40505,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G1384" t="n">
-        <v>3.67910623550415</v>
+        <v>3.67910599708557</v>
       </c>
       <c r="H1384" t="n">
         <v>2201</v>
@@ -40650,7 +40650,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G1389" t="n">
-        <v>3.70726251602173</v>
+        <v>3.70726275444031</v>
       </c>
       <c r="H1389" t="n">
         <v>3844</v>
@@ -40679,7 +40679,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G1390" t="n">
-        <v>3.70726251602173</v>
+        <v>3.70726275444031</v>
       </c>
       <c r="H1390" t="n">
         <v>0</v>
@@ -40708,7 +40708,7 @@
         <v>3.97000002861023</v>
       </c>
       <c r="G1391" t="n">
-        <v>3.72603368759155</v>
+        <v>3.72603344917297</v>
       </c>
       <c r="H1391" t="n">
         <v>2869</v>
@@ -40824,7 +40824,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G1395" t="n">
-        <v>3.70726251602173</v>
+        <v>3.70726275444031</v>
       </c>
       <c r="H1395" t="n">
         <v>742</v>
@@ -40853,7 +40853,7 @@
         <v>3.97000002861023</v>
       </c>
       <c r="G1396" t="n">
-        <v>3.72603368759155</v>
+        <v>3.72603344917297</v>
       </c>
       <c r="H1396" t="n">
         <v>2207</v>
@@ -41027,7 +41027,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G1402" t="n">
-        <v>3.57586574554443</v>
+        <v>3.57586598396301</v>
       </c>
       <c r="H1402" t="n">
         <v>11496</v>
@@ -41143,7 +41143,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G1406" t="n">
-        <v>3.63217878341675</v>
+        <v>3.63217854499817</v>
       </c>
       <c r="H1406" t="n">
         <v>4025</v>
@@ -41259,7 +41259,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G1410" t="n">
-        <v>3.55709481239319</v>
+        <v>3.55709505081177</v>
       </c>
       <c r="H1410" t="n">
         <v>3476</v>
@@ -41346,7 +41346,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G1413" t="n">
-        <v>3.63217878341675</v>
+        <v>3.63217854499817</v>
       </c>
       <c r="H1413" t="n">
         <v>2979</v>
@@ -41375,7 +41375,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G1414" t="n">
-        <v>3.57586574554443</v>
+        <v>3.57586598396301</v>
       </c>
       <c r="H1414" t="n">
         <v>350</v>
@@ -41433,7 +41433,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G1416" t="n">
-        <v>3.53832411766052</v>
+        <v>3.53832387924194</v>
       </c>
       <c r="H1416" t="n">
         <v>4236</v>
@@ -41462,7 +41462,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G1417" t="n">
-        <v>3.53832411766052</v>
+        <v>3.53832387924194</v>
       </c>
       <c r="H1417" t="n">
         <v>4168</v>
@@ -41607,7 +41607,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G1422" t="n">
-        <v>3.63217878341675</v>
+        <v>3.63217854499817</v>
       </c>
       <c r="H1422" t="n">
         <v>2196</v>
@@ -41665,7 +41665,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G1424" t="n">
-        <v>3.66972064971924</v>
+        <v>3.66972088813782</v>
       </c>
       <c r="H1424" t="n">
         <v>1314</v>
@@ -41694,7 +41694,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G1425" t="n">
-        <v>3.66972064971924</v>
+        <v>3.66972088813782</v>
       </c>
       <c r="H1425" t="n">
         <v>1063</v>
@@ -41839,7 +41839,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G1430" t="n">
-        <v>3.67910623550415</v>
+        <v>3.67910599708557</v>
       </c>
       <c r="H1430" t="n">
         <v>1147</v>
@@ -41868,7 +41868,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G1431" t="n">
-        <v>3.65094995498657</v>
+        <v>3.65094971656799</v>
       </c>
       <c r="H1431" t="n">
         <v>550</v>
@@ -41897,7 +41897,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G1432" t="n">
-        <v>3.65094995498657</v>
+        <v>3.65094971656799</v>
       </c>
       <c r="H1432" t="n">
         <v>3160</v>
@@ -41926,7 +41926,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G1433" t="n">
-        <v>3.65094995498657</v>
+        <v>3.65094971656799</v>
       </c>
       <c r="H1433" t="n">
         <v>0</v>
@@ -41984,7 +41984,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G1435" t="n">
-        <v>3.63217878341675</v>
+        <v>3.63217854499817</v>
       </c>
       <c r="H1435" t="n">
         <v>2049</v>
@@ -42042,7 +42042,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G1437" t="n">
-        <v>3.63217878341675</v>
+        <v>3.63217854499817</v>
       </c>
       <c r="H1437" t="n">
         <v>2511</v>
@@ -42071,7 +42071,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G1438" t="n">
-        <v>3.66972064971924</v>
+        <v>3.66972088813782</v>
       </c>
       <c r="H1438" t="n">
         <v>1350</v>
@@ -42100,7 +42100,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G1439" t="n">
-        <v>3.65094995498657</v>
+        <v>3.65094971656799</v>
       </c>
       <c r="H1439" t="n">
         <v>1773</v>
@@ -42419,7 +42419,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G1450" t="n">
-        <v>3.55709481239319</v>
+        <v>3.55709505081177</v>
       </c>
       <c r="H1450" t="n">
         <v>2150</v>
@@ -42477,7 +42477,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G1452" t="n">
-        <v>3.57586574554443</v>
+        <v>3.57586598396301</v>
       </c>
       <c r="H1452" t="n">
         <v>3405</v>
@@ -42506,7 +42506,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G1453" t="n">
-        <v>3.57586574554443</v>
+        <v>3.57586598396301</v>
       </c>
       <c r="H1453" t="n">
         <v>0</v>
@@ -42535,7 +42535,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G1454" t="n">
-        <v>3.52893853187561</v>
+        <v>3.52893877029419</v>
       </c>
       <c r="H1454" t="n">
         <v>3322</v>
@@ -42622,7 +42622,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G1457" t="n">
-        <v>3.57586574554443</v>
+        <v>3.57586598396301</v>
       </c>
       <c r="H1457" t="n">
         <v>4238</v>
@@ -42709,7 +42709,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G1460" t="n">
-        <v>3.50078225135803</v>
+        <v>3.50078201293945</v>
       </c>
       <c r="H1460" t="n">
         <v>3660</v>
@@ -42912,7 +42912,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G1467" t="n">
-        <v>3.53832411766052</v>
+        <v>3.53832387924194</v>
       </c>
       <c r="H1467" t="n">
         <v>4090</v>
@@ -42941,7 +42941,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G1468" t="n">
-        <v>3.52893853187561</v>
+        <v>3.52893877029419</v>
       </c>
       <c r="H1468" t="n">
         <v>6042</v>
@@ -43115,7 +43115,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G1474" t="n">
-        <v>3.55709481239319</v>
+        <v>3.55709505081177</v>
       </c>
       <c r="H1474" t="n">
         <v>3622</v>
@@ -43173,7 +43173,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G1476" t="n">
-        <v>3.52893853187561</v>
+        <v>3.52893877029419</v>
       </c>
       <c r="H1476" t="n">
         <v>24081</v>
@@ -43289,7 +43289,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G1480" t="n">
-        <v>3.50078225135803</v>
+        <v>3.50078201293945</v>
       </c>
       <c r="H1480" t="n">
         <v>1258</v>
@@ -43318,7 +43318,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G1481" t="n">
-        <v>3.50078225135803</v>
+        <v>3.50078201293945</v>
       </c>
       <c r="H1481" t="n">
         <v>2361</v>
@@ -43405,7 +43405,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G1484" t="n">
-        <v>3.52893853187561</v>
+        <v>3.52893877029419</v>
       </c>
       <c r="H1484" t="n">
         <v>5050</v>
@@ -43463,7 +43463,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G1486" t="n">
-        <v>3.46324014663696</v>
+        <v>3.46324038505554</v>
       </c>
       <c r="H1486" t="n">
         <v>225</v>
@@ -43550,7 +43550,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G1489" t="n">
-        <v>3.4444694519043</v>
+        <v>3.44446921348572</v>
       </c>
       <c r="H1489" t="n">
         <v>12652</v>
@@ -43695,7 +43695,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G1494" t="n">
-        <v>3.46324014663696</v>
+        <v>3.46324038505554</v>
       </c>
       <c r="H1494" t="n">
         <v>18038</v>
@@ -43724,7 +43724,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G1495" t="n">
-        <v>3.50078225135803</v>
+        <v>3.50078201293945</v>
       </c>
       <c r="H1495" t="n">
         <v>7784</v>
@@ -43753,7 +43753,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G1496" t="n">
-        <v>3.50078225135803</v>
+        <v>3.50078201293945</v>
       </c>
       <c r="H1496" t="n">
         <v>1691</v>
@@ -43811,7 +43811,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G1498" t="n">
-        <v>3.52893853187561</v>
+        <v>3.52893877029419</v>
       </c>
       <c r="H1498" t="n">
         <v>5800</v>
@@ -43898,7 +43898,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G1501" t="n">
-        <v>3.50078225135803</v>
+        <v>3.50078201293945</v>
       </c>
       <c r="H1501" t="n">
         <v>1361</v>
@@ -44014,7 +44014,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G1505" t="n">
-        <v>3.46324014663696</v>
+        <v>3.46324038505554</v>
       </c>
       <c r="H1505" t="n">
         <v>1027</v>
@@ -44043,7 +44043,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G1506" t="n">
-        <v>3.39754199981689</v>
+        <v>3.39754176139832</v>
       </c>
       <c r="H1506" t="n">
         <v>6752</v>
@@ -44130,7 +44130,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G1509" t="n">
-        <v>3.1910617351532</v>
+        <v>3.19106149673462</v>
       </c>
       <c r="H1509" t="n">
         <v>12862</v>
@@ -44333,7 +44333,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G1516" t="n">
-        <v>3.14413404464722</v>
+        <v>3.14413380622864</v>
       </c>
       <c r="H1516" t="n">
         <v>21428</v>
@@ -44362,7 +44362,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G1517" t="n">
-        <v>3.25675964355469</v>
+        <v>3.25675988197327</v>
       </c>
       <c r="H1517" t="n">
         <v>9087</v>
@@ -44391,7 +44391,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G1518" t="n">
-        <v>3.46324014663696</v>
+        <v>3.46324038505554</v>
       </c>
       <c r="H1518" t="n">
         <v>19030</v>
@@ -44420,7 +44420,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G1519" t="n">
-        <v>3.55709481239319</v>
+        <v>3.55709505081177</v>
       </c>
       <c r="H1519" t="n">
         <v>48142</v>
@@ -44449,7 +44449,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G1520" t="n">
-        <v>3.57586574554443</v>
+        <v>3.57586598396301</v>
       </c>
       <c r="H1520" t="n">
         <v>10173</v>
@@ -44594,7 +44594,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G1525" t="n">
-        <v>3.39754199981689</v>
+        <v>3.39754176139832</v>
       </c>
       <c r="H1525" t="n">
         <v>4001</v>
@@ -44826,7 +44826,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G1533" t="n">
-        <v>3.37877082824707</v>
+        <v>3.37877106666565</v>
       </c>
       <c r="H1533" t="n">
         <v>250</v>
@@ -44913,7 +44913,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G1536" t="n">
-        <v>3.36938524246216</v>
+        <v>3.36938548088074</v>
       </c>
       <c r="H1536" t="n">
         <v>8974</v>
@@ -44942,7 +44942,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G1537" t="n">
-        <v>3.25675964355469</v>
+        <v>3.25675988197327</v>
       </c>
       <c r="H1537" t="n">
         <v>19752</v>
@@ -45029,7 +45029,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G1540" t="n">
-        <v>3.29430174827576</v>
+        <v>3.29430150985718</v>
       </c>
       <c r="H1540" t="n">
         <v>5966</v>
@@ -45058,7 +45058,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G1541" t="n">
-        <v>3.25675964355469</v>
+        <v>3.25675988197327</v>
       </c>
       <c r="H1541" t="n">
         <v>2307</v>
@@ -45116,7 +45116,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G1543" t="n">
-        <v>3.25675964355469</v>
+        <v>3.25675988197327</v>
       </c>
       <c r="H1543" t="n">
         <v>2719</v>
@@ -45145,7 +45145,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G1544" t="n">
-        <v>3.1910617351532</v>
+        <v>3.19106149673462</v>
       </c>
       <c r="H1544" t="n">
         <v>2411</v>
@@ -45174,7 +45174,7 @@
         <v>3.41000008583069</v>
       </c>
       <c r="G1545" t="n">
-        <v>3.20044708251953</v>
+        <v>3.20044684410095</v>
       </c>
       <c r="H1545" t="n">
         <v>1890</v>
@@ -45290,7 +45290,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G1549" t="n">
-        <v>3.1910617351532</v>
+        <v>3.19106149673462</v>
       </c>
       <c r="H1549" t="n">
         <v>1800</v>
@@ -45377,7 +45377,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G1552" t="n">
-        <v>3.04089379310608</v>
+        <v>3.04089403152466</v>
       </c>
       <c r="H1552" t="n">
         <v>14720</v>
@@ -45580,7 +45580,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G1559" t="n">
-        <v>3.52893853187561</v>
+        <v>3.52893877029419</v>
       </c>
       <c r="H1559" t="n">
         <v>13701</v>
@@ -45783,7 +45783,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G1566" t="n">
-        <v>3.37877082824707</v>
+        <v>3.37877106666565</v>
       </c>
       <c r="H1566" t="n">
         <v>4078</v>
@@ -45870,7 +45870,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G1569" t="n">
-        <v>3.37877082824707</v>
+        <v>3.37877106666565</v>
       </c>
       <c r="H1569" t="n">
         <v>4200</v>
@@ -45899,7 +45899,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G1570" t="n">
-        <v>3.4444694519043</v>
+        <v>3.44446921348572</v>
       </c>
       <c r="H1570" t="n">
         <v>300</v>
@@ -46015,7 +46015,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G1574" t="n">
-        <v>2.95642447471619</v>
+        <v>2.95642471313477</v>
       </c>
       <c r="H1574" t="n">
         <v>8919</v>
@@ -46131,7 +46131,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G1578" t="n">
-        <v>2.92826795578003</v>
+        <v>2.92826819419861</v>
       </c>
       <c r="H1578" t="n">
         <v>1638</v>
@@ -46189,7 +46189,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G1580" t="n">
-        <v>2.90011167526245</v>
+        <v>2.90011143684387</v>
       </c>
       <c r="H1580" t="n">
         <v>2297</v>
@@ -46218,7 +46218,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G1581" t="n">
-        <v>2.92826795578003</v>
+        <v>2.92826819419861</v>
       </c>
       <c r="H1581" t="n">
         <v>27</v>
@@ -46276,7 +46276,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G1583" t="n">
-        <v>3.27553057670593</v>
+        <v>3.27553081512451</v>
       </c>
       <c r="H1583" t="n">
         <v>25580</v>
@@ -46305,7 +46305,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G1584" t="n">
-        <v>3.55709481239319</v>
+        <v>3.55709505081177</v>
       </c>
       <c r="H1584" t="n">
         <v>34416</v>
@@ -46363,7 +46363,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G1586" t="n">
-        <v>3.66972064971924</v>
+        <v>3.66972088813782</v>
       </c>
       <c r="H1586" t="n">
         <v>8000</v>
@@ -46392,7 +46392,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G1587" t="n">
-        <v>3.65094995498657</v>
+        <v>3.65094971656799</v>
       </c>
       <c r="H1587" t="n">
         <v>7611</v>
@@ -46421,7 +46421,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G1588" t="n">
-        <v>3.4444694519043</v>
+        <v>3.44446921348572</v>
       </c>
       <c r="H1588" t="n">
         <v>21839</v>
@@ -46508,7 +46508,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G1591" t="n">
-        <v>3.55709481239319</v>
+        <v>3.55709505081177</v>
       </c>
       <c r="H1591" t="n">
         <v>301</v>
@@ -46566,7 +46566,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G1593" t="n">
-        <v>3.52893853187561</v>
+        <v>3.52893877029419</v>
       </c>
       <c r="H1593" t="n">
         <v>6425</v>
@@ -46595,7 +46595,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G1594" t="n">
-        <v>3.55709481239319</v>
+        <v>3.55709505081177</v>
       </c>
       <c r="H1594" t="n">
         <v>6850</v>
@@ -46624,7 +46624,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G1595" t="n">
-        <v>3.55709481239319</v>
+        <v>3.55709505081177</v>
       </c>
       <c r="H1595" t="n">
         <v>0</v>
@@ -46653,7 +46653,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G1596" t="n">
-        <v>3.57586574554443</v>
+        <v>3.57586598396301</v>
       </c>
       <c r="H1596" t="n">
         <v>9294</v>
@@ -46769,7 +46769,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G1600" t="n">
-        <v>3.46324014663696</v>
+        <v>3.46324038505554</v>
       </c>
       <c r="H1600" t="n">
         <v>1700</v>
@@ -47030,7 +47030,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G1609" t="n">
-        <v>3.46324014663696</v>
+        <v>3.46324038505554</v>
       </c>
       <c r="H1609" t="n">
         <v>70</v>
@@ -47088,7 +47088,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G1611" t="n">
-        <v>3.39754199981689</v>
+        <v>3.39754176139832</v>
       </c>
       <c r="H1611" t="n">
         <v>3575</v>
@@ -47117,7 +47117,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G1612" t="n">
-        <v>3.39754199981689</v>
+        <v>3.39754176139832</v>
       </c>
       <c r="H1612" t="n">
         <v>0</v>
@@ -47175,7 +47175,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G1614" t="n">
-        <v>3.38815641403198</v>
+        <v>3.3881561756134</v>
       </c>
       <c r="H1614" t="n">
         <v>3973</v>
@@ -47204,7 +47204,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G1615" t="n">
-        <v>3.1910617351532</v>
+        <v>3.19106149673462</v>
       </c>
       <c r="H1615" t="n">
         <v>6407</v>
@@ -47262,7 +47262,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G1617" t="n">
-        <v>3.25675964355469</v>
+        <v>3.25675988197327</v>
       </c>
       <c r="H1617" t="n">
         <v>5292</v>
@@ -47291,7 +47291,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G1618" t="n">
-        <v>3.25675964355469</v>
+        <v>3.25675988197327</v>
       </c>
       <c r="H1618" t="n">
         <v>1000</v>
@@ -80038,6 +80038,35 @@
         <v>100805</v>
       </c>
       <c r="I2747" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2748">
+      <c r="A2748" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2748" s="1" t="n">
+        <v>46317.2916666667</v>
+      </c>
+      <c r="C2748" t="n">
+        <v>0.975000023841858</v>
+      </c>
+      <c r="D2748" t="n">
+        <v>0.975000023841858</v>
+      </c>
+      <c r="E2748" t="n">
+        <v>0.959999978542328</v>
+      </c>
+      <c r="F2748" t="n">
+        <v>0.975000023841858</v>
+      </c>
+      <c r="G2748" t="n">
+        <v>0.975000023841858</v>
+      </c>
+      <c r="H2748" t="n">
+        <v>2194</v>
+      </c>
+      <c r="I2748" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/RAT.MI.xlsx
+++ b/data/RAT.MI.xlsx
@@ -427,7 +427,7 @@
         <v>2.3659999370575</v>
       </c>
       <c r="G2" t="n">
-        <v>1.85825943946838</v>
+        <v>1.85825955867767</v>
       </c>
       <c r="H2" t="n">
         <v>1350</v>
@@ -485,7 +485,7 @@
         <v>2.44600009918213</v>
       </c>
       <c r="G4" t="n">
-        <v>1.92109155654907</v>
+        <v>1.92109191417694</v>
       </c>
       <c r="H4" t="n">
         <v>365</v>
@@ -514,7 +514,7 @@
         <v>2.44600009918213</v>
       </c>
       <c r="G5" t="n">
-        <v>1.92109155654907</v>
+        <v>1.92109191417694</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -543,7 +543,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G6" t="n">
-        <v>1.8849630355835</v>
+        <v>1.88496315479279</v>
       </c>
       <c r="H6" t="n">
         <v>5635</v>
@@ -572,7 +572,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G7" t="n">
-        <v>1.8849630355835</v>
+        <v>1.88496315479279</v>
       </c>
       <c r="H7" t="n">
         <v>1000</v>
@@ -601,7 +601,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G8" t="n">
-        <v>1.9242330789566</v>
+        <v>1.92423319816589</v>
       </c>
       <c r="H8" t="n">
         <v>4000</v>
@@ -630,7 +630,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G9" t="n">
-        <v>1.8849630355835</v>
+        <v>1.88496315479279</v>
       </c>
       <c r="H9" t="n">
         <v>155</v>
@@ -659,7 +659,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G10" t="n">
-        <v>1.8849630355835</v>
+        <v>1.88496315479279</v>
       </c>
       <c r="H10" t="n">
         <v>559</v>
@@ -688,7 +688,7 @@
         <v>2.3659999370575</v>
       </c>
       <c r="G11" t="n">
-        <v>1.85825943946838</v>
+        <v>1.85825955867767</v>
       </c>
       <c r="H11" t="n">
         <v>1414</v>
@@ -717,7 +717,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G12" t="n">
-        <v>1.80642306804657</v>
+        <v>1.80642282962799</v>
       </c>
       <c r="H12" t="n">
         <v>270</v>
@@ -746,7 +746,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G13" t="n">
-        <v>1.80642306804657</v>
+        <v>1.80642282962799</v>
       </c>
       <c r="H13" t="n">
         <v>1200</v>
@@ -775,7 +775,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G14" t="n">
-        <v>1.82998514175415</v>
+        <v>1.82998502254486</v>
       </c>
       <c r="H14" t="n">
         <v>193</v>
@@ -804,7 +804,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G15" t="n">
-        <v>1.79856896400452</v>
+        <v>1.79856884479523</v>
       </c>
       <c r="H15" t="n">
         <v>2788</v>
@@ -833,7 +833,7 @@
         <v>2.25</v>
       </c>
       <c r="G16" t="n">
-        <v>1.76715302467346</v>
+        <v>1.76715290546417</v>
       </c>
       <c r="H16" t="n">
         <v>2070</v>
@@ -862,7 +862,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G17" t="n">
-        <v>1.85354697704315</v>
+        <v>1.85354709625244</v>
       </c>
       <c r="H17" t="n">
         <v>4705</v>
@@ -891,7 +891,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G18" t="n">
-        <v>1.85354697704315</v>
+        <v>1.85354709625244</v>
       </c>
       <c r="H18" t="n">
         <v>2000</v>
@@ -920,7 +920,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G19" t="n">
-        <v>1.86925518512726</v>
+        <v>1.86925530433655</v>
       </c>
       <c r="H19" t="n">
         <v>3200</v>
@@ -978,7 +978,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G21" t="n">
-        <v>1.89281725883484</v>
+        <v>1.89281713962555</v>
       </c>
       <c r="H21" t="n">
         <v>100</v>
@@ -1007,7 +1007,7 @@
         <v>2.37800002098083</v>
       </c>
       <c r="G22" t="n">
-        <v>1.86768412590027</v>
+        <v>1.86768400669098</v>
       </c>
       <c r="H22" t="n">
         <v>2858</v>
@@ -1036,7 +1036,7 @@
         <v>2.31200003623962</v>
       </c>
       <c r="G23" t="n">
-        <v>1.81584787368774</v>
+        <v>1.81584763526917</v>
       </c>
       <c r="H23" t="n">
         <v>750</v>
@@ -1123,7 +1123,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G26" t="n">
-        <v>1.8849630355835</v>
+        <v>1.88496315479279</v>
       </c>
       <c r="H26" t="n">
         <v>330</v>
@@ -1210,7 +1210,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G29" t="n">
-        <v>1.8849630355835</v>
+        <v>1.88496315479279</v>
       </c>
       <c r="H29" t="n">
         <v>1810</v>
@@ -1239,7 +1239,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G30" t="n">
-        <v>1.80642306804657</v>
+        <v>1.80642282962799</v>
       </c>
       <c r="H30" t="n">
         <v>10919</v>
@@ -1297,7 +1297,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G32" t="n">
-        <v>1.84569299221039</v>
+        <v>1.84569275379181</v>
       </c>
       <c r="H32" t="n">
         <v>250</v>
@@ -1326,7 +1326,7 @@
         <v>2.31599998474121</v>
       </c>
       <c r="G33" t="n">
-        <v>1.81898939609528</v>
+        <v>1.81898927688599</v>
       </c>
       <c r="H33" t="n">
         <v>1023</v>
@@ -1355,7 +1355,7 @@
         <v>2.33800005912781</v>
       </c>
       <c r="G34" t="n">
-        <v>1.83626806735992</v>
+        <v>1.8362683057785</v>
       </c>
       <c r="H34" t="n">
         <v>9221</v>
@@ -1384,7 +1384,7 @@
         <v>2.36800003051758</v>
       </c>
       <c r="G35" t="n">
-        <v>1.85983037948608</v>
+        <v>1.8598301410675</v>
       </c>
       <c r="H35" t="n">
         <v>100</v>
@@ -1413,7 +1413,7 @@
         <v>2.36800003051758</v>
       </c>
       <c r="G36" t="n">
-        <v>1.85983037948608</v>
+        <v>1.8598301410675</v>
       </c>
       <c r="H36" t="n">
         <v>0</v>
@@ -1442,7 +1442,7 @@
         <v>2.36800003051758</v>
       </c>
       <c r="G37" t="n">
-        <v>1.85983037948608</v>
+        <v>1.8598301410675</v>
       </c>
       <c r="H37" t="n">
         <v>100</v>
@@ -1471,7 +1471,7 @@
         <v>2.29800009727478</v>
       </c>
       <c r="G38" t="n">
-        <v>1.80485224723816</v>
+        <v>1.80485212802887</v>
       </c>
       <c r="H38" t="n">
         <v>7831</v>
@@ -1529,7 +1529,7 @@
         <v>2.31399989128113</v>
       </c>
       <c r="G40" t="n">
-        <v>1.81741857528687</v>
+        <v>1.81741845607758</v>
       </c>
       <c r="H40" t="n">
         <v>150</v>
@@ -1558,7 +1558,7 @@
         <v>2.31399989128113</v>
       </c>
       <c r="G41" t="n">
-        <v>1.81741857528687</v>
+        <v>1.81741845607758</v>
       </c>
       <c r="H41" t="n">
         <v>0</v>
@@ -1587,7 +1587,7 @@
         <v>2.31399989128113</v>
       </c>
       <c r="G42" t="n">
-        <v>1.81741857528687</v>
+        <v>1.81741845607758</v>
       </c>
       <c r="H42" t="n">
         <v>0</v>
@@ -1616,7 +1616,7 @@
         <v>2.33800005912781</v>
       </c>
       <c r="G43" t="n">
-        <v>1.83626806735992</v>
+        <v>1.8362683057785</v>
       </c>
       <c r="H43" t="n">
         <v>950</v>
@@ -1645,7 +1645,7 @@
         <v>2.36800003051758</v>
       </c>
       <c r="G44" t="n">
-        <v>1.85983037948608</v>
+        <v>1.8598301410675</v>
       </c>
       <c r="H44" t="n">
         <v>540</v>
@@ -1674,7 +1674,7 @@
         <v>2.37800002098083</v>
       </c>
       <c r="G45" t="n">
-        <v>1.86768412590027</v>
+        <v>1.86768400669098</v>
       </c>
       <c r="H45" t="n">
         <v>2230</v>
@@ -1703,7 +1703,7 @@
         <v>2.35599994659424</v>
       </c>
       <c r="G46" t="n">
-        <v>1.85040533542633</v>
+        <v>1.85040545463562</v>
       </c>
       <c r="H46" t="n">
         <v>253</v>
@@ -1790,7 +1790,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G49" t="n">
-        <v>1.81427669525146</v>
+        <v>1.81427705287933</v>
       </c>
       <c r="H49" t="n">
         <v>1530</v>
@@ -1819,7 +1819,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G50" t="n">
-        <v>1.84569299221039</v>
+        <v>1.84569275379181</v>
       </c>
       <c r="H50" t="n">
         <v>396</v>
@@ -1848,7 +1848,7 @@
         <v>2.33800005912781</v>
       </c>
       <c r="G51" t="n">
-        <v>1.83626806735992</v>
+        <v>1.8362683057785</v>
       </c>
       <c r="H51" t="n">
         <v>1660</v>
@@ -1877,7 +1877,7 @@
         <v>2.35800004005432</v>
       </c>
       <c r="G52" t="n">
-        <v>1.85197639465332</v>
+        <v>1.85197615623474</v>
       </c>
       <c r="H52" t="n">
         <v>3419</v>
@@ -1906,7 +1906,7 @@
         <v>2.34800004959106</v>
       </c>
       <c r="G53" t="n">
-        <v>1.84412229061127</v>
+        <v>1.84412217140198</v>
       </c>
       <c r="H53" t="n">
         <v>3348</v>
@@ -1935,7 +1935,7 @@
         <v>2.34400010108948</v>
       </c>
       <c r="G54" t="n">
-        <v>1.84098064899445</v>
+        <v>1.84098052978516</v>
       </c>
       <c r="H54" t="n">
         <v>600</v>
@@ -1964,7 +1964,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G55" t="n">
-        <v>1.84569299221039</v>
+        <v>1.84569275379181</v>
       </c>
       <c r="H55" t="n">
         <v>386</v>
@@ -1993,7 +1993,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G56" t="n">
-        <v>1.84569299221039</v>
+        <v>1.84569275379181</v>
       </c>
       <c r="H56" t="n">
         <v>5025</v>
@@ -2022,7 +2022,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G57" t="n">
-        <v>1.85354697704315</v>
+        <v>1.85354709625244</v>
       </c>
       <c r="H57" t="n">
         <v>50</v>
@@ -2051,7 +2051,7 @@
         <v>2.32200002670288</v>
       </c>
       <c r="G58" t="n">
-        <v>1.8237019777298</v>
+        <v>1.82370173931122</v>
       </c>
       <c r="H58" t="n">
         <v>1606</v>
@@ -2080,7 +2080,7 @@
         <v>2.32200002670288</v>
       </c>
       <c r="G59" t="n">
-        <v>1.8237019777298</v>
+        <v>1.82370173931122</v>
       </c>
       <c r="H59" t="n">
         <v>0</v>
@@ -2109,7 +2109,7 @@
         <v>2.30599999427795</v>
       </c>
       <c r="G60" t="n">
-        <v>1.81113529205322</v>
+        <v>1.8111355304718</v>
       </c>
       <c r="H60" t="n">
         <v>6820</v>
@@ -2138,7 +2138,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G61" t="n">
-        <v>1.81427669525146</v>
+        <v>1.81427705287933</v>
       </c>
       <c r="H61" t="n">
         <v>150</v>
@@ -2167,7 +2167,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G62" t="n">
-        <v>1.8221310377121</v>
+        <v>1.82213115692139</v>
       </c>
       <c r="H62" t="n">
         <v>7700</v>
@@ -2196,7 +2196,7 @@
         <v>2.35599994659424</v>
       </c>
       <c r="G63" t="n">
-        <v>1.85040533542633</v>
+        <v>1.85040545463562</v>
       </c>
       <c r="H63" t="n">
         <v>100</v>
@@ -2225,7 +2225,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G64" t="n">
-        <v>1.84569299221039</v>
+        <v>1.84569275379181</v>
       </c>
       <c r="H64" t="n">
         <v>1054</v>
@@ -2254,7 +2254,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G65" t="n">
-        <v>1.9242330789566</v>
+        <v>1.92423319816589</v>
       </c>
       <c r="H65" t="n">
         <v>19358</v>
@@ -2283,7 +2283,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G66" t="n">
-        <v>1.9242330789566</v>
+        <v>1.92423319816589</v>
       </c>
       <c r="H66" t="n">
         <v>0</v>
@@ -2312,7 +2312,7 @@
         <v>2.46600008010864</v>
       </c>
       <c r="G67" t="n">
-        <v>1.93679976463318</v>
+        <v>1.9367995262146</v>
       </c>
       <c r="H67" t="n">
         <v>1695</v>
@@ -2341,7 +2341,7 @@
         <v>2.4779999256134</v>
       </c>
       <c r="G68" t="n">
-        <v>1.94622457027435</v>
+        <v>1.94622445106506</v>
       </c>
       <c r="H68" t="n">
         <v>120</v>
@@ -2399,7 +2399,7 @@
         <v>2.5</v>
       </c>
       <c r="G70" t="n">
-        <v>1.96350359916687</v>
+        <v>1.96350300312042</v>
       </c>
       <c r="H70" t="n">
         <v>23697</v>
@@ -2428,7 +2428,7 @@
         <v>2.50200009346008</v>
       </c>
       <c r="G71" t="n">
-        <v>1.9650741815567</v>
+        <v>1.96507441997528</v>
       </c>
       <c r="H71" t="n">
         <v>350</v>
@@ -2457,7 +2457,7 @@
         <v>2.53800010681152</v>
       </c>
       <c r="G72" t="n">
-        <v>1.9933488368988</v>
+        <v>1.99334847927094</v>
       </c>
       <c r="H72" t="n">
         <v>1951</v>
@@ -2486,7 +2486,7 @@
         <v>2.55200004577637</v>
       </c>
       <c r="G73" t="n">
-        <v>2.00434422492981</v>
+        <v>2.00434398651123</v>
       </c>
       <c r="H73" t="n">
         <v>3450</v>
@@ -2515,7 +2515,7 @@
         <v>2.5</v>
       </c>
       <c r="G74" t="n">
-        <v>1.96350359916687</v>
+        <v>1.96350300312042</v>
       </c>
       <c r="H74" t="n">
         <v>1853</v>
@@ -2544,7 +2544,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G75" t="n">
-        <v>1.987065076828</v>
+        <v>1.98706543445587</v>
       </c>
       <c r="H75" t="n">
         <v>41607</v>
@@ -2573,7 +2573,7 @@
         <v>2.50200009346008</v>
       </c>
       <c r="G76" t="n">
-        <v>1.9650741815567</v>
+        <v>1.96507441997528</v>
       </c>
       <c r="H76" t="n">
         <v>3085</v>
@@ -2660,7 +2660,7 @@
         <v>2.45799994468689</v>
       </c>
       <c r="G79" t="n">
-        <v>1.93051636219025</v>
+        <v>1.93051648139954</v>
       </c>
       <c r="H79" t="n">
         <v>9175</v>
@@ -2689,7 +2689,7 @@
         <v>2.45799994468689</v>
       </c>
       <c r="G80" t="n">
-        <v>1.93051636219025</v>
+        <v>1.93051648139954</v>
       </c>
       <c r="H80" t="n">
         <v>1464</v>
@@ -2718,7 +2718,7 @@
         <v>2.5</v>
       </c>
       <c r="G81" t="n">
-        <v>1.96350359916687</v>
+        <v>1.96350300312042</v>
       </c>
       <c r="H81" t="n">
         <v>50</v>
@@ -2747,7 +2747,7 @@
         <v>2.49799990653992</v>
       </c>
       <c r="G82" t="n">
-        <v>1.9619323015213</v>
+        <v>1.96193242073059</v>
       </c>
       <c r="H82" t="n">
         <v>2294</v>
@@ -2776,7 +2776,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G83" t="n">
-        <v>1.93994140625</v>
+        <v>1.93994116783142</v>
       </c>
       <c r="H83" t="n">
         <v>1443</v>
@@ -2834,7 +2834,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G85" t="n">
-        <v>1.95564901828766</v>
+        <v>1.95564925670624</v>
       </c>
       <c r="H85" t="n">
         <v>2700</v>
@@ -2863,7 +2863,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G86" t="n">
-        <v>1.95564901828766</v>
+        <v>1.95564925670624</v>
       </c>
       <c r="H86" t="n">
         <v>0</v>
@@ -2892,7 +2892,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G87" t="n">
-        <v>1.93994140625</v>
+        <v>1.93994116783142</v>
       </c>
       <c r="H87" t="n">
         <v>303</v>
@@ -2921,7 +2921,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G88" t="n">
-        <v>1.91637945175171</v>
+        <v>1.91637897491455</v>
       </c>
       <c r="H88" t="n">
         <v>1187</v>
@@ -2950,7 +2950,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G89" t="n">
-        <v>1.8849630355835</v>
+        <v>1.88496315479279</v>
       </c>
       <c r="H89" t="n">
         <v>4181</v>
@@ -2979,7 +2979,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G90" t="n">
-        <v>1.91637945175171</v>
+        <v>1.91637897491455</v>
       </c>
       <c r="H90" t="n">
         <v>65</v>
@@ -3008,7 +3008,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G91" t="n">
-        <v>1.91637945175171</v>
+        <v>1.91637897491455</v>
       </c>
       <c r="H91" t="n">
         <v>0</v>
@@ -3153,7 +3153,7 @@
         <v>2.29800009727478</v>
       </c>
       <c r="G96" t="n">
-        <v>1.80485224723816</v>
+        <v>1.80485212802887</v>
       </c>
       <c r="H96" t="n">
         <v>5665</v>
@@ -3182,7 +3182,7 @@
         <v>2.29800009727478</v>
       </c>
       <c r="G97" t="n">
-        <v>1.80485224723816</v>
+        <v>1.80485212802887</v>
       </c>
       <c r="H97" t="n">
         <v>50</v>
@@ -3211,7 +3211,7 @@
         <v>2.34800004959106</v>
       </c>
       <c r="G98" t="n">
-        <v>1.84412229061127</v>
+        <v>1.84412217140198</v>
       </c>
       <c r="H98" t="n">
         <v>8904</v>
@@ -3240,7 +3240,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G99" t="n">
-        <v>1.89281725883484</v>
+        <v>1.89281713962555</v>
       </c>
       <c r="H99" t="n">
         <v>14550</v>
@@ -3269,7 +3269,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G100" t="n">
-        <v>1.93378710746765</v>
+        <v>1.93378722667694</v>
       </c>
       <c r="H100" t="n">
         <v>1125</v>
@@ -3298,7 +3298,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G101" t="n">
-        <v>1.95017516613007</v>
+        <v>1.95017540454865</v>
       </c>
       <c r="H101" t="n">
         <v>176</v>
@@ -3327,7 +3327,7 @@
         <v>2.34599995613098</v>
       </c>
       <c r="G102" t="n">
-        <v>1.92231547832489</v>
+        <v>1.92231559753418</v>
       </c>
       <c r="H102" t="n">
         <v>195</v>
@@ -3356,7 +3356,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G103" t="n">
-        <v>1.93378710746765</v>
+        <v>1.93378722667694</v>
       </c>
       <c r="H103" t="n">
         <v>3800</v>
@@ -3385,7 +3385,7 @@
         <v>2.35599994659424</v>
       </c>
       <c r="G104" t="n">
-        <v>1.93050968647003</v>
+        <v>1.93050956726074</v>
       </c>
       <c r="H104" t="n">
         <v>3779</v>
@@ -3501,7 +3501,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G108" t="n">
-        <v>1.9583694934845</v>
+        <v>1.95836925506592</v>
       </c>
       <c r="H108" t="n">
         <v>668</v>
@@ -3530,7 +3530,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G109" t="n">
-        <v>1.9583694934845</v>
+        <v>1.95836925506592</v>
       </c>
       <c r="H109" t="n">
         <v>0</v>
@@ -3559,7 +3559,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G110" t="n">
-        <v>1.95017516613007</v>
+        <v>1.95017540454865</v>
       </c>
       <c r="H110" t="n">
         <v>403</v>
@@ -3588,7 +3588,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G111" t="n">
-        <v>1.95017516613007</v>
+        <v>1.95017540454865</v>
       </c>
       <c r="H111" t="n">
         <v>0</v>
@@ -3617,7 +3617,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G112" t="n">
-        <v>1.91739916801453</v>
+        <v>1.91739904880524</v>
       </c>
       <c r="H112" t="n">
         <v>778</v>
@@ -3733,7 +3733,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G116" t="n">
-        <v>1.94198107719421</v>
+        <v>1.9419811964035</v>
       </c>
       <c r="H116" t="n">
         <v>5088</v>
@@ -3762,7 +3762,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G117" t="n">
-        <v>1.94198107719421</v>
+        <v>1.9419811964035</v>
       </c>
       <c r="H117" t="n">
         <v>0</v>
@@ -3791,7 +3791,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G118" t="n">
-        <v>1.91739916801453</v>
+        <v>1.91739904880524</v>
       </c>
       <c r="H118" t="n">
         <v>2740</v>
@@ -3849,7 +3849,7 @@
         <v>2.33200001716614</v>
       </c>
       <c r="G120" t="n">
-        <v>1.91084396839142</v>
+        <v>1.91084408760071</v>
       </c>
       <c r="H120" t="n">
         <v>1532</v>
@@ -3878,7 +3878,7 @@
         <v>2.33200001716614</v>
       </c>
       <c r="G121" t="n">
-        <v>1.91084396839142</v>
+        <v>1.91084408760071</v>
       </c>
       <c r="H121" t="n">
         <v>0</v>
@@ -3965,7 +3965,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G124" t="n">
-        <v>1.83545875549316</v>
+        <v>1.83545887470245</v>
       </c>
       <c r="H124" t="n">
         <v>348</v>
@@ -3994,7 +3994,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G125" t="n">
-        <v>1.8026829957962</v>
+        <v>1.80268287658691</v>
       </c>
       <c r="H125" t="n">
         <v>3159</v>
@@ -4052,7 +4052,7 @@
         <v>2.23600006103516</v>
       </c>
       <c r="G127" t="n">
-        <v>1.83218133449554</v>
+        <v>1.83218145370483</v>
       </c>
       <c r="H127" t="n">
         <v>773</v>
@@ -4110,7 +4110,7 @@
         <v>2.29800009727478</v>
       </c>
       <c r="G129" t="n">
-        <v>1.88298439979553</v>
+        <v>1.88298428058624</v>
       </c>
       <c r="H129" t="n">
         <v>100</v>
@@ -4139,7 +4139,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G130" t="n">
-        <v>1.86823511123657</v>
+        <v>1.86823523044586</v>
       </c>
       <c r="H130" t="n">
         <v>2288</v>
@@ -4168,7 +4168,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G131" t="n">
-        <v>1.94198107719421</v>
+        <v>1.9419811964035</v>
       </c>
       <c r="H131" t="n">
         <v>150</v>
@@ -4197,7 +4197,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G132" t="n">
-        <v>1.94198107719421</v>
+        <v>1.9419811964035</v>
       </c>
       <c r="H132" t="n">
         <v>0</v>
@@ -4226,7 +4226,7 @@
         <v>2.32800006866455</v>
       </c>
       <c r="G133" t="n">
-        <v>1.90756642818451</v>
+        <v>1.9075665473938</v>
       </c>
       <c r="H133" t="n">
         <v>510</v>
@@ -4255,7 +4255,7 @@
         <v>2.32800006866455</v>
       </c>
       <c r="G134" t="n">
-        <v>1.90756642818451</v>
+        <v>1.9075665473938</v>
       </c>
       <c r="H134" t="n">
         <v>0</v>
@@ -4284,7 +4284,7 @@
         <v>2.32800006866455</v>
       </c>
       <c r="G135" t="n">
-        <v>1.90756642818451</v>
+        <v>1.9075665473938</v>
       </c>
       <c r="H135" t="n">
         <v>0</v>
@@ -4313,7 +4313,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G136" t="n">
-        <v>1.89281702041626</v>
+        <v>1.89281713962555</v>
       </c>
       <c r="H136" t="n">
         <v>6553</v>
@@ -4342,7 +4342,7 @@
         <v>2.32599997520447</v>
       </c>
       <c r="G137" t="n">
-        <v>1.90592765808105</v>
+        <v>1.90592741966248</v>
       </c>
       <c r="H137" t="n">
         <v>600</v>
@@ -4371,7 +4371,7 @@
         <v>2.32599997520447</v>
       </c>
       <c r="G138" t="n">
-        <v>1.90592765808105</v>
+        <v>1.90592741966248</v>
       </c>
       <c r="H138" t="n">
         <v>815</v>
@@ -4429,7 +4429,7 @@
         <v>2.32599997520447</v>
       </c>
       <c r="G140" t="n">
-        <v>1.90592765808105</v>
+        <v>1.90592741966248</v>
       </c>
       <c r="H140" t="n">
         <v>50</v>
@@ -4458,7 +4458,7 @@
         <v>2.32599997520447</v>
       </c>
       <c r="G141" t="n">
-        <v>1.90592765808105</v>
+        <v>1.90592741966248</v>
       </c>
       <c r="H141" t="n">
         <v>0</v>
@@ -4487,7 +4487,7 @@
         <v>2.32800006866455</v>
       </c>
       <c r="G142" t="n">
-        <v>1.90756642818451</v>
+        <v>1.9075665473938</v>
       </c>
       <c r="H142" t="n">
         <v>80</v>
@@ -4574,7 +4574,7 @@
         <v>2.28399991989136</v>
       </c>
       <c r="G145" t="n">
-        <v>1.87151265144348</v>
+        <v>1.87151277065277</v>
       </c>
       <c r="H145" t="n">
         <v>10583</v>
@@ -4603,7 +4603,7 @@
         <v>2.31599998474121</v>
       </c>
       <c r="G146" t="n">
-        <v>1.8977335691452</v>
+        <v>1.89773344993591</v>
       </c>
       <c r="H146" t="n">
         <v>5883</v>
@@ -4632,7 +4632,7 @@
         <v>2.32599997520447</v>
       </c>
       <c r="G147" t="n">
-        <v>1.90592765808105</v>
+        <v>1.90592741966248</v>
       </c>
       <c r="H147" t="n">
         <v>1070</v>
@@ -4690,7 +4690,7 @@
         <v>2.2260000705719</v>
       </c>
       <c r="G149" t="n">
-        <v>1.82398736476898</v>
+        <v>1.82398748397827</v>
       </c>
       <c r="H149" t="n">
         <v>2820</v>
@@ -4777,7 +4777,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G152" t="n">
-        <v>1.78629505634308</v>
+        <v>1.78629493713379</v>
       </c>
       <c r="H152" t="n">
         <v>7134</v>
@@ -4864,7 +4864,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G155" t="n">
-        <v>1.75351905822754</v>
+        <v>1.75351893901825</v>
       </c>
       <c r="H155" t="n">
         <v>606</v>
@@ -4893,7 +4893,7 @@
         <v>2.17199993133545</v>
       </c>
       <c r="G156" t="n">
-        <v>1.77973985671997</v>
+        <v>1.77973973751068</v>
       </c>
       <c r="H156" t="n">
         <v>975</v>
@@ -4922,7 +4922,7 @@
         <v>2.17199993133545</v>
       </c>
       <c r="G157" t="n">
-        <v>1.77973985671997</v>
+        <v>1.77973973751068</v>
       </c>
       <c r="H157" t="n">
         <v>0</v>
@@ -4980,7 +4980,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G159" t="n">
-        <v>1.72074282169342</v>
+        <v>1.72074270248413</v>
       </c>
       <c r="H159" t="n">
         <v>2791</v>
@@ -5038,7 +5038,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G161" t="n">
-        <v>1.72893691062927</v>
+        <v>1.72893667221069</v>
       </c>
       <c r="H161" t="n">
         <v>12639</v>
@@ -5067,7 +5067,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G162" t="n">
-        <v>1.72893691062927</v>
+        <v>1.72893667221069</v>
       </c>
       <c r="H162" t="n">
         <v>0</v>
@@ -5096,7 +5096,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G163" t="n">
-        <v>1.69616079330444</v>
+        <v>1.69616067409515</v>
       </c>
       <c r="H163" t="n">
         <v>4541</v>
@@ -5125,7 +5125,7 @@
         <v>2.14800000190735</v>
       </c>
       <c r="G164" t="n">
-        <v>1.76007413864136</v>
+        <v>1.76007401943207</v>
       </c>
       <c r="H164" t="n">
         <v>2324</v>
@@ -5154,7 +5154,7 @@
         <v>2.14800000190735</v>
       </c>
       <c r="G165" t="n">
-        <v>1.76007413864136</v>
+        <v>1.76007401943207</v>
       </c>
       <c r="H165" t="n">
         <v>0</v>
@@ -5183,7 +5183,7 @@
         <v>2.14800000190735</v>
       </c>
       <c r="G166" t="n">
-        <v>1.76007413864136</v>
+        <v>1.76007401943207</v>
       </c>
       <c r="H166" t="n">
         <v>0</v>
@@ -5212,7 +5212,7 @@
         <v>2.14800000190735</v>
       </c>
       <c r="G167" t="n">
-        <v>1.76007413864136</v>
+        <v>1.76007401943207</v>
       </c>
       <c r="H167" t="n">
         <v>0</v>
@@ -5241,7 +5241,7 @@
         <v>2.14800000190735</v>
       </c>
       <c r="G168" t="n">
-        <v>1.76007413864136</v>
+        <v>1.76007401943207</v>
       </c>
       <c r="H168" t="n">
         <v>0</v>
@@ -5270,7 +5270,7 @@
         <v>2.14800000190735</v>
       </c>
       <c r="G169" t="n">
-        <v>1.76007413864136</v>
+        <v>1.76007401943207</v>
       </c>
       <c r="H169" t="n">
         <v>206</v>
@@ -5299,7 +5299,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G170" t="n">
-        <v>1.70435464382172</v>
+        <v>1.70435476303101</v>
       </c>
       <c r="H170" t="n">
         <v>12329</v>
@@ -5415,7 +5415,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G174" t="n">
-        <v>1.71254873275757</v>
+        <v>1.71254861354828</v>
       </c>
       <c r="H174" t="n">
         <v>36026</v>
@@ -5531,7 +5531,7 @@
         <v>1.9650000333786</v>
       </c>
       <c r="G178" t="n">
-        <v>1.61012375354767</v>
+        <v>1.61012363433838</v>
       </c>
       <c r="H178" t="n">
         <v>11222</v>
@@ -5560,7 +5560,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G179" t="n">
-        <v>1.62241470813751</v>
+        <v>1.62241458892822</v>
       </c>
       <c r="H179" t="n">
         <v>20086</v>
@@ -6082,7 +6082,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G197" t="n">
-        <v>1.65519058704376</v>
+        <v>1.65519070625305</v>
       </c>
       <c r="H197" t="n">
         <v>4191</v>
@@ -6111,7 +6111,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G198" t="n">
-        <v>1.65519058704376</v>
+        <v>1.65519070625305</v>
       </c>
       <c r="H198" t="n">
         <v>0</v>
@@ -6140,7 +6140,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G199" t="n">
-        <v>1.65519058704376</v>
+        <v>1.65519070625305</v>
       </c>
       <c r="H199" t="n">
         <v>1000</v>
@@ -6169,7 +6169,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G200" t="n">
-        <v>1.65519058704376</v>
+        <v>1.65519070625305</v>
       </c>
       <c r="H200" t="n">
         <v>0</v>
@@ -6198,7 +6198,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G201" t="n">
-        <v>1.65519058704376</v>
+        <v>1.65519070625305</v>
       </c>
       <c r="H201" t="n">
         <v>100</v>
@@ -6343,7 +6343,7 @@
         <v>1.99899995326996</v>
       </c>
       <c r="G206" t="n">
-        <v>1.63798320293427</v>
+        <v>1.63798332214355</v>
       </c>
       <c r="H206" t="n">
         <v>2595</v>
@@ -6401,7 +6401,7 @@
         <v>1.9889999628067</v>
       </c>
       <c r="G208" t="n">
-        <v>1.62978911399841</v>
+        <v>1.6297892332077</v>
       </c>
       <c r="H208" t="n">
         <v>50</v>
@@ -6459,7 +6459,7 @@
         <v>1.94700002670288</v>
       </c>
       <c r="G210" t="n">
-        <v>1.59537446498871</v>
+        <v>1.59537434577942</v>
       </c>
       <c r="H210" t="n">
         <v>7151</v>
@@ -6575,7 +6575,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G214" t="n">
-        <v>1.54047453403473</v>
+        <v>1.54047441482544</v>
       </c>
       <c r="H214" t="n">
         <v>2780</v>
@@ -6604,7 +6604,7 @@
         <v>1.91299998760223</v>
       </c>
       <c r="G215" t="n">
-        <v>1.56751465797424</v>
+        <v>1.56751477718353</v>
       </c>
       <c r="H215" t="n">
         <v>8016</v>
@@ -6633,7 +6633,7 @@
         <v>1.91600000858307</v>
       </c>
       <c r="G216" t="n">
-        <v>1.56997299194336</v>
+        <v>1.56997287273407</v>
       </c>
       <c r="H216" t="n">
         <v>8053</v>
@@ -6662,7 +6662,7 @@
         <v>1.91199994087219</v>
       </c>
       <c r="G217" t="n">
-        <v>1.56669521331787</v>
+        <v>1.56669533252716</v>
       </c>
       <c r="H217" t="n">
         <v>1680</v>
@@ -6691,7 +6691,7 @@
         <v>1.90199995040894</v>
       </c>
       <c r="G218" t="n">
-        <v>1.5585013628006</v>
+        <v>1.55850124359131</v>
       </c>
       <c r="H218" t="n">
         <v>2601</v>
@@ -6836,7 +6836,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G223" t="n">
-        <v>1.60602653026581</v>
+        <v>1.6060266494751</v>
       </c>
       <c r="H223" t="n">
         <v>3500</v>
@@ -6952,7 +6952,7 @@
         <v>1.8860000371933</v>
       </c>
       <c r="G227" t="n">
-        <v>1.54539108276367</v>
+        <v>1.54539096355438</v>
       </c>
       <c r="H227" t="n">
         <v>11268</v>
@@ -7010,7 +7010,7 @@
         <v>1.72399997711182</v>
       </c>
       <c r="G229" t="n">
-        <v>1.4126478433609</v>
+        <v>1.41264796257019</v>
       </c>
       <c r="H229" t="n">
         <v>18656</v>
@@ -7039,7 +7039,7 @@
         <v>1.70200002193451</v>
       </c>
       <c r="G230" t="n">
-        <v>1.39462113380432</v>
+        <v>1.39462101459503</v>
       </c>
       <c r="H230" t="n">
         <v>23064</v>
@@ -7097,7 +7097,7 @@
         <v>1.79499995708466</v>
       </c>
       <c r="G232" t="n">
-        <v>1.47082531452179</v>
+        <v>1.47082543373108</v>
       </c>
       <c r="H232" t="n">
         <v>2527</v>
@@ -7155,7 +7155,7 @@
         <v>1.96800005435944</v>
       </c>
       <c r="G234" t="n">
-        <v>1.61258172988892</v>
+        <v>1.61258184909821</v>
       </c>
       <c r="H234" t="n">
         <v>5088</v>
@@ -7184,7 +7184,7 @@
         <v>1.96700000762939</v>
       </c>
       <c r="G235" t="n">
-        <v>1.61176252365112</v>
+        <v>1.61176240444183</v>
       </c>
       <c r="H235" t="n">
         <v>99</v>
@@ -7300,7 +7300,7 @@
         <v>1.96700000762939</v>
       </c>
       <c r="G239" t="n">
-        <v>1.61176252365112</v>
+        <v>1.61176240444183</v>
       </c>
       <c r="H239" t="n">
         <v>50</v>
@@ -7358,7 +7358,7 @@
         <v>1.84500002861023</v>
       </c>
       <c r="G241" t="n">
-        <v>1.51179563999176</v>
+        <v>1.51179552078247</v>
       </c>
       <c r="H241" t="n">
         <v>3642</v>
@@ -7387,7 +7387,7 @@
         <v>1.89800000190735</v>
       </c>
       <c r="G242" t="n">
-        <v>1.5552237033844</v>
+        <v>1.55522382259369</v>
       </c>
       <c r="H242" t="n">
         <v>6374</v>
@@ -7416,7 +7416,7 @@
         <v>1.89800000190735</v>
       </c>
       <c r="G243" t="n">
-        <v>1.5552237033844</v>
+        <v>1.55522382259369</v>
       </c>
       <c r="H243" t="n">
         <v>3380</v>
@@ -7445,7 +7445,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G244" t="n">
-        <v>1.56505656242371</v>
+        <v>1.56505644321442</v>
       </c>
       <c r="H244" t="n">
         <v>627</v>
@@ -7474,7 +7474,7 @@
         <v>1.90900003910065</v>
       </c>
       <c r="G245" t="n">
-        <v>1.56423723697662</v>
+        <v>1.56423711776733</v>
       </c>
       <c r="H245" t="n">
         <v>250</v>
@@ -7503,7 +7503,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G246" t="n">
-        <v>1.54047453403473</v>
+        <v>1.54047441482544</v>
       </c>
       <c r="H246" t="n">
         <v>430</v>
@@ -7532,7 +7532,7 @@
         <v>1.94400000572205</v>
       </c>
       <c r="G247" t="n">
-        <v>1.59291613101959</v>
+        <v>1.59291625022888</v>
       </c>
       <c r="H247" t="n">
         <v>10</v>
@@ -7561,7 +7561,7 @@
         <v>1.94400000572205</v>
       </c>
       <c r="G248" t="n">
-        <v>1.59291613101959</v>
+        <v>1.59291625022888</v>
       </c>
       <c r="H248" t="n">
         <v>5280</v>
@@ -7706,7 +7706,7 @@
         <v>1.84399998188019</v>
       </c>
       <c r="G253" t="n">
-        <v>1.5109760761261</v>
+        <v>1.51097619533539</v>
       </c>
       <c r="H253" t="n">
         <v>15268</v>
@@ -7764,7 +7764,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G255" t="n">
-        <v>1.51589238643646</v>
+        <v>1.51589250564575</v>
       </c>
       <c r="H255" t="n">
         <v>3734</v>
@@ -7909,7 +7909,7 @@
         <v>1.84200000762939</v>
       </c>
       <c r="G260" t="n">
-        <v>1.50933718681335</v>
+        <v>1.50933730602264</v>
       </c>
       <c r="H260" t="n">
         <v>15155</v>
@@ -7996,7 +7996,7 @@
         <v>1.84200000762939</v>
       </c>
       <c r="G263" t="n">
-        <v>1.50933718681335</v>
+        <v>1.50933730602264</v>
       </c>
       <c r="H263" t="n">
         <v>8077</v>
@@ -8141,7 +8141,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G268" t="n">
-        <v>1.54047453403473</v>
+        <v>1.54047441482544</v>
       </c>
       <c r="H268" t="n">
         <v>27145</v>
@@ -8170,7 +8170,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G269" t="n">
-        <v>1.57325041294098</v>
+        <v>1.57325065135956</v>
       </c>
       <c r="H269" t="n">
         <v>3905</v>
@@ -8199,7 +8199,7 @@
         <v>1.93499994277954</v>
       </c>
       <c r="G270" t="n">
-        <v>1.5855416059494</v>
+        <v>1.58554148674011</v>
       </c>
       <c r="H270" t="n">
         <v>11884</v>
@@ -8257,7 +8257,7 @@
         <v>1.94599997997284</v>
       </c>
       <c r="G272" t="n">
-        <v>1.59455502033234</v>
+        <v>1.59455513954163</v>
       </c>
       <c r="H272" t="n">
         <v>20610</v>
@@ -8286,7 +8286,7 @@
         <v>1.96099996566772</v>
       </c>
       <c r="G273" t="n">
-        <v>1.60684609413147</v>
+        <v>1.60684585571289</v>
       </c>
       <c r="H273" t="n">
         <v>4589</v>
@@ -8344,7 +8344,7 @@
         <v>1.96800005435944</v>
       </c>
       <c r="G275" t="n">
-        <v>1.61258172988892</v>
+        <v>1.61258184909821</v>
       </c>
       <c r="H275" t="n">
         <v>19986</v>
@@ -8431,7 +8431,7 @@
         <v>1.88399994373322</v>
       </c>
       <c r="G278" t="n">
-        <v>1.54375219345093</v>
+        <v>1.54375207424164</v>
       </c>
       <c r="H278" t="n">
         <v>4401</v>
@@ -8692,7 +8692,7 @@
         <v>1.93099999427795</v>
       </c>
       <c r="G287" t="n">
-        <v>1.5822639465332</v>
+        <v>1.58226406574249</v>
       </c>
       <c r="H287" t="n">
         <v>1210</v>
@@ -8750,7 +8750,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G289" t="n">
-        <v>1.54047453403473</v>
+        <v>1.54047441482544</v>
       </c>
       <c r="H289" t="n">
         <v>1385</v>
@@ -8866,7 +8866,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G293" t="n">
-        <v>1.56505656242371</v>
+        <v>1.56505644321442</v>
       </c>
       <c r="H293" t="n">
         <v>3832</v>
@@ -8924,7 +8924,7 @@
         <v>1.88900005817413</v>
       </c>
       <c r="G295" t="n">
-        <v>1.54784905910492</v>
+        <v>1.54784917831421</v>
       </c>
       <c r="H295" t="n">
         <v>658</v>
@@ -8953,7 +8953,7 @@
         <v>1.88900005817413</v>
       </c>
       <c r="G296" t="n">
-        <v>1.54784905910492</v>
+        <v>1.54784917831421</v>
       </c>
       <c r="H296" t="n">
         <v>0</v>
@@ -9040,7 +9040,7 @@
         <v>1.89100003242493</v>
       </c>
       <c r="G299" t="n">
-        <v>1.54948782920837</v>
+        <v>1.54948794841766</v>
       </c>
       <c r="H299" t="n">
         <v>50</v>
@@ -9069,7 +9069,7 @@
         <v>1.87699997425079</v>
       </c>
       <c r="G300" t="n">
-        <v>1.53801620006561</v>
+        <v>1.5380163192749</v>
       </c>
       <c r="H300" t="n">
         <v>1972</v>
@@ -9156,7 +9156,7 @@
         <v>1.89100003242493</v>
       </c>
       <c r="G303" t="n">
-        <v>1.54948782920837</v>
+        <v>1.54948794841766</v>
       </c>
       <c r="H303" t="n">
         <v>4699</v>
@@ -9185,7 +9185,7 @@
         <v>1.875</v>
       </c>
       <c r="G304" t="n">
-        <v>1.53637731075287</v>
+        <v>1.53637742996216</v>
       </c>
       <c r="H304" t="n">
         <v>4192</v>
@@ -9214,7 +9214,7 @@
         <v>1.87899994850159</v>
       </c>
       <c r="G305" t="n">
-        <v>1.53965497016907</v>
+        <v>1.53965508937836</v>
       </c>
       <c r="H305" t="n">
         <v>5851</v>
@@ -9504,7 +9504,7 @@
         <v>2.01799988746643</v>
       </c>
       <c r="G315" t="n">
-        <v>1.65355181694031</v>
+        <v>1.65355169773102</v>
       </c>
       <c r="H315" t="n">
         <v>15632</v>
@@ -9533,7 +9533,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G316" t="n">
-        <v>1.65519058704376</v>
+        <v>1.65519070625305</v>
       </c>
       <c r="H316" t="n">
         <v>11483</v>
@@ -9591,7 +9591,7 @@
         <v>2.29800009727478</v>
       </c>
       <c r="G318" t="n">
-        <v>1.88298439979553</v>
+        <v>1.88298428058624</v>
       </c>
       <c r="H318" t="n">
         <v>94367</v>
@@ -9620,7 +9620,7 @@
         <v>2.22199988365173</v>
       </c>
       <c r="G319" t="n">
-        <v>1.82070970535278</v>
+        <v>1.82070958614349</v>
       </c>
       <c r="H319" t="n">
         <v>37358</v>
@@ -9678,7 +9678,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G321" t="n">
-        <v>1.78629505634308</v>
+        <v>1.78629493713379</v>
       </c>
       <c r="H321" t="n">
         <v>16351</v>
@@ -9707,7 +9707,7 @@
         <v>2.21799993515015</v>
       </c>
       <c r="G322" t="n">
-        <v>1.81743216514587</v>
+        <v>1.81743204593658</v>
       </c>
       <c r="H322" t="n">
         <v>3920</v>
@@ -9736,7 +9736,7 @@
         <v>2.21600008010864</v>
       </c>
       <c r="G323" t="n">
-        <v>1.81579351425171</v>
+        <v>1.815793633461</v>
       </c>
       <c r="H323" t="n">
         <v>40297</v>
@@ -9765,7 +9765,7 @@
         <v>2.17199993133545</v>
       </c>
       <c r="G324" t="n">
-        <v>1.77973985671997</v>
+        <v>1.77973973751068</v>
       </c>
       <c r="H324" t="n">
         <v>11729</v>
@@ -9794,7 +9794,7 @@
         <v>2.29399991035461</v>
       </c>
       <c r="G325" t="n">
-        <v>1.87970662117004</v>
+        <v>1.87970650196075</v>
       </c>
       <c r="H325" t="n">
         <v>82545</v>
@@ -9910,7 +9910,7 @@
         <v>2.2260000705719</v>
       </c>
       <c r="G329" t="n">
-        <v>1.82398736476898</v>
+        <v>1.82398748397827</v>
       </c>
       <c r="H329" t="n">
         <v>4573</v>
@@ -9939,7 +9939,7 @@
         <v>2.21600008010864</v>
       </c>
       <c r="G330" t="n">
-        <v>1.81579351425171</v>
+        <v>1.815793633461</v>
       </c>
       <c r="H330" t="n">
         <v>2603</v>
@@ -10026,7 +10026,7 @@
         <v>2.10800004005432</v>
       </c>
       <c r="G333" t="n">
-        <v>1.72729814052582</v>
+        <v>1.72729802131653</v>
       </c>
       <c r="H333" t="n">
         <v>5276</v>
@@ -10055,7 +10055,7 @@
         <v>2.13199996948242</v>
       </c>
       <c r="G334" t="n">
-        <v>1.74696373939514</v>
+        <v>1.74696362018585</v>
       </c>
       <c r="H334" t="n">
         <v>2476</v>
@@ -10084,7 +10084,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G335" t="n">
-        <v>1.72893691062927</v>
+        <v>1.72893667221069</v>
       </c>
       <c r="H335" t="n">
         <v>3195</v>
@@ -10142,7 +10142,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G337" t="n">
-        <v>1.8026829957962</v>
+        <v>1.80268287658691</v>
       </c>
       <c r="H337" t="n">
         <v>8773</v>
@@ -10171,7 +10171,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G338" t="n">
-        <v>1.8026829957962</v>
+        <v>1.80268287658691</v>
       </c>
       <c r="H338" t="n">
         <v>13339</v>
@@ -10200,7 +10200,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G339" t="n">
-        <v>1.83545875549316</v>
+        <v>1.83545887470245</v>
       </c>
       <c r="H339" t="n">
         <v>10440</v>
@@ -10287,7 +10287,7 @@
         <v>2.20799994468689</v>
       </c>
       <c r="G342" t="n">
-        <v>1.80923819541931</v>
+        <v>1.80923795700073</v>
       </c>
       <c r="H342" t="n">
         <v>10083</v>
@@ -10345,7 +10345,7 @@
         <v>2.2720000743866</v>
       </c>
       <c r="G344" t="n">
-        <v>1.86167967319489</v>
+        <v>1.86168015003204</v>
       </c>
       <c r="H344" t="n">
         <v>19071</v>
@@ -10374,7 +10374,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G345" t="n">
-        <v>1.83545875549316</v>
+        <v>1.83545887470245</v>
       </c>
       <c r="H345" t="n">
         <v>20200</v>
@@ -10432,7 +10432,7 @@
         <v>2.26799988746643</v>
       </c>
       <c r="G347" t="n">
-        <v>1.85840201377869</v>
+        <v>1.85840213298798</v>
       </c>
       <c r="H347" t="n">
         <v>10030</v>
@@ -10519,7 +10519,7 @@
         <v>2.31800007820129</v>
       </c>
       <c r="G350" t="n">
-        <v>1.89937245845795</v>
+        <v>1.89937257766724</v>
       </c>
       <c r="H350" t="n">
         <v>4160</v>
@@ -10548,7 +10548,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G351" t="n">
-        <v>1.91739916801453</v>
+        <v>1.91739904880524</v>
       </c>
       <c r="H351" t="n">
         <v>6240</v>
@@ -10635,7 +10635,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G354" t="n">
-        <v>1.86823511123657</v>
+        <v>1.86823523044586</v>
       </c>
       <c r="H354" t="n">
         <v>9851</v>
@@ -10664,7 +10664,7 @@
         <v>2.24600005149841</v>
       </c>
       <c r="G355" t="n">
-        <v>1.92479634284973</v>
+        <v>1.92479622364044</v>
       </c>
       <c r="H355" t="n">
         <v>11951</v>
@@ -10722,7 +10722,7 @@
         <v>2.26200008392334</v>
       </c>
       <c r="G357" t="n">
-        <v>1.93850815296173</v>
+        <v>1.93850839138031</v>
       </c>
       <c r="H357" t="n">
         <v>47650</v>
@@ -10838,7 +10838,7 @@
         <v>2.26600003242493</v>
       </c>
       <c r="G361" t="n">
-        <v>1.94193613529205</v>
+        <v>1.94193625450134</v>
       </c>
       <c r="H361" t="n">
         <v>10334</v>
@@ -10867,7 +10867,7 @@
         <v>2.26799988746643</v>
       </c>
       <c r="G362" t="n">
-        <v>1.94364988803864</v>
+        <v>1.94365000724792</v>
       </c>
       <c r="H362" t="n">
         <v>9505</v>
@@ -11128,7 +11128,7 @@
         <v>2.25600004196167</v>
       </c>
       <c r="G371" t="n">
-        <v>1.93336629867554</v>
+        <v>1.93336617946625</v>
       </c>
       <c r="H371" t="n">
         <v>4289</v>
@@ -11157,7 +11157,7 @@
         <v>2.22399997711182</v>
       </c>
       <c r="G372" t="n">
-        <v>1.90594244003296</v>
+        <v>1.90594267845154</v>
       </c>
       <c r="H372" t="n">
         <v>8910</v>
@@ -11186,7 +11186,7 @@
         <v>2.22399997711182</v>
       </c>
       <c r="G373" t="n">
-        <v>1.90594244003296</v>
+        <v>1.90594267845154</v>
       </c>
       <c r="H373" t="n">
         <v>0</v>
@@ -11302,7 +11302,7 @@
         <v>2.21799993515015</v>
       </c>
       <c r="G377" t="n">
-        <v>1.90080058574677</v>
+        <v>1.90080046653748</v>
       </c>
       <c r="H377" t="n">
         <v>500</v>
@@ -11331,7 +11331,7 @@
         <v>2.23399996757507</v>
       </c>
       <c r="G378" t="n">
-        <v>1.91451227664948</v>
+        <v>1.91451251506805</v>
       </c>
       <c r="H378" t="n">
         <v>12050</v>
@@ -11360,7 +11360,7 @@
         <v>2.20199990272522</v>
       </c>
       <c r="G379" t="n">
-        <v>1.88708853721619</v>
+        <v>1.88708877563477</v>
       </c>
       <c r="H379" t="n">
         <v>17691</v>
@@ -11418,7 +11418,7 @@
         <v>2.23799991607666</v>
       </c>
       <c r="G381" t="n">
-        <v>1.9179402589798</v>
+        <v>1.91794049739838</v>
       </c>
       <c r="H381" t="n">
         <v>6850</v>
@@ -11476,7 +11476,7 @@
         <v>2.18199992179871</v>
       </c>
       <c r="G383" t="n">
-        <v>1.86994898319244</v>
+        <v>1.86994886398315</v>
       </c>
       <c r="H383" t="n">
         <v>1040</v>
@@ -11505,7 +11505,7 @@
         <v>2.2039999961853</v>
       </c>
       <c r="G384" t="n">
-        <v>1.88880300521851</v>
+        <v>1.88880288600922</v>
       </c>
       <c r="H384" t="n">
         <v>6700</v>
@@ -11534,7 +11534,7 @@
         <v>2.2279999256134</v>
       </c>
       <c r="G385" t="n">
-        <v>1.90937042236328</v>
+        <v>1.90937054157257</v>
       </c>
       <c r="H385" t="n">
         <v>9416</v>
@@ -11563,7 +11563,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G386" t="n">
-        <v>1.90251469612122</v>
+        <v>1.90251457691193</v>
       </c>
       <c r="H386" t="n">
         <v>12328</v>
@@ -11679,7 +11679,7 @@
         <v>2.23399996757507</v>
       </c>
       <c r="G390" t="n">
-        <v>1.91451227664948</v>
+        <v>1.91451251506805</v>
       </c>
       <c r="H390" t="n">
         <v>7104</v>
@@ -11708,7 +11708,7 @@
         <v>2.23799991607666</v>
       </c>
       <c r="G391" t="n">
-        <v>1.9179402589798</v>
+        <v>1.91794049739838</v>
       </c>
       <c r="H391" t="n">
         <v>125</v>
@@ -11737,7 +11737,7 @@
         <v>2.25600004196167</v>
       </c>
       <c r="G392" t="n">
-        <v>1.93336629867554</v>
+        <v>1.93336617946625</v>
       </c>
       <c r="H392" t="n">
         <v>4625</v>
@@ -12114,7 +12114,7 @@
         <v>2.42600011825562</v>
       </c>
       <c r="G405" t="n">
-        <v>2.07905411720276</v>
+        <v>2.07905435562134</v>
       </c>
       <c r="H405" t="n">
         <v>6400</v>
@@ -12143,7 +12143,7 @@
         <v>2.42799997329712</v>
       </c>
       <c r="G406" t="n">
-        <v>2.08076858520508</v>
+        <v>2.0807683467865</v>
       </c>
       <c r="H406" t="n">
         <v>5713</v>
@@ -12172,7 +12172,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G407" t="n">
-        <v>2.06534242630005</v>
+        <v>2.06534266471863</v>
       </c>
       <c r="H407" t="n">
         <v>8713</v>
@@ -12201,7 +12201,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G408" t="n">
-        <v>2.06534242630005</v>
+        <v>2.06534266471863</v>
       </c>
       <c r="H408" t="n">
         <v>0</v>
@@ -12259,7 +12259,7 @@
         <v>2.41799998283386</v>
       </c>
       <c r="G410" t="n">
-        <v>2.07219815254211</v>
+        <v>2.07219839096069</v>
       </c>
       <c r="H410" t="n">
         <v>1517</v>
@@ -12288,7 +12288,7 @@
         <v>2.41799998283386</v>
       </c>
       <c r="G411" t="n">
-        <v>2.07219815254211</v>
+        <v>2.07219839096069</v>
       </c>
       <c r="H411" t="n">
         <v>22152</v>
@@ -12520,7 +12520,7 @@
         <v>2.46799993515015</v>
       </c>
       <c r="G419" t="n">
-        <v>2.11504793167114</v>
+        <v>2.11504769325256</v>
       </c>
       <c r="H419" t="n">
         <v>13804</v>
@@ -12549,7 +12549,7 @@
         <v>2.46799993515015</v>
       </c>
       <c r="G420" t="n">
-        <v>2.11504793167114</v>
+        <v>2.11504769325256</v>
       </c>
       <c r="H420" t="n">
         <v>0</v>
@@ -12607,7 +12607,7 @@
         <v>2.44799995422363</v>
       </c>
       <c r="G422" t="n">
-        <v>2.09790802001953</v>
+        <v>2.09790778160095</v>
       </c>
       <c r="H422" t="n">
         <v>3874</v>
@@ -12723,7 +12723,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G426" t="n">
-        <v>2.08248233795166</v>
+        <v>2.08248209953308</v>
       </c>
       <c r="H426" t="n">
         <v>2302</v>
@@ -12752,7 +12752,7 @@
         <v>2.46799993515015</v>
       </c>
       <c r="G427" t="n">
-        <v>2.11504793167114</v>
+        <v>2.11504769325256</v>
       </c>
       <c r="H427" t="n">
         <v>15505</v>
@@ -12781,7 +12781,7 @@
         <v>2.41199994087219</v>
       </c>
       <c r="G428" t="n">
-        <v>2.06705641746521</v>
+        <v>2.06705665588379</v>
       </c>
       <c r="H428" t="n">
         <v>650</v>
@@ -12839,7 +12839,7 @@
         <v>2.45799994468689</v>
       </c>
       <c r="G430" t="n">
-        <v>2.10647773742676</v>
+        <v>2.10647797584534</v>
       </c>
       <c r="H430" t="n">
         <v>4919</v>
@@ -12868,7 +12868,7 @@
         <v>2.45799994468689</v>
       </c>
       <c r="G431" t="n">
-        <v>2.10647773742676</v>
+        <v>2.10647797584534</v>
       </c>
       <c r="H431" t="n">
         <v>0</v>
@@ -13042,7 +13042,7 @@
         <v>2.44799995422363</v>
       </c>
       <c r="G437" t="n">
-        <v>2.09790802001953</v>
+        <v>2.09790778160095</v>
       </c>
       <c r="H437" t="n">
         <v>5750</v>
@@ -13071,7 +13071,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G438" t="n">
-        <v>2.08248233795166</v>
+        <v>2.08248209953308</v>
       </c>
       <c r="H438" t="n">
         <v>13950</v>
@@ -13100,7 +13100,7 @@
         <v>2.44799995422363</v>
       </c>
       <c r="G439" t="n">
-        <v>2.09790802001953</v>
+        <v>2.09790778160095</v>
       </c>
       <c r="H439" t="n">
         <v>10563</v>
@@ -13129,7 +13129,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G440" t="n">
-        <v>2.17675113677979</v>
+        <v>2.17675089836121</v>
       </c>
       <c r="H440" t="n">
         <v>17588</v>
@@ -13187,7 +13187,7 @@
         <v>2.48799991607666</v>
       </c>
       <c r="G442" t="n">
-        <v>2.1321873664856</v>
+        <v>2.13218760490417</v>
       </c>
       <c r="H442" t="n">
         <v>1580</v>
@@ -13245,7 +13245,7 @@
         <v>2.48799991607666</v>
       </c>
       <c r="G444" t="n">
-        <v>2.1321873664856</v>
+        <v>2.13218760490417</v>
       </c>
       <c r="H444" t="n">
         <v>5230</v>
@@ -13303,7 +13303,7 @@
         <v>2.47199988365173</v>
       </c>
       <c r="G446" t="n">
-        <v>2.11847567558289</v>
+        <v>2.11847543716431</v>
       </c>
       <c r="H446" t="n">
         <v>7321</v>
@@ -13361,7 +13361,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G448" t="n">
-        <v>2.09105229377747</v>
+        <v>2.09105205535889</v>
       </c>
       <c r="H448" t="n">
         <v>6572</v>
@@ -13477,7 +13477,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G452" t="n">
-        <v>2.09105229377747</v>
+        <v>2.09105205535889</v>
       </c>
       <c r="H452" t="n">
         <v>5134</v>
@@ -13506,7 +13506,7 @@
         <v>2.46799993515015</v>
       </c>
       <c r="G453" t="n">
-        <v>2.11504793167114</v>
+        <v>2.11504769325256</v>
       </c>
       <c r="H453" t="n">
         <v>3583</v>
@@ -13651,7 +13651,7 @@
         <v>2.48799991607666</v>
       </c>
       <c r="G458" t="n">
-        <v>2.1321873664856</v>
+        <v>2.13218760490417</v>
       </c>
       <c r="H458" t="n">
         <v>220</v>
@@ -13767,7 +13767,7 @@
         <v>2.49799990653992</v>
       </c>
       <c r="G462" t="n">
-        <v>2.14075708389282</v>
+        <v>2.1407573223114</v>
       </c>
       <c r="H462" t="n">
         <v>6700</v>
@@ -13854,7 +13854,7 @@
         <v>2.50799989700317</v>
       </c>
       <c r="G465" t="n">
-        <v>2.14932727813721</v>
+        <v>2.14932703971863</v>
       </c>
       <c r="H465" t="n">
         <v>747</v>
@@ -13883,7 +13883,7 @@
         <v>2.49600005149841</v>
       </c>
       <c r="G466" t="n">
-        <v>2.13904356956482</v>
+        <v>2.13904333114624</v>
       </c>
       <c r="H466" t="n">
         <v>763</v>
@@ -13912,7 +13912,7 @@
         <v>2.49600005149841</v>
       </c>
       <c r="G467" t="n">
-        <v>2.13904356956482</v>
+        <v>2.13904333114624</v>
       </c>
       <c r="H467" t="n">
         <v>1434</v>
@@ -14028,7 +14028,7 @@
         <v>2.49799990653992</v>
       </c>
       <c r="G471" t="n">
-        <v>2.14075708389282</v>
+        <v>2.1407573223114</v>
       </c>
       <c r="H471" t="n">
         <v>150</v>
@@ -14318,7 +14318,7 @@
         <v>2.37199997901917</v>
       </c>
       <c r="G481" t="n">
-        <v>2.03277707099915</v>
+        <v>2.03277683258057</v>
       </c>
       <c r="H481" t="n">
         <v>6951</v>
@@ -14347,7 +14347,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G482" t="n">
-        <v>2.0482029914856</v>
+        <v>2.04820275306702</v>
       </c>
       <c r="H482" t="n">
         <v>5071</v>
@@ -14376,7 +14376,7 @@
         <v>2.42600011825562</v>
       </c>
       <c r="G483" t="n">
-        <v>2.07905411720276</v>
+        <v>2.07905435562134</v>
       </c>
       <c r="H483" t="n">
         <v>2813</v>
@@ -14405,7 +14405,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G484" t="n">
-        <v>2.0482029914856</v>
+        <v>2.04820275306702</v>
       </c>
       <c r="H484" t="n">
         <v>355</v>
@@ -14463,7 +14463,7 @@
         <v>2.37199997901917</v>
       </c>
       <c r="G486" t="n">
-        <v>2.03277707099915</v>
+        <v>2.03277683258057</v>
       </c>
       <c r="H486" t="n">
         <v>1218</v>
@@ -14492,7 +14492,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G487" t="n">
-        <v>2.06534242630005</v>
+        <v>2.06534266471863</v>
       </c>
       <c r="H487" t="n">
         <v>3267</v>
@@ -14521,7 +14521,7 @@
         <v>2.39199995994568</v>
       </c>
       <c r="G488" t="n">
-        <v>2.04991674423218</v>
+        <v>2.0499165058136</v>
       </c>
       <c r="H488" t="n">
         <v>1156</v>
@@ -14550,7 +14550,7 @@
         <v>2.49799990653992</v>
       </c>
       <c r="G489" t="n">
-        <v>2.14075708389282</v>
+        <v>2.1407573223114</v>
       </c>
       <c r="H489" t="n">
         <v>2763</v>
@@ -14579,7 +14579,7 @@
         <v>2.49600005149841</v>
       </c>
       <c r="G490" t="n">
-        <v>2.13904356956482</v>
+        <v>2.13904333114624</v>
       </c>
       <c r="H490" t="n">
         <v>1802</v>
@@ -14608,7 +14608,7 @@
         <v>2.44799995422363</v>
       </c>
       <c r="G491" t="n">
-        <v>2.09790802001953</v>
+        <v>2.09790778160095</v>
       </c>
       <c r="H491" t="n">
         <v>2342</v>
@@ -14695,7 +14695,7 @@
         <v>2.48399996757507</v>
       </c>
       <c r="G494" t="n">
-        <v>2.12875962257385</v>
+        <v>2.12875938415527</v>
       </c>
       <c r="H494" t="n">
         <v>150</v>
@@ -14869,7 +14869,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G500" t="n">
-        <v>2.08248233795166</v>
+        <v>2.08248209953308</v>
       </c>
       <c r="H500" t="n">
         <v>6624</v>
@@ -14898,7 +14898,7 @@
         <v>2.43600010871887</v>
       </c>
       <c r="G501" t="n">
-        <v>2.08762431144714</v>
+        <v>2.08762407302856</v>
       </c>
       <c r="H501" t="n">
         <v>2450</v>
@@ -15014,7 +15014,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G505" t="n">
-        <v>2.08248233795166</v>
+        <v>2.08248209953308</v>
       </c>
       <c r="H505" t="n">
         <v>608</v>
@@ -15101,7 +15101,7 @@
         <v>2.44799995422363</v>
       </c>
       <c r="G508" t="n">
-        <v>2.09790802001953</v>
+        <v>2.09790778160095</v>
       </c>
       <c r="H508" t="n">
         <v>2286</v>
@@ -15130,7 +15130,7 @@
         <v>2.44799995422363</v>
       </c>
       <c r="G509" t="n">
-        <v>2.09790802001953</v>
+        <v>2.09790778160095</v>
       </c>
       <c r="H509" t="n">
         <v>0</v>
@@ -15333,7 +15333,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G516" t="n">
-        <v>2.08248233795166</v>
+        <v>2.08248209953308</v>
       </c>
       <c r="H516" t="n">
         <v>1125</v>
@@ -15362,7 +15362,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G517" t="n">
-        <v>2.09105229377747</v>
+        <v>2.09105205535889</v>
       </c>
       <c r="H517" t="n">
         <v>5717</v>
@@ -15391,7 +15391,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G518" t="n">
-        <v>2.09105229377747</v>
+        <v>2.09105205535889</v>
       </c>
       <c r="H518" t="n">
         <v>10837</v>
@@ -15420,7 +15420,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G519" t="n">
-        <v>2.08248233795166</v>
+        <v>2.08248209953308</v>
       </c>
       <c r="H519" t="n">
         <v>8541</v>
@@ -15449,7 +15449,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G520" t="n">
-        <v>2.08248233795166</v>
+        <v>2.08248209953308</v>
       </c>
       <c r="H520" t="n">
         <v>321</v>
@@ -15913,7 +15913,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G536" t="n">
-        <v>2.0482029914856</v>
+        <v>2.04820275306702</v>
       </c>
       <c r="H536" t="n">
         <v>1440</v>
@@ -16058,7 +16058,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G541" t="n">
-        <v>2.09105229377747</v>
+        <v>2.09105205535889</v>
       </c>
       <c r="H541" t="n">
         <v>6273</v>
@@ -16087,7 +16087,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G542" t="n">
-        <v>2.09105229377747</v>
+        <v>2.09105205535889</v>
       </c>
       <c r="H542" t="n">
         <v>0</v>
@@ -16232,7 +16232,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G547" t="n">
-        <v>2.08248233795166</v>
+        <v>2.08248209953308</v>
       </c>
       <c r="H547" t="n">
         <v>3430</v>
@@ -16261,7 +16261,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G548" t="n">
-        <v>2.0482029914856</v>
+        <v>2.04820275306702</v>
       </c>
       <c r="H548" t="n">
         <v>110</v>
@@ -16319,7 +16319,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G550" t="n">
-        <v>2.08248233795166</v>
+        <v>2.08248209953308</v>
       </c>
       <c r="H550" t="n">
         <v>678</v>
@@ -16406,7 +16406,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G553" t="n">
-        <v>2.08248233795166</v>
+        <v>2.08248209953308</v>
       </c>
       <c r="H553" t="n">
         <v>290</v>
@@ -16464,7 +16464,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G555" t="n">
-        <v>2.06534242630005</v>
+        <v>2.06534266471863</v>
       </c>
       <c r="H555" t="n">
         <v>1952</v>
@@ -16580,7 +16580,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G559" t="n">
-        <v>2.06534242630005</v>
+        <v>2.06534266471863</v>
       </c>
       <c r="H559" t="n">
         <v>459</v>
@@ -16609,7 +16609,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G560" t="n">
-        <v>2.06534242630005</v>
+        <v>2.06534266471863</v>
       </c>
       <c r="H560" t="n">
         <v>2100</v>
@@ -16638,7 +16638,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G561" t="n">
-        <v>2.09105229377747</v>
+        <v>2.09105205535889</v>
       </c>
       <c r="H561" t="n">
         <v>8100</v>
@@ -16667,7 +16667,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G562" t="n">
-        <v>2.08248233795166</v>
+        <v>2.08248209953308</v>
       </c>
       <c r="H562" t="n">
         <v>10</v>
@@ -16696,7 +16696,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G563" t="n">
-        <v>2.08248233795166</v>
+        <v>2.08248209953308</v>
       </c>
       <c r="H563" t="n">
         <v>0</v>
@@ -16957,7 +16957,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G572" t="n">
-        <v>2.09105229377747</v>
+        <v>2.09105205535889</v>
       </c>
       <c r="H572" t="n">
         <v>2665</v>
@@ -16986,7 +16986,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G573" t="n">
-        <v>2.09105229377747</v>
+        <v>2.09105205535889</v>
       </c>
       <c r="H573" t="n">
         <v>2589</v>
@@ -17247,7 +17247,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G582" t="n">
-        <v>2.1681809425354</v>
+        <v>2.16818118095398</v>
       </c>
       <c r="H582" t="n">
         <v>1455</v>
@@ -17276,7 +17276,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G583" t="n">
-        <v>2.1681809425354</v>
+        <v>2.16818118095398</v>
       </c>
       <c r="H583" t="n">
         <v>2779</v>
@@ -17363,7 +17363,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G586" t="n">
-        <v>2.1681809425354</v>
+        <v>2.16818118095398</v>
       </c>
       <c r="H586" t="n">
         <v>6585</v>
@@ -17479,7 +17479,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G590" t="n">
-        <v>2.17675113677979</v>
+        <v>2.17675089836121</v>
       </c>
       <c r="H590" t="n">
         <v>47108</v>
@@ -17508,7 +17508,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G591" t="n">
-        <v>2.18532061576843</v>
+        <v>2.18532085418701</v>
       </c>
       <c r="H591" t="n">
         <v>11111</v>
@@ -17624,7 +17624,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G595" t="n">
-        <v>2.32243895530701</v>
+        <v>2.32243919372559</v>
       </c>
       <c r="H595" t="n">
         <v>49282</v>
@@ -17653,7 +17653,7 @@
         <v>2.75</v>
       </c>
       <c r="G596" t="n">
-        <v>2.35671854019165</v>
+        <v>2.35671830177307</v>
       </c>
       <c r="H596" t="n">
         <v>31138</v>
@@ -17682,7 +17682,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G597" t="n">
-        <v>2.44241738319397</v>
+        <v>2.44241714477539</v>
       </c>
       <c r="H597" t="n">
         <v>71018</v>
@@ -17711,7 +17711,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G598" t="n">
-        <v>2.49383687973022</v>
+        <v>2.49383664131165</v>
       </c>
       <c r="H598" t="n">
         <v>37011</v>
@@ -17769,7 +17769,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G600" t="n">
-        <v>2.47669720649719</v>
+        <v>2.47669696807861</v>
       </c>
       <c r="H600" t="n">
         <v>11231</v>
@@ -17856,7 +17856,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G603" t="n">
-        <v>2.53668618202209</v>
+        <v>2.53668642044067</v>
       </c>
       <c r="H603" t="n">
         <v>32941</v>
@@ -17885,7 +17885,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G604" t="n">
-        <v>2.57953548431396</v>
+        <v>2.57953572273254</v>
       </c>
       <c r="H604" t="n">
         <v>152006</v>
@@ -18001,7 +18001,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G608" t="n">
-        <v>2.63447308540344</v>
+        <v>2.63447332382202</v>
       </c>
       <c r="H608" t="n">
         <v>30164</v>
@@ -18088,7 +18088,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G611" t="n">
-        <v>2.61655163764954</v>
+        <v>2.61655139923096</v>
       </c>
       <c r="H611" t="n">
         <v>13758</v>
@@ -18465,7 +18465,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G624" t="n">
-        <v>2.57174730300903</v>
+        <v>2.57174754142761</v>
       </c>
       <c r="H624" t="n">
         <v>2231</v>
@@ -18494,7 +18494,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G625" t="n">
-        <v>2.57174730300903</v>
+        <v>2.57174754142761</v>
       </c>
       <c r="H625" t="n">
         <v>3450</v>
@@ -18668,7 +18668,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G631" t="n">
-        <v>2.53590440750122</v>
+        <v>2.53590416908264</v>
       </c>
       <c r="H631" t="n">
         <v>519</v>
@@ -18697,7 +18697,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G632" t="n">
-        <v>2.4911003112793</v>
+        <v>2.49110054969788</v>
       </c>
       <c r="H632" t="n">
         <v>100</v>
@@ -18900,7 +18900,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G639" t="n">
-        <v>2.53590440750122</v>
+        <v>2.53590416908264</v>
       </c>
       <c r="H639" t="n">
         <v>2002</v>
@@ -18929,7 +18929,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G640" t="n">
-        <v>2.53590440750122</v>
+        <v>2.53590416908264</v>
       </c>
       <c r="H640" t="n">
         <v>1371</v>
@@ -18958,7 +18958,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G641" t="n">
-        <v>2.53590440750122</v>
+        <v>2.53590416908264</v>
       </c>
       <c r="H641" t="n">
         <v>230</v>
@@ -18987,7 +18987,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G642" t="n">
-        <v>2.53590440750122</v>
+        <v>2.53590416908264</v>
       </c>
       <c r="H642" t="n">
         <v>418</v>
@@ -19016,7 +19016,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G643" t="n">
-        <v>2.53590440750122</v>
+        <v>2.53590416908264</v>
       </c>
       <c r="H643" t="n">
         <v>0</v>
@@ -19074,7 +19074,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G645" t="n">
-        <v>2.53590440750122</v>
+        <v>2.53590416908264</v>
       </c>
       <c r="H645" t="n">
         <v>2500</v>
@@ -19451,7 +19451,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G658" t="n">
-        <v>2.77784562110901</v>
+        <v>2.77784585952759</v>
       </c>
       <c r="H658" t="n">
         <v>16052</v>
@@ -19480,7 +19480,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G659" t="n">
-        <v>2.77784562110901</v>
+        <v>2.77784585952759</v>
       </c>
       <c r="H659" t="n">
         <v>15393</v>
@@ -19654,7 +19654,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G665" t="n">
-        <v>2.76888489723206</v>
+        <v>2.76888513565063</v>
       </c>
       <c r="H665" t="n">
         <v>3767</v>
@@ -19683,7 +19683,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G666" t="n">
-        <v>2.71512007713318</v>
+        <v>2.71512031555176</v>
       </c>
       <c r="H666" t="n">
         <v>9512</v>
@@ -19712,7 +19712,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G667" t="n">
-        <v>2.75096344947815</v>
+        <v>2.75096321105957</v>
       </c>
       <c r="H667" t="n">
         <v>2365</v>
@@ -19741,7 +19741,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G668" t="n">
-        <v>2.67031645774841</v>
+        <v>2.67031621932983</v>
       </c>
       <c r="H668" t="n">
         <v>16566</v>
@@ -19770,7 +19770,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G669" t="n">
-        <v>2.63447308540344</v>
+        <v>2.63447332382202</v>
       </c>
       <c r="H669" t="n">
         <v>764</v>
@@ -19828,7 +19828,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G671" t="n">
-        <v>2.75096344947815</v>
+        <v>2.75096321105957</v>
       </c>
       <c r="H671" t="n">
         <v>1370</v>
@@ -19915,7 +19915,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G674" t="n">
-        <v>2.65239453315735</v>
+        <v>2.65239477157593</v>
       </c>
       <c r="H674" t="n">
         <v>1869</v>
@@ -19944,7 +19944,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G675" t="n">
-        <v>2.65239453315735</v>
+        <v>2.65239477157593</v>
       </c>
       <c r="H675" t="n">
         <v>0</v>
@@ -20002,7 +20002,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G677" t="n">
-        <v>2.67031645774841</v>
+        <v>2.67031621932983</v>
       </c>
       <c r="H677" t="n">
         <v>1645</v>
@@ -20031,7 +20031,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G678" t="n">
-        <v>2.67031645774841</v>
+        <v>2.67031621932983</v>
       </c>
       <c r="H678" t="n">
         <v>0</v>
@@ -20147,7 +20147,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G682" t="n">
-        <v>2.75096344947815</v>
+        <v>2.75096321105957</v>
       </c>
       <c r="H682" t="n">
         <v>10777</v>
@@ -20176,7 +20176,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G683" t="n">
-        <v>2.73304200172424</v>
+        <v>2.73304176330566</v>
       </c>
       <c r="H683" t="n">
         <v>1575</v>
@@ -20292,7 +20292,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G687" t="n">
-        <v>2.71512007713318</v>
+        <v>2.71512031555176</v>
       </c>
       <c r="H687" t="n">
         <v>2971</v>
@@ -20321,7 +20321,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G688" t="n">
-        <v>2.75096344947815</v>
+        <v>2.75096321105957</v>
       </c>
       <c r="H688" t="n">
         <v>5155</v>
@@ -20350,7 +20350,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G689" t="n">
-        <v>2.71512007713318</v>
+        <v>2.71512031555176</v>
       </c>
       <c r="H689" t="n">
         <v>7369</v>
@@ -20379,7 +20379,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G690" t="n">
-        <v>2.69719862937927</v>
+        <v>2.69719886779785</v>
       </c>
       <c r="H690" t="n">
         <v>5352</v>
@@ -20408,7 +20408,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G691" t="n">
-        <v>2.67927718162537</v>
+        <v>2.67927694320679</v>
       </c>
       <c r="H691" t="n">
         <v>996</v>
@@ -20553,7 +20553,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G696" t="n">
-        <v>2.73304200172424</v>
+        <v>2.73304176330566</v>
       </c>
       <c r="H696" t="n">
         <v>20211</v>
@@ -20582,7 +20582,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G697" t="n">
-        <v>2.75096344947815</v>
+        <v>2.75096321105957</v>
       </c>
       <c r="H697" t="n">
         <v>927</v>
@@ -20669,7 +20669,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G700" t="n">
-        <v>2.75096344947815</v>
+        <v>2.75096321105957</v>
       </c>
       <c r="H700" t="n">
         <v>3068</v>
@@ -20698,7 +20698,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G701" t="n">
-        <v>2.75096344947815</v>
+        <v>2.75096321105957</v>
       </c>
       <c r="H701" t="n">
         <v>1928</v>
@@ -20727,7 +20727,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G702" t="n">
-        <v>2.75096344947815</v>
+        <v>2.75096321105957</v>
       </c>
       <c r="H702" t="n">
         <v>0</v>
@@ -20785,7 +20785,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G704" t="n">
-        <v>2.65239453315735</v>
+        <v>2.65239477157593</v>
       </c>
       <c r="H704" t="n">
         <v>4663</v>
@@ -20814,7 +20814,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G705" t="n">
-        <v>2.69719862937927</v>
+        <v>2.69719886779785</v>
       </c>
       <c r="H705" t="n">
         <v>193</v>
@@ -20843,7 +20843,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G706" t="n">
-        <v>2.67927718162537</v>
+        <v>2.67927694320679</v>
       </c>
       <c r="H706" t="n">
         <v>6101</v>
@@ -20901,7 +20901,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G708" t="n">
-        <v>2.63447308540344</v>
+        <v>2.63447332382202</v>
       </c>
       <c r="H708" t="n">
         <v>4328</v>
@@ -20930,7 +20930,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G709" t="n">
-        <v>2.62551236152649</v>
+        <v>2.62551259994507</v>
       </c>
       <c r="H709" t="n">
         <v>1121</v>
@@ -21046,7 +21046,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G713" t="n">
-        <v>2.61655163764954</v>
+        <v>2.61655139923096</v>
       </c>
       <c r="H713" t="n">
         <v>1</v>
@@ -21191,7 +21191,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G718" t="n">
-        <v>2.57174730300903</v>
+        <v>2.57174754142761</v>
       </c>
       <c r="H718" t="n">
         <v>1700</v>
@@ -21249,7 +21249,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G720" t="n">
-        <v>2.61655163764954</v>
+        <v>2.61655139923096</v>
       </c>
       <c r="H720" t="n">
         <v>1330</v>
@@ -21278,7 +21278,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G721" t="n">
-        <v>2.61655163764954</v>
+        <v>2.61655139923096</v>
       </c>
       <c r="H721" t="n">
         <v>2</v>
@@ -21423,7 +21423,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G726" t="n">
-        <v>2.62551236152649</v>
+        <v>2.62551259994507</v>
       </c>
       <c r="H726" t="n">
         <v>4198</v>
@@ -21452,7 +21452,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G727" t="n">
-        <v>2.61655163764954</v>
+        <v>2.61655139923096</v>
       </c>
       <c r="H727" t="n">
         <v>3600</v>
@@ -21481,7 +21481,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G728" t="n">
-        <v>2.61655163764954</v>
+        <v>2.61655139923096</v>
       </c>
       <c r="H728" t="n">
         <v>343</v>
@@ -21510,7 +21510,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G729" t="n">
-        <v>2.61655163764954</v>
+        <v>2.61655139923096</v>
       </c>
       <c r="H729" t="n">
         <v>0</v>
@@ -21539,7 +21539,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G730" t="n">
-        <v>2.60759091377258</v>
+        <v>2.607590675354</v>
       </c>
       <c r="H730" t="n">
         <v>5732</v>
@@ -21568,7 +21568,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G731" t="n">
-        <v>2.61655163764954</v>
+        <v>2.61655139923096</v>
       </c>
       <c r="H731" t="n">
         <v>3102</v>
@@ -21771,7 +21771,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G738" t="n">
-        <v>2.57174730300903</v>
+        <v>2.57174754142761</v>
       </c>
       <c r="H738" t="n">
         <v>2354</v>
@@ -22003,7 +22003,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G746" t="n">
-        <v>2.41941428184509</v>
+        <v>2.41941404342651</v>
       </c>
       <c r="H746" t="n">
         <v>10198</v>
@@ -22061,7 +22061,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G748" t="n">
-        <v>2.57174730300903</v>
+        <v>2.57174754142761</v>
       </c>
       <c r="H748" t="n">
         <v>2700</v>
@@ -22119,7 +22119,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G750" t="n">
-        <v>2.57174730300903</v>
+        <v>2.57174754142761</v>
       </c>
       <c r="H750" t="n">
         <v>1555</v>
@@ -22148,7 +22148,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G751" t="n">
-        <v>2.57174730300903</v>
+        <v>2.57174754142761</v>
       </c>
       <c r="H751" t="n">
         <v>0</v>
@@ -22177,7 +22177,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G752" t="n">
-        <v>2.57174730300903</v>
+        <v>2.57174754142761</v>
       </c>
       <c r="H752" t="n">
         <v>0</v>
@@ -22293,7 +22293,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G756" t="n">
-        <v>2.53590440750122</v>
+        <v>2.53590416908264</v>
       </c>
       <c r="H756" t="n">
         <v>50</v>
@@ -22322,7 +22322,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G757" t="n">
-        <v>2.53590440750122</v>
+        <v>2.53590416908264</v>
       </c>
       <c r="H757" t="n">
         <v>0</v>
@@ -22351,7 +22351,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G758" t="n">
-        <v>2.53590440750122</v>
+        <v>2.53590416908264</v>
       </c>
       <c r="H758" t="n">
         <v>0</v>
@@ -22496,7 +22496,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G763" t="n">
-        <v>2.53590440750122</v>
+        <v>2.53590416908264</v>
       </c>
       <c r="H763" t="n">
         <v>1110</v>
@@ -22525,7 +22525,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G764" t="n">
-        <v>2.53590440750122</v>
+        <v>2.53590416908264</v>
       </c>
       <c r="H764" t="n">
         <v>2491</v>
@@ -22554,7 +22554,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G765" t="n">
-        <v>2.60759091377258</v>
+        <v>2.607590675354</v>
       </c>
       <c r="H765" t="n">
         <v>2167</v>
@@ -22583,7 +22583,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G766" t="n">
-        <v>2.63447308540344</v>
+        <v>2.63447332382202</v>
       </c>
       <c r="H766" t="n">
         <v>1525</v>
@@ -22612,7 +22612,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G767" t="n">
-        <v>2.67031645774841</v>
+        <v>2.67031621932983</v>
       </c>
       <c r="H767" t="n">
         <v>1992</v>
@@ -22670,7 +22670,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G769" t="n">
-        <v>2.67031645774841</v>
+        <v>2.67031621932983</v>
       </c>
       <c r="H769" t="n">
         <v>2001</v>
@@ -22699,7 +22699,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G770" t="n">
-        <v>2.69719862937927</v>
+        <v>2.69719886779785</v>
       </c>
       <c r="H770" t="n">
         <v>753</v>
@@ -22728,7 +22728,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G771" t="n">
-        <v>2.67927718162537</v>
+        <v>2.67927694320679</v>
       </c>
       <c r="H771" t="n">
         <v>2755</v>
@@ -22757,7 +22757,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G772" t="n">
-        <v>2.67031645774841</v>
+        <v>2.67031621932983</v>
       </c>
       <c r="H772" t="n">
         <v>1014</v>
@@ -22786,7 +22786,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G773" t="n">
-        <v>2.71512007713318</v>
+        <v>2.71512031555176</v>
       </c>
       <c r="H773" t="n">
         <v>19800</v>
@@ -22844,7 +22844,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G775" t="n">
-        <v>2.69719862937927</v>
+        <v>2.69719886779785</v>
       </c>
       <c r="H775" t="n">
         <v>12499</v>
@@ -22873,7 +22873,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G776" t="n">
-        <v>2.67927718162537</v>
+        <v>2.67927694320679</v>
       </c>
       <c r="H776" t="n">
         <v>5677</v>
@@ -22902,7 +22902,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G777" t="n">
-        <v>2.75096344947815</v>
+        <v>2.75096321105957</v>
       </c>
       <c r="H777" t="n">
         <v>1940</v>
@@ -22931,7 +22931,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G778" t="n">
-        <v>2.81368923187256</v>
+        <v>2.81368899345398</v>
       </c>
       <c r="H778" t="n">
         <v>12625</v>
@@ -22960,7 +22960,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G779" t="n">
-        <v>2.84057140350342</v>
+        <v>2.840571641922</v>
       </c>
       <c r="H779" t="n">
         <v>24224</v>
@@ -22989,7 +22989,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G780" t="n">
-        <v>2.93914031982422</v>
+        <v>2.93914008140564</v>
       </c>
       <c r="H780" t="n">
         <v>37762</v>
@@ -23018,7 +23018,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G781" t="n">
-        <v>2.87641477584839</v>
+        <v>2.87641453742981</v>
       </c>
       <c r="H781" t="n">
         <v>16941</v>
@@ -23076,7 +23076,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G783" t="n">
-        <v>2.82264995574951</v>
+        <v>2.82264971733093</v>
       </c>
       <c r="H783" t="n">
         <v>3132</v>
@@ -23163,7 +23163,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G786" t="n">
-        <v>2.82264995574951</v>
+        <v>2.82264971733093</v>
       </c>
       <c r="H786" t="n">
         <v>757</v>
@@ -23192,7 +23192,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G787" t="n">
-        <v>2.77784562110901</v>
+        <v>2.77784585952759</v>
       </c>
       <c r="H787" t="n">
         <v>127</v>
@@ -23221,7 +23221,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G788" t="n">
-        <v>2.84057140350342</v>
+        <v>2.840571641922</v>
       </c>
       <c r="H788" t="n">
         <v>23401</v>
@@ -23250,7 +23250,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G789" t="n">
-        <v>2.77784562110901</v>
+        <v>2.77784585952759</v>
       </c>
       <c r="H789" t="n">
         <v>7830</v>
@@ -23279,7 +23279,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G790" t="n">
-        <v>2.76888489723206</v>
+        <v>2.76888513565063</v>
       </c>
       <c r="H790" t="n">
         <v>501</v>
@@ -23337,7 +23337,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G792" t="n">
-        <v>2.77784562110901</v>
+        <v>2.77784585952759</v>
       </c>
       <c r="H792" t="n">
         <v>1540</v>
@@ -23395,7 +23395,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G794" t="n">
-        <v>2.87641477584839</v>
+        <v>2.87641453742981</v>
       </c>
       <c r="H794" t="n">
         <v>5745</v>
@@ -23424,7 +23424,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G795" t="n">
-        <v>2.87641477584839</v>
+        <v>2.87641453742981</v>
       </c>
       <c r="H795" t="n">
         <v>10690</v>
@@ -23511,7 +23511,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G798" t="n">
-        <v>3.16315984725952</v>
+        <v>3.16315960884094</v>
       </c>
       <c r="H798" t="n">
         <v>77776</v>
@@ -23598,7 +23598,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G801" t="n">
-        <v>3.25276803970337</v>
+        <v>3.25276780128479</v>
       </c>
       <c r="H801" t="n">
         <v>35656</v>
@@ -23656,7 +23656,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G803" t="n">
-        <v>3.25276803970337</v>
+        <v>3.25276780128479</v>
       </c>
       <c r="H803" t="n">
         <v>24537</v>
@@ -23830,7 +23830,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G809" t="n">
-        <v>3.33341503143311</v>
+        <v>3.33341479301453</v>
       </c>
       <c r="H809" t="n">
         <v>6694</v>
@@ -23888,7 +23888,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G811" t="n">
-        <v>3.33341503143311</v>
+        <v>3.33341479301453</v>
       </c>
       <c r="H811" t="n">
         <v>1777</v>
@@ -23917,7 +23917,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G812" t="n">
-        <v>3.34237551689148</v>
+        <v>3.34237575531006</v>
       </c>
       <c r="H812" t="n">
         <v>14717</v>
@@ -24004,7 +24004,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G815" t="n">
-        <v>3.40510106086731</v>
+        <v>3.40510129928589</v>
       </c>
       <c r="H815" t="n">
         <v>25970</v>
@@ -24062,7 +24062,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G817" t="n">
-        <v>3.3692581653595</v>
+        <v>3.36925792694092</v>
       </c>
       <c r="H817" t="n">
         <v>26326</v>
@@ -24120,7 +24120,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G819" t="n">
-        <v>3.40510106086731</v>
+        <v>3.40510129928589</v>
       </c>
       <c r="H819" t="n">
         <v>2828</v>
@@ -24207,7 +24207,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G822" t="n">
-        <v>3.48574829101562</v>
+        <v>3.4857485294342</v>
       </c>
       <c r="H822" t="n">
         <v>8734</v>
@@ -24236,7 +24236,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G823" t="n">
-        <v>3.47678780555725</v>
+        <v>3.47678756713867</v>
       </c>
       <c r="H823" t="n">
         <v>7457</v>
@@ -24555,7 +24555,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G834" t="n">
-        <v>3.51263070106506</v>
+        <v>3.51263093948364</v>
       </c>
       <c r="H834" t="n">
         <v>17785</v>
@@ -24584,7 +24584,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G835" t="n">
-        <v>3.51263070106506</v>
+        <v>3.51263093948364</v>
       </c>
       <c r="H835" t="n">
         <v>9370</v>
@@ -24642,7 +24642,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G837" t="n">
-        <v>3.51263070106506</v>
+        <v>3.51263093948364</v>
       </c>
       <c r="H837" t="n">
         <v>3704</v>
@@ -24671,7 +24671,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G838" t="n">
-        <v>3.53951334953308</v>
+        <v>3.5395131111145</v>
       </c>
       <c r="H838" t="n">
         <v>9297</v>
@@ -24729,7 +24729,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G840" t="n">
-        <v>3.51263070106506</v>
+        <v>3.51263093948364</v>
       </c>
       <c r="H840" t="n">
         <v>9839</v>
@@ -24903,7 +24903,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G846" t="n">
-        <v>3.71872901916504</v>
+        <v>3.71872925758362</v>
       </c>
       <c r="H846" t="n">
         <v>10814</v>
@@ -24932,7 +24932,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G847" t="n">
-        <v>3.69184637069702</v>
+        <v>3.6918466091156</v>
       </c>
       <c r="H847" t="n">
         <v>15171</v>
@@ -24961,7 +24961,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G848" t="n">
-        <v>3.70976829528809</v>
+        <v>3.70976805686951</v>
       </c>
       <c r="H848" t="n">
         <v>16414</v>
@@ -24990,7 +24990,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G849" t="n">
-        <v>3.68288612365723</v>
+        <v>3.68288588523865</v>
       </c>
       <c r="H849" t="n">
         <v>10497</v>
@@ -25048,7 +25048,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G851" t="n">
-        <v>3.70976829528809</v>
+        <v>3.70976805686951</v>
       </c>
       <c r="H851" t="n">
         <v>3613</v>
@@ -25164,7 +25164,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G855" t="n">
-        <v>3.7904155254364</v>
+        <v>3.79041528701782</v>
       </c>
       <c r="H855" t="n">
         <v>50118</v>
@@ -80067,6 +80067,35 @@
         <v>2194</v>
       </c>
       <c r="I2748" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2749">
+      <c r="A2749" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2749" s="1" t="n">
+        <v>46318.2916666667</v>
+      </c>
+      <c r="C2749" t="n">
+        <v>0.959999978542328</v>
+      </c>
+      <c r="D2749" t="n">
+        <v>0.959999978542328</v>
+      </c>
+      <c r="E2749" t="n">
+        <v>0.959999978542328</v>
+      </c>
+      <c r="F2749" t="n">
+        <v>0.995000004768372</v>
+      </c>
+      <c r="G2749" t="n">
+        <v>0.995000004768372</v>
+      </c>
+      <c r="H2749" t="n">
+        <v>35</v>
+      </c>
+      <c r="I2749" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/RAT.MI.xlsx
+++ b/data/RAT.MI.xlsx
@@ -427,7 +427,7 @@
         <v>2.3659999370575</v>
       </c>
       <c r="G2" t="n">
-        <v>1.85825955867767</v>
+        <v>1.85825943946838</v>
       </c>
       <c r="H2" t="n">
         <v>1350</v>
@@ -485,7 +485,7 @@
         <v>2.44600009918213</v>
       </c>
       <c r="G4" t="n">
-        <v>1.92109191417694</v>
+        <v>1.92109167575836</v>
       </c>
       <c r="H4" t="n">
         <v>365</v>
@@ -514,7 +514,7 @@
         <v>2.44600009918213</v>
       </c>
       <c r="G5" t="n">
-        <v>1.92109191417694</v>
+        <v>1.92109167575836</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -601,7 +601,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G8" t="n">
-        <v>1.92423319816589</v>
+        <v>1.92423295974731</v>
       </c>
       <c r="H8" t="n">
         <v>4000</v>
@@ -688,7 +688,7 @@
         <v>2.3659999370575</v>
       </c>
       <c r="G11" t="n">
-        <v>1.85825955867767</v>
+        <v>1.85825943946838</v>
       </c>
       <c r="H11" t="n">
         <v>1414</v>
@@ -775,7 +775,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G14" t="n">
-        <v>1.82998502254486</v>
+        <v>1.82998490333557</v>
       </c>
       <c r="H14" t="n">
         <v>193</v>
@@ -920,7 +920,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G19" t="n">
-        <v>1.86925530433655</v>
+        <v>1.86925494670868</v>
       </c>
       <c r="H19" t="n">
         <v>3200</v>
@@ -949,7 +949,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G20" t="n">
-        <v>1.87710916996002</v>
+        <v>1.87710905075073</v>
       </c>
       <c r="H20" t="n">
         <v>460</v>
@@ -978,7 +978,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G21" t="n">
-        <v>1.89281713962555</v>
+        <v>1.89281702041626</v>
       </c>
       <c r="H21" t="n">
         <v>100</v>
@@ -1007,7 +1007,7 @@
         <v>2.37800002098083</v>
       </c>
       <c r="G22" t="n">
-        <v>1.86768400669098</v>
+        <v>1.86768412590027</v>
       </c>
       <c r="H22" t="n">
         <v>2858</v>
@@ -1036,7 +1036,7 @@
         <v>2.31200003623962</v>
       </c>
       <c r="G23" t="n">
-        <v>1.81584763526917</v>
+        <v>1.81584787368774</v>
       </c>
       <c r="H23" t="n">
         <v>750</v>
@@ -1065,7 +1065,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G24" t="n">
-        <v>1.83783888816833</v>
+        <v>1.8378392457962</v>
       </c>
       <c r="H24" t="n">
         <v>1435</v>
@@ -1094,7 +1094,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G25" t="n">
-        <v>1.83783888816833</v>
+        <v>1.8378392457962</v>
       </c>
       <c r="H25" t="n">
         <v>475</v>
@@ -1152,7 +1152,7 @@
         <v>2.38800001144409</v>
       </c>
       <c r="G27" t="n">
-        <v>1.87553834915161</v>
+        <v>1.8755384683609</v>
       </c>
       <c r="H27" t="n">
         <v>2173</v>
@@ -1181,7 +1181,7 @@
         <v>2.38800001144409</v>
       </c>
       <c r="G28" t="n">
-        <v>1.87553834915161</v>
+        <v>1.8755384683609</v>
       </c>
       <c r="H28" t="n">
         <v>0</v>
@@ -1268,7 +1268,7 @@
         <v>2.32599997520447</v>
       </c>
       <c r="G31" t="n">
-        <v>1.82684326171875</v>
+        <v>1.82684338092804</v>
       </c>
       <c r="H31" t="n">
         <v>9925</v>
@@ -1297,7 +1297,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G32" t="n">
-        <v>1.84569275379181</v>
+        <v>1.84569299221039</v>
       </c>
       <c r="H32" t="n">
         <v>250</v>
@@ -1326,7 +1326,7 @@
         <v>2.31599998474121</v>
       </c>
       <c r="G33" t="n">
-        <v>1.81898927688599</v>
+        <v>1.81898951530457</v>
       </c>
       <c r="H33" t="n">
         <v>1023</v>
@@ -1384,7 +1384,7 @@
         <v>2.36800003051758</v>
       </c>
       <c r="G35" t="n">
-        <v>1.8598301410675</v>
+        <v>1.85983037948608</v>
       </c>
       <c r="H35" t="n">
         <v>100</v>
@@ -1413,7 +1413,7 @@
         <v>2.36800003051758</v>
       </c>
       <c r="G36" t="n">
-        <v>1.8598301410675</v>
+        <v>1.85983037948608</v>
       </c>
       <c r="H36" t="n">
         <v>0</v>
@@ -1442,7 +1442,7 @@
         <v>2.36800003051758</v>
       </c>
       <c r="G37" t="n">
-        <v>1.8598301410675</v>
+        <v>1.85983037948608</v>
       </c>
       <c r="H37" t="n">
         <v>100</v>
@@ -1500,7 +1500,7 @@
         <v>2.31800007820129</v>
       </c>
       <c r="G39" t="n">
-        <v>1.82056045532227</v>
+        <v>1.82056021690369</v>
       </c>
       <c r="H39" t="n">
         <v>330</v>
@@ -1529,7 +1529,7 @@
         <v>2.31399989128113</v>
       </c>
       <c r="G40" t="n">
-        <v>1.81741845607758</v>
+        <v>1.81741857528687</v>
       </c>
       <c r="H40" t="n">
         <v>150</v>
@@ -1558,7 +1558,7 @@
         <v>2.31399989128113</v>
       </c>
       <c r="G41" t="n">
-        <v>1.81741845607758</v>
+        <v>1.81741857528687</v>
       </c>
       <c r="H41" t="n">
         <v>0</v>
@@ -1587,7 +1587,7 @@
         <v>2.31399989128113</v>
       </c>
       <c r="G42" t="n">
-        <v>1.81741845607758</v>
+        <v>1.81741857528687</v>
       </c>
       <c r="H42" t="n">
         <v>0</v>
@@ -1645,7 +1645,7 @@
         <v>2.36800003051758</v>
       </c>
       <c r="G44" t="n">
-        <v>1.8598301410675</v>
+        <v>1.85983037948608</v>
       </c>
       <c r="H44" t="n">
         <v>540</v>
@@ -1674,7 +1674,7 @@
         <v>2.37800002098083</v>
       </c>
       <c r="G45" t="n">
-        <v>1.86768400669098</v>
+        <v>1.86768412590027</v>
       </c>
       <c r="H45" t="n">
         <v>2230</v>
@@ -1703,7 +1703,7 @@
         <v>2.35599994659424</v>
       </c>
       <c r="G46" t="n">
-        <v>1.85040545463562</v>
+        <v>1.85040509700775</v>
       </c>
       <c r="H46" t="n">
         <v>253</v>
@@ -1819,7 +1819,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G50" t="n">
-        <v>1.84569275379181</v>
+        <v>1.84569299221039</v>
       </c>
       <c r="H50" t="n">
         <v>396</v>
@@ -1877,7 +1877,7 @@
         <v>2.35800004005432</v>
       </c>
       <c r="G52" t="n">
-        <v>1.85197615623474</v>
+        <v>1.85197627544403</v>
       </c>
       <c r="H52" t="n">
         <v>3419</v>
@@ -1906,7 +1906,7 @@
         <v>2.34800004959106</v>
       </c>
       <c r="G53" t="n">
-        <v>1.84412217140198</v>
+        <v>1.84412205219269</v>
       </c>
       <c r="H53" t="n">
         <v>3348</v>
@@ -1964,7 +1964,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G55" t="n">
-        <v>1.84569275379181</v>
+        <v>1.84569299221039</v>
       </c>
       <c r="H55" t="n">
         <v>386</v>
@@ -1993,7 +1993,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G56" t="n">
-        <v>1.84569275379181</v>
+        <v>1.84569299221039</v>
       </c>
       <c r="H56" t="n">
         <v>5025</v>
@@ -2167,7 +2167,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G62" t="n">
-        <v>1.82213115692139</v>
+        <v>1.82213091850281</v>
       </c>
       <c r="H62" t="n">
         <v>7700</v>
@@ -2196,7 +2196,7 @@
         <v>2.35599994659424</v>
       </c>
       <c r="G63" t="n">
-        <v>1.85040545463562</v>
+        <v>1.85040509700775</v>
       </c>
       <c r="H63" t="n">
         <v>100</v>
@@ -2225,7 +2225,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G64" t="n">
-        <v>1.84569275379181</v>
+        <v>1.84569299221039</v>
       </c>
       <c r="H64" t="n">
         <v>1054</v>
@@ -2254,7 +2254,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G65" t="n">
-        <v>1.92423319816589</v>
+        <v>1.92423295974731</v>
       </c>
       <c r="H65" t="n">
         <v>19358</v>
@@ -2283,7 +2283,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G66" t="n">
-        <v>1.92423319816589</v>
+        <v>1.92423295974731</v>
       </c>
       <c r="H66" t="n">
         <v>0</v>
@@ -2341,7 +2341,7 @@
         <v>2.4779999256134</v>
       </c>
       <c r="G68" t="n">
-        <v>1.94622445106506</v>
+        <v>1.94622421264648</v>
       </c>
       <c r="H68" t="n">
         <v>120</v>
@@ -2399,7 +2399,7 @@
         <v>2.5</v>
       </c>
       <c r="G70" t="n">
-        <v>1.96350300312042</v>
+        <v>1.963503241539</v>
       </c>
       <c r="H70" t="n">
         <v>23697</v>
@@ -2428,7 +2428,7 @@
         <v>2.50200009346008</v>
       </c>
       <c r="G71" t="n">
-        <v>1.96507441997528</v>
+        <v>1.9650741815567</v>
       </c>
       <c r="H71" t="n">
         <v>350</v>
@@ -2457,7 +2457,7 @@
         <v>2.53800010681152</v>
       </c>
       <c r="G72" t="n">
-        <v>1.99334847927094</v>
+        <v>1.99334871768951</v>
       </c>
       <c r="H72" t="n">
         <v>1951</v>
@@ -2486,7 +2486,7 @@
         <v>2.55200004577637</v>
       </c>
       <c r="G73" t="n">
-        <v>2.00434398651123</v>
+        <v>2.00434422492981</v>
       </c>
       <c r="H73" t="n">
         <v>3450</v>
@@ -2515,7 +2515,7 @@
         <v>2.5</v>
       </c>
       <c r="G74" t="n">
-        <v>1.96350300312042</v>
+        <v>1.963503241539</v>
       </c>
       <c r="H74" t="n">
         <v>1853</v>
@@ -2544,7 +2544,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G75" t="n">
-        <v>1.98706543445587</v>
+        <v>1.98706519603729</v>
       </c>
       <c r="H75" t="n">
         <v>41607</v>
@@ -2573,7 +2573,7 @@
         <v>2.50200009346008</v>
       </c>
       <c r="G76" t="n">
-        <v>1.96507441997528</v>
+        <v>1.9650741815567</v>
       </c>
       <c r="H76" t="n">
         <v>3085</v>
@@ -2660,7 +2660,7 @@
         <v>2.45799994468689</v>
       </c>
       <c r="G79" t="n">
-        <v>1.93051648139954</v>
+        <v>1.93051600456238</v>
       </c>
       <c r="H79" t="n">
         <v>9175</v>
@@ -2689,7 +2689,7 @@
         <v>2.45799994468689</v>
       </c>
       <c r="G80" t="n">
-        <v>1.93051648139954</v>
+        <v>1.93051600456238</v>
       </c>
       <c r="H80" t="n">
         <v>1464</v>
@@ -2718,7 +2718,7 @@
         <v>2.5</v>
       </c>
       <c r="G81" t="n">
-        <v>1.96350300312042</v>
+        <v>1.963503241539</v>
       </c>
       <c r="H81" t="n">
         <v>50</v>
@@ -2921,7 +2921,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G88" t="n">
-        <v>1.91637897491455</v>
+        <v>1.91637921333313</v>
       </c>
       <c r="H88" t="n">
         <v>1187</v>
@@ -2979,7 +2979,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G90" t="n">
-        <v>1.91637897491455</v>
+        <v>1.91637921333313</v>
       </c>
       <c r="H90" t="n">
         <v>65</v>
@@ -3008,7 +3008,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G91" t="n">
-        <v>1.91637897491455</v>
+        <v>1.91637921333313</v>
       </c>
       <c r="H91" t="n">
         <v>0</v>
@@ -3066,7 +3066,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G93" t="n">
-        <v>1.87710916996002</v>
+        <v>1.87710905075073</v>
       </c>
       <c r="H93" t="n">
         <v>2251</v>
@@ -3095,7 +3095,7 @@
         <v>2.38599991798401</v>
       </c>
       <c r="G94" t="n">
-        <v>1.87396740913391</v>
+        <v>1.87396728992462</v>
       </c>
       <c r="H94" t="n">
         <v>11190</v>
@@ -3124,7 +3124,7 @@
         <v>2.38599991798401</v>
       </c>
       <c r="G95" t="n">
-        <v>1.87396740913391</v>
+        <v>1.87396728992462</v>
       </c>
       <c r="H95" t="n">
         <v>0</v>
@@ -3211,7 +3211,7 @@
         <v>2.34800004959106</v>
       </c>
       <c r="G98" t="n">
-        <v>1.84412217140198</v>
+        <v>1.84412205219269</v>
       </c>
       <c r="H98" t="n">
         <v>8904</v>
@@ -3240,7 +3240,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G99" t="n">
-        <v>1.89281713962555</v>
+        <v>1.89281702041626</v>
       </c>
       <c r="H99" t="n">
         <v>14550</v>
@@ -3298,7 +3298,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G101" t="n">
-        <v>1.95017540454865</v>
+        <v>1.95017504692078</v>
       </c>
       <c r="H101" t="n">
         <v>176</v>
@@ -3327,7 +3327,7 @@
         <v>2.34599995613098</v>
       </c>
       <c r="G102" t="n">
-        <v>1.92231559753418</v>
+        <v>1.92231547832489</v>
       </c>
       <c r="H102" t="n">
         <v>195</v>
@@ -3385,7 +3385,7 @@
         <v>2.35599994659424</v>
       </c>
       <c r="G104" t="n">
-        <v>1.93050956726074</v>
+        <v>1.93050920963287</v>
       </c>
       <c r="H104" t="n">
         <v>3779</v>
@@ -3472,7 +3472,7 @@
         <v>2.38599991798401</v>
       </c>
       <c r="G107" t="n">
-        <v>1.95509147644043</v>
+        <v>1.95509135723114</v>
       </c>
       <c r="H107" t="n">
         <v>523</v>
@@ -3501,7 +3501,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G108" t="n">
-        <v>1.95836925506592</v>
+        <v>1.95836913585663</v>
       </c>
       <c r="H108" t="n">
         <v>668</v>
@@ -3530,7 +3530,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G109" t="n">
-        <v>1.95836925506592</v>
+        <v>1.95836913585663</v>
       </c>
       <c r="H109" t="n">
         <v>0</v>
@@ -3559,7 +3559,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G110" t="n">
-        <v>1.95017540454865</v>
+        <v>1.95017504692078</v>
       </c>
       <c r="H110" t="n">
         <v>403</v>
@@ -3588,7 +3588,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G111" t="n">
-        <v>1.95017540454865</v>
+        <v>1.95017504692078</v>
       </c>
       <c r="H111" t="n">
         <v>0</v>
@@ -3617,7 +3617,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G112" t="n">
-        <v>1.91739904880524</v>
+        <v>1.91739940643311</v>
       </c>
       <c r="H112" t="n">
         <v>778</v>
@@ -3646,7 +3646,7 @@
         <v>2.36199998855591</v>
       </c>
       <c r="G113" t="n">
-        <v>1.93542587757111</v>
+        <v>1.9354259967804</v>
       </c>
       <c r="H113" t="n">
         <v>1461</v>
@@ -3675,7 +3675,7 @@
         <v>2.36199998855591</v>
       </c>
       <c r="G114" t="n">
-        <v>1.93542587757111</v>
+        <v>1.9354259967804</v>
       </c>
       <c r="H114" t="n">
         <v>0</v>
@@ -3704,7 +3704,7 @@
         <v>2.36199998855591</v>
       </c>
       <c r="G115" t="n">
-        <v>1.93542587757111</v>
+        <v>1.9354259967804</v>
       </c>
       <c r="H115" t="n">
         <v>635</v>
@@ -3733,7 +3733,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G116" t="n">
-        <v>1.9419811964035</v>
+        <v>1.94198131561279</v>
       </c>
       <c r="H116" t="n">
         <v>5088</v>
@@ -3762,7 +3762,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G117" t="n">
-        <v>1.9419811964035</v>
+        <v>1.94198131561279</v>
       </c>
       <c r="H117" t="n">
         <v>0</v>
@@ -3791,7 +3791,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G118" t="n">
-        <v>1.91739904880524</v>
+        <v>1.91739940643311</v>
       </c>
       <c r="H118" t="n">
         <v>2740</v>
@@ -3849,7 +3849,7 @@
         <v>2.33200001716614</v>
       </c>
       <c r="G120" t="n">
-        <v>1.91084408760071</v>
+        <v>1.91084396839142</v>
       </c>
       <c r="H120" t="n">
         <v>1532</v>
@@ -3878,7 +3878,7 @@
         <v>2.33200001716614</v>
       </c>
       <c r="G121" t="n">
-        <v>1.91084408760071</v>
+        <v>1.91084396839142</v>
       </c>
       <c r="H121" t="n">
         <v>0</v>
@@ -3965,7 +3965,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G124" t="n">
-        <v>1.83545887470245</v>
+        <v>1.83545899391174</v>
       </c>
       <c r="H124" t="n">
         <v>348</v>
@@ -3994,7 +3994,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G125" t="n">
-        <v>1.80268287658691</v>
+        <v>1.8026829957962</v>
       </c>
       <c r="H125" t="n">
         <v>3159</v>
@@ -4023,7 +4023,7 @@
         <v>2.24799990653992</v>
       </c>
       <c r="G126" t="n">
-        <v>1.84201419353485</v>
+        <v>1.84201407432556</v>
       </c>
       <c r="H126" t="n">
         <v>1490</v>
@@ -4052,7 +4052,7 @@
         <v>2.23600006103516</v>
       </c>
       <c r="G127" t="n">
-        <v>1.83218145370483</v>
+        <v>1.83218157291412</v>
       </c>
       <c r="H127" t="n">
         <v>773</v>
@@ -4081,7 +4081,7 @@
         <v>2.24799990653992</v>
       </c>
       <c r="G128" t="n">
-        <v>1.84201419353485</v>
+        <v>1.84201407432556</v>
       </c>
       <c r="H128" t="n">
         <v>370</v>
@@ -4139,7 +4139,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G130" t="n">
-        <v>1.86823523044586</v>
+        <v>1.86823499202728</v>
       </c>
       <c r="H130" t="n">
         <v>2288</v>
@@ -4168,7 +4168,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G131" t="n">
-        <v>1.9419811964035</v>
+        <v>1.94198131561279</v>
       </c>
       <c r="H131" t="n">
         <v>150</v>
@@ -4197,7 +4197,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G132" t="n">
-        <v>1.9419811964035</v>
+        <v>1.94198131561279</v>
       </c>
       <c r="H132" t="n">
         <v>0</v>
@@ -4226,7 +4226,7 @@
         <v>2.32800006866455</v>
       </c>
       <c r="G133" t="n">
-        <v>1.9075665473938</v>
+        <v>1.90756618976593</v>
       </c>
       <c r="H133" t="n">
         <v>510</v>
@@ -4255,7 +4255,7 @@
         <v>2.32800006866455</v>
       </c>
       <c r="G134" t="n">
-        <v>1.9075665473938</v>
+        <v>1.90756618976593</v>
       </c>
       <c r="H134" t="n">
         <v>0</v>
@@ -4284,7 +4284,7 @@
         <v>2.32800006866455</v>
       </c>
       <c r="G135" t="n">
-        <v>1.9075665473938</v>
+        <v>1.90756618976593</v>
       </c>
       <c r="H135" t="n">
         <v>0</v>
@@ -4342,7 +4342,7 @@
         <v>2.32599997520447</v>
       </c>
       <c r="G137" t="n">
-        <v>1.90592741966248</v>
+        <v>1.90592753887177</v>
       </c>
       <c r="H137" t="n">
         <v>600</v>
@@ -4371,7 +4371,7 @@
         <v>2.32599997520447</v>
       </c>
       <c r="G138" t="n">
-        <v>1.90592741966248</v>
+        <v>1.90592753887177</v>
       </c>
       <c r="H138" t="n">
         <v>815</v>
@@ -4429,7 +4429,7 @@
         <v>2.32599997520447</v>
       </c>
       <c r="G140" t="n">
-        <v>1.90592741966248</v>
+        <v>1.90592753887177</v>
       </c>
       <c r="H140" t="n">
         <v>50</v>
@@ -4458,7 +4458,7 @@
         <v>2.32599997520447</v>
       </c>
       <c r="G141" t="n">
-        <v>1.90592741966248</v>
+        <v>1.90592753887177</v>
       </c>
       <c r="H141" t="n">
         <v>0</v>
@@ -4487,7 +4487,7 @@
         <v>2.32800006866455</v>
       </c>
       <c r="G142" t="n">
-        <v>1.9075665473938</v>
+        <v>1.90756618976593</v>
       </c>
       <c r="H142" t="n">
         <v>80</v>
@@ -4516,7 +4516,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G143" t="n">
-        <v>1.90920519828796</v>
+        <v>1.90920507907867</v>
       </c>
       <c r="H143" t="n">
         <v>1045</v>
@@ -4545,7 +4545,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G144" t="n">
-        <v>1.90920519828796</v>
+        <v>1.90920507907867</v>
       </c>
       <c r="H144" t="n">
         <v>1250</v>
@@ -4603,7 +4603,7 @@
         <v>2.31599998474121</v>
       </c>
       <c r="G146" t="n">
-        <v>1.89773344993591</v>
+        <v>1.89773368835449</v>
       </c>
       <c r="H146" t="n">
         <v>5883</v>
@@ -4632,7 +4632,7 @@
         <v>2.32599997520447</v>
       </c>
       <c r="G147" t="n">
-        <v>1.90592741966248</v>
+        <v>1.90592753887177</v>
       </c>
       <c r="H147" t="n">
         <v>1070</v>
@@ -4661,7 +4661,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G148" t="n">
-        <v>1.90920519828796</v>
+        <v>1.90920507907867</v>
       </c>
       <c r="H148" t="n">
         <v>1371</v>
@@ -4690,7 +4690,7 @@
         <v>2.2260000705719</v>
       </c>
       <c r="G149" t="n">
-        <v>1.82398748397827</v>
+        <v>1.82398724555969</v>
       </c>
       <c r="H149" t="n">
         <v>2820</v>
@@ -4719,7 +4719,7 @@
         <v>2.14599990844727</v>
       </c>
       <c r="G150" t="n">
-        <v>1.75843513011932</v>
+        <v>1.75843501091003</v>
       </c>
       <c r="H150" t="n">
         <v>12851</v>
@@ -4777,7 +4777,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G152" t="n">
-        <v>1.78629493713379</v>
+        <v>1.78629505634308</v>
       </c>
       <c r="H152" t="n">
         <v>7134</v>
@@ -4806,7 +4806,7 @@
         <v>2.16799998283386</v>
       </c>
       <c r="G153" t="n">
-        <v>1.77646219730377</v>
+        <v>1.77646207809448</v>
       </c>
       <c r="H153" t="n">
         <v>1600</v>
@@ -4835,7 +4835,7 @@
         <v>2.13800001144409</v>
       </c>
       <c r="G154" t="n">
-        <v>1.75188004970551</v>
+        <v>1.75188016891479</v>
       </c>
       <c r="H154" t="n">
         <v>6911</v>
@@ -4864,7 +4864,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G155" t="n">
-        <v>1.75351893901825</v>
+        <v>1.75351905822754</v>
       </c>
       <c r="H155" t="n">
         <v>606</v>
@@ -4893,7 +4893,7 @@
         <v>2.17199993133545</v>
       </c>
       <c r="G156" t="n">
-        <v>1.77973973751068</v>
+        <v>1.77973961830139</v>
       </c>
       <c r="H156" t="n">
         <v>975</v>
@@ -4922,7 +4922,7 @@
         <v>2.17199993133545</v>
       </c>
       <c r="G157" t="n">
-        <v>1.77973973751068</v>
+        <v>1.77973961830139</v>
       </c>
       <c r="H157" t="n">
         <v>0</v>
@@ -4951,7 +4951,7 @@
         <v>2.13599991798401</v>
       </c>
       <c r="G158" t="n">
-        <v>1.75024116039276</v>
+        <v>1.75024127960205</v>
       </c>
       <c r="H158" t="n">
         <v>4584</v>
@@ -4980,7 +4980,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G159" t="n">
-        <v>1.72074270248413</v>
+        <v>1.72074258327484</v>
       </c>
       <c r="H159" t="n">
         <v>2791</v>
@@ -5038,7 +5038,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G161" t="n">
-        <v>1.72893667221069</v>
+        <v>1.72893679141998</v>
       </c>
       <c r="H161" t="n">
         <v>12639</v>
@@ -5067,7 +5067,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G162" t="n">
-        <v>1.72893667221069</v>
+        <v>1.72893679141998</v>
       </c>
       <c r="H162" t="n">
         <v>0</v>
@@ -5096,7 +5096,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G163" t="n">
-        <v>1.69616067409515</v>
+        <v>1.69616091251373</v>
       </c>
       <c r="H163" t="n">
         <v>4541</v>
@@ -5328,7 +5328,7 @@
         <v>2.11800003051758</v>
       </c>
       <c r="G171" t="n">
-        <v>1.73549211025238</v>
+        <v>1.73549199104309</v>
       </c>
       <c r="H171" t="n">
         <v>263</v>
@@ -5357,7 +5357,7 @@
         <v>2.1159999370575</v>
       </c>
       <c r="G172" t="n">
-        <v>1.73385322093964</v>
+        <v>1.73385310173035</v>
       </c>
       <c r="H172" t="n">
         <v>5150</v>
@@ -5386,7 +5386,7 @@
         <v>2.1159999370575</v>
       </c>
       <c r="G173" t="n">
-        <v>1.73385322093964</v>
+        <v>1.73385310173035</v>
       </c>
       <c r="H173" t="n">
         <v>0</v>
@@ -5444,7 +5444,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G175" t="n">
-        <v>1.63060867786407</v>
+        <v>1.63060879707336</v>
       </c>
       <c r="H175" t="n">
         <v>32041</v>
@@ -5502,7 +5502,7 @@
         <v>2.03399991989136</v>
       </c>
       <c r="G177" t="n">
-        <v>1.66666221618652</v>
+        <v>1.66666233539581</v>
       </c>
       <c r="H177" t="n">
         <v>7268</v>
@@ -5850,7 +5850,7 @@
         <v>2.00799989700317</v>
       </c>
       <c r="G189" t="n">
-        <v>1.64535784721375</v>
+        <v>1.64535772800446</v>
       </c>
       <c r="H189" t="n">
         <v>2513</v>
@@ -5879,7 +5879,7 @@
         <v>2</v>
       </c>
       <c r="G190" t="n">
-        <v>1.63880276679993</v>
+        <v>1.63880264759064</v>
       </c>
       <c r="H190" t="n">
         <v>288</v>
@@ -5908,7 +5908,7 @@
         <v>1.98399996757507</v>
       </c>
       <c r="G191" t="n">
-        <v>1.62569212913513</v>
+        <v>1.62569224834442</v>
       </c>
       <c r="H191" t="n">
         <v>9477</v>
@@ -5966,7 +5966,7 @@
         <v>2.03399991989136</v>
       </c>
       <c r="G193" t="n">
-        <v>1.66666221618652</v>
+        <v>1.66666233539581</v>
       </c>
       <c r="H193" t="n">
         <v>2852</v>
@@ -6227,7 +6227,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G202" t="n">
-        <v>1.64699673652649</v>
+        <v>1.6469966173172</v>
       </c>
       <c r="H202" t="n">
         <v>487</v>
@@ -6256,7 +6256,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G203" t="n">
-        <v>1.64699673652649</v>
+        <v>1.6469966173172</v>
       </c>
       <c r="H203" t="n">
         <v>4278</v>
@@ -6285,7 +6285,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G204" t="n">
-        <v>1.64699673652649</v>
+        <v>1.6469966173172</v>
       </c>
       <c r="H204" t="n">
         <v>180</v>
@@ -6314,7 +6314,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G205" t="n">
-        <v>1.64699673652649</v>
+        <v>1.6469966173172</v>
       </c>
       <c r="H205" t="n">
         <v>0</v>
@@ -6343,7 +6343,7 @@
         <v>1.99899995326996</v>
       </c>
       <c r="G206" t="n">
-        <v>1.63798332214355</v>
+        <v>1.63798320293427</v>
       </c>
       <c r="H206" t="n">
         <v>2595</v>
@@ -6401,7 +6401,7 @@
         <v>1.9889999628067</v>
       </c>
       <c r="G208" t="n">
-        <v>1.6297892332077</v>
+        <v>1.62978911399841</v>
       </c>
       <c r="H208" t="n">
         <v>50</v>
@@ -6430,7 +6430,7 @@
         <v>1.932000041008</v>
       </c>
       <c r="G209" t="n">
-        <v>1.58308339118958</v>
+        <v>1.58308351039886</v>
       </c>
       <c r="H209" t="n">
         <v>10501</v>
@@ -6517,7 +6517,7 @@
         <v>1.94200003147125</v>
       </c>
       <c r="G212" t="n">
-        <v>1.59127748012543</v>
+        <v>1.59127724170685</v>
       </c>
       <c r="H212" t="n">
         <v>8960</v>
@@ -6546,7 +6546,7 @@
         <v>1.94200003147125</v>
       </c>
       <c r="G213" t="n">
-        <v>1.59127748012543</v>
+        <v>1.59127724170685</v>
       </c>
       <c r="H213" t="n">
         <v>0</v>
@@ -6575,7 +6575,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G214" t="n">
-        <v>1.54047441482544</v>
+        <v>1.54047453403473</v>
       </c>
       <c r="H214" t="n">
         <v>2780</v>
@@ -6604,7 +6604,7 @@
         <v>1.91299998760223</v>
       </c>
       <c r="G215" t="n">
-        <v>1.56751477718353</v>
+        <v>1.56751465797424</v>
       </c>
       <c r="H215" t="n">
         <v>8016</v>
@@ -6720,7 +6720,7 @@
         <v>1.9559999704361</v>
       </c>
       <c r="G219" t="n">
-        <v>1.6027489900589</v>
+        <v>1.60274910926819</v>
       </c>
       <c r="H219" t="n">
         <v>100</v>
@@ -6749,7 +6749,7 @@
         <v>1.95700001716614</v>
       </c>
       <c r="G220" t="n">
-        <v>1.60356855392456</v>
+        <v>1.60356843471527</v>
       </c>
       <c r="H220" t="n">
         <v>5560</v>
@@ -6778,7 +6778,7 @@
         <v>1.9559999704361</v>
       </c>
       <c r="G221" t="n">
-        <v>1.6027489900589</v>
+        <v>1.60274910926819</v>
       </c>
       <c r="H221" t="n">
         <v>280</v>
@@ -6807,7 +6807,7 @@
         <v>1.9559999704361</v>
       </c>
       <c r="G222" t="n">
-        <v>1.6027489900589</v>
+        <v>1.60274910926819</v>
       </c>
       <c r="H222" t="n">
         <v>0</v>
@@ -6836,7 +6836,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G223" t="n">
-        <v>1.6060266494751</v>
+        <v>1.60602676868439</v>
       </c>
       <c r="H223" t="n">
         <v>3500</v>
@@ -6865,7 +6865,7 @@
         <v>2.00799989700317</v>
       </c>
       <c r="G224" t="n">
-        <v>1.64535784721375</v>
+        <v>1.64535772800446</v>
       </c>
       <c r="H224" t="n">
         <v>100</v>
@@ -6894,7 +6894,7 @@
         <v>1.85399997234344</v>
       </c>
       <c r="G225" t="n">
-        <v>1.51917004585266</v>
+        <v>1.51917016506195</v>
       </c>
       <c r="H225" t="n">
         <v>20310</v>
@@ -6923,7 +6923,7 @@
         <v>1.90600001811981</v>
       </c>
       <c r="G226" t="n">
-        <v>1.56177890300751</v>
+        <v>1.5617790222168</v>
       </c>
       <c r="H226" t="n">
         <v>3632</v>
@@ -6981,7 +6981,7 @@
         <v>1.67999994754791</v>
       </c>
       <c r="G228" t="n">
-        <v>1.37659418582916</v>
+        <v>1.37659406661987</v>
       </c>
       <c r="H228" t="n">
         <v>40640</v>
@@ -7010,7 +7010,7 @@
         <v>1.72399997711182</v>
       </c>
       <c r="G229" t="n">
-        <v>1.41264796257019</v>
+        <v>1.4126478433609</v>
       </c>
       <c r="H229" t="n">
         <v>18656</v>
@@ -7039,7 +7039,7 @@
         <v>1.70200002193451</v>
       </c>
       <c r="G230" t="n">
-        <v>1.39462101459503</v>
+        <v>1.39462113380432</v>
       </c>
       <c r="H230" t="n">
         <v>23064</v>
@@ -7068,7 +7068,7 @@
         <v>1.77900004386902</v>
       </c>
       <c r="G231" t="n">
-        <v>1.45771491527557</v>
+        <v>1.45771503448486</v>
       </c>
       <c r="H231" t="n">
         <v>4259</v>
@@ -7155,7 +7155,7 @@
         <v>1.96800005435944</v>
       </c>
       <c r="G234" t="n">
-        <v>1.61258184909821</v>
+        <v>1.61258172988892</v>
       </c>
       <c r="H234" t="n">
         <v>5088</v>
@@ -7358,7 +7358,7 @@
         <v>1.84500002861023</v>
       </c>
       <c r="G241" t="n">
-        <v>1.51179552078247</v>
+        <v>1.51179540157318</v>
       </c>
       <c r="H241" t="n">
         <v>3642</v>
@@ -7445,7 +7445,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G244" t="n">
-        <v>1.56505644321442</v>
+        <v>1.56505656242371</v>
       </c>
       <c r="H244" t="n">
         <v>627</v>
@@ -7474,7 +7474,7 @@
         <v>1.90900003910065</v>
       </c>
       <c r="G245" t="n">
-        <v>1.56423711776733</v>
+        <v>1.56423723697662</v>
       </c>
       <c r="H245" t="n">
         <v>250</v>
@@ -7503,7 +7503,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G246" t="n">
-        <v>1.54047441482544</v>
+        <v>1.54047453403473</v>
       </c>
       <c r="H246" t="n">
         <v>430</v>
@@ -7590,7 +7590,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G249" t="n">
-        <v>1.55686259269714</v>
+        <v>1.55686247348785</v>
       </c>
       <c r="H249" t="n">
         <v>17229</v>
@@ -7648,7 +7648,7 @@
         <v>1.88100004196167</v>
       </c>
       <c r="G251" t="n">
-        <v>1.54129385948181</v>
+        <v>1.5412939786911</v>
       </c>
       <c r="H251" t="n">
         <v>33196</v>
@@ -7735,7 +7735,7 @@
         <v>1.89300000667572</v>
       </c>
       <c r="G254" t="n">
-        <v>1.55112671852112</v>
+        <v>1.55112683773041</v>
       </c>
       <c r="H254" t="n">
         <v>2118</v>
@@ -7793,7 +7793,7 @@
         <v>1.89400005340576</v>
       </c>
       <c r="G256" t="n">
-        <v>1.55194628238678</v>
+        <v>1.55194616317749</v>
       </c>
       <c r="H256" t="n">
         <v>1370</v>
@@ -7909,7 +7909,7 @@
         <v>1.84200000762939</v>
       </c>
       <c r="G260" t="n">
-        <v>1.50933730602264</v>
+        <v>1.50933742523193</v>
       </c>
       <c r="H260" t="n">
         <v>15155</v>
@@ -7967,7 +7967,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G262" t="n">
-        <v>1.50769853591919</v>
+        <v>1.5076984167099</v>
       </c>
       <c r="H262" t="n">
         <v>110</v>
@@ -7996,7 +7996,7 @@
         <v>1.84200000762939</v>
       </c>
       <c r="G263" t="n">
-        <v>1.50933730602264</v>
+        <v>1.50933742523193</v>
       </c>
       <c r="H263" t="n">
         <v>8077</v>
@@ -8025,7 +8025,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G264" t="n">
-        <v>1.50769853591919</v>
+        <v>1.5076984167099</v>
       </c>
       <c r="H264" t="n">
         <v>10670</v>
@@ -8083,7 +8083,7 @@
         <v>1.82500004768372</v>
       </c>
       <c r="G266" t="n">
-        <v>1.49540746212006</v>
+        <v>1.49540758132935</v>
       </c>
       <c r="H266" t="n">
         <v>6063</v>
@@ -8112,7 +8112,7 @@
         <v>1.84300005435944</v>
       </c>
       <c r="G267" t="n">
-        <v>1.51015675067902</v>
+        <v>1.51015663146973</v>
       </c>
       <c r="H267" t="n">
         <v>9047</v>
@@ -8141,7 +8141,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G268" t="n">
-        <v>1.54047441482544</v>
+        <v>1.54047453403473</v>
       </c>
       <c r="H268" t="n">
         <v>27145</v>
@@ -8228,7 +8228,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G271" t="n">
-        <v>1.55686259269714</v>
+        <v>1.55686247348785</v>
       </c>
       <c r="H271" t="n">
         <v>15130</v>
@@ -8257,7 +8257,7 @@
         <v>1.94599997997284</v>
       </c>
       <c r="G272" t="n">
-        <v>1.59455513954163</v>
+        <v>1.59455502033234</v>
       </c>
       <c r="H272" t="n">
         <v>20610</v>
@@ -8286,7 +8286,7 @@
         <v>1.96099996566772</v>
       </c>
       <c r="G273" t="n">
-        <v>1.60684585571289</v>
+        <v>1.60684597492218</v>
       </c>
       <c r="H273" t="n">
         <v>4589</v>
@@ -8315,7 +8315,7 @@
         <v>1.95700001716614</v>
       </c>
       <c r="G274" t="n">
-        <v>1.60356855392456</v>
+        <v>1.60356843471527</v>
       </c>
       <c r="H274" t="n">
         <v>6671</v>
@@ -8344,7 +8344,7 @@
         <v>1.96800005435944</v>
       </c>
       <c r="G275" t="n">
-        <v>1.61258184909821</v>
+        <v>1.61258172988892</v>
       </c>
       <c r="H275" t="n">
         <v>19986</v>
@@ -8576,7 +8576,7 @@
         <v>1.90100002288818</v>
       </c>
       <c r="G283" t="n">
-        <v>1.55768203735352</v>
+        <v>1.55768191814423</v>
       </c>
       <c r="H283" t="n">
         <v>371</v>
@@ -8605,7 +8605,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G284" t="n">
-        <v>1.55686259269714</v>
+        <v>1.55686247348785</v>
       </c>
       <c r="H284" t="n">
         <v>6242</v>
@@ -8663,7 +8663,7 @@
         <v>1.87300002574921</v>
       </c>
       <c r="G286" t="n">
-        <v>1.5347386598587</v>
+        <v>1.53473877906799</v>
       </c>
       <c r="H286" t="n">
         <v>168</v>
@@ -8750,7 +8750,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G289" t="n">
-        <v>1.54047441482544</v>
+        <v>1.54047453403473</v>
       </c>
       <c r="H289" t="n">
         <v>1385</v>
@@ -8866,7 +8866,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G293" t="n">
-        <v>1.56505644321442</v>
+        <v>1.56505656242371</v>
       </c>
       <c r="H293" t="n">
         <v>3832</v>
@@ -8895,7 +8895,7 @@
         <v>1.89400005340576</v>
       </c>
       <c r="G294" t="n">
-        <v>1.55194628238678</v>
+        <v>1.55194616317749</v>
       </c>
       <c r="H294" t="n">
         <v>2920</v>
@@ -8982,7 +8982,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G297" t="n">
-        <v>1.55686259269714</v>
+        <v>1.55686247348785</v>
       </c>
       <c r="H297" t="n">
         <v>1280</v>
@@ -9069,7 +9069,7 @@
         <v>1.87699997425079</v>
       </c>
       <c r="G300" t="n">
-        <v>1.5380163192749</v>
+        <v>1.53801620006561</v>
       </c>
       <c r="H300" t="n">
         <v>1972</v>
@@ -9301,7 +9301,7 @@
         <v>1.89300000667572</v>
       </c>
       <c r="G308" t="n">
-        <v>1.55112671852112</v>
+        <v>1.55112683773041</v>
       </c>
       <c r="H308" t="n">
         <v>51626</v>
@@ -9330,7 +9330,7 @@
         <v>2</v>
       </c>
       <c r="G309" t="n">
-        <v>1.63880276679993</v>
+        <v>1.63880264759064</v>
       </c>
       <c r="H309" t="n">
         <v>57906</v>
@@ -9359,7 +9359,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G310" t="n">
-        <v>1.63060867786407</v>
+        <v>1.63060879707336</v>
       </c>
       <c r="H310" t="n">
         <v>16096</v>
@@ -9388,7 +9388,7 @@
         <v>2.01600003242493</v>
       </c>
       <c r="G311" t="n">
-        <v>1.65191304683685</v>
+        <v>1.65191316604614</v>
       </c>
       <c r="H311" t="n">
         <v>43485</v>
@@ -9417,7 +9417,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G312" t="n">
-        <v>1.64699673652649</v>
+        <v>1.6469966173172</v>
       </c>
       <c r="H312" t="n">
         <v>18453</v>
@@ -9504,7 +9504,7 @@
         <v>2.01799988746643</v>
       </c>
       <c r="G315" t="n">
-        <v>1.65355169773102</v>
+        <v>1.65355181694031</v>
       </c>
       <c r="H315" t="n">
         <v>15632</v>
@@ -9620,7 +9620,7 @@
         <v>2.22199988365173</v>
       </c>
       <c r="G319" t="n">
-        <v>1.82070958614349</v>
+        <v>1.82070970535278</v>
       </c>
       <c r="H319" t="n">
         <v>37358</v>
@@ -9649,7 +9649,7 @@
         <v>2.23200011253357</v>
       </c>
       <c r="G320" t="n">
-        <v>1.82890379428864</v>
+        <v>1.82890403270721</v>
       </c>
       <c r="H320" t="n">
         <v>71318</v>
@@ -9678,7 +9678,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G321" t="n">
-        <v>1.78629493713379</v>
+        <v>1.78629505634308</v>
       </c>
       <c r="H321" t="n">
         <v>16351</v>
@@ -9707,7 +9707,7 @@
         <v>2.21799993515015</v>
       </c>
       <c r="G322" t="n">
-        <v>1.81743204593658</v>
+        <v>1.81743216514587</v>
       </c>
       <c r="H322" t="n">
         <v>3920</v>
@@ -9736,7 +9736,7 @@
         <v>2.21600008010864</v>
       </c>
       <c r="G323" t="n">
-        <v>1.815793633461</v>
+        <v>1.81579339504242</v>
       </c>
       <c r="H323" t="n">
         <v>40297</v>
@@ -9765,7 +9765,7 @@
         <v>2.17199993133545</v>
       </c>
       <c r="G324" t="n">
-        <v>1.77973973751068</v>
+        <v>1.77973961830139</v>
       </c>
       <c r="H324" t="n">
         <v>11729</v>
@@ -9823,7 +9823,7 @@
         <v>2.24799990653992</v>
       </c>
       <c r="G326" t="n">
-        <v>1.84201419353485</v>
+        <v>1.84201407432556</v>
       </c>
       <c r="H326" t="n">
         <v>15070</v>
@@ -9852,7 +9852,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G327" t="n">
-        <v>1.79448890686035</v>
+        <v>1.79448902606964</v>
       </c>
       <c r="H327" t="n">
         <v>24197</v>
@@ -9881,7 +9881,7 @@
         <v>2.19799995422363</v>
       </c>
       <c r="G328" t="n">
-        <v>1.80104410648346</v>
+        <v>1.80104398727417</v>
       </c>
       <c r="H328" t="n">
         <v>10476</v>
@@ -9910,7 +9910,7 @@
         <v>2.2260000705719</v>
       </c>
       <c r="G329" t="n">
-        <v>1.82398748397827</v>
+        <v>1.82398724555969</v>
       </c>
       <c r="H329" t="n">
         <v>4573</v>
@@ -9939,7 +9939,7 @@
         <v>2.21600008010864</v>
       </c>
       <c r="G330" t="n">
-        <v>1.815793633461</v>
+        <v>1.81579339504242</v>
       </c>
       <c r="H330" t="n">
         <v>2603</v>
@@ -9968,7 +9968,7 @@
         <v>2.19799995422363</v>
       </c>
       <c r="G331" t="n">
-        <v>1.80104410648346</v>
+        <v>1.80104398727417</v>
       </c>
       <c r="H331" t="n">
         <v>14355</v>
@@ -10026,7 +10026,7 @@
         <v>2.10800004005432</v>
       </c>
       <c r="G333" t="n">
-        <v>1.72729802131653</v>
+        <v>1.72729814052582</v>
       </c>
       <c r="H333" t="n">
         <v>5276</v>
@@ -10055,7 +10055,7 @@
         <v>2.13199996948242</v>
       </c>
       <c r="G334" t="n">
-        <v>1.74696362018585</v>
+        <v>1.74696373939514</v>
       </c>
       <c r="H334" t="n">
         <v>2476</v>
@@ -10084,7 +10084,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G335" t="n">
-        <v>1.72893667221069</v>
+        <v>1.72893679141998</v>
       </c>
       <c r="H335" t="n">
         <v>3195</v>
@@ -10113,7 +10113,7 @@
         <v>2.15199995040894</v>
       </c>
       <c r="G336" t="n">
-        <v>1.76335155963898</v>
+        <v>1.76335144042969</v>
       </c>
       <c r="H336" t="n">
         <v>6305</v>
@@ -10142,7 +10142,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G337" t="n">
-        <v>1.80268287658691</v>
+        <v>1.8026829957962</v>
       </c>
       <c r="H337" t="n">
         <v>8773</v>
@@ -10171,7 +10171,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G338" t="n">
-        <v>1.80268287658691</v>
+        <v>1.8026829957962</v>
       </c>
       <c r="H338" t="n">
         <v>13339</v>
@@ -10200,7 +10200,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G339" t="n">
-        <v>1.83545887470245</v>
+        <v>1.83545899391174</v>
       </c>
       <c r="H339" t="n">
         <v>10440</v>
@@ -10229,7 +10229,7 @@
         <v>2.25399994850159</v>
       </c>
       <c r="G340" t="n">
-        <v>1.84693050384521</v>
+        <v>1.84693038463593</v>
       </c>
       <c r="H340" t="n">
         <v>14315</v>
@@ -10287,7 +10287,7 @@
         <v>2.20799994468689</v>
       </c>
       <c r="G342" t="n">
-        <v>1.80923795700073</v>
+        <v>1.8092383146286</v>
       </c>
       <c r="H342" t="n">
         <v>10083</v>
@@ -10316,7 +10316,7 @@
         <v>2.21199989318848</v>
       </c>
       <c r="G343" t="n">
-        <v>1.81251573562622</v>
+        <v>1.81251561641693</v>
       </c>
       <c r="H343" t="n">
         <v>17654</v>
@@ -10345,7 +10345,7 @@
         <v>2.2720000743866</v>
       </c>
       <c r="G344" t="n">
-        <v>1.86168015003204</v>
+        <v>1.86167991161346</v>
       </c>
       <c r="H344" t="n">
         <v>19071</v>
@@ -10374,7 +10374,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G345" t="n">
-        <v>1.83545887470245</v>
+        <v>1.83545899391174</v>
       </c>
       <c r="H345" t="n">
         <v>20200</v>
@@ -10432,7 +10432,7 @@
         <v>2.26799988746643</v>
       </c>
       <c r="G347" t="n">
-        <v>1.85840213298798</v>
+        <v>1.85840201377869</v>
       </c>
       <c r="H347" t="n">
         <v>10030</v>
@@ -10519,7 +10519,7 @@
         <v>2.31800007820129</v>
       </c>
       <c r="G350" t="n">
-        <v>1.89937257766724</v>
+        <v>1.89937233924866</v>
       </c>
       <c r="H350" t="n">
         <v>4160</v>
@@ -10548,7 +10548,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G351" t="n">
-        <v>1.91739904880524</v>
+        <v>1.91739940643311</v>
       </c>
       <c r="H351" t="n">
         <v>6240</v>
@@ -10577,7 +10577,7 @@
         <v>2.25600004196167</v>
       </c>
       <c r="G352" t="n">
-        <v>1.84856939315796</v>
+        <v>1.84856963157654</v>
       </c>
       <c r="H352" t="n">
         <v>9093</v>
@@ -10635,7 +10635,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G354" t="n">
-        <v>1.86823523044586</v>
+        <v>1.86823499202728</v>
       </c>
       <c r="H354" t="n">
         <v>9851</v>
@@ -10693,7 +10693,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G356" t="n">
-        <v>1.93679416179657</v>
+        <v>1.93679404258728</v>
       </c>
       <c r="H356" t="n">
         <v>8052</v>
@@ -10722,7 +10722,7 @@
         <v>2.26200008392334</v>
       </c>
       <c r="G357" t="n">
-        <v>1.93850839138031</v>
+        <v>1.93850815296173</v>
       </c>
       <c r="H357" t="n">
         <v>47650</v>
@@ -10751,7 +10751,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G358" t="n">
-        <v>1.97107374668121</v>
+        <v>1.97107362747192</v>
       </c>
       <c r="H358" t="n">
         <v>23455</v>
@@ -10780,7 +10780,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G359" t="n">
-        <v>1.97107374668121</v>
+        <v>1.97107362747192</v>
       </c>
       <c r="H359" t="n">
         <v>18785</v>
@@ -10838,7 +10838,7 @@
         <v>2.26600003242493</v>
       </c>
       <c r="G361" t="n">
-        <v>1.94193625450134</v>
+        <v>1.94193613529205</v>
       </c>
       <c r="H361" t="n">
         <v>10334</v>
@@ -10867,7 +10867,7 @@
         <v>2.26799988746643</v>
       </c>
       <c r="G362" t="n">
-        <v>1.94365000724792</v>
+        <v>1.94364988803864</v>
       </c>
       <c r="H362" t="n">
         <v>9505</v>
@@ -11012,7 +11012,7 @@
         <v>2.24799990653992</v>
       </c>
       <c r="G367" t="n">
-        <v>1.92651033401489</v>
+        <v>1.9265102148056</v>
       </c>
       <c r="H367" t="n">
         <v>1585</v>
@@ -11041,7 +11041,7 @@
         <v>2.24799990653992</v>
       </c>
       <c r="G368" t="n">
-        <v>1.92651033401489</v>
+        <v>1.9265102148056</v>
       </c>
       <c r="H368" t="n">
         <v>0</v>
@@ -11070,7 +11070,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G369" t="n">
-        <v>1.95393407344818</v>
+        <v>1.95393395423889</v>
       </c>
       <c r="H369" t="n">
         <v>20269</v>
@@ -11099,7 +11099,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G370" t="n">
-        <v>1.95393407344818</v>
+        <v>1.95393395423889</v>
       </c>
       <c r="H370" t="n">
         <v>0</v>
@@ -11128,7 +11128,7 @@
         <v>2.25600004196167</v>
       </c>
       <c r="G371" t="n">
-        <v>1.93336617946625</v>
+        <v>1.93336629867554</v>
       </c>
       <c r="H371" t="n">
         <v>4289</v>
@@ -11157,7 +11157,7 @@
         <v>2.22399997711182</v>
       </c>
       <c r="G372" t="n">
-        <v>1.90594267845154</v>
+        <v>1.90594244003296</v>
       </c>
       <c r="H372" t="n">
         <v>8910</v>
@@ -11186,7 +11186,7 @@
         <v>2.22399997711182</v>
       </c>
       <c r="G373" t="n">
-        <v>1.90594267845154</v>
+        <v>1.90594244003296</v>
       </c>
       <c r="H373" t="n">
         <v>0</v>
@@ -11302,7 +11302,7 @@
         <v>2.21799993515015</v>
       </c>
       <c r="G377" t="n">
-        <v>1.90080046653748</v>
+        <v>1.90080070495605</v>
       </c>
       <c r="H377" t="n">
         <v>500</v>
@@ -11331,7 +11331,7 @@
         <v>2.23399996757507</v>
       </c>
       <c r="G378" t="n">
-        <v>1.91451251506805</v>
+        <v>1.91451239585876</v>
       </c>
       <c r="H378" t="n">
         <v>12050</v>
@@ -11360,7 +11360,7 @@
         <v>2.20199990272522</v>
       </c>
       <c r="G379" t="n">
-        <v>1.88708877563477</v>
+        <v>1.88708889484406</v>
       </c>
       <c r="H379" t="n">
         <v>17691</v>
@@ -11389,7 +11389,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G380" t="n">
-        <v>1.87680494785309</v>
+        <v>1.87680518627167</v>
       </c>
       <c r="H380" t="n">
         <v>3841</v>
@@ -11418,7 +11418,7 @@
         <v>2.23799991607666</v>
       </c>
       <c r="G381" t="n">
-        <v>1.91794049739838</v>
+        <v>1.9179402589798</v>
       </c>
       <c r="H381" t="n">
         <v>6850</v>
@@ -11476,7 +11476,7 @@
         <v>2.18199992179871</v>
       </c>
       <c r="G383" t="n">
-        <v>1.86994886398315</v>
+        <v>1.86994922161102</v>
       </c>
       <c r="H383" t="n">
         <v>1040</v>
@@ -11563,7 +11563,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G386" t="n">
-        <v>1.90251457691193</v>
+        <v>1.90251469612122</v>
       </c>
       <c r="H386" t="n">
         <v>12328</v>
@@ -11679,7 +11679,7 @@
         <v>2.23399996757507</v>
       </c>
       <c r="G390" t="n">
-        <v>1.91451251506805</v>
+        <v>1.91451239585876</v>
       </c>
       <c r="H390" t="n">
         <v>7104</v>
@@ -11708,7 +11708,7 @@
         <v>2.23799991607666</v>
       </c>
       <c r="G391" t="n">
-        <v>1.91794049739838</v>
+        <v>1.9179402589798</v>
       </c>
       <c r="H391" t="n">
         <v>125</v>
@@ -11737,7 +11737,7 @@
         <v>2.25600004196167</v>
       </c>
       <c r="G392" t="n">
-        <v>1.93336617946625</v>
+        <v>1.93336629867554</v>
       </c>
       <c r="H392" t="n">
         <v>4625</v>
@@ -11795,7 +11795,7 @@
         <v>2.29200005531311</v>
       </c>
       <c r="G394" t="n">
-        <v>1.96421790122986</v>
+        <v>1.96421778202057</v>
       </c>
       <c r="H394" t="n">
         <v>3374</v>
@@ -11824,7 +11824,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G395" t="n">
-        <v>1.96250379085541</v>
+        <v>1.96250355243683</v>
       </c>
       <c r="H395" t="n">
         <v>2472</v>
@@ -11853,7 +11853,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G396" t="n">
-        <v>1.97107374668121</v>
+        <v>1.97107362747192</v>
       </c>
       <c r="H396" t="n">
         <v>2881</v>
@@ -11882,7 +11882,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G397" t="n">
-        <v>1.98821353912354</v>
+        <v>1.98821341991425</v>
       </c>
       <c r="H397" t="n">
         <v>4950</v>
@@ -11911,7 +11911,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G398" t="n">
-        <v>1.98821353912354</v>
+        <v>1.98821341991425</v>
       </c>
       <c r="H398" t="n">
         <v>1201</v>
@@ -11940,7 +11940,7 @@
         <v>2.31800007820129</v>
       </c>
       <c r="G399" t="n">
-        <v>1.98649966716766</v>
+        <v>1.98649942874908</v>
       </c>
       <c r="H399" t="n">
         <v>506</v>
@@ -12027,7 +12027,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G402" t="n">
-        <v>2.12533164024353</v>
+        <v>2.12533140182495</v>
       </c>
       <c r="H402" t="n">
         <v>107928</v>
@@ -12056,7 +12056,7 @@
         <v>2.43400001525879</v>
       </c>
       <c r="G403" t="n">
-        <v>2.08591032028198</v>
+        <v>2.0859100818634</v>
       </c>
       <c r="H403" t="n">
         <v>66474</v>
@@ -12085,7 +12085,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G404" t="n">
-        <v>2.0567729473114</v>
+        <v>2.05677270889282</v>
       </c>
       <c r="H404" t="n">
         <v>20365</v>
@@ -12143,7 +12143,7 @@
         <v>2.42799997329712</v>
       </c>
       <c r="G406" t="n">
-        <v>2.0807683467865</v>
+        <v>2.08076810836792</v>
       </c>
       <c r="H406" t="n">
         <v>5713</v>
@@ -12172,7 +12172,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G407" t="n">
-        <v>2.06534266471863</v>
+        <v>2.06534242630005</v>
       </c>
       <c r="H407" t="n">
         <v>8713</v>
@@ -12201,7 +12201,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G408" t="n">
-        <v>2.06534266471863</v>
+        <v>2.06534242630005</v>
       </c>
       <c r="H408" t="n">
         <v>0</v>
@@ -12317,7 +12317,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G412" t="n">
-        <v>2.12533164024353</v>
+        <v>2.12533140182495</v>
       </c>
       <c r="H412" t="n">
         <v>13189</v>
@@ -12375,7 +12375,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G414" t="n">
-        <v>2.10819172859192</v>
+        <v>2.1081919670105</v>
       </c>
       <c r="H414" t="n">
         <v>12585</v>
@@ -12404,7 +12404,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G415" t="n">
-        <v>2.09962201118469</v>
+        <v>2.09962177276611</v>
       </c>
       <c r="H415" t="n">
         <v>3641</v>
@@ -12607,7 +12607,7 @@
         <v>2.44799995422363</v>
       </c>
       <c r="G422" t="n">
-        <v>2.09790778160095</v>
+        <v>2.09790802001953</v>
       </c>
       <c r="H422" t="n">
         <v>3874</v>
@@ -12636,7 +12636,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G423" t="n">
-        <v>2.11676168441772</v>
+        <v>2.1167619228363</v>
       </c>
       <c r="H423" t="n">
         <v>2588</v>
@@ -12694,7 +12694,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G425" t="n">
-        <v>2.09962201118469</v>
+        <v>2.09962177276611</v>
       </c>
       <c r="H425" t="n">
         <v>5724</v>
@@ -12781,7 +12781,7 @@
         <v>2.41199994087219</v>
       </c>
       <c r="G428" t="n">
-        <v>2.06705665588379</v>
+        <v>2.06705641746521</v>
       </c>
       <c r="H428" t="n">
         <v>650</v>
@@ -12810,7 +12810,7 @@
         <v>2.4760000705719</v>
       </c>
       <c r="G429" t="n">
-        <v>2.12190389633179</v>
+        <v>2.12190365791321</v>
       </c>
       <c r="H429" t="n">
         <v>2150</v>
@@ -12839,7 +12839,7 @@
         <v>2.45799994468689</v>
       </c>
       <c r="G430" t="n">
-        <v>2.10647797584534</v>
+        <v>2.10647773742676</v>
       </c>
       <c r="H430" t="n">
         <v>4919</v>
@@ -12868,7 +12868,7 @@
         <v>2.45799994468689</v>
       </c>
       <c r="G431" t="n">
-        <v>2.10647797584534</v>
+        <v>2.10647773742676</v>
       </c>
       <c r="H431" t="n">
         <v>0</v>
@@ -12897,7 +12897,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G432" t="n">
-        <v>2.10819172859192</v>
+        <v>2.1081919670105</v>
       </c>
       <c r="H432" t="n">
         <v>150</v>
@@ -12926,7 +12926,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G433" t="n">
-        <v>2.09962201118469</v>
+        <v>2.09962177276611</v>
       </c>
       <c r="H433" t="n">
         <v>1120</v>
@@ -13042,7 +13042,7 @@
         <v>2.44799995422363</v>
       </c>
       <c r="G437" t="n">
-        <v>2.09790778160095</v>
+        <v>2.09790802001953</v>
       </c>
       <c r="H437" t="n">
         <v>5750</v>
@@ -13100,7 +13100,7 @@
         <v>2.44799995422363</v>
       </c>
       <c r="G439" t="n">
-        <v>2.09790778160095</v>
+        <v>2.09790802001953</v>
       </c>
       <c r="H439" t="n">
         <v>10563</v>
@@ -13129,7 +13129,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G440" t="n">
-        <v>2.17675089836121</v>
+        <v>2.17675113677979</v>
       </c>
       <c r="H440" t="n">
         <v>17588</v>
@@ -13158,7 +13158,7 @@
         <v>2.5</v>
       </c>
       <c r="G441" t="n">
-        <v>2.14247155189514</v>
+        <v>2.14247131347656</v>
       </c>
       <c r="H441" t="n">
         <v>3339</v>
@@ -13187,7 +13187,7 @@
         <v>2.48799991607666</v>
       </c>
       <c r="G442" t="n">
-        <v>2.13218760490417</v>
+        <v>2.1321873664856</v>
       </c>
       <c r="H442" t="n">
         <v>1580</v>
@@ -13216,7 +13216,7 @@
         <v>2.48600006103516</v>
       </c>
       <c r="G443" t="n">
-        <v>2.13047361373901</v>
+        <v>2.13047385215759</v>
       </c>
       <c r="H443" t="n">
         <v>8200</v>
@@ -13245,7 +13245,7 @@
         <v>2.48799991607666</v>
       </c>
       <c r="G444" t="n">
-        <v>2.13218760490417</v>
+        <v>2.1321873664856</v>
       </c>
       <c r="H444" t="n">
         <v>5230</v>
@@ -13274,7 +13274,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G445" t="n">
-        <v>2.15961122512817</v>
+        <v>2.15961098670959</v>
       </c>
       <c r="H445" t="n">
         <v>3123</v>
@@ -13303,7 +13303,7 @@
         <v>2.47199988365173</v>
       </c>
       <c r="G446" t="n">
-        <v>2.11847543716431</v>
+        <v>2.11847567558289</v>
       </c>
       <c r="H446" t="n">
         <v>7321</v>
@@ -13332,7 +13332,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G447" t="n">
-        <v>2.11676168441772</v>
+        <v>2.1167619228363</v>
       </c>
       <c r="H447" t="n">
         <v>3053</v>
@@ -13361,7 +13361,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G448" t="n">
-        <v>2.09105205535889</v>
+        <v>2.09105229377747</v>
       </c>
       <c r="H448" t="n">
         <v>6572</v>
@@ -13390,7 +13390,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G449" t="n">
-        <v>2.09962201118469</v>
+        <v>2.09962177276611</v>
       </c>
       <c r="H449" t="n">
         <v>450</v>
@@ -13477,7 +13477,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G452" t="n">
-        <v>2.09105205535889</v>
+        <v>2.09105229377747</v>
       </c>
       <c r="H452" t="n">
         <v>5134</v>
@@ -13622,7 +13622,7 @@
         <v>2.45199990272522</v>
       </c>
       <c r="G457" t="n">
-        <v>2.10133600234985</v>
+        <v>2.10133576393127</v>
       </c>
       <c r="H457" t="n">
         <v>4958</v>
@@ -13651,7 +13651,7 @@
         <v>2.48799991607666</v>
       </c>
       <c r="G458" t="n">
-        <v>2.13218760490417</v>
+        <v>2.1321873664856</v>
       </c>
       <c r="H458" t="n">
         <v>220</v>
@@ -13854,7 +13854,7 @@
         <v>2.50799989700317</v>
       </c>
       <c r="G465" t="n">
-        <v>2.14932703971863</v>
+        <v>2.14932727813721</v>
       </c>
       <c r="H465" t="n">
         <v>747</v>
@@ -13999,7 +13999,7 @@
         <v>2.4760000705719</v>
       </c>
       <c r="G470" t="n">
-        <v>2.12190389633179</v>
+        <v>2.12190365791321</v>
       </c>
       <c r="H470" t="n">
         <v>8809</v>
@@ -14057,7 +14057,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G472" t="n">
-        <v>2.12533164024353</v>
+        <v>2.12533140182495</v>
       </c>
       <c r="H472" t="n">
         <v>8551</v>
@@ -14115,7 +14115,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G474" t="n">
-        <v>2.15104126930237</v>
+        <v>2.15104150772095</v>
       </c>
       <c r="H474" t="n">
         <v>6956</v>
@@ -14202,7 +14202,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G477" t="n">
-        <v>2.09962201118469</v>
+        <v>2.09962177276611</v>
       </c>
       <c r="H477" t="n">
         <v>893</v>
@@ -14289,7 +14289,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G480" t="n">
-        <v>2.0567729473114</v>
+        <v>2.05677270889282</v>
       </c>
       <c r="H480" t="n">
         <v>6507</v>
@@ -14434,7 +14434,7 @@
         <v>2.41599988937378</v>
       </c>
       <c r="G485" t="n">
-        <v>2.07048416137695</v>
+        <v>2.07048439979553</v>
       </c>
       <c r="H485" t="n">
         <v>14203</v>
@@ -14492,7 +14492,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G487" t="n">
-        <v>2.06534266471863</v>
+        <v>2.06534242630005</v>
       </c>
       <c r="H487" t="n">
         <v>3267</v>
@@ -14521,7 +14521,7 @@
         <v>2.39199995994568</v>
       </c>
       <c r="G488" t="n">
-        <v>2.0499165058136</v>
+        <v>2.04991674423218</v>
       </c>
       <c r="H488" t="n">
         <v>1156</v>
@@ -14608,7 +14608,7 @@
         <v>2.44799995422363</v>
       </c>
       <c r="G491" t="n">
-        <v>2.09790778160095</v>
+        <v>2.09790802001953</v>
       </c>
       <c r="H491" t="n">
         <v>2342</v>
@@ -14637,7 +14637,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G492" t="n">
-        <v>2.12533164024353</v>
+        <v>2.12533140182495</v>
       </c>
       <c r="H492" t="n">
         <v>182</v>
@@ -14695,7 +14695,7 @@
         <v>2.48399996757507</v>
       </c>
       <c r="G494" t="n">
-        <v>2.12875938415527</v>
+        <v>2.12875962257385</v>
       </c>
       <c r="H494" t="n">
         <v>150</v>
@@ -14724,7 +14724,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G495" t="n">
-        <v>2.12533164024353</v>
+        <v>2.12533140182495</v>
       </c>
       <c r="H495" t="n">
         <v>1145</v>
@@ -14753,7 +14753,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G496" t="n">
-        <v>2.11676168441772</v>
+        <v>2.1167619228363</v>
       </c>
       <c r="H496" t="n">
         <v>950</v>
@@ -14782,7 +14782,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G497" t="n">
-        <v>2.11676168441772</v>
+        <v>2.1167619228363</v>
       </c>
       <c r="H497" t="n">
         <v>0</v>
@@ -14811,7 +14811,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G498" t="n">
-        <v>2.11676168441772</v>
+        <v>2.1167619228363</v>
       </c>
       <c r="H498" t="n">
         <v>0</v>
@@ -14840,7 +14840,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G499" t="n">
-        <v>2.11676168441772</v>
+        <v>2.1167619228363</v>
       </c>
       <c r="H499" t="n">
         <v>0</v>
@@ -14898,7 +14898,7 @@
         <v>2.43600010871887</v>
       </c>
       <c r="G501" t="n">
-        <v>2.08762407302856</v>
+        <v>2.08762431144714</v>
       </c>
       <c r="H501" t="n">
         <v>2450</v>
@@ -15072,7 +15072,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G507" t="n">
-        <v>2.09962201118469</v>
+        <v>2.09962177276611</v>
       </c>
       <c r="H507" t="n">
         <v>2401</v>
@@ -15101,7 +15101,7 @@
         <v>2.44799995422363</v>
       </c>
       <c r="G508" t="n">
-        <v>2.09790778160095</v>
+        <v>2.09790802001953</v>
       </c>
       <c r="H508" t="n">
         <v>2286</v>
@@ -15130,7 +15130,7 @@
         <v>2.44799995422363</v>
       </c>
       <c r="G509" t="n">
-        <v>2.09790778160095</v>
+        <v>2.09790802001953</v>
       </c>
       <c r="H509" t="n">
         <v>0</v>
@@ -15159,7 +15159,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G510" t="n">
-        <v>2.09962201118469</v>
+        <v>2.09962177276611</v>
       </c>
       <c r="H510" t="n">
         <v>370</v>
@@ -15188,7 +15188,7 @@
         <v>2.41599988937378</v>
       </c>
       <c r="G511" t="n">
-        <v>2.07048416137695</v>
+        <v>2.07048439979553</v>
       </c>
       <c r="H511" t="n">
         <v>4705</v>
@@ -15217,7 +15217,7 @@
         <v>2.4760000705719</v>
       </c>
       <c r="G512" t="n">
-        <v>2.12190389633179</v>
+        <v>2.12190365791321</v>
       </c>
       <c r="H512" t="n">
         <v>1515</v>
@@ -15246,7 +15246,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G513" t="n">
-        <v>2.09962201118469</v>
+        <v>2.09962177276611</v>
       </c>
       <c r="H513" t="n">
         <v>8107</v>
@@ -15304,7 +15304,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G515" t="n">
-        <v>2.0567729473114</v>
+        <v>2.05677270889282</v>
       </c>
       <c r="H515" t="n">
         <v>7000</v>
@@ -15362,7 +15362,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G517" t="n">
-        <v>2.09105205535889</v>
+        <v>2.09105229377747</v>
       </c>
       <c r="H517" t="n">
         <v>5717</v>
@@ -15391,7 +15391,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G518" t="n">
-        <v>2.09105205535889</v>
+        <v>2.09105229377747</v>
       </c>
       <c r="H518" t="n">
         <v>10837</v>
@@ -15594,7 +15594,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G525" t="n">
-        <v>2.0567729473114</v>
+        <v>2.05677270889282</v>
       </c>
       <c r="H525" t="n">
         <v>398</v>
@@ -15623,7 +15623,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G526" t="n">
-        <v>2.0567729473114</v>
+        <v>2.05677270889282</v>
       </c>
       <c r="H526" t="n">
         <v>5700</v>
@@ -15652,7 +15652,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G527" t="n">
-        <v>2.0224928855896</v>
+        <v>2.02249264717102</v>
       </c>
       <c r="H527" t="n">
         <v>6064</v>
@@ -15681,7 +15681,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G528" t="n">
-        <v>2.0224928855896</v>
+        <v>2.02249264717102</v>
       </c>
       <c r="H528" t="n">
         <v>3718</v>
@@ -15710,7 +15710,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G529" t="n">
-        <v>2.0224928855896</v>
+        <v>2.02249264717102</v>
       </c>
       <c r="H529" t="n">
         <v>0</v>
@@ -15739,7 +15739,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G530" t="n">
-        <v>2.09962201118469</v>
+        <v>2.09962177276611</v>
       </c>
       <c r="H530" t="n">
         <v>9824</v>
@@ -15855,7 +15855,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G534" t="n">
-        <v>2.0567729473114</v>
+        <v>2.05677270889282</v>
       </c>
       <c r="H534" t="n">
         <v>361</v>
@@ -15884,7 +15884,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G535" t="n">
-        <v>2.0567729473114</v>
+        <v>2.05677270889282</v>
       </c>
       <c r="H535" t="n">
         <v>1190</v>
@@ -15942,7 +15942,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G537" t="n">
-        <v>2.01392292976379</v>
+        <v>2.01392316818237</v>
       </c>
       <c r="H537" t="n">
         <v>4028</v>
@@ -16029,7 +16029,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G540" t="n">
-        <v>2.0567729473114</v>
+        <v>2.05677270889282</v>
       </c>
       <c r="H540" t="n">
         <v>910</v>
@@ -16058,7 +16058,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G541" t="n">
-        <v>2.09105205535889</v>
+        <v>2.09105229377747</v>
       </c>
       <c r="H541" t="n">
         <v>6273</v>
@@ -16087,7 +16087,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G542" t="n">
-        <v>2.09105205535889</v>
+        <v>2.09105229377747</v>
       </c>
       <c r="H542" t="n">
         <v>0</v>
@@ -16116,7 +16116,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G543" t="n">
-        <v>2.09962201118469</v>
+        <v>2.09962177276611</v>
       </c>
       <c r="H543" t="n">
         <v>100</v>
@@ -16145,7 +16145,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G544" t="n">
-        <v>2.09962201118469</v>
+        <v>2.09962177276611</v>
       </c>
       <c r="H544" t="n">
         <v>2265</v>
@@ -16174,7 +16174,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G545" t="n">
-        <v>2.09962201118469</v>
+        <v>2.09962177276611</v>
       </c>
       <c r="H545" t="n">
         <v>0</v>
@@ -16203,7 +16203,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G546" t="n">
-        <v>2.0224928855896</v>
+        <v>2.02249264717102</v>
       </c>
       <c r="H546" t="n">
         <v>4243</v>
@@ -16464,7 +16464,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G555" t="n">
-        <v>2.06534266471863</v>
+        <v>2.06534242630005</v>
       </c>
       <c r="H555" t="n">
         <v>1952</v>
@@ -16522,7 +16522,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G557" t="n">
-        <v>2.11676168441772</v>
+        <v>2.1167619228363</v>
       </c>
       <c r="H557" t="n">
         <v>24020</v>
@@ -16551,7 +16551,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G558" t="n">
-        <v>2.10819172859192</v>
+        <v>2.1081919670105</v>
       </c>
       <c r="H558" t="n">
         <v>7260</v>
@@ -16580,7 +16580,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G559" t="n">
-        <v>2.06534266471863</v>
+        <v>2.06534242630005</v>
       </c>
       <c r="H559" t="n">
         <v>459</v>
@@ -16609,7 +16609,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G560" t="n">
-        <v>2.06534266471863</v>
+        <v>2.06534242630005</v>
       </c>
       <c r="H560" t="n">
         <v>2100</v>
@@ -16638,7 +16638,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G561" t="n">
-        <v>2.09105205535889</v>
+        <v>2.09105229377747</v>
       </c>
       <c r="H561" t="n">
         <v>8100</v>
@@ -16725,7 +16725,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G564" t="n">
-        <v>2.10819172859192</v>
+        <v>2.1081919670105</v>
       </c>
       <c r="H564" t="n">
         <v>95554</v>
@@ -16754,7 +16754,7 @@
         <v>2.5</v>
       </c>
       <c r="G565" t="n">
-        <v>2.14247155189514</v>
+        <v>2.14247131347656</v>
       </c>
       <c r="H565" t="n">
         <v>21097</v>
@@ -16783,7 +16783,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G566" t="n">
-        <v>2.12533164024353</v>
+        <v>2.12533140182495</v>
       </c>
       <c r="H566" t="n">
         <v>11930</v>
@@ -16812,7 +16812,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G567" t="n">
-        <v>2.10819172859192</v>
+        <v>2.1081919670105</v>
       </c>
       <c r="H567" t="n">
         <v>4589</v>
@@ -16841,7 +16841,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G568" t="n">
-        <v>2.10819172859192</v>
+        <v>2.1081919670105</v>
       </c>
       <c r="H568" t="n">
         <v>0</v>
@@ -16899,7 +16899,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G570" t="n">
-        <v>2.09962201118469</v>
+        <v>2.09962177276611</v>
       </c>
       <c r="H570" t="n">
         <v>1093</v>
@@ -16928,7 +16928,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G571" t="n">
-        <v>2.10819172859192</v>
+        <v>2.1081919670105</v>
       </c>
       <c r="H571" t="n">
         <v>9876</v>
@@ -16957,7 +16957,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G572" t="n">
-        <v>2.09105205535889</v>
+        <v>2.09105229377747</v>
       </c>
       <c r="H572" t="n">
         <v>2665</v>
@@ -16986,7 +16986,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G573" t="n">
-        <v>2.09105205535889</v>
+        <v>2.09105229377747</v>
       </c>
       <c r="H573" t="n">
         <v>2589</v>
@@ -17015,7 +17015,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G574" t="n">
-        <v>2.09962201118469</v>
+        <v>2.09962177276611</v>
       </c>
       <c r="H574" t="n">
         <v>7837</v>
@@ -17044,7 +17044,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G575" t="n">
-        <v>2.10819172859192</v>
+        <v>2.1081919670105</v>
       </c>
       <c r="H575" t="n">
         <v>14550</v>
@@ -17073,7 +17073,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G576" t="n">
-        <v>2.09962201118469</v>
+        <v>2.09962177276611</v>
       </c>
       <c r="H576" t="n">
         <v>7199</v>
@@ -17131,7 +17131,7 @@
         <v>2.5</v>
       </c>
       <c r="G578" t="n">
-        <v>2.14247155189514</v>
+        <v>2.14247131347656</v>
       </c>
       <c r="H578" t="n">
         <v>2736</v>
@@ -17160,7 +17160,7 @@
         <v>2.5</v>
       </c>
       <c r="G579" t="n">
-        <v>2.14247155189514</v>
+        <v>2.14247131347656</v>
       </c>
       <c r="H579" t="n">
         <v>4410</v>
@@ -17218,7 +17218,7 @@
         <v>2.5</v>
       </c>
       <c r="G581" t="n">
-        <v>2.14247155189514</v>
+        <v>2.14247131347656</v>
       </c>
       <c r="H581" t="n">
         <v>8524</v>
@@ -17247,7 +17247,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G582" t="n">
-        <v>2.16818118095398</v>
+        <v>2.1681809425354</v>
       </c>
       <c r="H582" t="n">
         <v>1455</v>
@@ -17276,7 +17276,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G583" t="n">
-        <v>2.16818118095398</v>
+        <v>2.1681809425354</v>
       </c>
       <c r="H583" t="n">
         <v>2779</v>
@@ -17305,7 +17305,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G584" t="n">
-        <v>2.15961122512817</v>
+        <v>2.15961098670959</v>
       </c>
       <c r="H584" t="n">
         <v>21594</v>
@@ -17334,7 +17334,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G585" t="n">
-        <v>2.15961122512817</v>
+        <v>2.15961098670959</v>
       </c>
       <c r="H585" t="n">
         <v>4446</v>
@@ -17363,7 +17363,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G586" t="n">
-        <v>2.16818118095398</v>
+        <v>2.1681809425354</v>
       </c>
       <c r="H586" t="n">
         <v>6585</v>
@@ -17392,7 +17392,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G587" t="n">
-        <v>2.15961122512817</v>
+        <v>2.15961098670959</v>
       </c>
       <c r="H587" t="n">
         <v>17966</v>
@@ -17421,7 +17421,7 @@
         <v>2.5</v>
       </c>
       <c r="G588" t="n">
-        <v>2.14247155189514</v>
+        <v>2.14247131347656</v>
       </c>
       <c r="H588" t="n">
         <v>216</v>
@@ -17450,7 +17450,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G589" t="n">
-        <v>2.15961122512817</v>
+        <v>2.15961098670959</v>
       </c>
       <c r="H589" t="n">
         <v>5280</v>
@@ -17479,7 +17479,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G590" t="n">
-        <v>2.17675089836121</v>
+        <v>2.17675113677979</v>
       </c>
       <c r="H590" t="n">
         <v>47108</v>
@@ -17508,7 +17508,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G591" t="n">
-        <v>2.18532085418701</v>
+        <v>2.18532061576843</v>
       </c>
       <c r="H591" t="n">
         <v>11111</v>
@@ -17624,7 +17624,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G595" t="n">
-        <v>2.32243919372559</v>
+        <v>2.32243895530701</v>
       </c>
       <c r="H595" t="n">
         <v>49282</v>
@@ -17653,7 +17653,7 @@
         <v>2.75</v>
       </c>
       <c r="G596" t="n">
-        <v>2.35671830177307</v>
+        <v>2.35671854019165</v>
       </c>
       <c r="H596" t="n">
         <v>31138</v>
@@ -17682,7 +17682,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G597" t="n">
-        <v>2.44241714477539</v>
+        <v>2.44241738319397</v>
       </c>
       <c r="H597" t="n">
         <v>71018</v>
@@ -17711,7 +17711,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G598" t="n">
-        <v>2.49383664131165</v>
+        <v>2.49383687973022</v>
       </c>
       <c r="H598" t="n">
         <v>37011</v>
@@ -17856,7 +17856,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G603" t="n">
-        <v>2.53668642044067</v>
+        <v>2.53668594360352</v>
       </c>
       <c r="H603" t="n">
         <v>32941</v>
@@ -17885,7 +17885,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G604" t="n">
-        <v>2.57953572273254</v>
+        <v>2.57953548431396</v>
       </c>
       <c r="H604" t="n">
         <v>152006</v>
@@ -17914,7 +17914,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G605" t="n">
-        <v>2.59667539596558</v>
+        <v>2.596675157547</v>
       </c>
       <c r="H605" t="n">
         <v>23766</v>
@@ -17943,7 +17943,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G606" t="n">
-        <v>2.61381506919861</v>
+        <v>2.61381530761719</v>
       </c>
       <c r="H606" t="n">
         <v>17863</v>
@@ -17972,7 +17972,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G607" t="n">
-        <v>2.55382585525513</v>
+        <v>2.55382609367371</v>
       </c>
       <c r="H607" t="n">
         <v>22011</v>
@@ -18001,7 +18001,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G608" t="n">
-        <v>2.63447332382202</v>
+        <v>2.63447308540344</v>
       </c>
       <c r="H608" t="n">
         <v>30164</v>
@@ -18088,7 +18088,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G611" t="n">
-        <v>2.61655139923096</v>
+        <v>2.61655163764954</v>
       </c>
       <c r="H611" t="n">
         <v>13758</v>
@@ -18465,7 +18465,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G624" t="n">
-        <v>2.57174754142761</v>
+        <v>2.57174730300903</v>
       </c>
       <c r="H624" t="n">
         <v>2231</v>
@@ -18494,7 +18494,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G625" t="n">
-        <v>2.57174754142761</v>
+        <v>2.57174730300903</v>
       </c>
       <c r="H625" t="n">
         <v>3450</v>
@@ -18668,7 +18668,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G631" t="n">
-        <v>2.53590416908264</v>
+        <v>2.53590440750122</v>
       </c>
       <c r="H631" t="n">
         <v>519</v>
@@ -18697,7 +18697,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G632" t="n">
-        <v>2.49110054969788</v>
+        <v>2.4911003112793</v>
       </c>
       <c r="H632" t="n">
         <v>100</v>
@@ -18900,7 +18900,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G639" t="n">
-        <v>2.53590416908264</v>
+        <v>2.53590440750122</v>
       </c>
       <c r="H639" t="n">
         <v>2002</v>
@@ -18929,7 +18929,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G640" t="n">
-        <v>2.53590416908264</v>
+        <v>2.53590440750122</v>
       </c>
       <c r="H640" t="n">
         <v>1371</v>
@@ -18958,7 +18958,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G641" t="n">
-        <v>2.53590416908264</v>
+        <v>2.53590440750122</v>
       </c>
       <c r="H641" t="n">
         <v>230</v>
@@ -18987,7 +18987,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G642" t="n">
-        <v>2.53590416908264</v>
+        <v>2.53590440750122</v>
       </c>
       <c r="H642" t="n">
         <v>418</v>
@@ -19016,7 +19016,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G643" t="n">
-        <v>2.53590416908264</v>
+        <v>2.53590440750122</v>
       </c>
       <c r="H643" t="n">
         <v>0</v>
@@ -19074,7 +19074,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G645" t="n">
-        <v>2.53590416908264</v>
+        <v>2.53590440750122</v>
       </c>
       <c r="H645" t="n">
         <v>2500</v>
@@ -19451,7 +19451,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G658" t="n">
-        <v>2.77784585952759</v>
+        <v>2.77784562110901</v>
       </c>
       <c r="H658" t="n">
         <v>16052</v>
@@ -19480,7 +19480,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G659" t="n">
-        <v>2.77784585952759</v>
+        <v>2.77784562110901</v>
       </c>
       <c r="H659" t="n">
         <v>15393</v>
@@ -19654,7 +19654,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G665" t="n">
-        <v>2.76888513565063</v>
+        <v>2.76888489723206</v>
       </c>
       <c r="H665" t="n">
         <v>3767</v>
@@ -19683,7 +19683,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G666" t="n">
-        <v>2.71512031555176</v>
+        <v>2.71512007713318</v>
       </c>
       <c r="H666" t="n">
         <v>9512</v>
@@ -19712,7 +19712,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G667" t="n">
-        <v>2.75096321105957</v>
+        <v>2.75096344947815</v>
       </c>
       <c r="H667" t="n">
         <v>2365</v>
@@ -19741,7 +19741,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G668" t="n">
-        <v>2.67031621932983</v>
+        <v>2.67031645774841</v>
       </c>
       <c r="H668" t="n">
         <v>16566</v>
@@ -19770,7 +19770,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G669" t="n">
-        <v>2.63447332382202</v>
+        <v>2.63447308540344</v>
       </c>
       <c r="H669" t="n">
         <v>764</v>
@@ -19828,7 +19828,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G671" t="n">
-        <v>2.75096321105957</v>
+        <v>2.75096344947815</v>
       </c>
       <c r="H671" t="n">
         <v>1370</v>
@@ -19915,7 +19915,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G674" t="n">
-        <v>2.65239477157593</v>
+        <v>2.65239453315735</v>
       </c>
       <c r="H674" t="n">
         <v>1869</v>
@@ -19944,7 +19944,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G675" t="n">
-        <v>2.65239477157593</v>
+        <v>2.65239453315735</v>
       </c>
       <c r="H675" t="n">
         <v>0</v>
@@ -20002,7 +20002,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G677" t="n">
-        <v>2.67031621932983</v>
+        <v>2.67031645774841</v>
       </c>
       <c r="H677" t="n">
         <v>1645</v>
@@ -20031,7 +20031,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G678" t="n">
-        <v>2.67031621932983</v>
+        <v>2.67031645774841</v>
       </c>
       <c r="H678" t="n">
         <v>0</v>
@@ -20147,7 +20147,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G682" t="n">
-        <v>2.75096321105957</v>
+        <v>2.75096344947815</v>
       </c>
       <c r="H682" t="n">
         <v>10777</v>
@@ -20176,7 +20176,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G683" t="n">
-        <v>2.73304176330566</v>
+        <v>2.73304200172424</v>
       </c>
       <c r="H683" t="n">
         <v>1575</v>
@@ -20292,7 +20292,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G687" t="n">
-        <v>2.71512031555176</v>
+        <v>2.71512007713318</v>
       </c>
       <c r="H687" t="n">
         <v>2971</v>
@@ -20321,7 +20321,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G688" t="n">
-        <v>2.75096321105957</v>
+        <v>2.75096344947815</v>
       </c>
       <c r="H688" t="n">
         <v>5155</v>
@@ -20350,7 +20350,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G689" t="n">
-        <v>2.71512031555176</v>
+        <v>2.71512007713318</v>
       </c>
       <c r="H689" t="n">
         <v>7369</v>
@@ -20379,7 +20379,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G690" t="n">
-        <v>2.69719886779785</v>
+        <v>2.69719862937927</v>
       </c>
       <c r="H690" t="n">
         <v>5352</v>
@@ -20408,7 +20408,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G691" t="n">
-        <v>2.67927694320679</v>
+        <v>2.67927718162537</v>
       </c>
       <c r="H691" t="n">
         <v>996</v>
@@ -20553,7 +20553,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G696" t="n">
-        <v>2.73304176330566</v>
+        <v>2.73304200172424</v>
       </c>
       <c r="H696" t="n">
         <v>20211</v>
@@ -20582,7 +20582,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G697" t="n">
-        <v>2.75096321105957</v>
+        <v>2.75096344947815</v>
       </c>
       <c r="H697" t="n">
         <v>927</v>
@@ -20669,7 +20669,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G700" t="n">
-        <v>2.75096321105957</v>
+        <v>2.75096344947815</v>
       </c>
       <c r="H700" t="n">
         <v>3068</v>
@@ -20698,7 +20698,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G701" t="n">
-        <v>2.75096321105957</v>
+        <v>2.75096344947815</v>
       </c>
       <c r="H701" t="n">
         <v>1928</v>
@@ -20727,7 +20727,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G702" t="n">
-        <v>2.75096321105957</v>
+        <v>2.75096344947815</v>
       </c>
       <c r="H702" t="n">
         <v>0</v>
@@ -20785,7 +20785,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G704" t="n">
-        <v>2.65239477157593</v>
+        <v>2.65239453315735</v>
       </c>
       <c r="H704" t="n">
         <v>4663</v>
@@ -20814,7 +20814,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G705" t="n">
-        <v>2.69719886779785</v>
+        <v>2.69719862937927</v>
       </c>
       <c r="H705" t="n">
         <v>193</v>
@@ -20843,7 +20843,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G706" t="n">
-        <v>2.67927694320679</v>
+        <v>2.67927718162537</v>
       </c>
       <c r="H706" t="n">
         <v>6101</v>
@@ -20901,7 +20901,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G708" t="n">
-        <v>2.63447332382202</v>
+        <v>2.63447308540344</v>
       </c>
       <c r="H708" t="n">
         <v>4328</v>
@@ -20930,7 +20930,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G709" t="n">
-        <v>2.62551259994507</v>
+        <v>2.62551236152649</v>
       </c>
       <c r="H709" t="n">
         <v>1121</v>
@@ -21046,7 +21046,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G713" t="n">
-        <v>2.61655139923096</v>
+        <v>2.61655163764954</v>
       </c>
       <c r="H713" t="n">
         <v>1</v>
@@ -21191,7 +21191,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G718" t="n">
-        <v>2.57174754142761</v>
+        <v>2.57174730300903</v>
       </c>
       <c r="H718" t="n">
         <v>1700</v>
@@ -21249,7 +21249,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G720" t="n">
-        <v>2.61655139923096</v>
+        <v>2.61655163764954</v>
       </c>
       <c r="H720" t="n">
         <v>1330</v>
@@ -21278,7 +21278,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G721" t="n">
-        <v>2.61655139923096</v>
+        <v>2.61655163764954</v>
       </c>
       <c r="H721" t="n">
         <v>2</v>
@@ -21423,7 +21423,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G726" t="n">
-        <v>2.62551259994507</v>
+        <v>2.62551236152649</v>
       </c>
       <c r="H726" t="n">
         <v>4198</v>
@@ -21452,7 +21452,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G727" t="n">
-        <v>2.61655139923096</v>
+        <v>2.61655163764954</v>
       </c>
       <c r="H727" t="n">
         <v>3600</v>
@@ -21481,7 +21481,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G728" t="n">
-        <v>2.61655139923096</v>
+        <v>2.61655163764954</v>
       </c>
       <c r="H728" t="n">
         <v>343</v>
@@ -21510,7 +21510,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G729" t="n">
-        <v>2.61655139923096</v>
+        <v>2.61655163764954</v>
       </c>
       <c r="H729" t="n">
         <v>0</v>
@@ -21539,7 +21539,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G730" t="n">
-        <v>2.607590675354</v>
+        <v>2.60759091377258</v>
       </c>
       <c r="H730" t="n">
         <v>5732</v>
@@ -21568,7 +21568,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G731" t="n">
-        <v>2.61655139923096</v>
+        <v>2.61655163764954</v>
       </c>
       <c r="H731" t="n">
         <v>3102</v>
@@ -21771,7 +21771,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G738" t="n">
-        <v>2.57174754142761</v>
+        <v>2.57174730300903</v>
       </c>
       <c r="H738" t="n">
         <v>2354</v>
@@ -22003,7 +22003,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G746" t="n">
-        <v>2.41941404342651</v>
+        <v>2.41941428184509</v>
       </c>
       <c r="H746" t="n">
         <v>10198</v>
@@ -22061,7 +22061,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G748" t="n">
-        <v>2.57174754142761</v>
+        <v>2.57174730300903</v>
       </c>
       <c r="H748" t="n">
         <v>2700</v>
@@ -22119,7 +22119,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G750" t="n">
-        <v>2.57174754142761</v>
+        <v>2.57174730300903</v>
       </c>
       <c r="H750" t="n">
         <v>1555</v>
@@ -22148,7 +22148,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G751" t="n">
-        <v>2.57174754142761</v>
+        <v>2.57174730300903</v>
       </c>
       <c r="H751" t="n">
         <v>0</v>
@@ -22177,7 +22177,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G752" t="n">
-        <v>2.57174754142761</v>
+        <v>2.57174730300903</v>
       </c>
       <c r="H752" t="n">
         <v>0</v>
@@ -22293,7 +22293,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G756" t="n">
-        <v>2.53590416908264</v>
+        <v>2.53590440750122</v>
       </c>
       <c r="H756" t="n">
         <v>50</v>
@@ -22322,7 +22322,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G757" t="n">
-        <v>2.53590416908264</v>
+        <v>2.53590440750122</v>
       </c>
       <c r="H757" t="n">
         <v>0</v>
@@ -22351,7 +22351,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G758" t="n">
-        <v>2.53590416908264</v>
+        <v>2.53590440750122</v>
       </c>
       <c r="H758" t="n">
         <v>0</v>
@@ -22496,7 +22496,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G763" t="n">
-        <v>2.53590416908264</v>
+        <v>2.53590440750122</v>
       </c>
       <c r="H763" t="n">
         <v>1110</v>
@@ -22525,7 +22525,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G764" t="n">
-        <v>2.53590416908264</v>
+        <v>2.53590440750122</v>
       </c>
       <c r="H764" t="n">
         <v>2491</v>
@@ -22554,7 +22554,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G765" t="n">
-        <v>2.607590675354</v>
+        <v>2.60759091377258</v>
       </c>
       <c r="H765" t="n">
         <v>2167</v>
@@ -22583,7 +22583,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G766" t="n">
-        <v>2.63447332382202</v>
+        <v>2.63447308540344</v>
       </c>
       <c r="H766" t="n">
         <v>1525</v>
@@ -22612,7 +22612,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G767" t="n">
-        <v>2.67031621932983</v>
+        <v>2.67031645774841</v>
       </c>
       <c r="H767" t="n">
         <v>1992</v>
@@ -22670,7 +22670,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G769" t="n">
-        <v>2.67031621932983</v>
+        <v>2.67031645774841</v>
       </c>
       <c r="H769" t="n">
         <v>2001</v>
@@ -22699,7 +22699,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G770" t="n">
-        <v>2.69719886779785</v>
+        <v>2.69719862937927</v>
       </c>
       <c r="H770" t="n">
         <v>753</v>
@@ -22728,7 +22728,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G771" t="n">
-        <v>2.67927694320679</v>
+        <v>2.67927718162537</v>
       </c>
       <c r="H771" t="n">
         <v>2755</v>
@@ -22757,7 +22757,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G772" t="n">
-        <v>2.67031621932983</v>
+        <v>2.67031645774841</v>
       </c>
       <c r="H772" t="n">
         <v>1014</v>
@@ -22786,7 +22786,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G773" t="n">
-        <v>2.71512031555176</v>
+        <v>2.71512007713318</v>
       </c>
       <c r="H773" t="n">
         <v>19800</v>
@@ -22844,7 +22844,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G775" t="n">
-        <v>2.69719886779785</v>
+        <v>2.69719862937927</v>
       </c>
       <c r="H775" t="n">
         <v>12499</v>
@@ -22873,7 +22873,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G776" t="n">
-        <v>2.67927694320679</v>
+        <v>2.67927718162537</v>
       </c>
       <c r="H776" t="n">
         <v>5677</v>
@@ -22902,7 +22902,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G777" t="n">
-        <v>2.75096321105957</v>
+        <v>2.75096344947815</v>
       </c>
       <c r="H777" t="n">
         <v>1940</v>
@@ -22931,7 +22931,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G778" t="n">
-        <v>2.81368899345398</v>
+        <v>2.81368923187256</v>
       </c>
       <c r="H778" t="n">
         <v>12625</v>
@@ -22960,7 +22960,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G779" t="n">
-        <v>2.840571641922</v>
+        <v>2.84057140350342</v>
       </c>
       <c r="H779" t="n">
         <v>24224</v>
@@ -22989,7 +22989,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G780" t="n">
-        <v>2.93914008140564</v>
+        <v>2.93914031982422</v>
       </c>
       <c r="H780" t="n">
         <v>37762</v>
@@ -23018,7 +23018,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G781" t="n">
-        <v>2.87641453742981</v>
+        <v>2.87641477584839</v>
       </c>
       <c r="H781" t="n">
         <v>16941</v>
@@ -23076,7 +23076,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G783" t="n">
-        <v>2.82264971733093</v>
+        <v>2.82264995574951</v>
       </c>
       <c r="H783" t="n">
         <v>3132</v>
@@ -23163,7 +23163,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G786" t="n">
-        <v>2.82264971733093</v>
+        <v>2.82264995574951</v>
       </c>
       <c r="H786" t="n">
         <v>757</v>
@@ -23192,7 +23192,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G787" t="n">
-        <v>2.77784585952759</v>
+        <v>2.77784562110901</v>
       </c>
       <c r="H787" t="n">
         <v>127</v>
@@ -23221,7 +23221,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G788" t="n">
-        <v>2.840571641922</v>
+        <v>2.84057140350342</v>
       </c>
       <c r="H788" t="n">
         <v>23401</v>
@@ -23250,7 +23250,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G789" t="n">
-        <v>2.77784585952759</v>
+        <v>2.77784562110901</v>
       </c>
       <c r="H789" t="n">
         <v>7830</v>
@@ -23279,7 +23279,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G790" t="n">
-        <v>2.76888513565063</v>
+        <v>2.76888489723206</v>
       </c>
       <c r="H790" t="n">
         <v>501</v>
@@ -23337,7 +23337,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G792" t="n">
-        <v>2.77784585952759</v>
+        <v>2.77784562110901</v>
       </c>
       <c r="H792" t="n">
         <v>1540</v>
@@ -23395,7 +23395,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G794" t="n">
-        <v>2.87641453742981</v>
+        <v>2.87641477584839</v>
       </c>
       <c r="H794" t="n">
         <v>5745</v>
@@ -23424,7 +23424,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G795" t="n">
-        <v>2.87641453742981</v>
+        <v>2.87641477584839</v>
       </c>
       <c r="H795" t="n">
         <v>10690</v>
@@ -23511,7 +23511,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G798" t="n">
-        <v>3.16315960884094</v>
+        <v>3.16315984725952</v>
       </c>
       <c r="H798" t="n">
         <v>77776</v>
@@ -23598,7 +23598,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G801" t="n">
-        <v>3.25276780128479</v>
+        <v>3.25276803970337</v>
       </c>
       <c r="H801" t="n">
         <v>35656</v>
@@ -23656,7 +23656,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G803" t="n">
-        <v>3.25276780128479</v>
+        <v>3.25276803970337</v>
       </c>
       <c r="H803" t="n">
         <v>24537</v>
@@ -23830,7 +23830,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G809" t="n">
-        <v>3.33341479301453</v>
+        <v>3.33341503143311</v>
       </c>
       <c r="H809" t="n">
         <v>6694</v>
@@ -23888,7 +23888,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G811" t="n">
-        <v>3.33341479301453</v>
+        <v>3.33341503143311</v>
       </c>
       <c r="H811" t="n">
         <v>1777</v>
@@ -23917,7 +23917,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G812" t="n">
-        <v>3.34237575531006</v>
+        <v>3.34237551689148</v>
       </c>
       <c r="H812" t="n">
         <v>14717</v>
@@ -24004,7 +24004,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G815" t="n">
-        <v>3.40510129928589</v>
+        <v>3.40510106086731</v>
       </c>
       <c r="H815" t="n">
         <v>25970</v>
@@ -24062,7 +24062,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G817" t="n">
-        <v>3.36925792694092</v>
+        <v>3.3692581653595</v>
       </c>
       <c r="H817" t="n">
         <v>26326</v>
@@ -24120,7 +24120,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G819" t="n">
-        <v>3.40510129928589</v>
+        <v>3.40510106086731</v>
       </c>
       <c r="H819" t="n">
         <v>2828</v>
@@ -24207,7 +24207,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G822" t="n">
-        <v>3.4857485294342</v>
+        <v>3.48574829101562</v>
       </c>
       <c r="H822" t="n">
         <v>8734</v>
@@ -24236,7 +24236,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G823" t="n">
-        <v>3.47678756713867</v>
+        <v>3.47678780555725</v>
       </c>
       <c r="H823" t="n">
         <v>7457</v>
@@ -24555,7 +24555,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G834" t="n">
-        <v>3.51263093948364</v>
+        <v>3.51263070106506</v>
       </c>
       <c r="H834" t="n">
         <v>17785</v>
@@ -24584,7 +24584,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G835" t="n">
-        <v>3.51263093948364</v>
+        <v>3.51263070106506</v>
       </c>
       <c r="H835" t="n">
         <v>9370</v>
@@ -24642,7 +24642,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G837" t="n">
-        <v>3.51263093948364</v>
+        <v>3.51263070106506</v>
       </c>
       <c r="H837" t="n">
         <v>3704</v>
@@ -24671,7 +24671,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G838" t="n">
-        <v>3.5395131111145</v>
+        <v>3.53951334953308</v>
       </c>
       <c r="H838" t="n">
         <v>9297</v>
@@ -24729,7 +24729,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G840" t="n">
-        <v>3.51263093948364</v>
+        <v>3.51263070106506</v>
       </c>
       <c r="H840" t="n">
         <v>9839</v>
@@ -24903,7 +24903,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G846" t="n">
-        <v>3.71872925758362</v>
+        <v>3.71872901916504</v>
       </c>
       <c r="H846" t="n">
         <v>10814</v>
@@ -24932,7 +24932,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G847" t="n">
-        <v>3.6918466091156</v>
+        <v>3.69184637069702</v>
       </c>
       <c r="H847" t="n">
         <v>15171</v>
@@ -24961,7 +24961,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G848" t="n">
-        <v>3.70976805686951</v>
+        <v>3.70976829528809</v>
       </c>
       <c r="H848" t="n">
         <v>16414</v>
@@ -24990,7 +24990,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G849" t="n">
-        <v>3.68288588523865</v>
+        <v>3.68288612365723</v>
       </c>
       <c r="H849" t="n">
         <v>10497</v>
@@ -25048,7 +25048,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G851" t="n">
-        <v>3.70976805686951</v>
+        <v>3.70976829528809</v>
       </c>
       <c r="H851" t="n">
         <v>3613</v>
@@ -25164,7 +25164,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G855" t="n">
-        <v>3.79041528701782</v>
+        <v>3.7904155254364</v>
       </c>
       <c r="H855" t="n">
         <v>50118</v>
@@ -80081,7 +80081,7 @@
         <v>0.959999978542328</v>
       </c>
       <c r="D2749" t="n">
-        <v>0.959999978542328</v>
+        <v>0.995000004768372</v>
       </c>
       <c r="E2749" t="n">
         <v>0.959999978542328</v>
@@ -80096,6 +80096,35 @@
         <v>35</v>
       </c>
       <c r="I2749" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2750">
+      <c r="A2750" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2750" s="1" t="n">
+        <v>46321.3333333333</v>
+      </c>
+      <c r="C2750" t="n">
+        <v>0.959999978542328</v>
+      </c>
+      <c r="D2750" t="n">
+        <v>0.959999978542328</v>
+      </c>
+      <c r="E2750" t="n">
+        <v>0.959999978542328</v>
+      </c>
+      <c r="F2750" t="n">
+        <v>0.959999978542328</v>
+      </c>
+      <c r="G2750" t="n">
+        <v>0.959999978542328</v>
+      </c>
+      <c r="H2750" t="n">
+        <v>9</v>
+      </c>
+      <c r="I2750" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/RAT.MI.xlsx
+++ b/data/RAT.MI.xlsx
@@ -427,7 +427,7 @@
         <v>2.3659999370575</v>
       </c>
       <c r="G2" t="n">
-        <v>1.85825943946838</v>
+        <v>1.85825955867767</v>
       </c>
       <c r="H2" t="n">
         <v>1350</v>
@@ -456,7 +456,7 @@
         <v>2.43600010871887</v>
       </c>
       <c r="G3" t="n">
-        <v>1.9132376909256</v>
+        <v>1.91323781013489</v>
       </c>
       <c r="H3" t="n">
         <v>3199</v>
@@ -543,7 +543,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G6" t="n">
-        <v>1.88496315479279</v>
+        <v>1.8849630355835</v>
       </c>
       <c r="H6" t="n">
         <v>5635</v>
@@ -572,7 +572,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G7" t="n">
-        <v>1.88496315479279</v>
+        <v>1.8849630355835</v>
       </c>
       <c r="H7" t="n">
         <v>1000</v>
@@ -601,7 +601,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G8" t="n">
-        <v>1.92423295974731</v>
+        <v>1.92423331737518</v>
       </c>
       <c r="H8" t="n">
         <v>4000</v>
@@ -630,7 +630,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G9" t="n">
-        <v>1.88496315479279</v>
+        <v>1.8849630355835</v>
       </c>
       <c r="H9" t="n">
         <v>155</v>
@@ -659,7 +659,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G10" t="n">
-        <v>1.88496315479279</v>
+        <v>1.8849630355835</v>
       </c>
       <c r="H10" t="n">
         <v>559</v>
@@ -688,7 +688,7 @@
         <v>2.3659999370575</v>
       </c>
       <c r="G11" t="n">
-        <v>1.85825943946838</v>
+        <v>1.85825955867767</v>
       </c>
       <c r="H11" t="n">
         <v>1414</v>
@@ -717,7 +717,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G12" t="n">
-        <v>1.80642282962799</v>
+        <v>1.80642294883728</v>
       </c>
       <c r="H12" t="n">
         <v>270</v>
@@ -746,7 +746,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G13" t="n">
-        <v>1.80642282962799</v>
+        <v>1.80642294883728</v>
       </c>
       <c r="H13" t="n">
         <v>1200</v>
@@ -775,7 +775,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G14" t="n">
-        <v>1.82998490333557</v>
+        <v>1.82998514175415</v>
       </c>
       <c r="H14" t="n">
         <v>193</v>
@@ -804,7 +804,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G15" t="n">
-        <v>1.79856884479523</v>
+        <v>1.79856872558594</v>
       </c>
       <c r="H15" t="n">
         <v>2788</v>
@@ -833,7 +833,7 @@
         <v>2.25</v>
       </c>
       <c r="G16" t="n">
-        <v>1.76715290546417</v>
+        <v>1.76715302467346</v>
       </c>
       <c r="H16" t="n">
         <v>2070</v>
@@ -862,7 +862,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G17" t="n">
-        <v>1.85354709625244</v>
+        <v>1.85354685783386</v>
       </c>
       <c r="H17" t="n">
         <v>4705</v>
@@ -891,7 +891,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G18" t="n">
-        <v>1.85354709625244</v>
+        <v>1.85354685783386</v>
       </c>
       <c r="H18" t="n">
         <v>2000</v>
@@ -920,7 +920,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G19" t="n">
-        <v>1.86925494670868</v>
+        <v>1.86925530433655</v>
       </c>
       <c r="H19" t="n">
         <v>3200</v>
@@ -978,7 +978,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G21" t="n">
-        <v>1.89281702041626</v>
+        <v>1.89281713962555</v>
       </c>
       <c r="H21" t="n">
         <v>100</v>
@@ -1007,7 +1007,7 @@
         <v>2.37800002098083</v>
       </c>
       <c r="G22" t="n">
-        <v>1.86768412590027</v>
+        <v>1.86768436431885</v>
       </c>
       <c r="H22" t="n">
         <v>2858</v>
@@ -1036,7 +1036,7 @@
         <v>2.31200003623962</v>
       </c>
       <c r="G23" t="n">
-        <v>1.81584787368774</v>
+        <v>1.81584775447845</v>
       </c>
       <c r="H23" t="n">
         <v>750</v>
@@ -1065,7 +1065,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G24" t="n">
-        <v>1.8378392457962</v>
+        <v>1.83783888816833</v>
       </c>
       <c r="H24" t="n">
         <v>1435</v>
@@ -1094,7 +1094,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G25" t="n">
-        <v>1.8378392457962</v>
+        <v>1.83783888816833</v>
       </c>
       <c r="H25" t="n">
         <v>475</v>
@@ -1123,7 +1123,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G26" t="n">
-        <v>1.88496315479279</v>
+        <v>1.8849630355835</v>
       </c>
       <c r="H26" t="n">
         <v>330</v>
@@ -1210,7 +1210,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G29" t="n">
-        <v>1.88496315479279</v>
+        <v>1.8849630355835</v>
       </c>
       <c r="H29" t="n">
         <v>1810</v>
@@ -1239,7 +1239,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G30" t="n">
-        <v>1.80642282962799</v>
+        <v>1.80642294883728</v>
       </c>
       <c r="H30" t="n">
         <v>10919</v>
@@ -1268,7 +1268,7 @@
         <v>2.32599997520447</v>
       </c>
       <c r="G31" t="n">
-        <v>1.82684338092804</v>
+        <v>1.82684350013733</v>
       </c>
       <c r="H31" t="n">
         <v>9925</v>
@@ -1326,7 +1326,7 @@
         <v>2.31599998474121</v>
       </c>
       <c r="G33" t="n">
-        <v>1.81898951530457</v>
+        <v>1.81898939609528</v>
       </c>
       <c r="H33" t="n">
         <v>1023</v>
@@ -1384,7 +1384,7 @@
         <v>2.36800003051758</v>
       </c>
       <c r="G35" t="n">
-        <v>1.85983037948608</v>
+        <v>1.8598301410675</v>
       </c>
       <c r="H35" t="n">
         <v>100</v>
@@ -1413,7 +1413,7 @@
         <v>2.36800003051758</v>
       </c>
       <c r="G36" t="n">
-        <v>1.85983037948608</v>
+        <v>1.8598301410675</v>
       </c>
       <c r="H36" t="n">
         <v>0</v>
@@ -1442,7 +1442,7 @@
         <v>2.36800003051758</v>
       </c>
       <c r="G37" t="n">
-        <v>1.85983037948608</v>
+        <v>1.8598301410675</v>
       </c>
       <c r="H37" t="n">
         <v>100</v>
@@ -1529,7 +1529,7 @@
         <v>2.31399989128113</v>
       </c>
       <c r="G40" t="n">
-        <v>1.81741857528687</v>
+        <v>1.81741833686829</v>
       </c>
       <c r="H40" t="n">
         <v>150</v>
@@ -1558,7 +1558,7 @@
         <v>2.31399989128113</v>
       </c>
       <c r="G41" t="n">
-        <v>1.81741857528687</v>
+        <v>1.81741833686829</v>
       </c>
       <c r="H41" t="n">
         <v>0</v>
@@ -1587,7 +1587,7 @@
         <v>2.31399989128113</v>
       </c>
       <c r="G42" t="n">
-        <v>1.81741857528687</v>
+        <v>1.81741833686829</v>
       </c>
       <c r="H42" t="n">
         <v>0</v>
@@ -1645,7 +1645,7 @@
         <v>2.36800003051758</v>
       </c>
       <c r="G44" t="n">
-        <v>1.85983037948608</v>
+        <v>1.8598301410675</v>
       </c>
       <c r="H44" t="n">
         <v>540</v>
@@ -1674,7 +1674,7 @@
         <v>2.37800002098083</v>
       </c>
       <c r="G45" t="n">
-        <v>1.86768412590027</v>
+        <v>1.86768436431885</v>
       </c>
       <c r="H45" t="n">
         <v>2230</v>
@@ -1703,7 +1703,7 @@
         <v>2.35599994659424</v>
       </c>
       <c r="G46" t="n">
-        <v>1.85040509700775</v>
+        <v>1.85040545463562</v>
       </c>
       <c r="H46" t="n">
         <v>253</v>
@@ -1790,7 +1790,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G49" t="n">
-        <v>1.81427705287933</v>
+        <v>1.81427669525146</v>
       </c>
       <c r="H49" t="n">
         <v>1530</v>
@@ -1877,7 +1877,7 @@
         <v>2.35800004005432</v>
       </c>
       <c r="G52" t="n">
-        <v>1.85197627544403</v>
+        <v>1.85197651386261</v>
       </c>
       <c r="H52" t="n">
         <v>3419</v>
@@ -1906,7 +1906,7 @@
         <v>2.34800004959106</v>
       </c>
       <c r="G53" t="n">
-        <v>1.84412205219269</v>
+        <v>1.84412217140198</v>
       </c>
       <c r="H53" t="n">
         <v>3348</v>
@@ -1935,7 +1935,7 @@
         <v>2.34400010108948</v>
       </c>
       <c r="G54" t="n">
-        <v>1.84098052978516</v>
+        <v>1.84098076820374</v>
       </c>
       <c r="H54" t="n">
         <v>600</v>
@@ -2022,7 +2022,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G57" t="n">
-        <v>1.85354709625244</v>
+        <v>1.85354685783386</v>
       </c>
       <c r="H57" t="n">
         <v>50</v>
@@ -2051,7 +2051,7 @@
         <v>2.32200002670288</v>
       </c>
       <c r="G58" t="n">
-        <v>1.82370173931122</v>
+        <v>1.82370185852051</v>
       </c>
       <c r="H58" t="n">
         <v>1606</v>
@@ -2080,7 +2080,7 @@
         <v>2.32200002670288</v>
       </c>
       <c r="G59" t="n">
-        <v>1.82370173931122</v>
+        <v>1.82370185852051</v>
       </c>
       <c r="H59" t="n">
         <v>0</v>
@@ -2109,7 +2109,7 @@
         <v>2.30599999427795</v>
       </c>
       <c r="G60" t="n">
-        <v>1.8111355304718</v>
+        <v>1.81113541126251</v>
       </c>
       <c r="H60" t="n">
         <v>6820</v>
@@ -2138,7 +2138,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G61" t="n">
-        <v>1.81427705287933</v>
+        <v>1.81427669525146</v>
       </c>
       <c r="H61" t="n">
         <v>150</v>
@@ -2167,7 +2167,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G62" t="n">
-        <v>1.82213091850281</v>
+        <v>1.8221310377121</v>
       </c>
       <c r="H62" t="n">
         <v>7700</v>
@@ -2196,7 +2196,7 @@
         <v>2.35599994659424</v>
       </c>
       <c r="G63" t="n">
-        <v>1.85040509700775</v>
+        <v>1.85040545463562</v>
       </c>
       <c r="H63" t="n">
         <v>100</v>
@@ -2254,7 +2254,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G65" t="n">
-        <v>1.92423295974731</v>
+        <v>1.92423331737518</v>
       </c>
       <c r="H65" t="n">
         <v>19358</v>
@@ -2283,7 +2283,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G66" t="n">
-        <v>1.92423295974731</v>
+        <v>1.92423331737518</v>
       </c>
       <c r="H66" t="n">
         <v>0</v>
@@ -2312,7 +2312,7 @@
         <v>2.46600008010864</v>
       </c>
       <c r="G67" t="n">
-        <v>1.9367995262146</v>
+        <v>1.93679976463318</v>
       </c>
       <c r="H67" t="n">
         <v>1695</v>
@@ -2370,7 +2370,7 @@
         <v>2.48799991607666</v>
       </c>
       <c r="G69" t="n">
-        <v>1.95407819747925</v>
+        <v>1.95407855510712</v>
       </c>
       <c r="H69" t="n">
         <v>16224</v>
@@ -2428,7 +2428,7 @@
         <v>2.50200009346008</v>
       </c>
       <c r="G71" t="n">
-        <v>1.9650741815567</v>
+        <v>1.96507394313812</v>
       </c>
       <c r="H71" t="n">
         <v>350</v>
@@ -2573,7 +2573,7 @@
         <v>2.50200009346008</v>
       </c>
       <c r="G76" t="n">
-        <v>1.9650741815567</v>
+        <v>1.96507394313812</v>
       </c>
       <c r="H76" t="n">
         <v>3085</v>
@@ -2660,7 +2660,7 @@
         <v>2.45799994468689</v>
       </c>
       <c r="G79" t="n">
-        <v>1.93051600456238</v>
+        <v>1.93051648139954</v>
       </c>
       <c r="H79" t="n">
         <v>9175</v>
@@ -2689,7 +2689,7 @@
         <v>2.45799994468689</v>
       </c>
       <c r="G80" t="n">
-        <v>1.93051600456238</v>
+        <v>1.93051648139954</v>
       </c>
       <c r="H80" t="n">
         <v>1464</v>
@@ -2747,7 +2747,7 @@
         <v>2.49799990653992</v>
       </c>
       <c r="G82" t="n">
-        <v>1.96193242073059</v>
+        <v>1.96193218231201</v>
       </c>
       <c r="H82" t="n">
         <v>2294</v>
@@ -2805,7 +2805,7 @@
         <v>2.48799991607666</v>
       </c>
       <c r="G84" t="n">
-        <v>1.95407819747925</v>
+        <v>1.95407855510712</v>
       </c>
       <c r="H84" t="n">
         <v>371</v>
@@ -2834,7 +2834,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G85" t="n">
-        <v>1.95564925670624</v>
+        <v>1.95564913749695</v>
       </c>
       <c r="H85" t="n">
         <v>2700</v>
@@ -2863,7 +2863,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G86" t="n">
-        <v>1.95564925670624</v>
+        <v>1.95564913749695</v>
       </c>
       <c r="H86" t="n">
         <v>0</v>
@@ -2950,7 +2950,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G89" t="n">
-        <v>1.88496315479279</v>
+        <v>1.8849630355835</v>
       </c>
       <c r="H89" t="n">
         <v>4181</v>
@@ -3095,7 +3095,7 @@
         <v>2.38599991798401</v>
       </c>
       <c r="G94" t="n">
-        <v>1.87396728992462</v>
+        <v>1.87396764755249</v>
       </c>
       <c r="H94" t="n">
         <v>11190</v>
@@ -3124,7 +3124,7 @@
         <v>2.38599991798401</v>
       </c>
       <c r="G95" t="n">
-        <v>1.87396728992462</v>
+        <v>1.87396764755249</v>
       </c>
       <c r="H95" t="n">
         <v>0</v>
@@ -3211,7 +3211,7 @@
         <v>2.34800004959106</v>
       </c>
       <c r="G98" t="n">
-        <v>1.84412205219269</v>
+        <v>1.84412217140198</v>
       </c>
       <c r="H98" t="n">
         <v>8904</v>
@@ -3240,7 +3240,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G99" t="n">
-        <v>1.89281702041626</v>
+        <v>1.89281713962555</v>
       </c>
       <c r="H99" t="n">
         <v>14550</v>
@@ -3269,7 +3269,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G100" t="n">
-        <v>1.93378722667694</v>
+        <v>1.93378698825836</v>
       </c>
       <c r="H100" t="n">
         <v>1125</v>
@@ -3298,7 +3298,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G101" t="n">
-        <v>1.95017504692078</v>
+        <v>1.95017528533936</v>
       </c>
       <c r="H101" t="n">
         <v>176</v>
@@ -3356,7 +3356,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G103" t="n">
-        <v>1.93378722667694</v>
+        <v>1.93378698825836</v>
       </c>
       <c r="H103" t="n">
         <v>3800</v>
@@ -3385,7 +3385,7 @@
         <v>2.35599994659424</v>
       </c>
       <c r="G104" t="n">
-        <v>1.93050920963287</v>
+        <v>1.93050944805145</v>
       </c>
       <c r="H104" t="n">
         <v>3779</v>
@@ -3414,7 +3414,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G105" t="n">
-        <v>1.96656322479248</v>
+        <v>1.96656346321106</v>
       </c>
       <c r="H105" t="n">
         <v>160</v>
@@ -3443,7 +3443,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G106" t="n">
-        <v>1.96656322479248</v>
+        <v>1.96656346321106</v>
       </c>
       <c r="H106" t="n">
         <v>0</v>
@@ -3472,7 +3472,7 @@
         <v>2.38599991798401</v>
       </c>
       <c r="G107" t="n">
-        <v>1.95509135723114</v>
+        <v>1.95509159564972</v>
       </c>
       <c r="H107" t="n">
         <v>523</v>
@@ -3559,7 +3559,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G110" t="n">
-        <v>1.95017504692078</v>
+        <v>1.95017528533936</v>
       </c>
       <c r="H110" t="n">
         <v>403</v>
@@ -3588,7 +3588,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G111" t="n">
-        <v>1.95017504692078</v>
+        <v>1.95017528533936</v>
       </c>
       <c r="H111" t="n">
         <v>0</v>
@@ -3617,7 +3617,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G112" t="n">
-        <v>1.91739940643311</v>
+        <v>1.91739892959595</v>
       </c>
       <c r="H112" t="n">
         <v>778</v>
@@ -3733,7 +3733,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G116" t="n">
-        <v>1.94198131561279</v>
+        <v>1.94198107719421</v>
       </c>
       <c r="H116" t="n">
         <v>5088</v>
@@ -3762,7 +3762,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G117" t="n">
-        <v>1.94198131561279</v>
+        <v>1.94198107719421</v>
       </c>
       <c r="H117" t="n">
         <v>0</v>
@@ -3791,7 +3791,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G118" t="n">
-        <v>1.91739940643311</v>
+        <v>1.91739892959595</v>
       </c>
       <c r="H118" t="n">
         <v>2740</v>
@@ -3820,7 +3820,7 @@
         <v>2.33400011062622</v>
       </c>
       <c r="G119" t="n">
-        <v>1.91248285770416</v>
+        <v>1.91248297691345</v>
       </c>
       <c r="H119" t="n">
         <v>2002</v>
@@ -3849,7 +3849,7 @@
         <v>2.33200001716614</v>
       </c>
       <c r="G120" t="n">
-        <v>1.91084396839142</v>
+        <v>1.91084384918213</v>
       </c>
       <c r="H120" t="n">
         <v>1532</v>
@@ -3878,7 +3878,7 @@
         <v>2.33200001716614</v>
       </c>
       <c r="G121" t="n">
-        <v>1.91084396839142</v>
+        <v>1.91084384918213</v>
       </c>
       <c r="H121" t="n">
         <v>0</v>
@@ -3907,7 +3907,7 @@
         <v>2.33400011062622</v>
       </c>
       <c r="G122" t="n">
-        <v>1.91248285770416</v>
+        <v>1.91248297691345</v>
       </c>
       <c r="H122" t="n">
         <v>1260</v>
@@ -3936,7 +3936,7 @@
         <v>2.33400011062622</v>
       </c>
       <c r="G123" t="n">
-        <v>1.91248285770416</v>
+        <v>1.91248297691345</v>
       </c>
       <c r="H123" t="n">
         <v>0</v>
@@ -3965,7 +3965,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G124" t="n">
-        <v>1.83545899391174</v>
+        <v>1.83545887470245</v>
       </c>
       <c r="H124" t="n">
         <v>348</v>
@@ -4023,7 +4023,7 @@
         <v>2.24799990653992</v>
       </c>
       <c r="G126" t="n">
-        <v>1.84201407432556</v>
+        <v>1.84201419353485</v>
       </c>
       <c r="H126" t="n">
         <v>1490</v>
@@ -4052,7 +4052,7 @@
         <v>2.23600006103516</v>
       </c>
       <c r="G127" t="n">
-        <v>1.83218157291412</v>
+        <v>1.83218133449554</v>
       </c>
       <c r="H127" t="n">
         <v>773</v>
@@ -4081,7 +4081,7 @@
         <v>2.24799990653992</v>
       </c>
       <c r="G128" t="n">
-        <v>1.84201407432556</v>
+        <v>1.84201419353485</v>
       </c>
       <c r="H128" t="n">
         <v>370</v>
@@ -4110,7 +4110,7 @@
         <v>2.29800009727478</v>
       </c>
       <c r="G129" t="n">
-        <v>1.88298428058624</v>
+        <v>1.88298416137695</v>
       </c>
       <c r="H129" t="n">
         <v>100</v>
@@ -4139,7 +4139,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G130" t="n">
-        <v>1.86823499202728</v>
+        <v>1.86823511123657</v>
       </c>
       <c r="H130" t="n">
         <v>2288</v>
@@ -4168,7 +4168,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G131" t="n">
-        <v>1.94198131561279</v>
+        <v>1.94198107719421</v>
       </c>
       <c r="H131" t="n">
         <v>150</v>
@@ -4197,7 +4197,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G132" t="n">
-        <v>1.94198131561279</v>
+        <v>1.94198107719421</v>
       </c>
       <c r="H132" t="n">
         <v>0</v>
@@ -4313,7 +4313,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G136" t="n">
-        <v>1.89281713962555</v>
+        <v>1.89281690120697</v>
       </c>
       <c r="H136" t="n">
         <v>6553</v>
@@ -4574,7 +4574,7 @@
         <v>2.28399991989136</v>
       </c>
       <c r="G145" t="n">
-        <v>1.87151277065277</v>
+        <v>1.87151253223419</v>
       </c>
       <c r="H145" t="n">
         <v>10583</v>
@@ -4603,7 +4603,7 @@
         <v>2.31599998474121</v>
       </c>
       <c r="G146" t="n">
-        <v>1.89773368835449</v>
+        <v>1.89773344993591</v>
       </c>
       <c r="H146" t="n">
         <v>5883</v>
@@ -4690,7 +4690,7 @@
         <v>2.2260000705719</v>
       </c>
       <c r="G149" t="n">
-        <v>1.82398724555969</v>
+        <v>1.82398760318756</v>
       </c>
       <c r="H149" t="n">
         <v>2820</v>
@@ -4719,7 +4719,7 @@
         <v>2.14599990844727</v>
       </c>
       <c r="G150" t="n">
-        <v>1.75843501091003</v>
+        <v>1.75843513011932</v>
       </c>
       <c r="H150" t="n">
         <v>12851</v>
@@ -4980,7 +4980,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G159" t="n">
-        <v>1.72074258327484</v>
+        <v>1.72074270248413</v>
       </c>
       <c r="H159" t="n">
         <v>2791</v>
@@ -5096,7 +5096,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G163" t="n">
-        <v>1.69616091251373</v>
+        <v>1.69616079330444</v>
       </c>
       <c r="H163" t="n">
         <v>4541</v>
@@ -5125,7 +5125,7 @@
         <v>2.14800000190735</v>
       </c>
       <c r="G164" t="n">
-        <v>1.76007401943207</v>
+        <v>1.76007413864136</v>
       </c>
       <c r="H164" t="n">
         <v>2324</v>
@@ -5154,7 +5154,7 @@
         <v>2.14800000190735</v>
       </c>
       <c r="G165" t="n">
-        <v>1.76007401943207</v>
+        <v>1.76007413864136</v>
       </c>
       <c r="H165" t="n">
         <v>0</v>
@@ -5183,7 +5183,7 @@
         <v>2.14800000190735</v>
       </c>
       <c r="G166" t="n">
-        <v>1.76007401943207</v>
+        <v>1.76007413864136</v>
       </c>
       <c r="H166" t="n">
         <v>0</v>
@@ -5212,7 +5212,7 @@
         <v>2.14800000190735</v>
       </c>
       <c r="G167" t="n">
-        <v>1.76007401943207</v>
+        <v>1.76007413864136</v>
       </c>
       <c r="H167" t="n">
         <v>0</v>
@@ -5241,7 +5241,7 @@
         <v>2.14800000190735</v>
       </c>
       <c r="G168" t="n">
-        <v>1.76007401943207</v>
+        <v>1.76007413864136</v>
       </c>
       <c r="H168" t="n">
         <v>0</v>
@@ -5270,7 +5270,7 @@
         <v>2.14800000190735</v>
       </c>
       <c r="G169" t="n">
-        <v>1.76007401943207</v>
+        <v>1.76007413864136</v>
       </c>
       <c r="H169" t="n">
         <v>206</v>
@@ -5415,7 +5415,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G174" t="n">
-        <v>1.71254861354828</v>
+        <v>1.71254885196686</v>
       </c>
       <c r="H174" t="n">
         <v>36026</v>
@@ -5444,7 +5444,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G175" t="n">
-        <v>1.63060879707336</v>
+        <v>1.63060867786407</v>
       </c>
       <c r="H175" t="n">
         <v>32041</v>
@@ -5473,7 +5473,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G176" t="n">
-        <v>1.67157864570618</v>
+        <v>1.67157876491547</v>
       </c>
       <c r="H176" t="n">
         <v>12255</v>
@@ -5502,7 +5502,7 @@
         <v>2.03399991989136</v>
       </c>
       <c r="G177" t="n">
-        <v>1.66666233539581</v>
+        <v>1.66666221618652</v>
       </c>
       <c r="H177" t="n">
         <v>7268</v>
@@ -5647,7 +5647,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G182" t="n">
-        <v>1.67157864570618</v>
+        <v>1.67157876491547</v>
       </c>
       <c r="H182" t="n">
         <v>1012</v>
@@ -5676,7 +5676,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G183" t="n">
-        <v>1.67157864570618</v>
+        <v>1.67157876491547</v>
       </c>
       <c r="H183" t="n">
         <v>0</v>
@@ -5734,7 +5734,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G185" t="n">
-        <v>1.67157864570618</v>
+        <v>1.67157876491547</v>
       </c>
       <c r="H185" t="n">
         <v>1394</v>
@@ -5850,7 +5850,7 @@
         <v>2.00799989700317</v>
       </c>
       <c r="G189" t="n">
-        <v>1.64535772800446</v>
+        <v>1.64535784721375</v>
       </c>
       <c r="H189" t="n">
         <v>2513</v>
@@ -5908,7 +5908,7 @@
         <v>1.98399996757507</v>
       </c>
       <c r="G191" t="n">
-        <v>1.62569224834442</v>
+        <v>1.62569212913513</v>
       </c>
       <c r="H191" t="n">
         <v>9477</v>
@@ -5966,7 +5966,7 @@
         <v>2.03399991989136</v>
       </c>
       <c r="G193" t="n">
-        <v>1.66666233539581</v>
+        <v>1.66666221618652</v>
       </c>
       <c r="H193" t="n">
         <v>2852</v>
@@ -6024,7 +6024,7 @@
         <v>2.03600001335144</v>
       </c>
       <c r="G195" t="n">
-        <v>1.66830110549927</v>
+        <v>1.66830122470856</v>
       </c>
       <c r="H195" t="n">
         <v>6290</v>
@@ -6053,7 +6053,7 @@
         <v>2.03600001335144</v>
       </c>
       <c r="G196" t="n">
-        <v>1.66830110549927</v>
+        <v>1.66830122470856</v>
       </c>
       <c r="H196" t="n">
         <v>0</v>
@@ -6082,7 +6082,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G197" t="n">
-        <v>1.65519070625305</v>
+        <v>1.65519082546234</v>
       </c>
       <c r="H197" t="n">
         <v>4191</v>
@@ -6111,7 +6111,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G198" t="n">
-        <v>1.65519070625305</v>
+        <v>1.65519082546234</v>
       </c>
       <c r="H198" t="n">
         <v>0</v>
@@ -6140,7 +6140,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G199" t="n">
-        <v>1.65519070625305</v>
+        <v>1.65519082546234</v>
       </c>
       <c r="H199" t="n">
         <v>1000</v>
@@ -6169,7 +6169,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G200" t="n">
-        <v>1.65519070625305</v>
+        <v>1.65519082546234</v>
       </c>
       <c r="H200" t="n">
         <v>0</v>
@@ -6198,7 +6198,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G201" t="n">
-        <v>1.65519070625305</v>
+        <v>1.65519082546234</v>
       </c>
       <c r="H201" t="n">
         <v>100</v>
@@ -6401,7 +6401,7 @@
         <v>1.9889999628067</v>
       </c>
       <c r="G208" t="n">
-        <v>1.62978911399841</v>
+        <v>1.6297892332077</v>
       </c>
       <c r="H208" t="n">
         <v>50</v>
@@ -6459,7 +6459,7 @@
         <v>1.94700002670288</v>
       </c>
       <c r="G210" t="n">
-        <v>1.59537434577942</v>
+        <v>1.59537446498871</v>
       </c>
       <c r="H210" t="n">
         <v>7151</v>
@@ -6488,7 +6488,7 @@
         <v>1.92700004577637</v>
       </c>
       <c r="G211" t="n">
-        <v>1.57898640632629</v>
+        <v>1.578986287117</v>
       </c>
       <c r="H211" t="n">
         <v>3280</v>
@@ -6517,7 +6517,7 @@
         <v>1.94200003147125</v>
       </c>
       <c r="G212" t="n">
-        <v>1.59127724170685</v>
+        <v>1.59127736091614</v>
       </c>
       <c r="H212" t="n">
         <v>8960</v>
@@ -6546,7 +6546,7 @@
         <v>1.94200003147125</v>
       </c>
       <c r="G213" t="n">
-        <v>1.59127724170685</v>
+        <v>1.59127736091614</v>
       </c>
       <c r="H213" t="n">
         <v>0</v>
@@ -6604,7 +6604,7 @@
         <v>1.91299998760223</v>
       </c>
       <c r="G215" t="n">
-        <v>1.56751465797424</v>
+        <v>1.56751477718353</v>
       </c>
       <c r="H215" t="n">
         <v>8016</v>
@@ -6662,7 +6662,7 @@
         <v>1.91199994087219</v>
       </c>
       <c r="G217" t="n">
-        <v>1.56669533252716</v>
+        <v>1.56669521331787</v>
       </c>
       <c r="H217" t="n">
         <v>1680</v>
@@ -6691,7 +6691,7 @@
         <v>1.90199995040894</v>
       </c>
       <c r="G218" t="n">
-        <v>1.55850124359131</v>
+        <v>1.5585013628006</v>
       </c>
       <c r="H218" t="n">
         <v>2601</v>
@@ -6836,7 +6836,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G223" t="n">
-        <v>1.60602676868439</v>
+        <v>1.6060266494751</v>
       </c>
       <c r="H223" t="n">
         <v>3500</v>
@@ -6865,7 +6865,7 @@
         <v>2.00799989700317</v>
       </c>
       <c r="G224" t="n">
-        <v>1.64535772800446</v>
+        <v>1.64535784721375</v>
       </c>
       <c r="H224" t="n">
         <v>100</v>
@@ -6894,7 +6894,7 @@
         <v>1.85399997234344</v>
       </c>
       <c r="G225" t="n">
-        <v>1.51917016506195</v>
+        <v>1.51917004585266</v>
       </c>
       <c r="H225" t="n">
         <v>20310</v>
@@ -7039,7 +7039,7 @@
         <v>1.70200002193451</v>
       </c>
       <c r="G230" t="n">
-        <v>1.39462113380432</v>
+        <v>1.39462101459503</v>
       </c>
       <c r="H230" t="n">
         <v>23064</v>
@@ -7068,7 +7068,7 @@
         <v>1.77900004386902</v>
       </c>
       <c r="G231" t="n">
-        <v>1.45771503448486</v>
+        <v>1.45771491527557</v>
       </c>
       <c r="H231" t="n">
         <v>4259</v>
@@ -7097,7 +7097,7 @@
         <v>1.79499995708466</v>
       </c>
       <c r="G232" t="n">
-        <v>1.47082543373108</v>
+        <v>1.47082531452179</v>
       </c>
       <c r="H232" t="n">
         <v>2527</v>
@@ -7184,7 +7184,7 @@
         <v>1.96700000762939</v>
       </c>
       <c r="G235" t="n">
-        <v>1.61176240444183</v>
+        <v>1.61176252365112</v>
       </c>
       <c r="H235" t="n">
         <v>99</v>
@@ -7300,7 +7300,7 @@
         <v>1.96700000762939</v>
       </c>
       <c r="G239" t="n">
-        <v>1.61176240444183</v>
+        <v>1.61176252365112</v>
       </c>
       <c r="H239" t="n">
         <v>50</v>
@@ -7329,7 +7329,7 @@
         <v>1.88199996948242</v>
       </c>
       <c r="G240" t="n">
-        <v>1.54211330413818</v>
+        <v>1.54211318492889</v>
       </c>
       <c r="H240" t="n">
         <v>14504</v>
@@ -7358,7 +7358,7 @@
         <v>1.84500002861023</v>
       </c>
       <c r="G241" t="n">
-        <v>1.51179540157318</v>
+        <v>1.51179552078247</v>
       </c>
       <c r="H241" t="n">
         <v>3642</v>
@@ -7387,7 +7387,7 @@
         <v>1.89800000190735</v>
       </c>
       <c r="G242" t="n">
-        <v>1.55522382259369</v>
+        <v>1.5552237033844</v>
       </c>
       <c r="H242" t="n">
         <v>6374</v>
@@ -7416,7 +7416,7 @@
         <v>1.89800000190735</v>
       </c>
       <c r="G243" t="n">
-        <v>1.55522382259369</v>
+        <v>1.5552237033844</v>
       </c>
       <c r="H243" t="n">
         <v>3380</v>
@@ -7445,7 +7445,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G244" t="n">
-        <v>1.56505656242371</v>
+        <v>1.56505644321442</v>
       </c>
       <c r="H244" t="n">
         <v>627</v>
@@ -7619,7 +7619,7 @@
         <v>1.85699999332428</v>
       </c>
       <c r="G250" t="n">
-        <v>1.52162826061249</v>
+        <v>1.52162837982178</v>
       </c>
       <c r="H250" t="n">
         <v>5809</v>
@@ -7648,7 +7648,7 @@
         <v>1.88100004196167</v>
       </c>
       <c r="G251" t="n">
-        <v>1.5412939786911</v>
+        <v>1.54129385948181</v>
       </c>
       <c r="H251" t="n">
         <v>33196</v>
@@ -7706,7 +7706,7 @@
         <v>1.84399998188019</v>
       </c>
       <c r="G253" t="n">
-        <v>1.51097619533539</v>
+        <v>1.5109760761261</v>
       </c>
       <c r="H253" t="n">
         <v>15268</v>
@@ -7822,7 +7822,7 @@
         <v>1.84099996089935</v>
       </c>
       <c r="G257" t="n">
-        <v>1.50851774215698</v>
+        <v>1.50851786136627</v>
       </c>
       <c r="H257" t="n">
         <v>9</v>
@@ -7909,7 +7909,7 @@
         <v>1.84200000762939</v>
       </c>
       <c r="G260" t="n">
-        <v>1.50933742523193</v>
+        <v>1.50933718681335</v>
       </c>
       <c r="H260" t="n">
         <v>15155</v>
@@ -7938,7 +7938,7 @@
         <v>1.84099996089935</v>
       </c>
       <c r="G261" t="n">
-        <v>1.50851774215698</v>
+        <v>1.50851786136627</v>
       </c>
       <c r="H261" t="n">
         <v>9819</v>
@@ -7996,7 +7996,7 @@
         <v>1.84200000762939</v>
       </c>
       <c r="G263" t="n">
-        <v>1.50933742523193</v>
+        <v>1.50933718681335</v>
       </c>
       <c r="H263" t="n">
         <v>8077</v>
@@ -8170,7 +8170,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G269" t="n">
-        <v>1.57325065135956</v>
+        <v>1.57325053215027</v>
       </c>
       <c r="H269" t="n">
         <v>3905</v>
@@ -8257,7 +8257,7 @@
         <v>1.94599997997284</v>
       </c>
       <c r="G272" t="n">
-        <v>1.59455502033234</v>
+        <v>1.59455490112305</v>
       </c>
       <c r="H272" t="n">
         <v>20610</v>
@@ -8373,7 +8373,7 @@
         <v>1.97899997234344</v>
       </c>
       <c r="G276" t="n">
-        <v>1.62159526348114</v>
+        <v>1.62159538269043</v>
       </c>
       <c r="H276" t="n">
         <v>7358</v>
@@ -8431,7 +8431,7 @@
         <v>1.88399994373322</v>
       </c>
       <c r="G278" t="n">
-        <v>1.54375207424164</v>
+        <v>1.54375195503235</v>
       </c>
       <c r="H278" t="n">
         <v>4401</v>
@@ -8489,7 +8489,7 @@
         <v>1.9190000295639</v>
       </c>
       <c r="G280" t="n">
-        <v>1.57243132591248</v>
+        <v>1.57243120670319</v>
       </c>
       <c r="H280" t="n">
         <v>3432</v>
@@ -8518,7 +8518,7 @@
         <v>1.93700003623962</v>
       </c>
       <c r="G281" t="n">
-        <v>1.58718037605286</v>
+        <v>1.58718049526215</v>
       </c>
       <c r="H281" t="n">
         <v>5183</v>
@@ -8547,7 +8547,7 @@
         <v>1.88699996471405</v>
       </c>
       <c r="G282" t="n">
-        <v>1.54621028900146</v>
+        <v>1.54621040821075</v>
       </c>
       <c r="H282" t="n">
         <v>3939</v>
@@ -8663,7 +8663,7 @@
         <v>1.87300002574921</v>
       </c>
       <c r="G286" t="n">
-        <v>1.53473877906799</v>
+        <v>1.5347386598587</v>
       </c>
       <c r="H286" t="n">
         <v>168</v>
@@ -8692,7 +8692,7 @@
         <v>1.93099999427795</v>
       </c>
       <c r="G287" t="n">
-        <v>1.58226406574249</v>
+        <v>1.5822639465332</v>
       </c>
       <c r="H287" t="n">
         <v>1210</v>
@@ -8721,7 +8721,7 @@
         <v>1.88699996471405</v>
       </c>
       <c r="G288" t="n">
-        <v>1.54621028900146</v>
+        <v>1.54621040821075</v>
       </c>
       <c r="H288" t="n">
         <v>1302</v>
@@ -8779,7 +8779,7 @@
         <v>1.88800001144409</v>
       </c>
       <c r="G290" t="n">
-        <v>1.54702973365784</v>
+        <v>1.54702961444855</v>
       </c>
       <c r="H290" t="n">
         <v>3926</v>
@@ -8808,7 +8808,7 @@
         <v>1.88800001144409</v>
       </c>
       <c r="G291" t="n">
-        <v>1.54702973365784</v>
+        <v>1.54702961444855</v>
       </c>
       <c r="H291" t="n">
         <v>0</v>
@@ -8866,7 +8866,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G293" t="n">
-        <v>1.56505656242371</v>
+        <v>1.56505644321442</v>
       </c>
       <c r="H293" t="n">
         <v>3832</v>
@@ -8924,7 +8924,7 @@
         <v>1.88900005817413</v>
       </c>
       <c r="G295" t="n">
-        <v>1.54784917831421</v>
+        <v>1.5478492975235</v>
       </c>
       <c r="H295" t="n">
         <v>658</v>
@@ -8953,7 +8953,7 @@
         <v>1.88900005817413</v>
       </c>
       <c r="G296" t="n">
-        <v>1.54784917831421</v>
+        <v>1.5478492975235</v>
       </c>
       <c r="H296" t="n">
         <v>0</v>
@@ -9040,7 +9040,7 @@
         <v>1.89100003242493</v>
       </c>
       <c r="G299" t="n">
-        <v>1.54948794841766</v>
+        <v>1.54948806762695</v>
       </c>
       <c r="H299" t="n">
         <v>50</v>
@@ -9156,7 +9156,7 @@
         <v>1.89100003242493</v>
       </c>
       <c r="G303" t="n">
-        <v>1.54948794841766</v>
+        <v>1.54948806762695</v>
       </c>
       <c r="H303" t="n">
         <v>4699</v>
@@ -9214,7 +9214,7 @@
         <v>1.87899994850159</v>
       </c>
       <c r="G305" t="n">
-        <v>1.53965508937836</v>
+        <v>1.53965497016907</v>
       </c>
       <c r="H305" t="n">
         <v>5851</v>
@@ -9359,7 +9359,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G310" t="n">
-        <v>1.63060879707336</v>
+        <v>1.63060867786407</v>
       </c>
       <c r="H310" t="n">
         <v>16096</v>
@@ -9446,7 +9446,7 @@
         <v>2.06599998474121</v>
       </c>
       <c r="G313" t="n">
-        <v>1.69288313388824</v>
+        <v>1.69288325309753</v>
       </c>
       <c r="H313" t="n">
         <v>12262</v>
@@ -9533,7 +9533,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G316" t="n">
-        <v>1.65519070625305</v>
+        <v>1.65519082546234</v>
       </c>
       <c r="H316" t="n">
         <v>11483</v>
@@ -9591,7 +9591,7 @@
         <v>2.29800009727478</v>
       </c>
       <c r="G318" t="n">
-        <v>1.88298428058624</v>
+        <v>1.88298416137695</v>
       </c>
       <c r="H318" t="n">
         <v>94367</v>
@@ -9649,7 +9649,7 @@
         <v>2.23200011253357</v>
       </c>
       <c r="G320" t="n">
-        <v>1.82890403270721</v>
+        <v>1.82890367507935</v>
       </c>
       <c r="H320" t="n">
         <v>71318</v>
@@ -9707,7 +9707,7 @@
         <v>2.21799993515015</v>
       </c>
       <c r="G322" t="n">
-        <v>1.81743216514587</v>
+        <v>1.81743228435516</v>
       </c>
       <c r="H322" t="n">
         <v>3920</v>
@@ -9794,7 +9794,7 @@
         <v>2.29399991035461</v>
       </c>
       <c r="G325" t="n">
-        <v>1.87970650196075</v>
+        <v>1.87970638275146</v>
       </c>
       <c r="H325" t="n">
         <v>82545</v>
@@ -9823,7 +9823,7 @@
         <v>2.24799990653992</v>
       </c>
       <c r="G326" t="n">
-        <v>1.84201407432556</v>
+        <v>1.84201419353485</v>
       </c>
       <c r="H326" t="n">
         <v>15070</v>
@@ -9852,7 +9852,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G327" t="n">
-        <v>1.79448902606964</v>
+        <v>1.79448926448822</v>
       </c>
       <c r="H327" t="n">
         <v>24197</v>
@@ -9881,7 +9881,7 @@
         <v>2.19799995422363</v>
       </c>
       <c r="G328" t="n">
-        <v>1.80104398727417</v>
+        <v>1.80104434490204</v>
       </c>
       <c r="H328" t="n">
         <v>10476</v>
@@ -9910,7 +9910,7 @@
         <v>2.2260000705719</v>
       </c>
       <c r="G329" t="n">
-        <v>1.82398724555969</v>
+        <v>1.82398760318756</v>
       </c>
       <c r="H329" t="n">
         <v>4573</v>
@@ -9968,7 +9968,7 @@
         <v>2.19799995422363</v>
       </c>
       <c r="G331" t="n">
-        <v>1.80104398727417</v>
+        <v>1.80104434490204</v>
       </c>
       <c r="H331" t="n">
         <v>14355</v>
@@ -10026,7 +10026,7 @@
         <v>2.10800004005432</v>
       </c>
       <c r="G333" t="n">
-        <v>1.72729814052582</v>
+        <v>1.72729802131653</v>
       </c>
       <c r="H333" t="n">
         <v>5276</v>
@@ -10055,7 +10055,7 @@
         <v>2.13199996948242</v>
       </c>
       <c r="G334" t="n">
-        <v>1.74696373939514</v>
+        <v>1.74696362018585</v>
       </c>
       <c r="H334" t="n">
         <v>2476</v>
@@ -10113,7 +10113,7 @@
         <v>2.15199995040894</v>
       </c>
       <c r="G336" t="n">
-        <v>1.76335144042969</v>
+        <v>1.76335179805756</v>
       </c>
       <c r="H336" t="n">
         <v>6305</v>
@@ -10200,7 +10200,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G339" t="n">
-        <v>1.83545899391174</v>
+        <v>1.83545887470245</v>
       </c>
       <c r="H339" t="n">
         <v>10440</v>
@@ -10229,7 +10229,7 @@
         <v>2.25399994850159</v>
       </c>
       <c r="G340" t="n">
-        <v>1.84693038463593</v>
+        <v>1.84693050384521</v>
       </c>
       <c r="H340" t="n">
         <v>14315</v>
@@ -10287,7 +10287,7 @@
         <v>2.20799994468689</v>
       </c>
       <c r="G342" t="n">
-        <v>1.8092383146286</v>
+        <v>1.80923807621002</v>
       </c>
       <c r="H342" t="n">
         <v>10083</v>
@@ -10316,7 +10316,7 @@
         <v>2.21199989318848</v>
       </c>
       <c r="G343" t="n">
-        <v>1.81251561641693</v>
+        <v>1.81251573562622</v>
       </c>
       <c r="H343" t="n">
         <v>17654</v>
@@ -10374,7 +10374,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G345" t="n">
-        <v>1.83545899391174</v>
+        <v>1.83545887470245</v>
       </c>
       <c r="H345" t="n">
         <v>20200</v>
@@ -10461,7 +10461,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G348" t="n">
-        <v>1.87642896175385</v>
+        <v>1.87642884254456</v>
       </c>
       <c r="H348" t="n">
         <v>15563</v>
@@ -10519,7 +10519,7 @@
         <v>2.31800007820129</v>
       </c>
       <c r="G350" t="n">
-        <v>1.89937233924866</v>
+        <v>1.89937222003937</v>
       </c>
       <c r="H350" t="n">
         <v>4160</v>
@@ -10548,7 +10548,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G351" t="n">
-        <v>1.91739940643311</v>
+        <v>1.91739892959595</v>
       </c>
       <c r="H351" t="n">
         <v>6240</v>
@@ -10577,7 +10577,7 @@
         <v>2.25600004196167</v>
       </c>
       <c r="G352" t="n">
-        <v>1.84856963157654</v>
+        <v>1.84856951236725</v>
       </c>
       <c r="H352" t="n">
         <v>9093</v>
@@ -10635,7 +10635,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G354" t="n">
-        <v>1.86823499202728</v>
+        <v>1.86823511123657</v>
       </c>
       <c r="H354" t="n">
         <v>9851</v>
@@ -80125,6 +80125,35 @@
         <v>9</v>
       </c>
       <c r="I2750" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2751">
+      <c r="A2751" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2751" s="1" t="n">
+        <v>46322.3333333333</v>
+      </c>
+      <c r="C2751" t="n">
+        <v>0.990000009536743</v>
+      </c>
+      <c r="D2751" t="n">
+        <v>0.990000009536743</v>
+      </c>
+      <c r="E2751" t="n">
+        <v>0.990000009536743</v>
+      </c>
+      <c r="F2751" t="n">
+        <v>0.990000009536743</v>
+      </c>
+      <c r="G2751" t="n">
+        <v>0.990000009536743</v>
+      </c>
+      <c r="H2751" t="n">
+        <v>5</v>
+      </c>
+      <c r="I2751" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/RAT.MI.xlsx
+++ b/data/RAT.MI.xlsx
@@ -427,7 +427,7 @@
         <v>2.3659999370575</v>
       </c>
       <c r="G2" t="n">
-        <v>1.85825955867767</v>
+        <v>1.85825932025909</v>
       </c>
       <c r="H2" t="n">
         <v>1350</v>
@@ -456,7 +456,7 @@
         <v>2.43600010871887</v>
       </c>
       <c r="G3" t="n">
-        <v>1.91323781013489</v>
+        <v>1.91323745250702</v>
       </c>
       <c r="H3" t="n">
         <v>3199</v>
@@ -543,7 +543,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G6" t="n">
-        <v>1.8849630355835</v>
+        <v>1.88496351242065</v>
       </c>
       <c r="H6" t="n">
         <v>5635</v>
@@ -572,7 +572,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G7" t="n">
-        <v>1.8849630355835</v>
+        <v>1.88496351242065</v>
       </c>
       <c r="H7" t="n">
         <v>1000</v>
@@ -601,7 +601,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G8" t="n">
-        <v>1.92423331737518</v>
+        <v>1.92423295974731</v>
       </c>
       <c r="H8" t="n">
         <v>4000</v>
@@ -630,7 +630,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G9" t="n">
-        <v>1.8849630355835</v>
+        <v>1.88496351242065</v>
       </c>
       <c r="H9" t="n">
         <v>155</v>
@@ -659,7 +659,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G10" t="n">
-        <v>1.8849630355835</v>
+        <v>1.88496351242065</v>
       </c>
       <c r="H10" t="n">
         <v>559</v>
@@ -688,7 +688,7 @@
         <v>2.3659999370575</v>
       </c>
       <c r="G11" t="n">
-        <v>1.85825955867767</v>
+        <v>1.85825932025909</v>
       </c>
       <c r="H11" t="n">
         <v>1414</v>
@@ -717,7 +717,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G12" t="n">
-        <v>1.80642294883728</v>
+        <v>1.80642306804657</v>
       </c>
       <c r="H12" t="n">
         <v>270</v>
@@ -746,7 +746,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G13" t="n">
-        <v>1.80642294883728</v>
+        <v>1.80642306804657</v>
       </c>
       <c r="H13" t="n">
         <v>1200</v>
@@ -775,7 +775,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G14" t="n">
-        <v>1.82998514175415</v>
+        <v>1.82998490333557</v>
       </c>
       <c r="H14" t="n">
         <v>193</v>
@@ -833,7 +833,7 @@
         <v>2.25</v>
       </c>
       <c r="G16" t="n">
-        <v>1.76715302467346</v>
+        <v>1.76715290546417</v>
       </c>
       <c r="H16" t="n">
         <v>2070</v>
@@ -862,7 +862,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G17" t="n">
-        <v>1.85354685783386</v>
+        <v>1.85354673862457</v>
       </c>
       <c r="H17" t="n">
         <v>4705</v>
@@ -891,7 +891,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G18" t="n">
-        <v>1.85354685783386</v>
+        <v>1.85354673862457</v>
       </c>
       <c r="H18" t="n">
         <v>2000</v>
@@ -920,7 +920,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G19" t="n">
-        <v>1.86925530433655</v>
+        <v>1.86925506591797</v>
       </c>
       <c r="H19" t="n">
         <v>3200</v>
@@ -949,7 +949,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G20" t="n">
-        <v>1.87710905075073</v>
+        <v>1.87710916996002</v>
       </c>
       <c r="H20" t="n">
         <v>460</v>
@@ -978,7 +978,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G21" t="n">
-        <v>1.89281713962555</v>
+        <v>1.89281725883484</v>
       </c>
       <c r="H21" t="n">
         <v>100</v>
@@ -1007,7 +1007,7 @@
         <v>2.37800002098083</v>
       </c>
       <c r="G22" t="n">
-        <v>1.86768436431885</v>
+        <v>1.86768424510956</v>
       </c>
       <c r="H22" t="n">
         <v>2858</v>
@@ -1065,7 +1065,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G24" t="n">
-        <v>1.83783888816833</v>
+        <v>1.83783900737762</v>
       </c>
       <c r="H24" t="n">
         <v>1435</v>
@@ -1094,7 +1094,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G25" t="n">
-        <v>1.83783888816833</v>
+        <v>1.83783900737762</v>
       </c>
       <c r="H25" t="n">
         <v>475</v>
@@ -1123,7 +1123,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G26" t="n">
-        <v>1.8849630355835</v>
+        <v>1.88496351242065</v>
       </c>
       <c r="H26" t="n">
         <v>330</v>
@@ -1152,7 +1152,7 @@
         <v>2.38800001144409</v>
       </c>
       <c r="G27" t="n">
-        <v>1.8755384683609</v>
+        <v>1.87553822994232</v>
       </c>
       <c r="H27" t="n">
         <v>2173</v>
@@ -1181,7 +1181,7 @@
         <v>2.38800001144409</v>
       </c>
       <c r="G28" t="n">
-        <v>1.8755384683609</v>
+        <v>1.87553822994232</v>
       </c>
       <c r="H28" t="n">
         <v>0</v>
@@ -1210,7 +1210,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G29" t="n">
-        <v>1.8849630355835</v>
+        <v>1.88496351242065</v>
       </c>
       <c r="H29" t="n">
         <v>1810</v>
@@ -1239,7 +1239,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G30" t="n">
-        <v>1.80642294883728</v>
+        <v>1.80642306804657</v>
       </c>
       <c r="H30" t="n">
         <v>10919</v>
@@ -1297,7 +1297,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G32" t="n">
-        <v>1.84569299221039</v>
+        <v>1.84569311141968</v>
       </c>
       <c r="H32" t="n">
         <v>250</v>
@@ -1471,7 +1471,7 @@
         <v>2.29800009727478</v>
       </c>
       <c r="G38" t="n">
-        <v>1.80485212802887</v>
+        <v>1.80485200881958</v>
       </c>
       <c r="H38" t="n">
         <v>7831</v>
@@ -1500,7 +1500,7 @@
         <v>2.31800007820129</v>
       </c>
       <c r="G39" t="n">
-        <v>1.82056021690369</v>
+        <v>1.82056033611298</v>
       </c>
       <c r="H39" t="n">
         <v>330</v>
@@ -1529,7 +1529,7 @@
         <v>2.31399989128113</v>
       </c>
       <c r="G40" t="n">
-        <v>1.81741833686829</v>
+        <v>1.81741845607758</v>
       </c>
       <c r="H40" t="n">
         <v>150</v>
@@ -1558,7 +1558,7 @@
         <v>2.31399989128113</v>
       </c>
       <c r="G41" t="n">
-        <v>1.81741833686829</v>
+        <v>1.81741845607758</v>
       </c>
       <c r="H41" t="n">
         <v>0</v>
@@ -1587,7 +1587,7 @@
         <v>2.31399989128113</v>
       </c>
       <c r="G42" t="n">
-        <v>1.81741833686829</v>
+        <v>1.81741845607758</v>
       </c>
       <c r="H42" t="n">
         <v>0</v>
@@ -1674,7 +1674,7 @@
         <v>2.37800002098083</v>
       </c>
       <c r="G45" t="n">
-        <v>1.86768436431885</v>
+        <v>1.86768424510956</v>
       </c>
       <c r="H45" t="n">
         <v>2230</v>
@@ -1703,7 +1703,7 @@
         <v>2.35599994659424</v>
       </c>
       <c r="G46" t="n">
-        <v>1.85040545463562</v>
+        <v>1.85040533542633</v>
       </c>
       <c r="H46" t="n">
         <v>253</v>
@@ -1790,7 +1790,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G49" t="n">
-        <v>1.81427669525146</v>
+        <v>1.81427693367004</v>
       </c>
       <c r="H49" t="n">
         <v>1530</v>
@@ -1819,7 +1819,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G50" t="n">
-        <v>1.84569299221039</v>
+        <v>1.84569311141968</v>
       </c>
       <c r="H50" t="n">
         <v>396</v>
@@ -1935,7 +1935,7 @@
         <v>2.34400010108948</v>
       </c>
       <c r="G54" t="n">
-        <v>1.84098076820374</v>
+        <v>1.84098052978516</v>
       </c>
       <c r="H54" t="n">
         <v>600</v>
@@ -1964,7 +1964,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G55" t="n">
-        <v>1.84569299221039</v>
+        <v>1.84569311141968</v>
       </c>
       <c r="H55" t="n">
         <v>386</v>
@@ -1993,7 +1993,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G56" t="n">
-        <v>1.84569299221039</v>
+        <v>1.84569311141968</v>
       </c>
       <c r="H56" t="n">
         <v>5025</v>
@@ -2022,7 +2022,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G57" t="n">
-        <v>1.85354685783386</v>
+        <v>1.85354673862457</v>
       </c>
       <c r="H57" t="n">
         <v>50</v>
@@ -2138,7 +2138,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G61" t="n">
-        <v>1.81427669525146</v>
+        <v>1.81427693367004</v>
       </c>
       <c r="H61" t="n">
         <v>150</v>
@@ -2196,7 +2196,7 @@
         <v>2.35599994659424</v>
       </c>
       <c r="G63" t="n">
-        <v>1.85040545463562</v>
+        <v>1.85040533542633</v>
       </c>
       <c r="H63" t="n">
         <v>100</v>
@@ -2225,7 +2225,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G64" t="n">
-        <v>1.84569299221039</v>
+        <v>1.84569311141968</v>
       </c>
       <c r="H64" t="n">
         <v>1054</v>
@@ -2254,7 +2254,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G65" t="n">
-        <v>1.92423331737518</v>
+        <v>1.92423295974731</v>
       </c>
       <c r="H65" t="n">
         <v>19358</v>
@@ -2283,7 +2283,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G66" t="n">
-        <v>1.92423331737518</v>
+        <v>1.92423295974731</v>
       </c>
       <c r="H66" t="n">
         <v>0</v>
@@ -2341,7 +2341,7 @@
         <v>2.4779999256134</v>
       </c>
       <c r="G68" t="n">
-        <v>1.94622421264648</v>
+        <v>1.94622445106506</v>
       </c>
       <c r="H68" t="n">
         <v>120</v>
@@ -2370,7 +2370,7 @@
         <v>2.48799991607666</v>
       </c>
       <c r="G69" t="n">
-        <v>1.95407855510712</v>
+        <v>1.95407807826996</v>
       </c>
       <c r="H69" t="n">
         <v>16224</v>
@@ -2399,7 +2399,7 @@
         <v>2.5</v>
       </c>
       <c r="G70" t="n">
-        <v>1.963503241539</v>
+        <v>1.96350347995758</v>
       </c>
       <c r="H70" t="n">
         <v>23697</v>
@@ -2428,7 +2428,7 @@
         <v>2.50200009346008</v>
       </c>
       <c r="G71" t="n">
-        <v>1.96507394313812</v>
+        <v>1.96507406234741</v>
       </c>
       <c r="H71" t="n">
         <v>350</v>
@@ -2457,7 +2457,7 @@
         <v>2.53800010681152</v>
       </c>
       <c r="G72" t="n">
-        <v>1.99334871768951</v>
+        <v>1.99334859848022</v>
       </c>
       <c r="H72" t="n">
         <v>1951</v>
@@ -2486,7 +2486,7 @@
         <v>2.55200004577637</v>
       </c>
       <c r="G73" t="n">
-        <v>2.00434422492981</v>
+        <v>2.00434446334839</v>
       </c>
       <c r="H73" t="n">
         <v>3450</v>
@@ -2515,7 +2515,7 @@
         <v>2.5</v>
       </c>
       <c r="G74" t="n">
-        <v>1.963503241539</v>
+        <v>1.96350347995758</v>
       </c>
       <c r="H74" t="n">
         <v>1853</v>
@@ -2544,7 +2544,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G75" t="n">
-        <v>1.98706519603729</v>
+        <v>1.98706531524658</v>
       </c>
       <c r="H75" t="n">
         <v>41607</v>
@@ -2573,7 +2573,7 @@
         <v>2.50200009346008</v>
       </c>
       <c r="G76" t="n">
-        <v>1.96507394313812</v>
+        <v>1.96507406234741</v>
       </c>
       <c r="H76" t="n">
         <v>3085</v>
@@ -2660,7 +2660,7 @@
         <v>2.45799994468689</v>
       </c>
       <c r="G79" t="n">
-        <v>1.93051648139954</v>
+        <v>1.93051624298096</v>
       </c>
       <c r="H79" t="n">
         <v>9175</v>
@@ -2689,7 +2689,7 @@
         <v>2.45799994468689</v>
       </c>
       <c r="G80" t="n">
-        <v>1.93051648139954</v>
+        <v>1.93051624298096</v>
       </c>
       <c r="H80" t="n">
         <v>1464</v>
@@ -2718,7 +2718,7 @@
         <v>2.5</v>
       </c>
       <c r="G81" t="n">
-        <v>1.963503241539</v>
+        <v>1.96350347995758</v>
       </c>
       <c r="H81" t="n">
         <v>50</v>
@@ -2747,7 +2747,7 @@
         <v>2.49799990653992</v>
       </c>
       <c r="G82" t="n">
-        <v>1.96193218231201</v>
+        <v>1.9619323015213</v>
       </c>
       <c r="H82" t="n">
         <v>2294</v>
@@ -2776,7 +2776,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G83" t="n">
-        <v>1.93994116783142</v>
+        <v>1.93994128704071</v>
       </c>
       <c r="H83" t="n">
         <v>1443</v>
@@ -2805,7 +2805,7 @@
         <v>2.48799991607666</v>
       </c>
       <c r="G84" t="n">
-        <v>1.95407855510712</v>
+        <v>1.95407807826996</v>
       </c>
       <c r="H84" t="n">
         <v>371</v>
@@ -2834,7 +2834,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G85" t="n">
-        <v>1.95564913749695</v>
+        <v>1.95564925670624</v>
       </c>
       <c r="H85" t="n">
         <v>2700</v>
@@ -2863,7 +2863,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G86" t="n">
-        <v>1.95564913749695</v>
+        <v>1.95564925670624</v>
       </c>
       <c r="H86" t="n">
         <v>0</v>
@@ -2892,7 +2892,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G87" t="n">
-        <v>1.93994116783142</v>
+        <v>1.93994128704071</v>
       </c>
       <c r="H87" t="n">
         <v>303</v>
@@ -2950,7 +2950,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G89" t="n">
-        <v>1.8849630355835</v>
+        <v>1.88496351242065</v>
       </c>
       <c r="H89" t="n">
         <v>4181</v>
@@ -3066,7 +3066,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G93" t="n">
-        <v>1.87710905075073</v>
+        <v>1.87710916996002</v>
       </c>
       <c r="H93" t="n">
         <v>2251</v>
@@ -3095,7 +3095,7 @@
         <v>2.38599991798401</v>
       </c>
       <c r="G94" t="n">
-        <v>1.87396764755249</v>
+        <v>1.8739675283432</v>
       </c>
       <c r="H94" t="n">
         <v>11190</v>
@@ -3124,7 +3124,7 @@
         <v>2.38599991798401</v>
       </c>
       <c r="G95" t="n">
-        <v>1.87396764755249</v>
+        <v>1.8739675283432</v>
       </c>
       <c r="H95" t="n">
         <v>0</v>
@@ -3153,7 +3153,7 @@
         <v>2.29800009727478</v>
       </c>
       <c r="G96" t="n">
-        <v>1.80485212802887</v>
+        <v>1.80485200881958</v>
       </c>
       <c r="H96" t="n">
         <v>5665</v>
@@ -3182,7 +3182,7 @@
         <v>2.29800009727478</v>
       </c>
       <c r="G97" t="n">
-        <v>1.80485212802887</v>
+        <v>1.80485200881958</v>
       </c>
       <c r="H97" t="n">
         <v>50</v>
@@ -3240,7 +3240,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G99" t="n">
-        <v>1.89281713962555</v>
+        <v>1.89281725883484</v>
       </c>
       <c r="H99" t="n">
         <v>14550</v>
@@ -3269,7 +3269,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G100" t="n">
-        <v>1.93378698825836</v>
+        <v>1.93378674983978</v>
       </c>
       <c r="H100" t="n">
         <v>1125</v>
@@ -3298,7 +3298,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G101" t="n">
-        <v>1.95017528533936</v>
+        <v>1.95017516613007</v>
       </c>
       <c r="H101" t="n">
         <v>176</v>
@@ -3327,7 +3327,7 @@
         <v>2.34599995613098</v>
       </c>
       <c r="G102" t="n">
-        <v>1.92231547832489</v>
+        <v>1.92231559753418</v>
       </c>
       <c r="H102" t="n">
         <v>195</v>
@@ -3356,7 +3356,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G103" t="n">
-        <v>1.93378698825836</v>
+        <v>1.93378674983978</v>
       </c>
       <c r="H103" t="n">
         <v>3800</v>
@@ -3414,7 +3414,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G105" t="n">
-        <v>1.96656346321106</v>
+        <v>1.96656358242035</v>
       </c>
       <c r="H105" t="n">
         <v>160</v>
@@ -3443,7 +3443,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G106" t="n">
-        <v>1.96656346321106</v>
+        <v>1.96656358242035</v>
       </c>
       <c r="H106" t="n">
         <v>0</v>
@@ -3501,7 +3501,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G108" t="n">
-        <v>1.95836913585663</v>
+        <v>1.95836925506592</v>
       </c>
       <c r="H108" t="n">
         <v>668</v>
@@ -3530,7 +3530,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G109" t="n">
-        <v>1.95836913585663</v>
+        <v>1.95836925506592</v>
       </c>
       <c r="H109" t="n">
         <v>0</v>
@@ -3559,7 +3559,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G110" t="n">
-        <v>1.95017528533936</v>
+        <v>1.95017516613007</v>
       </c>
       <c r="H110" t="n">
         <v>403</v>
@@ -3588,7 +3588,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G111" t="n">
-        <v>1.95017528533936</v>
+        <v>1.95017516613007</v>
       </c>
       <c r="H111" t="n">
         <v>0</v>
@@ -3617,7 +3617,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G112" t="n">
-        <v>1.91739892959595</v>
+        <v>1.91739904880524</v>
       </c>
       <c r="H112" t="n">
         <v>778</v>
@@ -3646,7 +3646,7 @@
         <v>2.36199998855591</v>
       </c>
       <c r="G113" t="n">
-        <v>1.9354259967804</v>
+        <v>1.93542611598969</v>
       </c>
       <c r="H113" t="n">
         <v>1461</v>
@@ -3675,7 +3675,7 @@
         <v>2.36199998855591</v>
       </c>
       <c r="G114" t="n">
-        <v>1.9354259967804</v>
+        <v>1.93542611598969</v>
       </c>
       <c r="H114" t="n">
         <v>0</v>
@@ -3704,7 +3704,7 @@
         <v>2.36199998855591</v>
       </c>
       <c r="G115" t="n">
-        <v>1.9354259967804</v>
+        <v>1.93542611598969</v>
       </c>
       <c r="H115" t="n">
         <v>635</v>
@@ -3791,7 +3791,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G118" t="n">
-        <v>1.91739892959595</v>
+        <v>1.91739904880524</v>
       </c>
       <c r="H118" t="n">
         <v>2740</v>
@@ -3820,7 +3820,7 @@
         <v>2.33400011062622</v>
       </c>
       <c r="G119" t="n">
-        <v>1.91248297691345</v>
+        <v>1.91248309612274</v>
       </c>
       <c r="H119" t="n">
         <v>2002</v>
@@ -3849,7 +3849,7 @@
         <v>2.33200001716614</v>
       </c>
       <c r="G120" t="n">
-        <v>1.91084384918213</v>
+        <v>1.91084396839142</v>
       </c>
       <c r="H120" t="n">
         <v>1532</v>
@@ -3878,7 +3878,7 @@
         <v>2.33200001716614</v>
       </c>
       <c r="G121" t="n">
-        <v>1.91084384918213</v>
+        <v>1.91084396839142</v>
       </c>
       <c r="H121" t="n">
         <v>0</v>
@@ -3907,7 +3907,7 @@
         <v>2.33400011062622</v>
       </c>
       <c r="G122" t="n">
-        <v>1.91248297691345</v>
+        <v>1.91248309612274</v>
       </c>
       <c r="H122" t="n">
         <v>1260</v>
@@ -3936,7 +3936,7 @@
         <v>2.33400011062622</v>
       </c>
       <c r="G123" t="n">
-        <v>1.91248297691345</v>
+        <v>1.91248309612274</v>
       </c>
       <c r="H123" t="n">
         <v>0</v>
@@ -3965,7 +3965,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G124" t="n">
-        <v>1.83545887470245</v>
+        <v>1.83545899391174</v>
       </c>
       <c r="H124" t="n">
         <v>348</v>
@@ -3994,7 +3994,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G125" t="n">
-        <v>1.8026829957962</v>
+        <v>1.80268287658691</v>
       </c>
       <c r="H125" t="n">
         <v>3159</v>
@@ -4052,7 +4052,7 @@
         <v>2.23600006103516</v>
       </c>
       <c r="G127" t="n">
-        <v>1.83218133449554</v>
+        <v>1.83218145370483</v>
       </c>
       <c r="H127" t="n">
         <v>773</v>
@@ -4139,7 +4139,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G130" t="n">
-        <v>1.86823511123657</v>
+        <v>1.86823523044586</v>
       </c>
       <c r="H130" t="n">
         <v>2288</v>
@@ -4226,7 +4226,7 @@
         <v>2.32800006866455</v>
       </c>
       <c r="G133" t="n">
-        <v>1.90756618976593</v>
+        <v>1.90756630897522</v>
       </c>
       <c r="H133" t="n">
         <v>510</v>
@@ -4255,7 +4255,7 @@
         <v>2.32800006866455</v>
       </c>
       <c r="G134" t="n">
-        <v>1.90756618976593</v>
+        <v>1.90756630897522</v>
       </c>
       <c r="H134" t="n">
         <v>0</v>
@@ -4284,7 +4284,7 @@
         <v>2.32800006866455</v>
       </c>
       <c r="G135" t="n">
-        <v>1.90756618976593</v>
+        <v>1.90756630897522</v>
       </c>
       <c r="H135" t="n">
         <v>0</v>
@@ -4313,7 +4313,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G136" t="n">
-        <v>1.89281690120697</v>
+        <v>1.89281702041626</v>
       </c>
       <c r="H136" t="n">
         <v>6553</v>
@@ -4342,7 +4342,7 @@
         <v>2.32599997520447</v>
       </c>
       <c r="G137" t="n">
-        <v>1.90592753887177</v>
+        <v>1.90592765808105</v>
       </c>
       <c r="H137" t="n">
         <v>600</v>
@@ -4371,7 +4371,7 @@
         <v>2.32599997520447</v>
       </c>
       <c r="G138" t="n">
-        <v>1.90592753887177</v>
+        <v>1.90592765808105</v>
       </c>
       <c r="H138" t="n">
         <v>815</v>
@@ -4400,7 +4400,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G139" t="n">
-        <v>1.88462293148041</v>
+        <v>1.88462316989899</v>
       </c>
       <c r="H139" t="n">
         <v>110</v>
@@ -4429,7 +4429,7 @@
         <v>2.32599997520447</v>
       </c>
       <c r="G140" t="n">
-        <v>1.90592753887177</v>
+        <v>1.90592765808105</v>
       </c>
       <c r="H140" t="n">
         <v>50</v>
@@ -4458,7 +4458,7 @@
         <v>2.32599997520447</v>
       </c>
       <c r="G141" t="n">
-        <v>1.90592753887177</v>
+        <v>1.90592765808105</v>
       </c>
       <c r="H141" t="n">
         <v>0</v>
@@ -4487,7 +4487,7 @@
         <v>2.32800006866455</v>
       </c>
       <c r="G142" t="n">
-        <v>1.90756618976593</v>
+        <v>1.90756630897522</v>
       </c>
       <c r="H142" t="n">
         <v>80</v>
@@ -4603,7 +4603,7 @@
         <v>2.31599998474121</v>
       </c>
       <c r="G146" t="n">
-        <v>1.89773344993591</v>
+        <v>1.8977335691452</v>
       </c>
       <c r="H146" t="n">
         <v>5883</v>
@@ -4632,7 +4632,7 @@
         <v>2.32599997520447</v>
       </c>
       <c r="G147" t="n">
-        <v>1.90592753887177</v>
+        <v>1.90592765808105</v>
       </c>
       <c r="H147" t="n">
         <v>1070</v>
@@ -4690,7 +4690,7 @@
         <v>2.2260000705719</v>
       </c>
       <c r="G149" t="n">
-        <v>1.82398760318756</v>
+        <v>1.82398748397827</v>
       </c>
       <c r="H149" t="n">
         <v>2820</v>
@@ -4835,7 +4835,7 @@
         <v>2.13800001144409</v>
       </c>
       <c r="G154" t="n">
-        <v>1.75188016891479</v>
+        <v>1.75188004970551</v>
       </c>
       <c r="H154" t="n">
         <v>6911</v>
@@ -4864,7 +4864,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G155" t="n">
-        <v>1.75351905822754</v>
+        <v>1.75351893901825</v>
       </c>
       <c r="H155" t="n">
         <v>606</v>
@@ -4893,7 +4893,7 @@
         <v>2.17199993133545</v>
       </c>
       <c r="G156" t="n">
-        <v>1.77973961830139</v>
+        <v>1.77973973751068</v>
       </c>
       <c r="H156" t="n">
         <v>975</v>
@@ -4922,7 +4922,7 @@
         <v>2.17199993133545</v>
       </c>
       <c r="G157" t="n">
-        <v>1.77973961830139</v>
+        <v>1.77973973751068</v>
       </c>
       <c r="H157" t="n">
         <v>0</v>
@@ -5357,7 +5357,7 @@
         <v>2.1159999370575</v>
       </c>
       <c r="G172" t="n">
-        <v>1.73385310173035</v>
+        <v>1.73385322093964</v>
       </c>
       <c r="H172" t="n">
         <v>5150</v>
@@ -5386,7 +5386,7 @@
         <v>2.1159999370575</v>
       </c>
       <c r="G173" t="n">
-        <v>1.73385310173035</v>
+        <v>1.73385322093964</v>
       </c>
       <c r="H173" t="n">
         <v>0</v>
@@ -5531,7 +5531,7 @@
         <v>1.9650000333786</v>
       </c>
       <c r="G178" t="n">
-        <v>1.61012363433838</v>
+        <v>1.61012375354767</v>
       </c>
       <c r="H178" t="n">
         <v>11222</v>
@@ -5879,7 +5879,7 @@
         <v>2</v>
       </c>
       <c r="G190" t="n">
-        <v>1.63880264759064</v>
+        <v>1.63880276679993</v>
       </c>
       <c r="H190" t="n">
         <v>288</v>
@@ -6082,7 +6082,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G197" t="n">
-        <v>1.65519082546234</v>
+        <v>1.65519070625305</v>
       </c>
       <c r="H197" t="n">
         <v>4191</v>
@@ -6111,7 +6111,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G198" t="n">
-        <v>1.65519082546234</v>
+        <v>1.65519070625305</v>
       </c>
       <c r="H198" t="n">
         <v>0</v>
@@ -6140,7 +6140,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G199" t="n">
-        <v>1.65519082546234</v>
+        <v>1.65519070625305</v>
       </c>
       <c r="H199" t="n">
         <v>1000</v>
@@ -6169,7 +6169,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G200" t="n">
-        <v>1.65519082546234</v>
+        <v>1.65519070625305</v>
       </c>
       <c r="H200" t="n">
         <v>0</v>
@@ -6198,7 +6198,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G201" t="n">
-        <v>1.65519082546234</v>
+        <v>1.65519070625305</v>
       </c>
       <c r="H201" t="n">
         <v>100</v>
@@ -6227,7 +6227,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G202" t="n">
-        <v>1.6469966173172</v>
+        <v>1.64699673652649</v>
       </c>
       <c r="H202" t="n">
         <v>487</v>
@@ -6256,7 +6256,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G203" t="n">
-        <v>1.6469966173172</v>
+        <v>1.64699673652649</v>
       </c>
       <c r="H203" t="n">
         <v>4278</v>
@@ -6285,7 +6285,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G204" t="n">
-        <v>1.6469966173172</v>
+        <v>1.64699673652649</v>
       </c>
       <c r="H204" t="n">
         <v>180</v>
@@ -6314,7 +6314,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G205" t="n">
-        <v>1.6469966173172</v>
+        <v>1.64699673652649</v>
       </c>
       <c r="H205" t="n">
         <v>0</v>
@@ -6343,7 +6343,7 @@
         <v>1.99899995326996</v>
       </c>
       <c r="G206" t="n">
-        <v>1.63798320293427</v>
+        <v>1.63798308372498</v>
       </c>
       <c r="H206" t="n">
         <v>2595</v>
@@ -6459,7 +6459,7 @@
         <v>1.94700002670288</v>
       </c>
       <c r="G210" t="n">
-        <v>1.59537446498871</v>
+        <v>1.59537434577942</v>
       </c>
       <c r="H210" t="n">
         <v>7151</v>
@@ -6488,7 +6488,7 @@
         <v>1.92700004577637</v>
       </c>
       <c r="G211" t="n">
-        <v>1.578986287117</v>
+        <v>1.57898640632629</v>
       </c>
       <c r="H211" t="n">
         <v>3280</v>
@@ -6517,7 +6517,7 @@
         <v>1.94200003147125</v>
       </c>
       <c r="G212" t="n">
-        <v>1.59127736091614</v>
+        <v>1.59127748012543</v>
       </c>
       <c r="H212" t="n">
         <v>8960</v>
@@ -6546,7 +6546,7 @@
         <v>1.94200003147125</v>
       </c>
       <c r="G213" t="n">
-        <v>1.59127736091614</v>
+        <v>1.59127748012543</v>
       </c>
       <c r="H213" t="n">
         <v>0</v>
@@ -6633,7 +6633,7 @@
         <v>1.91600000858307</v>
       </c>
       <c r="G216" t="n">
-        <v>1.56997287273407</v>
+        <v>1.56997299194336</v>
       </c>
       <c r="H216" t="n">
         <v>8053</v>
@@ -6662,7 +6662,7 @@
         <v>1.91199994087219</v>
       </c>
       <c r="G217" t="n">
-        <v>1.56669521331787</v>
+        <v>1.56669533252716</v>
       </c>
       <c r="H217" t="n">
         <v>1680</v>
@@ -6691,7 +6691,7 @@
         <v>1.90199995040894</v>
       </c>
       <c r="G218" t="n">
-        <v>1.5585013628006</v>
+        <v>1.55850124359131</v>
       </c>
       <c r="H218" t="n">
         <v>2601</v>
@@ -6720,7 +6720,7 @@
         <v>1.9559999704361</v>
       </c>
       <c r="G219" t="n">
-        <v>1.60274910926819</v>
+        <v>1.6027489900589</v>
       </c>
       <c r="H219" t="n">
         <v>100</v>
@@ -6749,7 +6749,7 @@
         <v>1.95700001716614</v>
       </c>
       <c r="G220" t="n">
-        <v>1.60356843471527</v>
+        <v>1.60356855392456</v>
       </c>
       <c r="H220" t="n">
         <v>5560</v>
@@ -6778,7 +6778,7 @@
         <v>1.9559999704361</v>
       </c>
       <c r="G221" t="n">
-        <v>1.60274910926819</v>
+        <v>1.6027489900589</v>
       </c>
       <c r="H221" t="n">
         <v>280</v>
@@ -6807,7 +6807,7 @@
         <v>1.9559999704361</v>
       </c>
       <c r="G222" t="n">
-        <v>1.60274910926819</v>
+        <v>1.6027489900589</v>
       </c>
       <c r="H222" t="n">
         <v>0</v>
@@ -6952,7 +6952,7 @@
         <v>1.8860000371933</v>
       </c>
       <c r="G227" t="n">
-        <v>1.54539096355438</v>
+        <v>1.54539108276367</v>
       </c>
       <c r="H227" t="n">
         <v>11268</v>
@@ -6981,7 +6981,7 @@
         <v>1.67999994754791</v>
       </c>
       <c r="G228" t="n">
-        <v>1.37659406661987</v>
+        <v>1.37659418582916</v>
       </c>
       <c r="H228" t="n">
         <v>40640</v>
@@ -7068,7 +7068,7 @@
         <v>1.77900004386902</v>
       </c>
       <c r="G231" t="n">
-        <v>1.45771491527557</v>
+        <v>1.45771503448486</v>
       </c>
       <c r="H231" t="n">
         <v>4259</v>
@@ -7155,7 +7155,7 @@
         <v>1.96800005435944</v>
       </c>
       <c r="G234" t="n">
-        <v>1.61258172988892</v>
+        <v>1.61258184909821</v>
       </c>
       <c r="H234" t="n">
         <v>5088</v>
@@ -7329,7 +7329,7 @@
         <v>1.88199996948242</v>
       </c>
       <c r="G240" t="n">
-        <v>1.54211318492889</v>
+        <v>1.54211330413818</v>
       </c>
       <c r="H240" t="n">
         <v>14504</v>
@@ -7387,7 +7387,7 @@
         <v>1.89800000190735</v>
       </c>
       <c r="G242" t="n">
-        <v>1.5552237033844</v>
+        <v>1.55522382259369</v>
       </c>
       <c r="H242" t="n">
         <v>6374</v>
@@ -7416,7 +7416,7 @@
         <v>1.89800000190735</v>
       </c>
       <c r="G243" t="n">
-        <v>1.5552237033844</v>
+        <v>1.55522382259369</v>
       </c>
       <c r="H243" t="n">
         <v>3380</v>
@@ -7445,7 +7445,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G244" t="n">
-        <v>1.56505644321442</v>
+        <v>1.56505656242371</v>
       </c>
       <c r="H244" t="n">
         <v>627</v>
@@ -7619,7 +7619,7 @@
         <v>1.85699999332428</v>
       </c>
       <c r="G250" t="n">
-        <v>1.52162837982178</v>
+        <v>1.52162826061249</v>
       </c>
       <c r="H250" t="n">
         <v>5809</v>
@@ -7677,7 +7677,7 @@
         <v>1.83599996566772</v>
       </c>
       <c r="G252" t="n">
-        <v>1.5044207572937</v>
+        <v>1.50442087650299</v>
       </c>
       <c r="H252" t="n">
         <v>920</v>
@@ -7706,7 +7706,7 @@
         <v>1.84399998188019</v>
       </c>
       <c r="G253" t="n">
-        <v>1.5109760761261</v>
+        <v>1.51097595691681</v>
       </c>
       <c r="H253" t="n">
         <v>15268</v>
@@ -7764,7 +7764,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G255" t="n">
-        <v>1.51589250564575</v>
+        <v>1.51589262485504</v>
       </c>
       <c r="H255" t="n">
         <v>3734</v>
@@ -8054,7 +8054,7 @@
         <v>1.83399999141693</v>
       </c>
       <c r="G265" t="n">
-        <v>1.50278198719025</v>
+        <v>1.50278210639954</v>
       </c>
       <c r="H265" t="n">
         <v>16963</v>
@@ -8083,7 +8083,7 @@
         <v>1.82500004768372</v>
       </c>
       <c r="G266" t="n">
-        <v>1.49540758132935</v>
+        <v>1.49540746212006</v>
       </c>
       <c r="H266" t="n">
         <v>6063</v>
@@ -8112,7 +8112,7 @@
         <v>1.84300005435944</v>
       </c>
       <c r="G267" t="n">
-        <v>1.51015663146973</v>
+        <v>1.51015675067902</v>
       </c>
       <c r="H267" t="n">
         <v>9047</v>
@@ -8315,7 +8315,7 @@
         <v>1.95700001716614</v>
       </c>
       <c r="G274" t="n">
-        <v>1.60356843471527</v>
+        <v>1.60356855392456</v>
       </c>
       <c r="H274" t="n">
         <v>6671</v>
@@ -8344,7 +8344,7 @@
         <v>1.96800005435944</v>
       </c>
       <c r="G275" t="n">
-        <v>1.61258172988892</v>
+        <v>1.61258184909821</v>
       </c>
       <c r="H275" t="n">
         <v>19986</v>
@@ -8373,7 +8373,7 @@
         <v>1.97899997234344</v>
       </c>
       <c r="G276" t="n">
-        <v>1.62159538269043</v>
+        <v>1.62159526348114</v>
       </c>
       <c r="H276" t="n">
         <v>7358</v>
@@ -8518,7 +8518,7 @@
         <v>1.93700003623962</v>
       </c>
       <c r="G281" t="n">
-        <v>1.58718049526215</v>
+        <v>1.58718037605286</v>
       </c>
       <c r="H281" t="n">
         <v>5183</v>
@@ -8547,7 +8547,7 @@
         <v>1.88699996471405</v>
       </c>
       <c r="G282" t="n">
-        <v>1.54621040821075</v>
+        <v>1.54621028900146</v>
       </c>
       <c r="H282" t="n">
         <v>3939</v>
@@ -8576,7 +8576,7 @@
         <v>1.90100002288818</v>
       </c>
       <c r="G283" t="n">
-        <v>1.55768191814423</v>
+        <v>1.55768203735352</v>
       </c>
       <c r="H283" t="n">
         <v>371</v>
@@ -8721,7 +8721,7 @@
         <v>1.88699996471405</v>
       </c>
       <c r="G288" t="n">
-        <v>1.54621040821075</v>
+        <v>1.54621028900146</v>
       </c>
       <c r="H288" t="n">
         <v>1302</v>
@@ -8779,7 +8779,7 @@
         <v>1.88800001144409</v>
       </c>
       <c r="G290" t="n">
-        <v>1.54702961444855</v>
+        <v>1.54702973365784</v>
       </c>
       <c r="H290" t="n">
         <v>3926</v>
@@ -8808,7 +8808,7 @@
         <v>1.88800001144409</v>
       </c>
       <c r="G291" t="n">
-        <v>1.54702961444855</v>
+        <v>1.54702973365784</v>
       </c>
       <c r="H291" t="n">
         <v>0</v>
@@ -8837,7 +8837,7 @@
         <v>1.87800002098083</v>
       </c>
       <c r="G292" t="n">
-        <v>1.53883576393127</v>
+        <v>1.53883564472198</v>
       </c>
       <c r="H292" t="n">
         <v>1219</v>
@@ -8866,7 +8866,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G293" t="n">
-        <v>1.56505644321442</v>
+        <v>1.56505656242371</v>
       </c>
       <c r="H293" t="n">
         <v>3832</v>
@@ -9011,7 +9011,7 @@
         <v>1.89499998092651</v>
       </c>
       <c r="G298" t="n">
-        <v>1.55276548862457</v>
+        <v>1.55276560783386</v>
       </c>
       <c r="H298" t="n">
         <v>1397</v>
@@ -9127,7 +9127,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G302" t="n">
-        <v>1.54866850376129</v>
+        <v>1.548668384552</v>
       </c>
       <c r="H302" t="n">
         <v>18974</v>
@@ -9214,7 +9214,7 @@
         <v>1.87899994850159</v>
       </c>
       <c r="G305" t="n">
-        <v>1.53965497016907</v>
+        <v>1.53965508937836</v>
       </c>
       <c r="H305" t="n">
         <v>5851</v>
@@ -9243,7 +9243,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G306" t="n">
-        <v>1.54866850376129</v>
+        <v>1.548668384552</v>
       </c>
       <c r="H306" t="n">
         <v>3292</v>
@@ -9330,7 +9330,7 @@
         <v>2</v>
       </c>
       <c r="G309" t="n">
-        <v>1.63880264759064</v>
+        <v>1.63880276679993</v>
       </c>
       <c r="H309" t="n">
         <v>57906</v>
@@ -9417,7 +9417,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G312" t="n">
-        <v>1.6469966173172</v>
+        <v>1.64699673652649</v>
       </c>
       <c r="H312" t="n">
         <v>18453</v>
@@ -9446,7 +9446,7 @@
         <v>2.06599998474121</v>
       </c>
       <c r="G313" t="n">
-        <v>1.69288325309753</v>
+        <v>1.69288337230682</v>
       </c>
       <c r="H313" t="n">
         <v>12262</v>
@@ -9533,7 +9533,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G316" t="n">
-        <v>1.65519082546234</v>
+        <v>1.65519070625305</v>
       </c>
       <c r="H316" t="n">
         <v>11483</v>
@@ -9620,7 +9620,7 @@
         <v>2.22199988365173</v>
       </c>
       <c r="G319" t="n">
-        <v>1.82070970535278</v>
+        <v>1.82070958614349</v>
       </c>
       <c r="H319" t="n">
         <v>37358</v>
@@ -9649,7 +9649,7 @@
         <v>2.23200011253357</v>
       </c>
       <c r="G320" t="n">
-        <v>1.82890367507935</v>
+        <v>1.82890379428864</v>
       </c>
       <c r="H320" t="n">
         <v>71318</v>
@@ -9765,7 +9765,7 @@
         <v>2.17199993133545</v>
       </c>
       <c r="G324" t="n">
-        <v>1.77973961830139</v>
+        <v>1.77973973751068</v>
       </c>
       <c r="H324" t="n">
         <v>11729</v>
@@ -9794,7 +9794,7 @@
         <v>2.29399991035461</v>
       </c>
       <c r="G325" t="n">
-        <v>1.87970638275146</v>
+        <v>1.87970662117004</v>
       </c>
       <c r="H325" t="n">
         <v>82545</v>
@@ -9852,7 +9852,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G327" t="n">
-        <v>1.79448926448822</v>
+        <v>1.79448914527893</v>
       </c>
       <c r="H327" t="n">
         <v>24197</v>
@@ -9910,7 +9910,7 @@
         <v>2.2260000705719</v>
       </c>
       <c r="G329" t="n">
-        <v>1.82398760318756</v>
+        <v>1.82398748397827</v>
       </c>
       <c r="H329" t="n">
         <v>4573</v>
@@ -10026,7 +10026,7 @@
         <v>2.10800004005432</v>
       </c>
       <c r="G333" t="n">
-        <v>1.72729802131653</v>
+        <v>1.72729790210724</v>
       </c>
       <c r="H333" t="n">
         <v>5276</v>
@@ -10055,7 +10055,7 @@
         <v>2.13199996948242</v>
       </c>
       <c r="G334" t="n">
-        <v>1.74696362018585</v>
+        <v>1.74696350097656</v>
       </c>
       <c r="H334" t="n">
         <v>2476</v>
@@ -10142,7 +10142,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G337" t="n">
-        <v>1.8026829957962</v>
+        <v>1.80268287658691</v>
       </c>
       <c r="H337" t="n">
         <v>8773</v>
@@ -10171,7 +10171,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G338" t="n">
-        <v>1.8026829957962</v>
+        <v>1.80268287658691</v>
       </c>
       <c r="H338" t="n">
         <v>13339</v>
@@ -10200,7 +10200,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G339" t="n">
-        <v>1.83545887470245</v>
+        <v>1.83545899391174</v>
       </c>
       <c r="H339" t="n">
         <v>10440</v>
@@ -10229,7 +10229,7 @@
         <v>2.25399994850159</v>
       </c>
       <c r="G340" t="n">
-        <v>1.84693050384521</v>
+        <v>1.8469306230545</v>
       </c>
       <c r="H340" t="n">
         <v>14315</v>
@@ -10287,7 +10287,7 @@
         <v>2.20799994468689</v>
       </c>
       <c r="G342" t="n">
-        <v>1.80923807621002</v>
+        <v>1.80923795700073</v>
       </c>
       <c r="H342" t="n">
         <v>10083</v>
@@ -10316,7 +10316,7 @@
         <v>2.21199989318848</v>
       </c>
       <c r="G343" t="n">
-        <v>1.81251573562622</v>
+        <v>1.81251561641693</v>
       </c>
       <c r="H343" t="n">
         <v>17654</v>
@@ -10374,7 +10374,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G345" t="n">
-        <v>1.83545887470245</v>
+        <v>1.83545899391174</v>
       </c>
       <c r="H345" t="n">
         <v>20200</v>
@@ -10403,7 +10403,7 @@
         <v>2.27600002288818</v>
       </c>
       <c r="G346" t="n">
-        <v>1.86495745182037</v>
+        <v>1.86495757102966</v>
       </c>
       <c r="H346" t="n">
         <v>12118</v>
@@ -10432,7 +10432,7 @@
         <v>2.26799988746643</v>
       </c>
       <c r="G347" t="n">
-        <v>1.85840201377869</v>
+        <v>1.85840213298798</v>
       </c>
       <c r="H347" t="n">
         <v>10030</v>
@@ -10490,7 +10490,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G349" t="n">
-        <v>1.88462293148041</v>
+        <v>1.88462316989899</v>
       </c>
       <c r="H349" t="n">
         <v>33981</v>
@@ -10519,7 +10519,7 @@
         <v>2.31800007820129</v>
       </c>
       <c r="G350" t="n">
-        <v>1.89937222003937</v>
+        <v>1.89937245845795</v>
       </c>
       <c r="H350" t="n">
         <v>4160</v>
@@ -10548,7 +10548,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G351" t="n">
-        <v>1.91739892959595</v>
+        <v>1.91739904880524</v>
       </c>
       <c r="H351" t="n">
         <v>6240</v>
@@ -10577,7 +10577,7 @@
         <v>2.25600004196167</v>
       </c>
       <c r="G352" t="n">
-        <v>1.84856951236725</v>
+        <v>1.84856963157654</v>
       </c>
       <c r="H352" t="n">
         <v>9093</v>
@@ -10606,7 +10606,7 @@
         <v>2.27600002288818</v>
       </c>
       <c r="G353" t="n">
-        <v>1.86495745182037</v>
+        <v>1.86495757102966</v>
       </c>
       <c r="H353" t="n">
         <v>5451</v>
@@ -10635,7 +10635,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G354" t="n">
-        <v>1.86823511123657</v>
+        <v>1.86823523044586</v>
       </c>
       <c r="H354" t="n">
         <v>9851</v>
@@ -10693,7 +10693,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G356" t="n">
-        <v>1.93679404258728</v>
+        <v>1.93679416179657</v>
       </c>
       <c r="H356" t="n">
         <v>8052</v>
@@ -10751,7 +10751,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G358" t="n">
-        <v>1.97107362747192</v>
+        <v>1.97107374668121</v>
       </c>
       <c r="H358" t="n">
         <v>23455</v>
@@ -10780,7 +10780,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G359" t="n">
-        <v>1.97107362747192</v>
+        <v>1.97107374668121</v>
       </c>
       <c r="H359" t="n">
         <v>18785</v>
@@ -10838,7 +10838,7 @@
         <v>2.26600003242493</v>
       </c>
       <c r="G361" t="n">
-        <v>1.94193613529205</v>
+        <v>1.94193625450134</v>
       </c>
       <c r="H361" t="n">
         <v>10334</v>
@@ -10867,7 +10867,7 @@
         <v>2.26799988746643</v>
       </c>
       <c r="G362" t="n">
-        <v>1.94364988803864</v>
+        <v>1.94365000724792</v>
       </c>
       <c r="H362" t="n">
         <v>9505</v>
@@ -11012,7 +11012,7 @@
         <v>2.24799990653992</v>
       </c>
       <c r="G367" t="n">
-        <v>1.9265102148056</v>
+        <v>1.92651033401489</v>
       </c>
       <c r="H367" t="n">
         <v>1585</v>
@@ -11041,7 +11041,7 @@
         <v>2.24799990653992</v>
       </c>
       <c r="G368" t="n">
-        <v>1.9265102148056</v>
+        <v>1.92651033401489</v>
       </c>
       <c r="H368" t="n">
         <v>0</v>
@@ -11070,7 +11070,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G369" t="n">
-        <v>1.95393395423889</v>
+        <v>1.95393407344818</v>
       </c>
       <c r="H369" t="n">
         <v>20269</v>
@@ -11099,7 +11099,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G370" t="n">
-        <v>1.95393395423889</v>
+        <v>1.95393407344818</v>
       </c>
       <c r="H370" t="n">
         <v>0</v>
@@ -11128,7 +11128,7 @@
         <v>2.25600004196167</v>
       </c>
       <c r="G371" t="n">
-        <v>1.93336629867554</v>
+        <v>1.93336641788483</v>
       </c>
       <c r="H371" t="n">
         <v>4289</v>
@@ -11331,7 +11331,7 @@
         <v>2.23399996757507</v>
       </c>
       <c r="G378" t="n">
-        <v>1.91451239585876</v>
+        <v>1.91451251506805</v>
       </c>
       <c r="H378" t="n">
         <v>12050</v>
@@ -11360,7 +11360,7 @@
         <v>2.20199990272522</v>
       </c>
       <c r="G379" t="n">
-        <v>1.88708889484406</v>
+        <v>1.88708877563477</v>
       </c>
       <c r="H379" t="n">
         <v>17691</v>
@@ -11476,7 +11476,7 @@
         <v>2.18199992179871</v>
       </c>
       <c r="G383" t="n">
-        <v>1.86994922161102</v>
+        <v>1.86994910240173</v>
       </c>
       <c r="H383" t="n">
         <v>1040</v>
@@ -11563,7 +11563,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G386" t="n">
-        <v>1.90251469612122</v>
+        <v>1.90251457691193</v>
       </c>
       <c r="H386" t="n">
         <v>12328</v>
@@ -11679,7 +11679,7 @@
         <v>2.23399996757507</v>
       </c>
       <c r="G390" t="n">
-        <v>1.91451239585876</v>
+        <v>1.91451251506805</v>
       </c>
       <c r="H390" t="n">
         <v>7104</v>
@@ -11737,7 +11737,7 @@
         <v>2.25600004196167</v>
       </c>
       <c r="G392" t="n">
-        <v>1.93336629867554</v>
+        <v>1.93336641788483</v>
       </c>
       <c r="H392" t="n">
         <v>4625</v>
@@ -11795,7 +11795,7 @@
         <v>2.29200005531311</v>
       </c>
       <c r="G394" t="n">
-        <v>1.96421778202057</v>
+        <v>1.96421790122986</v>
       </c>
       <c r="H394" t="n">
         <v>3374</v>
@@ -11853,7 +11853,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G396" t="n">
-        <v>1.97107362747192</v>
+        <v>1.97107374668121</v>
       </c>
       <c r="H396" t="n">
         <v>2881</v>
@@ -11882,7 +11882,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G397" t="n">
-        <v>1.98821341991425</v>
+        <v>1.98821353912354</v>
       </c>
       <c r="H397" t="n">
         <v>4950</v>
@@ -11911,7 +11911,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G398" t="n">
-        <v>1.98821341991425</v>
+        <v>1.98821353912354</v>
       </c>
       <c r="H398" t="n">
         <v>1201</v>
@@ -11940,7 +11940,7 @@
         <v>2.31800007820129</v>
       </c>
       <c r="G399" t="n">
-        <v>1.98649942874908</v>
+        <v>1.98649966716766</v>
       </c>
       <c r="H399" t="n">
         <v>506</v>
@@ -12027,7 +12027,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G402" t="n">
-        <v>2.12533140182495</v>
+        <v>2.12533164024353</v>
       </c>
       <c r="H402" t="n">
         <v>107928</v>
@@ -12056,7 +12056,7 @@
         <v>2.43400001525879</v>
       </c>
       <c r="G403" t="n">
-        <v>2.0859100818634</v>
+        <v>2.08591032028198</v>
       </c>
       <c r="H403" t="n">
         <v>66474</v>
@@ -12085,7 +12085,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G404" t="n">
-        <v>2.05677270889282</v>
+        <v>2.0567729473114</v>
       </c>
       <c r="H404" t="n">
         <v>20365</v>
@@ -12143,7 +12143,7 @@
         <v>2.42799997329712</v>
       </c>
       <c r="G406" t="n">
-        <v>2.08076810836792</v>
+        <v>2.0807683467865</v>
       </c>
       <c r="H406" t="n">
         <v>5713</v>
@@ -12172,7 +12172,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G407" t="n">
-        <v>2.06534242630005</v>
+        <v>2.06534266471863</v>
       </c>
       <c r="H407" t="n">
         <v>8713</v>
@@ -12201,7 +12201,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G408" t="n">
-        <v>2.06534242630005</v>
+        <v>2.06534266471863</v>
       </c>
       <c r="H408" t="n">
         <v>0</v>
@@ -12317,7 +12317,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G412" t="n">
-        <v>2.12533140182495</v>
+        <v>2.12533164024353</v>
       </c>
       <c r="H412" t="n">
         <v>13189</v>
@@ -12375,7 +12375,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G414" t="n">
-        <v>2.1081919670105</v>
+        <v>2.10819172859192</v>
       </c>
       <c r="H414" t="n">
         <v>12585</v>
@@ -12810,7 +12810,7 @@
         <v>2.4760000705719</v>
       </c>
       <c r="G429" t="n">
-        <v>2.12190365791321</v>
+        <v>2.12190389633179</v>
       </c>
       <c r="H429" t="n">
         <v>2150</v>
@@ -12897,7 +12897,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G432" t="n">
-        <v>2.1081919670105</v>
+        <v>2.10819172859192</v>
       </c>
       <c r="H432" t="n">
         <v>150</v>
@@ -13158,7 +13158,7 @@
         <v>2.5</v>
       </c>
       <c r="G441" t="n">
-        <v>2.14247131347656</v>
+        <v>2.14247155189514</v>
       </c>
       <c r="H441" t="n">
         <v>3339</v>
@@ -13622,7 +13622,7 @@
         <v>2.45199990272522</v>
       </c>
       <c r="G457" t="n">
-        <v>2.10133576393127</v>
+        <v>2.10133600234985</v>
       </c>
       <c r="H457" t="n">
         <v>4958</v>
@@ -13854,7 +13854,7 @@
         <v>2.50799989700317</v>
       </c>
       <c r="G465" t="n">
-        <v>2.14932727813721</v>
+        <v>2.14932703971863</v>
       </c>
       <c r="H465" t="n">
         <v>747</v>
@@ -13999,7 +13999,7 @@
         <v>2.4760000705719</v>
       </c>
       <c r="G470" t="n">
-        <v>2.12190365791321</v>
+        <v>2.12190389633179</v>
       </c>
       <c r="H470" t="n">
         <v>8809</v>
@@ -14057,7 +14057,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G472" t="n">
-        <v>2.12533140182495</v>
+        <v>2.12533164024353</v>
       </c>
       <c r="H472" t="n">
         <v>8551</v>
@@ -14289,7 +14289,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G480" t="n">
-        <v>2.05677270889282</v>
+        <v>2.0567729473114</v>
       </c>
       <c r="H480" t="n">
         <v>6507</v>
@@ -14492,7 +14492,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G487" t="n">
-        <v>2.06534242630005</v>
+        <v>2.06534266471863</v>
       </c>
       <c r="H487" t="n">
         <v>3267</v>
@@ -14637,7 +14637,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G492" t="n">
-        <v>2.12533140182495</v>
+        <v>2.12533164024353</v>
       </c>
       <c r="H492" t="n">
         <v>182</v>
@@ -14695,7 +14695,7 @@
         <v>2.48399996757507</v>
       </c>
       <c r="G494" t="n">
-        <v>2.12875962257385</v>
+        <v>2.12875938415527</v>
       </c>
       <c r="H494" t="n">
         <v>150</v>
@@ -14724,7 +14724,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G495" t="n">
-        <v>2.12533140182495</v>
+        <v>2.12533164024353</v>
       </c>
       <c r="H495" t="n">
         <v>1145</v>
@@ -14898,7 +14898,7 @@
         <v>2.43600010871887</v>
       </c>
       <c r="G501" t="n">
-        <v>2.08762431144714</v>
+        <v>2.08762407302856</v>
       </c>
       <c r="H501" t="n">
         <v>2450</v>
@@ -14956,7 +14956,7 @@
         <v>2.35800004005432</v>
       </c>
       <c r="G503" t="n">
-        <v>2.02077913284302</v>
+        <v>2.0207793712616</v>
       </c>
       <c r="H503" t="n">
         <v>2564</v>
@@ -15217,7 +15217,7 @@
         <v>2.4760000705719</v>
       </c>
       <c r="G512" t="n">
-        <v>2.12190365791321</v>
+        <v>2.12190389633179</v>
       </c>
       <c r="H512" t="n">
         <v>1515</v>
@@ -15304,7 +15304,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G515" t="n">
-        <v>2.05677270889282</v>
+        <v>2.0567729473114</v>
       </c>
       <c r="H515" t="n">
         <v>7000</v>
@@ -15594,7 +15594,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G525" t="n">
-        <v>2.05677270889282</v>
+        <v>2.0567729473114</v>
       </c>
       <c r="H525" t="n">
         <v>398</v>
@@ -15623,7 +15623,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G526" t="n">
-        <v>2.05677270889282</v>
+        <v>2.0567729473114</v>
       </c>
       <c r="H526" t="n">
         <v>5700</v>
@@ -15855,7 +15855,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G534" t="n">
-        <v>2.05677270889282</v>
+        <v>2.0567729473114</v>
       </c>
       <c r="H534" t="n">
         <v>361</v>
@@ -15884,7 +15884,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G535" t="n">
-        <v>2.05677270889282</v>
+        <v>2.0567729473114</v>
       </c>
       <c r="H535" t="n">
         <v>1190</v>
@@ -16029,7 +16029,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G540" t="n">
-        <v>2.05677270889282</v>
+        <v>2.0567729473114</v>
       </c>
       <c r="H540" t="n">
         <v>910</v>
@@ -16464,7 +16464,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G555" t="n">
-        <v>2.06534242630005</v>
+        <v>2.06534266471863</v>
       </c>
       <c r="H555" t="n">
         <v>1952</v>
@@ -16551,7 +16551,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G558" t="n">
-        <v>2.1081919670105</v>
+        <v>2.10819172859192</v>
       </c>
       <c r="H558" t="n">
         <v>7260</v>
@@ -16580,7 +16580,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G559" t="n">
-        <v>2.06534242630005</v>
+        <v>2.06534266471863</v>
       </c>
       <c r="H559" t="n">
         <v>459</v>
@@ -16609,7 +16609,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G560" t="n">
-        <v>2.06534242630005</v>
+        <v>2.06534266471863</v>
       </c>
       <c r="H560" t="n">
         <v>2100</v>
@@ -16725,7 +16725,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G564" t="n">
-        <v>2.1081919670105</v>
+        <v>2.10819172859192</v>
       </c>
       <c r="H564" t="n">
         <v>95554</v>
@@ -16754,7 +16754,7 @@
         <v>2.5</v>
       </c>
       <c r="G565" t="n">
-        <v>2.14247131347656</v>
+        <v>2.14247155189514</v>
       </c>
       <c r="H565" t="n">
         <v>21097</v>
@@ -16783,7 +16783,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G566" t="n">
-        <v>2.12533140182495</v>
+        <v>2.12533164024353</v>
       </c>
       <c r="H566" t="n">
         <v>11930</v>
@@ -16812,7 +16812,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G567" t="n">
-        <v>2.1081919670105</v>
+        <v>2.10819172859192</v>
       </c>
       <c r="H567" t="n">
         <v>4589</v>
@@ -16841,7 +16841,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G568" t="n">
-        <v>2.1081919670105</v>
+        <v>2.10819172859192</v>
       </c>
       <c r="H568" t="n">
         <v>0</v>
@@ -16928,7 +16928,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G571" t="n">
-        <v>2.1081919670105</v>
+        <v>2.10819172859192</v>
       </c>
       <c r="H571" t="n">
         <v>9876</v>
@@ -17044,7 +17044,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G575" t="n">
-        <v>2.1081919670105</v>
+        <v>2.10819172859192</v>
       </c>
       <c r="H575" t="n">
         <v>14550</v>
@@ -17131,7 +17131,7 @@
         <v>2.5</v>
       </c>
       <c r="G578" t="n">
-        <v>2.14247131347656</v>
+        <v>2.14247155189514</v>
       </c>
       <c r="H578" t="n">
         <v>2736</v>
@@ -17160,7 +17160,7 @@
         <v>2.5</v>
       </c>
       <c r="G579" t="n">
-        <v>2.14247131347656</v>
+        <v>2.14247155189514</v>
       </c>
       <c r="H579" t="n">
         <v>4410</v>
@@ -17218,7 +17218,7 @@
         <v>2.5</v>
       </c>
       <c r="G581" t="n">
-        <v>2.14247131347656</v>
+        <v>2.14247155189514</v>
       </c>
       <c r="H581" t="n">
         <v>8524</v>
@@ -17247,7 +17247,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G582" t="n">
-        <v>2.1681809425354</v>
+        <v>2.16818118095398</v>
       </c>
       <c r="H582" t="n">
         <v>1455</v>
@@ -17276,7 +17276,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G583" t="n">
-        <v>2.1681809425354</v>
+        <v>2.16818118095398</v>
       </c>
       <c r="H583" t="n">
         <v>2779</v>
@@ -17363,7 +17363,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G586" t="n">
-        <v>2.1681809425354</v>
+        <v>2.16818118095398</v>
       </c>
       <c r="H586" t="n">
         <v>6585</v>
@@ -17421,7 +17421,7 @@
         <v>2.5</v>
       </c>
       <c r="G588" t="n">
-        <v>2.14247131347656</v>
+        <v>2.14247155189514</v>
       </c>
       <c r="H588" t="n">
         <v>216</v>
@@ -17653,7 +17653,7 @@
         <v>2.75</v>
       </c>
       <c r="G596" t="n">
-        <v>2.35671854019165</v>
+        <v>2.35671830177307</v>
       </c>
       <c r="H596" t="n">
         <v>31138</v>
@@ -17682,7 +17682,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G597" t="n">
-        <v>2.44241738319397</v>
+        <v>2.44241714477539</v>
       </c>
       <c r="H597" t="n">
         <v>71018</v>
@@ -17856,7 +17856,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G603" t="n">
-        <v>2.53668594360352</v>
+        <v>2.53668618202209</v>
       </c>
       <c r="H603" t="n">
         <v>32941</v>

--- a/data/RAT.MI.xlsx
+++ b/data/RAT.MI.xlsx
@@ -427,7 +427,7 @@
         <v>2.3659999370575</v>
       </c>
       <c r="G2" t="n">
-        <v>1.85825932025909</v>
+        <v>1.8582592010498</v>
       </c>
       <c r="H2" t="n">
         <v>1350</v>
@@ -456,7 +456,7 @@
         <v>2.43600010871887</v>
       </c>
       <c r="G3" t="n">
-        <v>1.91323745250702</v>
+        <v>1.9132376909256</v>
       </c>
       <c r="H3" t="n">
         <v>3199</v>
@@ -543,7 +543,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G6" t="n">
-        <v>1.88496351242065</v>
+        <v>1.88496315479279</v>
       </c>
       <c r="H6" t="n">
         <v>5635</v>
@@ -572,7 +572,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G7" t="n">
-        <v>1.88496351242065</v>
+        <v>1.88496315479279</v>
       </c>
       <c r="H7" t="n">
         <v>1000</v>
@@ -601,7 +601,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G8" t="n">
-        <v>1.92423295974731</v>
+        <v>1.92423319816589</v>
       </c>
       <c r="H8" t="n">
         <v>4000</v>
@@ -630,7 +630,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G9" t="n">
-        <v>1.88496351242065</v>
+        <v>1.88496315479279</v>
       </c>
       <c r="H9" t="n">
         <v>155</v>
@@ -659,7 +659,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G10" t="n">
-        <v>1.88496351242065</v>
+        <v>1.88496315479279</v>
       </c>
       <c r="H10" t="n">
         <v>559</v>
@@ -688,7 +688,7 @@
         <v>2.3659999370575</v>
       </c>
       <c r="G11" t="n">
-        <v>1.85825932025909</v>
+        <v>1.8582592010498</v>
       </c>
       <c r="H11" t="n">
         <v>1414</v>
@@ -717,7 +717,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G12" t="n">
-        <v>1.80642306804657</v>
+        <v>1.80642294883728</v>
       </c>
       <c r="H12" t="n">
         <v>270</v>
@@ -746,7 +746,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G13" t="n">
-        <v>1.80642306804657</v>
+        <v>1.80642294883728</v>
       </c>
       <c r="H13" t="n">
         <v>1200</v>
@@ -833,7 +833,7 @@
         <v>2.25</v>
       </c>
       <c r="G16" t="n">
-        <v>1.76715290546417</v>
+        <v>1.76715314388275</v>
       </c>
       <c r="H16" t="n">
         <v>2070</v>
@@ -862,7 +862,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G17" t="n">
-        <v>1.85354673862457</v>
+        <v>1.85354697704315</v>
       </c>
       <c r="H17" t="n">
         <v>4705</v>
@@ -891,7 +891,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G18" t="n">
-        <v>1.85354673862457</v>
+        <v>1.85354697704315</v>
       </c>
       <c r="H18" t="n">
         <v>2000</v>
@@ -920,7 +920,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G19" t="n">
-        <v>1.86925506591797</v>
+        <v>1.86925530433655</v>
       </c>
       <c r="H19" t="n">
         <v>3200</v>
@@ -1007,7 +1007,7 @@
         <v>2.37800002098083</v>
       </c>
       <c r="G22" t="n">
-        <v>1.86768424510956</v>
+        <v>1.86768448352814</v>
       </c>
       <c r="H22" t="n">
         <v>2858</v>
@@ -1036,7 +1036,7 @@
         <v>2.31200003623962</v>
       </c>
       <c r="G23" t="n">
-        <v>1.81584775447845</v>
+        <v>1.81584787368774</v>
       </c>
       <c r="H23" t="n">
         <v>750</v>
@@ -1065,7 +1065,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G24" t="n">
-        <v>1.83783900737762</v>
+        <v>1.83783864974976</v>
       </c>
       <c r="H24" t="n">
         <v>1435</v>
@@ -1094,7 +1094,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G25" t="n">
-        <v>1.83783900737762</v>
+        <v>1.83783864974976</v>
       </c>
       <c r="H25" t="n">
         <v>475</v>
@@ -1123,7 +1123,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G26" t="n">
-        <v>1.88496351242065</v>
+        <v>1.88496315479279</v>
       </c>
       <c r="H26" t="n">
         <v>330</v>
@@ -1152,7 +1152,7 @@
         <v>2.38800001144409</v>
       </c>
       <c r="G27" t="n">
-        <v>1.87553822994232</v>
+        <v>1.87553834915161</v>
       </c>
       <c r="H27" t="n">
         <v>2173</v>
@@ -1181,7 +1181,7 @@
         <v>2.38800001144409</v>
       </c>
       <c r="G28" t="n">
-        <v>1.87553822994232</v>
+        <v>1.87553834915161</v>
       </c>
       <c r="H28" t="n">
         <v>0</v>
@@ -1210,7 +1210,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G29" t="n">
-        <v>1.88496351242065</v>
+        <v>1.88496315479279</v>
       </c>
       <c r="H29" t="n">
         <v>1810</v>
@@ -1239,7 +1239,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G30" t="n">
-        <v>1.80642306804657</v>
+        <v>1.80642294883728</v>
       </c>
       <c r="H30" t="n">
         <v>10919</v>
@@ -1268,7 +1268,7 @@
         <v>2.32599997520447</v>
       </c>
       <c r="G31" t="n">
-        <v>1.82684350013733</v>
+        <v>1.82684338092804</v>
       </c>
       <c r="H31" t="n">
         <v>9925</v>
@@ -1297,7 +1297,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G32" t="n">
-        <v>1.84569311141968</v>
+        <v>1.84569299221039</v>
       </c>
       <c r="H32" t="n">
         <v>250</v>
@@ -1326,7 +1326,7 @@
         <v>2.31599998474121</v>
       </c>
       <c r="G33" t="n">
-        <v>1.81898939609528</v>
+        <v>1.8189891576767</v>
       </c>
       <c r="H33" t="n">
         <v>1023</v>
@@ -1355,7 +1355,7 @@
         <v>2.33800005912781</v>
       </c>
       <c r="G34" t="n">
-        <v>1.8362683057785</v>
+        <v>1.83626818656921</v>
       </c>
       <c r="H34" t="n">
         <v>9221</v>
@@ -1529,7 +1529,7 @@
         <v>2.31399989128113</v>
       </c>
       <c r="G40" t="n">
-        <v>1.81741845607758</v>
+        <v>1.81741833686829</v>
       </c>
       <c r="H40" t="n">
         <v>150</v>
@@ -1558,7 +1558,7 @@
         <v>2.31399989128113</v>
       </c>
       <c r="G41" t="n">
-        <v>1.81741845607758</v>
+        <v>1.81741833686829</v>
       </c>
       <c r="H41" t="n">
         <v>0</v>
@@ -1587,7 +1587,7 @@
         <v>2.31399989128113</v>
       </c>
       <c r="G42" t="n">
-        <v>1.81741845607758</v>
+        <v>1.81741833686829</v>
       </c>
       <c r="H42" t="n">
         <v>0</v>
@@ -1616,7 +1616,7 @@
         <v>2.33800005912781</v>
       </c>
       <c r="G43" t="n">
-        <v>1.8362683057785</v>
+        <v>1.83626818656921</v>
       </c>
       <c r="H43" t="n">
         <v>950</v>
@@ -1674,7 +1674,7 @@
         <v>2.37800002098083</v>
       </c>
       <c r="G45" t="n">
-        <v>1.86768424510956</v>
+        <v>1.86768448352814</v>
       </c>
       <c r="H45" t="n">
         <v>2230</v>
@@ -1703,7 +1703,7 @@
         <v>2.35599994659424</v>
       </c>
       <c r="G46" t="n">
-        <v>1.85040533542633</v>
+        <v>1.85040545463562</v>
       </c>
       <c r="H46" t="n">
         <v>253</v>
@@ -1732,7 +1732,7 @@
         <v>2.39400005340576</v>
       </c>
       <c r="G47" t="n">
-        <v>1.88025081157684</v>
+        <v>1.88025057315826</v>
       </c>
       <c r="H47" t="n">
         <v>110</v>
@@ -1761,7 +1761,7 @@
         <v>2.39400005340576</v>
       </c>
       <c r="G48" t="n">
-        <v>1.88025081157684</v>
+        <v>1.88025057315826</v>
       </c>
       <c r="H48" t="n">
         <v>0</v>
@@ -1790,7 +1790,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G49" t="n">
-        <v>1.81427693367004</v>
+        <v>1.81427681446075</v>
       </c>
       <c r="H49" t="n">
         <v>1530</v>
@@ -1819,7 +1819,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G50" t="n">
-        <v>1.84569311141968</v>
+        <v>1.84569299221039</v>
       </c>
       <c r="H50" t="n">
         <v>396</v>
@@ -1848,7 +1848,7 @@
         <v>2.33800005912781</v>
       </c>
       <c r="G51" t="n">
-        <v>1.8362683057785</v>
+        <v>1.83626818656921</v>
       </c>
       <c r="H51" t="n">
         <v>1660</v>
@@ -1877,7 +1877,7 @@
         <v>2.35800004005432</v>
       </c>
       <c r="G52" t="n">
-        <v>1.85197651386261</v>
+        <v>1.85197639465332</v>
       </c>
       <c r="H52" t="n">
         <v>3419</v>
@@ -1906,7 +1906,7 @@
         <v>2.34800004959106</v>
       </c>
       <c r="G53" t="n">
-        <v>1.84412217140198</v>
+        <v>1.84412240982056</v>
       </c>
       <c r="H53" t="n">
         <v>3348</v>
@@ -1935,7 +1935,7 @@
         <v>2.34400010108948</v>
       </c>
       <c r="G54" t="n">
-        <v>1.84098052978516</v>
+        <v>1.84098064899445</v>
       </c>
       <c r="H54" t="n">
         <v>600</v>
@@ -1964,7 +1964,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G55" t="n">
-        <v>1.84569311141968</v>
+        <v>1.84569299221039</v>
       </c>
       <c r="H55" t="n">
         <v>386</v>
@@ -1993,7 +1993,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G56" t="n">
-        <v>1.84569311141968</v>
+        <v>1.84569299221039</v>
       </c>
       <c r="H56" t="n">
         <v>5025</v>
@@ -2022,7 +2022,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G57" t="n">
-        <v>1.85354673862457</v>
+        <v>1.85354697704315</v>
       </c>
       <c r="H57" t="n">
         <v>50</v>
@@ -2051,7 +2051,7 @@
         <v>2.32200002670288</v>
       </c>
       <c r="G58" t="n">
-        <v>1.82370185852051</v>
+        <v>1.82370173931122</v>
       </c>
       <c r="H58" t="n">
         <v>1606</v>
@@ -2080,7 +2080,7 @@
         <v>2.32200002670288</v>
       </c>
       <c r="G59" t="n">
-        <v>1.82370185852051</v>
+        <v>1.82370173931122</v>
       </c>
       <c r="H59" t="n">
         <v>0</v>
@@ -2109,7 +2109,7 @@
         <v>2.30599999427795</v>
       </c>
       <c r="G60" t="n">
-        <v>1.81113541126251</v>
+        <v>1.8111355304718</v>
       </c>
       <c r="H60" t="n">
         <v>6820</v>
@@ -2138,7 +2138,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G61" t="n">
-        <v>1.81427693367004</v>
+        <v>1.81427681446075</v>
       </c>
       <c r="H61" t="n">
         <v>150</v>
@@ -2196,7 +2196,7 @@
         <v>2.35599994659424</v>
       </c>
       <c r="G63" t="n">
-        <v>1.85040533542633</v>
+        <v>1.85040545463562</v>
       </c>
       <c r="H63" t="n">
         <v>100</v>
@@ -2225,7 +2225,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G64" t="n">
-        <v>1.84569311141968</v>
+        <v>1.84569299221039</v>
       </c>
       <c r="H64" t="n">
         <v>1054</v>
@@ -2254,7 +2254,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G65" t="n">
-        <v>1.92423295974731</v>
+        <v>1.92423319816589</v>
       </c>
       <c r="H65" t="n">
         <v>19358</v>
@@ -2283,7 +2283,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G66" t="n">
-        <v>1.92423295974731</v>
+        <v>1.92423319816589</v>
       </c>
       <c r="H66" t="n">
         <v>0</v>
@@ -2312,7 +2312,7 @@
         <v>2.46600008010864</v>
       </c>
       <c r="G67" t="n">
-        <v>1.93679976463318</v>
+        <v>1.9367995262146</v>
       </c>
       <c r="H67" t="n">
         <v>1695</v>
@@ -2341,7 +2341,7 @@
         <v>2.4779999256134</v>
       </c>
       <c r="G68" t="n">
-        <v>1.94622445106506</v>
+        <v>1.94622421264648</v>
       </c>
       <c r="H68" t="n">
         <v>120</v>
@@ -2399,7 +2399,7 @@
         <v>2.5</v>
       </c>
       <c r="G70" t="n">
-        <v>1.96350347995758</v>
+        <v>1.96350300312042</v>
       </c>
       <c r="H70" t="n">
         <v>23697</v>
@@ -2515,7 +2515,7 @@
         <v>2.5</v>
       </c>
       <c r="G74" t="n">
-        <v>1.96350347995758</v>
+        <v>1.96350300312042</v>
       </c>
       <c r="H74" t="n">
         <v>1853</v>
@@ -2544,7 +2544,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G75" t="n">
-        <v>1.98706531524658</v>
+        <v>1.987065076828</v>
       </c>
       <c r="H75" t="n">
         <v>41607</v>
@@ -2631,7 +2631,7 @@
         <v>2.57800006866455</v>
       </c>
       <c r="G78" t="n">
-        <v>2.02476453781128</v>
+        <v>2.02476477622986</v>
       </c>
       <c r="H78" t="n">
         <v>1952</v>
@@ -2718,7 +2718,7 @@
         <v>2.5</v>
       </c>
       <c r="G81" t="n">
-        <v>1.96350347995758</v>
+        <v>1.96350300312042</v>
       </c>
       <c r="H81" t="n">
         <v>50</v>
@@ -2747,7 +2747,7 @@
         <v>2.49799990653992</v>
       </c>
       <c r="G82" t="n">
-        <v>1.9619323015213</v>
+        <v>1.96193253993988</v>
       </c>
       <c r="H82" t="n">
         <v>2294</v>
@@ -2834,7 +2834,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G85" t="n">
-        <v>1.95564925670624</v>
+        <v>1.95564901828766</v>
       </c>
       <c r="H85" t="n">
         <v>2700</v>
@@ -2863,7 +2863,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G86" t="n">
-        <v>1.95564925670624</v>
+        <v>1.95564901828766</v>
       </c>
       <c r="H86" t="n">
         <v>0</v>
@@ -2921,7 +2921,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G88" t="n">
-        <v>1.91637921333313</v>
+        <v>1.91637945175171</v>
       </c>
       <c r="H88" t="n">
         <v>1187</v>
@@ -2950,7 +2950,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G89" t="n">
-        <v>1.88496351242065</v>
+        <v>1.88496315479279</v>
       </c>
       <c r="H89" t="n">
         <v>4181</v>
@@ -2979,7 +2979,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G90" t="n">
-        <v>1.91637921333313</v>
+        <v>1.91637945175171</v>
       </c>
       <c r="H90" t="n">
         <v>65</v>
@@ -3008,7 +3008,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G91" t="n">
-        <v>1.91637921333313</v>
+        <v>1.91637945175171</v>
       </c>
       <c r="H91" t="n">
         <v>0</v>
@@ -3037,7 +3037,7 @@
         <v>2.39400005340576</v>
       </c>
       <c r="G92" t="n">
-        <v>1.88025081157684</v>
+        <v>1.88025057315826</v>
       </c>
       <c r="H92" t="n">
         <v>260</v>
@@ -3095,7 +3095,7 @@
         <v>2.38599991798401</v>
       </c>
       <c r="G94" t="n">
-        <v>1.8739675283432</v>
+        <v>1.87396740913391</v>
       </c>
       <c r="H94" t="n">
         <v>11190</v>
@@ -3124,7 +3124,7 @@
         <v>2.38599991798401</v>
       </c>
       <c r="G95" t="n">
-        <v>1.8739675283432</v>
+        <v>1.87396740913391</v>
       </c>
       <c r="H95" t="n">
         <v>0</v>
@@ -3211,7 +3211,7 @@
         <v>2.34800004959106</v>
       </c>
       <c r="G98" t="n">
-        <v>1.84412217140198</v>
+        <v>1.84412240982056</v>
       </c>
       <c r="H98" t="n">
         <v>8904</v>
@@ -3269,7 +3269,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G100" t="n">
-        <v>1.93378674983978</v>
+        <v>1.93378698825836</v>
       </c>
       <c r="H100" t="n">
         <v>1125</v>
@@ -3298,7 +3298,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G101" t="n">
-        <v>1.95017516613007</v>
+        <v>1.95017540454865</v>
       </c>
       <c r="H101" t="n">
         <v>176</v>
@@ -3327,7 +3327,7 @@
         <v>2.34599995613098</v>
       </c>
       <c r="G102" t="n">
-        <v>1.92231559753418</v>
+        <v>1.9223153591156</v>
       </c>
       <c r="H102" t="n">
         <v>195</v>
@@ -3356,7 +3356,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G103" t="n">
-        <v>1.93378674983978</v>
+        <v>1.93378698825836</v>
       </c>
       <c r="H103" t="n">
         <v>3800</v>
@@ -3385,7 +3385,7 @@
         <v>2.35599994659424</v>
       </c>
       <c r="G104" t="n">
-        <v>1.93050944805145</v>
+        <v>1.93050968647003</v>
       </c>
       <c r="H104" t="n">
         <v>3779</v>
@@ -3414,7 +3414,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G105" t="n">
-        <v>1.96656358242035</v>
+        <v>1.96656310558319</v>
       </c>
       <c r="H105" t="n">
         <v>160</v>
@@ -3443,7 +3443,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G106" t="n">
-        <v>1.96656358242035</v>
+        <v>1.96656310558319</v>
       </c>
       <c r="H106" t="n">
         <v>0</v>
@@ -3559,7 +3559,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G110" t="n">
-        <v>1.95017516613007</v>
+        <v>1.95017540454865</v>
       </c>
       <c r="H110" t="n">
         <v>403</v>
@@ -3588,7 +3588,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G111" t="n">
-        <v>1.95017516613007</v>
+        <v>1.95017540454865</v>
       </c>
       <c r="H111" t="n">
         <v>0</v>
@@ -3820,7 +3820,7 @@
         <v>2.33400011062622</v>
       </c>
       <c r="G119" t="n">
-        <v>1.91248309612274</v>
+        <v>1.91248285770416</v>
       </c>
       <c r="H119" t="n">
         <v>2002</v>
@@ -3849,7 +3849,7 @@
         <v>2.33200001716614</v>
       </c>
       <c r="G120" t="n">
-        <v>1.91084396839142</v>
+        <v>1.91084420681</v>
       </c>
       <c r="H120" t="n">
         <v>1532</v>
@@ -3878,7 +3878,7 @@
         <v>2.33200001716614</v>
       </c>
       <c r="G121" t="n">
-        <v>1.91084396839142</v>
+        <v>1.91084420681</v>
       </c>
       <c r="H121" t="n">
         <v>0</v>
@@ -3907,7 +3907,7 @@
         <v>2.33400011062622</v>
       </c>
       <c r="G122" t="n">
-        <v>1.91248309612274</v>
+        <v>1.91248285770416</v>
       </c>
       <c r="H122" t="n">
         <v>1260</v>
@@ -3936,7 +3936,7 @@
         <v>2.33400011062622</v>
       </c>
       <c r="G123" t="n">
-        <v>1.91248309612274</v>
+        <v>1.91248285770416</v>
       </c>
       <c r="H123" t="n">
         <v>0</v>
@@ -3965,7 +3965,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G124" t="n">
-        <v>1.83545899391174</v>
+        <v>1.83545923233032</v>
       </c>
       <c r="H124" t="n">
         <v>348</v>
@@ -4023,7 +4023,7 @@
         <v>2.24799990653992</v>
       </c>
       <c r="G126" t="n">
-        <v>1.84201419353485</v>
+        <v>1.84201407432556</v>
       </c>
       <c r="H126" t="n">
         <v>1490</v>
@@ -4081,7 +4081,7 @@
         <v>2.24799990653992</v>
       </c>
       <c r="G128" t="n">
-        <v>1.84201419353485</v>
+        <v>1.84201407432556</v>
       </c>
       <c r="H128" t="n">
         <v>370</v>
@@ -4110,7 +4110,7 @@
         <v>2.29800009727478</v>
       </c>
       <c r="G129" t="n">
-        <v>1.88298416137695</v>
+        <v>1.88298428058624</v>
       </c>
       <c r="H129" t="n">
         <v>100</v>
@@ -4139,7 +4139,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G130" t="n">
-        <v>1.86823523044586</v>
+        <v>1.86823511123657</v>
       </c>
       <c r="H130" t="n">
         <v>2288</v>
@@ -4226,7 +4226,7 @@
         <v>2.32800006866455</v>
       </c>
       <c r="G133" t="n">
-        <v>1.90756630897522</v>
+        <v>1.90756618976593</v>
       </c>
       <c r="H133" t="n">
         <v>510</v>
@@ -4255,7 +4255,7 @@
         <v>2.32800006866455</v>
       </c>
       <c r="G134" t="n">
-        <v>1.90756630897522</v>
+        <v>1.90756618976593</v>
       </c>
       <c r="H134" t="n">
         <v>0</v>
@@ -4284,7 +4284,7 @@
         <v>2.32800006866455</v>
       </c>
       <c r="G135" t="n">
-        <v>1.90756630897522</v>
+        <v>1.90756618976593</v>
       </c>
       <c r="H135" t="n">
         <v>0</v>
@@ -4313,7 +4313,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G136" t="n">
-        <v>1.89281702041626</v>
+        <v>1.89281713962555</v>
       </c>
       <c r="H136" t="n">
         <v>6553</v>
@@ -4342,7 +4342,7 @@
         <v>2.32599997520447</v>
       </c>
       <c r="G137" t="n">
-        <v>1.90592765808105</v>
+        <v>1.90592753887177</v>
       </c>
       <c r="H137" t="n">
         <v>600</v>
@@ -4371,7 +4371,7 @@
         <v>2.32599997520447</v>
       </c>
       <c r="G138" t="n">
-        <v>1.90592765808105</v>
+        <v>1.90592753887177</v>
       </c>
       <c r="H138" t="n">
         <v>815</v>
@@ -4429,7 +4429,7 @@
         <v>2.32599997520447</v>
       </c>
       <c r="G140" t="n">
-        <v>1.90592765808105</v>
+        <v>1.90592753887177</v>
       </c>
       <c r="H140" t="n">
         <v>50</v>
@@ -4458,7 +4458,7 @@
         <v>2.32599997520447</v>
       </c>
       <c r="G141" t="n">
-        <v>1.90592765808105</v>
+        <v>1.90592753887177</v>
       </c>
       <c r="H141" t="n">
         <v>0</v>
@@ -4487,7 +4487,7 @@
         <v>2.32800006866455</v>
       </c>
       <c r="G142" t="n">
-        <v>1.90756630897522</v>
+        <v>1.90756618976593</v>
       </c>
       <c r="H142" t="n">
         <v>80</v>
@@ -4574,7 +4574,7 @@
         <v>2.28399991989136</v>
       </c>
       <c r="G145" t="n">
-        <v>1.87151253223419</v>
+        <v>1.87151265144348</v>
       </c>
       <c r="H145" t="n">
         <v>10583</v>
@@ -4632,7 +4632,7 @@
         <v>2.32599997520447</v>
       </c>
       <c r="G147" t="n">
-        <v>1.90592765808105</v>
+        <v>1.90592753887177</v>
       </c>
       <c r="H147" t="n">
         <v>1070</v>
@@ -4777,7 +4777,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G152" t="n">
-        <v>1.78629505634308</v>
+        <v>1.7862948179245</v>
       </c>
       <c r="H152" t="n">
         <v>7134</v>
@@ -4806,7 +4806,7 @@
         <v>2.16799998283386</v>
       </c>
       <c r="G153" t="n">
-        <v>1.77646207809448</v>
+        <v>1.77646195888519</v>
       </c>
       <c r="H153" t="n">
         <v>1600</v>
@@ -4951,7 +4951,7 @@
         <v>2.13599991798401</v>
       </c>
       <c r="G158" t="n">
-        <v>1.75024127960205</v>
+        <v>1.75024139881134</v>
       </c>
       <c r="H158" t="n">
         <v>4584</v>
@@ -5125,7 +5125,7 @@
         <v>2.14800000190735</v>
       </c>
       <c r="G164" t="n">
-        <v>1.76007413864136</v>
+        <v>1.76007401943207</v>
       </c>
       <c r="H164" t="n">
         <v>2324</v>
@@ -5154,7 +5154,7 @@
         <v>2.14800000190735</v>
       </c>
       <c r="G165" t="n">
-        <v>1.76007413864136</v>
+        <v>1.76007401943207</v>
       </c>
       <c r="H165" t="n">
         <v>0</v>
@@ -5183,7 +5183,7 @@
         <v>2.14800000190735</v>
       </c>
       <c r="G166" t="n">
-        <v>1.76007413864136</v>
+        <v>1.76007401943207</v>
       </c>
       <c r="H166" t="n">
         <v>0</v>
@@ -5212,7 +5212,7 @@
         <v>2.14800000190735</v>
       </c>
       <c r="G167" t="n">
-        <v>1.76007413864136</v>
+        <v>1.76007401943207</v>
       </c>
       <c r="H167" t="n">
         <v>0</v>
@@ -5241,7 +5241,7 @@
         <v>2.14800000190735</v>
       </c>
       <c r="G168" t="n">
-        <v>1.76007413864136</v>
+        <v>1.76007401943207</v>
       </c>
       <c r="H168" t="n">
         <v>0</v>
@@ -5270,7 +5270,7 @@
         <v>2.14800000190735</v>
       </c>
       <c r="G169" t="n">
-        <v>1.76007413864136</v>
+        <v>1.76007401943207</v>
       </c>
       <c r="H169" t="n">
         <v>206</v>
@@ -5444,7 +5444,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G175" t="n">
-        <v>1.63060867786407</v>
+        <v>1.63060879707336</v>
       </c>
       <c r="H175" t="n">
         <v>32041</v>
@@ -5502,7 +5502,7 @@
         <v>2.03399991989136</v>
       </c>
       <c r="G177" t="n">
-        <v>1.66666221618652</v>
+        <v>1.66666233539581</v>
       </c>
       <c r="H177" t="n">
         <v>7268</v>
@@ -5618,7 +5618,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G181" t="n">
-        <v>1.66338467597961</v>
+        <v>1.6633847951889</v>
       </c>
       <c r="H181" t="n">
         <v>8509</v>
@@ -5908,7 +5908,7 @@
         <v>1.98399996757507</v>
       </c>
       <c r="G191" t="n">
-        <v>1.62569212913513</v>
+        <v>1.62569224834442</v>
       </c>
       <c r="H191" t="n">
         <v>9477</v>
@@ -5937,7 +5937,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G192" t="n">
-        <v>1.66338467597961</v>
+        <v>1.6633847951889</v>
       </c>
       <c r="H192" t="n">
         <v>5125</v>
@@ -5966,7 +5966,7 @@
         <v>2.03399991989136</v>
       </c>
       <c r="G193" t="n">
-        <v>1.66666221618652</v>
+        <v>1.66666233539581</v>
       </c>
       <c r="H193" t="n">
         <v>2852</v>
@@ -6227,7 +6227,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G202" t="n">
-        <v>1.64699673652649</v>
+        <v>1.6469966173172</v>
       </c>
       <c r="H202" t="n">
         <v>487</v>
@@ -6256,7 +6256,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G203" t="n">
-        <v>1.64699673652649</v>
+        <v>1.6469966173172</v>
       </c>
       <c r="H203" t="n">
         <v>4278</v>
@@ -6285,7 +6285,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G204" t="n">
-        <v>1.64699673652649</v>
+        <v>1.6469966173172</v>
       </c>
       <c r="H204" t="n">
         <v>180</v>
@@ -6314,7 +6314,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G205" t="n">
-        <v>1.64699673652649</v>
+        <v>1.6469966173172</v>
       </c>
       <c r="H205" t="n">
         <v>0</v>
@@ -6343,7 +6343,7 @@
         <v>1.99899995326996</v>
       </c>
       <c r="G206" t="n">
-        <v>1.63798308372498</v>
+        <v>1.63798320293427</v>
       </c>
       <c r="H206" t="n">
         <v>2595</v>
@@ -6372,7 +6372,7 @@
         <v>1.95099997520447</v>
       </c>
       <c r="G207" t="n">
-        <v>1.59865200519562</v>
+        <v>1.59865212440491</v>
       </c>
       <c r="H207" t="n">
         <v>3446</v>
@@ -6604,7 +6604,7 @@
         <v>1.91299998760223</v>
       </c>
       <c r="G215" t="n">
-        <v>1.56751477718353</v>
+        <v>1.56751465797424</v>
       </c>
       <c r="H215" t="n">
         <v>8016</v>
@@ -6662,7 +6662,7 @@
         <v>1.91199994087219</v>
       </c>
       <c r="G217" t="n">
-        <v>1.56669533252716</v>
+        <v>1.56669521331787</v>
       </c>
       <c r="H217" t="n">
         <v>1680</v>
@@ -6691,7 +6691,7 @@
         <v>1.90199995040894</v>
       </c>
       <c r="G218" t="n">
-        <v>1.55850124359131</v>
+        <v>1.5585013628006</v>
       </c>
       <c r="H218" t="n">
         <v>2601</v>
@@ -6749,7 +6749,7 @@
         <v>1.95700001716614</v>
       </c>
       <c r="G220" t="n">
-        <v>1.60356855392456</v>
+        <v>1.60356843471527</v>
       </c>
       <c r="H220" t="n">
         <v>5560</v>
@@ -6894,7 +6894,7 @@
         <v>1.85399997234344</v>
       </c>
       <c r="G225" t="n">
-        <v>1.51917004585266</v>
+        <v>1.51916992664337</v>
       </c>
       <c r="H225" t="n">
         <v>20310</v>
@@ -6981,7 +6981,7 @@
         <v>1.67999994754791</v>
       </c>
       <c r="G228" t="n">
-        <v>1.37659418582916</v>
+        <v>1.37659406661987</v>
       </c>
       <c r="H228" t="n">
         <v>40640</v>
@@ -7039,7 +7039,7 @@
         <v>1.70200002193451</v>
       </c>
       <c r="G230" t="n">
-        <v>1.39462101459503</v>
+        <v>1.39462113380432</v>
       </c>
       <c r="H230" t="n">
         <v>23064</v>
@@ -7068,7 +7068,7 @@
         <v>1.77900004386902</v>
       </c>
       <c r="G231" t="n">
-        <v>1.45771503448486</v>
+        <v>1.45771491527557</v>
       </c>
       <c r="H231" t="n">
         <v>4259</v>
@@ -7184,7 +7184,7 @@
         <v>1.96700000762939</v>
       </c>
       <c r="G235" t="n">
-        <v>1.61176252365112</v>
+        <v>1.61176240444183</v>
       </c>
       <c r="H235" t="n">
         <v>99</v>
@@ -7213,7 +7213,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G236" t="n">
-        <v>1.59783267974854</v>
+        <v>1.59783256053925</v>
       </c>
       <c r="H236" t="n">
         <v>3027</v>
@@ -7242,7 +7242,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G237" t="n">
-        <v>1.59783267974854</v>
+        <v>1.59783256053925</v>
       </c>
       <c r="H237" t="n">
         <v>0</v>
@@ -7271,7 +7271,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G238" t="n">
-        <v>1.59783267974854</v>
+        <v>1.59783256053925</v>
       </c>
       <c r="H238" t="n">
         <v>0</v>
@@ -7300,7 +7300,7 @@
         <v>1.96700000762939</v>
       </c>
       <c r="G239" t="n">
-        <v>1.61176252365112</v>
+        <v>1.61176240444183</v>
       </c>
       <c r="H239" t="n">
         <v>50</v>
@@ -7329,7 +7329,7 @@
         <v>1.88199996948242</v>
       </c>
       <c r="G240" t="n">
-        <v>1.54211330413818</v>
+        <v>1.54211318492889</v>
       </c>
       <c r="H240" t="n">
         <v>14504</v>
@@ -7387,7 +7387,7 @@
         <v>1.89800000190735</v>
       </c>
       <c r="G242" t="n">
-        <v>1.55522382259369</v>
+        <v>1.5552237033844</v>
       </c>
       <c r="H242" t="n">
         <v>6374</v>
@@ -7416,7 +7416,7 @@
         <v>1.89800000190735</v>
       </c>
       <c r="G243" t="n">
-        <v>1.55522382259369</v>
+        <v>1.5552237033844</v>
       </c>
       <c r="H243" t="n">
         <v>3380</v>
@@ -7474,7 +7474,7 @@
         <v>1.90900003910065</v>
       </c>
       <c r="G245" t="n">
-        <v>1.56423723697662</v>
+        <v>1.56423711776733</v>
       </c>
       <c r="H245" t="n">
         <v>250</v>
@@ -7532,7 +7532,7 @@
         <v>1.94400000572205</v>
       </c>
       <c r="G247" t="n">
-        <v>1.59291625022888</v>
+        <v>1.59291613101959</v>
       </c>
       <c r="H247" t="n">
         <v>10</v>
@@ -7561,7 +7561,7 @@
         <v>1.94400000572205</v>
       </c>
       <c r="G248" t="n">
-        <v>1.59291625022888</v>
+        <v>1.59291613101959</v>
       </c>
       <c r="H248" t="n">
         <v>5280</v>
@@ -7648,7 +7648,7 @@
         <v>1.88100004196167</v>
       </c>
       <c r="G251" t="n">
-        <v>1.54129385948181</v>
+        <v>1.5412939786911</v>
       </c>
       <c r="H251" t="n">
         <v>33196</v>
@@ -7677,7 +7677,7 @@
         <v>1.83599996566772</v>
       </c>
       <c r="G252" t="n">
-        <v>1.50442087650299</v>
+        <v>1.5044207572937</v>
       </c>
       <c r="H252" t="n">
         <v>920</v>
@@ -7764,7 +7764,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G255" t="n">
-        <v>1.51589262485504</v>
+        <v>1.51589250564575</v>
       </c>
       <c r="H255" t="n">
         <v>3734</v>
@@ -7967,7 +7967,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G262" t="n">
-        <v>1.5076984167099</v>
+        <v>1.50769853591919</v>
       </c>
       <c r="H262" t="n">
         <v>110</v>
@@ -8025,7 +8025,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G264" t="n">
-        <v>1.5076984167099</v>
+        <v>1.50769853591919</v>
       </c>
       <c r="H264" t="n">
         <v>10670</v>
@@ -8170,7 +8170,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G269" t="n">
-        <v>1.57325053215027</v>
+        <v>1.57325041294098</v>
       </c>
       <c r="H269" t="n">
         <v>3905</v>
@@ -8199,7 +8199,7 @@
         <v>1.93499994277954</v>
       </c>
       <c r="G270" t="n">
-        <v>1.58554148674011</v>
+        <v>1.5855416059494</v>
       </c>
       <c r="H270" t="n">
         <v>11884</v>
@@ -8286,7 +8286,7 @@
         <v>1.96099996566772</v>
       </c>
       <c r="G273" t="n">
-        <v>1.60684597492218</v>
+        <v>1.60684585571289</v>
       </c>
       <c r="H273" t="n">
         <v>4589</v>
@@ -8315,7 +8315,7 @@
         <v>1.95700001716614</v>
       </c>
       <c r="G274" t="n">
-        <v>1.60356855392456</v>
+        <v>1.60356843471527</v>
       </c>
       <c r="H274" t="n">
         <v>6671</v>
@@ -8373,7 +8373,7 @@
         <v>1.97899997234344</v>
       </c>
       <c r="G276" t="n">
-        <v>1.62159526348114</v>
+        <v>1.62159538269043</v>
       </c>
       <c r="H276" t="n">
         <v>7358</v>
@@ -8431,7 +8431,7 @@
         <v>1.88399994373322</v>
       </c>
       <c r="G278" t="n">
-        <v>1.54375195503235</v>
+        <v>1.54375207424164</v>
       </c>
       <c r="H278" t="n">
         <v>4401</v>
@@ -8547,7 +8547,7 @@
         <v>1.88699996471405</v>
       </c>
       <c r="G282" t="n">
-        <v>1.54621028900146</v>
+        <v>1.54621040821075</v>
       </c>
       <c r="H282" t="n">
         <v>3939</v>
@@ -8576,7 +8576,7 @@
         <v>1.90100002288818</v>
       </c>
       <c r="G283" t="n">
-        <v>1.55768203735352</v>
+        <v>1.55768191814423</v>
       </c>
       <c r="H283" t="n">
         <v>371</v>
@@ -8663,7 +8663,7 @@
         <v>1.87300002574921</v>
       </c>
       <c r="G286" t="n">
-        <v>1.5347386598587</v>
+        <v>1.53473877906799</v>
       </c>
       <c r="H286" t="n">
         <v>168</v>
@@ -8721,7 +8721,7 @@
         <v>1.88699996471405</v>
       </c>
       <c r="G288" t="n">
-        <v>1.54621028900146</v>
+        <v>1.54621040821075</v>
       </c>
       <c r="H288" t="n">
         <v>1302</v>
@@ -8779,7 +8779,7 @@
         <v>1.88800001144409</v>
       </c>
       <c r="G290" t="n">
-        <v>1.54702973365784</v>
+        <v>1.54702961444855</v>
       </c>
       <c r="H290" t="n">
         <v>3926</v>
@@ -8808,7 +8808,7 @@
         <v>1.88800001144409</v>
       </c>
       <c r="G291" t="n">
-        <v>1.54702973365784</v>
+        <v>1.54702961444855</v>
       </c>
       <c r="H291" t="n">
         <v>0</v>
@@ -8837,7 +8837,7 @@
         <v>1.87800002098083</v>
       </c>
       <c r="G292" t="n">
-        <v>1.53883564472198</v>
+        <v>1.53883576393127</v>
       </c>
       <c r="H292" t="n">
         <v>1219</v>
@@ -8924,7 +8924,7 @@
         <v>1.88900005817413</v>
       </c>
       <c r="G295" t="n">
-        <v>1.5478492975235</v>
+        <v>1.54784917831421</v>
       </c>
       <c r="H295" t="n">
         <v>658</v>
@@ -8953,7 +8953,7 @@
         <v>1.88900005817413</v>
       </c>
       <c r="G296" t="n">
-        <v>1.5478492975235</v>
+        <v>1.54784917831421</v>
       </c>
       <c r="H296" t="n">
         <v>0</v>
@@ -9040,7 +9040,7 @@
         <v>1.89100003242493</v>
       </c>
       <c r="G299" t="n">
-        <v>1.54948806762695</v>
+        <v>1.54948794841766</v>
       </c>
       <c r="H299" t="n">
         <v>50</v>
@@ -9127,7 +9127,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G302" t="n">
-        <v>1.548668384552</v>
+        <v>1.54866850376129</v>
       </c>
       <c r="H302" t="n">
         <v>18974</v>
@@ -9156,7 +9156,7 @@
         <v>1.89100003242493</v>
       </c>
       <c r="G303" t="n">
-        <v>1.54948806762695</v>
+        <v>1.54948794841766</v>
       </c>
       <c r="H303" t="n">
         <v>4699</v>
@@ -9185,7 +9185,7 @@
         <v>1.875</v>
       </c>
       <c r="G304" t="n">
-        <v>1.53637742996216</v>
+        <v>1.53637754917145</v>
       </c>
       <c r="H304" t="n">
         <v>4192</v>
@@ -9243,7 +9243,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G306" t="n">
-        <v>1.548668384552</v>
+        <v>1.54866850376129</v>
       </c>
       <c r="H306" t="n">
         <v>3292</v>
@@ -9359,7 +9359,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G310" t="n">
-        <v>1.63060867786407</v>
+        <v>1.63060879707336</v>
       </c>
       <c r="H310" t="n">
         <v>16096</v>
@@ -9388,7 +9388,7 @@
         <v>2.01600003242493</v>
       </c>
       <c r="G311" t="n">
-        <v>1.65191316604614</v>
+        <v>1.65191304683685</v>
       </c>
       <c r="H311" t="n">
         <v>43485</v>
@@ -9417,7 +9417,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G312" t="n">
-        <v>1.64699673652649</v>
+        <v>1.6469966173172</v>
       </c>
       <c r="H312" t="n">
         <v>18453</v>
@@ -9446,7 +9446,7 @@
         <v>2.06599998474121</v>
       </c>
       <c r="G313" t="n">
-        <v>1.69288337230682</v>
+        <v>1.69288313388824</v>
       </c>
       <c r="H313" t="n">
         <v>12262</v>
@@ -9562,7 +9562,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G317" t="n">
-        <v>1.66338467597961</v>
+        <v>1.6633847951889</v>
       </c>
       <c r="H317" t="n">
         <v>4273</v>
@@ -9591,7 +9591,7 @@
         <v>2.29800009727478</v>
       </c>
       <c r="G318" t="n">
-        <v>1.88298416137695</v>
+        <v>1.88298428058624</v>
       </c>
       <c r="H318" t="n">
         <v>94367</v>
@@ -9620,7 +9620,7 @@
         <v>2.22199988365173</v>
       </c>
       <c r="G319" t="n">
-        <v>1.82070958614349</v>
+        <v>1.82070970535278</v>
       </c>
       <c r="H319" t="n">
         <v>37358</v>
@@ -9649,7 +9649,7 @@
         <v>2.23200011253357</v>
       </c>
       <c r="G320" t="n">
-        <v>1.82890379428864</v>
+        <v>1.82890391349792</v>
       </c>
       <c r="H320" t="n">
         <v>71318</v>
@@ -9678,7 +9678,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G321" t="n">
-        <v>1.78629505634308</v>
+        <v>1.7862948179245</v>
       </c>
       <c r="H321" t="n">
         <v>16351</v>
@@ -9707,7 +9707,7 @@
         <v>2.21799993515015</v>
       </c>
       <c r="G322" t="n">
-        <v>1.81743228435516</v>
+        <v>1.81743216514587</v>
       </c>
       <c r="H322" t="n">
         <v>3920</v>
@@ -9736,7 +9736,7 @@
         <v>2.21600008010864</v>
       </c>
       <c r="G323" t="n">
-        <v>1.81579339504242</v>
+        <v>1.81579327583313</v>
       </c>
       <c r="H323" t="n">
         <v>40297</v>
@@ -9794,7 +9794,7 @@
         <v>2.29399991035461</v>
       </c>
       <c r="G325" t="n">
-        <v>1.87970662117004</v>
+        <v>1.87970674037933</v>
       </c>
       <c r="H325" t="n">
         <v>82545</v>
@@ -9823,7 +9823,7 @@
         <v>2.24799990653992</v>
       </c>
       <c r="G326" t="n">
-        <v>1.84201419353485</v>
+        <v>1.84201407432556</v>
       </c>
       <c r="H326" t="n">
         <v>15070</v>
@@ -9881,7 +9881,7 @@
         <v>2.19799995422363</v>
       </c>
       <c r="G328" t="n">
-        <v>1.80104434490204</v>
+        <v>1.80104422569275</v>
       </c>
       <c r="H328" t="n">
         <v>10476</v>
@@ -9939,7 +9939,7 @@
         <v>2.21600008010864</v>
       </c>
       <c r="G330" t="n">
-        <v>1.81579339504242</v>
+        <v>1.81579327583313</v>
       </c>
       <c r="H330" t="n">
         <v>2603</v>
@@ -9968,7 +9968,7 @@
         <v>2.19799995422363</v>
       </c>
       <c r="G331" t="n">
-        <v>1.80104434490204</v>
+        <v>1.80104422569275</v>
       </c>
       <c r="H331" t="n">
         <v>14355</v>
@@ -10055,7 +10055,7 @@
         <v>2.13199996948242</v>
       </c>
       <c r="G334" t="n">
-        <v>1.74696350097656</v>
+        <v>1.74696362018585</v>
       </c>
       <c r="H334" t="n">
         <v>2476</v>
@@ -10200,7 +10200,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G339" t="n">
-        <v>1.83545899391174</v>
+        <v>1.83545923233032</v>
       </c>
       <c r="H339" t="n">
         <v>10440</v>
@@ -10229,7 +10229,7 @@
         <v>2.25399994850159</v>
       </c>
       <c r="G340" t="n">
-        <v>1.8469306230545</v>
+        <v>1.84693050384521</v>
       </c>
       <c r="H340" t="n">
         <v>14315</v>
@@ -10258,7 +10258,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G341" t="n">
-        <v>1.81087708473206</v>
+        <v>1.81087684631348</v>
       </c>
       <c r="H341" t="n">
         <v>19150</v>
@@ -10287,7 +10287,7 @@
         <v>2.20799994468689</v>
       </c>
       <c r="G342" t="n">
-        <v>1.80923795700073</v>
+        <v>1.80923819541931</v>
       </c>
       <c r="H342" t="n">
         <v>10083</v>
@@ -10316,7 +10316,7 @@
         <v>2.21199989318848</v>
       </c>
       <c r="G343" t="n">
-        <v>1.81251561641693</v>
+        <v>1.81251573562622</v>
       </c>
       <c r="H343" t="n">
         <v>17654</v>
@@ -10374,7 +10374,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G345" t="n">
-        <v>1.83545899391174</v>
+        <v>1.83545923233032</v>
       </c>
       <c r="H345" t="n">
         <v>20200</v>
@@ -10403,7 +10403,7 @@
         <v>2.27600002288818</v>
       </c>
       <c r="G346" t="n">
-        <v>1.86495757102966</v>
+        <v>1.86495745182037</v>
       </c>
       <c r="H346" t="n">
         <v>12118</v>
@@ -10432,7 +10432,7 @@
         <v>2.26799988746643</v>
       </c>
       <c r="G347" t="n">
-        <v>1.85840213298798</v>
+        <v>1.8584018945694</v>
       </c>
       <c r="H347" t="n">
         <v>10030</v>
@@ -10577,7 +10577,7 @@
         <v>2.25600004196167</v>
       </c>
       <c r="G352" t="n">
-        <v>1.84856963157654</v>
+        <v>1.84856951236725</v>
       </c>
       <c r="H352" t="n">
         <v>9093</v>
@@ -10606,7 +10606,7 @@
         <v>2.27600002288818</v>
       </c>
       <c r="G353" t="n">
-        <v>1.86495757102966</v>
+        <v>1.86495745182037</v>
       </c>
       <c r="H353" t="n">
         <v>5451</v>
@@ -10635,7 +10635,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G354" t="n">
-        <v>1.86823523044586</v>
+        <v>1.86823511123657</v>
       </c>
       <c r="H354" t="n">
         <v>9851</v>
@@ -10664,7 +10664,7 @@
         <v>2.24600005149841</v>
       </c>
       <c r="G355" t="n">
-        <v>1.92479622364044</v>
+        <v>1.92479658126831</v>
       </c>
       <c r="H355" t="n">
         <v>11951</v>
@@ -10693,7 +10693,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G356" t="n">
-        <v>1.93679416179657</v>
+        <v>1.93679404258728</v>
       </c>
       <c r="H356" t="n">
         <v>8052</v>
@@ -10722,7 +10722,7 @@
         <v>2.26200008392334</v>
       </c>
       <c r="G357" t="n">
-        <v>1.93850815296173</v>
+        <v>1.93850827217102</v>
       </c>
       <c r="H357" t="n">
         <v>47650</v>
@@ -10809,7 +10809,7 @@
         <v>2.25</v>
       </c>
       <c r="G360" t="n">
-        <v>1.92822432518005</v>
+        <v>1.92822444438934</v>
       </c>
       <c r="H360" t="n">
         <v>25228</v>
@@ -10838,7 +10838,7 @@
         <v>2.26600003242493</v>
       </c>
       <c r="G361" t="n">
-        <v>1.94193625450134</v>
+        <v>1.94193613529205</v>
       </c>
       <c r="H361" t="n">
         <v>10334</v>
@@ -10867,7 +10867,7 @@
         <v>2.26799988746643</v>
       </c>
       <c r="G362" t="n">
-        <v>1.94365000724792</v>
+        <v>1.94364976882935</v>
       </c>
       <c r="H362" t="n">
         <v>9505</v>
@@ -10954,7 +10954,7 @@
         <v>2.2960000038147</v>
       </c>
       <c r="G365" t="n">
-        <v>1.96764576435089</v>
+        <v>1.9676456451416</v>
       </c>
       <c r="H365" t="n">
         <v>6191</v>
@@ -10983,7 +10983,7 @@
         <v>2.25</v>
       </c>
       <c r="G366" t="n">
-        <v>1.92822432518005</v>
+        <v>1.92822444438934</v>
       </c>
       <c r="H366" t="n">
         <v>799</v>
@@ -11012,7 +11012,7 @@
         <v>2.24799990653992</v>
       </c>
       <c r="G367" t="n">
-        <v>1.92651033401489</v>
+        <v>1.92651009559631</v>
       </c>
       <c r="H367" t="n">
         <v>1585</v>
@@ -11041,7 +11041,7 @@
         <v>2.24799990653992</v>
       </c>
       <c r="G368" t="n">
-        <v>1.92651033401489</v>
+        <v>1.92651009559631</v>
       </c>
       <c r="H368" t="n">
         <v>0</v>
@@ -11070,7 +11070,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G369" t="n">
-        <v>1.95393407344818</v>
+        <v>1.95393395423889</v>
       </c>
       <c r="H369" t="n">
         <v>20269</v>
@@ -11099,7 +11099,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G370" t="n">
-        <v>1.95393407344818</v>
+        <v>1.95393395423889</v>
       </c>
       <c r="H370" t="n">
         <v>0</v>
@@ -11128,7 +11128,7 @@
         <v>2.25600004196167</v>
       </c>
       <c r="G371" t="n">
-        <v>1.93336641788483</v>
+        <v>1.93336629867554</v>
       </c>
       <c r="H371" t="n">
         <v>4289</v>
@@ -11215,7 +11215,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G374" t="n">
-        <v>1.8939448595047</v>
+        <v>1.89394462108612</v>
       </c>
       <c r="H374" t="n">
         <v>3200</v>
@@ -11244,7 +11244,7 @@
         <v>2.18400001525879</v>
       </c>
       <c r="G375" t="n">
-        <v>1.8716629743576</v>
+        <v>1.87166309356689</v>
       </c>
       <c r="H375" t="n">
         <v>10669</v>
@@ -11273,7 +11273,7 @@
         <v>2.25200009346008</v>
       </c>
       <c r="G376" t="n">
-        <v>1.92993831634521</v>
+        <v>1.92993819713593</v>
       </c>
       <c r="H376" t="n">
         <v>2547</v>
@@ -11302,7 +11302,7 @@
         <v>2.21799993515015</v>
       </c>
       <c r="G377" t="n">
-        <v>1.90080070495605</v>
+        <v>1.90080058574677</v>
       </c>
       <c r="H377" t="n">
         <v>500</v>
@@ -11331,7 +11331,7 @@
         <v>2.23399996757507</v>
       </c>
       <c r="G378" t="n">
-        <v>1.91451251506805</v>
+        <v>1.91451263427734</v>
       </c>
       <c r="H378" t="n">
         <v>12050</v>
@@ -11505,7 +11505,7 @@
         <v>2.2039999961853</v>
       </c>
       <c r="G384" t="n">
-        <v>1.88880288600922</v>
+        <v>1.88880276679993</v>
       </c>
       <c r="H384" t="n">
         <v>6700</v>
@@ -11534,7 +11534,7 @@
         <v>2.2279999256134</v>
       </c>
       <c r="G385" t="n">
-        <v>1.90937054157257</v>
+        <v>1.90937066078186</v>
       </c>
       <c r="H385" t="n">
         <v>9416</v>
@@ -11563,7 +11563,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G386" t="n">
-        <v>1.90251457691193</v>
+        <v>1.90251481533051</v>
       </c>
       <c r="H386" t="n">
         <v>12328</v>
@@ -11592,7 +11592,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G387" t="n">
-        <v>1.8939448595047</v>
+        <v>1.89394462108612</v>
       </c>
       <c r="H387" t="n">
         <v>391</v>
@@ -11621,7 +11621,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G388" t="n">
-        <v>1.8939448595047</v>
+        <v>1.89394462108612</v>
       </c>
       <c r="H388" t="n">
         <v>0</v>
@@ -11650,7 +11650,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G389" t="n">
-        <v>1.8939448595047</v>
+        <v>1.89394462108612</v>
       </c>
       <c r="H389" t="n">
         <v>3804</v>
@@ -11679,7 +11679,7 @@
         <v>2.23399996757507</v>
       </c>
       <c r="G390" t="n">
-        <v>1.91451251506805</v>
+        <v>1.91451263427734</v>
       </c>
       <c r="H390" t="n">
         <v>7104</v>
@@ -11737,7 +11737,7 @@
         <v>2.25600004196167</v>
       </c>
       <c r="G392" t="n">
-        <v>1.93336641788483</v>
+        <v>1.93336629867554</v>
       </c>
       <c r="H392" t="n">
         <v>4625</v>
@@ -11766,7 +11766,7 @@
         <v>2.2960000038147</v>
       </c>
       <c r="G393" t="n">
-        <v>1.96764576435089</v>
+        <v>1.9676456451416</v>
       </c>
       <c r="H393" t="n">
         <v>11250</v>
@@ -11795,7 +11795,7 @@
         <v>2.29200005531311</v>
       </c>
       <c r="G394" t="n">
-        <v>1.96421790122986</v>
+        <v>1.96421778202057</v>
       </c>
       <c r="H394" t="n">
         <v>3374</v>
@@ -11882,7 +11882,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G397" t="n">
-        <v>1.98821353912354</v>
+        <v>1.98821341991425</v>
       </c>
       <c r="H397" t="n">
         <v>4950</v>
@@ -11911,7 +11911,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G398" t="n">
-        <v>1.98821353912354</v>
+        <v>1.98821341991425</v>
       </c>
       <c r="H398" t="n">
         <v>1201</v>
@@ -11969,7 +11969,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G400" t="n">
-        <v>1.97964346408844</v>
+        <v>1.97964358329773</v>
       </c>
       <c r="H400" t="n">
         <v>5628</v>
@@ -11998,7 +11998,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G401" t="n">
-        <v>1.97964346408844</v>
+        <v>1.97964358329773</v>
       </c>
       <c r="H401" t="n">
         <v>0</v>
@@ -12027,7 +12027,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G402" t="n">
-        <v>2.12533164024353</v>
+        <v>2.12533140182495</v>
       </c>
       <c r="H402" t="n">
         <v>107928</v>
@@ -12085,7 +12085,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G404" t="n">
-        <v>2.0567729473114</v>
+        <v>2.05677247047424</v>
       </c>
       <c r="H404" t="n">
         <v>20365</v>
@@ -12143,7 +12143,7 @@
         <v>2.42799997329712</v>
       </c>
       <c r="G406" t="n">
-        <v>2.0807683467865</v>
+        <v>2.08076810836792</v>
       </c>
       <c r="H406" t="n">
         <v>5713</v>
@@ -12317,7 +12317,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G412" t="n">
-        <v>2.12533164024353</v>
+        <v>2.12533140182495</v>
       </c>
       <c r="H412" t="n">
         <v>13189</v>
@@ -12346,7 +12346,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G413" t="n">
-        <v>2.13390159606934</v>
+        <v>2.13390135765076</v>
       </c>
       <c r="H413" t="n">
         <v>51781</v>
@@ -12375,7 +12375,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G414" t="n">
-        <v>2.10819172859192</v>
+        <v>2.1081919670105</v>
       </c>
       <c r="H414" t="n">
         <v>12585</v>
@@ -12404,7 +12404,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G415" t="n">
-        <v>2.09962177276611</v>
+        <v>2.09962201118469</v>
       </c>
       <c r="H415" t="n">
         <v>3641</v>
@@ -12433,7 +12433,7 @@
         <v>2.4539999961853</v>
       </c>
       <c r="G416" t="n">
-        <v>2.10304975509644</v>
+        <v>2.10304999351501</v>
       </c>
       <c r="H416" t="n">
         <v>4434</v>
@@ -12462,7 +12462,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G417" t="n">
-        <v>2.03963279724121</v>
+        <v>2.03963303565979</v>
       </c>
       <c r="H417" t="n">
         <v>6304</v>
@@ -12578,7 +12578,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G421" t="n">
-        <v>2.07391238212585</v>
+        <v>2.07391214370728</v>
       </c>
       <c r="H421" t="n">
         <v>13845</v>
@@ -12665,7 +12665,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G424" t="n">
-        <v>2.07391238212585</v>
+        <v>2.07391214370728</v>
       </c>
       <c r="H424" t="n">
         <v>2466</v>
@@ -12694,7 +12694,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G425" t="n">
-        <v>2.09962177276611</v>
+        <v>2.09962201118469</v>
       </c>
       <c r="H425" t="n">
         <v>5724</v>
@@ -12723,7 +12723,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G426" t="n">
-        <v>2.08248209953308</v>
+        <v>2.08248233795166</v>
       </c>
       <c r="H426" t="n">
         <v>2302</v>
@@ -12781,7 +12781,7 @@
         <v>2.41199994087219</v>
       </c>
       <c r="G428" t="n">
-        <v>2.06705641746521</v>
+        <v>2.06705617904663</v>
       </c>
       <c r="H428" t="n">
         <v>650</v>
@@ -12810,7 +12810,7 @@
         <v>2.4760000705719</v>
       </c>
       <c r="G429" t="n">
-        <v>2.12190389633179</v>
+        <v>2.12190365791321</v>
       </c>
       <c r="H429" t="n">
         <v>2150</v>
@@ -12897,7 +12897,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G432" t="n">
-        <v>2.10819172859192</v>
+        <v>2.1081919670105</v>
       </c>
       <c r="H432" t="n">
         <v>150</v>
@@ -12926,7 +12926,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G433" t="n">
-        <v>2.09962177276611</v>
+        <v>2.09962201118469</v>
       </c>
       <c r="H433" t="n">
         <v>1120</v>
@@ -12955,7 +12955,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G434" t="n">
-        <v>2.13390159606934</v>
+        <v>2.13390135765076</v>
       </c>
       <c r="H434" t="n">
         <v>13299</v>
@@ -13013,7 +13013,7 @@
         <v>2.39400005340576</v>
       </c>
       <c r="G436" t="n">
-        <v>2.05163073539734</v>
+        <v>2.05163049697876</v>
       </c>
       <c r="H436" t="n">
         <v>6502</v>
@@ -13071,7 +13071,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G438" t="n">
-        <v>2.08248209953308</v>
+        <v>2.08248233795166</v>
       </c>
       <c r="H438" t="n">
         <v>13950</v>
@@ -13129,7 +13129,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G440" t="n">
-        <v>2.17675113677979</v>
+        <v>2.17675089836121</v>
       </c>
       <c r="H440" t="n">
         <v>17588</v>
@@ -13216,7 +13216,7 @@
         <v>2.48600006103516</v>
       </c>
       <c r="G443" t="n">
-        <v>2.13047385215759</v>
+        <v>2.13047361373901</v>
       </c>
       <c r="H443" t="n">
         <v>8200</v>
@@ -13274,7 +13274,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G445" t="n">
-        <v>2.15961098670959</v>
+        <v>2.15961122512817</v>
       </c>
       <c r="H445" t="n">
         <v>3123</v>
@@ -13303,7 +13303,7 @@
         <v>2.47199988365173</v>
       </c>
       <c r="G446" t="n">
-        <v>2.11847567558289</v>
+        <v>2.11847591400146</v>
       </c>
       <c r="H446" t="n">
         <v>7321</v>
@@ -13390,7 +13390,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G449" t="n">
-        <v>2.09962177276611</v>
+        <v>2.09962201118469</v>
       </c>
       <c r="H449" t="n">
         <v>450</v>
@@ -13419,7 +13419,7 @@
         <v>2.4779999256134</v>
       </c>
       <c r="G450" t="n">
-        <v>2.12361764907837</v>
+        <v>2.12361788749695</v>
       </c>
       <c r="H450" t="n">
         <v>13080</v>
@@ -13535,7 +13535,7 @@
         <v>2.4539999961853</v>
       </c>
       <c r="G454" t="n">
-        <v>2.10304975509644</v>
+        <v>2.10304999351501</v>
       </c>
       <c r="H454" t="n">
         <v>7892</v>
@@ -13593,7 +13593,7 @@
         <v>2.4779999256134</v>
       </c>
       <c r="G456" t="n">
-        <v>2.12361764907837</v>
+        <v>2.12361788749695</v>
       </c>
       <c r="H456" t="n">
         <v>1700</v>
@@ -13825,7 +13825,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G464" t="n">
-        <v>2.13390159606934</v>
+        <v>2.13390135765076</v>
       </c>
       <c r="H464" t="n">
         <v>2100</v>
@@ -13854,7 +13854,7 @@
         <v>2.50799989700317</v>
       </c>
       <c r="G465" t="n">
-        <v>2.14932703971863</v>
+        <v>2.14932727813721</v>
       </c>
       <c r="H465" t="n">
         <v>747</v>
@@ -13999,7 +13999,7 @@
         <v>2.4760000705719</v>
       </c>
       <c r="G470" t="n">
-        <v>2.12190389633179</v>
+        <v>2.12190365791321</v>
       </c>
       <c r="H470" t="n">
         <v>8809</v>
@@ -14057,7 +14057,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G472" t="n">
-        <v>2.12533164024353</v>
+        <v>2.12533140182495</v>
       </c>
       <c r="H472" t="n">
         <v>8551</v>
@@ -14115,7 +14115,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G474" t="n">
-        <v>2.15104150772095</v>
+        <v>2.15104126930237</v>
       </c>
       <c r="H474" t="n">
         <v>6956</v>
@@ -14173,7 +14173,7 @@
         <v>2.47399997711182</v>
       </c>
       <c r="G476" t="n">
-        <v>2.12018966674805</v>
+        <v>2.12018942832947</v>
       </c>
       <c r="H476" t="n">
         <v>944</v>
@@ -14202,7 +14202,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G477" t="n">
-        <v>2.09962177276611</v>
+        <v>2.09962201118469</v>
       </c>
       <c r="H477" t="n">
         <v>893</v>
@@ -14289,7 +14289,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G480" t="n">
-        <v>2.0567729473114</v>
+        <v>2.05677247047424</v>
       </c>
       <c r="H480" t="n">
         <v>6507</v>
@@ -14637,7 +14637,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G492" t="n">
-        <v>2.12533164024353</v>
+        <v>2.12533140182495</v>
       </c>
       <c r="H492" t="n">
         <v>182</v>
@@ -14695,7 +14695,7 @@
         <v>2.48399996757507</v>
       </c>
       <c r="G494" t="n">
-        <v>2.12875938415527</v>
+        <v>2.12875986099243</v>
       </c>
       <c r="H494" t="n">
         <v>150</v>
@@ -14724,7 +14724,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G495" t="n">
-        <v>2.12533164024353</v>
+        <v>2.12533140182495</v>
       </c>
       <c r="H495" t="n">
         <v>1145</v>
@@ -14869,7 +14869,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G500" t="n">
-        <v>2.08248209953308</v>
+        <v>2.08248233795166</v>
       </c>
       <c r="H500" t="n">
         <v>6624</v>
@@ -14898,7 +14898,7 @@
         <v>2.43600010871887</v>
       </c>
       <c r="G501" t="n">
-        <v>2.08762407302856</v>
+        <v>2.08762431144714</v>
       </c>
       <c r="H501" t="n">
         <v>2450</v>
@@ -14927,7 +14927,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G502" t="n">
-        <v>2.03963279724121</v>
+        <v>2.03963303565979</v>
       </c>
       <c r="H502" t="n">
         <v>6495</v>
@@ -14956,7 +14956,7 @@
         <v>2.35800004005432</v>
       </c>
       <c r="G503" t="n">
-        <v>2.0207793712616</v>
+        <v>2.02077913284302</v>
       </c>
       <c r="H503" t="n">
         <v>2564</v>
@@ -15014,7 +15014,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G505" t="n">
-        <v>2.08248209953308</v>
+        <v>2.08248233795166</v>
       </c>
       <c r="H505" t="n">
         <v>608</v>
@@ -15072,7 +15072,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G507" t="n">
-        <v>2.09962177276611</v>
+        <v>2.09962201118469</v>
       </c>
       <c r="H507" t="n">
         <v>2401</v>
@@ -15159,7 +15159,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G510" t="n">
-        <v>2.09962177276611</v>
+        <v>2.09962201118469</v>
       </c>
       <c r="H510" t="n">
         <v>370</v>
@@ -15217,7 +15217,7 @@
         <v>2.4760000705719</v>
       </c>
       <c r="G512" t="n">
-        <v>2.12190389633179</v>
+        <v>2.12190365791321</v>
       </c>
       <c r="H512" t="n">
         <v>1515</v>
@@ -15246,7 +15246,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G513" t="n">
-        <v>2.09962177276611</v>
+        <v>2.09962201118469</v>
       </c>
       <c r="H513" t="n">
         <v>8107</v>
@@ -15275,7 +15275,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G514" t="n">
-        <v>2.07391238212585</v>
+        <v>2.07391214370728</v>
       </c>
       <c r="H514" t="n">
         <v>7736</v>
@@ -15304,7 +15304,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G515" t="n">
-        <v>2.0567729473114</v>
+        <v>2.05677247047424</v>
       </c>
       <c r="H515" t="n">
         <v>7000</v>
@@ -15333,7 +15333,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G516" t="n">
-        <v>2.08248209953308</v>
+        <v>2.08248233795166</v>
       </c>
       <c r="H516" t="n">
         <v>1125</v>
@@ -15420,7 +15420,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G519" t="n">
-        <v>2.08248209953308</v>
+        <v>2.08248233795166</v>
       </c>
       <c r="H519" t="n">
         <v>8541</v>
@@ -15449,7 +15449,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G520" t="n">
-        <v>2.08248209953308</v>
+        <v>2.08248233795166</v>
       </c>
       <c r="H520" t="n">
         <v>321</v>
@@ -15478,7 +15478,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G521" t="n">
-        <v>2.03963279724121</v>
+        <v>2.03963303565979</v>
       </c>
       <c r="H521" t="n">
         <v>2339</v>
@@ -15507,7 +15507,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G522" t="n">
-        <v>2.03963279724121</v>
+        <v>2.03963303565979</v>
       </c>
       <c r="H522" t="n">
         <v>5533</v>
@@ -15536,7 +15536,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G523" t="n">
-        <v>2.03963279724121</v>
+        <v>2.03963303565979</v>
       </c>
       <c r="H523" t="n">
         <v>10984</v>
@@ -15565,7 +15565,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G524" t="n">
-        <v>2.03963279724121</v>
+        <v>2.03963303565979</v>
       </c>
       <c r="H524" t="n">
         <v>22316</v>
@@ -15594,7 +15594,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G525" t="n">
-        <v>2.0567729473114</v>
+        <v>2.05677247047424</v>
       </c>
       <c r="H525" t="n">
         <v>398</v>
@@ -15623,7 +15623,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G526" t="n">
-        <v>2.0567729473114</v>
+        <v>2.05677247047424</v>
       </c>
       <c r="H526" t="n">
         <v>5700</v>
@@ -15652,7 +15652,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G527" t="n">
-        <v>2.02249264717102</v>
+        <v>2.0224928855896</v>
       </c>
       <c r="H527" t="n">
         <v>6064</v>
@@ -15681,7 +15681,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G528" t="n">
-        <v>2.02249264717102</v>
+        <v>2.0224928855896</v>
       </c>
       <c r="H528" t="n">
         <v>3718</v>
@@ -15710,7 +15710,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G529" t="n">
-        <v>2.02249264717102</v>
+        <v>2.0224928855896</v>
       </c>
       <c r="H529" t="n">
         <v>0</v>
@@ -15739,7 +15739,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G530" t="n">
-        <v>2.09962177276611</v>
+        <v>2.09962201118469</v>
       </c>
       <c r="H530" t="n">
         <v>9824</v>
@@ -15768,7 +15768,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G531" t="n">
-        <v>2.07391238212585</v>
+        <v>2.07391214370728</v>
       </c>
       <c r="H531" t="n">
         <v>7994</v>
@@ -15797,7 +15797,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G532" t="n">
-        <v>2.07391238212585</v>
+        <v>2.07391214370728</v>
       </c>
       <c r="H532" t="n">
         <v>23272</v>
@@ -15826,7 +15826,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G533" t="n">
-        <v>2.07391238212585</v>
+        <v>2.07391214370728</v>
       </c>
       <c r="H533" t="n">
         <v>0</v>
@@ -15855,7 +15855,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G534" t="n">
-        <v>2.0567729473114</v>
+        <v>2.05677247047424</v>
       </c>
       <c r="H534" t="n">
         <v>361</v>
@@ -15884,7 +15884,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G535" t="n">
-        <v>2.0567729473114</v>
+        <v>2.05677247047424</v>
       </c>
       <c r="H535" t="n">
         <v>1190</v>
@@ -16029,7 +16029,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G540" t="n">
-        <v>2.0567729473114</v>
+        <v>2.05677247047424</v>
       </c>
       <c r="H540" t="n">
         <v>910</v>
@@ -16116,7 +16116,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G543" t="n">
-        <v>2.09962177276611</v>
+        <v>2.09962201118469</v>
       </c>
       <c r="H543" t="n">
         <v>100</v>
@@ -16145,7 +16145,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G544" t="n">
-        <v>2.09962177276611</v>
+        <v>2.09962201118469</v>
       </c>
       <c r="H544" t="n">
         <v>2265</v>
@@ -16174,7 +16174,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G545" t="n">
-        <v>2.09962177276611</v>
+        <v>2.09962201118469</v>
       </c>
       <c r="H545" t="n">
         <v>0</v>
@@ -16203,7 +16203,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G546" t="n">
-        <v>2.02249264717102</v>
+        <v>2.0224928855896</v>
       </c>
       <c r="H546" t="n">
         <v>4243</v>
@@ -16232,7 +16232,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G547" t="n">
-        <v>2.08248209953308</v>
+        <v>2.08248233795166</v>
       </c>
       <c r="H547" t="n">
         <v>3430</v>
@@ -16290,7 +16290,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G549" t="n">
-        <v>2.03963279724121</v>
+        <v>2.03963303565979</v>
       </c>
       <c r="H549" t="n">
         <v>320</v>
@@ -16319,7 +16319,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G550" t="n">
-        <v>2.08248209953308</v>
+        <v>2.08248233795166</v>
       </c>
       <c r="H550" t="n">
         <v>678</v>
@@ -16348,7 +16348,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G551" t="n">
-        <v>2.03963279724121</v>
+        <v>2.03963303565979</v>
       </c>
       <c r="H551" t="n">
         <v>2684</v>
@@ -16377,7 +16377,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G552" t="n">
-        <v>2.03963279724121</v>
+        <v>2.03963303565979</v>
       </c>
       <c r="H552" t="n">
         <v>2904</v>
@@ -16406,7 +16406,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G553" t="n">
-        <v>2.08248209953308</v>
+        <v>2.08248233795166</v>
       </c>
       <c r="H553" t="n">
         <v>290</v>
@@ -16435,7 +16435,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G554" t="n">
-        <v>2.07391238212585</v>
+        <v>2.07391214370728</v>
       </c>
       <c r="H554" t="n">
         <v>1580</v>
@@ -16493,7 +16493,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G556" t="n">
-        <v>2.03963279724121</v>
+        <v>2.03963303565979</v>
       </c>
       <c r="H556" t="n">
         <v>230</v>
@@ -16551,7 +16551,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G558" t="n">
-        <v>2.10819172859192</v>
+        <v>2.1081919670105</v>
       </c>
       <c r="H558" t="n">
         <v>7260</v>
@@ -16667,7 +16667,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G562" t="n">
-        <v>2.08248209953308</v>
+        <v>2.08248233795166</v>
       </c>
       <c r="H562" t="n">
         <v>10</v>
@@ -16696,7 +16696,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G563" t="n">
-        <v>2.08248209953308</v>
+        <v>2.08248233795166</v>
       </c>
       <c r="H563" t="n">
         <v>0</v>
@@ -16725,7 +16725,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G564" t="n">
-        <v>2.10819172859192</v>
+        <v>2.1081919670105</v>
       </c>
       <c r="H564" t="n">
         <v>95554</v>
@@ -16783,7 +16783,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G566" t="n">
-        <v>2.12533164024353</v>
+        <v>2.12533140182495</v>
       </c>
       <c r="H566" t="n">
         <v>11930</v>
@@ -16812,7 +16812,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G567" t="n">
-        <v>2.10819172859192</v>
+        <v>2.1081919670105</v>
       </c>
       <c r="H567" t="n">
         <v>4589</v>
@@ -16841,7 +16841,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G568" t="n">
-        <v>2.10819172859192</v>
+        <v>2.1081919670105</v>
       </c>
       <c r="H568" t="n">
         <v>0</v>
@@ -16870,7 +16870,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G569" t="n">
-        <v>2.07391238212585</v>
+        <v>2.07391214370728</v>
       </c>
       <c r="H569" t="n">
         <v>6674</v>
@@ -16899,7 +16899,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G570" t="n">
-        <v>2.09962177276611</v>
+        <v>2.09962201118469</v>
       </c>
       <c r="H570" t="n">
         <v>1093</v>
@@ -16928,7 +16928,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G571" t="n">
-        <v>2.10819172859192</v>
+        <v>2.1081919670105</v>
       </c>
       <c r="H571" t="n">
         <v>9876</v>
@@ -17015,7 +17015,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G574" t="n">
-        <v>2.09962177276611</v>
+        <v>2.09962201118469</v>
       </c>
       <c r="H574" t="n">
         <v>7837</v>
@@ -17044,7 +17044,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G575" t="n">
-        <v>2.10819172859192</v>
+        <v>2.1081919670105</v>
       </c>
       <c r="H575" t="n">
         <v>14550</v>
@@ -17073,7 +17073,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G576" t="n">
-        <v>2.09962177276611</v>
+        <v>2.09962201118469</v>
       </c>
       <c r="H576" t="n">
         <v>7199</v>
@@ -17102,7 +17102,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G577" t="n">
-        <v>2.13390159606934</v>
+        <v>2.13390135765076</v>
       </c>
       <c r="H577" t="n">
         <v>18463</v>
@@ -17189,7 +17189,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G580" t="n">
-        <v>2.13390159606934</v>
+        <v>2.13390135765076</v>
       </c>
       <c r="H580" t="n">
         <v>5118</v>
@@ -17247,7 +17247,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G582" t="n">
-        <v>2.16818118095398</v>
+        <v>2.1681809425354</v>
       </c>
       <c r="H582" t="n">
         <v>1455</v>
@@ -17276,7 +17276,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G583" t="n">
-        <v>2.16818118095398</v>
+        <v>2.1681809425354</v>
       </c>
       <c r="H583" t="n">
         <v>2779</v>
@@ -17305,7 +17305,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G584" t="n">
-        <v>2.15961098670959</v>
+        <v>2.15961122512817</v>
       </c>
       <c r="H584" t="n">
         <v>21594</v>
@@ -17334,7 +17334,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G585" t="n">
-        <v>2.15961098670959</v>
+        <v>2.15961122512817</v>
       </c>
       <c r="H585" t="n">
         <v>4446</v>
@@ -17363,7 +17363,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G586" t="n">
-        <v>2.16818118095398</v>
+        <v>2.1681809425354</v>
       </c>
       <c r="H586" t="n">
         <v>6585</v>
@@ -17392,7 +17392,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G587" t="n">
-        <v>2.15961098670959</v>
+        <v>2.15961122512817</v>
       </c>
       <c r="H587" t="n">
         <v>17966</v>
@@ -17450,7 +17450,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G589" t="n">
-        <v>2.15961098670959</v>
+        <v>2.15961122512817</v>
       </c>
       <c r="H589" t="n">
         <v>5280</v>
@@ -17479,7 +17479,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G590" t="n">
-        <v>2.17675113677979</v>
+        <v>2.17675089836121</v>
       </c>
       <c r="H590" t="n">
         <v>47108</v>
@@ -17624,7 +17624,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G595" t="n">
-        <v>2.32243895530701</v>
+        <v>2.32243919372559</v>
       </c>
       <c r="H595" t="n">
         <v>49282</v>
@@ -17653,7 +17653,7 @@
         <v>2.75</v>
       </c>
       <c r="G596" t="n">
-        <v>2.35671830177307</v>
+        <v>2.35671854019165</v>
       </c>
       <c r="H596" t="n">
         <v>31138</v>
@@ -17682,7 +17682,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G597" t="n">
-        <v>2.44241714477539</v>
+        <v>2.44241738319397</v>
       </c>
       <c r="H597" t="n">
         <v>71018</v>
@@ -17769,7 +17769,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G600" t="n">
-        <v>2.47669696807861</v>
+        <v>2.47669720649719</v>
       </c>
       <c r="H600" t="n">
         <v>11231</v>
@@ -17885,7 +17885,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G604" t="n">
-        <v>2.57953548431396</v>
+        <v>2.57953572273254</v>
       </c>
       <c r="H604" t="n">
         <v>152006</v>
@@ -17943,7 +17943,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G606" t="n">
-        <v>2.61381530761719</v>
+        <v>2.61381506919861</v>
       </c>
       <c r="H606" t="n">
         <v>17863</v>
@@ -18146,7 +18146,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G613" t="n">
-        <v>2.52694344520569</v>
+        <v>2.52694368362427</v>
       </c>
       <c r="H613" t="n">
         <v>7434</v>
@@ -18233,7 +18233,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G616" t="n">
-        <v>2.50006127357483</v>
+        <v>2.50006103515625</v>
       </c>
       <c r="H616" t="n">
         <v>13877</v>
@@ -18407,7 +18407,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G622" t="n">
-        <v>2.54486513137817</v>
+        <v>2.54486489295959</v>
       </c>
       <c r="H622" t="n">
         <v>14707</v>
@@ -18610,7 +18610,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G629" t="n">
-        <v>2.54486513137817</v>
+        <v>2.54486489295959</v>
       </c>
       <c r="H629" t="n">
         <v>2778</v>
@@ -18668,7 +18668,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G631" t="n">
-        <v>2.53590440750122</v>
+        <v>2.53590416908264</v>
       </c>
       <c r="H631" t="n">
         <v>519</v>
@@ -18813,7 +18813,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G636" t="n">
-        <v>2.54486513137817</v>
+        <v>2.54486489295959</v>
       </c>
       <c r="H636" t="n">
         <v>3801</v>
@@ -18900,7 +18900,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G639" t="n">
-        <v>2.53590440750122</v>
+        <v>2.53590416908264</v>
       </c>
       <c r="H639" t="n">
         <v>2002</v>
@@ -18929,7 +18929,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G640" t="n">
-        <v>2.53590440750122</v>
+        <v>2.53590416908264</v>
       </c>
       <c r="H640" t="n">
         <v>1371</v>
@@ -18958,7 +18958,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G641" t="n">
-        <v>2.53590440750122</v>
+        <v>2.53590416908264</v>
       </c>
       <c r="H641" t="n">
         <v>230</v>
@@ -18987,7 +18987,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G642" t="n">
-        <v>2.53590440750122</v>
+        <v>2.53590416908264</v>
       </c>
       <c r="H642" t="n">
         <v>418</v>
@@ -19016,7 +19016,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G643" t="n">
-        <v>2.53590440750122</v>
+        <v>2.53590416908264</v>
       </c>
       <c r="H643" t="n">
         <v>0</v>
@@ -19045,7 +19045,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G644" t="n">
-        <v>2.52694344520569</v>
+        <v>2.52694368362427</v>
       </c>
       <c r="H644" t="n">
         <v>3990</v>
@@ -19074,7 +19074,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G645" t="n">
-        <v>2.53590440750122</v>
+        <v>2.53590416908264</v>
       </c>
       <c r="H645" t="n">
         <v>2500</v>
@@ -19248,7 +19248,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G651" t="n">
-        <v>2.54486513137817</v>
+        <v>2.54486489295959</v>
       </c>
       <c r="H651" t="n">
         <v>253</v>
@@ -19306,7 +19306,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G653" t="n">
-        <v>2.52694344520569</v>
+        <v>2.52694368362427</v>
       </c>
       <c r="H653" t="n">
         <v>3121</v>
@@ -19654,7 +19654,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G665" t="n">
-        <v>2.76888489723206</v>
+        <v>2.76888465881348</v>
       </c>
       <c r="H665" t="n">
         <v>3767</v>
@@ -19683,7 +19683,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G666" t="n">
-        <v>2.71512007713318</v>
+        <v>2.71512031555176</v>
       </c>
       <c r="H666" t="n">
         <v>9512</v>
@@ -19799,7 +19799,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G670" t="n">
-        <v>2.72408103942871</v>
+        <v>2.72408080101013</v>
       </c>
       <c r="H670" t="n">
         <v>3475</v>
@@ -19973,7 +19973,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G676" t="n">
-        <v>2.72408103942871</v>
+        <v>2.72408080101013</v>
       </c>
       <c r="H676" t="n">
         <v>600</v>
@@ -20089,7 +20089,7 @@
         <v>3</v>
       </c>
       <c r="G680" t="n">
-        <v>2.68823790550232</v>
+        <v>2.68823766708374</v>
       </c>
       <c r="H680" t="n">
         <v>1900</v>
@@ -20118,7 +20118,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G681" t="n">
-        <v>2.72408103942871</v>
+        <v>2.72408080101013</v>
       </c>
       <c r="H681" t="n">
         <v>5313</v>
@@ -20176,7 +20176,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G683" t="n">
-        <v>2.73304200172424</v>
+        <v>2.73304176330566</v>
       </c>
       <c r="H683" t="n">
         <v>1575</v>
@@ -20205,7 +20205,7 @@
         <v>3</v>
       </c>
       <c r="G684" t="n">
-        <v>2.68823790550232</v>
+        <v>2.68823766708374</v>
       </c>
       <c r="H684" t="n">
         <v>795</v>
@@ -20234,7 +20234,7 @@
         <v>3</v>
       </c>
       <c r="G685" t="n">
-        <v>2.68823790550232</v>
+        <v>2.68823766708374</v>
       </c>
       <c r="H685" t="n">
         <v>9614</v>
@@ -20263,7 +20263,7 @@
         <v>3</v>
       </c>
       <c r="G686" t="n">
-        <v>2.68823790550232</v>
+        <v>2.68823766708374</v>
       </c>
       <c r="H686" t="n">
         <v>669</v>
@@ -20292,7 +20292,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G687" t="n">
-        <v>2.71512007713318</v>
+        <v>2.71512031555176</v>
       </c>
       <c r="H687" t="n">
         <v>2971</v>
@@ -20350,7 +20350,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G689" t="n">
-        <v>2.71512007713318</v>
+        <v>2.71512031555176</v>
       </c>
       <c r="H689" t="n">
         <v>7369</v>
@@ -20408,7 +20408,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G691" t="n">
-        <v>2.67927718162537</v>
+        <v>2.67927694320679</v>
       </c>
       <c r="H691" t="n">
         <v>996</v>
@@ -20495,7 +20495,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G694" t="n">
-        <v>2.86745381355286</v>
+        <v>2.86745357513428</v>
       </c>
       <c r="H694" t="n">
         <v>9450</v>
@@ -20524,7 +20524,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G695" t="n">
-        <v>2.83161067962646</v>
+        <v>2.83161044120789</v>
       </c>
       <c r="H695" t="n">
         <v>10899</v>
@@ -20553,7 +20553,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G696" t="n">
-        <v>2.73304200172424</v>
+        <v>2.73304176330566</v>
       </c>
       <c r="H696" t="n">
         <v>20211</v>
@@ -20611,7 +20611,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G698" t="n">
-        <v>2.72408103942871</v>
+        <v>2.72408080101013</v>
       </c>
       <c r="H698" t="n">
         <v>5679</v>
@@ -20756,7 +20756,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G703" t="n">
-        <v>2.72408103942871</v>
+        <v>2.72408080101013</v>
       </c>
       <c r="H703" t="n">
         <v>2265</v>
@@ -20843,7 +20843,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G706" t="n">
-        <v>2.67927718162537</v>
+        <v>2.67927694320679</v>
       </c>
       <c r="H706" t="n">
         <v>6101</v>
@@ -20872,7 +20872,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G707" t="n">
-        <v>2.64343404769897</v>
+        <v>2.6434338092804</v>
       </c>
       <c r="H707" t="n">
         <v>9896</v>
@@ -20959,7 +20959,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G710" t="n">
-        <v>2.58070850372314</v>
+        <v>2.58070826530457</v>
       </c>
       <c r="H710" t="n">
         <v>9964</v>
@@ -20988,7 +20988,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G711" t="n">
-        <v>2.58070850372314</v>
+        <v>2.58070826530457</v>
       </c>
       <c r="H711" t="n">
         <v>401</v>
@@ -21162,7 +21162,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G717" t="n">
-        <v>2.58070850372314</v>
+        <v>2.58070826530457</v>
       </c>
       <c r="H717" t="n">
         <v>3201</v>
@@ -21539,7 +21539,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G730" t="n">
-        <v>2.60759091377258</v>
+        <v>2.607590675354</v>
       </c>
       <c r="H730" t="n">
         <v>5732</v>
@@ -22032,7 +22032,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G747" t="n">
-        <v>2.50006127357483</v>
+        <v>2.50006103515625</v>
       </c>
       <c r="H747" t="n">
         <v>11156</v>
@@ -22293,7 +22293,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G756" t="n">
-        <v>2.53590440750122</v>
+        <v>2.53590416908264</v>
       </c>
       <c r="H756" t="n">
         <v>50</v>
@@ -22322,7 +22322,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G757" t="n">
-        <v>2.53590440750122</v>
+        <v>2.53590416908264</v>
       </c>
       <c r="H757" t="n">
         <v>0</v>
@@ -22351,7 +22351,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G758" t="n">
-        <v>2.53590440750122</v>
+        <v>2.53590416908264</v>
       </c>
       <c r="H758" t="n">
         <v>0</v>
@@ -22496,7 +22496,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G763" t="n">
-        <v>2.53590440750122</v>
+        <v>2.53590416908264</v>
       </c>
       <c r="H763" t="n">
         <v>1110</v>
@@ -22525,7 +22525,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G764" t="n">
-        <v>2.53590440750122</v>
+        <v>2.53590416908264</v>
       </c>
       <c r="H764" t="n">
         <v>2491</v>
@@ -22554,7 +22554,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G765" t="n">
-        <v>2.60759091377258</v>
+        <v>2.607590675354</v>
       </c>
       <c r="H765" t="n">
         <v>2167</v>
@@ -22728,7 +22728,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G771" t="n">
-        <v>2.67927718162537</v>
+        <v>2.67927694320679</v>
       </c>
       <c r="H771" t="n">
         <v>2755</v>
@@ -22786,7 +22786,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G773" t="n">
-        <v>2.71512007713318</v>
+        <v>2.71512031555176</v>
       </c>
       <c r="H773" t="n">
         <v>19800</v>
@@ -22815,7 +22815,7 @@
         <v>3</v>
       </c>
       <c r="G774" t="n">
-        <v>2.68823790550232</v>
+        <v>2.68823766708374</v>
       </c>
       <c r="H774" t="n">
         <v>22062</v>
@@ -22873,7 +22873,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G776" t="n">
-        <v>2.67927718162537</v>
+        <v>2.67927694320679</v>
       </c>
       <c r="H776" t="n">
         <v>5677</v>
@@ -22931,7 +22931,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G778" t="n">
-        <v>2.81368923187256</v>
+        <v>2.81368899345398</v>
       </c>
       <c r="H778" t="n">
         <v>12625</v>
@@ -22989,7 +22989,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G780" t="n">
-        <v>2.93914031982422</v>
+        <v>2.93914008140564</v>
       </c>
       <c r="H780" t="n">
         <v>37762</v>
@@ -23018,7 +23018,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G781" t="n">
-        <v>2.87641477584839</v>
+        <v>2.87641453742981</v>
       </c>
       <c r="H781" t="n">
         <v>16941</v>
@@ -23134,7 +23134,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G785" t="n">
-        <v>2.83161067962646</v>
+        <v>2.83161044120789</v>
       </c>
       <c r="H785" t="n">
         <v>2913</v>
@@ -23279,7 +23279,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G790" t="n">
-        <v>2.76888489723206</v>
+        <v>2.76888465881348</v>
       </c>
       <c r="H790" t="n">
         <v>501</v>
@@ -23308,7 +23308,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G791" t="n">
-        <v>2.83161067962646</v>
+        <v>2.83161044120789</v>
       </c>
       <c r="H791" t="n">
         <v>3533</v>
@@ -23395,7 +23395,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G794" t="n">
-        <v>2.87641477584839</v>
+        <v>2.87641453742981</v>
       </c>
       <c r="H794" t="n">
         <v>5745</v>
@@ -23424,7 +23424,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G795" t="n">
-        <v>2.87641477584839</v>
+        <v>2.87641453742981</v>
       </c>
       <c r="H795" t="n">
         <v>10690</v>
@@ -23540,7 +23540,7 @@
         <v>3.5</v>
       </c>
       <c r="G799" t="n">
-        <v>3.13627743721008</v>
+        <v>3.13627767562866</v>
       </c>
       <c r="H799" t="n">
         <v>4784</v>
@@ -23627,7 +23627,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G802" t="n">
-        <v>3.26172852516174</v>
+        <v>3.26172876358032</v>
       </c>
       <c r="H802" t="n">
         <v>84823</v>
@@ -23743,7 +23743,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G806" t="n">
-        <v>3.29757165908813</v>
+        <v>3.29757189750671</v>
       </c>
       <c r="H806" t="n">
         <v>24295</v>
@@ -24004,7 +24004,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G815" t="n">
-        <v>3.40510106086731</v>
+        <v>3.40510129928589</v>
       </c>
       <c r="H815" t="n">
         <v>25970</v>
@@ -24062,7 +24062,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G817" t="n">
-        <v>3.3692581653595</v>
+        <v>3.36925840377808</v>
       </c>
       <c r="H817" t="n">
         <v>26326</v>
@@ -24120,7 +24120,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G819" t="n">
-        <v>3.40510106086731</v>
+        <v>3.40510129928589</v>
       </c>
       <c r="H819" t="n">
         <v>2828</v>
@@ -24149,7 +24149,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G820" t="n">
-        <v>3.37821888923645</v>
+        <v>3.37821865081787</v>
       </c>
       <c r="H820" t="n">
         <v>7703</v>
@@ -24439,7 +24439,7 @@
         <v>3.97000002861023</v>
       </c>
       <c r="G830" t="n">
-        <v>3.55743479728699</v>
+        <v>3.55743455886841</v>
       </c>
       <c r="H830" t="n">
         <v>19641</v>
@@ -24526,7 +24526,7 @@
         <v>3.9300000667572</v>
       </c>
       <c r="G833" t="n">
-        <v>3.5215916633606</v>
+        <v>3.52159142494202</v>
       </c>
       <c r="H833" t="n">
         <v>15187</v>
@@ -24613,7 +24613,7 @@
         <v>3.97000002861023</v>
       </c>
       <c r="G836" t="n">
-        <v>3.55743479728699</v>
+        <v>3.55743455886841</v>
       </c>
       <c r="H836" t="n">
         <v>10063</v>
@@ -24845,7 +24845,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G844" t="n">
-        <v>3.66496443748474</v>
+        <v>3.66496419906616</v>
       </c>
       <c r="H844" t="n">
         <v>14188</v>
@@ -24932,7 +24932,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G847" t="n">
-        <v>3.69184637069702</v>
+        <v>3.6918466091156</v>
       </c>
       <c r="H847" t="n">
         <v>15171</v>
@@ -24961,7 +24961,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G848" t="n">
-        <v>3.70976829528809</v>
+        <v>3.70976805686951</v>
       </c>
       <c r="H848" t="n">
         <v>16414</v>
@@ -25048,7 +25048,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G851" t="n">
-        <v>3.70976829528809</v>
+        <v>3.70976805686951</v>
       </c>
       <c r="H851" t="n">
         <v>3613</v>
@@ -25135,7 +25135,7 @@
         <v>4.25</v>
       </c>
       <c r="G854" t="n">
-        <v>3.80833721160889</v>
+        <v>3.80833697319031</v>
       </c>
       <c r="H854" t="n">
         <v>30581</v>
@@ -25164,7 +25164,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G855" t="n">
-        <v>3.7904155254364</v>
+        <v>3.79041528701782</v>
       </c>
       <c r="H855" t="n">
         <v>50118</v>
@@ -25193,7 +25193,7 @@
         <v>4.25</v>
       </c>
       <c r="G856" t="n">
-        <v>3.80833721160889</v>
+        <v>3.80833697319031</v>
       </c>
       <c r="H856" t="n">
         <v>29263</v>
@@ -25251,7 +25251,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G858" t="n">
-        <v>3.96067070960999</v>
+        <v>3.96067023277283</v>
       </c>
       <c r="H858" t="n">
         <v>45171</v>
@@ -80154,6 +80154,64 @@
         <v>5</v>
       </c>
       <c r="I2751" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2752">
+      <c r="A2752" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2752" s="1" t="n">
+        <v>46323.3333333333</v>
+      </c>
+      <c r="C2752" t="n">
+        <v>0.990000009536743</v>
+      </c>
+      <c r="D2752" t="n">
+        <v>0.990000009536743</v>
+      </c>
+      <c r="E2752" t="n">
+        <v>0.990000009536743</v>
+      </c>
+      <c r="F2752" t="n">
+        <v>0.990000009536743</v>
+      </c>
+      <c r="G2752" t="n">
+        <v>0.990000009536743</v>
+      </c>
+      <c r="H2752" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2752" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2753">
+      <c r="A2753" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2753" s="1" t="n">
+        <v>46324.3333333333</v>
+      </c>
+      <c r="C2753" t="n">
+        <v>0.959999978542328</v>
+      </c>
+      <c r="D2753" t="n">
+        <v>0.995000004768372</v>
+      </c>
+      <c r="E2753" t="n">
+        <v>0.959999978542328</v>
+      </c>
+      <c r="F2753" t="n">
+        <v>0.995000004768372</v>
+      </c>
+      <c r="G2753" t="n">
+        <v>0.995000004768372</v>
+      </c>
+      <c r="H2753" t="n">
+        <v>2885</v>
+      </c>
+      <c r="I2753" t="s">
         <v>9</v>
       </c>
     </row>
